--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C7F7D8-BAF5-47D8-949F-C32F6508BE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77526DD-822A-4C9A-875C-B65DCCCEBE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="20985" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="6225" yWindow="3285" windowWidth="40080" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Foglio1!$B:$B</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcOnSave="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4183" uniqueCount="1369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="1403">
   <si>
     <t>Sigla</t>
   </si>
@@ -3449,9 +3449,6 @@
     <t>kosovo, montenegro, bosnia ed erzegovina, croazia, ungheria, romania, bulgaria, macedonia del nord</t>
   </si>
   <si>
-    <t>blu, giallo, rosso, bianco</t>
-  </si>
-  <si>
     <t>guinea, liberia, mare</t>
   </si>
   <si>
@@ -3725,9 +3722,6 @@
     <t>emblema nazionale, union jack</t>
   </si>
   <si>
-    <t>mezzaluna, emblema nazionale</t>
-  </si>
-  <si>
     <t>emblema nazionale, corona</t>
   </si>
   <si>
@@ -3941,9 +3935,6 @@
     <t>*Johannesburg, *Città del Capo, Capetown</t>
   </si>
   <si>
-    <t>*Swatziland</t>
-  </si>
-  <si>
     <t>*La Paz</t>
   </si>
   <si>
@@ -4007,15 +3998,9 @@
     <t>cerchio giallo, mezzaluna gialla, stella gialla</t>
   </si>
   <si>
-    <t>mezzaluna gialla</t>
-  </si>
-  <si>
     <t>mezzaluna bianca</t>
   </si>
   <si>
-    <t>stella verde</t>
-  </si>
-  <si>
     <t>strisce orizzontali, mezzaluna gialla, stella gialla</t>
   </si>
   <si>
@@ -4058,9 +4043,6 @@
     <t>triangolo a sinistra nero, stella bianca</t>
   </si>
   <si>
-    <t>cerchio bianco, mezzaluna rossa, stella rossa</t>
-  </si>
-  <si>
     <t>stella, croce del sud, union jack</t>
   </si>
   <si>
@@ -4118,9 +4100,6 @@
     <t>Europa, Mediterraneo, Balcani</t>
   </si>
   <si>
-    <t>asia, Medio Oriente, Penisola Arabica</t>
-  </si>
-  <si>
     <t>Sud America, Ande</t>
   </si>
   <si>
@@ -4136,9 +4115,6 @@
     <t>europa, Balcani</t>
   </si>
   <si>
-    <t>Asia, Sud-Est asiatico, Penisola indocinese</t>
-  </si>
-  <si>
     <t>Sud America, Amazzonia</t>
   </si>
   <si>
@@ -4146,13 +4122,139 @@
   </si>
   <si>
     <t>europa, Mediterraneo, Balcani</t>
+  </si>
+  <si>
+    <t>rosso, nero, giallo, blu, bianco</t>
+  </si>
+  <si>
+    <t>bianco, blu, giallo</t>
+  </si>
+  <si>
+    <t>mezzaluna rossa</t>
+  </si>
+  <si>
+    <t>mezzaluna, emblema nazionale, scritta</t>
+  </si>
+  <si>
+    <t>Asia, Medio Oriente, Penisola Arabica</t>
+  </si>
+  <si>
+    <t>Asia, Sud-Est Asiatico</t>
+  </si>
+  <si>
+    <t>Asia, Sud-Est Asiatico, Penisola indocinese</t>
+  </si>
+  <si>
+    <t>Asia, medio oriente</t>
+  </si>
+  <si>
+    <t>Asia, Medio Oriente</t>
+  </si>
+  <si>
+    <t>mezzaluna gialla, stella gialla</t>
+  </si>
+  <si>
+    <t>*Malabo</t>
+  </si>
+  <si>
+    <t>Nusantara, Jacarta</t>
+  </si>
+  <si>
+    <t>arancione, verde</t>
+  </si>
+  <si>
+    <t>Kotte, Sri Jayawardenapura, Colombo</t>
+  </si>
+  <si>
+    <t>lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>lenzuolo verde</t>
+  </si>
+  <si>
+    <t>lenzuolo bianco</t>
+  </si>
+  <si>
+    <t>cerchio rosso, lenzuolo verde</t>
+  </si>
+  <si>
+    <t>cerchio blu, lenzuolo verde</t>
+  </si>
+  <si>
+    <t>stella gialla, lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>cerchio rosso, lenzuolo bianco</t>
+  </si>
+  <si>
+    <t>stella bianca, lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>stella bianca, lenzuolo blu</t>
+  </si>
+  <si>
+    <t>lenzuolo azzurro</t>
+  </si>
+  <si>
+    <t>stella gialla, lenzuolo verde</t>
+  </si>
+  <si>
+    <t>stella verde, lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>mezzaluna bianca, lenzuolo bianco</t>
+  </si>
+  <si>
+    <t>cerchio giallo, lenzuolo azzurro</t>
+  </si>
+  <si>
+    <t>stella bianca, lenzuolo azzurro</t>
+  </si>
+  <si>
+    <t>bandiera quadrata, lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>cerchio bianco, mezzaluna rossa, stella rossa, lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>mezzaluna bianca, stella bianca, lenzuolo rosso</t>
+  </si>
+  <si>
+    <t>europa, mediterraneo</t>
+  </si>
+  <si>
+    <t>stella rossa, croce di Sant'Andrea (X)</t>
+  </si>
+  <si>
+    <t>*Swaziland</t>
+  </si>
+  <si>
+    <t>Tristan</t>
+  </si>
+  <si>
+    <t>Jersey</t>
+  </si>
+  <si>
+    <t>Turks, Caicos</t>
+  </si>
+  <si>
+    <t>Trinidad, Tobago</t>
+  </si>
+  <si>
+    <t>Polinesia</t>
+  </si>
+  <si>
+    <t>S Helier</t>
+  </si>
+  <si>
+    <t>emblema nazionale, sole</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4170,6 +4272,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4240,7 +4350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4255,6 +4365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -15956,10 +16067,10 @@
         <v>925</v>
       </c>
       <c r="L1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="M1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -15991,7 +16102,7 @@
         <v>782</v>
       </c>
       <c r="L2" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
@@ -16015,10 +16126,10 @@
         <v>499</v>
       </c>
       <c r="F3" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G3" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="H3" t="s">
         <v>754</v>
@@ -16028,6 +16139,9 @@
       </c>
       <c r="J3" t="s">
         <v>780</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1375</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
@@ -16066,7 +16180,7 @@
         <v>819</v>
       </c>
       <c r="L4" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="M4" s="1">
         <v>1</v>
@@ -16102,10 +16216,10 @@
         <v>758</v>
       </c>
       <c r="J5" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L5" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M5" s="1">
         <v>2</v>
@@ -16134,10 +16248,10 @@
         <v>777</v>
       </c>
       <c r="J6" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="L6" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="M6" s="1">
         <v>2</v>
@@ -16157,10 +16271,10 @@
         <v>889</v>
       </c>
       <c r="H7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="K7" t="s">
         <v>494</v>
@@ -16189,7 +16303,7 @@
         <v>889</v>
       </c>
       <c r="H8" t="s">
-        <v>761</v>
+        <v>1361</v>
       </c>
       <c r="J8" t="s">
         <v>783</v>
@@ -16218,7 +16332,7 @@
         <v>830</v>
       </c>
       <c r="G9" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="H9" t="s">
         <v>778</v>
@@ -16227,7 +16341,10 @@
         <v>773</v>
       </c>
       <c r="J9" t="s">
-        <v>1221</v>
+        <v>1220</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1376</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
@@ -16247,7 +16364,7 @@
         <v>831</v>
       </c>
       <c r="G10" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="H10" t="s">
         <v>787</v>
@@ -16259,7 +16376,7 @@
         <v>783</v>
       </c>
       <c r="L10" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M10" s="1">
         <v>1</v>
@@ -16285,7 +16402,7 @@
         <v>766</v>
       </c>
       <c r="L11" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M11" s="1">
         <v>2</v>
@@ -16314,7 +16431,7 @@
         <v>494</v>
       </c>
       <c r="L12" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="M12" s="1">
         <v>3</v>
@@ -16337,10 +16454,10 @@
         <v>844</v>
       </c>
       <c r="H13" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J13" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="K13" t="s">
         <v>494</v>
@@ -16363,13 +16480,16 @@
         <v>845</v>
       </c>
       <c r="H14" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I14" t="s">
         <v>773</v>
       </c>
       <c r="J14" t="s">
         <v>1078</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1308</v>
       </c>
       <c r="M14" s="1">
         <v>1</v>
@@ -16395,7 +16515,7 @@
         <v>769</v>
       </c>
       <c r="L15" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
@@ -16427,7 +16547,7 @@
         <v>819</v>
       </c>
       <c r="L16" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>
@@ -16450,7 +16570,7 @@
         <v>791</v>
       </c>
       <c r="L17" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="M17" s="1">
         <v>2</v>
@@ -16473,7 +16593,7 @@
         <v>832</v>
       </c>
       <c r="G18" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="H18" t="s">
         <v>795</v>
@@ -16489,9 +16609,15 @@
       <c r="B19" t="s">
         <v>18</v>
       </c>
+      <c r="C19" t="s">
+        <v>1397</v>
+      </c>
       <c r="D19" t="s">
         <v>512</v>
       </c>
+      <c r="E19" t="s">
+        <v>1401</v>
+      </c>
       <c r="G19" t="s">
         <v>843</v>
       </c>
@@ -16502,7 +16628,7 @@
         <v>494</v>
       </c>
       <c r="L19" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="M19" s="1">
         <v>3</v>
@@ -16522,7 +16648,7 @@
         <v>833</v>
       </c>
       <c r="G20" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H20" t="s">
         <v>797</v>
@@ -16534,7 +16660,7 @@
         <v>793</v>
       </c>
       <c r="L20" t="s">
-        <v>1250</v>
+        <v>1378</v>
       </c>
       <c r="M20" s="1">
         <v>2</v>
@@ -16563,7 +16689,7 @@
         <v>799</v>
       </c>
       <c r="L21" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M21" s="1">
         <v>2</v>
@@ -16580,7 +16706,7 @@
         <v>517</v>
       </c>
       <c r="F22" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G22" t="s">
         <v>847</v>
@@ -16589,7 +16715,7 @@
         <v>800</v>
       </c>
       <c r="L22" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M22" s="1">
         <v>1</v>
@@ -16618,10 +16744,10 @@
         <v>773</v>
       </c>
       <c r="J23" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="L23" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="M23" s="1">
         <v>2</v>
@@ -16641,7 +16767,7 @@
         <v>835</v>
       </c>
       <c r="G24" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H24" t="s">
         <v>802</v>
@@ -16667,7 +16793,7 @@
         <v>776</v>
       </c>
       <c r="J25" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="K25" t="s">
         <v>494</v>
@@ -16693,7 +16819,7 @@
         <v>803</v>
       </c>
       <c r="G26" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H26" t="s">
         <v>1067</v>
@@ -16716,7 +16842,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="D27" t="s">
         <v>522</v>
@@ -16748,22 +16874,22 @@
         <v>524</v>
       </c>
       <c r="E28" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="F28" t="s">
         <v>811</v>
       </c>
       <c r="G28" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="H28" t="s">
         <v>812</v>
       </c>
       <c r="J28" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L28" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M28" s="1">
         <v>1</v>
@@ -16795,7 +16921,7 @@
         <v>494</v>
       </c>
       <c r="L29" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="M29" s="1">
         <v>3</v>
@@ -16818,7 +16944,7 @@
         <v>837</v>
       </c>
       <c r="G30" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="H30" t="s">
         <v>815</v>
@@ -16827,7 +16953,7 @@
         <v>789</v>
       </c>
       <c r="L30" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M30" s="1">
         <v>1</v>
@@ -16853,7 +16979,7 @@
         <v>814</v>
       </c>
       <c r="L31" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M31" s="1">
         <v>2</v>
@@ -16873,7 +16999,7 @@
         <v>838</v>
       </c>
       <c r="G32" t="s">
-        <v>851</v>
+        <v>1358</v>
       </c>
       <c r="H32" t="s">
         <v>817</v>
@@ -16882,10 +17008,10 @@
         <v>816</v>
       </c>
       <c r="J32" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="L32" t="s">
-        <v>1255</v>
+        <v>1379</v>
       </c>
       <c r="M32" s="1">
         <v>1</v>
@@ -16908,7 +17034,7 @@
         <v>1032</v>
       </c>
       <c r="G33" t="s">
-        <v>850</v>
+        <v>1366</v>
       </c>
       <c r="H33" t="s">
         <v>818</v>
@@ -16917,7 +17043,10 @@
         <v>776</v>
       </c>
       <c r="J33" t="s">
-        <v>1228</v>
+        <v>1364</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1363</v>
       </c>
       <c r="M33" s="1">
         <v>2</v>
@@ -16937,13 +17066,13 @@
         <v>839</v>
       </c>
       <c r="G34" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="H34" t="s">
         <v>820</v>
       </c>
       <c r="L34" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M34" s="1">
         <v>1</v>
@@ -16978,7 +17107,7 @@
         <v>789</v>
       </c>
       <c r="L35" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="M35" s="1">
         <v>2</v>
@@ -17010,7 +17139,7 @@
         <v>789</v>
       </c>
       <c r="L36" t="s">
-        <v>1308</v>
+        <v>1394</v>
       </c>
       <c r="M36" s="1">
         <v>2</v>
@@ -17033,7 +17162,7 @@
         <v>930</v>
       </c>
       <c r="G37" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H37" t="s">
         <v>854</v>
@@ -17045,7 +17174,7 @@
         <v>855</v>
       </c>
       <c r="L37" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
@@ -17071,7 +17200,7 @@
         <v>857</v>
       </c>
       <c r="G38" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H38" t="s">
         <v>858</v>
@@ -17083,7 +17212,7 @@
         <v>789</v>
       </c>
       <c r="L38" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -17112,10 +17241,10 @@
         <v>776</v>
       </c>
       <c r="J39" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="L39" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
@@ -17138,7 +17267,7 @@
         <v>859</v>
       </c>
       <c r="L40" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="M40" s="9">
         <v>2</v>
@@ -17167,7 +17296,7 @@
         <v>767</v>
       </c>
       <c r="L41" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="M41" s="1">
         <v>1</v>
@@ -17193,7 +17322,7 @@
         <v>758</v>
       </c>
       <c r="L42" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M42" s="1">
         <v>2</v>
@@ -17216,7 +17345,7 @@
         <v>866</v>
       </c>
       <c r="G43" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="H43" t="s">
         <v>767</v>
@@ -17228,7 +17357,7 @@
         <v>789</v>
       </c>
       <c r="L43" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
@@ -17263,7 +17392,7 @@
         <v>789</v>
       </c>
       <c r="L44" t="s">
-        <v>1313</v>
+        <v>1380</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
@@ -17286,10 +17415,13 @@
         <v>867</v>
       </c>
       <c r="I45" t="s">
-        <v>868</v>
+        <v>1373</v>
       </c>
       <c r="J45" t="s">
         <v>876</v>
+      </c>
+      <c r="L45" t="s">
+        <v>1377</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -17321,10 +17453,10 @@
         <v>870</v>
       </c>
       <c r="J46" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="L46" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="M46" s="1">
         <v>3</v>
@@ -17344,13 +17476,13 @@
         <v>871</v>
       </c>
       <c r="G47" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="H47" t="s">
         <v>872</v>
       </c>
       <c r="L47" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M47" s="1">
         <v>1</v>
@@ -17379,7 +17511,7 @@
         <v>819</v>
       </c>
       <c r="L48" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="M48" s="1">
         <v>2</v>
@@ -17440,7 +17572,7 @@
         <v>880</v>
       </c>
       <c r="L50" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
@@ -17477,6 +17609,9 @@
       <c r="J51" t="s">
         <v>793</v>
       </c>
+      <c r="L51" t="s">
+        <v>1377</v>
+      </c>
       <c r="M51" s="1">
         <v>1</v>
       </c>
@@ -17501,13 +17636,13 @@
         <v>966</v>
       </c>
       <c r="G52" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H52" t="s">
         <v>1068</v>
       </c>
       <c r="L52" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M52" s="1">
         <v>2</v>
@@ -17533,10 +17668,10 @@
         <v>767</v>
       </c>
       <c r="J53" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L53" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -17556,16 +17691,16 @@
         <v>968</v>
       </c>
       <c r="G54" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="H54" t="s">
         <v>785</v>
       </c>
       <c r="J54" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L54" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
@@ -17591,10 +17726,10 @@
         <v>773</v>
       </c>
       <c r="J55" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L55" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
@@ -17626,7 +17761,7 @@
         <v>494</v>
       </c>
       <c r="L56" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M56" s="1">
         <v>3</v>
@@ -17643,7 +17778,7 @@
         <v>551</v>
       </c>
       <c r="F57" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="G57" t="s">
         <v>846</v>
@@ -17681,7 +17816,7 @@
         <v>971</v>
       </c>
       <c r="L58" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="M58" s="1">
         <v>2</v>
@@ -17701,16 +17836,16 @@
         <v>893</v>
       </c>
       <c r="G59" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="H59" t="s">
         <v>872</v>
       </c>
       <c r="J59" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L59" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -17739,10 +17874,10 @@
         <v>777</v>
       </c>
       <c r="J60" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="L60" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -17771,10 +17906,10 @@
         <v>816</v>
       </c>
       <c r="J61" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L61" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M61" s="1">
         <v>2</v>
@@ -17800,7 +17935,7 @@
         <v>903</v>
       </c>
       <c r="G62" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="H62" t="s">
         <v>904</v>
@@ -17832,7 +17967,7 @@
         <v>777</v>
       </c>
       <c r="J63" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M63" s="1">
         <v>2</v>
@@ -17858,7 +17993,7 @@
         <v>908</v>
       </c>
       <c r="L64" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -17872,7 +18007,7 @@
         <v>741</v>
       </c>
       <c r="C65" t="s">
-        <v>1300</v>
+        <v>1395</v>
       </c>
       <c r="D65" t="s">
         <v>709</v>
@@ -17887,10 +18022,10 @@
         <v>914</v>
       </c>
       <c r="J65" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="L65" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M65" s="1">
         <v>2</v>
@@ -17919,10 +18054,10 @@
         <v>798</v>
       </c>
       <c r="J66" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="L66" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
@@ -17945,7 +18080,7 @@
         <v>975</v>
       </c>
       <c r="J67" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M67" s="1">
         <v>2</v>
@@ -17962,7 +18097,7 @@
         <v>561</v>
       </c>
       <c r="G68" t="s">
-        <v>850</v>
+        <v>1366</v>
       </c>
       <c r="H68" t="s">
         <v>917</v>
@@ -17971,10 +18106,10 @@
         <v>777</v>
       </c>
       <c r="J68" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="L68" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="M68" s="1">
         <v>1</v>
@@ -18026,7 +18161,7 @@
         <v>767</v>
       </c>
       <c r="L70" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M70" s="1">
         <v>1</v>
@@ -18046,13 +18181,13 @@
         <v>969</v>
       </c>
       <c r="G71" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H71" t="s">
-        <v>923</v>
+        <v>817</v>
       </c>
       <c r="L71" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M71" s="1">
         <v>2</v>
@@ -18113,7 +18248,7 @@
         <v>928</v>
       </c>
       <c r="L73" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M73" s="1">
         <v>2</v>
@@ -18133,7 +18268,7 @@
         <v>932</v>
       </c>
       <c r="G74" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H74" t="s">
         <v>795</v>
@@ -18165,10 +18300,10 @@
         <v>851</v>
       </c>
       <c r="H75" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J75" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="K75" t="s">
         <v>494</v>
@@ -18197,7 +18332,7 @@
         <v>936</v>
       </c>
       <c r="L76" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M76" s="1">
         <v>1</v>
@@ -18217,7 +18352,7 @@
         <v>970</v>
       </c>
       <c r="G77" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H77" t="s">
         <v>937</v>
@@ -18229,7 +18364,7 @@
         <v>789</v>
       </c>
       <c r="L77" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="M77" s="1">
         <v>1</v>
@@ -18243,7 +18378,7 @@
         <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="D78" t="s">
         <v>571</v>
@@ -18255,7 +18390,7 @@
         <v>938</v>
       </c>
       <c r="L78" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="M78" s="1">
         <v>1</v>
@@ -18272,7 +18407,7 @@
         <v>572</v>
       </c>
       <c r="G79" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H79" t="s">
         <v>795</v>
@@ -18284,7 +18419,7 @@
         <v>793</v>
       </c>
       <c r="L79" t="s">
-        <v>1250</v>
+        <v>1381</v>
       </c>
       <c r="M79" s="1">
         <v>1</v>
@@ -18304,7 +18439,7 @@
         <v>939</v>
       </c>
       <c r="G80" t="s">
-        <v>847</v>
+        <v>1393</v>
       </c>
       <c r="H80" t="s">
         <v>795</v>
@@ -18319,7 +18454,7 @@
         <v>494</v>
       </c>
       <c r="L80" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M80" s="1">
         <v>3</v>
@@ -18351,7 +18486,7 @@
         <v>789</v>
       </c>
       <c r="L81" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="M81" s="1">
         <v>2</v>
@@ -18371,7 +18506,7 @@
         <v>962</v>
       </c>
       <c r="G82" t="s">
-        <v>931</v>
+        <v>1368</v>
       </c>
       <c r="H82" t="s">
         <v>899</v>
@@ -18380,10 +18515,10 @@
         <v>773</v>
       </c>
       <c r="J82" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L82" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="M82" s="1">
         <v>2</v>
@@ -18403,7 +18538,7 @@
         <v>946</v>
       </c>
       <c r="G83" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="H83" t="s">
         <v>920</v>
@@ -18441,7 +18576,7 @@
         <v>880</v>
       </c>
       <c r="L84" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="M84" s="1">
         <v>2</v>
@@ -18461,7 +18596,7 @@
         <v>961</v>
       </c>
       <c r="G85" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H85" t="s">
         <v>769</v>
@@ -18493,7 +18628,7 @@
         <v>942</v>
       </c>
       <c r="J86" t="s">
-        <v>783</v>
+        <v>1402</v>
       </c>
       <c r="K86" t="s">
         <v>494</v>
@@ -18513,13 +18648,13 @@
         <v>578</v>
       </c>
       <c r="G87" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H87" t="s">
         <v>943</v>
       </c>
       <c r="J87" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="K87" t="s">
         <v>494</v>
@@ -18551,10 +18686,10 @@
         <v>787</v>
       </c>
       <c r="J88" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L88" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M88" s="1">
         <v>2</v>
@@ -18571,7 +18706,7 @@
         <v>580</v>
       </c>
       <c r="E89" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="G89" t="s">
         <v>847</v>
@@ -18609,7 +18744,7 @@
         <v>812</v>
       </c>
       <c r="L90" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M90" s="1">
         <v>2</v>
@@ -18626,22 +18761,22 @@
         <v>949</v>
       </c>
       <c r="E91" t="s">
-        <v>948</v>
+        <v>1371</v>
       </c>
       <c r="F91" t="s">
         <v>950</v>
       </c>
       <c r="G91" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H91" t="s">
         <v>951</v>
       </c>
       <c r="J91" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="L91" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M91" s="1">
         <v>2</v>
@@ -18676,7 +18811,7 @@
         <v>789</v>
       </c>
       <c r="L92" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="M92" s="1">
         <v>2</v>
@@ -18696,13 +18831,13 @@
         <v>953</v>
       </c>
       <c r="G93" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="H93" t="s">
         <v>812</v>
       </c>
       <c r="L93" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M93" s="1">
         <v>2</v>
@@ -18725,7 +18860,7 @@
         <v>956</v>
       </c>
       <c r="G94" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="H94" t="s">
         <v>957</v>
@@ -18740,7 +18875,7 @@
         <v>494</v>
       </c>
       <c r="L94" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="M94" s="1">
         <v>3</v>
@@ -18769,10 +18904,10 @@
         <v>943</v>
       </c>
       <c r="J95" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="L95" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M95" s="1">
         <v>1</v>
@@ -18804,7 +18939,7 @@
         <v>789</v>
       </c>
       <c r="L96" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="M96" s="1">
         <v>2</v>
@@ -18824,7 +18959,7 @@
         <v>976</v>
       </c>
       <c r="G97" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H97" t="s">
         <v>769</v>
@@ -18837,6 +18972,9 @@
       </c>
       <c r="K97" t="s">
         <v>494</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1382</v>
       </c>
       <c r="M97" s="1">
         <v>3</v>
@@ -18856,22 +18994,22 @@
         <v>1054</v>
       </c>
       <c r="F98" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G98" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H98" t="s">
         <v>1068</v>
       </c>
       <c r="I98" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J98" t="s">
         <v>793</v>
       </c>
       <c r="L98" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M98" s="1">
         <v>1</v>
@@ -18888,19 +19026,19 @@
         <v>588</v>
       </c>
       <c r="E99" t="s">
-        <v>1195</v>
+        <v>1372</v>
       </c>
       <c r="F99" t="s">
         <v>1033</v>
       </c>
       <c r="G99" t="s">
-        <v>850</v>
+        <v>1366</v>
       </c>
       <c r="H99" t="s">
         <v>769</v>
       </c>
       <c r="L99" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M99" s="1">
         <v>1</v>
@@ -18949,7 +19087,7 @@
         <v>979</v>
       </c>
       <c r="G101" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H101" t="s">
         <v>980</v>
@@ -18958,10 +19096,10 @@
         <v>776</v>
       </c>
       <c r="J101" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L101" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M101" s="1">
         <v>1</v>
@@ -18981,7 +19119,7 @@
         <v>981</v>
       </c>
       <c r="G102" t="s">
-        <v>958</v>
+        <v>1369</v>
       </c>
       <c r="H102" t="s">
         <v>897</v>
@@ -18993,7 +19131,7 @@
         <v>782</v>
       </c>
       <c r="L102" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M102" s="1">
         <v>1</v>
@@ -19019,7 +19157,7 @@
         <v>1069</v>
       </c>
       <c r="L103" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M103" s="1">
         <v>1</v>
@@ -19048,7 +19186,7 @@
         <v>795</v>
       </c>
       <c r="J104" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="K104" t="s">
         <v>494</v>
@@ -19108,6 +19246,9 @@
       <c r="K106" t="s">
         <v>494</v>
       </c>
+      <c r="L106" t="s">
+        <v>1375</v>
+      </c>
       <c r="M106" s="1">
         <v>3</v>
       </c>
@@ -19135,13 +19276,13 @@
         <v>778</v>
       </c>
       <c r="J107" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="K107" t="s">
         <v>494</v>
       </c>
       <c r="L107" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M107" s="1">
         <v>3</v>
@@ -19176,7 +19317,7 @@
         <v>494</v>
       </c>
       <c r="L108" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M108" s="1">
         <v>3</v>
@@ -19228,10 +19369,10 @@
         <v>889</v>
       </c>
       <c r="H110" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J110" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="K110" t="s">
         <v>494</v>
@@ -19269,7 +19410,7 @@
         <v>494</v>
       </c>
       <c r="L111" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="M111" s="1">
         <v>3</v>
@@ -19292,7 +19433,7 @@
         <v>845</v>
       </c>
       <c r="H112" t="s">
-        <v>816</v>
+        <v>1215</v>
       </c>
       <c r="I112" t="s">
         <v>773</v>
@@ -19304,7 +19445,7 @@
         <v>494</v>
       </c>
       <c r="L112" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M112" s="1">
         <v>3</v>
@@ -19327,10 +19468,10 @@
         <v>851</v>
       </c>
       <c r="H113" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J113" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="K113" t="s">
         <v>494</v>
@@ -19376,7 +19517,7 @@
         <v>108</v>
       </c>
       <c r="C115" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D115" t="s">
         <v>605</v>
@@ -19388,10 +19529,13 @@
         <v>816</v>
       </c>
       <c r="J115" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="K115" t="s">
         <v>494</v>
+      </c>
+      <c r="L115" t="s">
+        <v>1383</v>
       </c>
       <c r="M115" s="1">
         <v>3</v>
@@ -19417,7 +19561,10 @@
         <v>1070</v>
       </c>
       <c r="J116" t="s">
-        <v>783</v>
+        <v>789</v>
+      </c>
+      <c r="L116" t="s">
+        <v>1308</v>
       </c>
       <c r="M116" s="1">
         <v>2</v>
@@ -19440,10 +19587,10 @@
         <v>845</v>
       </c>
       <c r="H117" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J117" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="K117" t="s">
         <v>494</v>
@@ -19478,7 +19625,7 @@
         <v>789</v>
       </c>
       <c r="L118" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M118" s="1">
         <v>2</v>
@@ -19501,13 +19648,16 @@
         <v>889</v>
       </c>
       <c r="H119" t="s">
-        <v>994</v>
+        <v>1362</v>
       </c>
       <c r="J119" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="K119" t="s">
         <v>494</v>
+      </c>
+      <c r="L119" t="s">
+        <v>1377</v>
       </c>
       <c r="M119" s="1">
         <v>3</v>
@@ -19530,10 +19680,10 @@
         <v>889</v>
       </c>
       <c r="H120" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J120" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="K120" t="s">
         <v>494</v>
@@ -19556,19 +19706,19 @@
         <v>995</v>
       </c>
       <c r="G121" t="s">
-        <v>931</v>
+        <v>1368</v>
       </c>
       <c r="H121" t="s">
         <v>816</v>
       </c>
       <c r="I121" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J121" t="s">
         <v>789</v>
       </c>
       <c r="L121" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="M121" s="1">
         <v>1</v>
@@ -19594,7 +19744,7 @@
         <v>980</v>
       </c>
       <c r="L122" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M122" s="1">
         <v>1</v>
@@ -19614,13 +19764,16 @@
         <v>999</v>
       </c>
       <c r="G123" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H123" t="s">
         <v>1000</v>
       </c>
       <c r="J123" t="s">
         <v>1006</v>
+      </c>
+      <c r="L123" t="s">
+        <v>1384</v>
       </c>
       <c r="M123" s="1">
         <v>1</v>
@@ -19637,7 +19790,7 @@
         <v>613</v>
       </c>
       <c r="F124" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="G124" t="s">
         <v>848</v>
@@ -19646,7 +19799,10 @@
         <v>1002</v>
       </c>
       <c r="J124" t="s">
-        <v>1222</v>
+        <v>1221</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1246</v>
       </c>
       <c r="M124" s="1">
         <v>1</v>
@@ -19669,7 +19825,7 @@
         <v>1003</v>
       </c>
       <c r="G125" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H125" t="s">
         <v>865</v>
@@ -19679,6 +19835,9 @@
       </c>
       <c r="J125" t="s">
         <v>783</v>
+      </c>
+      <c r="L125" t="s">
+        <v>1375</v>
       </c>
       <c r="M125" s="1">
         <v>2</v>
@@ -19727,10 +19886,13 @@
         <v>1007</v>
       </c>
       <c r="G127" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="H127" t="s">
-        <v>815</v>
+        <v>798</v>
+      </c>
+      <c r="I127" t="s">
+        <v>1091</v>
       </c>
       <c r="J127" t="s">
         <v>1008</v>
@@ -19739,7 +19901,7 @@
         <v>494</v>
       </c>
       <c r="L127" t="s">
-        <v>1311</v>
+        <v>1383</v>
       </c>
       <c r="M127" s="1">
         <v>3</v>
@@ -19762,13 +19924,13 @@
         <v>1009</v>
       </c>
       <c r="G128" t="s">
-        <v>931</v>
+        <v>1368</v>
       </c>
       <c r="H128" t="s">
         <v>1002</v>
       </c>
       <c r="L128" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="M128" s="1">
         <v>2</v>
@@ -19788,7 +19950,7 @@
         <v>1014</v>
       </c>
       <c r="G129" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H129" t="s">
         <v>854</v>
@@ -19800,7 +19962,7 @@
         <v>793</v>
       </c>
       <c r="L129" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="M129" s="1">
         <v>2</v>
@@ -19829,7 +19991,7 @@
         <v>775</v>
       </c>
       <c r="L130" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M130" s="1">
         <v>2</v>
@@ -19855,7 +20017,7 @@
         <v>769</v>
       </c>
       <c r="L131" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M131" s="1">
         <v>1</v>
@@ -19875,7 +20037,7 @@
         <v>1017</v>
       </c>
       <c r="G132" t="s">
-        <v>931</v>
+        <v>1368</v>
       </c>
       <c r="H132" t="s">
         <v>1018</v>
@@ -19887,7 +20049,7 @@
         <v>974</v>
       </c>
       <c r="L132" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M132" s="1">
         <v>1</v>
@@ -19919,7 +20081,7 @@
         <v>789</v>
       </c>
       <c r="L133" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M133" s="1">
         <v>2</v>
@@ -19951,7 +20113,7 @@
         <v>819</v>
       </c>
       <c r="L134" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="M134" s="1">
         <v>1</v>
@@ -19983,7 +20145,7 @@
         <v>1023</v>
       </c>
       <c r="L135" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M135" s="1">
         <v>2</v>
@@ -20009,7 +20171,7 @@
         <v>808</v>
       </c>
       <c r="L136" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M136" s="1">
         <v>1</v>
@@ -20035,7 +20197,7 @@
         <v>1026</v>
       </c>
       <c r="L137" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M137" s="1">
         <v>2</v>
@@ -20055,7 +20217,7 @@
         <v>976</v>
       </c>
       <c r="G138" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H138" t="s">
         <v>778</v>
@@ -20070,7 +20232,7 @@
         <v>494</v>
       </c>
       <c r="L138" t="s">
-        <v>1313</v>
+        <v>1385</v>
       </c>
       <c r="M138" s="1">
         <v>3</v>
@@ -20093,10 +20255,10 @@
         <v>1029</v>
       </c>
       <c r="F139" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G139" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="H139" t="s">
         <v>865</v>
@@ -20154,7 +20316,7 @@
         <v>783</v>
       </c>
       <c r="L141" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M141" s="1">
         <v>2</v>
@@ -20177,7 +20339,7 @@
         <v>1048</v>
       </c>
       <c r="G142" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H142" t="s">
         <v>860</v>
@@ -20186,10 +20348,10 @@
         <v>777</v>
       </c>
       <c r="J142" t="s">
-        <v>1034</v>
+        <v>819</v>
       </c>
       <c r="L142" t="s">
-        <v>1322</v>
+        <v>1370</v>
       </c>
       <c r="M142" s="1">
         <v>1</v>
@@ -20206,7 +20368,7 @@
         <v>631</v>
       </c>
       <c r="G143" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H143" t="s">
         <v>806</v>
@@ -20218,7 +20380,7 @@
         <v>874</v>
       </c>
       <c r="L143" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="M143" s="1">
         <v>2</v>
@@ -20244,7 +20406,7 @@
         <v>802</v>
       </c>
       <c r="L144" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M144" s="1">
         <v>2</v>
@@ -20273,7 +20435,7 @@
         <v>1055</v>
       </c>
       <c r="L145" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M145" s="1">
         <v>1</v>
@@ -20305,7 +20467,7 @@
         <v>789</v>
       </c>
       <c r="L146" t="s">
-        <v>1324</v>
+        <v>1386</v>
       </c>
       <c r="M146" s="1">
         <v>1</v>
@@ -20334,7 +20496,7 @@
         <v>494</v>
       </c>
       <c r="L147" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M147" s="1">
         <v>3</v>
@@ -20369,7 +20531,7 @@
         <v>819</v>
       </c>
       <c r="L148" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="M148" s="1">
         <v>2</v>
@@ -20392,7 +20554,7 @@
         <v>1039</v>
       </c>
       <c r="L149" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M149" s="1">
         <v>2</v>
@@ -20409,7 +20571,7 @@
         <v>638</v>
       </c>
       <c r="E150" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G150" t="s">
         <v>1038</v>
@@ -20418,13 +20580,13 @@
         <v>917</v>
       </c>
       <c r="J150" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="K150" t="s">
         <v>494</v>
       </c>
       <c r="L150" t="s">
-        <v>1323</v>
+        <v>1387</v>
       </c>
       <c r="M150" s="1">
         <v>3</v>
@@ -20456,10 +20618,10 @@
         <v>980</v>
       </c>
       <c r="J151" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="L151" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M151" s="1">
         <v>1</v>
@@ -20485,10 +20647,10 @@
         <v>758</v>
       </c>
       <c r="J152" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="L152" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M152" s="1">
         <v>2</v>
@@ -20511,7 +20673,7 @@
         <v>1041</v>
       </c>
       <c r="G153" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H153" t="s">
         <v>801</v>
@@ -20520,10 +20682,10 @@
         <v>777</v>
       </c>
       <c r="J153" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L153" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M153" s="1">
         <v>2</v>
@@ -20540,10 +20702,10 @@
         <v>644</v>
       </c>
       <c r="F154" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G154" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="H154" t="s">
         <v>865</v>
@@ -20552,7 +20714,7 @@
         <v>777</v>
       </c>
       <c r="J154" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="M154" s="1">
         <v>1</v>
@@ -20575,10 +20737,10 @@
         <v>1118</v>
       </c>
       <c r="H155" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J155" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="K155" t="s">
         <v>494</v>
@@ -20607,10 +20769,10 @@
         <v>1042</v>
       </c>
       <c r="J156" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="L156" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="M156" s="1">
         <v>2</v>
@@ -20624,7 +20786,7 @@
         <v>796</v>
       </c>
       <c r="C157" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D157" t="s">
         <v>523</v>
@@ -20636,7 +20798,7 @@
         <v>836</v>
       </c>
       <c r="G157" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H157" t="s">
         <v>808</v>
@@ -20648,7 +20810,7 @@
         <v>789</v>
       </c>
       <c r="L157" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="M157" s="1">
         <v>2</v>
@@ -20709,7 +20871,7 @@
         <v>789</v>
       </c>
       <c r="L159" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M159" s="1">
         <v>2</v>
@@ -20729,7 +20891,7 @@
         <v>1062</v>
       </c>
       <c r="G160" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H160" t="s">
         <v>801</v>
@@ -20741,7 +20903,7 @@
         <v>783</v>
       </c>
       <c r="L160" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="M160" s="1">
         <v>2</v>
@@ -20767,10 +20929,10 @@
         <v>787</v>
       </c>
       <c r="J161" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="L161" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M161" s="1">
         <v>2</v>
@@ -20802,7 +20964,7 @@
         <v>793</v>
       </c>
       <c r="L162" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="M162" s="1">
         <v>1</v>
@@ -20822,13 +20984,13 @@
         <v>1071</v>
       </c>
       <c r="G163" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H163" t="s">
         <v>764</v>
       </c>
       <c r="L163" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M163" s="1">
         <v>1</v>
@@ -20859,6 +21021,9 @@
       <c r="K164" t="s">
         <v>494</v>
       </c>
+      <c r="L164" t="s">
+        <v>1310</v>
+      </c>
       <c r="M164" s="1">
         <v>3</v>
       </c>
@@ -20921,7 +21086,7 @@
         <v>494</v>
       </c>
       <c r="L166" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M166" s="1">
         <v>3</v>
@@ -20941,16 +21106,16 @@
         <v>845</v>
       </c>
       <c r="H167" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I167" t="s">
         <v>769</v>
       </c>
       <c r="J167" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="L167" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="M167" s="1">
         <v>1</v>
@@ -20967,16 +21132,16 @@
         <v>658</v>
       </c>
       <c r="F168" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="G168" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="H168" t="s">
         <v>1027</v>
       </c>
       <c r="J168" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M168" s="1">
         <v>2</v>
@@ -20990,7 +21155,7 @@
         <v>1080</v>
       </c>
       <c r="C169" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D169" t="s">
         <v>657</v>
@@ -21004,11 +21169,8 @@
       <c r="H169" t="s">
         <v>785</v>
       </c>
-      <c r="I169" t="s">
-        <v>773</v>
-      </c>
       <c r="L169" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M169" s="1">
         <v>1</v>
@@ -21028,7 +21190,7 @@
         <v>1084</v>
       </c>
       <c r="G170" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H170" t="s">
         <v>1086</v>
@@ -21040,7 +21202,7 @@
         <v>819</v>
       </c>
       <c r="L170" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="M170" s="1">
         <v>1</v>
@@ -21069,7 +21231,7 @@
         <v>793</v>
       </c>
       <c r="L171" t="s">
-        <v>1259</v>
+        <v>1388</v>
       </c>
       <c r="M171" s="1">
         <v>2</v>
@@ -21086,10 +21248,10 @@
         <v>661</v>
       </c>
       <c r="F172" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="G172" t="s">
-        <v>931</v>
+        <v>1368</v>
       </c>
       <c r="H172" t="s">
         <v>899</v>
@@ -21098,7 +21260,7 @@
         <v>494</v>
       </c>
       <c r="L172" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M172" s="1">
         <v>3</v>
@@ -21133,7 +21295,7 @@
         <v>789</v>
       </c>
       <c r="L173" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="M173" s="1">
         <v>1</v>
@@ -21168,7 +21330,7 @@
         <v>1092</v>
       </c>
       <c r="L174" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M174" s="1">
         <v>2</v>
@@ -21194,10 +21356,10 @@
         <v>785</v>
       </c>
       <c r="J175" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="L175" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M175" s="1">
         <v>2</v>
@@ -21217,13 +21379,13 @@
         <v>1094</v>
       </c>
       <c r="G176" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="H176" t="s">
         <v>769</v>
       </c>
       <c r="L176" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M176" s="1">
         <v>1</v>
@@ -21236,6 +21398,9 @@
       <c r="B177" t="s">
         <v>167</v>
       </c>
+      <c r="C177" t="s">
+        <v>1400</v>
+      </c>
       <c r="D177" t="s">
         <v>665</v>
       </c>
@@ -21246,13 +21411,13 @@
         <v>769</v>
       </c>
       <c r="J177" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="K177" t="s">
         <v>494</v>
       </c>
       <c r="L177" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M177" s="1">
         <v>3</v>
@@ -21269,7 +21434,7 @@
         <v>666</v>
       </c>
       <c r="F178" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="G178" t="s">
         <v>847</v>
@@ -21278,7 +21443,7 @@
         <v>795</v>
       </c>
       <c r="L178" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M178" s="1">
         <v>1</v>
@@ -21304,13 +21469,13 @@
         <v>773</v>
       </c>
       <c r="J179" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="K179" t="s">
         <v>494</v>
       </c>
       <c r="L179" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="M179" s="1">
         <v>3</v>
@@ -21339,7 +21504,7 @@
         <v>777</v>
       </c>
       <c r="J180" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M180" s="1">
         <v>1</v>
@@ -21353,7 +21518,7 @@
         <v>171</v>
       </c>
       <c r="C181" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D181" t="s">
         <v>669</v>
@@ -21368,7 +21533,7 @@
         <v>769</v>
       </c>
       <c r="L181" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M181" s="1">
         <v>2</v>
@@ -21388,7 +21553,7 @@
         <v>832</v>
       </c>
       <c r="G182" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="H182" t="s">
         <v>795</v>
@@ -21405,7 +21570,7 @@
         <v>173</v>
       </c>
       <c r="C183" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D183" t="s">
         <v>589</v>
@@ -21455,7 +21620,7 @@
         <v>789</v>
       </c>
       <c r="L184" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="M184" s="1">
         <v>2</v>
@@ -21490,7 +21655,7 @@
         <v>789</v>
       </c>
       <c r="L185" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="M185" s="1">
         <v>1</v>
@@ -21519,7 +21684,7 @@
         <v>767</v>
       </c>
       <c r="J186" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M186" s="1">
         <v>1</v>
@@ -21568,13 +21733,13 @@
         <v>1112</v>
       </c>
       <c r="G188" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="H188" t="s">
         <v>758</v>
       </c>
       <c r="L188" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M188" s="1">
         <v>1</v>
@@ -21606,7 +21771,7 @@
         <v>783</v>
       </c>
       <c r="L189" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M189" s="1">
         <v>2</v>
@@ -21632,7 +21797,7 @@
         <v>1116</v>
       </c>
       <c r="L190" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M190" s="1">
         <v>1</v>
@@ -21667,7 +21832,7 @@
         <v>494</v>
       </c>
       <c r="L191" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="M191" s="1">
         <v>3</v>
@@ -21699,13 +21864,13 @@
         <v>776</v>
       </c>
       <c r="J192" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K192" t="s">
         <v>494</v>
       </c>
       <c r="L192" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="M192" s="1">
         <v>3</v>
@@ -21737,7 +21902,7 @@
         <v>789</v>
       </c>
       <c r="L193" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M193" s="1">
         <v>2</v>
@@ -21765,6 +21930,9 @@
       <c r="I194" t="s">
         <v>1122</v>
       </c>
+      <c r="L194" t="s">
+        <v>1384</v>
+      </c>
       <c r="M194" s="1">
         <v>2</v>
       </c>
@@ -21777,7 +21945,7 @@
         <v>182</v>
       </c>
       <c r="C195" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D195" t="s">
         <v>682</v>
@@ -21792,7 +21960,7 @@
         <v>778</v>
       </c>
       <c r="L195" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M195" s="1">
         <v>2</v>
@@ -21818,10 +21986,13 @@
         <v>773</v>
       </c>
       <c r="J196" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="K196" t="s">
         <v>494</v>
+      </c>
+      <c r="L196" t="s">
+        <v>1377</v>
       </c>
       <c r="M196" s="1">
         <v>3</v>
@@ -21841,7 +22012,7 @@
         <v>684</v>
       </c>
       <c r="F197" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G197" t="s">
         <v>1118</v>
@@ -21853,7 +22024,7 @@
         <v>494</v>
       </c>
       <c r="L197" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M197" s="1">
         <v>3</v>
@@ -21876,7 +22047,7 @@
         <v>1134</v>
       </c>
       <c r="G198" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H198" t="s">
         <v>1132</v>
@@ -21917,7 +22088,7 @@
         <v>1076</v>
       </c>
       <c r="L199" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M199" s="1">
         <v>2</v>
@@ -21940,7 +22111,7 @@
         <v>767</v>
       </c>
       <c r="J200" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="K200" t="s">
         <v>494</v>
@@ -21957,7 +22128,7 @@
         <v>187</v>
       </c>
       <c r="C201" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="D201" t="s">
         <v>688</v>
@@ -21975,10 +22146,10 @@
         <v>920</v>
       </c>
       <c r="J201" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="L201" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M201" s="1">
         <v>2</v>
@@ -21998,10 +22169,10 @@
         <v>1038</v>
       </c>
       <c r="H202" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J202" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="K202" t="s">
         <v>494</v>
@@ -22027,7 +22198,7 @@
         <v>1131</v>
       </c>
       <c r="G203" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="H203" t="s">
         <v>802</v>
@@ -22036,10 +22207,10 @@
         <v>775</v>
       </c>
       <c r="J203" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L203" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="M203" s="1">
         <v>2</v>
@@ -22068,7 +22239,7 @@
         <v>494</v>
       </c>
       <c r="L204" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="M204" s="1">
         <v>3</v>
@@ -22085,7 +22256,7 @@
         <v>692</v>
       </c>
       <c r="F205" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="G205" t="s">
         <v>848</v>
@@ -22100,7 +22271,7 @@
         <v>789</v>
       </c>
       <c r="L205" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="M205" s="1">
         <v>1</v>
@@ -22120,16 +22291,16 @@
         <v>1135</v>
       </c>
       <c r="G206" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="H206" t="s">
         <v>854</v>
       </c>
       <c r="J206" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="L206" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M206" s="1">
         <v>1</v>
@@ -22149,7 +22320,7 @@
         <v>1038</v>
       </c>
       <c r="H207" t="s">
-        <v>1136</v>
+        <v>1284</v>
       </c>
       <c r="M207" s="1">
         <v>2</v>
@@ -22166,16 +22337,16 @@
         <v>694</v>
       </c>
       <c r="F208" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G208" t="s">
         <v>848</v>
       </c>
       <c r="H208" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L208" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M208" s="1">
         <v>2</v>
@@ -22192,10 +22363,10 @@
         <v>194</v>
       </c>
       <c r="F209" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G209" t="s">
-        <v>850</v>
+        <v>1366</v>
       </c>
       <c r="H209" t="s">
         <v>769</v>
@@ -22204,7 +22375,7 @@
         <v>819</v>
       </c>
       <c r="L209" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="M209" s="1">
         <v>1</v>
@@ -22218,7 +22389,7 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D210" t="s">
         <v>513</v>
@@ -22227,7 +22398,7 @@
         <v>889</v>
       </c>
       <c r="H210" t="s">
-        <v>1139</v>
+        <v>854</v>
       </c>
       <c r="I210" t="s">
         <v>764</v>
@@ -22237,6 +22408,9 @@
       </c>
       <c r="K210" t="s">
         <v>494</v>
+      </c>
+      <c r="L210" t="s">
+        <v>1310</v>
       </c>
       <c r="M210" s="1">
         <v>3</v>
@@ -22256,19 +22430,19 @@
         <v>695</v>
       </c>
       <c r="F211" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H211" t="s">
         <v>917</v>
       </c>
       <c r="J211" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="K211" t="s">
         <v>494</v>
       </c>
       <c r="L211" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="M211" s="1">
         <v>3</v>
@@ -22285,13 +22459,13 @@
         <v>696</v>
       </c>
       <c r="F212" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G212" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H212" t="s">
         <v>1142</v>
-      </c>
-      <c r="G212" t="s">
-        <v>931</v>
-      </c>
-      <c r="H212" t="s">
-        <v>1143</v>
       </c>
       <c r="I212" t="s">
         <v>776</v>
@@ -22300,7 +22474,7 @@
         <v>789</v>
       </c>
       <c r="L212" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="M212" s="1">
         <v>1</v>
@@ -22317,7 +22491,7 @@
         <v>697</v>
       </c>
       <c r="F213" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G213" t="s">
         <v>847</v>
@@ -22326,10 +22500,10 @@
         <v>1116</v>
       </c>
       <c r="J213" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L213" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M213" s="1">
         <v>1</v>
@@ -22346,19 +22520,19 @@
         <v>698</v>
       </c>
       <c r="F214" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G214" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="H214" t="s">
         <v>1116</v>
       </c>
       <c r="J214" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L214" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="M214" s="1">
         <v>1</v>
@@ -22375,7 +22549,7 @@
         <v>699</v>
       </c>
       <c r="F215" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G215" t="s">
         <v>848</v>
@@ -22390,7 +22564,7 @@
         <v>789</v>
       </c>
       <c r="L215" t="s">
-        <v>1311</v>
+        <v>1389</v>
       </c>
       <c r="M215" s="1">
         <v>1</v>
@@ -22407,7 +22581,7 @@
         <v>700</v>
       </c>
       <c r="F216" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="G216" t="s">
         <v>849</v>
@@ -22416,10 +22590,10 @@
         <v>865</v>
       </c>
       <c r="J216" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="L216" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M216" s="1">
         <v>1</v>
@@ -22436,19 +22610,19 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1194</v>
+        <v>1374</v>
       </c>
       <c r="G217" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="H217" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="I217" t="s">
         <v>777</v>
       </c>
       <c r="J217" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M217" s="1">
         <v>2</v>
@@ -22462,7 +22636,7 @@
         <v>740</v>
       </c>
       <c r="C218" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="D218" t="s">
         <v>640</v>
@@ -22480,7 +22654,7 @@
         <v>789</v>
       </c>
       <c r="L218" t="s">
-        <v>1311</v>
+        <v>1389</v>
       </c>
       <c r="M218" s="1">
         <v>2</v>
@@ -22494,19 +22668,19 @@
         <v>202</v>
       </c>
       <c r="C219" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D219" t="s">
         <v>1190</v>
-      </c>
-      <c r="D219" t="s">
-        <v>1191</v>
       </c>
       <c r="E219" t="s">
         <v>702</v>
       </c>
       <c r="F219" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G219" t="s">
         <v>1148</v>
-      </c>
-      <c r="G219" t="s">
-        <v>1149</v>
       </c>
       <c r="H219" t="s">
         <v>860</v>
@@ -22518,7 +22692,7 @@
         <v>789</v>
       </c>
       <c r="L219" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M219" s="1">
         <v>1</v>
@@ -22535,16 +22709,16 @@
         <v>703</v>
       </c>
       <c r="E220" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F220" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G220" t="s">
         <v>911</v>
       </c>
       <c r="H220" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M220" s="1">
         <v>1</v>
@@ -22561,19 +22735,19 @@
         <v>704</v>
       </c>
       <c r="F221" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G221" t="s">
         <v>1021</v>
       </c>
       <c r="H221" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="I221" t="s">
         <v>778</v>
       </c>
       <c r="L221" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="M221" s="1">
         <v>1</v>
@@ -22587,28 +22761,28 @@
         <v>205</v>
       </c>
       <c r="C222" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D222" t="s">
         <v>705</v>
       </c>
       <c r="F222" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="G222" t="s">
         <v>848</v>
       </c>
       <c r="H222" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="I222" t="s">
         <v>777</v>
       </c>
       <c r="J222" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L222" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="M222" s="1">
         <v>2</v>
@@ -22625,10 +22799,10 @@
         <v>706</v>
       </c>
       <c r="F223" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G223" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="H223" t="s">
         <v>980</v>
@@ -22640,7 +22814,7 @@
         <v>789</v>
       </c>
       <c r="L223" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="M223" s="1">
         <v>2</v>
@@ -22657,7 +22831,7 @@
         <v>707</v>
       </c>
       <c r="F224" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G224" t="s">
         <v>846</v>
@@ -22683,7 +22857,7 @@
         <v>708</v>
       </c>
       <c r="F225" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G225" t="s">
         <v>847</v>
@@ -22698,7 +22872,7 @@
         <v>1055</v>
       </c>
       <c r="L225" t="s">
-        <v>1260</v>
+        <v>1390</v>
       </c>
       <c r="M225" s="1">
         <v>1</v>
@@ -22715,10 +22889,10 @@
         <v>710</v>
       </c>
       <c r="F226" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G226" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H226" t="s">
         <v>1018</v>
@@ -22727,10 +22901,10 @@
         <v>777</v>
       </c>
       <c r="J226" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="L226" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="M226" s="1">
         <v>2</v>
@@ -22747,7 +22921,7 @@
         <v>711</v>
       </c>
       <c r="G227" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H227" t="s">
         <v>943</v>
@@ -22776,13 +22950,13 @@
         <v>712</v>
       </c>
       <c r="F228" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G228" t="s">
         <v>848</v>
       </c>
       <c r="H228" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="M228" s="1">
         <v>1</v>
@@ -22796,13 +22970,13 @@
         <v>487</v>
       </c>
       <c r="C229" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D229" t="s">
         <v>713</v>
       </c>
       <c r="E229" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G229" t="s">
         <v>1038</v>
@@ -22814,7 +22988,7 @@
         <v>773</v>
       </c>
       <c r="J229" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="K229" t="s">
         <v>494</v>
@@ -22831,19 +23005,19 @@
         <v>212</v>
       </c>
       <c r="C230" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D230" t="s">
         <v>714</v>
       </c>
       <c r="G230" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H230" t="s">
         <v>816</v>
       </c>
       <c r="J230" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K230" t="s">
         <v>494</v>
@@ -22863,16 +23037,16 @@
         <v>715</v>
       </c>
       <c r="F231" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G231" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H231" t="s">
         <v>785</v>
       </c>
       <c r="L231" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M231" s="1">
         <v>1</v>
@@ -22892,7 +23066,7 @@
         <v>1089</v>
       </c>
       <c r="G232" t="s">
-        <v>850</v>
+        <v>1366</v>
       </c>
       <c r="H232" t="s">
         <v>800</v>
@@ -22904,7 +23078,7 @@
         <v>789</v>
       </c>
       <c r="L232" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="M232" s="1">
         <v>2</v>
@@ -22921,13 +23095,13 @@
         <v>717</v>
       </c>
       <c r="F233" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G233" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H233" t="s">
         <v>1162</v>
-      </c>
-      <c r="G233" t="s">
-        <v>1362</v>
-      </c>
-      <c r="H233" t="s">
-        <v>1163</v>
       </c>
       <c r="I233" t="s">
         <v>773</v>
@@ -22936,7 +23110,7 @@
         <v>789</v>
       </c>
       <c r="L233" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="M233" s="1">
         <v>2</v>
@@ -22968,7 +23142,7 @@
         <v>494</v>
       </c>
       <c r="L234" t="s">
-        <v>1311</v>
+        <v>1383</v>
       </c>
       <c r="M234" s="1">
         <v>3</v>
@@ -22985,7 +23159,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G235" t="s">
         <v>845</v>
@@ -23010,6 +23184,9 @@
       <c r="B236" t="s">
         <v>218</v>
       </c>
+      <c r="C236" t="s">
+        <v>1399</v>
+      </c>
       <c r="D236" t="s">
         <v>720</v>
       </c>
@@ -23030,26 +23207,29 @@
       <c r="B237" t="s">
         <v>746</v>
       </c>
+      <c r="C237" s="10" t="s">
+        <v>1396</v>
+      </c>
       <c r="D237" t="s">
         <v>747</v>
       </c>
       <c r="E237" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G237" t="s">
         <v>1038</v>
       </c>
       <c r="H237" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J237" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="K237" t="s">
         <v>494</v>
       </c>
       <c r="L237" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M237" s="1">
         <v>3</v>
@@ -23066,7 +23246,7 @@
         <v>721</v>
       </c>
       <c r="F238" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G238" t="s">
         <v>912</v>
@@ -23078,10 +23258,10 @@
         <v>769</v>
       </c>
       <c r="J238" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="L238" t="s">
-        <v>1339</v>
+        <v>1391</v>
       </c>
       <c r="M238" s="1">
         <v>1</v>
@@ -23098,7 +23278,7 @@
         <v>722</v>
       </c>
       <c r="F239" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="G239" t="s">
         <v>896</v>
@@ -23113,7 +23293,7 @@
         <v>819</v>
       </c>
       <c r="L239" t="s">
-        <v>1329</v>
+        <v>1392</v>
       </c>
       <c r="M239" s="1">
         <v>1</v>
@@ -23130,10 +23310,10 @@
         <v>723</v>
       </c>
       <c r="F240" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G240" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H240" t="s">
         <v>797</v>
@@ -23145,7 +23325,7 @@
         <v>819</v>
       </c>
       <c r="L240" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="M240" s="1">
         <v>2</v>
@@ -23158,17 +23338,20 @@
       <c r="B241" t="s">
         <v>222</v>
       </c>
+      <c r="C241" t="s">
+        <v>1398</v>
+      </c>
       <c r="D241" t="s">
         <v>724</v>
       </c>
       <c r="G241" t="s">
-        <v>1149</v>
+        <v>1118</v>
       </c>
       <c r="H241" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J241" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="K241" t="s">
         <v>494</v>
@@ -23200,7 +23383,7 @@
         <v>1072</v>
       </c>
       <c r="L242" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="M242" s="1">
         <v>2</v>
@@ -23217,7 +23400,7 @@
         <v>726</v>
       </c>
       <c r="F243" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G243" t="s">
         <v>847</v>
@@ -23226,7 +23409,7 @@
         <v>798</v>
       </c>
       <c r="L243" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M243" s="1">
         <v>1</v>
@@ -23243,7 +23426,7 @@
         <v>727</v>
       </c>
       <c r="F244" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G244" t="s">
         <v>848</v>
@@ -23258,7 +23441,7 @@
         <v>971</v>
       </c>
       <c r="L244" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M244" s="1">
         <v>2</v>
@@ -23275,7 +23458,7 @@
         <v>728</v>
       </c>
       <c r="F245" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G245" t="s">
         <v>847</v>
@@ -23284,7 +23467,7 @@
         <v>1018</v>
       </c>
       <c r="L245" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M245" s="1">
         <v>1</v>
@@ -23301,7 +23484,7 @@
         <v>729</v>
       </c>
       <c r="F246" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G246" t="s">
         <v>851</v>
@@ -23330,13 +23513,13 @@
         <v>730</v>
       </c>
       <c r="F247" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G247" t="s">
+        <v>842</v>
+      </c>
+      <c r="H247" t="s">
         <v>1172</v>
-      </c>
-      <c r="G247" t="s">
-        <v>841</v>
-      </c>
-      <c r="H247" t="s">
-        <v>1173</v>
       </c>
       <c r="I247" t="s">
         <v>773</v>
@@ -23345,7 +23528,7 @@
         <v>819</v>
       </c>
       <c r="L247" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="M247" s="1">
         <v>2</v>
@@ -23365,7 +23548,7 @@
         <v>845</v>
       </c>
       <c r="H248" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="I248" t="s">
         <v>777</v>
@@ -23385,10 +23568,10 @@
         <v>732</v>
       </c>
       <c r="F249" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G249" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="H249" t="s">
         <v>872</v>
@@ -23400,7 +23583,7 @@
         <v>789</v>
       </c>
       <c r="L249" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="M249" s="1">
         <v>1</v>
@@ -23417,10 +23600,10 @@
         <v>733</v>
       </c>
       <c r="F250" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G250" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H250" t="s">
         <v>865</v>
@@ -23432,7 +23615,7 @@
         <v>789</v>
       </c>
       <c r="L250" t="s">
-        <v>1313</v>
+        <v>1380</v>
       </c>
       <c r="M250" s="1">
         <v>1</v>
@@ -23458,7 +23641,7 @@
         <v>773</v>
       </c>
       <c r="J251" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="K251" t="s">
         <v>494</v>
@@ -23478,19 +23661,19 @@
         <v>735</v>
       </c>
       <c r="E252" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F252" t="s">
         <v>903</v>
       </c>
       <c r="G252" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="H252" t="s">
         <v>897</v>
       </c>
       <c r="L252" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M252" s="1">
         <v>2</v>
@@ -23507,19 +23690,19 @@
         <v>736</v>
       </c>
       <c r="F253" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="G253" t="s">
         <v>911</v>
       </c>
       <c r="H253" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="I253" t="s">
         <v>868</v>
       </c>
       <c r="J253" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M253" s="1">
         <v>2</v>
@@ -23536,13 +23719,13 @@
         <v>737</v>
       </c>
       <c r="F254" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G254" t="s">
         <v>911</v>
       </c>
       <c r="H254" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I254" t="s">
         <v>865</v>
@@ -23551,7 +23734,7 @@
         <v>789</v>
       </c>
       <c r="L254" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="M254" s="1">
         <v>1</v>
@@ -23624,10 +23807,10 @@
         <v>925</v>
       </c>
       <c r="L1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="M1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="N1" t="s">
         <v>751</v>
@@ -23660,10 +23843,10 @@
         <v>776</v>
       </c>
       <c r="J2" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L2" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -23729,7 +23912,7 @@
         <v>782</v>
       </c>
       <c r="L4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -23785,11 +23968,11 @@
         <v>844</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="K6" t="s">
         <v>494</v>
@@ -23815,11 +23998,11 @@
         <v>889</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="K7" t="s">
         <v>494</v>
@@ -23841,7 +24024,7 @@
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>849</v>
@@ -23882,7 +24065,7 @@
       </c>
       <c r="I9" s="4"/>
       <c r="L9" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -23916,7 +24099,7 @@
         <v>781</v>
       </c>
       <c r="L10" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M10">
         <v>2</v>
@@ -23950,7 +24133,7 @@
         <v>783</v>
       </c>
       <c r="L11" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -23977,7 +24160,7 @@
       </c>
       <c r="I12" s="6"/>
       <c r="J12" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="K12" t="s">
         <v>494</v>
@@ -24009,7 +24192,7 @@
       </c>
       <c r="I13" s="4"/>
       <c r="L13" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -24132,7 +24315,7 @@
         <v>819</v>
       </c>
       <c r="L17" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M17">
         <v>2</v>
@@ -24192,7 +24375,7 @@
         <v>799</v>
       </c>
       <c r="L19" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M19">
         <v>2</v>
@@ -24226,7 +24409,7 @@
         <v>793</v>
       </c>
       <c r="L20" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="M20">
         <v>1</v>
@@ -24245,7 +24428,7 @@
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>847</v>
@@ -24255,7 +24438,7 @@
       </c>
       <c r="I21" s="4"/>
       <c r="L21" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -24291,7 +24474,7 @@
         <v>789</v>
       </c>
       <c r="L22" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M22">
         <v>2</v>
@@ -24320,7 +24503,7 @@
       </c>
       <c r="I23" s="4"/>
       <c r="L23" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -24434,7 +24617,7 @@
       </c>
       <c r="I27" s="4"/>
       <c r="J27" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="K27" t="s">
         <v>494</v>
@@ -24464,7 +24647,7 @@
       </c>
       <c r="I28" s="6"/>
       <c r="J28" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="K28" t="s">
         <v>494</v>
@@ -24500,7 +24683,7 @@
         <v>776</v>
       </c>
       <c r="J29" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="M29">
         <v>2</v>
@@ -24531,10 +24714,10 @@
       </c>
       <c r="I30" s="6"/>
       <c r="J30" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L30" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -24597,10 +24780,10 @@
         <v>816</v>
       </c>
       <c r="J32" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="L32" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="M32">
         <v>1</v>
@@ -24627,7 +24810,7 @@
       </c>
       <c r="I33" s="4"/>
       <c r="L33" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="M33">
         <v>2</v>
@@ -24689,7 +24872,7 @@
       </c>
       <c r="I35" s="4"/>
       <c r="L35" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M35">
         <v>1</v>
@@ -24746,10 +24929,10 @@
         <v>773</v>
       </c>
       <c r="J37" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="L37" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="M37">
         <v>2</v>
@@ -24780,10 +24963,10 @@
         <v>776</v>
       </c>
       <c r="J38" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L38" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M38">
         <v>1</v>
@@ -24820,7 +25003,7 @@
         <v>494</v>
       </c>
       <c r="L39" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="M39">
         <v>3</v>
@@ -24928,7 +25111,7 @@
         <v>708</v>
       </c>
       <c r="F43" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G43" t="s">
         <v>847</v>
@@ -24943,7 +25126,7 @@
         <v>1055</v>
       </c>
       <c r="L43" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="M43">
         <v>1</v>
@@ -24975,7 +25158,7 @@
         <v>1068</v>
       </c>
       <c r="L44" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M44">
         <v>1</v>
@@ -24998,7 +25181,7 @@
         <v>845</v>
       </c>
       <c r="H45" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I45" t="s">
         <v>773</v>
@@ -25077,7 +25260,7 @@
         <v>789</v>
       </c>
       <c r="L47" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -25135,7 +25318,7 @@
         <v>872</v>
       </c>
       <c r="L49" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M49">
         <v>1</v>
@@ -25161,10 +25344,10 @@
         <v>767</v>
       </c>
       <c r="J50" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L50" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M50">
         <v>1</v>
@@ -25190,10 +25373,10 @@
         <v>773</v>
       </c>
       <c r="J51" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L51" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="M51">
         <v>1</v>
@@ -25216,7 +25399,7 @@
         <v>859</v>
       </c>
       <c r="L52" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -25332,7 +25515,7 @@
         <v>767</v>
       </c>
       <c r="L56" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="M56">
         <v>1</v>
@@ -25358,7 +25541,7 @@
         <v>936</v>
       </c>
       <c r="L57" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M57">
         <v>1</v>
@@ -25390,7 +25573,7 @@
         <v>789</v>
       </c>
       <c r="L58" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="M58">
         <v>2</v>
@@ -25442,10 +25625,10 @@
         <v>892</v>
       </c>
       <c r="J60" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="L60" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="M60">
         <v>2</v>
@@ -25474,7 +25657,7 @@
         <v>767</v>
       </c>
       <c r="J61" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="M61">
         <v>1</v>
@@ -25506,7 +25689,7 @@
         <v>819</v>
       </c>
       <c r="L62" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M62">
         <v>1</v>
@@ -25532,10 +25715,10 @@
         <v>872</v>
       </c>
       <c r="J63" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L63" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M63">
         <v>1</v>
@@ -25561,7 +25744,7 @@
         <v>908</v>
       </c>
       <c r="L64" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M64">
         <v>1</v>
@@ -25590,10 +25773,10 @@
         <v>777</v>
       </c>
       <c r="J65" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="L65" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M65">
         <v>1</v>
@@ -25625,13 +25808,13 @@
         <v>776</v>
       </c>
       <c r="J66" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K66" t="s">
         <v>494</v>
       </c>
       <c r="L66" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M66">
         <v>3</v>
@@ -25660,7 +25843,7 @@
         <v>777</v>
       </c>
       <c r="J67" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="M67">
         <v>1</v>
@@ -25677,7 +25860,7 @@
         <v>700</v>
       </c>
       <c r="F68" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G68" t="s">
         <v>849</v>
@@ -25686,10 +25869,10 @@
         <v>865</v>
       </c>
       <c r="J68" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="L68" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M68">
         <v>1</v>
@@ -25718,10 +25901,10 @@
         <v>798</v>
       </c>
       <c r="J69" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L69" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="M69">
         <v>1</v>
@@ -25770,7 +25953,7 @@
         <v>975</v>
       </c>
       <c r="J71" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="M71">
         <v>2</v>
@@ -25793,10 +25976,10 @@
         <v>851</v>
       </c>
       <c r="H72" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J72" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="K72" t="s">
         <v>494</v>
@@ -25813,7 +25996,7 @@
         <v>740</v>
       </c>
       <c r="C73" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D73" t="s">
         <v>640</v>
@@ -25883,7 +26066,7 @@
         <v>767</v>
       </c>
       <c r="L75" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M75">
         <v>1</v>
@@ -25909,7 +26092,7 @@
         <v>923</v>
       </c>
       <c r="L76" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M76">
         <v>2</v>
@@ -25996,7 +26179,7 @@
         <v>795</v>
       </c>
       <c r="J79" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="K79" t="s">
         <v>494</v>
@@ -26089,7 +26272,7 @@
         <v>880</v>
       </c>
       <c r="L82" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="M82">
         <v>2</v>
@@ -26208,7 +26391,7 @@
         <v>789</v>
       </c>
       <c r="L86" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M86">
         <v>1</v>
@@ -26243,7 +26426,7 @@
         <v>494</v>
       </c>
       <c r="L87" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M87">
         <v>3</v>
@@ -26263,7 +26446,7 @@
         <v>961</v>
       </c>
       <c r="G88" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H88" t="s">
         <v>769</v>
@@ -26301,7 +26484,7 @@
         <v>928</v>
       </c>
       <c r="L89" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M89">
         <v>2</v>
@@ -26327,7 +26510,7 @@
         <v>812</v>
       </c>
       <c r="L90" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M90">
         <v>1</v>
@@ -26382,10 +26565,10 @@
         <v>951</v>
       </c>
       <c r="J92" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="L92" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M92">
         <v>2</v>
@@ -26437,10 +26620,10 @@
         <v>851</v>
       </c>
       <c r="H94" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J94" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="K94" t="s">
         <v>494</v>
@@ -26472,10 +26655,10 @@
         <v>787</v>
       </c>
       <c r="J95" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L95" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M95">
         <v>1</v>
@@ -26498,7 +26681,7 @@
         <v>943</v>
       </c>
       <c r="J96" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="K96" t="s">
         <v>494</v>
@@ -26559,7 +26742,7 @@
         <v>812</v>
       </c>
       <c r="L98" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M98">
         <v>2</v>
@@ -26623,7 +26806,7 @@
         <v>789</v>
       </c>
       <c r="L100" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M100">
         <v>1</v>
@@ -26649,10 +26832,10 @@
         <v>785</v>
       </c>
       <c r="J101" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L101" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M101">
         <v>1</v>
@@ -26681,10 +26864,10 @@
         <v>943</v>
       </c>
       <c r="J102" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="L102" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M102">
         <v>1</v>
@@ -26701,7 +26884,7 @@
         <v>728</v>
       </c>
       <c r="F103" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G103" t="s">
         <v>847</v>
@@ -26710,7 +26893,7 @@
         <v>1018</v>
       </c>
       <c r="L103" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M103">
         <v>1</v>
@@ -26727,7 +26910,7 @@
         <v>588</v>
       </c>
       <c r="E104" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F104" t="s">
         <v>1033</v>
@@ -26739,7 +26922,7 @@
         <v>769</v>
       </c>
       <c r="L104" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M104">
         <v>1</v>
@@ -26765,7 +26948,7 @@
         <v>1069</v>
       </c>
       <c r="L105" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M105">
         <v>1</v>
@@ -26797,7 +26980,7 @@
         <v>789</v>
       </c>
       <c r="L106" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M106">
         <v>1</v>
@@ -26846,7 +27029,7 @@
         <v>1054</v>
       </c>
       <c r="F108" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G108" t="s">
         <v>841</v>
@@ -26861,7 +27044,7 @@
         <v>793</v>
       </c>
       <c r="L108" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M108">
         <v>1</v>
@@ -26875,7 +27058,7 @@
         <v>212</v>
       </c>
       <c r="C109" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D109" t="s">
         <v>714</v>
@@ -26887,7 +27070,7 @@
         <v>816</v>
       </c>
       <c r="J109" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K109" t="s">
         <v>494</v>
@@ -26922,7 +27105,7 @@
         <v>782</v>
       </c>
       <c r="L110" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M110">
         <v>1</v>
@@ -26951,10 +27134,10 @@
         <v>776</v>
       </c>
       <c r="J111" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L111" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M111">
         <v>1</v>
@@ -27006,7 +27189,7 @@
         <v>980</v>
       </c>
       <c r="L113" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M113">
         <v>1</v>
@@ -27040,7 +27223,7 @@
         <v>75</v>
       </c>
       <c r="C115" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D115" t="s">
         <v>571</v>
@@ -27078,10 +27261,10 @@
         <v>773</v>
       </c>
       <c r="J116" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L116" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="M116">
         <v>2</v>
@@ -27110,7 +27293,7 @@
         <v>793</v>
       </c>
       <c r="L117" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="M117">
         <v>1</v>
@@ -27200,7 +27383,7 @@
         <v>855</v>
       </c>
       <c r="L120" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M120">
         <v>1</v>
@@ -27258,7 +27441,7 @@
         <v>874</v>
       </c>
       <c r="L122" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="M122">
         <v>2</v>
@@ -27322,7 +27505,7 @@
         <v>880</v>
       </c>
       <c r="L124" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="M124">
         <v>1</v>
@@ -27386,7 +27569,7 @@
         <v>1002</v>
       </c>
       <c r="L126" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="M126">
         <v>2</v>
@@ -27409,10 +27592,10 @@
         <v>889</v>
       </c>
       <c r="H127" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J127" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="K127" t="s">
         <v>494</v>
@@ -27473,7 +27656,7 @@
         <v>793</v>
       </c>
       <c r="L129" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="M129">
         <v>1</v>
@@ -27505,7 +27688,7 @@
         <v>974</v>
       </c>
       <c r="L130" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M130">
         <v>1</v>
@@ -27563,7 +27746,7 @@
         <v>1023</v>
       </c>
       <c r="L132" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M132">
         <v>2</v>
@@ -27580,19 +27763,19 @@
         <v>701</v>
       </c>
       <c r="E133" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G133" t="s">
         <v>841</v>
       </c>
       <c r="H133" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="I133" t="s">
         <v>777</v>
       </c>
       <c r="J133" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="M133">
         <v>2</v>
@@ -27650,7 +27833,7 @@
         <v>775</v>
       </c>
       <c r="L135" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M135">
         <v>2</v>
@@ -27676,7 +27859,7 @@
         <v>808</v>
       </c>
       <c r="L136" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M136">
         <v>1</v>
@@ -27702,7 +27885,7 @@
         <v>1026</v>
       </c>
       <c r="L137" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M137">
         <v>2</v>
@@ -27728,7 +27911,7 @@
         <v>769</v>
       </c>
       <c r="L138" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M138">
         <v>1</v>
@@ -27760,7 +27943,7 @@
         <v>819</v>
       </c>
       <c r="L139" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M139">
         <v>1</v>
@@ -27818,7 +28001,7 @@
         <v>769</v>
       </c>
       <c r="L141" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M141">
         <v>2</v>
@@ -27844,10 +28027,10 @@
         <v>758</v>
       </c>
       <c r="J142" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="L142" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M142">
         <v>1</v>
@@ -27864,7 +28047,7 @@
         <v>644</v>
       </c>
       <c r="F143" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G143" t="s">
         <v>849</v>
@@ -27876,7 +28059,7 @@
         <v>777</v>
       </c>
       <c r="J143" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="M143">
         <v>1</v>
@@ -27896,7 +28079,7 @@
         <v>684</v>
       </c>
       <c r="F144" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G144" t="s">
         <v>1118</v>
@@ -27908,7 +28091,7 @@
         <v>494</v>
       </c>
       <c r="L144" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M144">
         <v>3</v>
@@ -27977,7 +28160,7 @@
         <v>1029</v>
       </c>
       <c r="F147" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G147" t="s">
         <v>847</v>
@@ -28012,7 +28195,7 @@
         <v>802</v>
       </c>
       <c r="L148" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M148">
         <v>2</v>
@@ -28050,7 +28233,7 @@
         <v>789</v>
       </c>
       <c r="L149" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M149">
         <v>1</v>
@@ -28082,10 +28265,10 @@
         <v>777</v>
       </c>
       <c r="J150" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L150" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M150">
         <v>1</v>
@@ -28131,7 +28314,7 @@
         <v>108</v>
       </c>
       <c r="C152" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D152" t="s">
         <v>605</v>
@@ -28143,7 +28326,7 @@
         <v>816</v>
       </c>
       <c r="J152" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="K152" t="s">
         <v>494</v>
@@ -28175,7 +28358,7 @@
         <v>494</v>
       </c>
       <c r="L153" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="M153">
         <v>3</v>
@@ -28210,7 +28393,7 @@
         <v>819</v>
       </c>
       <c r="L154" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M154">
         <v>2</v>
@@ -28233,10 +28416,10 @@
         <v>1118</v>
       </c>
       <c r="H155" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J155" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="K155" t="s">
         <v>494</v>
@@ -28265,10 +28448,10 @@
         <v>795</v>
       </c>
       <c r="J156" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="L156" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M156">
         <v>1</v>
@@ -28291,7 +28474,7 @@
         <v>1039</v>
       </c>
       <c r="L157" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M157">
         <v>2</v>
@@ -28349,7 +28532,7 @@
         <v>783</v>
       </c>
       <c r="L159" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M159">
         <v>1</v>
@@ -28381,10 +28564,10 @@
         <v>980</v>
       </c>
       <c r="J160" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="L160" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M160">
         <v>1</v>
@@ -28442,10 +28625,10 @@
         <v>1042</v>
       </c>
       <c r="J162" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="L162" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="M162">
         <v>1</v>
@@ -28515,7 +28698,7 @@
         <v>494</v>
       </c>
       <c r="L164" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M164">
         <v>3</v>
@@ -28547,7 +28730,7 @@
         <v>793</v>
       </c>
       <c r="L165" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="M165">
         <v>1</v>
@@ -28582,7 +28765,7 @@
         <v>494</v>
       </c>
       <c r="L166" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M166">
         <v>3</v>
@@ -28608,7 +28791,7 @@
         <v>764</v>
       </c>
       <c r="L167" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M167">
         <v>1</v>
@@ -28634,10 +28817,10 @@
         <v>787</v>
       </c>
       <c r="J168" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="L168" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M168">
         <v>1</v>
@@ -28666,7 +28849,7 @@
         <v>785</v>
       </c>
       <c r="L169" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M169">
         <v>1</v>
@@ -28724,7 +28907,7 @@
         <v>783</v>
       </c>
       <c r="L171" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M171">
         <v>2</v>
@@ -28828,7 +29011,7 @@
         <v>1027</v>
       </c>
       <c r="J175" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="M175">
         <v>1</v>
@@ -28886,7 +29069,7 @@
         <v>769</v>
       </c>
       <c r="L177" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M177">
         <v>1</v>
@@ -28909,13 +29092,13 @@
         <v>769</v>
       </c>
       <c r="J178" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="K178" t="s">
         <v>494</v>
       </c>
       <c r="L178" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M178">
         <v>3</v>
@@ -28973,10 +29156,10 @@
         <v>777</v>
       </c>
       <c r="J180" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="L180" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="M180">
         <v>1</v>
@@ -29031,7 +29214,7 @@
         <v>795</v>
       </c>
       <c r="L182" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M182">
         <v>1</v>
@@ -29054,7 +29237,7 @@
         <v>1134</v>
       </c>
       <c r="G183" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H183" t="s">
         <v>1132</v>
@@ -29089,10 +29272,10 @@
         <v>845</v>
       </c>
       <c r="H184" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J184" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="K184" t="s">
         <v>494</v>
@@ -29121,13 +29304,13 @@
         <v>773</v>
       </c>
       <c r="J185" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="K185" t="s">
         <v>494</v>
       </c>
       <c r="L185" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="M185">
         <v>3</v>
@@ -29156,7 +29339,7 @@
         <v>494</v>
       </c>
       <c r="L186" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M186">
         <v>3</v>
@@ -29182,7 +29365,7 @@
         <v>797</v>
       </c>
       <c r="J187" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="M187">
         <v>1</v>
@@ -29211,7 +29394,7 @@
         <v>793</v>
       </c>
       <c r="L188" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="M188">
         <v>2</v>
@@ -29237,10 +29420,10 @@
         <v>785</v>
       </c>
       <c r="J189" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="L189" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M189">
         <v>1</v>
@@ -29318,7 +29501,7 @@
         <v>758</v>
       </c>
       <c r="L192" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M192">
         <v>1</v>
@@ -29344,10 +29527,10 @@
         <v>854</v>
       </c>
       <c r="J193" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="L193" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M193">
         <v>1</v>
@@ -29373,7 +29556,7 @@
         <v>1116</v>
       </c>
       <c r="L194" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M194">
         <v>1</v>
@@ -29405,7 +29588,7 @@
         <v>783</v>
       </c>
       <c r="L195" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M195">
         <v>2</v>
@@ -29521,7 +29704,7 @@
         <v>1038</v>
       </c>
       <c r="H199" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="M199">
         <v>2</v>
@@ -29538,19 +29721,19 @@
         <v>704</v>
       </c>
       <c r="F200" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G200" t="s">
         <v>1021</v>
       </c>
       <c r="H200" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="I200" t="s">
         <v>778</v>
       </c>
       <c r="L200" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="M200">
         <v>1</v>
@@ -29567,7 +29750,7 @@
         <v>707</v>
       </c>
       <c r="F201" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G201" t="s">
         <v>846</v>
@@ -29593,7 +29776,7 @@
         <v>194</v>
       </c>
       <c r="F202" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G202" t="s">
         <v>850</v>
@@ -29605,7 +29788,7 @@
         <v>819</v>
       </c>
       <c r="L202" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M202">
         <v>1</v>
@@ -29625,10 +29808,10 @@
         <v>1038</v>
       </c>
       <c r="H203" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J203" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="K203" t="s">
         <v>494</v>
@@ -29648,7 +29831,7 @@
         <v>698</v>
       </c>
       <c r="F204" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G204" t="s">
         <v>847</v>
@@ -29657,10 +29840,10 @@
         <v>1116</v>
       </c>
       <c r="J204" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L204" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M204">
         <v>1</v>
@@ -29677,7 +29860,7 @@
         <v>697</v>
       </c>
       <c r="F205" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G205" t="s">
         <v>847</v>
@@ -29686,10 +29869,10 @@
         <v>1116</v>
       </c>
       <c r="J205" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L205" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M205">
         <v>1</v>
@@ -29706,16 +29889,16 @@
         <v>694</v>
       </c>
       <c r="F206" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G206" t="s">
         <v>848</v>
       </c>
       <c r="H206" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L206" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M206">
         <v>1</v>
@@ -29729,7 +29912,7 @@
         <v>187</v>
       </c>
       <c r="C207" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D207" t="s">
         <v>688</v>
@@ -29747,10 +29930,10 @@
         <v>920</v>
       </c>
       <c r="J207" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="L207" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M207">
         <v>2</v>
@@ -29767,7 +29950,7 @@
         <v>692</v>
       </c>
       <c r="F208" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="G208" t="s">
         <v>848</v>
@@ -29782,7 +29965,7 @@
         <v>789</v>
       </c>
       <c r="L208" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M208">
         <v>1</v>
@@ -29799,7 +29982,7 @@
         <v>699</v>
       </c>
       <c r="F209" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G209" t="s">
         <v>848</v>
@@ -29828,7 +30011,7 @@
         <v>706</v>
       </c>
       <c r="F210" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G210" t="s">
         <v>851</v>
@@ -29843,7 +30026,7 @@
         <v>789</v>
       </c>
       <c r="L210" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M210">
         <v>2</v>
@@ -29857,28 +30040,28 @@
         <v>205</v>
       </c>
       <c r="C211" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D211" t="s">
         <v>705</v>
       </c>
       <c r="F211" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G211" t="s">
         <v>848</v>
       </c>
       <c r="H211" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="I211" t="s">
         <v>1000</v>
       </c>
       <c r="J211" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L211" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M211">
         <v>1</v>
@@ -29910,10 +30093,10 @@
         <v>754</v>
       </c>
       <c r="J212" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="L212" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="M212">
         <v>2</v>
@@ -29927,7 +30110,7 @@
         <v>485</v>
       </c>
       <c r="C213" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D213" t="s">
         <v>513</v>
@@ -29936,7 +30119,7 @@
         <v>889</v>
       </c>
       <c r="H213" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="I213" t="s">
         <v>764</v>
@@ -29974,10 +30157,10 @@
         <v>816</v>
       </c>
       <c r="J214" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L214" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M214">
         <v>1</v>
@@ -29997,19 +30180,19 @@
         <v>695</v>
       </c>
       <c r="F215" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H215" t="s">
         <v>917</v>
       </c>
       <c r="J215" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="K215" t="s">
         <v>494</v>
       </c>
       <c r="L215" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="M215">
         <v>3</v>
@@ -30026,13 +30209,13 @@
         <v>696</v>
       </c>
       <c r="F216" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G216" t="s">
         <v>931</v>
       </c>
       <c r="H216" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="I216" t="s">
         <v>776</v>
@@ -30041,7 +30224,7 @@
         <v>789</v>
       </c>
       <c r="L216" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M216">
         <v>1</v>
@@ -30070,7 +30253,7 @@
         <v>914</v>
       </c>
       <c r="J217" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="M217">
         <v>2</v>
@@ -30087,22 +30270,22 @@
         <v>747</v>
       </c>
       <c r="E218" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G218" t="s">
         <v>1038</v>
       </c>
       <c r="H218" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J218" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="K218" t="s">
         <v>494</v>
       </c>
       <c r="L218" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M218">
         <v>3</v>
@@ -30119,13 +30302,13 @@
         <v>724</v>
       </c>
       <c r="G219" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H219" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J219" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="K219" t="s">
         <v>494</v>
@@ -30154,7 +30337,7 @@
         <v>758</v>
       </c>
       <c r="L220" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M220">
         <v>2</v>
@@ -30168,13 +30351,13 @@
         <v>487</v>
       </c>
       <c r="C221" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D221" t="s">
         <v>713</v>
       </c>
       <c r="E221" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G221" t="s">
         <v>1038</v>
@@ -30186,7 +30369,7 @@
         <v>773</v>
       </c>
       <c r="J221" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="K221" t="s">
         <v>494</v>
@@ -30206,13 +30389,13 @@
         <v>717</v>
       </c>
       <c r="F222" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G222" t="s">
         <v>848</v>
       </c>
       <c r="H222" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="I222" t="s">
         <v>773</v>
@@ -30235,7 +30418,7 @@
         <v>715</v>
       </c>
       <c r="F223" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G223" t="s">
         <v>850</v>
@@ -30244,7 +30427,7 @@
         <v>785</v>
       </c>
       <c r="L223" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M223">
         <v>1</v>
@@ -30261,7 +30444,7 @@
         <v>710</v>
       </c>
       <c r="F224" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G224" t="s">
         <v>841</v>
@@ -30273,10 +30456,10 @@
         <v>777</v>
       </c>
       <c r="J224" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="L224" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M224">
         <v>2</v>
@@ -30337,7 +30520,7 @@
         <v>789</v>
       </c>
       <c r="L226" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="M226">
         <v>2</v>
@@ -30354,7 +30537,7 @@
         <v>723</v>
       </c>
       <c r="F227" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G227" t="s">
         <v>841</v>
@@ -30383,7 +30566,7 @@
         <v>721</v>
       </c>
       <c r="F228" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G228" t="s">
         <v>1021</v>
@@ -30395,10 +30578,10 @@
         <v>769</v>
       </c>
       <c r="J228" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="L228" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="M228">
         <v>1</v>
@@ -30415,7 +30598,7 @@
         <v>719</v>
       </c>
       <c r="E229" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G229" t="s">
         <v>845</v>
@@ -30444,7 +30627,7 @@
         <v>722</v>
       </c>
       <c r="F230" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G230" t="s">
         <v>841</v>
@@ -30548,13 +30731,13 @@
         <v>712</v>
       </c>
       <c r="F234" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G234" t="s">
         <v>848</v>
       </c>
       <c r="H234" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="M234">
         <v>1</v>
@@ -30571,7 +30754,7 @@
         <v>726</v>
       </c>
       <c r="F235" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G235" t="s">
         <v>847</v>
@@ -30580,7 +30763,7 @@
         <v>798</v>
       </c>
       <c r="L235" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M235">
         <v>1</v>
@@ -30597,7 +30780,7 @@
         <v>727</v>
       </c>
       <c r="F236" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G236" t="s">
         <v>848</v>
@@ -30612,7 +30795,7 @@
         <v>971</v>
       </c>
       <c r="L236" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M236">
         <v>2</v>
@@ -30626,19 +30809,19 @@
         <v>202</v>
       </c>
       <c r="C237" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D237" t="s">
         <v>702</v>
       </c>
       <c r="E237" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F237" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G237" t="s">
         <v>1148</v>
-      </c>
-      <c r="G237" t="s">
-        <v>1149</v>
       </c>
       <c r="H237" t="s">
         <v>860</v>
@@ -30664,7 +30847,7 @@
         <v>729</v>
       </c>
       <c r="F238" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G238" t="s">
         <v>851</v>
@@ -30693,13 +30876,13 @@
         <v>730</v>
       </c>
       <c r="F239" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G239" t="s">
         <v>841</v>
       </c>
       <c r="H239" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="I239" t="s">
         <v>773</v>
@@ -30708,7 +30891,7 @@
         <v>819</v>
       </c>
       <c r="L239" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M239">
         <v>2</v>
@@ -30740,10 +30923,10 @@
         <v>870</v>
       </c>
       <c r="J240" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="L240" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="M240">
         <v>2</v>
@@ -30757,7 +30940,7 @@
         <v>182</v>
       </c>
       <c r="C241" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D241" t="s">
         <v>682</v>
@@ -30772,7 +30955,7 @@
         <v>778</v>
       </c>
       <c r="L241" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="M241">
         <v>2</v>
@@ -30789,13 +30972,13 @@
         <v>732</v>
       </c>
       <c r="F242" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G242" t="s">
         <v>851</v>
       </c>
       <c r="H242" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="I242" t="s">
         <v>773</v>
@@ -30804,7 +30987,7 @@
         <v>789</v>
       </c>
       <c r="L242" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M242">
         <v>1</v>
@@ -30827,10 +31010,10 @@
         <v>889</v>
       </c>
       <c r="H243" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J243" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="K243" t="s">
         <v>494</v>
@@ -30859,7 +31042,7 @@
         <v>994</v>
       </c>
       <c r="J244" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="K244" t="s">
         <v>494</v>
@@ -30879,7 +31062,7 @@
         <v>733</v>
       </c>
       <c r="F245" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G245" t="s">
         <v>850</v>
@@ -30911,7 +31094,7 @@
         <v>845</v>
       </c>
       <c r="H246" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="I246" t="s">
         <v>777</v>
@@ -30940,7 +31123,7 @@
         <v>773</v>
       </c>
       <c r="J247" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="K247" t="s">
         <v>494</v>
@@ -31015,7 +31198,7 @@
         <v>735</v>
       </c>
       <c r="E250" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F250" t="s">
         <v>903</v>
@@ -31027,7 +31210,7 @@
         <v>897</v>
       </c>
       <c r="L250" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="M250">
         <v>1</v>
@@ -31044,7 +31227,7 @@
         <v>638</v>
       </c>
       <c r="E251" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G251" t="s">
         <v>1038</v>
@@ -31053,7 +31236,7 @@
         <v>773</v>
       </c>
       <c r="J251" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="K251" t="s">
         <v>494</v>
@@ -31073,16 +31256,16 @@
         <v>703</v>
       </c>
       <c r="E252" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F252" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G252" t="s">
         <v>911</v>
       </c>
       <c r="H252" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M252">
         <v>1</v>
@@ -31099,19 +31282,19 @@
         <v>736</v>
       </c>
       <c r="F253" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G253" t="s">
         <v>911</v>
       </c>
       <c r="H253" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="I253" t="s">
         <v>868</v>
       </c>
       <c r="J253" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M253">
         <v>1</v>
@@ -31128,13 +31311,13 @@
         <v>737</v>
       </c>
       <c r="F254" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G254" t="s">
         <v>911</v>
       </c>
       <c r="H254" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I254" t="s">
         <v>947</v>
@@ -31143,7 +31326,7 @@
         <v>789</v>
       </c>
       <c r="L254" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="M254">
         <v>1</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551F43FE-C552-4669-BD5D-072F8B21FB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ACD201-2951-4F2F-A138-D97743D3CA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="20985" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="1424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4248" uniqueCount="1468">
   <si>
     <t>Sigla</t>
   </si>
@@ -4145,18 +4145,12 @@
     <t>mezzaluna gialla, stella gialla</t>
   </si>
   <si>
-    <t>*Malabo</t>
-  </si>
-  <si>
     <t>Nusantara, Jacarta</t>
   </si>
   <si>
     <t>arancione, verde</t>
   </si>
   <si>
-    <t>Kotte, Sri Jayawardenapura, Colombo</t>
-  </si>
-  <si>
     <t>lenzuolo rosso</t>
   </si>
   <si>
@@ -4311,6 +4305,144 @@
   </si>
   <si>
     <t>Asia, Mediterraneo</t>
+  </si>
+  <si>
+    <t>Babbane</t>
+  </si>
+  <si>
+    <t>Nuk</t>
+  </si>
+  <si>
+    <t>Adam's Town</t>
+  </si>
+  <si>
+    <t>Bishkek, Biscake</t>
+  </si>
+  <si>
+    <t>Un gerol wood</t>
+  </si>
+  <si>
+    <t>Assunzione</t>
+  </si>
+  <si>
+    <t>el aiun, aaiun, Ela jun</t>
+  </si>
+  <si>
+    <t>Valichir</t>
+  </si>
+  <si>
+    <t>Nuku alofa, Mutualopa</t>
+  </si>
+  <si>
+    <t>Taschent</t>
+  </si>
+  <si>
+    <t>Nibbia</t>
+  </si>
+  <si>
+    <t>St John's, Saint Johns, St Johns, Saint Jones</t>
+  </si>
+  <si>
+    <t>Portonovo</t>
+  </si>
+  <si>
+    <t>Pnom Pen, Non Pen, Pnonten</t>
+  </si>
+  <si>
+    <t>Dillendstadt</t>
+  </si>
+  <si>
+    <t>st george's, st george, saint george, Giorgis</t>
+  </si>
+  <si>
+    <t>Flying Fish Club</t>
+  </si>
+  <si>
+    <t>Dr Shadn</t>
+  </si>
+  <si>
+    <t>Onyara</t>
+  </si>
+  <si>
+    <t>Naypidaw, Naipidau, Mypidau, Naked out</t>
+  </si>
+  <si>
+    <t>Mia Mail</t>
+  </si>
+  <si>
+    <t>Abbia, Appia</t>
+  </si>
+  <si>
+    <t>Ruba</t>
+  </si>
+  <si>
+    <t>Con Acri</t>
+  </si>
+  <si>
+    <t>West highland</t>
+  </si>
+  <si>
+    <t>Con rovia</t>
+  </si>
+  <si>
+    <t>Marigoz</t>
+  </si>
+  <si>
+    <t>Philips burger</t>
+  </si>
+  <si>
+    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte</t>
+  </si>
+  <si>
+    <t>Sport Villa</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>Al-Kuwait, Kuwait city, Q8, Madina al Q8</t>
+  </si>
+  <si>
+    <t>Yamussukro, Yamusucro</t>
+  </si>
+  <si>
+    <t>*Malabo, la pass</t>
+  </si>
+  <si>
+    <t>Coq burn town</t>
+  </si>
+  <si>
+    <t>Arare</t>
+  </si>
+  <si>
+    <t>Wally se futura</t>
+  </si>
+  <si>
+    <t>Gtega</t>
+  </si>
+  <si>
+    <t>Irama</t>
+  </si>
+  <si>
+    <t>oranistad, oranistadt, orangestar</t>
+  </si>
+  <si>
+    <t>Mary Anne,</t>
+  </si>
+  <si>
+    <t>Windoek, Windows</t>
+  </si>
+  <si>
+    <t>King's Town</t>
+  </si>
+  <si>
+    <t>Dujabbe</t>
+  </si>
+  <si>
+    <t>Azkaban, Azkabat</t>
+  </si>
+  <si>
+    <t>Sara Occidentale</t>
   </si>
 </sst>
 </file>
@@ -4405,7 +4537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4418,6 +4550,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -15679,6 +15815,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D12C1757-22C2-4B5F-923A-7373BC58AED5}" name="Elenco" displayName="Elenco" ref="A1:M254" totalsRowShown="0">
   <autoFilter ref="A1:M254" xr:uid="{D12C1757-22C2-4B5F-923A-7373BC58AED5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M254">
+    <sortCondition ref="B1:B254"/>
+  </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{C69A84BF-08C6-4051-820A-053DF45718B4}" name="Sigla" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{E07D78F6-8AAC-46C7-9978-B6D2697016C9}" name="Paese" dataDxfId="2"/>
@@ -16150,7 +16289,7 @@
         <v>773</v>
       </c>
       <c r="J2" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="L2" t="s">
         <v>1242</v>
@@ -16176,6 +16315,9 @@
       <c r="D3" t="s">
         <v>499</v>
       </c>
+      <c r="E3" t="s">
+        <v>1460</v>
+      </c>
       <c r="F3" t="s">
         <v>1195</v>
       </c>
@@ -16192,7 +16334,7 @@
         <v>780</v>
       </c>
       <c r="L3" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
@@ -16261,7 +16403,7 @@
         <v>757</v>
       </c>
       <c r="G5" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="H5" t="s">
         <v>758</v>
@@ -16290,7 +16432,7 @@
         <v>828</v>
       </c>
       <c r="G6" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="H6" t="s">
         <v>754</v>
@@ -16348,7 +16490,7 @@
         <v>504</v>
       </c>
       <c r="E8" t="s">
-        <v>760</v>
+        <v>1433</v>
       </c>
       <c r="G8" t="s">
         <v>888</v>
@@ -16395,7 +16537,7 @@
         <v>1219</v>
       </c>
       <c r="L9" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
@@ -16447,10 +16589,10 @@
         <v>765</v>
       </c>
       <c r="G11" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="H11" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="L11" t="s">
         <v>1245</v>
@@ -16469,6 +16611,9 @@
       <c r="D12" t="s">
         <v>513</v>
       </c>
+      <c r="E12" t="s">
+        <v>1461</v>
+      </c>
       <c r="G12" t="s">
         <v>888</v>
       </c>
@@ -16502,7 +16647,7 @@
         <v>583</v>
       </c>
       <c r="G13" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="H13" t="s">
         <v>1214</v>
@@ -16586,7 +16731,7 @@
         <v>887</v>
       </c>
       <c r="G16" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="H16" t="s">
         <v>770</v>
@@ -16661,16 +16806,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
       </c>
       <c r="E19" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G19" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H19" t="s">
         <v>794</v>
@@ -16711,7 +16856,7 @@
         <v>792</v>
       </c>
       <c r="L20" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="M20" s="1">
         <v>2</v>
@@ -16760,7 +16905,7 @@
         <v>1205</v>
       </c>
       <c r="G22" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="H22" t="s">
         <v>799</v>
@@ -16814,11 +16959,14 @@
       <c r="D24" t="s">
         <v>519</v>
       </c>
+      <c r="E24" t="s">
+        <v>1434</v>
+      </c>
       <c r="F24" t="s">
         <v>834</v>
       </c>
       <c r="G24" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="H24" t="s">
         <v>801</v>
@@ -17062,7 +17210,7 @@
         <v>1216</v>
       </c>
       <c r="L32" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="M32" s="1">
         <v>1</v>
@@ -17146,7 +17294,7 @@
         <v>820</v>
       </c>
       <c r="G35" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H35" t="s">
         <v>805</v>
@@ -17174,11 +17322,14 @@
       <c r="D36" t="s">
         <v>532</v>
       </c>
+      <c r="E36" t="s">
+        <v>1459</v>
+      </c>
       <c r="F36" t="s">
         <v>826</v>
       </c>
       <c r="G36" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H36" t="s">
         <v>755</v>
@@ -17190,7 +17341,7 @@
         <v>788</v>
       </c>
       <c r="L36" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="M36" s="1">
         <v>2</v>
@@ -17207,7 +17358,7 @@
         <v>533</v>
       </c>
       <c r="E37" t="s">
-        <v>852</v>
+        <v>1435</v>
       </c>
       <c r="F37" t="s">
         <v>929</v>
@@ -17312,7 +17463,7 @@
         <v>536</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>858</v>
@@ -17434,7 +17585,7 @@
         <v>958</v>
       </c>
       <c r="G44" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H44" t="s">
         <v>864</v>
@@ -17446,7 +17597,7 @@
         <v>788</v>
       </c>
       <c r="L44" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
@@ -17463,19 +17614,19 @@
         <v>540</v>
       </c>
       <c r="G45" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="H45" t="s">
         <v>866</v>
       </c>
       <c r="I45" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J45" t="s">
         <v>875</v>
       </c>
       <c r="L45" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -17553,7 +17704,7 @@
         <v>542</v>
       </c>
       <c r="G48" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H48" t="s">
         <v>872</v>
@@ -17614,7 +17765,7 @@
         <v>963</v>
       </c>
       <c r="G50" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H50" t="s">
         <v>767</v>
@@ -17652,7 +17803,7 @@
         <v>964</v>
       </c>
       <c r="G51" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H51" t="s">
         <v>881</v>
@@ -17664,7 +17815,7 @@
         <v>792</v>
       </c>
       <c r="L51" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -17684,13 +17835,13 @@
         <v>546</v>
       </c>
       <c r="E52" t="s">
-        <v>883</v>
+        <v>1454</v>
       </c>
       <c r="F52" t="s">
         <v>965</v>
       </c>
       <c r="G52" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="H52" t="s">
         <v>1067</v>
@@ -17799,6 +17950,9 @@
       <c r="D56" t="s">
         <v>550</v>
       </c>
+      <c r="E56" t="s">
+        <v>1436</v>
+      </c>
       <c r="G56" t="s">
         <v>888</v>
       </c>
@@ -17835,7 +17989,7 @@
         <v>1344</v>
       </c>
       <c r="G57" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H57" t="s">
         <v>769</v>
@@ -18012,7 +18166,7 @@
         <v>905</v>
       </c>
       <c r="G63" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H63" t="s">
         <v>906</v>
@@ -18041,7 +18195,7 @@
         <v>909</v>
       </c>
       <c r="G64" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="H64" t="s">
         <v>907</v>
@@ -18061,10 +18215,13 @@
         <v>741</v>
       </c>
       <c r="C65" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D65" t="s">
         <v>709</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1422</v>
       </c>
       <c r="F65" t="s">
         <v>1057</v>
@@ -18099,7 +18256,7 @@
         <v>915</v>
       </c>
       <c r="G66" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H66" t="s">
         <v>801</v>
@@ -18183,7 +18340,7 @@
         <v>917</v>
       </c>
       <c r="G69" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H69" t="s">
         <v>918</v>
@@ -18296,7 +18453,7 @@
         <v>925</v>
       </c>
       <c r="G73" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H73" t="s">
         <v>927</v>
@@ -18322,7 +18479,7 @@
         <v>931</v>
       </c>
       <c r="G74" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="H74" t="s">
         <v>794</v>
@@ -18406,7 +18563,7 @@
         <v>969</v>
       </c>
       <c r="G77" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="H77" t="s">
         <v>936</v>
@@ -18461,7 +18618,7 @@
         <v>572</v>
       </c>
       <c r="G79" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H79" t="s">
         <v>794</v>
@@ -18473,7 +18630,7 @@
         <v>792</v>
       </c>
       <c r="L79" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="M79" s="1">
         <v>1</v>
@@ -18493,7 +18650,7 @@
         <v>938</v>
       </c>
       <c r="G80" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="H80" t="s">
         <v>794</v>
@@ -18528,7 +18685,7 @@
         <v>944</v>
       </c>
       <c r="G81" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H81" t="s">
         <v>939</v>
@@ -18615,7 +18772,7 @@
         <v>575</v>
       </c>
       <c r="E84" t="s">
-        <v>940</v>
+        <v>1437</v>
       </c>
       <c r="G84" t="s">
         <v>1117</v>
@@ -18646,6 +18803,9 @@
       <c r="D85" t="s">
         <v>576</v>
       </c>
+      <c r="E85" t="s">
+        <v>1423</v>
+      </c>
       <c r="F85" t="s">
         <v>960</v>
       </c>
@@ -18682,7 +18842,7 @@
         <v>941</v>
       </c>
       <c r="J86" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="K86" t="s">
         <v>494</v>
@@ -18763,7 +18923,7 @@
         <v>1298</v>
       </c>
       <c r="G89" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H89" t="s">
         <v>946</v>
@@ -18788,11 +18948,14 @@
       <c r="D90" t="s">
         <v>581</v>
       </c>
+      <c r="E90" t="s">
+        <v>1445</v>
+      </c>
       <c r="F90" t="s">
         <v>1012</v>
       </c>
       <c r="G90" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H90" t="s">
         <v>811</v>
@@ -18815,7 +18978,7 @@
         <v>948</v>
       </c>
       <c r="E91" t="s">
-        <v>1368</v>
+        <v>1455</v>
       </c>
       <c r="F91" t="s">
         <v>949</v>
@@ -18853,7 +19016,7 @@
         <v>951</v>
       </c>
       <c r="G92" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H92" t="s">
         <v>811</v>
@@ -19013,7 +19176,7 @@
         <v>975</v>
       </c>
       <c r="G97" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H97" t="s">
         <v>769</v>
@@ -19028,7 +19191,7 @@
         <v>494</v>
       </c>
       <c r="L97" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="M97" s="1">
         <v>3</v>
@@ -19080,7 +19243,7 @@
         <v>588</v>
       </c>
       <c r="E99" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="F99" t="s">
         <v>1032</v>
@@ -19205,7 +19368,7 @@
         <v>981</v>
       </c>
       <c r="G103" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H103" t="s">
         <v>1068</v>
@@ -19263,7 +19426,7 @@
         <v>983</v>
       </c>
       <c r="G105" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H105" t="s">
         <v>767</v>
@@ -19289,7 +19452,7 @@
         <v>595</v>
       </c>
       <c r="G106" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H106" t="s">
         <v>769</v>
@@ -19304,7 +19467,7 @@
         <v>494</v>
       </c>
       <c r="L106" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="M106" s="1">
         <v>3</v>
@@ -19323,6 +19486,9 @@
       <c r="D107" t="s">
         <v>596</v>
       </c>
+      <c r="E107" t="s">
+        <v>1438</v>
+      </c>
       <c r="G107" t="s">
         <v>844</v>
       </c>
@@ -19393,8 +19559,11 @@
       <c r="D109" t="s">
         <v>598</v>
       </c>
+      <c r="E109" t="s">
+        <v>1462</v>
+      </c>
       <c r="G109" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H109" t="s">
         <v>758</v>
@@ -19451,6 +19620,9 @@
       <c r="D111" t="s">
         <v>600</v>
       </c>
+      <c r="E111" t="s">
+        <v>1446</v>
+      </c>
       <c r="G111" t="s">
         <v>844</v>
       </c>
@@ -19550,8 +19722,11 @@
       <c r="D114" t="s">
         <v>604</v>
       </c>
+      <c r="E114" t="s">
+        <v>1439</v>
+      </c>
       <c r="G114" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H114" t="s">
         <v>916</v>
@@ -19574,13 +19749,13 @@
         <v>108</v>
       </c>
       <c r="C115" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="D115" t="s">
         <v>605</v>
       </c>
       <c r="E115" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="G115" t="s">
         <v>841</v>
@@ -19595,7 +19770,7 @@
         <v>494</v>
       </c>
       <c r="L115" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="M115" s="1">
         <v>3</v>
@@ -19643,6 +19818,9 @@
       <c r="D117" t="s">
         <v>597</v>
       </c>
+      <c r="E117" t="s">
+        <v>1424</v>
+      </c>
       <c r="G117" t="s">
         <v>844</v>
       </c>
@@ -19672,6 +19850,9 @@
       <c r="D118" t="s">
         <v>607</v>
       </c>
+      <c r="E118" t="s">
+        <v>1440</v>
+      </c>
       <c r="G118" t="s">
         <v>844</v>
       </c>
@@ -19717,7 +19898,7 @@
         <v>494</v>
       </c>
       <c r="L119" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="M119" s="1">
         <v>3</v>
@@ -19824,7 +20005,7 @@
         <v>998</v>
       </c>
       <c r="G123" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H123" t="s">
         <v>999</v>
@@ -19833,7 +20014,7 @@
         <v>1005</v>
       </c>
       <c r="L123" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="M123" s="1">
         <v>1</v>
@@ -19853,7 +20034,7 @@
         <v>1343</v>
       </c>
       <c r="G124" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H124" t="s">
         <v>1001</v>
@@ -19879,13 +20060,13 @@
         <v>614</v>
       </c>
       <c r="E125" t="s">
-        <v>1010</v>
+        <v>1425</v>
       </c>
       <c r="F125" t="s">
         <v>1002</v>
       </c>
       <c r="G125" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H125" t="s">
         <v>864</v>
@@ -19897,7 +20078,7 @@
         <v>783</v>
       </c>
       <c r="L125" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="M125" s="1">
         <v>2</v>
@@ -19961,7 +20142,7 @@
         <v>494</v>
       </c>
       <c r="L127" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="M127" s="1">
         <v>3</v>
@@ -19974,11 +20155,14 @@
       <c r="B128" t="s">
         <v>121</v>
       </c>
+      <c r="C128" t="s">
+        <v>1452</v>
+      </c>
       <c r="D128" t="s">
         <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>1011</v>
+        <v>1453</v>
       </c>
       <c r="F128" t="s">
         <v>1008</v>
@@ -20071,7 +20255,7 @@
         <v>1015</v>
       </c>
       <c r="G131" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="H131" t="s">
         <v>769</v>
@@ -20125,11 +20309,14 @@
       <c r="D133" t="s">
         <v>622</v>
       </c>
+      <c r="E133" t="s">
+        <v>1447</v>
+      </c>
       <c r="F133" t="s">
         <v>1018</v>
       </c>
       <c r="G133" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H133" t="s">
         <v>916</v>
@@ -20225,7 +20412,7 @@
         <v>1049</v>
       </c>
       <c r="G136" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="H136" t="s">
         <v>807</v>
@@ -20251,7 +20438,7 @@
         <v>1024</v>
       </c>
       <c r="G137" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="H137" t="s">
         <v>1025</v>
@@ -20277,7 +20464,7 @@
         <v>975</v>
       </c>
       <c r="G138" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H138" t="s">
         <v>778</v>
@@ -20292,7 +20479,7 @@
         <v>494</v>
       </c>
       <c r="L138" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="M138" s="1">
         <v>3</v>
@@ -20341,7 +20528,7 @@
         <v>628</v>
       </c>
       <c r="G140" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H140" t="s">
         <v>1026</v>
@@ -20364,7 +20551,7 @@
         <v>1027</v>
       </c>
       <c r="G141" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H141" t="s">
         <v>1023</v>
@@ -20460,7 +20647,7 @@
         <v>1034</v>
       </c>
       <c r="G144" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H144" t="s">
         <v>801</v>
@@ -20527,7 +20714,7 @@
         <v>788</v>
       </c>
       <c r="L146" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="M146" s="1">
         <v>1</v>
@@ -20579,7 +20766,7 @@
         <v>1036</v>
       </c>
       <c r="G148" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H148" t="s">
         <v>805</v>
@@ -20608,7 +20795,7 @@
         <v>637</v>
       </c>
       <c r="G149" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H149" t="s">
         <v>1038</v>
@@ -20634,7 +20821,7 @@
         <v>1215</v>
       </c>
       <c r="G150" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H150" t="s">
         <v>916</v>
@@ -20646,7 +20833,7 @@
         <v>494</v>
       </c>
       <c r="L150" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="M150" s="1">
         <v>3</v>
@@ -20733,7 +20920,7 @@
         <v>1040</v>
       </c>
       <c r="G153" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H153" t="s">
         <v>800</v>
@@ -20823,7 +21010,7 @@
         <v>1059</v>
       </c>
       <c r="G156" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H156" t="s">
         <v>1041</v>
@@ -20852,7 +21039,7 @@
         <v>523</v>
       </c>
       <c r="E157" t="s">
-        <v>806</v>
+        <v>1441</v>
       </c>
       <c r="F157" t="s">
         <v>835</v>
@@ -20883,11 +21070,14 @@
       <c r="B158" t="s">
         <v>149</v>
       </c>
+      <c r="C158" t="s">
+        <v>1432</v>
+      </c>
       <c r="D158" t="s">
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1055</v>
+        <v>1463</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21008,11 +21198,14 @@
       <c r="D162" t="s">
         <v>651</v>
       </c>
+      <c r="E162" t="s">
+        <v>1442</v>
+      </c>
       <c r="F162" t="s">
         <v>1064</v>
       </c>
       <c r="G162" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H162" t="s">
         <v>1067</v>
@@ -21044,7 +21237,7 @@
         <v>1070</v>
       </c>
       <c r="G163" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="H163" t="s">
         <v>764</v>
@@ -21102,7 +21295,7 @@
         <v>1072</v>
       </c>
       <c r="G165" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H165" t="s">
         <v>785</v>
@@ -21224,7 +21417,7 @@
         <v>1082</v>
       </c>
       <c r="G169" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="H169" t="s">
         <v>785</v>
@@ -21278,6 +21471,9 @@
       <c r="D171" t="s">
         <v>660</v>
       </c>
+      <c r="E171" t="s">
+        <v>1426</v>
+      </c>
       <c r="G171" t="s">
         <v>844</v>
       </c>
@@ -21291,7 +21487,7 @@
         <v>792</v>
       </c>
       <c r="L171" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="M171" s="1">
         <v>2</v>
@@ -21406,6 +21602,9 @@
       <c r="D175" t="s">
         <v>663</v>
       </c>
+      <c r="E175" t="s">
+        <v>1427</v>
+      </c>
       <c r="F175" t="s">
         <v>1092</v>
       </c>
@@ -21459,7 +21658,7 @@
         <v>167</v>
       </c>
       <c r="C177" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="D177" t="s">
         <v>665</v>
@@ -21555,7 +21754,7 @@
         <v>938</v>
       </c>
       <c r="G180" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H180" t="s">
         <v>796</v>
@@ -21639,7 +21838,7 @@
         <v>982</v>
       </c>
       <c r="G183" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H183" t="s">
         <v>859</v>
@@ -21723,214 +21922,211 @@
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>446</v>
+        <v>382</v>
       </c>
       <c r="B186" t="s">
-        <v>175</v>
+        <v>1202</v>
       </c>
       <c r="C186" t="s">
-        <v>1106</v>
+        <v>1401</v>
       </c>
       <c r="D186" t="s">
-        <v>674</v>
+        <v>688</v>
+      </c>
+      <c r="E186" t="s">
+        <v>187</v>
       </c>
       <c r="F186" t="s">
-        <v>1107</v>
+        <v>115</v>
       </c>
       <c r="G186" t="s">
-        <v>888</v>
+        <v>846</v>
       </c>
       <c r="H186" t="s">
-        <v>767</v>
+        <v>919</v>
       </c>
       <c r="J186" t="s">
-        <v>1221</v>
+        <v>1226</v>
+      </c>
+      <c r="L186" t="s">
+        <v>1245</v>
       </c>
       <c r="M186" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="B187" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C187" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D187" t="s">
-        <v>675</v>
-      </c>
-      <c r="E187" t="s">
-        <v>1109</v>
+        <v>674</v>
+      </c>
+      <c r="F187" t="s">
+        <v>1107</v>
       </c>
       <c r="G187" t="s">
-        <v>1409</v>
+        <v>888</v>
       </c>
       <c r="H187" t="s">
-        <v>1110</v>
-      </c>
-      <c r="K187" t="s">
-        <v>494</v>
+        <v>767</v>
+      </c>
+      <c r="J187" t="s">
+        <v>1221</v>
       </c>
       <c r="M187" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="B188" t="s">
-        <v>177</v>
+        <v>176</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1108</v>
       </c>
       <c r="D188" t="s">
-        <v>676</v>
-      </c>
-      <c r="F188" t="s">
-        <v>1111</v>
+        <v>675</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1109</v>
       </c>
       <c r="G188" t="s">
-        <v>1355</v>
+        <v>1407</v>
       </c>
       <c r="H188" t="s">
-        <v>758</v>
-      </c>
-      <c r="L188" t="s">
-        <v>1242</v>
+        <v>1110</v>
+      </c>
+      <c r="K188" t="s">
+        <v>494</v>
       </c>
       <c r="M188" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D189" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F189" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G189" t="s">
-        <v>1409</v>
+        <v>1355</v>
       </c>
       <c r="H189" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I189" t="s">
-        <v>777</v>
-      </c>
-      <c r="J189" t="s">
-        <v>783</v>
+        <v>758</v>
       </c>
       <c r="L189" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="M189" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B190" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D190" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F190" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G190" t="s">
-        <v>846</v>
+        <v>1407</v>
       </c>
       <c r="H190" t="s">
-        <v>1115</v>
+        <v>1113</v>
+      </c>
+      <c r="I190" t="s">
+        <v>777</v>
+      </c>
+      <c r="J190" t="s">
+        <v>783</v>
       </c>
       <c r="L190" t="s">
         <v>1245</v>
       </c>
       <c r="M190" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>495</v>
+        <v>373</v>
       </c>
       <c r="B191" t="s">
-        <v>486</v>
+        <v>179</v>
       </c>
       <c r="D191" t="s">
-        <v>679</v>
-      </c>
-      <c r="E191" t="s">
-        <v>1116</v>
+        <v>678</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1114</v>
       </c>
       <c r="G191" t="s">
-        <v>1117</v>
+        <v>846</v>
       </c>
       <c r="H191" t="s">
-        <v>785</v>
-      </c>
-      <c r="I191" t="s">
-        <v>777</v>
-      </c>
-      <c r="J191" t="s">
-        <v>788</v>
-      </c>
-      <c r="K191" t="s">
-        <v>494</v>
+        <v>1115</v>
       </c>
       <c r="L191" t="s">
-        <v>1309</v>
+        <v>1245</v>
       </c>
       <c r="M191" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="B192" t="s">
-        <v>180</v>
+        <v>486</v>
       </c>
       <c r="D192" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>897</v>
-      </c>
-      <c r="F192" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G192" t="s">
-        <v>912</v>
+        <v>1117</v>
       </c>
       <c r="H192" t="s">
-        <v>898</v>
+        <v>785</v>
       </c>
       <c r="I192" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J192" t="s">
-        <v>1201</v>
+        <v>788</v>
       </c>
       <c r="K192" t="s">
         <v>494</v>
       </c>
       <c r="L192" t="s">
-        <v>1326</v>
+        <v>1309</v>
       </c>
       <c r="M192" s="1">
         <v>3</v>
@@ -21938,60 +22134,72 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
       <c r="B193" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1126</v>
+        <v>1467</v>
       </c>
       <c r="D193" t="s">
-        <v>681</v>
+        <v>680</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1118</v>
       </c>
       <c r="G193" t="s">
-        <v>1117</v>
+        <v>912</v>
       </c>
       <c r="H193" t="s">
-        <v>1122</v>
+        <v>898</v>
       </c>
       <c r="I193" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="J193" t="s">
-        <v>788</v>
+        <v>1201</v>
+      </c>
+      <c r="K193" t="s">
+        <v>494</v>
       </c>
       <c r="L193" t="s">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="M193" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B194" t="s">
-        <v>739</v>
+        <v>181</v>
       </c>
       <c r="C194" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D194" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="G194" t="s">
         <v>1117</v>
       </c>
       <c r="H194" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="I194" t="s">
-        <v>1121</v>
+        <v>773</v>
+      </c>
+      <c r="J194" t="s">
+        <v>788</v>
       </c>
       <c r="L194" t="s">
-        <v>1381</v>
+        <v>1307</v>
       </c>
       <c r="M194" s="1">
         <v>2</v>
@@ -21999,28 +22207,28 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B195" t="s">
-        <v>182</v>
+        <v>739</v>
       </c>
       <c r="C195" t="s">
-        <v>1213</v>
+        <v>1124</v>
       </c>
       <c r="D195" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G195" t="s">
         <v>1117</v>
       </c>
       <c r="H195" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="I195" t="s">
-        <v>778</v>
+        <v>1121</v>
       </c>
       <c r="L195" t="s">
-        <v>1242</v>
+        <v>1379</v>
       </c>
       <c r="M195" s="1">
         <v>2</v>
@@ -22028,66 +22236,63 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C196" t="s">
-        <v>1127</v>
+        <v>1213</v>
       </c>
       <c r="D196" t="s">
-        <v>683</v>
+        <v>682</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1464</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
       </c>
       <c r="H196" t="s">
-        <v>773</v>
-      </c>
-      <c r="J196" t="s">
-        <v>1237</v>
-      </c>
-      <c r="K196" t="s">
-        <v>494</v>
+        <v>1123</v>
+      </c>
+      <c r="I196" t="s">
+        <v>778</v>
       </c>
       <c r="L196" t="s">
-        <v>1374</v>
+        <v>1242</v>
       </c>
       <c r="M196" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B197" t="s">
-        <v>482</v>
+        <v>183</v>
       </c>
       <c r="C197" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D197" t="s">
-        <v>684</v>
-      </c>
-      <c r="F197" t="s">
-        <v>1138</v>
+        <v>683</v>
       </c>
       <c r="G197" t="s">
         <v>1117</v>
       </c>
       <c r="H197" t="s">
-        <v>916</v>
+        <v>773</v>
       </c>
       <c r="J197" t="s">
-        <v>1176</v>
+        <v>1237</v>
       </c>
       <c r="K197" t="s">
         <v>494</v>
       </c>
       <c r="L197" t="s">
-        <v>1242</v>
+        <v>1372</v>
       </c>
       <c r="M197" s="1">
         <v>3</v>
@@ -22095,127 +22300,133 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>476</v>
+        <v>379</v>
       </c>
       <c r="B198" t="s">
-        <v>184</v>
+        <v>482</v>
       </c>
       <c r="C198" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D198" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E198" t="s">
-        <v>1133</v>
+        <v>1448</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1138</v>
       </c>
       <c r="G198" t="s">
-        <v>1147</v>
+        <v>1117</v>
       </c>
       <c r="H198" t="s">
-        <v>1131</v>
-      </c>
-      <c r="I198" t="s">
-        <v>777</v>
+        <v>916</v>
       </c>
       <c r="J198" t="s">
-        <v>1132</v>
+        <v>1176</v>
       </c>
       <c r="K198" t="s">
         <v>494</v>
       </c>
+      <c r="L198" t="s">
+        <v>1242</v>
+      </c>
       <c r="M198" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>381</v>
+        <v>476</v>
       </c>
       <c r="B199" t="s">
-        <v>185</v>
+        <v>184</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1129</v>
       </c>
       <c r="D199" t="s">
-        <v>686</v>
+        <v>685</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1133</v>
       </c>
       <c r="G199" t="s">
-        <v>844</v>
+        <v>1147</v>
       </c>
       <c r="H199" t="s">
-        <v>800</v>
+        <v>1131</v>
       </c>
       <c r="I199" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="J199" t="s">
-        <v>1075</v>
-      </c>
-      <c r="L199" t="s">
-        <v>1307</v>
+        <v>1132</v>
+      </c>
+      <c r="K199" t="s">
+        <v>494</v>
       </c>
       <c r="M199" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="B200" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D200" t="s">
-        <v>687</v>
+        <v>686</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1443</v>
       </c>
       <c r="G200" t="s">
         <v>844</v>
       </c>
       <c r="H200" t="s">
-        <v>767</v>
+        <v>800</v>
+      </c>
+      <c r="I200" t="s">
+        <v>773</v>
       </c>
       <c r="J200" t="s">
-        <v>1346</v>
-      </c>
-      <c r="K200" t="s">
-        <v>494</v>
+        <v>1075</v>
+      </c>
+      <c r="L200" t="s">
+        <v>1307</v>
       </c>
       <c r="M200" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="B201" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1403</v>
+        <v>186</v>
       </c>
       <c r="D201" t="s">
-        <v>688</v>
-      </c>
-      <c r="E201" t="s">
-        <v>187</v>
-      </c>
-      <c r="F201" t="s">
-        <v>115</v>
+        <v>687</v>
       </c>
       <c r="G201" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H201" t="s">
-        <v>919</v>
+        <v>767</v>
       </c>
       <c r="J201" t="s">
-        <v>1226</v>
-      </c>
-      <c r="L201" t="s">
-        <v>1245</v>
+        <v>1346</v>
+      </c>
+      <c r="K201" t="s">
+        <v>494</v>
       </c>
       <c r="M201" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.25">
@@ -22229,7 +22440,7 @@
         <v>738</v>
       </c>
       <c r="G202" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="H202" t="s">
         <v>1214</v>
@@ -22322,7 +22533,7 @@
         <v>1301</v>
       </c>
       <c r="G205" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H205" t="s">
         <v>801</v>
@@ -22380,7 +22591,7 @@
         <v>586</v>
       </c>
       <c r="G207" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H207" t="s">
         <v>1283</v>
@@ -22403,7 +22614,7 @@
         <v>1135</v>
       </c>
       <c r="G208" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H208" t="s">
         <v>1136</v>
@@ -22457,6 +22668,9 @@
       <c r="D210" t="s">
         <v>513</v>
       </c>
+      <c r="E210" t="s">
+        <v>1461</v>
+      </c>
       <c r="G210" t="s">
         <v>888</v>
       </c>
@@ -22492,6 +22706,9 @@
       <c r="D211" t="s">
         <v>695</v>
       </c>
+      <c r="E211" t="s">
+        <v>1449</v>
+      </c>
       <c r="F211" t="s">
         <v>1139</v>
       </c>
@@ -22547,31 +22764,35 @@
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D213" t="s">
+      <c r="C213" s="10"/>
+      <c r="D213" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="F213" t="s">
+      <c r="E213" s="10"/>
+      <c r="F213" s="10" t="s">
         <v>1142</v>
       </c>
-      <c r="G213" t="s">
+      <c r="G213" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="H213" t="s">
+      <c r="H213" s="10" t="s">
         <v>1115</v>
       </c>
-      <c r="J213" t="s">
+      <c r="I213" s="10"/>
+      <c r="J213" s="10" t="s">
         <v>1221</v>
       </c>
+      <c r="K213" s="10"/>
       <c r="L213" t="s">
         <v>1245</v>
       </c>
-      <c r="M213" s="1">
+      <c r="M213" s="11">
         <v>1</v>
       </c>
     </row>
@@ -22618,7 +22839,7 @@
         <v>1144</v>
       </c>
       <c r="G215" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H215" t="s">
         <v>786</v>
@@ -22630,7 +22851,7 @@
         <v>788</v>
       </c>
       <c r="L215" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="M215" s="1">
         <v>1</v>
@@ -22650,7 +22871,7 @@
         <v>1341</v>
       </c>
       <c r="G216" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="H216" t="s">
         <v>864</v>
@@ -22676,7 +22897,7 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1371</v>
+        <v>1450</v>
       </c>
       <c r="G217" t="s">
         <v>1352</v>
@@ -22707,6 +22928,9 @@
       <c r="D218" t="s">
         <v>640</v>
       </c>
+      <c r="E218" t="s">
+        <v>1429</v>
+      </c>
       <c r="G218" t="s">
         <v>844</v>
       </c>
@@ -22720,7 +22944,7 @@
         <v>788</v>
       </c>
       <c r="L218" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="M218" s="1">
         <v>2</v>
@@ -22832,11 +23056,14 @@
       <c r="D222" t="s">
         <v>705</v>
       </c>
+      <c r="E222" t="s">
+        <v>1444</v>
+      </c>
       <c r="F222" t="s">
         <v>1339</v>
       </c>
       <c r="G222" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H222" t="s">
         <v>1152</v>
@@ -22900,7 +23127,7 @@
         <v>1154</v>
       </c>
       <c r="G224" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H224" t="s">
         <v>797</v>
@@ -22938,7 +23165,7 @@
         <v>1054</v>
       </c>
       <c r="L225" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="M225" s="1">
         <v>1</v>
@@ -22954,11 +23181,14 @@
       <c r="D226" t="s">
         <v>710</v>
       </c>
+      <c r="E226" t="s">
+        <v>1465</v>
+      </c>
       <c r="F226" t="s">
         <v>1204</v>
       </c>
       <c r="G226" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H226" t="s">
         <v>1017</v>
@@ -22987,7 +23217,7 @@
         <v>711</v>
       </c>
       <c r="G227" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H227" t="s">
         <v>942</v>
@@ -23019,7 +23249,7 @@
         <v>1156</v>
       </c>
       <c r="G228" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H228" t="s">
         <v>1157</v>
@@ -23161,7 +23391,7 @@
         <v>1160</v>
       </c>
       <c r="G233" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="H233" t="s">
         <v>1161</v>
@@ -23205,7 +23435,7 @@
         <v>494</v>
       </c>
       <c r="L234" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="M234" s="1">
         <v>3</v>
@@ -23222,7 +23452,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1182</v>
+        <v>1430</v>
       </c>
       <c r="G235" t="s">
         <v>844</v>
@@ -23248,7 +23478,7 @@
         <v>218</v>
       </c>
       <c r="C236" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D236" t="s">
         <v>720</v>
@@ -23271,7 +23501,7 @@
         <v>746</v>
       </c>
       <c r="C237" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="D237" t="s">
         <v>747</v>
@@ -23280,7 +23510,7 @@
         <v>1181</v>
       </c>
       <c r="G237" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="H237" t="s">
         <v>1214</v>
@@ -23324,7 +23554,7 @@
         <v>1163</v>
       </c>
       <c r="L238" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="M238" s="1">
         <v>1</v>
@@ -23344,7 +23574,7 @@
         <v>1338</v>
       </c>
       <c r="G239" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="H239" t="s">
         <v>769</v>
@@ -23356,7 +23586,7 @@
         <v>818</v>
       </c>
       <c r="L239" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="M239" s="1">
         <v>1</v>
@@ -23372,11 +23602,14 @@
       <c r="D240" t="s">
         <v>723</v>
       </c>
+      <c r="E240" t="s">
+        <v>1466</v>
+      </c>
       <c r="F240" t="s">
         <v>1165</v>
       </c>
       <c r="G240" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H240" t="s">
         <v>796</v>
@@ -23402,10 +23635,13 @@
         <v>222</v>
       </c>
       <c r="C241" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="D241" t="s">
         <v>724</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1456</v>
       </c>
       <c r="G241" t="s">
         <v>1117</v>
@@ -23492,7 +23728,7 @@
         <v>1167</v>
       </c>
       <c r="G244" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H244" t="s">
         <v>799</v>
@@ -23575,11 +23811,14 @@
       <c r="D247" t="s">
         <v>730</v>
       </c>
+      <c r="E247" t="s">
+        <v>1431</v>
+      </c>
       <c r="F247" t="s">
         <v>1170</v>
       </c>
       <c r="G247" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H247" t="s">
         <v>1171</v>
@@ -23607,6 +23846,9 @@
       <c r="D248" t="s">
         <v>731</v>
       </c>
+      <c r="E248" t="s">
+        <v>1451</v>
+      </c>
       <c r="G248" t="s">
         <v>844</v>
       </c>
@@ -23681,7 +23923,7 @@
         <v>788</v>
       </c>
       <c r="L250" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="M250" s="1">
         <v>1</v>
@@ -23695,10 +23937,13 @@
         <v>232</v>
       </c>
       <c r="C251" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D251" t="s">
         <v>734</v>
+      </c>
+      <c r="E251" t="s">
+        <v>1458</v>
       </c>
       <c r="G251" t="s">
         <v>844</v>
@@ -23762,7 +24007,7 @@
         <v>1342</v>
       </c>
       <c r="G253" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H253" t="s">
         <v>1177</v>
@@ -23787,11 +24032,14 @@
       <c r="D254" t="s">
         <v>737</v>
       </c>
+      <c r="E254" t="s">
+        <v>1457</v>
+      </c>
       <c r="F254" t="s">
         <v>1179</v>
       </c>
       <c r="G254" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H254" t="s">
         <v>1180</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ACD201-2951-4F2F-A138-D97743D3CA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9399AD-178B-481A-AC97-FD3D5094D8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4248" uniqueCount="1468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4251" uniqueCount="1475">
   <si>
     <t>Sigla</t>
   </si>
@@ -4367,9 +4367,6 @@
     <t>Naypidaw, Naipidau, Mypidau, Naked out</t>
   </si>
   <si>
-    <t>Mia Mail</t>
-  </si>
-  <si>
     <t>Abbia, Appia</t>
   </si>
   <si>
@@ -4443,6 +4440,30 @@
   </si>
   <si>
     <t>Sara Occidentale</t>
+  </si>
+  <si>
+    <t>Bridgestone</t>
+  </si>
+  <si>
+    <t>graal dick</t>
+  </si>
+  <si>
+    <t>Maiuro</t>
+  </si>
+  <si>
+    <t>Nuakchot, No rock shot</t>
+  </si>
+  <si>
+    <t>Mia Mail, Nia may</t>
+  </si>
+  <si>
+    <t>Bandar, bandarzeri begawan</t>
+  </si>
+  <si>
+    <t>Port au Prince, Port u prince</t>
+  </si>
+  <si>
+    <t>Bottom, de botto</t>
   </si>
 </sst>
 </file>
@@ -16316,7 +16337,7 @@
         <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F3" t="s">
         <v>1195</v>
@@ -16612,7 +16633,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16872,6 +16893,9 @@
       <c r="D21" t="s">
         <v>516</v>
       </c>
+      <c r="E21" t="s">
+        <v>1467</v>
+      </c>
       <c r="G21" t="s">
         <v>888</v>
       </c>
@@ -17104,6 +17128,9 @@
       <c r="D29" t="s">
         <v>525</v>
       </c>
+      <c r="E29" t="s">
+        <v>1468</v>
+      </c>
       <c r="G29" t="s">
         <v>888</v>
       </c>
@@ -17227,7 +17254,7 @@
         <v>529</v>
       </c>
       <c r="E33" t="s">
-        <v>825</v>
+        <v>1472</v>
       </c>
       <c r="F33" t="s">
         <v>1031</v>
@@ -17323,7 +17350,7 @@
         <v>532</v>
       </c>
       <c r="E36" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F36" t="s">
         <v>826</v>
@@ -17835,7 +17862,7 @@
         <v>546</v>
       </c>
       <c r="E52" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F52" t="s">
         <v>965</v>
@@ -18949,7 +18976,7 @@
         <v>581</v>
       </c>
       <c r="E90" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="F90" t="s">
         <v>1012</v>
@@ -18978,7 +19005,7 @@
         <v>948</v>
       </c>
       <c r="E91" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F91" t="s">
         <v>949</v>
@@ -19109,7 +19136,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>971</v>
+        <v>1473</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -19560,7 +19587,7 @@
         <v>598</v>
       </c>
       <c r="E109" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G109" t="s">
         <v>1402</v>
@@ -19621,7 +19648,7 @@
         <v>600</v>
       </c>
       <c r="E111" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G111" t="s">
         <v>844</v>
@@ -19789,6 +19816,9 @@
       <c r="D116" t="s">
         <v>606</v>
       </c>
+      <c r="E116" t="s">
+        <v>1469</v>
+      </c>
       <c r="G116" t="s">
         <v>844</v>
       </c>
@@ -20156,13 +20186,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D128" t="s">
         <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F128" t="s">
         <v>1008</v>
@@ -20310,7 +20340,7 @@
         <v>622</v>
       </c>
       <c r="E133" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F133" t="s">
         <v>1018</v>
@@ -20760,7 +20790,7 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1046</v>
+        <v>1470</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
@@ -21077,7 +21107,7 @@
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21199,7 +21229,7 @@
         <v>651</v>
       </c>
       <c r="E162" t="s">
-        <v>1442</v>
+        <v>1471</v>
       </c>
       <c r="F162" t="s">
         <v>1064</v>
@@ -22108,7 +22138,7 @@
         <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>1116</v>
+        <v>1474</v>
       </c>
       <c r="G192" t="s">
         <v>1117</v>
@@ -22140,7 +22170,7 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="D193" t="s">
         <v>680</v>
@@ -22248,7 +22278,7 @@
         <v>682</v>
       </c>
       <c r="E196" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
@@ -22312,7 +22342,7 @@
         <v>684</v>
       </c>
       <c r="E198" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F198" t="s">
         <v>1138</v>
@@ -22382,7 +22412,7 @@
         <v>686</v>
       </c>
       <c r="E200" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G200" t="s">
         <v>844</v>
@@ -22669,7 +22699,7 @@
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22707,7 +22737,7 @@
         <v>695</v>
       </c>
       <c r="E211" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F211" t="s">
         <v>1139</v>
@@ -22897,7 +22927,7 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G217" t="s">
         <v>1352</v>
@@ -23057,7 +23087,7 @@
         <v>705</v>
       </c>
       <c r="E222" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F222" t="s">
         <v>1339</v>
@@ -23182,7 +23212,7 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
@@ -23603,7 +23633,7 @@
         <v>723</v>
       </c>
       <c r="E240" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F240" t="s">
         <v>1165</v>
@@ -23641,7 +23671,7 @@
         <v>724</v>
       </c>
       <c r="E241" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G241" t="s">
         <v>1117</v>
@@ -23847,7 +23877,7 @@
         <v>731</v>
       </c>
       <c r="E248" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G248" t="s">
         <v>844</v>
@@ -23943,7 +23973,7 @@
         <v>734</v>
       </c>
       <c r="E251" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G251" t="s">
         <v>844</v>
@@ -24033,7 +24063,7 @@
         <v>737</v>
       </c>
       <c r="E254" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="F254" t="s">
         <v>1179</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9399AD-178B-481A-AC97-FD3D5094D8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA60F78-AAF2-4530-9F4C-1C1F8DB477C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4251" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4253" uniqueCount="1477">
   <si>
     <t>Sigla</t>
   </si>
@@ -4319,9 +4319,6 @@
     <t>Bishkek, Biscake</t>
   </si>
   <si>
-    <t>Un gerol wood</t>
-  </si>
-  <si>
     <t>Assunzione</t>
   </si>
   <si>
@@ -4464,6 +4461,15 @@
   </si>
   <si>
     <t>Bottom, de botto</t>
+  </si>
+  <si>
+    <t>Cigali</t>
+  </si>
+  <si>
+    <t>Un gerol wood, in garol wood</t>
+  </si>
+  <si>
+    <t>Faco</t>
   </si>
 </sst>
 </file>
@@ -16337,7 +16343,7 @@
         <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F3" t="s">
         <v>1195</v>
@@ -16511,7 +16517,7 @@
         <v>504</v>
       </c>
       <c r="E8" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G8" t="s">
         <v>888</v>
@@ -16633,7 +16639,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16894,7 +16900,7 @@
         <v>516</v>
       </c>
       <c r="E21" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G21" t="s">
         <v>888</v>
@@ -16984,7 +16990,7 @@
         <v>519</v>
       </c>
       <c r="E24" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="F24" t="s">
         <v>834</v>
@@ -17129,7 +17135,7 @@
         <v>525</v>
       </c>
       <c r="E29" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G29" t="s">
         <v>888</v>
@@ -17254,7 +17260,7 @@
         <v>529</v>
       </c>
       <c r="E33" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F33" t="s">
         <v>1031</v>
@@ -17350,7 +17356,7 @@
         <v>532</v>
       </c>
       <c r="E36" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F36" t="s">
         <v>826</v>
@@ -17385,7 +17391,7 @@
         <v>533</v>
       </c>
       <c r="E37" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F37" t="s">
         <v>929</v>
@@ -17862,7 +17868,7 @@
         <v>546</v>
       </c>
       <c r="E52" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F52" t="s">
         <v>965</v>
@@ -17978,7 +17984,7 @@
         <v>550</v>
       </c>
       <c r="E56" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="G56" t="s">
         <v>888</v>
@@ -18799,7 +18805,7 @@
         <v>575</v>
       </c>
       <c r="E84" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G84" t="s">
         <v>1117</v>
@@ -18976,7 +18982,7 @@
         <v>581</v>
       </c>
       <c r="E90" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F90" t="s">
         <v>1012</v>
@@ -19005,7 +19011,7 @@
         <v>948</v>
       </c>
       <c r="E91" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F91" t="s">
         <v>949</v>
@@ -19136,7 +19142,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -19514,7 +19520,7 @@
         <v>596</v>
       </c>
       <c r="E107" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="G107" t="s">
         <v>844</v>
@@ -19587,7 +19593,7 @@
         <v>598</v>
       </c>
       <c r="E109" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G109" t="s">
         <v>1402</v>
@@ -19648,7 +19654,7 @@
         <v>600</v>
       </c>
       <c r="E111" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="G111" t="s">
         <v>844</v>
@@ -19750,7 +19756,7 @@
         <v>604</v>
       </c>
       <c r="E114" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="G114" t="s">
         <v>1402</v>
@@ -19817,7 +19823,7 @@
         <v>606</v>
       </c>
       <c r="E116" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G116" t="s">
         <v>844</v>
@@ -19881,7 +19887,7 @@
         <v>607</v>
       </c>
       <c r="E118" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G118" t="s">
         <v>844</v>
@@ -20186,13 +20192,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D128" t="s">
         <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="F128" t="s">
         <v>1008</v>
@@ -20340,7 +20346,7 @@
         <v>622</v>
       </c>
       <c r="E133" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F133" t="s">
         <v>1018</v>
@@ -20790,7 +20796,7 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
@@ -21069,7 +21075,7 @@
         <v>523</v>
       </c>
       <c r="E157" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F157" t="s">
         <v>835</v>
@@ -21101,13 +21107,13 @@
         <v>149</v>
       </c>
       <c r="C158" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D158" t="s">
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21229,7 +21235,7 @@
         <v>651</v>
       </c>
       <c r="E162" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="F162" t="s">
         <v>1064</v>
@@ -21502,7 +21508,7 @@
         <v>660</v>
       </c>
       <c r="E171" t="s">
-        <v>1426</v>
+        <v>1475</v>
       </c>
       <c r="G171" t="s">
         <v>844</v>
@@ -21633,7 +21639,7 @@
         <v>663</v>
       </c>
       <c r="E175" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F175" t="s">
         <v>1092</v>
@@ -22079,6 +22085,9 @@
       <c r="D190" t="s">
         <v>677</v>
       </c>
+      <c r="E190" t="s">
+        <v>1474</v>
+      </c>
       <c r="F190" t="s">
         <v>1112</v>
       </c>
@@ -22138,7 +22147,7 @@
         <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G192" t="s">
         <v>1117</v>
@@ -22170,13 +22179,13 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D193" t="s">
         <v>680</v>
       </c>
       <c r="E193" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F193" t="s">
         <v>1118</v>
@@ -22278,7 +22287,7 @@
         <v>682</v>
       </c>
       <c r="E196" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
@@ -22342,7 +22351,7 @@
         <v>684</v>
       </c>
       <c r="E198" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F198" t="s">
         <v>1138</v>
@@ -22412,7 +22421,7 @@
         <v>686</v>
       </c>
       <c r="E200" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G200" t="s">
         <v>844</v>
@@ -22699,7 +22708,7 @@
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22737,7 +22746,7 @@
         <v>695</v>
       </c>
       <c r="E211" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F211" t="s">
         <v>1139</v>
@@ -22927,7 +22936,7 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G217" t="s">
         <v>1352</v>
@@ -22959,7 +22968,7 @@
         <v>640</v>
       </c>
       <c r="E218" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G218" t="s">
         <v>844</v>
@@ -23087,7 +23096,7 @@
         <v>705</v>
       </c>
       <c r="E222" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F222" t="s">
         <v>1339</v>
@@ -23212,7 +23221,7 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
@@ -23449,6 +23458,9 @@
       <c r="D234" t="s">
         <v>718</v>
       </c>
+      <c r="E234" t="s">
+        <v>1476</v>
+      </c>
       <c r="G234" t="s">
         <v>844</v>
       </c>
@@ -23482,7 +23494,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="G235" t="s">
         <v>844</v>
@@ -23633,7 +23645,7 @@
         <v>723</v>
       </c>
       <c r="E240" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="F240" t="s">
         <v>1165</v>
@@ -23671,7 +23683,7 @@
         <v>724</v>
       </c>
       <c r="E241" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G241" t="s">
         <v>1117</v>
@@ -23842,7 +23854,7 @@
         <v>730</v>
       </c>
       <c r="E247" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F247" t="s">
         <v>1170</v>
@@ -23877,7 +23889,7 @@
         <v>731</v>
       </c>
       <c r="E248" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G248" t="s">
         <v>844</v>
@@ -23973,7 +23985,7 @@
         <v>734</v>
       </c>
       <c r="E251" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G251" t="s">
         <v>844</v>
@@ -24063,7 +24075,7 @@
         <v>737</v>
       </c>
       <c r="E254" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F254" t="s">
         <v>1179</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA60F78-AAF2-4530-9F4C-1C1F8DB477C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88455983-06BC-4683-B34A-D47276E526D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4253" uniqueCount="1477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4258" uniqueCount="1484">
   <si>
     <t>Sigla</t>
   </si>
@@ -4418,9 +4418,6 @@
     <t>Irama</t>
   </si>
   <si>
-    <t>oranistad, oranistadt, orangestar</t>
-  </si>
-  <si>
     <t>Mary Anne,</t>
   </si>
   <si>
@@ -4457,9 +4454,6 @@
     <t>Bandar, bandarzeri begawan</t>
   </si>
   <si>
-    <t>Port au Prince, Port u prince</t>
-  </si>
-  <si>
     <t>Bottom, de botto</t>
   </si>
   <si>
@@ -4469,7 +4463,34 @@
     <t>Un gerol wood, in garol wood</t>
   </si>
   <si>
-    <t>Faco</t>
+    <t>Yaundé, Young</t>
+  </si>
+  <si>
+    <t>Faco, Vaccarofo</t>
+  </si>
+  <si>
+    <t>Port au Prince, Port u prince, Porto Prince</t>
+  </si>
+  <si>
+    <t>Cartoon</t>
+  </si>
+  <si>
+    <t>Numea, Lumea</t>
+  </si>
+  <si>
+    <t>James Brown</t>
+  </si>
+  <si>
+    <t>oranistad, oranistadt, orangestar, Orari estad</t>
+  </si>
+  <si>
+    <t>Maiott</t>
+  </si>
+  <si>
+    <t>Tributi</t>
+  </si>
+  <si>
+    <t>S eustatius, sintestatius</t>
   </si>
 </sst>
 </file>
@@ -4564,7 +4585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4577,10 +4598,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -16639,7 +16656,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1459</v>
+        <v>1480</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16900,7 +16917,7 @@
         <v>516</v>
       </c>
       <c r="E21" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="G21" t="s">
         <v>888</v>
@@ -17135,7 +17152,7 @@
         <v>525</v>
       </c>
       <c r="E29" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G29" t="s">
         <v>888</v>
@@ -17260,7 +17277,7 @@
         <v>529</v>
       </c>
       <c r="E33" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="F33" t="s">
         <v>1031</v>
@@ -17429,7 +17446,7 @@
         <v>534</v>
       </c>
       <c r="E38" t="s">
-        <v>855</v>
+        <v>1474</v>
       </c>
       <c r="F38" t="s">
         <v>856</v>
@@ -18711,8 +18728,14 @@
       <c r="B81" t="s">
         <v>78</v>
       </c>
+      <c r="C81" t="s">
+        <v>1482</v>
+      </c>
       <c r="D81" t="s">
         <v>78</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1482</v>
       </c>
       <c r="F81" t="s">
         <v>944</v>
@@ -19142,7 +19165,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -19593,7 +19616,7 @@
         <v>598</v>
       </c>
       <c r="E109" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G109" t="s">
         <v>1402</v>
@@ -19823,7 +19846,7 @@
         <v>606</v>
       </c>
       <c r="E116" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G116" t="s">
         <v>844</v>
@@ -20796,7 +20819,7 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
@@ -20850,6 +20873,9 @@
       <c r="B150" t="s">
         <v>142</v>
       </c>
+      <c r="C150" t="s">
+        <v>1481</v>
+      </c>
       <c r="D150" t="s">
         <v>638</v>
       </c>
@@ -21113,7 +21139,7 @@
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21235,7 +21261,7 @@
         <v>651</v>
       </c>
       <c r="E162" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="F162" t="s">
         <v>1064</v>
@@ -21357,7 +21383,7 @@
         <v>655</v>
       </c>
       <c r="E166" t="s">
-        <v>1080</v>
+        <v>1478</v>
       </c>
       <c r="G166" t="s">
         <v>844</v>
@@ -21508,7 +21534,7 @@
         <v>660</v>
       </c>
       <c r="E171" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="G171" t="s">
         <v>844</v>
@@ -22086,7 +22112,7 @@
         <v>677</v>
       </c>
       <c r="E190" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="F190" t="s">
         <v>1112</v>
@@ -22147,7 +22173,7 @@
         <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="G192" t="s">
         <v>1117</v>
@@ -22179,7 +22205,7 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D193" t="s">
         <v>680</v>
@@ -22287,7 +22313,7 @@
         <v>682</v>
       </c>
       <c r="E196" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
@@ -22478,6 +22504,9 @@
       <c r="D202" t="s">
         <v>738</v>
       </c>
+      <c r="E202" t="s">
+        <v>1479</v>
+      </c>
       <c r="G202" t="s">
         <v>1409</v>
       </c>
@@ -22702,13 +22731,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1191</v>
+        <v>1483</v>
       </c>
       <c r="D210" t="s">
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1459</v>
+        <v>1480</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22803,35 +22832,31 @@
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A213" s="10" t="s">
+      <c r="A213" t="s">
         <v>391</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B213" t="s">
         <v>197</v>
       </c>
-      <c r="C213" s="10"/>
-      <c r="D213" s="10" t="s">
+      <c r="D213" t="s">
         <v>697</v>
       </c>
-      <c r="E213" s="10"/>
-      <c r="F213" s="10" t="s">
+      <c r="F213" t="s">
         <v>1142</v>
       </c>
-      <c r="G213" s="10" t="s">
+      <c r="G213" t="s">
         <v>846</v>
       </c>
-      <c r="H213" s="10" t="s">
+      <c r="H213" t="s">
         <v>1115</v>
       </c>
-      <c r="I213" s="10"/>
-      <c r="J213" s="10" t="s">
+      <c r="J213" t="s">
         <v>1221</v>
       </c>
-      <c r="K213" s="10"/>
       <c r="L213" t="s">
         <v>1245</v>
       </c>
-      <c r="M213" s="11">
+      <c r="M213" s="1">
         <v>1</v>
       </c>
     </row>
@@ -23063,6 +23088,9 @@
       <c r="D221" t="s">
         <v>704</v>
       </c>
+      <c r="E221" t="s">
+        <v>1477</v>
+      </c>
       <c r="F221" t="s">
         <v>1150</v>
       </c>
@@ -23221,7 +23249,7 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
@@ -23459,7 +23487,7 @@
         <v>718</v>
       </c>
       <c r="E234" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="G234" t="s">
         <v>844</v>
@@ -23645,7 +23673,7 @@
         <v>723</v>
       </c>
       <c r="E240" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F240" t="s">
         <v>1165</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88455983-06BC-4683-B34A-D47276E526D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324B20C7-81D7-4735-8BCB-4361F946C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4258" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4270" uniqueCount="1498">
   <si>
     <t>Sigla</t>
   </si>
@@ -4214,9 +4214,6 @@
     <t>Tristan</t>
   </si>
   <si>
-    <t>Jersey</t>
-  </si>
-  <si>
     <t>Turks, Caicos</t>
   </si>
   <si>
@@ -4322,9 +4319,6 @@
     <t>Assunzione</t>
   </si>
   <si>
-    <t>el aiun, aaiun, Ela jun</t>
-  </si>
-  <si>
     <t>Valichir</t>
   </si>
   <si>
@@ -4481,9 +4475,6 @@
     <t>James Brown</t>
   </si>
   <si>
-    <t>oranistad, oranistadt, orangestar, Orari estad</t>
-  </si>
-  <si>
     <t>Maiott</t>
   </si>
   <si>
@@ -4491,6 +4482,57 @@
   </si>
   <si>
     <t>S eustatius, sintestatius</t>
+  </si>
+  <si>
+    <t>Drama là</t>
+  </si>
+  <si>
+    <t>Costa Avorio, D'avorio</t>
+  </si>
+  <si>
+    <t>Mamodzu, Mamotzu</t>
+  </si>
+  <si>
+    <t>Masero</t>
+  </si>
+  <si>
+    <t>oranistad, oranistadt, orangestar, Orari estad, Orangestadt</t>
+  </si>
+  <si>
+    <t>Buia</t>
+  </si>
+  <si>
+    <t>Roso</t>
+  </si>
+  <si>
+    <t>Lume</t>
+  </si>
+  <si>
+    <t>Luviana</t>
+  </si>
+  <si>
+    <t>Ma lì</t>
+  </si>
+  <si>
+    <t>Jersey, Sbagliato di Jersey</t>
+  </si>
+  <si>
+    <t>Ciao</t>
+  </si>
+  <si>
+    <t>Salvador</t>
+  </si>
+  <si>
+    <t>Cairo</t>
+  </si>
+  <si>
+    <t>el aiun, aaiun, Ela jun, Aiun</t>
+  </si>
+  <si>
+    <t>Anoi</t>
+  </si>
+  <si>
+    <t>Avana</t>
   </si>
 </sst>
 </file>
@@ -16333,7 +16375,7 @@
         <v>773</v>
       </c>
       <c r="J2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="L2" t="s">
         <v>1242</v>
@@ -16360,7 +16402,7 @@
         <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="F3" t="s">
         <v>1195</v>
@@ -16447,7 +16489,7 @@
         <v>757</v>
       </c>
       <c r="G5" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H5" t="s">
         <v>758</v>
@@ -16476,7 +16518,7 @@
         <v>828</v>
       </c>
       <c r="G6" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H6" t="s">
         <v>754</v>
@@ -16534,7 +16576,7 @@
         <v>504</v>
       </c>
       <c r="E8" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="G8" t="s">
         <v>888</v>
@@ -16633,10 +16675,10 @@
         <v>765</v>
       </c>
       <c r="G11" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H11" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="L11" t="s">
         <v>1245</v>
@@ -16656,7 +16698,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16691,7 +16733,7 @@
         <v>583</v>
       </c>
       <c r="G13" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H13" t="s">
         <v>1214</v>
@@ -16775,7 +16817,7 @@
         <v>887</v>
       </c>
       <c r="G16" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H16" t="s">
         <v>770</v>
@@ -16850,16 +16892,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1391</v>
+        <v>1491</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
       </c>
       <c r="E19" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="G19" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H19" t="s">
         <v>794</v>
@@ -16917,7 +16959,7 @@
         <v>516</v>
       </c>
       <c r="E21" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G21" t="s">
         <v>888</v>
@@ -16952,7 +16994,7 @@
         <v>1205</v>
       </c>
       <c r="G22" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H22" t="s">
         <v>799</v>
@@ -17007,13 +17049,13 @@
         <v>519</v>
       </c>
       <c r="E24" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="F24" t="s">
         <v>834</v>
       </c>
       <c r="G24" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H24" t="s">
         <v>801</v>
@@ -17152,7 +17194,7 @@
         <v>525</v>
       </c>
       <c r="E29" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="G29" t="s">
         <v>888</v>
@@ -17277,7 +17319,7 @@
         <v>529</v>
       </c>
       <c r="E33" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="F33" t="s">
         <v>1031</v>
@@ -17344,7 +17386,7 @@
         <v>820</v>
       </c>
       <c r="G35" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H35" t="s">
         <v>805</v>
@@ -17373,13 +17415,13 @@
         <v>532</v>
       </c>
       <c r="E36" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="F36" t="s">
         <v>826</v>
       </c>
       <c r="G36" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H36" t="s">
         <v>755</v>
@@ -17408,7 +17450,7 @@
         <v>533</v>
       </c>
       <c r="E37" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="F37" t="s">
         <v>929</v>
@@ -17446,7 +17488,7 @@
         <v>534</v>
       </c>
       <c r="E38" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="F38" t="s">
         <v>856</v>
@@ -17513,7 +17555,7 @@
         <v>536</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>858</v>
@@ -17635,7 +17677,7 @@
         <v>958</v>
       </c>
       <c r="G44" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H44" t="s">
         <v>864</v>
@@ -17664,7 +17706,7 @@
         <v>540</v>
       </c>
       <c r="G45" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H45" t="s">
         <v>866</v>
@@ -17754,7 +17796,7 @@
         <v>542</v>
       </c>
       <c r="G48" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H48" t="s">
         <v>872</v>
@@ -17815,7 +17857,7 @@
         <v>963</v>
       </c>
       <c r="G50" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H50" t="s">
         <v>767</v>
@@ -17853,7 +17895,7 @@
         <v>964</v>
       </c>
       <c r="G51" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H51" t="s">
         <v>881</v>
@@ -17879,19 +17921,19 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>884</v>
+        <v>1482</v>
       </c>
       <c r="D52" t="s">
         <v>546</v>
       </c>
       <c r="E52" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="F52" t="s">
         <v>965</v>
       </c>
       <c r="G52" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H52" t="s">
         <v>1067</v>
@@ -17971,6 +18013,9 @@
       <c r="D55" t="s">
         <v>549</v>
       </c>
+      <c r="E55" t="s">
+        <v>1497</v>
+      </c>
       <c r="G55" t="s">
         <v>888</v>
       </c>
@@ -17997,11 +18042,14 @@
       <c r="B56" t="s">
         <v>54</v>
       </c>
+      <c r="C56" t="s">
+        <v>1492</v>
+      </c>
       <c r="D56" t="s">
         <v>550</v>
       </c>
       <c r="E56" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G56" t="s">
         <v>888</v>
@@ -18039,7 +18087,7 @@
         <v>1344</v>
       </c>
       <c r="G57" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H57" t="s">
         <v>769</v>
@@ -18061,6 +18109,9 @@
       <c r="D58" t="s">
         <v>552</v>
       </c>
+      <c r="E58" t="s">
+        <v>1487</v>
+      </c>
       <c r="G58" t="s">
         <v>888</v>
       </c>
@@ -18119,6 +18170,9 @@
       <c r="D60" t="s">
         <v>554</v>
       </c>
+      <c r="E60" t="s">
+        <v>1494</v>
+      </c>
       <c r="F60" t="s">
         <v>894</v>
       </c>
@@ -18148,6 +18202,9 @@
       <c r="B61" t="s">
         <v>59</v>
       </c>
+      <c r="C61" t="s">
+        <v>1493</v>
+      </c>
       <c r="D61" t="s">
         <v>555</v>
       </c>
@@ -18216,7 +18273,7 @@
         <v>905</v>
       </c>
       <c r="G63" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H63" t="s">
         <v>906</v>
@@ -18245,7 +18302,7 @@
         <v>909</v>
       </c>
       <c r="G64" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H64" t="s">
         <v>907</v>
@@ -18271,7 +18328,7 @@
         <v>709</v>
       </c>
       <c r="E65" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F65" t="s">
         <v>1057</v>
@@ -18306,7 +18363,7 @@
         <v>915</v>
       </c>
       <c r="G66" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H66" t="s">
         <v>801</v>
@@ -18390,7 +18447,7 @@
         <v>917</v>
       </c>
       <c r="G69" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H69" t="s">
         <v>918</v>
@@ -18503,7 +18560,7 @@
         <v>925</v>
       </c>
       <c r="G73" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H73" t="s">
         <v>927</v>
@@ -18529,7 +18586,7 @@
         <v>931</v>
       </c>
       <c r="G74" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H74" t="s">
         <v>794</v>
@@ -18613,7 +18670,7 @@
         <v>969</v>
       </c>
       <c r="G77" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H77" t="s">
         <v>936</v>
@@ -18668,7 +18725,7 @@
         <v>572</v>
       </c>
       <c r="G79" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H79" t="s">
         <v>794</v>
@@ -18700,7 +18757,7 @@
         <v>938</v>
       </c>
       <c r="G80" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H80" t="s">
         <v>794</v>
@@ -18729,19 +18786,19 @@
         <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="D81" t="s">
         <v>78</v>
       </c>
       <c r="E81" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="F81" t="s">
         <v>944</v>
       </c>
       <c r="G81" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H81" t="s">
         <v>939</v>
@@ -18828,7 +18885,7 @@
         <v>575</v>
       </c>
       <c r="E84" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="G84" t="s">
         <v>1117</v>
@@ -18860,7 +18917,7 @@
         <v>576</v>
       </c>
       <c r="E85" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F85" t="s">
         <v>960</v>
@@ -18898,7 +18955,7 @@
         <v>941</v>
       </c>
       <c r="J86" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="K86" t="s">
         <v>494</v>
@@ -18979,7 +19036,7 @@
         <v>1298</v>
       </c>
       <c r="G89" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H89" t="s">
         <v>946</v>
@@ -19005,13 +19062,13 @@
         <v>581</v>
       </c>
       <c r="E90" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="F90" t="s">
         <v>1012</v>
       </c>
       <c r="G90" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H90" t="s">
         <v>811</v>
@@ -19034,7 +19091,7 @@
         <v>948</v>
       </c>
       <c r="E91" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="F91" t="s">
         <v>949</v>
@@ -19072,7 +19129,7 @@
         <v>951</v>
       </c>
       <c r="G92" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H92" t="s">
         <v>811</v>
@@ -19165,7 +19222,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -19232,7 +19289,7 @@
         <v>975</v>
       </c>
       <c r="G97" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H97" t="s">
         <v>769</v>
@@ -19424,7 +19481,7 @@
         <v>981</v>
       </c>
       <c r="G103" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H103" t="s">
         <v>1068</v>
@@ -19482,7 +19539,7 @@
         <v>983</v>
       </c>
       <c r="G105" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H105" t="s">
         <v>767</v>
@@ -19508,7 +19565,7 @@
         <v>595</v>
       </c>
       <c r="G106" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H106" t="s">
         <v>769</v>
@@ -19543,7 +19600,7 @@
         <v>596</v>
       </c>
       <c r="E107" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G107" t="s">
         <v>844</v>
@@ -19616,10 +19673,10 @@
         <v>598</v>
       </c>
       <c r="E109" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G109" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H109" t="s">
         <v>758</v>
@@ -19677,7 +19734,7 @@
         <v>600</v>
       </c>
       <c r="E111" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="G111" t="s">
         <v>844</v>
@@ -19779,10 +19836,10 @@
         <v>604</v>
       </c>
       <c r="E114" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="G114" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H114" t="s">
         <v>916</v>
@@ -19805,13 +19862,13 @@
         <v>108</v>
       </c>
       <c r="C115" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="D115" t="s">
         <v>605</v>
       </c>
       <c r="E115" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G115" t="s">
         <v>841</v>
@@ -19846,7 +19903,7 @@
         <v>606</v>
       </c>
       <c r="E116" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G116" t="s">
         <v>844</v>
@@ -19878,7 +19935,7 @@
         <v>597</v>
       </c>
       <c r="E117" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G117" t="s">
         <v>844</v>
@@ -19910,7 +19967,7 @@
         <v>607</v>
       </c>
       <c r="E118" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G118" t="s">
         <v>844</v>
@@ -20064,7 +20121,7 @@
         <v>998</v>
       </c>
       <c r="G123" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H123" t="s">
         <v>999</v>
@@ -20093,7 +20150,7 @@
         <v>1343</v>
       </c>
       <c r="G124" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H124" t="s">
         <v>1001</v>
@@ -20119,13 +20176,13 @@
         <v>614</v>
       </c>
       <c r="E125" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F125" t="s">
         <v>1002</v>
       </c>
       <c r="G125" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H125" t="s">
         <v>864</v>
@@ -20215,13 +20272,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="D128" t="s">
         <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="F128" t="s">
         <v>1008</v>
@@ -20281,6 +20338,9 @@
       <c r="D130" t="s">
         <v>619</v>
       </c>
+      <c r="E130" t="s">
+        <v>1484</v>
+      </c>
       <c r="F130" t="s">
         <v>1058</v>
       </c>
@@ -20314,7 +20374,7 @@
         <v>1015</v>
       </c>
       <c r="G131" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H131" t="s">
         <v>769</v>
@@ -20369,13 +20429,13 @@
         <v>622</v>
       </c>
       <c r="E133" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F133" t="s">
         <v>1018</v>
       </c>
       <c r="G133" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H133" t="s">
         <v>916</v>
@@ -20471,7 +20531,7 @@
         <v>1049</v>
       </c>
       <c r="G136" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H136" t="s">
         <v>807</v>
@@ -20497,7 +20557,7 @@
         <v>1024</v>
       </c>
       <c r="G137" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H137" t="s">
         <v>1025</v>
@@ -20523,7 +20583,7 @@
         <v>975</v>
       </c>
       <c r="G138" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H138" t="s">
         <v>778</v>
@@ -20587,7 +20647,7 @@
         <v>628</v>
       </c>
       <c r="G140" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H140" t="s">
         <v>1026</v>
@@ -20610,7 +20670,7 @@
         <v>1027</v>
       </c>
       <c r="G141" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H141" t="s">
         <v>1023</v>
@@ -20673,6 +20733,9 @@
       <c r="D143" t="s">
         <v>631</v>
       </c>
+      <c r="E143" t="s">
+        <v>1490</v>
+      </c>
       <c r="G143" t="s">
         <v>1352</v>
       </c>
@@ -20706,7 +20769,7 @@
         <v>1034</v>
       </c>
       <c r="G144" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H144" t="s">
         <v>801</v>
@@ -20819,13 +20882,13 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
       </c>
       <c r="G148" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H148" t="s">
         <v>805</v>
@@ -20854,7 +20917,7 @@
         <v>637</v>
       </c>
       <c r="G149" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H149" t="s">
         <v>1038</v>
@@ -20874,16 +20937,16 @@
         <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="D150" t="s">
         <v>638</v>
       </c>
       <c r="E150" t="s">
-        <v>1215</v>
+        <v>1483</v>
       </c>
       <c r="G150" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H150" t="s">
         <v>916</v>
@@ -20982,7 +21045,7 @@
         <v>1040</v>
       </c>
       <c r="G153" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H153" t="s">
         <v>800</v>
@@ -21072,7 +21135,7 @@
         <v>1059</v>
       </c>
       <c r="G156" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H156" t="s">
         <v>1041</v>
@@ -21101,7 +21164,7 @@
         <v>523</v>
       </c>
       <c r="E157" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="F157" t="s">
         <v>835</v>
@@ -21133,13 +21196,13 @@
         <v>149</v>
       </c>
       <c r="C158" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D158" t="s">
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21261,13 +21324,13 @@
         <v>651</v>
       </c>
       <c r="E162" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F162" t="s">
         <v>1064</v>
       </c>
       <c r="G162" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H162" t="s">
         <v>1067</v>
@@ -21295,11 +21358,14 @@
       <c r="D163" t="s">
         <v>652</v>
       </c>
+      <c r="E163" t="s">
+        <v>1486</v>
+      </c>
       <c r="F163" t="s">
         <v>1070</v>
       </c>
       <c r="G163" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H163" t="s">
         <v>764</v>
@@ -21357,7 +21423,7 @@
         <v>1072</v>
       </c>
       <c r="G165" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H165" t="s">
         <v>785</v>
@@ -21383,7 +21449,7 @@
         <v>655</v>
       </c>
       <c r="E166" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="G166" t="s">
         <v>844</v>
@@ -21479,7 +21545,7 @@
         <v>1082</v>
       </c>
       <c r="G169" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H169" t="s">
         <v>785</v>
@@ -21534,7 +21600,7 @@
         <v>660</v>
       </c>
       <c r="E171" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="G171" t="s">
         <v>844</v>
@@ -21565,6 +21631,9 @@
       <c r="D172" t="s">
         <v>661</v>
       </c>
+      <c r="E172" t="s">
+        <v>1481</v>
+      </c>
       <c r="F172" t="s">
         <v>1345</v>
       </c>
@@ -21665,7 +21734,7 @@
         <v>663</v>
       </c>
       <c r="E175" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F175" t="s">
         <v>1092</v>
@@ -21720,7 +21789,7 @@
         <v>167</v>
       </c>
       <c r="C177" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D177" t="s">
         <v>665</v>
@@ -21816,7 +21885,7 @@
         <v>938</v>
       </c>
       <c r="G180" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H180" t="s">
         <v>796</v>
@@ -21900,7 +21969,7 @@
         <v>982</v>
       </c>
       <c r="G183" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H183" t="s">
         <v>859</v>
@@ -21990,7 +22059,7 @@
         <v>1202</v>
       </c>
       <c r="C186" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D186" t="s">
         <v>688</v>
@@ -22063,7 +22132,7 @@
         <v>1109</v>
       </c>
       <c r="G188" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H188" t="s">
         <v>1110</v>
@@ -22112,13 +22181,13 @@
         <v>677</v>
       </c>
       <c r="E190" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="F190" t="s">
         <v>1112</v>
       </c>
       <c r="G190" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H190" t="s">
         <v>1113</v>
@@ -22173,7 +22242,7 @@
         <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="G192" t="s">
         <v>1117</v>
@@ -22205,13 +22274,13 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="D193" t="s">
         <v>680</v>
       </c>
       <c r="E193" t="s">
-        <v>1427</v>
+        <v>1495</v>
       </c>
       <c r="F193" t="s">
         <v>1118</v>
@@ -22313,7 +22382,7 @@
         <v>682</v>
       </c>
       <c r="E196" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
@@ -22377,7 +22446,7 @@
         <v>684</v>
       </c>
       <c r="E198" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="F198" t="s">
         <v>1138</v>
@@ -22447,7 +22516,7 @@
         <v>686</v>
       </c>
       <c r="E200" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G200" t="s">
         <v>844</v>
@@ -22505,10 +22574,10 @@
         <v>738</v>
       </c>
       <c r="E202" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="G202" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H202" t="s">
         <v>1214</v>
@@ -22601,7 +22670,7 @@
         <v>1301</v>
       </c>
       <c r="G205" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H205" t="s">
         <v>801</v>
@@ -22659,7 +22728,7 @@
         <v>586</v>
       </c>
       <c r="G207" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H207" t="s">
         <v>1283</v>
@@ -22682,7 +22751,7 @@
         <v>1135</v>
       </c>
       <c r="G208" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H208" t="s">
         <v>1136</v>
@@ -22731,13 +22800,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="D210" t="s">
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22775,7 +22844,7 @@
         <v>695</v>
       </c>
       <c r="E211" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F211" t="s">
         <v>1139</v>
@@ -22870,6 +22939,9 @@
       <c r="D214" t="s">
         <v>698</v>
       </c>
+      <c r="E214" t="s">
+        <v>1489</v>
+      </c>
       <c r="F214" t="s">
         <v>1143</v>
       </c>
@@ -22903,7 +22975,7 @@
         <v>1144</v>
       </c>
       <c r="G215" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H215" t="s">
         <v>786</v>
@@ -22935,7 +23007,7 @@
         <v>1341</v>
       </c>
       <c r="G216" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H216" t="s">
         <v>864</v>
@@ -22961,7 +23033,7 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="G217" t="s">
         <v>1352</v>
@@ -22993,7 +23065,7 @@
         <v>640</v>
       </c>
       <c r="E218" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="G218" t="s">
         <v>844</v>
@@ -23089,7 +23161,7 @@
         <v>704</v>
       </c>
       <c r="E221" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="F221" t="s">
         <v>1150</v>
@@ -23124,13 +23196,13 @@
         <v>705</v>
       </c>
       <c r="E222" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="F222" t="s">
         <v>1339</v>
       </c>
       <c r="G222" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H222" t="s">
         <v>1152</v>
@@ -23194,7 +23266,7 @@
         <v>1154</v>
       </c>
       <c r="G224" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H224" t="s">
         <v>797</v>
@@ -23249,13 +23321,13 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
       </c>
       <c r="G226" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H226" t="s">
         <v>1017</v>
@@ -23284,7 +23356,7 @@
         <v>711</v>
       </c>
       <c r="G227" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H227" t="s">
         <v>942</v>
@@ -23316,7 +23388,7 @@
         <v>1156</v>
       </c>
       <c r="G228" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H228" t="s">
         <v>1157</v>
@@ -23454,11 +23526,14 @@
       <c r="D233" t="s">
         <v>717</v>
       </c>
+      <c r="E233" t="s">
+        <v>1488</v>
+      </c>
       <c r="F233" t="s">
         <v>1160</v>
       </c>
       <c r="G233" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H233" t="s">
         <v>1161</v>
@@ -23487,7 +23562,7 @@
         <v>718</v>
       </c>
       <c r="E234" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="G234" t="s">
         <v>844</v>
@@ -23522,7 +23597,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="G235" t="s">
         <v>844</v>
@@ -23548,7 +23623,7 @@
         <v>218</v>
       </c>
       <c r="C236" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D236" t="s">
         <v>720</v>
@@ -23580,7 +23655,7 @@
         <v>1181</v>
       </c>
       <c r="G237" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H237" t="s">
         <v>1214</v>
@@ -23644,7 +23719,7 @@
         <v>1338</v>
       </c>
       <c r="G239" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H239" t="s">
         <v>769</v>
@@ -23673,13 +23748,13 @@
         <v>723</v>
       </c>
       <c r="E240" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="F240" t="s">
         <v>1165</v>
       </c>
       <c r="G240" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H240" t="s">
         <v>796</v>
@@ -23705,13 +23780,13 @@
         <v>222</v>
       </c>
       <c r="C241" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D241" t="s">
         <v>724</v>
       </c>
       <c r="E241" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G241" t="s">
         <v>1117</v>
@@ -23798,7 +23873,7 @@
         <v>1167</v>
       </c>
       <c r="G244" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H244" t="s">
         <v>799</v>
@@ -23882,13 +23957,13 @@
         <v>730</v>
       </c>
       <c r="E247" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="F247" t="s">
         <v>1170</v>
       </c>
       <c r="G247" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H247" t="s">
         <v>1171</v>
@@ -23917,7 +23992,7 @@
         <v>731</v>
       </c>
       <c r="E248" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="G248" t="s">
         <v>844</v>
@@ -23977,6 +24052,9 @@
       <c r="D250" t="s">
         <v>733</v>
       </c>
+      <c r="E250" t="s">
+        <v>1496</v>
+      </c>
       <c r="F250" t="s">
         <v>1175</v>
       </c>
@@ -24007,13 +24085,13 @@
         <v>232</v>
       </c>
       <c r="C251" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D251" t="s">
         <v>734</v>
       </c>
       <c r="E251" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="G251" t="s">
         <v>844</v>
@@ -24077,7 +24155,7 @@
         <v>1342</v>
       </c>
       <c r="G253" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H253" t="s">
         <v>1177</v>
@@ -24103,13 +24181,13 @@
         <v>737</v>
       </c>
       <c r="E254" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="F254" t="s">
         <v>1179</v>
       </c>
       <c r="G254" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H254" t="s">
         <v>1180</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324B20C7-81D7-4735-8BCB-4361F946C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F692A11F-4918-4608-893A-9DE6EA250F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4270" uniqueCount="1498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1500">
   <si>
     <t>Sigla</t>
   </si>
@@ -4313,18 +4313,12 @@
     <t>Adam's Town</t>
   </si>
   <si>
-    <t>Bishkek, Biscake</t>
-  </si>
-  <si>
     <t>Assunzione</t>
   </si>
   <si>
     <t>Valichir</t>
   </si>
   <si>
-    <t>Nuku alofa, Mutualopa</t>
-  </si>
-  <si>
     <t>Taschent</t>
   </si>
   <si>
@@ -4421,9 +4415,6 @@
     <t>King's Town</t>
   </si>
   <si>
-    <t>Dujabbe</t>
-  </si>
-  <si>
     <t>Azkaban, Azkabat</t>
   </si>
   <si>
@@ -4439,9 +4430,6 @@
     <t>Maiuro</t>
   </si>
   <si>
-    <t>Nuakchot, No rock shot</t>
-  </si>
-  <si>
     <t>Mia Mail, Nia may</t>
   </si>
   <si>
@@ -4451,9 +4439,6 @@
     <t>Bottom, de botto</t>
   </si>
   <si>
-    <t>Cigali</t>
-  </si>
-  <si>
     <t>Un gerol wood, in garol wood</t>
   </si>
   <si>
@@ -4533,6 +4518,27 @@
   </si>
   <si>
     <t>Avana</t>
+  </si>
+  <si>
+    <t>Bangiul, Bonjour</t>
+  </si>
+  <si>
+    <t>Porti Lui</t>
+  </si>
+  <si>
+    <t>Dujabbe, Due gambe</t>
+  </si>
+  <si>
+    <t>Nuku alofa, Mutualopa, Nukolov</t>
+  </si>
+  <si>
+    <t>Bishkek, Biscake, Bistecca</t>
+  </si>
+  <si>
+    <t>Cigali, Cialis</t>
+  </si>
+  <si>
+    <t>Nuakchot, No rock shot, Workshop, mokchott</t>
   </si>
 </sst>
 </file>
@@ -16402,7 +16408,7 @@
         <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F3" t="s">
         <v>1195</v>
@@ -16576,7 +16582,7 @@
         <v>504</v>
       </c>
       <c r="E8" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G8" t="s">
         <v>888</v>
@@ -16698,7 +16704,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16892,7 +16898,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
@@ -16959,7 +16965,7 @@
         <v>516</v>
       </c>
       <c r="E21" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="G21" t="s">
         <v>888</v>
@@ -17049,7 +17055,7 @@
         <v>519</v>
       </c>
       <c r="E24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="F24" t="s">
         <v>834</v>
@@ -17103,6 +17109,9 @@
       <c r="D26" t="s">
         <v>521</v>
       </c>
+      <c r="E26" t="s">
+        <v>416</v>
+      </c>
       <c r="F26" t="s">
         <v>802</v>
       </c>
@@ -17194,7 +17203,7 @@
         <v>525</v>
       </c>
       <c r="E29" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="G29" t="s">
         <v>888</v>
@@ -17319,7 +17328,7 @@
         <v>529</v>
       </c>
       <c r="E33" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="F33" t="s">
         <v>1031</v>
@@ -17415,7 +17424,7 @@
         <v>532</v>
       </c>
       <c r="E36" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="F36" t="s">
         <v>826</v>
@@ -17450,7 +17459,7 @@
         <v>533</v>
       </c>
       <c r="E37" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="F37" t="s">
         <v>929</v>
@@ -17488,7 +17497,7 @@
         <v>534</v>
       </c>
       <c r="E38" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="s">
         <v>856</v>
@@ -17921,13 +17930,13 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="D52" t="s">
         <v>546</v>
       </c>
       <c r="E52" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F52" t="s">
         <v>965</v>
@@ -18014,7 +18023,7 @@
         <v>549</v>
       </c>
       <c r="E55" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="G55" t="s">
         <v>888</v>
@@ -18043,13 +18052,13 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="D56" t="s">
         <v>550</v>
       </c>
       <c r="E56" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="G56" t="s">
         <v>888</v>
@@ -18110,7 +18119,7 @@
         <v>552</v>
       </c>
       <c r="E58" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="G58" t="s">
         <v>888</v>
@@ -18171,7 +18180,7 @@
         <v>554</v>
       </c>
       <c r="E60" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F60" t="s">
         <v>894</v>
@@ -18203,7 +18212,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="D61" t="s">
         <v>555</v>
@@ -18554,7 +18563,7 @@
         <v>566</v>
       </c>
       <c r="E73" t="s">
-        <v>928</v>
+        <v>1493</v>
       </c>
       <c r="F73" t="s">
         <v>925</v>
@@ -18786,13 +18795,13 @@
         <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="D81" t="s">
         <v>78</v>
       </c>
       <c r="E81" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="F81" t="s">
         <v>944</v>
@@ -18885,7 +18894,7 @@
         <v>575</v>
       </c>
       <c r="E84" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="G84" t="s">
         <v>1117</v>
@@ -19062,7 +19071,7 @@
         <v>581</v>
       </c>
       <c r="E90" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="F90" t="s">
         <v>1012</v>
@@ -19091,7 +19100,7 @@
         <v>948</v>
       </c>
       <c r="E91" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="F91" t="s">
         <v>949</v>
@@ -19222,7 +19231,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -19600,7 +19609,7 @@
         <v>596</v>
       </c>
       <c r="E107" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G107" t="s">
         <v>844</v>
@@ -19673,7 +19682,7 @@
         <v>598</v>
       </c>
       <c r="E109" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G109" t="s">
         <v>1401</v>
@@ -19734,7 +19743,7 @@
         <v>600</v>
       </c>
       <c r="E111" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="G111" t="s">
         <v>844</v>
@@ -19836,7 +19845,7 @@
         <v>604</v>
       </c>
       <c r="E114" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="G114" t="s">
         <v>1401</v>
@@ -19903,7 +19912,7 @@
         <v>606</v>
       </c>
       <c r="E116" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="G116" t="s">
         <v>844</v>
@@ -19967,7 +19976,7 @@
         <v>607</v>
       </c>
       <c r="E118" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G118" t="s">
         <v>844</v>
@@ -20176,7 +20185,7 @@
         <v>614</v>
       </c>
       <c r="E125" t="s">
-        <v>1424</v>
+        <v>1497</v>
       </c>
       <c r="F125" t="s">
         <v>1002</v>
@@ -20272,13 +20281,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="D128" t="s">
         <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="F128" t="s">
         <v>1008</v>
@@ -20339,7 +20348,7 @@
         <v>619</v>
       </c>
       <c r="E130" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="F130" t="s">
         <v>1058</v>
@@ -20429,7 +20438,7 @@
         <v>622</v>
       </c>
       <c r="E133" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="F133" t="s">
         <v>1018</v>
@@ -20734,7 +20743,7 @@
         <v>631</v>
       </c>
       <c r="E143" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="G143" t="s">
         <v>1352</v>
@@ -20882,7 +20891,7 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1466</v>
+        <v>1499</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
@@ -20916,6 +20925,9 @@
       <c r="D149" t="s">
         <v>637</v>
       </c>
+      <c r="E149" t="s">
+        <v>1494</v>
+      </c>
       <c r="G149" t="s">
         <v>1406</v>
       </c>
@@ -20937,13 +20949,13 @@
         <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="D150" t="s">
         <v>638</v>
       </c>
       <c r="E150" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="G150" t="s">
         <v>1406</v>
@@ -21164,7 +21176,7 @@
         <v>523</v>
       </c>
       <c r="E157" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="F157" t="s">
         <v>835</v>
@@ -21196,13 +21208,13 @@
         <v>149</v>
       </c>
       <c r="C158" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="D158" t="s">
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21324,7 +21336,7 @@
         <v>651</v>
       </c>
       <c r="E162" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="F162" t="s">
         <v>1064</v>
@@ -21359,7 +21371,7 @@
         <v>652</v>
       </c>
       <c r="E163" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="F163" t="s">
         <v>1070</v>
@@ -21449,7 +21461,7 @@
         <v>655</v>
       </c>
       <c r="E166" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="G166" t="s">
         <v>844</v>
@@ -21600,7 +21612,7 @@
         <v>660</v>
       </c>
       <c r="E171" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="G171" t="s">
         <v>844</v>
@@ -21632,7 +21644,7 @@
         <v>661</v>
       </c>
       <c r="E172" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F172" t="s">
         <v>1345</v>
@@ -21734,7 +21746,7 @@
         <v>663</v>
       </c>
       <c r="E175" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F175" t="s">
         <v>1092</v>
@@ -22181,7 +22193,7 @@
         <v>677</v>
       </c>
       <c r="E190" t="s">
-        <v>1470</v>
+        <v>1498</v>
       </c>
       <c r="F190" t="s">
         <v>1112</v>
@@ -22242,7 +22254,7 @@
         <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="G192" t="s">
         <v>1117</v>
@@ -22274,13 +22286,13 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="D193" t="s">
         <v>680</v>
       </c>
       <c r="E193" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="F193" t="s">
         <v>1118</v>
@@ -22382,7 +22394,7 @@
         <v>682</v>
       </c>
       <c r="E196" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
@@ -22446,7 +22458,7 @@
         <v>684</v>
       </c>
       <c r="E198" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="F198" t="s">
         <v>1138</v>
@@ -22516,7 +22528,7 @@
         <v>686</v>
       </c>
       <c r="E200" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G200" t="s">
         <v>844</v>
@@ -22574,7 +22586,7 @@
         <v>738</v>
       </c>
       <c r="E202" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="G202" t="s">
         <v>1408</v>
@@ -22800,13 +22812,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="D210" t="s">
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22844,7 +22856,7 @@
         <v>695</v>
       </c>
       <c r="E211" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F211" t="s">
         <v>1139</v>
@@ -22940,7 +22952,7 @@
         <v>698</v>
       </c>
       <c r="E214" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F214" t="s">
         <v>1143</v>
@@ -23033,7 +23045,7 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="G217" t="s">
         <v>1352</v>
@@ -23065,7 +23077,7 @@
         <v>640</v>
       </c>
       <c r="E218" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G218" t="s">
         <v>844</v>
@@ -23161,7 +23173,7 @@
         <v>704</v>
       </c>
       <c r="E221" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F221" t="s">
         <v>1150</v>
@@ -23196,7 +23208,7 @@
         <v>705</v>
       </c>
       <c r="E222" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="F222" t="s">
         <v>1339</v>
@@ -23321,7 +23333,7 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1460</v>
+        <v>1495</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
@@ -23527,7 +23539,7 @@
         <v>717</v>
       </c>
       <c r="E233" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F233" t="s">
         <v>1160</v>
@@ -23562,7 +23574,7 @@
         <v>718</v>
       </c>
       <c r="E234" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="G234" t="s">
         <v>844</v>
@@ -23597,7 +23609,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1427</v>
+        <v>1496</v>
       </c>
       <c r="G235" t="s">
         <v>844</v>
@@ -23748,7 +23760,7 @@
         <v>723</v>
       </c>
       <c r="E240" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="F240" t="s">
         <v>1165</v>
@@ -23786,7 +23798,7 @@
         <v>724</v>
       </c>
       <c r="E241" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G241" t="s">
         <v>1117</v>
@@ -23957,7 +23969,7 @@
         <v>730</v>
       </c>
       <c r="E247" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="F247" t="s">
         <v>1170</v>
@@ -23992,7 +24004,7 @@
         <v>731</v>
       </c>
       <c r="E248" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G248" t="s">
         <v>844</v>
@@ -24053,7 +24065,7 @@
         <v>733</v>
       </c>
       <c r="E250" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F250" t="s">
         <v>1175</v>
@@ -24091,7 +24103,7 @@
         <v>734</v>
       </c>
       <c r="E251" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G251" t="s">
         <v>844</v>
@@ -24181,7 +24193,7 @@
         <v>737</v>
       </c>
       <c r="E254" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="F254" t="s">
         <v>1179</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F692A11F-4918-4608-893A-9DE6EA250F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F53B51-199B-4B85-9D8E-929EDB66BAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="1505">
   <si>
     <t>Sigla</t>
   </si>
@@ -4439,9 +4439,6 @@
     <t>Bottom, de botto</t>
   </si>
   <si>
-    <t>Un gerol wood, in garol wood</t>
-  </si>
-  <si>
     <t>Yaundé, Young</t>
   </si>
   <si>
@@ -4539,6 +4536,24 @@
   </si>
   <si>
     <t>Nuakchot, No rock shot, Workshop, mokchott</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>Sao Tome, Sao to me, Ciao tome</t>
+  </si>
+  <si>
+    <t>Un gerol wood, in garol wood, garolwood</t>
+  </si>
+  <si>
+    <t>azerbaijan</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>Malesia, Alessia</t>
   </si>
 </sst>
 </file>
@@ -16704,7 +16719,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16816,6 +16831,9 @@
       <c r="B16" t="s">
         <v>15</v>
       </c>
+      <c r="C16" t="s">
+        <v>1502</v>
+      </c>
       <c r="D16" t="s">
         <v>509</v>
       </c>
@@ -16898,7 +16916,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
@@ -17497,7 +17515,7 @@
         <v>534</v>
       </c>
       <c r="E38" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F38" t="s">
         <v>856</v>
@@ -17930,7 +17948,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="D52" t="s">
         <v>546</v>
@@ -18023,7 +18041,7 @@
         <v>549</v>
       </c>
       <c r="E55" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="G55" t="s">
         <v>888</v>
@@ -18052,7 +18070,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D56" t="s">
         <v>550</v>
@@ -18119,7 +18137,7 @@
         <v>552</v>
       </c>
       <c r="E58" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="G58" t="s">
         <v>888</v>
@@ -18180,7 +18198,7 @@
         <v>554</v>
       </c>
       <c r="E60" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="F60" t="s">
         <v>894</v>
@@ -18212,7 +18230,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D61" t="s">
         <v>555</v>
@@ -18563,7 +18581,7 @@
         <v>566</v>
       </c>
       <c r="E73" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="F73" t="s">
         <v>925</v>
@@ -18672,6 +18690,9 @@
       <c r="B77" t="s">
         <v>74</v>
       </c>
+      <c r="C77" t="s">
+        <v>1503</v>
+      </c>
       <c r="D77" t="s">
         <v>570</v>
       </c>
@@ -18795,13 +18816,13 @@
         <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="D81" t="s">
         <v>78</v>
       </c>
       <c r="E81" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="F81" t="s">
         <v>944</v>
@@ -19231,7 +19252,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -20185,7 +20206,7 @@
         <v>614</v>
       </c>
       <c r="E125" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F125" t="s">
         <v>1002</v>
@@ -20348,7 +20369,7 @@
         <v>619</v>
       </c>
       <c r="E130" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F130" t="s">
         <v>1058</v>
@@ -20705,7 +20726,7 @@
         <v>335</v>
       </c>
       <c r="C142" t="s">
-        <v>1030</v>
+        <v>1504</v>
       </c>
       <c r="D142" t="s">
         <v>630</v>
@@ -20743,7 +20764,7 @@
         <v>631</v>
       </c>
       <c r="E143" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G143" t="s">
         <v>1352</v>
@@ -20891,7 +20912,7 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
@@ -20926,7 +20947,7 @@
         <v>637</v>
       </c>
       <c r="E149" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="G149" t="s">
         <v>1406</v>
@@ -20949,13 +20970,13 @@
         <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="D150" t="s">
         <v>638</v>
       </c>
       <c r="E150" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G150" t="s">
         <v>1406</v>
@@ -21371,7 +21392,7 @@
         <v>652</v>
       </c>
       <c r="E163" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F163" t="s">
         <v>1070</v>
@@ -21461,7 +21482,7 @@
         <v>655</v>
       </c>
       <c r="E166" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G166" t="s">
         <v>844</v>
@@ -21521,6 +21542,9 @@
       <c r="B168" t="s">
         <v>159</v>
       </c>
+      <c r="C168" t="s">
+        <v>1499</v>
+      </c>
       <c r="D168" t="s">
         <v>658</v>
       </c>
@@ -21612,7 +21636,7 @@
         <v>660</v>
       </c>
       <c r="E171" t="s">
-        <v>1466</v>
+        <v>1501</v>
       </c>
       <c r="G171" t="s">
         <v>844</v>
@@ -21644,7 +21668,7 @@
         <v>661</v>
       </c>
       <c r="E172" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="F172" t="s">
         <v>1345</v>
@@ -22193,7 +22217,7 @@
         <v>677</v>
       </c>
       <c r="E190" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F190" t="s">
         <v>1112</v>
@@ -22292,7 +22316,7 @@
         <v>680</v>
       </c>
       <c r="E193" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F193" t="s">
         <v>1118</v>
@@ -22586,7 +22610,7 @@
         <v>738</v>
       </c>
       <c r="E202" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G202" t="s">
         <v>1408</v>
@@ -22612,13 +22636,13 @@
         <v>188</v>
       </c>
       <c r="C203" t="s">
-        <v>1130</v>
+        <v>1500</v>
       </c>
       <c r="D203" t="s">
         <v>690</v>
       </c>
       <c r="E203" t="s">
-        <v>1130</v>
+        <v>1500</v>
       </c>
       <c r="G203" t="s">
         <v>1353</v>
@@ -22812,13 +22836,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="D210" t="s">
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22952,7 +22976,7 @@
         <v>698</v>
       </c>
       <c r="E214" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F214" t="s">
         <v>1143</v>
@@ -23173,7 +23197,7 @@
         <v>704</v>
       </c>
       <c r="E221" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="F221" t="s">
         <v>1150</v>
@@ -23333,7 +23357,7 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
@@ -23539,7 +23563,7 @@
         <v>717</v>
       </c>
       <c r="E233" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="F233" t="s">
         <v>1160</v>
@@ -23574,7 +23598,7 @@
         <v>718</v>
       </c>
       <c r="E234" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G234" t="s">
         <v>844</v>
@@ -23609,7 +23633,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G235" t="s">
         <v>844</v>
@@ -24065,7 +24089,7 @@
         <v>733</v>
       </c>
       <c r="E250" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F250" t="s">
         <v>1175</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F53B51-199B-4B85-9D8E-929EDB66BAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB083DB5-A786-4D65-BB88-FBB275438593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="1505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="1514">
   <si>
     <t>Sigla</t>
   </si>
@@ -4337,15 +4337,9 @@
     <t>Dillendstadt</t>
   </si>
   <si>
-    <t>st george's, st george, saint george, Giorgis</t>
-  </si>
-  <si>
     <t>Flying Fish Club</t>
   </si>
   <si>
-    <t>Dr Shadn</t>
-  </si>
-  <si>
     <t>Onyara</t>
   </si>
   <si>
@@ -4439,9 +4433,6 @@
     <t>Bottom, de botto</t>
   </si>
   <si>
-    <t>Yaundé, Young</t>
-  </si>
-  <si>
     <t>Faco, Vaccarofo</t>
   </si>
   <si>
@@ -4457,15 +4448,9 @@
     <t>James Brown</t>
   </si>
   <si>
-    <t>Maiott</t>
-  </si>
-  <si>
     <t>Tributi</t>
   </si>
   <si>
-    <t>S eustatius, sintestatius</t>
-  </si>
-  <si>
     <t>Drama là</t>
   </si>
   <si>
@@ -4554,6 +4539,48 @@
   </si>
   <si>
     <t>Malesia, Alessia</t>
+  </si>
+  <si>
+    <t>Saint Pierre, S Pierre, Miquelon, san pierre michelon</t>
+  </si>
+  <si>
+    <t>st george's, st george, saint george, Giorgis, sangiorgis</t>
+  </si>
+  <si>
+    <t>S eustatius, sintestatius, sintastatius</t>
+  </si>
+  <si>
+    <t>Gigi</t>
+  </si>
+  <si>
+    <t>Repubblica Ceca, Rep Ceca, Cecchia</t>
+  </si>
+  <si>
+    <t>Maiott, Mariott, Mariotti, Mylot</t>
+  </si>
+  <si>
+    <t>Una foti,</t>
+  </si>
+  <si>
+    <t>Dr Shadn, thor charme</t>
+  </si>
+  <si>
+    <t>livrevilla</t>
+  </si>
+  <si>
+    <t>managya</t>
+  </si>
+  <si>
+    <t>tempo, tv</t>
+  </si>
+  <si>
+    <t>Vadux</t>
+  </si>
+  <si>
+    <t>Yaundé, Young, Yaounfe</t>
+  </si>
+  <si>
+    <t>jaren</t>
   </si>
 </sst>
 </file>
@@ -16423,7 +16450,7 @@
         <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="F3" t="s">
         <v>1195</v>
@@ -16719,7 +16746,7 @@
         <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="G12" t="s">
         <v>888</v>
@@ -16832,7 +16859,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="D16" t="s">
         <v>509</v>
@@ -16916,7 +16943,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
@@ -16983,7 +17010,7 @@
         <v>516</v>
       </c>
       <c r="E21" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G21" t="s">
         <v>888</v>
@@ -17128,7 +17155,7 @@
         <v>521</v>
       </c>
       <c r="E26" t="s">
-        <v>416</v>
+        <v>1510</v>
       </c>
       <c r="F26" t="s">
         <v>802</v>
@@ -17221,7 +17248,7 @@
         <v>525</v>
       </c>
       <c r="E29" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G29" t="s">
         <v>888</v>
@@ -17346,7 +17373,7 @@
         <v>529</v>
       </c>
       <c r="E33" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="F33" t="s">
         <v>1031</v>
@@ -17442,7 +17469,7 @@
         <v>532</v>
       </c>
       <c r="E36" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="F36" t="s">
         <v>826</v>
@@ -17515,7 +17542,7 @@
         <v>534</v>
       </c>
       <c r="E38" t="s">
-        <v>1466</v>
+        <v>1512</v>
       </c>
       <c r="F38" t="s">
         <v>856</v>
@@ -17605,7 +17632,7 @@
         <v>1097</v>
       </c>
       <c r="C41" t="s">
-        <v>1098</v>
+        <v>1504</v>
       </c>
       <c r="D41" t="s">
         <v>671</v>
@@ -17948,13 +17975,13 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="D52" t="s">
         <v>546</v>
       </c>
       <c r="E52" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="F52" t="s">
         <v>965</v>
@@ -18041,7 +18068,7 @@
         <v>549</v>
       </c>
       <c r="E55" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="G55" t="s">
         <v>888</v>
@@ -18070,7 +18097,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="D56" t="s">
         <v>550</v>
@@ -18137,7 +18164,7 @@
         <v>552</v>
       </c>
       <c r="E58" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="G58" t="s">
         <v>888</v>
@@ -18198,7 +18225,7 @@
         <v>554</v>
       </c>
       <c r="E60" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F60" t="s">
         <v>894</v>
@@ -18230,7 +18257,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="D61" t="s">
         <v>555</v>
@@ -18415,6 +18442,9 @@
       <c r="B67" t="s">
         <v>64</v>
       </c>
+      <c r="C67" t="s">
+        <v>1503</v>
+      </c>
       <c r="D67" t="s">
         <v>560</v>
       </c>
@@ -18522,6 +18552,9 @@
       <c r="D71" t="s">
         <v>564</v>
       </c>
+      <c r="E71" t="s">
+        <v>1508</v>
+      </c>
       <c r="F71" t="s">
         <v>968</v>
       </c>
@@ -18581,7 +18614,7 @@
         <v>566</v>
       </c>
       <c r="E73" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F73" t="s">
         <v>925</v>
@@ -18691,7 +18724,7 @@
         <v>74</v>
       </c>
       <c r="C77" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="D77" t="s">
         <v>570</v>
@@ -18816,13 +18849,13 @@
         <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="D81" t="s">
         <v>78</v>
       </c>
       <c r="E81" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="F81" t="s">
         <v>944</v>
@@ -18915,7 +18948,7 @@
         <v>575</v>
       </c>
       <c r="E84" t="s">
-        <v>1432</v>
+        <v>1501</v>
       </c>
       <c r="G84" t="s">
         <v>1117</v>
@@ -19092,7 +19125,7 @@
         <v>581</v>
       </c>
       <c r="E90" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="F90" t="s">
         <v>1012</v>
@@ -19121,7 +19154,7 @@
         <v>948</v>
       </c>
       <c r="E91" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="F91" t="s">
         <v>949</v>
@@ -19252,7 +19285,7 @@
         <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F95" t="s">
         <v>972</v>
@@ -19630,7 +19663,7 @@
         <v>596</v>
       </c>
       <c r="E107" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G107" t="s">
         <v>844</v>
@@ -19703,7 +19736,7 @@
         <v>598</v>
       </c>
       <c r="E109" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="G109" t="s">
         <v>1401</v>
@@ -19764,7 +19797,7 @@
         <v>600</v>
       </c>
       <c r="E111" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="G111" t="s">
         <v>844</v>
@@ -19866,7 +19899,7 @@
         <v>604</v>
       </c>
       <c r="E114" t="s">
-        <v>1434</v>
+        <v>1507</v>
       </c>
       <c r="G114" t="s">
         <v>1401</v>
@@ -19933,7 +19966,7 @@
         <v>606</v>
       </c>
       <c r="E116" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="G116" t="s">
         <v>844</v>
@@ -19997,7 +20030,7 @@
         <v>607</v>
       </c>
       <c r="E118" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G118" t="s">
         <v>844</v>
@@ -20206,7 +20239,7 @@
         <v>614</v>
       </c>
       <c r="E125" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F125" t="s">
         <v>1002</v>
@@ -20302,13 +20335,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="D128" t="s">
         <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F128" t="s">
         <v>1008</v>
@@ -20369,7 +20402,7 @@
         <v>619</v>
       </c>
       <c r="E130" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F130" t="s">
         <v>1058</v>
@@ -20459,7 +20492,7 @@
         <v>622</v>
       </c>
       <c r="E133" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="F133" t="s">
         <v>1018</v>
@@ -20525,6 +20558,9 @@
       <c r="D135" t="s">
         <v>624</v>
       </c>
+      <c r="E135" t="s">
+        <v>1511</v>
+      </c>
       <c r="F135" t="s">
         <v>1021</v>
       </c>
@@ -20726,7 +20762,7 @@
         <v>335</v>
       </c>
       <c r="C142" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="D142" t="s">
         <v>630</v>
@@ -20764,7 +20800,7 @@
         <v>631</v>
       </c>
       <c r="E143" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="G143" t="s">
         <v>1352</v>
@@ -20912,7 +20948,7 @@
         <v>636</v>
       </c>
       <c r="E148" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="F148" t="s">
         <v>1036</v>
@@ -20947,7 +20983,7 @@
         <v>637</v>
       </c>
       <c r="E149" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="G149" t="s">
         <v>1406</v>
@@ -20970,13 +21006,13 @@
         <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>1472</v>
+        <v>1505</v>
       </c>
       <c r="D150" t="s">
         <v>638</v>
       </c>
       <c r="E150" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="G150" t="s">
         <v>1406</v>
@@ -21197,7 +21233,7 @@
         <v>523</v>
       </c>
       <c r="E157" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="F157" t="s">
         <v>835</v>
@@ -21235,7 +21271,7 @@
         <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F158" t="s">
         <v>1065</v>
@@ -21266,6 +21302,9 @@
       <c r="D159" t="s">
         <v>648</v>
       </c>
+      <c r="E159" t="s">
+        <v>1513</v>
+      </c>
       <c r="G159" t="s">
         <v>844</v>
       </c>
@@ -21327,6 +21366,9 @@
       <c r="D161" t="s">
         <v>650</v>
       </c>
+      <c r="E161" t="s">
+        <v>1509</v>
+      </c>
       <c r="F161" t="s">
         <v>1062</v>
       </c>
@@ -21357,7 +21399,7 @@
         <v>651</v>
       </c>
       <c r="E162" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="F162" t="s">
         <v>1064</v>
@@ -21392,7 +21434,7 @@
         <v>652</v>
       </c>
       <c r="E163" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F163" t="s">
         <v>1070</v>
@@ -21482,7 +21524,7 @@
         <v>655</v>
       </c>
       <c r="E166" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="G166" t="s">
         <v>844</v>
@@ -21543,7 +21585,7 @@
         <v>159</v>
       </c>
       <c r="C168" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="D168" t="s">
         <v>658</v>
@@ -21636,7 +21678,7 @@
         <v>660</v>
       </c>
       <c r="E171" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="G171" t="s">
         <v>844</v>
@@ -21668,7 +21710,7 @@
         <v>661</v>
       </c>
       <c r="E172" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F172" t="s">
         <v>1345</v>
@@ -22217,7 +22259,7 @@
         <v>677</v>
       </c>
       <c r="E190" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F190" t="s">
         <v>1112</v>
@@ -22278,7 +22320,7 @@
         <v>679</v>
       </c>
       <c r="E192" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G192" t="s">
         <v>1117</v>
@@ -22310,13 +22352,13 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="D193" t="s">
         <v>680</v>
       </c>
       <c r="E193" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F193" t="s">
         <v>1118</v>
@@ -22418,7 +22460,7 @@
         <v>682</v>
       </c>
       <c r="E196" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G196" t="s">
         <v>1117</v>
@@ -22482,7 +22524,7 @@
         <v>684</v>
       </c>
       <c r="E198" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="F198" t="s">
         <v>1138</v>
@@ -22514,7 +22556,7 @@
         <v>184</v>
       </c>
       <c r="C199" t="s">
-        <v>1129</v>
+        <v>1500</v>
       </c>
       <c r="D199" t="s">
         <v>685</v>
@@ -22552,7 +22594,7 @@
         <v>686</v>
       </c>
       <c r="E200" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G200" t="s">
         <v>844</v>
@@ -22610,7 +22652,7 @@
         <v>738</v>
       </c>
       <c r="E202" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="G202" t="s">
         <v>1408</v>
@@ -22636,13 +22678,13 @@
         <v>188</v>
       </c>
       <c r="C203" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="D203" t="s">
         <v>690</v>
       </c>
       <c r="E203" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="G203" t="s">
         <v>1353</v>
@@ -22836,13 +22878,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1474</v>
+        <v>1502</v>
       </c>
       <c r="D210" t="s">
         <v>513</v>
       </c>
       <c r="E210" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="G210" t="s">
         <v>888</v>
@@ -22880,7 +22922,7 @@
         <v>695</v>
       </c>
       <c r="E211" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="F211" t="s">
         <v>1139</v>
@@ -22976,7 +23018,7 @@
         <v>698</v>
       </c>
       <c r="E214" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="F214" t="s">
         <v>1143</v>
@@ -23069,7 +23111,7 @@
         <v>701</v>
       </c>
       <c r="E217" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="G217" t="s">
         <v>1352</v>
@@ -23197,7 +23239,7 @@
         <v>704</v>
       </c>
       <c r="E221" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="F221" t="s">
         <v>1150</v>
@@ -23232,7 +23274,7 @@
         <v>705</v>
       </c>
       <c r="E222" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="F222" t="s">
         <v>1339</v>
@@ -23357,7 +23399,7 @@
         <v>710</v>
       </c>
       <c r="E226" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F226" t="s">
         <v>1204</v>
@@ -23563,7 +23605,7 @@
         <v>717</v>
       </c>
       <c r="E233" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="F233" t="s">
         <v>1160</v>
@@ -23598,7 +23640,7 @@
         <v>718</v>
       </c>
       <c r="E234" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="G234" t="s">
         <v>844</v>
@@ -23633,7 +23675,7 @@
         <v>719</v>
       </c>
       <c r="E235" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="G235" t="s">
         <v>844</v>
@@ -23784,7 +23826,7 @@
         <v>723</v>
       </c>
       <c r="E240" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="F240" t="s">
         <v>1165</v>
@@ -23822,7 +23864,7 @@
         <v>724</v>
       </c>
       <c r="E241" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="G241" t="s">
         <v>1117</v>
@@ -23850,6 +23892,9 @@
       <c r="D242" t="s">
         <v>725</v>
       </c>
+      <c r="E242" t="s">
+        <v>1506</v>
+      </c>
       <c r="G242" t="s">
         <v>844</v>
       </c>
@@ -24028,7 +24073,7 @@
         <v>731</v>
       </c>
       <c r="E248" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="G248" t="s">
         <v>844</v>
@@ -24089,7 +24134,7 @@
         <v>733</v>
       </c>
       <c r="E250" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="F250" t="s">
         <v>1175</v>
@@ -24127,7 +24172,7 @@
         <v>734</v>
       </c>
       <c r="E251" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G251" t="s">
         <v>844</v>
@@ -24217,7 +24262,7 @@
         <v>737</v>
       </c>
       <c r="E254" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="F254" t="s">
         <v>1179</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8AAD60-00D8-43D4-835E-FBB9394173EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111F5975-EF06-4C3E-9CEA-4BCC8A8C55F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8625" yWindow="375" windowWidth="34605" windowHeight="20985" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4283" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4292" uniqueCount="1525">
   <si>
     <t>Sigla</t>
   </si>
@@ -4590,13 +4590,37 @@
   </si>
   <si>
     <t>Pronuncia_capitale</t>
+  </si>
+  <si>
+    <t>Andòra la Vèglia</t>
+  </si>
+  <si>
+    <t>Andòra</t>
+  </si>
+  <si>
+    <t>Sènt Hélièr</t>
+  </si>
+  <si>
+    <t>Sùcre</t>
+  </si>
+  <si>
+    <t>Boneèr</t>
+  </si>
+  <si>
+    <t>Kràlendéic</t>
+  </si>
+  <si>
+    <t>Bandar Seri Begàuan</t>
+  </si>
+  <si>
+    <t>Librevìl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4614,6 +4638,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4684,7 +4716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4699,6 +4731,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -16544,11 +16577,17 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
+      <c r="D5" t="s">
+        <v>1518</v>
+      </c>
       <c r="E5" t="s">
         <v>501</v>
       </c>
       <c r="F5" t="s">
         <v>756</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1517</v>
       </c>
       <c r="H5" t="s">
         <v>757</v>
@@ -16579,6 +16618,7 @@
       <c r="E6" t="s">
         <v>502</v>
       </c>
+      <c r="G6" s="10"/>
       <c r="H6" t="s">
         <v>828</v>
       </c>
@@ -16968,6 +17008,9 @@
       <c r="F19" t="s">
         <v>1394</v>
       </c>
+      <c r="G19" t="s">
+        <v>1519</v>
+      </c>
       <c r="I19" t="s">
         <v>1401</v>
       </c>
@@ -16994,6 +17037,7 @@
       <c r="E20" t="s">
         <v>515</v>
       </c>
+      <c r="G20" s="10"/>
       <c r="H20" t="s">
         <v>832</v>
       </c>
@@ -17235,6 +17279,9 @@
       <c r="F28" t="s">
         <v>1297</v>
       </c>
+      <c r="G28" t="s">
+        <v>1520</v>
+      </c>
       <c r="H28" t="s">
         <v>810</v>
       </c>
@@ -17261,11 +17308,17 @@
       <c r="B29" t="s">
         <v>484</v>
       </c>
+      <c r="C29" t="s">
+        <v>1521</v>
+      </c>
       <c r="E29" t="s">
         <v>525</v>
       </c>
       <c r="F29" t="s">
         <v>1459</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1522</v>
       </c>
       <c r="I29" t="s">
         <v>888</v>
@@ -17302,6 +17355,7 @@
       <c r="E30" t="s">
         <v>526</v>
       </c>
+      <c r="G30" s="10"/>
       <c r="H30" t="s">
         <v>836</v>
       </c>
@@ -17392,6 +17446,9 @@
       <c r="F33" t="s">
         <v>1462</v>
       </c>
+      <c r="G33" t="s">
+        <v>1523</v>
+      </c>
       <c r="H33" t="s">
         <v>1031</v>
       </c>
@@ -18000,6 +18057,9 @@
       <c r="F52" t="s">
         <v>1446</v>
       </c>
+      <c r="G52" t="s">
+        <v>883</v>
+      </c>
       <c r="H52" t="s">
         <v>965</v>
       </c>
@@ -18571,6 +18631,9 @@
       </c>
       <c r="F71" t="s">
         <v>1506</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1524</v>
       </c>
       <c r="H71" t="s">
         <v>968</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111F5975-EF06-4C3E-9CEA-4BCC8A8C55F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD83DF1-C58B-4CC1-B23D-2AB0ABB5B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4292" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4318" uniqueCount="1549">
   <si>
     <t>Sigla</t>
   </si>
@@ -4028,9 +4028,6 @@
     <t>strisce verticali, stella verde</t>
   </si>
   <si>
-    <t>strisce verticali, mezzaluna bianca, stella bianca</t>
-  </si>
-  <si>
     <t>strisce orizzontali, stella rossa</t>
   </si>
   <si>
@@ -4214,9 +4211,6 @@
     <t>Tristan</t>
   </si>
   <si>
-    <t>Turks, Caicos</t>
-  </si>
-  <si>
     <t>Trinidad, Tobago</t>
   </si>
   <si>
@@ -4319,9 +4313,6 @@
     <t>Valichir</t>
   </si>
   <si>
-    <t>Taschent</t>
-  </si>
-  <si>
     <t>Nibbia</t>
   </si>
   <si>
@@ -4367,9 +4358,6 @@
     <t>Philips burger</t>
   </si>
   <si>
-    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte</t>
-  </si>
-  <si>
     <t>Sport Villa</t>
   </si>
   <si>
@@ -4574,9 +4562,6 @@
     <t>Yaundé, Young, Yaounfe</t>
   </si>
   <si>
-    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi</t>
-  </si>
-  <si>
     <t>Bishkek, Biscake, Bistecca, bisquet</t>
   </si>
   <si>
@@ -4614,6 +4599,93 @@
   </si>
   <si>
     <t>Librevìl</t>
+  </si>
+  <si>
+    <t>Ebay</t>
+  </si>
+  <si>
+    <t>Corone</t>
+  </si>
+  <si>
+    <t>Taschent, Dash kent</t>
+  </si>
+  <si>
+    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte</t>
+  </si>
+  <si>
+    <t>Srì Giaiauardenapùra Còtte</t>
+  </si>
+  <si>
+    <t>Trìstan da Cùgna</t>
+  </si>
+  <si>
+    <t>Èdinbra of de Sèven Sìs</t>
+  </si>
+  <si>
+    <t>emblema nazionale, animale, uccello</t>
+  </si>
+  <si>
+    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy</t>
+  </si>
+  <si>
+    <t>Turks, Caicos, turks and caicos</t>
+  </si>
+  <si>
+    <t>Agàtgna</t>
+  </si>
+  <si>
+    <t>Siutaàd de la pas</t>
+  </si>
+  <si>
+    <t>Caièn</t>
+  </si>
+  <si>
+    <t>Daaglas</t>
+  </si>
+  <si>
+    <t>Flying Fish Còv</t>
+  </si>
+  <si>
+    <t>Ava Rua</t>
+  </si>
+  <si>
+    <t>Isole Òlànd</t>
+  </si>
+  <si>
+    <t>Stènli</t>
+  </si>
+  <si>
+    <t>Tòrsciaven</t>
+  </si>
+  <si>
+    <t>Tarava Sud</t>
+  </si>
+  <si>
+    <t>Queeit</t>
+  </si>
+  <si>
+    <t>Madinat al Queeit</t>
+  </si>
+  <si>
+    <t>Malauui</t>
+  </si>
+  <si>
+    <t>Mamòdzu</t>
+  </si>
+  <si>
+    <t>Kiscinàu</t>
+  </si>
+  <si>
+    <t>Nèipi dòo</t>
+  </si>
+  <si>
+    <t>Niamè</t>
+  </si>
+  <si>
+    <t>Abùgia</t>
+  </si>
+  <si>
+    <t>Vìnd huk</t>
   </si>
 </sst>
 </file>
@@ -16411,7 +16483,7 @@
         <v>749</v>
       </c>
       <c r="D1" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="E1" t="s">
         <v>497</v>
@@ -16420,7 +16492,7 @@
         <v>750</v>
       </c>
       <c r="G1" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="H1" t="s">
         <v>748</v>
@@ -16464,7 +16536,7 @@
         <v>753</v>
       </c>
       <c r="I2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J2" t="s">
         <v>772</v>
@@ -16473,7 +16545,7 @@
         <v>773</v>
       </c>
       <c r="L2" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="N2" t="s">
         <v>1242</v>
@@ -16500,13 +16572,13 @@
         <v>499</v>
       </c>
       <c r="F3" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="H3" t="s">
         <v>1195</v>
       </c>
       <c r="I3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J3" t="s">
         <v>754</v>
@@ -16518,7 +16590,7 @@
         <v>780</v>
       </c>
       <c r="N3" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
@@ -16578,7 +16650,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="E5" t="s">
         <v>501</v>
@@ -16587,13 +16659,13 @@
         <v>756</v>
       </c>
       <c r="G5" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="H5" t="s">
         <v>757</v>
       </c>
       <c r="I5" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="J5" t="s">
         <v>758</v>
@@ -16623,7 +16695,7 @@
         <v>828</v>
       </c>
       <c r="I6" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="J6" t="s">
         <v>754</v>
@@ -16681,13 +16753,13 @@
         <v>504</v>
       </c>
       <c r="F8" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="I8" t="s">
         <v>888</v>
       </c>
       <c r="J8" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="L8" t="s">
         <v>783</v>
@@ -16716,7 +16788,7 @@
         <v>829</v>
       </c>
       <c r="I9" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J9" t="s">
         <v>778</v>
@@ -16728,7 +16800,7 @@
         <v>1219</v>
       </c>
       <c r="N9" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -16748,7 +16820,7 @@
         <v>830</v>
       </c>
       <c r="I10" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J10" t="s">
         <v>786</v>
@@ -16780,10 +16852,10 @@
         <v>765</v>
       </c>
       <c r="I11" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J11" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="N11" t="s">
         <v>1245</v>
@@ -16803,7 +16875,7 @@
         <v>513</v>
       </c>
       <c r="F12" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="I12" t="s">
         <v>888</v>
@@ -16838,7 +16910,7 @@
         <v>583</v>
       </c>
       <c r="I13" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J13" t="s">
         <v>1214</v>
@@ -16916,7 +16988,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="E16" t="s">
         <v>509</v>
@@ -16925,7 +16997,7 @@
         <v>887</v>
       </c>
       <c r="I16" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J16" t="s">
         <v>770</v>
@@ -16983,7 +17055,7 @@
         <v>831</v>
       </c>
       <c r="I18" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J18" t="s">
         <v>794</v>
@@ -17000,19 +17072,19 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="E19" t="s">
         <v>512</v>
       </c>
       <c r="F19" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G19" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="I19" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J19" t="s">
         <v>794</v>
@@ -17042,7 +17114,7 @@
         <v>832</v>
       </c>
       <c r="I20" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J20" t="s">
         <v>796</v>
@@ -17054,7 +17126,7 @@
         <v>792</v>
       </c>
       <c r="N20" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="O20" s="1">
         <v>2</v>
@@ -17071,7 +17143,7 @@
         <v>516</v>
       </c>
       <c r="F21" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="I21" t="s">
         <v>888</v>
@@ -17106,7 +17178,7 @@
         <v>1205</v>
       </c>
       <c r="I22" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="J22" t="s">
         <v>799</v>
@@ -17161,13 +17233,13 @@
         <v>519</v>
       </c>
       <c r="F24" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="H24" t="s">
         <v>834</v>
       </c>
       <c r="I24" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J24" t="s">
         <v>801</v>
@@ -17216,13 +17288,13 @@
         <v>521</v>
       </c>
       <c r="F26" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="H26" t="s">
         <v>802</v>
       </c>
       <c r="I26" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J26" t="s">
         <v>1066</v>
@@ -17280,13 +17352,13 @@
         <v>1297</v>
       </c>
       <c r="G28" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="H28" t="s">
         <v>810</v>
       </c>
       <c r="I28" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J28" t="s">
         <v>811</v>
@@ -17309,16 +17381,16 @@
         <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="E29" t="s">
         <v>525</v>
       </c>
       <c r="F29" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="G29" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="I29" t="s">
         <v>888</v>
@@ -17360,10 +17432,13 @@
         <v>836</v>
       </c>
       <c r="I30" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J30" t="s">
-        <v>814</v>
+        <v>797</v>
+      </c>
+      <c r="K30" t="s">
+        <v>773</v>
       </c>
       <c r="L30" t="s">
         <v>788</v>
@@ -17385,6 +17460,9 @@
       <c r="E31" t="s">
         <v>527</v>
       </c>
+      <c r="F31" t="s">
+        <v>1521</v>
+      </c>
       <c r="H31" t="s">
         <v>1056</v>
       </c>
@@ -17415,7 +17493,7 @@
         <v>837</v>
       </c>
       <c r="I32" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J32" t="s">
         <v>816</v>
@@ -17427,7 +17505,7 @@
         <v>1216</v>
       </c>
       <c r="N32" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="O32" s="1">
         <v>1</v>
@@ -17444,16 +17522,16 @@
         <v>529</v>
       </c>
       <c r="F33" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="G33" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="H33" t="s">
         <v>1031</v>
       </c>
       <c r="I33" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J33" t="s">
         <v>817</v>
@@ -17462,10 +17540,10 @@
         <v>776</v>
       </c>
       <c r="L33" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="N33" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="O33" s="1">
         <v>2</v>
@@ -17485,7 +17563,7 @@
         <v>838</v>
       </c>
       <c r="I34" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J34" t="s">
         <v>819</v>
@@ -17514,7 +17592,7 @@
         <v>820</v>
       </c>
       <c r="I35" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J35" t="s">
         <v>805</v>
@@ -17543,13 +17621,13 @@
         <v>532</v>
       </c>
       <c r="F36" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="H36" t="s">
         <v>826</v>
       </c>
       <c r="I36" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J36" t="s">
         <v>755</v>
@@ -17561,7 +17639,7 @@
         <v>788</v>
       </c>
       <c r="N36" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="O36" s="1">
         <v>2</v>
@@ -17578,13 +17656,13 @@
         <v>533</v>
       </c>
       <c r="F37" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="H37" t="s">
         <v>929</v>
       </c>
       <c r="I37" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J37" t="s">
         <v>853</v>
@@ -17616,13 +17694,13 @@
         <v>534</v>
       </c>
       <c r="F38" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="H38" t="s">
         <v>856</v>
       </c>
       <c r="I38" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J38" t="s">
         <v>857</v>
@@ -17683,7 +17761,7 @@
         <v>536</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>858</v>
@@ -17706,7 +17784,7 @@
         <v>1097</v>
       </c>
       <c r="C41" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="E41" t="s">
         <v>671</v>
@@ -17770,7 +17848,7 @@
         <v>865</v>
       </c>
       <c r="I43" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J43" t="s">
         <v>767</v>
@@ -17805,7 +17883,7 @@
         <v>958</v>
       </c>
       <c r="I44" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J44" t="s">
         <v>864</v>
@@ -17817,7 +17895,7 @@
         <v>788</v>
       </c>
       <c r="N44" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="O44" s="1">
         <v>1</v>
@@ -17834,19 +17912,19 @@
         <v>540</v>
       </c>
       <c r="I45" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="J45" t="s">
         <v>866</v>
       </c>
       <c r="K45" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="L45" t="s">
         <v>875</v>
       </c>
       <c r="N45" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="O45" s="1">
         <v>1</v>
@@ -17901,7 +17979,7 @@
         <v>870</v>
       </c>
       <c r="I47" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J47" t="s">
         <v>871</v>
@@ -17924,7 +18002,7 @@
         <v>542</v>
       </c>
       <c r="I48" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J48" t="s">
         <v>872</v>
@@ -17936,7 +18014,7 @@
         <v>818</v>
       </c>
       <c r="N48" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="O48" s="1">
         <v>2</v>
@@ -17985,7 +18063,7 @@
         <v>963</v>
       </c>
       <c r="I50" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J50" t="s">
         <v>767</v>
@@ -18023,7 +18101,7 @@
         <v>964</v>
       </c>
       <c r="I51" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J51" t="s">
         <v>881</v>
@@ -18035,7 +18113,7 @@
         <v>792</v>
       </c>
       <c r="N51" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -18049,13 +18127,13 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="E52" t="s">
         <v>546</v>
       </c>
       <c r="F52" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="G52" t="s">
         <v>883</v>
@@ -18064,7 +18142,7 @@
         <v>965</v>
       </c>
       <c r="I52" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J52" t="s">
         <v>1067</v>
@@ -18119,7 +18197,7 @@
         <v>967</v>
       </c>
       <c r="I54" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J54" t="s">
         <v>785</v>
@@ -18145,7 +18223,7 @@
         <v>549</v>
       </c>
       <c r="F55" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="I55" t="s">
         <v>888</v>
@@ -18160,7 +18238,7 @@
         <v>1200</v>
       </c>
       <c r="N55" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="O55" s="1">
         <v>1</v>
@@ -18174,13 +18252,13 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="E56" t="s">
         <v>550</v>
       </c>
       <c r="F56" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="I56" t="s">
         <v>888</v>
@@ -18215,10 +18293,10 @@
         <v>551</v>
       </c>
       <c r="H57" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I57" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J57" t="s">
         <v>769</v>
@@ -18241,7 +18319,7 @@
         <v>552</v>
       </c>
       <c r="F58" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="I58" t="s">
         <v>888</v>
@@ -18276,13 +18354,13 @@
         <v>892</v>
       </c>
       <c r="I59" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J59" t="s">
         <v>871</v>
       </c>
       <c r="L59" t="s">
-        <v>1221</v>
+        <v>1527</v>
       </c>
       <c r="N59" t="s">
         <v>1245</v>
@@ -18302,7 +18380,7 @@
         <v>554</v>
       </c>
       <c r="F60" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="H60" t="s">
         <v>894</v>
@@ -18334,7 +18412,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="E61" t="s">
         <v>555</v>
@@ -18381,7 +18459,7 @@
         <v>902</v>
       </c>
       <c r="I62" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J62" t="s">
         <v>903</v>
@@ -18404,7 +18482,7 @@
         <v>905</v>
       </c>
       <c r="I63" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="J63" t="s">
         <v>906</v>
@@ -18433,7 +18511,7 @@
         <v>909</v>
       </c>
       <c r="I64" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J64" t="s">
         <v>907</v>
@@ -18453,13 +18531,13 @@
         <v>741</v>
       </c>
       <c r="C65" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E65" t="s">
         <v>709</v>
       </c>
       <c r="F65" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H65" t="s">
         <v>1057</v>
@@ -18494,7 +18572,7 @@
         <v>915</v>
       </c>
       <c r="I66" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="J66" t="s">
         <v>801</v>
@@ -18520,7 +18598,7 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="E67" t="s">
         <v>560</v>
@@ -18549,7 +18627,7 @@
         <v>561</v>
       </c>
       <c r="I68" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J68" t="s">
         <v>916</v>
@@ -18581,7 +18659,7 @@
         <v>917</v>
       </c>
       <c r="I69" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J69" t="s">
         <v>918</v>
@@ -18630,16 +18708,16 @@
         <v>564</v>
       </c>
       <c r="F71" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="G71" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="H71" t="s">
         <v>968</v>
       </c>
       <c r="I71" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J71" t="s">
         <v>816</v>
@@ -18694,13 +18772,13 @@
         <v>566</v>
       </c>
       <c r="F73" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="H73" t="s">
         <v>925</v>
       </c>
       <c r="I73" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J73" t="s">
         <v>927</v>
@@ -18726,7 +18804,7 @@
         <v>931</v>
       </c>
       <c r="I74" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J74" t="s">
         <v>794</v>
@@ -18804,7 +18882,7 @@
         <v>74</v>
       </c>
       <c r="C77" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="E77" t="s">
         <v>570</v>
@@ -18813,7 +18891,7 @@
         <v>969</v>
       </c>
       <c r="I77" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J77" t="s">
         <v>936</v>
@@ -18839,7 +18917,7 @@
         <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E78" t="s">
         <v>571</v>
@@ -18868,7 +18946,7 @@
         <v>572</v>
       </c>
       <c r="I79" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J79" t="s">
         <v>794</v>
@@ -18880,7 +18958,7 @@
         <v>792</v>
       </c>
       <c r="N79" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="O79" s="1">
         <v>1</v>
@@ -18900,7 +18978,7 @@
         <v>938</v>
       </c>
       <c r="I80" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="J80" t="s">
         <v>794</v>
@@ -18929,19 +19007,19 @@
         <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="E81" t="s">
         <v>78</v>
       </c>
       <c r="F81" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="H81" t="s">
         <v>944</v>
       </c>
       <c r="I81" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="J81" t="s">
         <v>939</v>
@@ -18973,7 +19051,7 @@
         <v>961</v>
       </c>
       <c r="I82" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J82" t="s">
         <v>898</v>
@@ -18985,7 +19063,7 @@
         <v>1200</v>
       </c>
       <c r="N82" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="O82" s="1">
         <v>2</v>
@@ -19005,7 +19083,7 @@
         <v>945</v>
       </c>
       <c r="I83" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J83" t="s">
         <v>919</v>
@@ -19028,7 +19106,7 @@
         <v>575</v>
       </c>
       <c r="F84" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="I84" t="s">
         <v>1117</v>
@@ -19060,7 +19138,7 @@
         <v>576</v>
       </c>
       <c r="F85" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="H85" t="s">
         <v>960</v>
@@ -19098,7 +19176,7 @@
         <v>941</v>
       </c>
       <c r="L86" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="M86" t="s">
         <v>494</v>
@@ -19117,6 +19195,9 @@
       <c r="E87" t="s">
         <v>578</v>
       </c>
+      <c r="F87" t="s">
+        <v>1530</v>
+      </c>
       <c r="I87" t="s">
         <v>844</v>
       </c>
@@ -19179,7 +19260,7 @@
         <v>1298</v>
       </c>
       <c r="I89" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J89" t="s">
         <v>946</v>
@@ -19205,13 +19286,13 @@
         <v>581</v>
       </c>
       <c r="F90" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="H90" t="s">
         <v>1012</v>
       </c>
       <c r="I90" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J90" t="s">
         <v>811</v>
@@ -19234,13 +19315,16 @@
         <v>948</v>
       </c>
       <c r="F91" t="s">
-        <v>1447</v>
+        <v>1443</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1531</v>
       </c>
       <c r="H91" t="s">
         <v>949</v>
       </c>
       <c r="I91" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J91" t="s">
         <v>950</v>
@@ -19272,7 +19356,7 @@
         <v>951</v>
       </c>
       <c r="I92" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J92" t="s">
         <v>811</v>
@@ -19304,7 +19388,7 @@
         <v>952</v>
       </c>
       <c r="I93" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J93" t="s">
         <v>811</v>
@@ -19329,11 +19413,14 @@
       <c r="F94" t="s">
         <v>953</v>
       </c>
+      <c r="G94" t="s">
+        <v>1532</v>
+      </c>
       <c r="H94" t="s">
         <v>955</v>
       </c>
       <c r="I94" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J94" t="s">
         <v>956</v>
@@ -19365,7 +19452,7 @@
         <v>626</v>
       </c>
       <c r="F95" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="H95" t="s">
         <v>972</v>
@@ -19432,7 +19519,7 @@
         <v>975</v>
       </c>
       <c r="I97" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J97" t="s">
         <v>769</v>
@@ -19447,7 +19534,7 @@
         <v>494</v>
       </c>
       <c r="N97" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="O97" s="1">
         <v>3</v>
@@ -19470,7 +19557,7 @@
         <v>1207</v>
       </c>
       <c r="I98" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J98" t="s">
         <v>1067</v>
@@ -19499,13 +19586,13 @@
         <v>588</v>
       </c>
       <c r="F99" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H99" t="s">
         <v>1032</v>
       </c>
       <c r="I99" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J99" t="s">
         <v>769</v>
@@ -19560,7 +19647,7 @@
         <v>978</v>
       </c>
       <c r="I101" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="J101" t="s">
         <v>979</v>
@@ -19592,7 +19679,7 @@
         <v>980</v>
       </c>
       <c r="I102" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="J102" t="s">
         <v>896</v>
@@ -19624,7 +19711,7 @@
         <v>981</v>
       </c>
       <c r="I103" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J103" t="s">
         <v>1068</v>
@@ -19682,7 +19769,7 @@
         <v>983</v>
       </c>
       <c r="I105" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J105" t="s">
         <v>767</v>
@@ -19707,8 +19794,11 @@
       <c r="E106" t="s">
         <v>595</v>
       </c>
+      <c r="G106" t="s">
+        <v>1533</v>
+      </c>
       <c r="I106" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J106" t="s">
         <v>769</v>
@@ -19723,7 +19813,7 @@
         <v>494</v>
       </c>
       <c r="N106" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="O106" s="1">
         <v>3</v>
@@ -19743,7 +19833,10 @@
         <v>596</v>
       </c>
       <c r="F107" t="s">
-        <v>1432</v>
+        <v>1429</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1534</v>
       </c>
       <c r="I107" t="s">
         <v>844</v>
@@ -19812,14 +19905,17 @@
       <c r="C109" t="s">
         <v>789</v>
       </c>
+      <c r="D109" t="s">
+        <v>1536</v>
+      </c>
       <c r="E109" t="s">
         <v>598</v>
       </c>
       <c r="F109" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="I109" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J109" t="s">
         <v>758</v>
@@ -19877,7 +19973,7 @@
         <v>600</v>
       </c>
       <c r="F111" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="I111" t="s">
         <v>844</v>
@@ -19914,6 +20010,9 @@
       <c r="E112" t="s">
         <v>601</v>
       </c>
+      <c r="G112" t="s">
+        <v>1535</v>
+      </c>
       <c r="I112" t="s">
         <v>844</v>
       </c>
@@ -19949,6 +20048,9 @@
       <c r="E113" t="s">
         <v>602</v>
       </c>
+      <c r="G113" t="s">
+        <v>1537</v>
+      </c>
       <c r="I113" t="s">
         <v>850</v>
       </c>
@@ -19979,10 +20081,13 @@
         <v>604</v>
       </c>
       <c r="F114" t="s">
-        <v>1505</v>
+        <v>1501</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1538</v>
       </c>
       <c r="I114" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J114" t="s">
         <v>916</v>
@@ -20005,13 +20110,13 @@
         <v>108</v>
       </c>
       <c r="C115" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="E115" t="s">
         <v>605</v>
       </c>
       <c r="F115" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="I115" t="s">
         <v>841</v>
@@ -20026,7 +20131,7 @@
         <v>494</v>
       </c>
       <c r="N115" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="O115" s="1">
         <v>3</v>
@@ -20046,7 +20151,7 @@
         <v>606</v>
       </c>
       <c r="F116" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="I116" t="s">
         <v>844</v>
@@ -20078,7 +20183,7 @@
         <v>597</v>
       </c>
       <c r="F117" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="I117" t="s">
         <v>844</v>
@@ -20110,7 +20215,7 @@
         <v>607</v>
       </c>
       <c r="F118" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="I118" t="s">
         <v>844</v>
@@ -20148,7 +20253,7 @@
         <v>888</v>
       </c>
       <c r="J119" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="L119" t="s">
         <v>1232</v>
@@ -20157,7 +20262,7 @@
         <v>494</v>
       </c>
       <c r="N119" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="O119" s="1">
         <v>3</v>
@@ -20206,7 +20311,7 @@
         <v>994</v>
       </c>
       <c r="I121" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J121" t="s">
         <v>815</v>
@@ -20218,7 +20323,7 @@
         <v>788</v>
       </c>
       <c r="N121" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="O121" s="1">
         <v>1</v>
@@ -20264,7 +20369,7 @@
         <v>998</v>
       </c>
       <c r="I123" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J123" t="s">
         <v>999</v>
@@ -20273,7 +20378,7 @@
         <v>1005</v>
       </c>
       <c r="N123" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="O123" s="1">
         <v>1</v>
@@ -20290,10 +20395,10 @@
         <v>613</v>
       </c>
       <c r="H124" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I124" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J124" t="s">
         <v>1001</v>
@@ -20319,13 +20424,16 @@
         <v>614</v>
       </c>
       <c r="F125" t="s">
-        <v>1512</v>
+        <v>1507</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1010</v>
       </c>
       <c r="H125" t="s">
         <v>1002</v>
       </c>
       <c r="I125" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J125" t="s">
         <v>864</v>
@@ -20337,7 +20445,7 @@
         <v>783</v>
       </c>
       <c r="N125" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="O125" s="1">
         <v>2</v>
@@ -20356,6 +20464,9 @@
       <c r="F126" t="s">
         <v>1009</v>
       </c>
+      <c r="G126" t="s">
+        <v>1539</v>
+      </c>
       <c r="I126" t="s">
         <v>844</v>
       </c>
@@ -20386,7 +20497,7 @@
         <v>1006</v>
       </c>
       <c r="I127" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J127" t="s">
         <v>797</v>
@@ -20401,7 +20512,7 @@
         <v>494</v>
       </c>
       <c r="N127" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="O127" s="1">
         <v>3</v>
@@ -20415,19 +20526,25 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1444</v>
+        <v>1440</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1540</v>
       </c>
       <c r="E128" t="s">
         <v>617</v>
       </c>
       <c r="F128" t="s">
-        <v>1445</v>
+        <v>1441</v>
+      </c>
+      <c r="G128" t="s">
+        <v>1541</v>
       </c>
       <c r="H128" t="s">
         <v>1008</v>
       </c>
       <c r="I128" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J128" t="s">
         <v>1001</v>
@@ -20453,7 +20570,7 @@
         <v>1013</v>
       </c>
       <c r="I129" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J129" t="s">
         <v>853</v>
@@ -20482,7 +20599,7 @@
         <v>619</v>
       </c>
       <c r="F130" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="H130" t="s">
         <v>1058</v>
@@ -20517,7 +20634,7 @@
         <v>1015</v>
       </c>
       <c r="I131" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J131" t="s">
         <v>769</v>
@@ -20543,7 +20660,7 @@
         <v>1016</v>
       </c>
       <c r="I132" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J132" t="s">
         <v>1017</v>
@@ -20572,13 +20689,13 @@
         <v>622</v>
       </c>
       <c r="F133" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="H133" t="s">
         <v>1018</v>
       </c>
       <c r="I133" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J133" t="s">
         <v>916</v>
@@ -20639,7 +20756,7 @@
         <v>624</v>
       </c>
       <c r="F135" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="H135" t="s">
         <v>1021</v>
@@ -20677,7 +20794,7 @@
         <v>1049</v>
       </c>
       <c r="I136" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J136" t="s">
         <v>807</v>
@@ -20703,7 +20820,7 @@
         <v>1024</v>
       </c>
       <c r="I137" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="J137" t="s">
         <v>1025</v>
@@ -20729,7 +20846,7 @@
         <v>975</v>
       </c>
       <c r="I138" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J138" t="s">
         <v>778</v>
@@ -20744,7 +20861,7 @@
         <v>494</v>
       </c>
       <c r="N138" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="O138" s="1">
         <v>3</v>
@@ -20770,7 +20887,7 @@
         <v>1196</v>
       </c>
       <c r="I139" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J139" t="s">
         <v>864</v>
@@ -20793,7 +20910,7 @@
         <v>628</v>
       </c>
       <c r="I140" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J140" t="s">
         <v>1026</v>
@@ -20809,6 +20926,9 @@
       <c r="B141" t="s">
         <v>134</v>
       </c>
+      <c r="D141" t="s">
+        <v>1542</v>
+      </c>
       <c r="E141" t="s">
         <v>629</v>
       </c>
@@ -20816,7 +20936,7 @@
         <v>1027</v>
       </c>
       <c r="I141" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J141" t="s">
         <v>1023</v>
@@ -20842,7 +20962,7 @@
         <v>335</v>
       </c>
       <c r="C142" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="E142" t="s">
         <v>630</v>
@@ -20851,7 +20971,7 @@
         <v>1047</v>
       </c>
       <c r="I142" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J142" t="s">
         <v>859</v>
@@ -20863,7 +20983,7 @@
         <v>818</v>
       </c>
       <c r="N142" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="O142" s="1">
         <v>1</v>
@@ -20880,10 +21000,10 @@
         <v>631</v>
       </c>
       <c r="F143" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="I143" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J143" t="s">
         <v>805</v>
@@ -20915,7 +21035,7 @@
         <v>1034</v>
       </c>
       <c r="I144" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J144" t="s">
         <v>801</v>
@@ -20982,7 +21102,7 @@
         <v>788</v>
       </c>
       <c r="N146" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="O146" s="1">
         <v>1</v>
@@ -21028,13 +21148,13 @@
         <v>636</v>
       </c>
       <c r="F148" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="H148" t="s">
         <v>1036</v>
       </c>
       <c r="I148" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J148" t="s">
         <v>805</v>
@@ -21063,10 +21183,10 @@
         <v>637</v>
       </c>
       <c r="F149" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="I149" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J149" t="s">
         <v>1038</v>
@@ -21086,16 +21206,19 @@
         <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="E150" t="s">
         <v>638</v>
       </c>
       <c r="F150" t="s">
-        <v>1471</v>
+        <v>1467</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1543</v>
       </c>
       <c r="I150" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J150" t="s">
         <v>916</v>
@@ -21107,7 +21230,7 @@
         <v>494</v>
       </c>
       <c r="N150" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="O150" s="1">
         <v>3</v>
@@ -21158,6 +21281,9 @@
       <c r="E152" t="s">
         <v>641</v>
       </c>
+      <c r="G152" t="s">
+        <v>1544</v>
+      </c>
       <c r="H152" t="s">
         <v>1039</v>
       </c>
@@ -21194,7 +21320,7 @@
         <v>1040</v>
       </c>
       <c r="I153" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J153" t="s">
         <v>800</v>
@@ -21226,7 +21352,7 @@
         <v>1197</v>
       </c>
       <c r="I154" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J154" t="s">
         <v>864</v>
@@ -21284,7 +21410,7 @@
         <v>1059</v>
       </c>
       <c r="I156" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J156" t="s">
         <v>1041</v>
@@ -21293,7 +21419,7 @@
         <v>1236</v>
       </c>
       <c r="N156" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="O156" s="1">
         <v>2</v>
@@ -21313,13 +21439,16 @@
         <v>523</v>
       </c>
       <c r="F157" t="s">
-        <v>1434</v>
+        <v>1431</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1545</v>
       </c>
       <c r="H157" t="s">
         <v>835</v>
       </c>
       <c r="I157" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J157" t="s">
         <v>807</v>
@@ -21345,13 +21474,16 @@
         <v>149</v>
       </c>
       <c r="C158" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="E158" t="s">
         <v>647</v>
       </c>
       <c r="F158" t="s">
-        <v>1454</v>
+        <v>1450</v>
+      </c>
+      <c r="G158" t="s">
+        <v>1548</v>
       </c>
       <c r="H158" t="s">
         <v>1065</v>
@@ -21383,7 +21515,7 @@
         <v>648</v>
       </c>
       <c r="F159" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="I159" t="s">
         <v>844</v>
@@ -21418,7 +21550,7 @@
         <v>1061</v>
       </c>
       <c r="I160" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J160" t="s">
         <v>800</v>
@@ -21447,7 +21579,7 @@
         <v>650</v>
       </c>
       <c r="F161" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="H161" t="s">
         <v>1062</v>
@@ -21479,13 +21611,16 @@
         <v>651</v>
       </c>
       <c r="F162" t="s">
-        <v>1461</v>
+        <v>1457</v>
+      </c>
+      <c r="G162" t="s">
+        <v>1546</v>
       </c>
       <c r="H162" t="s">
         <v>1064</v>
       </c>
       <c r="I162" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J162" t="s">
         <v>1067</v>
@@ -21514,13 +21649,16 @@
         <v>652</v>
       </c>
       <c r="F163" t="s">
-        <v>1474</v>
+        <v>1470</v>
+      </c>
+      <c r="G163" t="s">
+        <v>1547</v>
       </c>
       <c r="H163" t="s">
         <v>1070</v>
       </c>
       <c r="I163" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J163" t="s">
         <v>764</v>
@@ -21578,7 +21716,7 @@
         <v>1072</v>
       </c>
       <c r="I165" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J165" t="s">
         <v>785</v>
@@ -21604,7 +21742,7 @@
         <v>655</v>
       </c>
       <c r="F166" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="I166" t="s">
         <v>844</v>
@@ -21648,7 +21786,7 @@
         <v>769</v>
       </c>
       <c r="L167" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="N167" t="s">
         <v>1304</v>
@@ -21665,16 +21803,16 @@
         <v>159</v>
       </c>
       <c r="C168" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="E168" t="s">
         <v>658</v>
       </c>
       <c r="H168" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I168" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J168" t="s">
         <v>1026</v>
@@ -21703,7 +21841,7 @@
         <v>1082</v>
       </c>
       <c r="I169" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="J169" t="s">
         <v>785</v>
@@ -21729,7 +21867,7 @@
         <v>1083</v>
       </c>
       <c r="I170" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J170" t="s">
         <v>1085</v>
@@ -21758,7 +21896,7 @@
         <v>660</v>
       </c>
       <c r="F171" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="I171" t="s">
         <v>844</v>
@@ -21773,7 +21911,7 @@
         <v>792</v>
       </c>
       <c r="N171" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="O171" s="1">
         <v>2</v>
@@ -21790,13 +21928,13 @@
         <v>661</v>
       </c>
       <c r="F172" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="H172" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I172" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J172" t="s">
         <v>898</v>
@@ -21892,7 +22030,7 @@
         <v>663</v>
       </c>
       <c r="F175" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="H175" t="s">
         <v>1092</v>
@@ -21927,7 +22065,7 @@
         <v>1093</v>
       </c>
       <c r="I176" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J176" t="s">
         <v>769</v>
@@ -21947,7 +22085,7 @@
         <v>167</v>
       </c>
       <c r="C177" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="E177" t="s">
         <v>665</v>
@@ -21982,7 +22120,7 @@
         <v>666</v>
       </c>
       <c r="H178" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I178" t="s">
         <v>846</v>
@@ -22043,7 +22181,7 @@
         <v>938</v>
       </c>
       <c r="I180" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="J180" t="s">
         <v>796</v>
@@ -22101,7 +22239,7 @@
         <v>831</v>
       </c>
       <c r="I182" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J182" t="s">
         <v>794</v>
@@ -22127,7 +22265,7 @@
         <v>982</v>
       </c>
       <c r="I183" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J183" t="s">
         <v>859</v>
@@ -22217,7 +22355,7 @@
         <v>1202</v>
       </c>
       <c r="C186" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="E186" t="s">
         <v>688</v>
@@ -22290,7 +22428,7 @@
         <v>1109</v>
       </c>
       <c r="I188" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J188" t="s">
         <v>1110</v>
@@ -22316,7 +22454,7 @@
         <v>1111</v>
       </c>
       <c r="I189" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J189" t="s">
         <v>758</v>
@@ -22339,13 +22477,13 @@
         <v>677</v>
       </c>
       <c r="F190" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="H190" t="s">
         <v>1112</v>
       </c>
       <c r="I190" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J190" t="s">
         <v>1113</v>
@@ -22400,7 +22538,7 @@
         <v>679</v>
       </c>
       <c r="F192" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="I192" t="s">
         <v>1117</v>
@@ -22432,13 +22570,13 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="E193" t="s">
         <v>680</v>
       </c>
       <c r="F193" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="H193" t="s">
         <v>1118</v>
@@ -22520,7 +22658,7 @@
         <v>1121</v>
       </c>
       <c r="N195" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="O195" s="1">
         <v>2</v>
@@ -22540,7 +22678,7 @@
         <v>682</v>
       </c>
       <c r="F196" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="I196" t="s">
         <v>1117</v>
@@ -22566,7 +22704,7 @@
         <v>183</v>
       </c>
       <c r="C197" t="s">
-        <v>1511</v>
+        <v>1528</v>
       </c>
       <c r="E197" t="s">
         <v>683</v>
@@ -22584,7 +22722,7 @@
         <v>494</v>
       </c>
       <c r="N197" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="O197" s="1">
         <v>3</v>
@@ -22604,7 +22742,7 @@
         <v>684</v>
       </c>
       <c r="F198" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="H198" t="s">
         <v>1138</v>
@@ -22636,7 +22774,7 @@
         <v>184</v>
       </c>
       <c r="C199" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="E199" t="s">
         <v>685</v>
@@ -22674,7 +22812,7 @@
         <v>686</v>
       </c>
       <c r="F200" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="I200" t="s">
         <v>844</v>
@@ -22712,7 +22850,7 @@
         <v>767</v>
       </c>
       <c r="L201" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="M201" t="s">
         <v>494</v>
@@ -22732,10 +22870,10 @@
         <v>738</v>
       </c>
       <c r="F202" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="I202" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J202" t="s">
         <v>1214</v>
@@ -22758,16 +22896,16 @@
         <v>188</v>
       </c>
       <c r="C203" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="E203" t="s">
         <v>690</v>
       </c>
       <c r="F203" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="I203" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J203" t="s">
         <v>801</v>
@@ -22828,7 +22966,7 @@
         <v>1301</v>
       </c>
       <c r="I205" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J205" t="s">
         <v>801</v>
@@ -22860,7 +22998,7 @@
         <v>1134</v>
       </c>
       <c r="I206" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J206" t="s">
         <v>853</v>
@@ -22886,7 +23024,7 @@
         <v>586</v>
       </c>
       <c r="I207" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J207" t="s">
         <v>1283</v>
@@ -22909,7 +23047,7 @@
         <v>1135</v>
       </c>
       <c r="I208" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J208" t="s">
         <v>1136</v>
@@ -22935,7 +23073,7 @@
         <v>1208</v>
       </c>
       <c r="I209" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J209" t="s">
         <v>769</v>
@@ -22944,7 +23082,7 @@
         <v>818</v>
       </c>
       <c r="N209" t="s">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="O209" s="1">
         <v>1</v>
@@ -22958,13 +23096,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="E210" t="s">
         <v>513</v>
       </c>
       <c r="F210" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="I210" t="s">
         <v>888</v>
@@ -23002,7 +23140,7 @@
         <v>695</v>
       </c>
       <c r="F211" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H211" t="s">
         <v>1139</v>
@@ -23040,7 +23178,7 @@
         <v>1140</v>
       </c>
       <c r="I212" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J212" t="s">
         <v>1141</v>
@@ -23052,7 +23190,7 @@
         <v>788</v>
       </c>
       <c r="N212" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="O212" s="1">
         <v>1</v>
@@ -23098,13 +23236,13 @@
         <v>698</v>
       </c>
       <c r="F214" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="H214" t="s">
         <v>1143</v>
       </c>
       <c r="I214" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J214" t="s">
         <v>1115</v>
@@ -23133,7 +23271,7 @@
         <v>1144</v>
       </c>
       <c r="I215" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="J215" t="s">
         <v>786</v>
@@ -23145,7 +23283,7 @@
         <v>788</v>
       </c>
       <c r="N215" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="O215" s="1">
         <v>1</v>
@@ -23162,10 +23300,10 @@
         <v>700</v>
       </c>
       <c r="H216" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I216" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="J216" t="s">
         <v>864</v>
@@ -23191,10 +23329,13 @@
         <v>701</v>
       </c>
       <c r="F217" t="s">
-        <v>1442</v>
+        <v>1523</v>
+      </c>
+      <c r="G217" t="s">
+        <v>1524</v>
       </c>
       <c r="I217" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J217" t="s">
         <v>1145</v>
@@ -23217,13 +23358,13 @@
         <v>740</v>
       </c>
       <c r="C218" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="E218" t="s">
         <v>640</v>
       </c>
       <c r="F218" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="I218" t="s">
         <v>844</v>
@@ -23238,7 +23379,7 @@
         <v>788</v>
       </c>
       <c r="N218" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="O218" s="1">
         <v>2</v>
@@ -23319,7 +23460,7 @@
         <v>704</v>
       </c>
       <c r="F221" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="H221" t="s">
         <v>1150</v>
@@ -23354,13 +23495,13 @@
         <v>705</v>
       </c>
       <c r="F222" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="H222" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I222" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J222" t="s">
         <v>1152</v>
@@ -23372,7 +23513,7 @@
         <v>1200</v>
       </c>
       <c r="N222" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="O222" s="1">
         <v>2</v>
@@ -23392,7 +23533,7 @@
         <v>1153</v>
       </c>
       <c r="I223" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J223" t="s">
         <v>979</v>
@@ -23424,7 +23565,7 @@
         <v>1154</v>
       </c>
       <c r="I224" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J224" t="s">
         <v>797</v>
@@ -23462,7 +23603,7 @@
         <v>1054</v>
       </c>
       <c r="N225" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="O225" s="1">
         <v>1</v>
@@ -23479,13 +23620,13 @@
         <v>710</v>
       </c>
       <c r="F226" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="H226" t="s">
         <v>1204</v>
       </c>
       <c r="I226" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J226" t="s">
         <v>1017</v>
@@ -23513,8 +23654,11 @@
       <c r="E227" t="s">
         <v>711</v>
       </c>
+      <c r="F227" t="s">
+        <v>1520</v>
+      </c>
       <c r="I227" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J227" t="s">
         <v>942</v>
@@ -23546,7 +23690,7 @@
         <v>1156</v>
       </c>
       <c r="I228" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J228" t="s">
         <v>1157</v>
@@ -23601,7 +23745,7 @@
         <v>714</v>
       </c>
       <c r="I230" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J230" t="s">
         <v>815</v>
@@ -23630,7 +23774,7 @@
         <v>1159</v>
       </c>
       <c r="I231" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J231" t="s">
         <v>785</v>
@@ -23656,7 +23800,7 @@
         <v>1088</v>
       </c>
       <c r="I232" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J232" t="s">
         <v>799</v>
@@ -23668,7 +23812,7 @@
         <v>788</v>
       </c>
       <c r="N232" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="O232" s="1">
         <v>2</v>
@@ -23685,13 +23829,13 @@
         <v>717</v>
       </c>
       <c r="F233" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="H233" t="s">
         <v>1160</v>
       </c>
       <c r="I233" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J233" t="s">
         <v>1161</v>
@@ -23720,7 +23864,7 @@
         <v>718</v>
       </c>
       <c r="F234" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="I234" t="s">
         <v>844</v>
@@ -23738,7 +23882,7 @@
         <v>494</v>
       </c>
       <c r="N234" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="O234" s="1">
         <v>3</v>
@@ -23755,7 +23899,7 @@
         <v>719</v>
       </c>
       <c r="F235" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="I235" t="s">
         <v>844</v>
@@ -23781,7 +23925,7 @@
         <v>218</v>
       </c>
       <c r="C236" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E236" t="s">
         <v>720</v>
@@ -23804,7 +23948,10 @@
         <v>746</v>
       </c>
       <c r="C237" t="s">
-        <v>1390</v>
+        <v>1389</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1525</v>
       </c>
       <c r="E237" t="s">
         <v>747</v>
@@ -23812,8 +23959,11 @@
       <c r="F237" t="s">
         <v>1181</v>
       </c>
+      <c r="G237" t="s">
+        <v>1526</v>
+      </c>
       <c r="I237" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J237" t="s">
         <v>1214</v>
@@ -23857,7 +24007,7 @@
         <v>1163</v>
       </c>
       <c r="N238" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="O238" s="1">
         <v>1</v>
@@ -23874,10 +24024,10 @@
         <v>722</v>
       </c>
       <c r="H239" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I239" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="J239" t="s">
         <v>769</v>
@@ -23889,7 +24039,7 @@
         <v>818</v>
       </c>
       <c r="N239" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="O239" s="1">
         <v>1</v>
@@ -23906,13 +24056,13 @@
         <v>723</v>
       </c>
       <c r="F240" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="H240" t="s">
         <v>1165</v>
       </c>
       <c r="I240" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J240" t="s">
         <v>796</v>
@@ -23938,13 +24088,13 @@
         <v>222</v>
       </c>
       <c r="C241" t="s">
-        <v>1391</v>
+        <v>1529</v>
       </c>
       <c r="E241" t="s">
         <v>724</v>
       </c>
       <c r="F241" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="I241" t="s">
         <v>1117</v>
@@ -23973,7 +24123,7 @@
         <v>725</v>
       </c>
       <c r="F242" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="I242" t="s">
         <v>844</v>
@@ -24034,7 +24184,7 @@
         <v>1167</v>
       </c>
       <c r="I244" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J244" t="s">
         <v>799</v>
@@ -24118,13 +24268,13 @@
         <v>730</v>
       </c>
       <c r="F247" t="s">
-        <v>1426</v>
+        <v>1522</v>
       </c>
       <c r="H247" t="s">
         <v>1170</v>
       </c>
       <c r="I247" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J247" t="s">
         <v>1171</v>
@@ -24153,7 +24303,7 @@
         <v>731</v>
       </c>
       <c r="F248" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="I248" t="s">
         <v>844</v>
@@ -24185,7 +24335,7 @@
         <v>1173</v>
       </c>
       <c r="I249" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J249" t="s">
         <v>871</v>
@@ -24214,13 +24364,13 @@
         <v>733</v>
       </c>
       <c r="F250" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="H250" t="s">
         <v>1175</v>
       </c>
       <c r="I250" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J250" t="s">
         <v>864</v>
@@ -24232,7 +24382,7 @@
         <v>788</v>
       </c>
       <c r="N250" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="O250" s="1">
         <v>1</v>
@@ -24246,13 +24396,13 @@
         <v>232</v>
       </c>
       <c r="C251" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="E251" t="s">
         <v>734</v>
       </c>
       <c r="F251" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="I251" t="s">
         <v>844</v>
@@ -24290,7 +24440,7 @@
         <v>902</v>
       </c>
       <c r="I252" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J252" t="s">
         <v>896</v>
@@ -24313,10 +24463,10 @@
         <v>736</v>
       </c>
       <c r="H253" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I253" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J253" t="s">
         <v>1177</v>
@@ -24342,13 +24492,13 @@
         <v>737</v>
       </c>
       <c r="F254" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="H254" t="s">
         <v>1179</v>
       </c>
       <c r="I254" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J254" t="s">
         <v>1180</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD83DF1-C58B-4CC1-B23D-2AB0ABB5B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC743B6-BE69-4187-8984-0C288A73C7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4318" uniqueCount="1549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="1568">
   <si>
     <t>Sigla</t>
   </si>
@@ -3935,9 +3935,6 @@
     <t>*La Paz</t>
   </si>
   <si>
-    <t>Porto di San Pietro</t>
-  </si>
-  <si>
     <t>*Belarus</t>
   </si>
   <si>
@@ -4043,9 +4040,6 @@
     <t>*Jamaica</t>
   </si>
   <si>
-    <t>*Micronesia</t>
-  </si>
-  <si>
     <t>strisce orizzontali, stella blu</t>
   </si>
   <si>
@@ -4298,9 +4292,6 @@
     <t>Asia, Mediterraneo</t>
   </si>
   <si>
-    <t>Babbane</t>
-  </si>
-  <si>
     <t>Nuk</t>
   </si>
   <si>
@@ -4409,9 +4400,6 @@
     <t>graal dick</t>
   </si>
   <si>
-    <t>Maiuro</t>
-  </si>
-  <si>
     <t>Mia Mail, Nia may</t>
   </si>
   <si>
@@ -4511,9 +4499,6 @@
     <t>Sao Tome, Sao to me, Ciao tome</t>
   </si>
   <si>
-    <t>Un gerol wood, in garol wood, garolwood</t>
-  </si>
-  <si>
     <t>azerbaijan</t>
   </si>
   <si>
@@ -4532,18 +4517,12 @@
     <t>S eustatius, sintestatius, sintastatius</t>
   </si>
   <si>
-    <t>Gigi</t>
-  </si>
-  <si>
     <t>Repubblica Ceca, Rep Ceca, Cecchia</t>
   </si>
   <si>
     <t>Maiott, Mariott, Mariotti, Mylot</t>
   </si>
   <si>
-    <t>Una foti,</t>
-  </si>
-  <si>
     <t>Dr Shadn, thor charme</t>
   </si>
   <si>
@@ -4619,15 +4598,9 @@
     <t>Trìstan da Cùgna</t>
   </si>
   <si>
-    <t>Èdinbra of de Sèven Sìs</t>
-  </si>
-  <si>
     <t>emblema nazionale, animale, uccello</t>
   </si>
   <si>
-    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy</t>
-  </si>
-  <si>
     <t>Turks, Caicos, turks and caicos</t>
   </si>
   <si>
@@ -4686,6 +4659,90 @@
   </si>
   <si>
     <t>Vìnd huk</t>
+  </si>
+  <si>
+    <t>Batman 2, Cat mando</t>
+  </si>
+  <si>
+    <t>Porto di San Pietro, tempi per port</t>
+  </si>
+  <si>
+    <t>Gigi, Fiji</t>
+  </si>
+  <si>
+    <t>*Micronesia, datti federati di micronesia</t>
+  </si>
+  <si>
+    <t>S Maarten, Sint Marten</t>
+  </si>
+  <si>
+    <t>New e</t>
+  </si>
+  <si>
+    <t>Sènt Denì</t>
+  </si>
+  <si>
+    <t>Ngherùlmud</t>
+  </si>
+  <si>
+    <t>El Aiùn</t>
+  </si>
+  <si>
+    <t>Marigò</t>
+  </si>
+  <si>
+    <t>San Martèn</t>
+  </si>
+  <si>
+    <t>Duscianbé</t>
+  </si>
+  <si>
+    <t>Por Dusièm</t>
+  </si>
+  <si>
+    <t>Èdinbrha of de Sèven Sìis</t>
+  </si>
+  <si>
+    <t>Ashgabàt</t>
+  </si>
+  <si>
+    <t>Tashkènt</t>
+  </si>
+  <si>
+    <t>Anòi</t>
+  </si>
+  <si>
+    <t>Sanà a</t>
+  </si>
+  <si>
+    <t>Una foti, fai una foto</t>
+  </si>
+  <si>
+    <t>Maiuro, Ma giuro</t>
+  </si>
+  <si>
+    <t>Plymuth, Plasmat</t>
+  </si>
+  <si>
+    <t>Agatnia, agatna</t>
+  </si>
+  <si>
+    <t>Chiama Bud</t>
+  </si>
+  <si>
+    <t>Un gerol wood, in garol wood, garolwood, indietro il mood</t>
+  </si>
+  <si>
+    <t>Babbane, un babbane</t>
+  </si>
+  <si>
+    <t>Rii Ad</t>
+  </si>
+  <si>
+    <t>Cartum</t>
+  </si>
+  <si>
+    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy, bartalemi</t>
   </si>
 </sst>
 </file>
@@ -16483,7 +16540,7 @@
         <v>749</v>
       </c>
       <c r="D1" t="s">
-        <v>1510</v>
+        <v>1503</v>
       </c>
       <c r="E1" t="s">
         <v>497</v>
@@ -16492,7 +16549,7 @@
         <v>750</v>
       </c>
       <c r="G1" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="H1" t="s">
         <v>748</v>
@@ -16536,7 +16593,7 @@
         <v>753</v>
       </c>
       <c r="I2" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J2" t="s">
         <v>772</v>
@@ -16545,7 +16602,7 @@
         <v>773</v>
       </c>
       <c r="L2" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="N2" t="s">
         <v>1242</v>
@@ -16572,13 +16629,13 @@
         <v>499</v>
       </c>
       <c r="F3" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="H3" t="s">
         <v>1195</v>
       </c>
       <c r="I3" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="J3" t="s">
         <v>754</v>
@@ -16590,7 +16647,7 @@
         <v>780</v>
       </c>
       <c r="N3" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
@@ -16629,7 +16686,7 @@
         <v>818</v>
       </c>
       <c r="N4" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -16650,7 +16707,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1513</v>
+        <v>1506</v>
       </c>
       <c r="E5" t="s">
         <v>501</v>
@@ -16659,13 +16716,13 @@
         <v>756</v>
       </c>
       <c r="G5" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="H5" t="s">
         <v>757</v>
       </c>
       <c r="I5" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="J5" t="s">
         <v>758</v>
@@ -16695,7 +16752,7 @@
         <v>828</v>
       </c>
       <c r="I6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="J6" t="s">
         <v>754</v>
@@ -16707,7 +16764,7 @@
         <v>1218</v>
       </c>
       <c r="N6" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O6" s="1">
         <v>2</v>
@@ -16753,13 +16810,13 @@
         <v>504</v>
       </c>
       <c r="F8" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="I8" t="s">
         <v>888</v>
       </c>
       <c r="J8" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="L8" t="s">
         <v>783</v>
@@ -16784,11 +16841,14 @@
       <c r="F9" t="s">
         <v>763</v>
       </c>
+      <c r="G9" t="s">
+        <v>1565</v>
+      </c>
       <c r="H9" t="s">
         <v>829</v>
       </c>
       <c r="I9" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J9" t="s">
         <v>778</v>
@@ -16800,7 +16860,7 @@
         <v>1219</v>
       </c>
       <c r="N9" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -16820,7 +16880,7 @@
         <v>830</v>
       </c>
       <c r="I10" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="J10" t="s">
         <v>786</v>
@@ -16852,10 +16912,10 @@
         <v>765</v>
       </c>
       <c r="I11" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J11" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="N11" t="s">
         <v>1245</v>
@@ -16875,7 +16935,7 @@
         <v>513</v>
       </c>
       <c r="F12" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="I12" t="s">
         <v>888</v>
@@ -16890,7 +16950,7 @@
         <v>494</v>
       </c>
       <c r="N12" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="O12" s="1">
         <v>3</v>
@@ -16910,7 +16970,7 @@
         <v>583</v>
       </c>
       <c r="I13" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J13" t="s">
         <v>1214</v>
@@ -16948,7 +17008,7 @@
         <v>1077</v>
       </c>
       <c r="N14" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O14" s="1">
         <v>1</v>
@@ -16988,7 +17048,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="E16" t="s">
         <v>509</v>
@@ -16997,7 +17057,7 @@
         <v>887</v>
       </c>
       <c r="I16" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J16" t="s">
         <v>770</v>
@@ -17009,7 +17069,7 @@
         <v>818</v>
       </c>
       <c r="N16" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="O16" s="1">
         <v>2</v>
@@ -17055,7 +17115,7 @@
         <v>831</v>
       </c>
       <c r="I18" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J18" t="s">
         <v>794</v>
@@ -17072,19 +17132,19 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="E19" t="s">
         <v>512</v>
       </c>
       <c r="F19" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G19" t="s">
-        <v>1514</v>
+        <v>1507</v>
       </c>
       <c r="I19" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J19" t="s">
         <v>794</v>
@@ -17093,7 +17153,7 @@
         <v>494</v>
       </c>
       <c r="N19" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="O19" s="1">
         <v>3</v>
@@ -17114,7 +17174,7 @@
         <v>832</v>
       </c>
       <c r="I20" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J20" t="s">
         <v>796</v>
@@ -17126,7 +17186,7 @@
         <v>792</v>
       </c>
       <c r="N20" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="O20" s="1">
         <v>2</v>
@@ -17143,7 +17203,7 @@
         <v>516</v>
       </c>
       <c r="F21" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="I21" t="s">
         <v>888</v>
@@ -17178,7 +17238,7 @@
         <v>1205</v>
       </c>
       <c r="I22" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J22" t="s">
         <v>799</v>
@@ -17233,13 +17293,13 @@
         <v>519</v>
       </c>
       <c r="F24" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="H24" t="s">
         <v>834</v>
       </c>
       <c r="I24" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="J24" t="s">
         <v>801</v>
@@ -17288,13 +17348,13 @@
         <v>521</v>
       </c>
       <c r="F26" t="s">
-        <v>1504</v>
+        <v>1497</v>
       </c>
       <c r="H26" t="s">
         <v>802</v>
       </c>
       <c r="I26" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J26" t="s">
         <v>1066</v>
@@ -17317,7 +17377,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E27" t="s">
         <v>522</v>
@@ -17352,13 +17412,13 @@
         <v>1297</v>
       </c>
       <c r="G28" t="s">
-        <v>1515</v>
+        <v>1508</v>
       </c>
       <c r="H28" t="s">
         <v>810</v>
       </c>
       <c r="I28" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="J28" t="s">
         <v>811</v>
@@ -17381,16 +17441,16 @@
         <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>1516</v>
+        <v>1509</v>
       </c>
       <c r="E29" t="s">
         <v>525</v>
       </c>
       <c r="F29" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="G29" t="s">
-        <v>1517</v>
+        <v>1510</v>
       </c>
       <c r="I29" t="s">
         <v>888</v>
@@ -17408,7 +17468,7 @@
         <v>494</v>
       </c>
       <c r="N29" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="O29" s="1">
         <v>3</v>
@@ -17432,7 +17492,7 @@
         <v>836</v>
       </c>
       <c r="I30" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="J30" t="s">
         <v>797</v>
@@ -17444,7 +17504,7 @@
         <v>788</v>
       </c>
       <c r="N30" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O30" s="1">
         <v>1</v>
@@ -17461,7 +17521,7 @@
         <v>527</v>
       </c>
       <c r="F31" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="H31" t="s">
         <v>1056</v>
@@ -17493,7 +17553,7 @@
         <v>837</v>
       </c>
       <c r="I32" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="J32" t="s">
         <v>816</v>
@@ -17505,7 +17565,7 @@
         <v>1216</v>
       </c>
       <c r="N32" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="O32" s="1">
         <v>1</v>
@@ -17522,16 +17582,16 @@
         <v>529</v>
       </c>
       <c r="F33" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="G33" t="s">
-        <v>1518</v>
+        <v>1511</v>
       </c>
       <c r="H33" t="s">
         <v>1031</v>
       </c>
       <c r="I33" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="J33" t="s">
         <v>817</v>
@@ -17540,10 +17600,10 @@
         <v>776</v>
       </c>
       <c r="L33" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="N33" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="O33" s="1">
         <v>2</v>
@@ -17563,7 +17623,7 @@
         <v>838</v>
       </c>
       <c r="I34" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J34" t="s">
         <v>819</v>
@@ -17592,7 +17652,7 @@
         <v>820</v>
       </c>
       <c r="I35" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J35" t="s">
         <v>805</v>
@@ -17604,7 +17664,7 @@
         <v>788</v>
       </c>
       <c r="N35" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O35" s="1">
         <v>2</v>
@@ -17621,13 +17681,13 @@
         <v>532</v>
       </c>
       <c r="F36" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="H36" t="s">
         <v>826</v>
       </c>
       <c r="I36" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J36" t="s">
         <v>755</v>
@@ -17639,7 +17699,7 @@
         <v>788</v>
       </c>
       <c r="N36" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="O36" s="1">
         <v>2</v>
@@ -17656,13 +17716,13 @@
         <v>533</v>
       </c>
       <c r="F37" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="H37" t="s">
         <v>929</v>
       </c>
       <c r="I37" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J37" t="s">
         <v>853</v>
@@ -17694,13 +17754,13 @@
         <v>534</v>
       </c>
       <c r="F38" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="H38" t="s">
         <v>856</v>
       </c>
       <c r="I38" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="J38" t="s">
         <v>857</v>
@@ -17712,7 +17772,7 @@
         <v>788</v>
       </c>
       <c r="N38" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="O38" s="1">
         <v>1</v>
@@ -17761,7 +17821,7 @@
         <v>536</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>858</v>
@@ -17770,7 +17830,7 @@
         <v>788</v>
       </c>
       <c r="N40" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O40" s="9">
         <v>2</v>
@@ -17784,7 +17844,7 @@
         <v>1097</v>
       </c>
       <c r="C41" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="E41" t="s">
         <v>671</v>
@@ -17848,7 +17908,7 @@
         <v>865</v>
       </c>
       <c r="I43" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="J43" t="s">
         <v>767</v>
@@ -17860,7 +17920,7 @@
         <v>788</v>
       </c>
       <c r="N43" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O43" s="1">
         <v>1</v>
@@ -17883,7 +17943,7 @@
         <v>958</v>
       </c>
       <c r="I44" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J44" t="s">
         <v>864</v>
@@ -17895,7 +17955,7 @@
         <v>788</v>
       </c>
       <c r="N44" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="O44" s="1">
         <v>1</v>
@@ -17912,19 +17972,19 @@
         <v>540</v>
       </c>
       <c r="I45" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="J45" t="s">
         <v>866</v>
       </c>
       <c r="K45" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="L45" t="s">
         <v>875</v>
       </c>
       <c r="N45" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="O45" s="1">
         <v>1</v>
@@ -17979,7 +18039,7 @@
         <v>870</v>
       </c>
       <c r="I47" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="J47" t="s">
         <v>871</v>
@@ -18002,7 +18062,7 @@
         <v>542</v>
       </c>
       <c r="I48" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J48" t="s">
         <v>872</v>
@@ -18014,7 +18074,7 @@
         <v>818</v>
       </c>
       <c r="N48" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="O48" s="1">
         <v>2</v>
@@ -18063,7 +18123,7 @@
         <v>963</v>
       </c>
       <c r="I50" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J50" t="s">
         <v>767</v>
@@ -18075,7 +18135,7 @@
         <v>879</v>
       </c>
       <c r="N50" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="O50" s="1">
         <v>1</v>
@@ -18101,7 +18161,7 @@
         <v>964</v>
       </c>
       <c r="I51" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J51" t="s">
         <v>881</v>
@@ -18113,7 +18173,7 @@
         <v>792</v>
       </c>
       <c r="N51" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -18127,13 +18187,13 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="E52" t="s">
         <v>546</v>
       </c>
       <c r="F52" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="G52" t="s">
         <v>883</v>
@@ -18142,7 +18202,7 @@
         <v>965</v>
       </c>
       <c r="I52" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J52" t="s">
         <v>1067</v>
@@ -18197,7 +18257,7 @@
         <v>967</v>
       </c>
       <c r="I54" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="J54" t="s">
         <v>785</v>
@@ -18223,7 +18283,7 @@
         <v>549</v>
       </c>
       <c r="F55" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="I55" t="s">
         <v>888</v>
@@ -18238,7 +18298,7 @@
         <v>1200</v>
       </c>
       <c r="N55" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="O55" s="1">
         <v>1</v>
@@ -18252,13 +18312,13 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="E56" t="s">
         <v>550</v>
       </c>
       <c r="F56" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="I56" t="s">
         <v>888</v>
@@ -18276,7 +18336,7 @@
         <v>494</v>
       </c>
       <c r="N56" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O56" s="1">
         <v>3</v>
@@ -18293,10 +18353,10 @@
         <v>551</v>
       </c>
       <c r="H57" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="I57" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J57" t="s">
         <v>769</v>
@@ -18319,7 +18379,7 @@
         <v>552</v>
       </c>
       <c r="F58" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="I58" t="s">
         <v>888</v>
@@ -18354,13 +18414,13 @@
         <v>892</v>
       </c>
       <c r="I59" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="J59" t="s">
         <v>871</v>
       </c>
       <c r="L59" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
       <c r="N59" t="s">
         <v>1245</v>
@@ -18380,7 +18440,7 @@
         <v>554</v>
       </c>
       <c r="F60" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="H60" t="s">
         <v>894</v>
@@ -18412,7 +18472,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="E61" t="s">
         <v>555</v>
@@ -18459,7 +18519,7 @@
         <v>902</v>
       </c>
       <c r="I62" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J62" t="s">
         <v>903</v>
@@ -18482,7 +18542,7 @@
         <v>905</v>
       </c>
       <c r="I63" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J63" t="s">
         <v>906</v>
@@ -18511,7 +18571,7 @@
         <v>909</v>
       </c>
       <c r="I64" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J64" t="s">
         <v>907</v>
@@ -18531,13 +18591,13 @@
         <v>741</v>
       </c>
       <c r="C65" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="E65" t="s">
         <v>709</v>
       </c>
       <c r="F65" t="s">
-        <v>1419</v>
+        <v>1564</v>
       </c>
       <c r="H65" t="s">
         <v>1057</v>
@@ -18572,7 +18632,7 @@
         <v>915</v>
       </c>
       <c r="I66" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J66" t="s">
         <v>801</v>
@@ -18584,7 +18644,7 @@
         <v>1231</v>
       </c>
       <c r="N66" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O66" s="1">
         <v>1</v>
@@ -18598,7 +18658,7 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>1497</v>
+        <v>1542</v>
       </c>
       <c r="E67" t="s">
         <v>560</v>
@@ -18627,7 +18687,7 @@
         <v>561</v>
       </c>
       <c r="I68" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="J68" t="s">
         <v>916</v>
@@ -18639,7 +18699,7 @@
         <v>1228</v>
       </c>
       <c r="N68" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="O68" s="1">
         <v>1</v>
@@ -18659,7 +18719,7 @@
         <v>917</v>
       </c>
       <c r="I69" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J69" t="s">
         <v>918</v>
@@ -18708,16 +18768,16 @@
         <v>564</v>
       </c>
       <c r="F71" t="s">
-        <v>1502</v>
+        <v>1495</v>
       </c>
       <c r="G71" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
       <c r="H71" t="s">
         <v>968</v>
       </c>
       <c r="I71" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="J71" t="s">
         <v>816</v>
@@ -18772,13 +18832,13 @@
         <v>566</v>
       </c>
       <c r="F73" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="H73" t="s">
         <v>925</v>
       </c>
       <c r="I73" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J73" t="s">
         <v>927</v>
@@ -18804,7 +18864,7 @@
         <v>931</v>
       </c>
       <c r="I74" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J74" t="s">
         <v>794</v>
@@ -18882,7 +18942,7 @@
         <v>74</v>
       </c>
       <c r="C77" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="E77" t="s">
         <v>570</v>
@@ -18891,7 +18951,7 @@
         <v>969</v>
       </c>
       <c r="I77" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J77" t="s">
         <v>936</v>
@@ -18903,7 +18963,7 @@
         <v>788</v>
       </c>
       <c r="N77" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="O77" s="1">
         <v>1</v>
@@ -18917,7 +18977,7 @@
         <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E78" t="s">
         <v>571</v>
@@ -18929,7 +18989,7 @@
         <v>937</v>
       </c>
       <c r="N78" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="O78" s="1">
         <v>1</v>
@@ -18946,7 +19006,7 @@
         <v>572</v>
       </c>
       <c r="I79" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J79" t="s">
         <v>794</v>
@@ -18958,7 +19018,7 @@
         <v>792</v>
       </c>
       <c r="N79" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="O79" s="1">
         <v>1</v>
@@ -18978,7 +19038,7 @@
         <v>938</v>
       </c>
       <c r="I80" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="J80" t="s">
         <v>794</v>
@@ -19007,19 +19067,19 @@
         <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="E81" t="s">
         <v>78</v>
       </c>
       <c r="F81" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="H81" t="s">
         <v>944</v>
       </c>
       <c r="I81" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J81" t="s">
         <v>939</v>
@@ -19031,7 +19091,7 @@
         <v>788</v>
       </c>
       <c r="N81" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="O81" s="1">
         <v>2</v>
@@ -19051,7 +19111,7 @@
         <v>961</v>
       </c>
       <c r="I82" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J82" t="s">
         <v>898</v>
@@ -19063,7 +19123,7 @@
         <v>1200</v>
       </c>
       <c r="N82" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="O82" s="1">
         <v>2</v>
@@ -19083,7 +19143,7 @@
         <v>945</v>
       </c>
       <c r="I83" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="J83" t="s">
         <v>919</v>
@@ -19106,7 +19166,7 @@
         <v>575</v>
       </c>
       <c r="F84" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="I84" t="s">
         <v>1117</v>
@@ -19121,7 +19181,7 @@
         <v>879</v>
       </c>
       <c r="N84" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="O84" s="1">
         <v>2</v>
@@ -19138,7 +19198,7 @@
         <v>576</v>
       </c>
       <c r="F85" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="H85" t="s">
         <v>960</v>
@@ -19176,7 +19236,7 @@
         <v>941</v>
       </c>
       <c r="L86" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="M86" t="s">
         <v>494</v>
@@ -19196,7 +19256,10 @@
         <v>578</v>
       </c>
       <c r="F87" t="s">
-        <v>1530</v>
+        <v>1561</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1521</v>
       </c>
       <c r="I87" t="s">
         <v>844</v>
@@ -19257,10 +19320,10 @@
         <v>580</v>
       </c>
       <c r="F89" t="s">
-        <v>1298</v>
+        <v>1541</v>
       </c>
       <c r="I89" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J89" t="s">
         <v>946</v>
@@ -19286,13 +19349,13 @@
         <v>581</v>
       </c>
       <c r="F90" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="H90" t="s">
         <v>1012</v>
       </c>
       <c r="I90" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J90" t="s">
         <v>811</v>
@@ -19315,16 +19378,16 @@
         <v>948</v>
       </c>
       <c r="F91" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="G91" t="s">
-        <v>1531</v>
+        <v>1522</v>
       </c>
       <c r="H91" t="s">
         <v>949</v>
       </c>
       <c r="I91" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="J91" t="s">
         <v>950</v>
@@ -19356,7 +19419,7 @@
         <v>951</v>
       </c>
       <c r="I92" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J92" t="s">
         <v>811</v>
@@ -19368,7 +19431,7 @@
         <v>788</v>
       </c>
       <c r="N92" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="O92" s="1">
         <v>2</v>
@@ -19388,7 +19451,7 @@
         <v>952</v>
       </c>
       <c r="I93" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="J93" t="s">
         <v>811</v>
@@ -19414,13 +19477,13 @@
         <v>953</v>
       </c>
       <c r="G94" t="s">
-        <v>1532</v>
+        <v>1523</v>
       </c>
       <c r="H94" t="s">
         <v>955</v>
       </c>
       <c r="I94" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="J94" t="s">
         <v>956</v>
@@ -19435,7 +19498,7 @@
         <v>494</v>
       </c>
       <c r="N94" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="O94" s="1">
         <v>3</v>
@@ -19452,7 +19515,7 @@
         <v>626</v>
       </c>
       <c r="F95" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="H95" t="s">
         <v>972</v>
@@ -19499,7 +19562,7 @@
         <v>788</v>
       </c>
       <c r="N96" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="O96" s="1">
         <v>2</v>
@@ -19519,7 +19582,7 @@
         <v>975</v>
       </c>
       <c r="I97" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J97" t="s">
         <v>769</v>
@@ -19534,7 +19597,7 @@
         <v>494</v>
       </c>
       <c r="N97" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="O97" s="1">
         <v>3</v>
@@ -19557,7 +19620,7 @@
         <v>1207</v>
       </c>
       <c r="I98" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J98" t="s">
         <v>1067</v>
@@ -19586,13 +19649,13 @@
         <v>588</v>
       </c>
       <c r="F99" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="H99" t="s">
         <v>1032</v>
       </c>
       <c r="I99" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="J99" t="s">
         <v>769</v>
@@ -19647,7 +19710,7 @@
         <v>978</v>
       </c>
       <c r="I101" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="J101" t="s">
         <v>979</v>
@@ -19679,7 +19742,7 @@
         <v>980</v>
       </c>
       <c r="I102" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="J102" t="s">
         <v>896</v>
@@ -19711,7 +19774,7 @@
         <v>981</v>
       </c>
       <c r="I103" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J103" t="s">
         <v>1068</v>
@@ -19769,7 +19832,7 @@
         <v>983</v>
       </c>
       <c r="I105" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J105" t="s">
         <v>767</v>
@@ -19795,10 +19858,10 @@
         <v>595</v>
       </c>
       <c r="G106" t="s">
-        <v>1533</v>
+        <v>1524</v>
       </c>
       <c r="I106" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J106" t="s">
         <v>769</v>
@@ -19813,7 +19876,7 @@
         <v>494</v>
       </c>
       <c r="N106" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="O106" s="1">
         <v>3</v>
@@ -19833,10 +19896,10 @@
         <v>596</v>
       </c>
       <c r="F107" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="G107" t="s">
-        <v>1534</v>
+        <v>1525</v>
       </c>
       <c r="I107" t="s">
         <v>844</v>
@@ -19848,13 +19911,13 @@
         <v>778</v>
       </c>
       <c r="L107" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="M107" t="s">
         <v>494</v>
       </c>
       <c r="N107" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O107" s="1">
         <v>3</v>
@@ -19906,16 +19969,16 @@
         <v>789</v>
       </c>
       <c r="D109" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="E109" t="s">
         <v>598</v>
       </c>
       <c r="F109" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="I109" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J109" t="s">
         <v>758</v>
@@ -19973,7 +20036,7 @@
         <v>600</v>
       </c>
       <c r="F111" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="I111" t="s">
         <v>844</v>
@@ -19991,7 +20054,7 @@
         <v>494</v>
       </c>
       <c r="N111" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O111" s="1">
         <v>3</v>
@@ -20011,7 +20074,7 @@
         <v>601</v>
       </c>
       <c r="G112" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="I112" t="s">
         <v>844</v>
@@ -20029,7 +20092,7 @@
         <v>494</v>
       </c>
       <c r="N112" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O112" s="1">
         <v>3</v>
@@ -20049,7 +20112,7 @@
         <v>602</v>
       </c>
       <c r="G113" t="s">
-        <v>1537</v>
+        <v>1528</v>
       </c>
       <c r="I113" t="s">
         <v>850</v>
@@ -20081,13 +20144,13 @@
         <v>604</v>
       </c>
       <c r="F114" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="G114" t="s">
-        <v>1538</v>
+        <v>1529</v>
       </c>
       <c r="I114" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J114" t="s">
         <v>916</v>
@@ -20110,13 +20173,13 @@
         <v>108</v>
       </c>
       <c r="C115" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="E115" t="s">
         <v>605</v>
       </c>
       <c r="F115" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="I115" t="s">
         <v>841</v>
@@ -20131,7 +20194,7 @@
         <v>494</v>
       </c>
       <c r="N115" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="O115" s="1">
         <v>3</v>
@@ -20151,7 +20214,7 @@
         <v>606</v>
       </c>
       <c r="F116" t="s">
-        <v>1456</v>
+        <v>1559</v>
       </c>
       <c r="I116" t="s">
         <v>844</v>
@@ -20163,7 +20226,7 @@
         <v>788</v>
       </c>
       <c r="N116" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O116" s="1">
         <v>2</v>
@@ -20183,7 +20246,7 @@
         <v>597</v>
       </c>
       <c r="F117" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="I117" t="s">
         <v>844</v>
@@ -20215,7 +20278,7 @@
         <v>607</v>
       </c>
       <c r="F118" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I118" t="s">
         <v>844</v>
@@ -20230,7 +20293,7 @@
         <v>788</v>
       </c>
       <c r="N118" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O118" s="1">
         <v>2</v>
@@ -20253,7 +20316,7 @@
         <v>888</v>
       </c>
       <c r="J119" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="L119" t="s">
         <v>1232</v>
@@ -20262,7 +20325,7 @@
         <v>494</v>
       </c>
       <c r="N119" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="O119" s="1">
         <v>3</v>
@@ -20311,7 +20374,7 @@
         <v>994</v>
       </c>
       <c r="I121" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J121" t="s">
         <v>815</v>
@@ -20323,7 +20386,7 @@
         <v>788</v>
       </c>
       <c r="N121" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="O121" s="1">
         <v>1</v>
@@ -20369,7 +20432,7 @@
         <v>998</v>
       </c>
       <c r="I123" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J123" t="s">
         <v>999</v>
@@ -20378,7 +20441,7 @@
         <v>1005</v>
       </c>
       <c r="N123" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="O123" s="1">
         <v>1</v>
@@ -20395,10 +20458,10 @@
         <v>613</v>
       </c>
       <c r="H124" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="I124" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J124" t="s">
         <v>1001</v>
@@ -20424,7 +20487,7 @@
         <v>614</v>
       </c>
       <c r="F125" t="s">
-        <v>1507</v>
+        <v>1500</v>
       </c>
       <c r="G125" t="s">
         <v>1010</v>
@@ -20433,7 +20496,7 @@
         <v>1002</v>
       </c>
       <c r="I125" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J125" t="s">
         <v>864</v>
@@ -20445,7 +20508,7 @@
         <v>783</v>
       </c>
       <c r="N125" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="O125" s="1">
         <v>2</v>
@@ -20465,7 +20528,7 @@
         <v>1009</v>
       </c>
       <c r="G126" t="s">
-        <v>1539</v>
+        <v>1530</v>
       </c>
       <c r="I126" t="s">
         <v>844</v>
@@ -20497,7 +20560,7 @@
         <v>1006</v>
       </c>
       <c r="I127" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J127" t="s">
         <v>797</v>
@@ -20512,7 +20575,7 @@
         <v>494</v>
       </c>
       <c r="N127" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="O127" s="1">
         <v>3</v>
@@ -20526,25 +20589,25 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="D128" t="s">
-        <v>1540</v>
+        <v>1531</v>
       </c>
       <c r="E128" t="s">
         <v>617</v>
       </c>
       <c r="F128" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="G128" t="s">
-        <v>1541</v>
+        <v>1532</v>
       </c>
       <c r="H128" t="s">
         <v>1008</v>
       </c>
       <c r="I128" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J128" t="s">
         <v>1001</v>
@@ -20570,7 +20633,7 @@
         <v>1013</v>
       </c>
       <c r="I129" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J129" t="s">
         <v>853</v>
@@ -20599,7 +20662,7 @@
         <v>619</v>
       </c>
       <c r="F130" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="H130" t="s">
         <v>1058</v>
@@ -20634,7 +20697,7 @@
         <v>1015</v>
       </c>
       <c r="I131" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J131" t="s">
         <v>769</v>
@@ -20660,7 +20723,7 @@
         <v>1016</v>
       </c>
       <c r="I132" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J132" t="s">
         <v>1017</v>
@@ -20689,13 +20752,13 @@
         <v>622</v>
       </c>
       <c r="F133" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="H133" t="s">
         <v>1018</v>
       </c>
       <c r="I133" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J133" t="s">
         <v>916</v>
@@ -20707,7 +20770,7 @@
         <v>788</v>
       </c>
       <c r="N133" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O133" s="1">
         <v>2</v>
@@ -20739,7 +20802,7 @@
         <v>818</v>
       </c>
       <c r="N134" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="O134" s="1">
         <v>1</v>
@@ -20756,7 +20819,7 @@
         <v>624</v>
       </c>
       <c r="F135" t="s">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="H135" t="s">
         <v>1021</v>
@@ -20794,7 +20857,7 @@
         <v>1049</v>
       </c>
       <c r="I136" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J136" t="s">
         <v>807</v>
@@ -20820,7 +20883,7 @@
         <v>1024</v>
       </c>
       <c r="I137" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J137" t="s">
         <v>1025</v>
@@ -20846,7 +20909,7 @@
         <v>975</v>
       </c>
       <c r="I138" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J138" t="s">
         <v>778</v>
@@ -20861,7 +20924,7 @@
         <v>494</v>
       </c>
       <c r="N138" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="O138" s="1">
         <v>3</v>
@@ -20887,7 +20950,7 @@
         <v>1196</v>
       </c>
       <c r="I139" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J139" t="s">
         <v>864</v>
@@ -20910,7 +20973,7 @@
         <v>628</v>
       </c>
       <c r="I140" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J140" t="s">
         <v>1026</v>
@@ -20927,7 +20990,7 @@
         <v>134</v>
       </c>
       <c r="D141" t="s">
-        <v>1542</v>
+        <v>1533</v>
       </c>
       <c r="E141" t="s">
         <v>629</v>
@@ -20936,7 +20999,7 @@
         <v>1027</v>
       </c>
       <c r="I141" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J141" t="s">
         <v>1023</v>
@@ -20962,7 +21025,7 @@
         <v>335</v>
       </c>
       <c r="C142" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="E142" t="s">
         <v>630</v>
@@ -20971,7 +21034,7 @@
         <v>1047</v>
       </c>
       <c r="I142" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J142" t="s">
         <v>859</v>
@@ -20983,7 +21046,7 @@
         <v>818</v>
       </c>
       <c r="N142" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="O142" s="1">
         <v>1</v>
@@ -21000,10 +21063,10 @@
         <v>631</v>
       </c>
       <c r="F143" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="I143" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J143" t="s">
         <v>805</v>
@@ -21015,7 +21078,7 @@
         <v>873</v>
       </c>
       <c r="N143" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="O143" s="1">
         <v>2</v>
@@ -21035,7 +21098,7 @@
         <v>1034</v>
       </c>
       <c r="I144" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J144" t="s">
         <v>801</v>
@@ -21102,7 +21165,7 @@
         <v>788</v>
       </c>
       <c r="N146" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="O146" s="1">
         <v>1</v>
@@ -21148,13 +21211,13 @@
         <v>636</v>
       </c>
       <c r="F148" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="H148" t="s">
         <v>1036</v>
       </c>
       <c r="I148" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J148" t="s">
         <v>805</v>
@@ -21166,7 +21229,7 @@
         <v>818</v>
       </c>
       <c r="N148" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="O148" s="1">
         <v>2</v>
@@ -21183,10 +21246,10 @@
         <v>637</v>
       </c>
       <c r="F149" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="I149" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J149" t="s">
         <v>1038</v>
@@ -21206,31 +21269,31 @@
         <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E150" t="s">
         <v>638</v>
       </c>
       <c r="F150" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="G150" t="s">
-        <v>1543</v>
+        <v>1534</v>
       </c>
       <c r="I150" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J150" t="s">
         <v>916</v>
       </c>
       <c r="L150" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="M150" t="s">
         <v>494</v>
       </c>
       <c r="N150" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="O150" s="1">
         <v>3</v>
@@ -21282,7 +21345,7 @@
         <v>641</v>
       </c>
       <c r="G152" t="s">
-        <v>1544</v>
+        <v>1535</v>
       </c>
       <c r="H152" t="s">
         <v>1039</v>
@@ -21320,7 +21383,7 @@
         <v>1040</v>
       </c>
       <c r="I153" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J153" t="s">
         <v>800</v>
@@ -21352,7 +21415,7 @@
         <v>1197</v>
       </c>
       <c r="I154" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="J154" t="s">
         <v>864</v>
@@ -21378,7 +21441,7 @@
         <v>645</v>
       </c>
       <c r="F155" t="s">
-        <v>1042</v>
+        <v>1560</v>
       </c>
       <c r="I155" t="s">
         <v>1117</v>
@@ -21410,7 +21473,7 @@
         <v>1059</v>
       </c>
       <c r="I156" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J156" t="s">
         <v>1041</v>
@@ -21419,7 +21482,7 @@
         <v>1236</v>
       </c>
       <c r="N156" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="O156" s="1">
         <v>2</v>
@@ -21439,16 +21502,16 @@
         <v>523</v>
       </c>
       <c r="F157" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="G157" t="s">
-        <v>1545</v>
+        <v>1536</v>
       </c>
       <c r="H157" t="s">
         <v>835</v>
       </c>
       <c r="I157" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J157" t="s">
         <v>807</v>
@@ -21460,7 +21523,7 @@
         <v>788</v>
       </c>
       <c r="N157" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="O157" s="1">
         <v>2</v>
@@ -21474,16 +21537,16 @@
         <v>149</v>
       </c>
       <c r="C158" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="E158" t="s">
         <v>647</v>
       </c>
       <c r="F158" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="G158" t="s">
-        <v>1548</v>
+        <v>1539</v>
       </c>
       <c r="H158" t="s">
         <v>1065</v>
@@ -21515,7 +21578,7 @@
         <v>648</v>
       </c>
       <c r="F159" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
       <c r="I159" t="s">
         <v>844</v>
@@ -21530,7 +21593,7 @@
         <v>788</v>
       </c>
       <c r="N159" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O159" s="1">
         <v>2</v>
@@ -21546,11 +21609,14 @@
       <c r="E160" t="s">
         <v>649</v>
       </c>
+      <c r="F160" t="s">
+        <v>1540</v>
+      </c>
       <c r="H160" t="s">
         <v>1061</v>
       </c>
       <c r="I160" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J160" t="s">
         <v>800</v>
@@ -21562,7 +21628,7 @@
         <v>783</v>
       </c>
       <c r="N160" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="O160" s="1">
         <v>2</v>
@@ -21579,7 +21645,7 @@
         <v>650</v>
       </c>
       <c r="F161" t="s">
-        <v>1503</v>
+        <v>1496</v>
       </c>
       <c r="H161" t="s">
         <v>1062</v>
@@ -21611,16 +21677,16 @@
         <v>651</v>
       </c>
       <c r="F162" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="G162" t="s">
-        <v>1546</v>
+        <v>1537</v>
       </c>
       <c r="H162" t="s">
         <v>1064</v>
       </c>
       <c r="I162" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J162" t="s">
         <v>1067</v>
@@ -21649,16 +21715,16 @@
         <v>652</v>
       </c>
       <c r="F163" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="G163" t="s">
-        <v>1547</v>
+        <v>1538</v>
       </c>
       <c r="H163" t="s">
         <v>1070</v>
       </c>
       <c r="I163" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J163" t="s">
         <v>764</v>
@@ -21677,6 +21743,9 @@
       <c r="B164" t="s">
         <v>155</v>
       </c>
+      <c r="D164" t="s">
+        <v>1545</v>
+      </c>
       <c r="E164" t="s">
         <v>653</v>
       </c>
@@ -21696,7 +21765,7 @@
         <v>494</v>
       </c>
       <c r="N164" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="O164" s="1">
         <v>3</v>
@@ -21716,7 +21785,7 @@
         <v>1072</v>
       </c>
       <c r="I165" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J165" t="s">
         <v>785</v>
@@ -21742,7 +21811,7 @@
         <v>655</v>
       </c>
       <c r="F166" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="I166" t="s">
         <v>844</v>
@@ -21786,10 +21855,10 @@
         <v>769</v>
       </c>
       <c r="L167" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="N167" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="O167" s="1">
         <v>1</v>
@@ -21803,16 +21872,16 @@
         <v>159</v>
       </c>
       <c r="C168" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="E168" t="s">
         <v>658</v>
       </c>
       <c r="H168" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="I168" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J168" t="s">
         <v>1026</v>
@@ -21841,7 +21910,7 @@
         <v>1082</v>
       </c>
       <c r="I169" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J169" t="s">
         <v>785</v>
@@ -21863,11 +21932,14 @@
       <c r="E170" t="s">
         <v>659</v>
       </c>
+      <c r="F170" t="s">
+        <v>1562</v>
+      </c>
       <c r="H170" t="s">
         <v>1083</v>
       </c>
       <c r="I170" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J170" t="s">
         <v>1085</v>
@@ -21879,7 +21951,7 @@
         <v>818</v>
       </c>
       <c r="N170" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="O170" s="1">
         <v>1</v>
@@ -21896,7 +21968,10 @@
         <v>660</v>
       </c>
       <c r="F171" t="s">
-        <v>1490</v>
+        <v>1563</v>
+      </c>
+      <c r="G171" t="s">
+        <v>1547</v>
       </c>
       <c r="I171" t="s">
         <v>844</v>
@@ -21911,7 +21986,7 @@
         <v>792</v>
       </c>
       <c r="N171" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="O171" s="1">
         <v>2</v>
@@ -21928,13 +22003,13 @@
         <v>661</v>
       </c>
       <c r="F172" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="H172" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="I172" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J172" t="s">
         <v>898</v>
@@ -21978,7 +22053,7 @@
         <v>788</v>
       </c>
       <c r="N173" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="O173" s="1">
         <v>1</v>
@@ -22013,7 +22088,7 @@
         <v>1091</v>
       </c>
       <c r="N174" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O174" s="1">
         <v>2</v>
@@ -22030,7 +22105,7 @@
         <v>663</v>
       </c>
       <c r="F175" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="H175" t="s">
         <v>1092</v>
@@ -22065,7 +22140,7 @@
         <v>1093</v>
       </c>
       <c r="I176" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="J176" t="s">
         <v>769</v>
@@ -22085,7 +22160,7 @@
         <v>167</v>
       </c>
       <c r="C177" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="E177" t="s">
         <v>665</v>
@@ -22120,7 +22195,7 @@
         <v>666</v>
       </c>
       <c r="H178" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="I178" t="s">
         <v>846</v>
@@ -22161,7 +22236,7 @@
         <v>494</v>
       </c>
       <c r="N179" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="O179" s="1">
         <v>3</v>
@@ -22181,7 +22256,7 @@
         <v>938</v>
       </c>
       <c r="I180" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="J180" t="s">
         <v>796</v>
@@ -22239,7 +22314,7 @@
         <v>831</v>
       </c>
       <c r="I182" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J182" t="s">
         <v>794</v>
@@ -22265,7 +22340,7 @@
         <v>982</v>
       </c>
       <c r="I183" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J183" t="s">
         <v>859</v>
@@ -22306,7 +22381,7 @@
         <v>788</v>
       </c>
       <c r="N184" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="O184" s="1">
         <v>2</v>
@@ -22341,7 +22416,7 @@
         <v>788</v>
       </c>
       <c r="N185" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="O185" s="1">
         <v>1</v>
@@ -22355,7 +22430,7 @@
         <v>1202</v>
       </c>
       <c r="C186" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="E186" t="s">
         <v>688</v>
@@ -22427,8 +22502,11 @@
       <c r="F188" t="s">
         <v>1109</v>
       </c>
+      <c r="G188" t="s">
+        <v>1546</v>
+      </c>
       <c r="I188" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J188" t="s">
         <v>1110</v>
@@ -22454,7 +22532,7 @@
         <v>1111</v>
       </c>
       <c r="I189" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J189" t="s">
         <v>758</v>
@@ -22477,13 +22555,13 @@
         <v>677</v>
       </c>
       <c r="F190" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="H190" t="s">
         <v>1112</v>
       </c>
       <c r="I190" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J190" t="s">
         <v>1113</v>
@@ -22538,7 +22616,7 @@
         <v>679</v>
       </c>
       <c r="F192" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="I192" t="s">
         <v>1117</v>
@@ -22556,7 +22634,7 @@
         <v>494</v>
       </c>
       <c r="N192" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="O192" s="1">
         <v>3</v>
@@ -22570,13 +22648,16 @@
         <v>180</v>
       </c>
       <c r="C193" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="E193" t="s">
         <v>680</v>
       </c>
       <c r="F193" t="s">
-        <v>1479</v>
+        <v>1475</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1548</v>
       </c>
       <c r="H193" t="s">
         <v>1118</v>
@@ -22597,7 +22678,7 @@
         <v>494</v>
       </c>
       <c r="N193" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="O193" s="1">
         <v>3</v>
@@ -22629,7 +22710,7 @@
         <v>788</v>
       </c>
       <c r="N194" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O194" s="1">
         <v>2</v>
@@ -22658,7 +22739,7 @@
         <v>1121</v>
       </c>
       <c r="N195" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="O195" s="1">
         <v>2</v>
@@ -22678,7 +22759,7 @@
         <v>682</v>
       </c>
       <c r="F196" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="I196" t="s">
         <v>1117</v>
@@ -22704,7 +22785,7 @@
         <v>183</v>
       </c>
       <c r="C197" t="s">
-        <v>1528</v>
+        <v>1567</v>
       </c>
       <c r="E197" t="s">
         <v>683</v>
@@ -22722,7 +22803,7 @@
         <v>494</v>
       </c>
       <c r="N197" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="O197" s="1">
         <v>3</v>
@@ -22738,11 +22819,17 @@
       <c r="C198" t="s">
         <v>1128</v>
       </c>
+      <c r="D198" t="s">
+        <v>1550</v>
+      </c>
       <c r="E198" t="s">
         <v>684</v>
       </c>
       <c r="F198" t="s">
-        <v>1437</v>
+        <v>1434</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1549</v>
       </c>
       <c r="H198" t="s">
         <v>1138</v>
@@ -22774,7 +22861,7 @@
         <v>184</v>
       </c>
       <c r="C199" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="E199" t="s">
         <v>685</v>
@@ -22812,7 +22899,7 @@
         <v>686</v>
       </c>
       <c r="F200" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="I200" t="s">
         <v>844</v>
@@ -22827,7 +22914,7 @@
         <v>1075</v>
       </c>
       <c r="N200" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O200" s="1">
         <v>2</v>
@@ -22850,7 +22937,7 @@
         <v>767</v>
       </c>
       <c r="L201" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="M201" t="s">
         <v>494</v>
@@ -22870,10 +22957,10 @@
         <v>738</v>
       </c>
       <c r="F202" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="I202" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J202" t="s">
         <v>1214</v>
@@ -22896,16 +22983,16 @@
         <v>188</v>
       </c>
       <c r="C203" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="E203" t="s">
         <v>690</v>
       </c>
       <c r="F203" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="I203" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="J203" t="s">
         <v>801</v>
@@ -22917,7 +23004,7 @@
         <v>1200</v>
       </c>
       <c r="N203" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="O203" s="1">
         <v>2</v>
@@ -22946,7 +23033,7 @@
         <v>494</v>
       </c>
       <c r="N204" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="O204" s="1">
         <v>3</v>
@@ -22963,10 +23050,10 @@
         <v>692</v>
       </c>
       <c r="H205" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="I205" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J205" t="s">
         <v>801</v>
@@ -22978,7 +23065,7 @@
         <v>788</v>
       </c>
       <c r="N205" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="O205" s="1">
         <v>1</v>
@@ -22998,7 +23085,7 @@
         <v>1134</v>
       </c>
       <c r="I206" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J206" t="s">
         <v>853</v>
@@ -23024,7 +23111,7 @@
         <v>586</v>
       </c>
       <c r="I207" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J207" t="s">
         <v>1283</v>
@@ -23047,7 +23134,7 @@
         <v>1135</v>
       </c>
       <c r="I208" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J208" t="s">
         <v>1136</v>
@@ -23073,7 +23160,7 @@
         <v>1208</v>
       </c>
       <c r="I209" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="J209" t="s">
         <v>769</v>
@@ -23082,7 +23169,7 @@
         <v>818</v>
       </c>
       <c r="N209" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="O209" s="1">
         <v>1</v>
@@ -23096,13 +23183,13 @@
         <v>485</v>
       </c>
       <c r="C210" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="E210" t="s">
         <v>513</v>
       </c>
       <c r="F210" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="I210" t="s">
         <v>888</v>
@@ -23120,7 +23207,7 @@
         <v>494</v>
       </c>
       <c r="N210" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="O210" s="1">
         <v>3</v>
@@ -23134,13 +23221,13 @@
         <v>195</v>
       </c>
       <c r="C211" t="s">
-        <v>1125</v>
+        <v>1544</v>
       </c>
       <c r="E211" t="s">
         <v>695</v>
       </c>
       <c r="F211" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H211" t="s">
         <v>1139</v>
@@ -23178,7 +23265,7 @@
         <v>1140</v>
       </c>
       <c r="I212" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J212" t="s">
         <v>1141</v>
@@ -23190,7 +23277,7 @@
         <v>788</v>
       </c>
       <c r="N212" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="O212" s="1">
         <v>1</v>
@@ -23236,13 +23323,13 @@
         <v>698</v>
       </c>
       <c r="F214" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="H214" t="s">
         <v>1143</v>
       </c>
       <c r="I214" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="J214" t="s">
         <v>1115</v>
@@ -23271,7 +23358,7 @@
         <v>1144</v>
       </c>
       <c r="I215" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J215" t="s">
         <v>786</v>
@@ -23283,7 +23370,7 @@
         <v>788</v>
       </c>
       <c r="N215" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="O215" s="1">
         <v>1</v>
@@ -23300,10 +23387,10 @@
         <v>700</v>
       </c>
       <c r="H216" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="I216" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="J216" t="s">
         <v>864</v>
@@ -23329,13 +23416,13 @@
         <v>701</v>
       </c>
       <c r="F217" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
       <c r="G217" t="s">
-        <v>1524</v>
+        <v>1517</v>
       </c>
       <c r="I217" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J217" t="s">
         <v>1145</v>
@@ -23358,13 +23445,13 @@
         <v>740</v>
       </c>
       <c r="C218" t="s">
-        <v>1334</v>
+        <v>1543</v>
       </c>
       <c r="E218" t="s">
         <v>640</v>
       </c>
       <c r="F218" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="I218" t="s">
         <v>844</v>
@@ -23379,7 +23466,7 @@
         <v>788</v>
       </c>
       <c r="N218" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="O218" s="1">
         <v>2</v>
@@ -23417,7 +23504,7 @@
         <v>788</v>
       </c>
       <c r="N219" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O219" s="1">
         <v>1</v>
@@ -23460,7 +23547,10 @@
         <v>704</v>
       </c>
       <c r="F221" t="s">
-        <v>1462</v>
+        <v>1458</v>
+      </c>
+      <c r="G221" t="s">
+        <v>1566</v>
       </c>
       <c r="H221" t="s">
         <v>1150</v>
@@ -23495,13 +23585,14 @@
         <v>705</v>
       </c>
       <c r="F222" t="s">
-        <v>1433</v>
-      </c>
+        <v>1430</v>
+      </c>
+      <c r="G222" s="10"/>
       <c r="H222" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="I222" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J222" t="s">
         <v>1152</v>
@@ -23513,7 +23604,7 @@
         <v>1200</v>
       </c>
       <c r="N222" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="O222" s="1">
         <v>2</v>
@@ -23533,7 +23624,7 @@
         <v>1153</v>
       </c>
       <c r="I223" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="J223" t="s">
         <v>979</v>
@@ -23545,7 +23636,7 @@
         <v>788</v>
       </c>
       <c r="N223" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O223" s="1">
         <v>2</v>
@@ -23565,7 +23656,7 @@
         <v>1154</v>
       </c>
       <c r="I224" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J224" t="s">
         <v>797</v>
@@ -23603,7 +23694,7 @@
         <v>1054</v>
       </c>
       <c r="N225" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="O225" s="1">
         <v>1</v>
@@ -23620,13 +23711,16 @@
         <v>710</v>
       </c>
       <c r="F226" t="s">
-        <v>1484</v>
+        <v>1480</v>
+      </c>
+      <c r="G226" t="s">
+        <v>1551</v>
       </c>
       <c r="H226" t="s">
         <v>1204</v>
       </c>
       <c r="I226" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J226" t="s">
         <v>1017</v>
@@ -23638,7 +23732,7 @@
         <v>1194</v>
       </c>
       <c r="N226" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O226" s="1">
         <v>2</v>
@@ -23655,10 +23749,10 @@
         <v>711</v>
       </c>
       <c r="F227" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="I227" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J227" t="s">
         <v>942</v>
@@ -23690,7 +23784,7 @@
         <v>1156</v>
       </c>
       <c r="I228" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J228" t="s">
         <v>1157</v>
@@ -23715,6 +23809,9 @@
       <c r="F229" t="s">
         <v>1186</v>
       </c>
+      <c r="G229" t="s">
+        <v>1552</v>
+      </c>
       <c r="J229" t="s">
         <v>767</v>
       </c>
@@ -23745,7 +23842,7 @@
         <v>714</v>
       </c>
       <c r="I230" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="J230" t="s">
         <v>815</v>
@@ -23774,7 +23871,7 @@
         <v>1159</v>
       </c>
       <c r="I231" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J231" t="s">
         <v>785</v>
@@ -23800,7 +23897,7 @@
         <v>1088</v>
       </c>
       <c r="I232" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="J232" t="s">
         <v>799</v>
@@ -23812,7 +23909,7 @@
         <v>788</v>
       </c>
       <c r="N232" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="O232" s="1">
         <v>2</v>
@@ -23829,13 +23926,13 @@
         <v>717</v>
       </c>
       <c r="F233" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="H233" t="s">
         <v>1160</v>
       </c>
       <c r="I233" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J233" t="s">
         <v>1161</v>
@@ -23847,7 +23944,7 @@
         <v>788</v>
       </c>
       <c r="N233" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O233" s="1">
         <v>2</v>
@@ -23864,7 +23961,7 @@
         <v>718</v>
       </c>
       <c r="F234" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="I234" t="s">
         <v>844</v>
@@ -23882,7 +23979,7 @@
         <v>494</v>
       </c>
       <c r="N234" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="O234" s="1">
         <v>3</v>
@@ -23899,7 +23996,7 @@
         <v>719</v>
       </c>
       <c r="F235" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="I235" t="s">
         <v>844</v>
@@ -23925,7 +24022,7 @@
         <v>218</v>
       </c>
       <c r="C236" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E236" t="s">
         <v>720</v>
@@ -23948,10 +24045,10 @@
         <v>746</v>
       </c>
       <c r="C237" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D237" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="E237" t="s">
         <v>747</v>
@@ -23960,10 +24057,10 @@
         <v>1181</v>
       </c>
       <c r="G237" t="s">
-        <v>1526</v>
+        <v>1553</v>
       </c>
       <c r="I237" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J237" t="s">
         <v>1214</v>
@@ -24007,7 +24104,7 @@
         <v>1163</v>
       </c>
       <c r="N238" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="O238" s="1">
         <v>1</v>
@@ -24024,10 +24121,10 @@
         <v>722</v>
       </c>
       <c r="H239" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I239" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="J239" t="s">
         <v>769</v>
@@ -24039,7 +24136,7 @@
         <v>818</v>
       </c>
       <c r="N239" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="O239" s="1">
         <v>1</v>
@@ -24056,13 +24153,16 @@
         <v>723</v>
       </c>
       <c r="F240" t="s">
-        <v>1452</v>
+        <v>1449</v>
+      </c>
+      <c r="G240" t="s">
+        <v>1554</v>
       </c>
       <c r="H240" t="s">
         <v>1165</v>
       </c>
       <c r="I240" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J240" t="s">
         <v>796</v>
@@ -24074,7 +24174,7 @@
         <v>818</v>
       </c>
       <c r="N240" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="O240" s="1">
         <v>2</v>
@@ -24088,13 +24188,13 @@
         <v>222</v>
       </c>
       <c r="C241" t="s">
-        <v>1529</v>
+        <v>1520</v>
       </c>
       <c r="E241" t="s">
         <v>724</v>
       </c>
       <c r="F241" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="I241" t="s">
         <v>1117</v>
@@ -24123,7 +24223,7 @@
         <v>725</v>
       </c>
       <c r="F242" t="s">
-        <v>1500</v>
+        <v>1558</v>
       </c>
       <c r="I242" t="s">
         <v>844</v>
@@ -24138,7 +24238,7 @@
         <v>1071</v>
       </c>
       <c r="N242" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="O242" s="1">
         <v>2</v>
@@ -24184,7 +24284,7 @@
         <v>1167</v>
       </c>
       <c r="I244" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J244" t="s">
         <v>799</v>
@@ -24268,13 +24368,16 @@
         <v>730</v>
       </c>
       <c r="F247" t="s">
-        <v>1522</v>
+        <v>1515</v>
+      </c>
+      <c r="G247" t="s">
+        <v>1555</v>
       </c>
       <c r="H247" t="s">
         <v>1170</v>
       </c>
       <c r="I247" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J247" t="s">
         <v>1171</v>
@@ -24286,7 +24389,7 @@
         <v>818</v>
       </c>
       <c r="N247" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="O247" s="1">
         <v>2</v>
@@ -24303,7 +24406,7 @@
         <v>731</v>
       </c>
       <c r="F248" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="I248" t="s">
         <v>844</v>
@@ -24335,7 +24438,7 @@
         <v>1173</v>
       </c>
       <c r="I249" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="J249" t="s">
         <v>871</v>
@@ -24347,7 +24450,7 @@
         <v>788</v>
       </c>
       <c r="N249" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="O249" s="1">
         <v>1</v>
@@ -24364,13 +24467,16 @@
         <v>733</v>
       </c>
       <c r="F250" t="s">
-        <v>1480</v>
+        <v>1476</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1556</v>
       </c>
       <c r="H250" t="s">
         <v>1175</v>
       </c>
       <c r="I250" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J250" t="s">
         <v>864</v>
@@ -24382,7 +24488,7 @@
         <v>788</v>
       </c>
       <c r="N250" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="O250" s="1">
         <v>1</v>
@@ -24396,13 +24502,13 @@
         <v>232</v>
       </c>
       <c r="C251" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="E251" t="s">
         <v>734</v>
       </c>
       <c r="F251" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="I251" t="s">
         <v>844</v>
@@ -24436,11 +24542,14 @@
       <c r="F252" t="s">
         <v>1183</v>
       </c>
+      <c r="G252" t="s">
+        <v>1557</v>
+      </c>
       <c r="H252" t="s">
         <v>902</v>
       </c>
       <c r="I252" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J252" t="s">
         <v>896</v>
@@ -24463,10 +24572,10 @@
         <v>736</v>
       </c>
       <c r="H253" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="I253" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J253" t="s">
         <v>1177</v>
@@ -24492,13 +24601,13 @@
         <v>737</v>
       </c>
       <c r="F254" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="H254" t="s">
         <v>1179</v>
       </c>
       <c r="I254" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J254" t="s">
         <v>1180</v>
@@ -24510,7 +24619,7 @@
         <v>788</v>
       </c>
       <c r="N254" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="O254" s="1">
         <v>1</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC743B6-BE69-4187-8984-0C288A73C7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BBD004-E85B-4C4A-BA93-6285B37417CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="1568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4339" uniqueCount="1573">
   <si>
     <t>Sigla</t>
   </si>
@@ -4743,6 +4743,21 @@
   </si>
   <si>
     <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy, bartalemi</t>
+  </si>
+  <si>
+    <t>Bosnia, Erzegovina</t>
+  </si>
+  <si>
+    <t>Tonia</t>
+  </si>
+  <si>
+    <t>Wham</t>
+  </si>
+  <si>
+    <t>Mari</t>
+  </si>
+  <si>
+    <t>Mauro</t>
   </si>
 </sst>
 </file>
@@ -4845,7 +4860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4861,6 +4876,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -17482,7 +17501,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>812</v>
+        <v>1568</v>
       </c>
       <c r="E30" t="s">
         <v>526</v>
@@ -18564,6 +18583,9 @@
       <c r="B64" t="s">
         <v>62</v>
       </c>
+      <c r="C64" t="s">
+        <v>1569</v>
+      </c>
       <c r="E64" t="s">
         <v>558</v>
       </c>
@@ -19252,6 +19274,9 @@
       <c r="B87" t="s">
         <v>84</v>
       </c>
+      <c r="C87" t="s">
+        <v>1570</v>
+      </c>
       <c r="E87" t="s">
         <v>578</v>
       </c>
@@ -21091,6 +21116,9 @@
       <c r="B144" t="s">
         <v>136</v>
       </c>
+      <c r="C144" t="s">
+        <v>1571</v>
+      </c>
       <c r="E144" t="s">
         <v>632</v>
       </c>
@@ -21574,6 +21602,9 @@
       <c r="B159" t="s">
         <v>150</v>
       </c>
+      <c r="C159" t="s">
+        <v>1572</v>
+      </c>
       <c r="E159" t="s">
         <v>648</v>
       </c>
@@ -22230,7 +22261,7 @@
         <v>773</v>
       </c>
       <c r="L179" t="s">
-        <v>1200</v>
+        <v>788</v>
       </c>
       <c r="M179" t="s">
         <v>494</v>
@@ -23284,31 +23315,37 @@
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E213" t="s">
+      <c r="C213" s="11"/>
+      <c r="D213" s="11"/>
+      <c r="E213" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="H213" t="s">
+      <c r="F213" s="11"/>
+      <c r="G213" s="11"/>
+      <c r="H213" s="11" t="s">
         <v>1142</v>
       </c>
-      <c r="I213" t="s">
+      <c r="I213" s="11" t="s">
         <v>846</v>
       </c>
-      <c r="J213" t="s">
+      <c r="J213" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="L213" t="s">
+      <c r="K213" s="11"/>
+      <c r="L213" s="11" t="s">
         <v>1221</v>
       </c>
+      <c r="M213" s="11"/>
       <c r="N213" t="s">
         <v>1245</v>
       </c>
-      <c r="O213" s="1">
+      <c r="O213" s="12">
         <v>1</v>
       </c>
     </row>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BBD004-E85B-4C4A-BA93-6285B37417CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E76307-CC90-41AC-8D43-26B8F5A2CC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="2640" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="20985" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4339" uniqueCount="1573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4359" uniqueCount="1597">
   <si>
     <t>Sigla</t>
   </si>
@@ -4301,9 +4301,6 @@
     <t>Assunzione</t>
   </si>
   <si>
-    <t>Valichir</t>
-  </si>
-  <si>
     <t>Nibbia</t>
   </si>
   <si>
@@ -4358,21 +4355,12 @@
     <t>Al-Kuwait, Kuwait city, Q8, Madina al Q8</t>
   </si>
   <si>
-    <t>Yamussukro, Yamusucro</t>
-  </si>
-  <si>
     <t>*Malabo, la pass</t>
   </si>
   <si>
-    <t>Coq burn town</t>
-  </si>
-  <si>
     <t>Arare</t>
   </si>
   <si>
-    <t>Wally se futura</t>
-  </si>
-  <si>
     <t>Gtega</t>
   </si>
   <si>
@@ -4388,21 +4376,12 @@
     <t>King's Town</t>
   </si>
   <si>
-    <t>Azkaban, Azkabat</t>
-  </si>
-  <si>
     <t>Sara Occidentale</t>
   </si>
   <si>
     <t>Bridgestone</t>
   </si>
   <si>
-    <t>graal dick</t>
-  </si>
-  <si>
-    <t>Mia Mail, Nia may</t>
-  </si>
-  <si>
     <t>Bandar, bandarzeri begawan</t>
   </si>
   <si>
@@ -4430,9 +4409,6 @@
     <t>Costa Avorio, D'avorio</t>
   </si>
   <si>
-    <t>Mamodzu, Mamotzu</t>
-  </si>
-  <si>
     <t>Masero</t>
   </si>
   <si>
@@ -4442,9 +4418,6 @@
     <t>Buia</t>
   </si>
   <si>
-    <t>Roso</t>
-  </si>
-  <si>
     <t>Lume</t>
   </si>
   <si>
@@ -4481,15 +4454,6 @@
     <t>Porti Lui</t>
   </si>
   <si>
-    <t>Dujabbe, Due gambe</t>
-  </si>
-  <si>
-    <t>Nuku alofa, Mutualopa, Nukolov</t>
-  </si>
-  <si>
-    <t>Cigali, Cialis</t>
-  </si>
-  <si>
     <t>Nuakchot, No rock shot, Workshop, mokchott</t>
   </si>
   <si>
@@ -4541,9 +4505,6 @@
     <t>Yaundé, Young, Yaounfe</t>
   </si>
   <si>
-    <t>Bishkek, Biscake, Bistecca, bisquet</t>
-  </si>
-  <si>
     <t>Numea, Lumea, nomea</t>
   </si>
   <si>
@@ -4589,9 +4550,6 @@
     <t>Taschent, Dash kent</t>
   </si>
   <si>
-    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte</t>
-  </si>
-  <si>
     <t>Srì Giaiauardenapùra Còtte</t>
   </si>
   <si>
@@ -4604,9 +4562,6 @@
     <t>Turks, Caicos, turks and caicos</t>
   </si>
   <si>
-    <t>Agàtgna</t>
-  </si>
-  <si>
     <t>Siutaàd de la pas</t>
   </si>
   <si>
@@ -4676,9 +4631,6 @@
     <t>S Maarten, Sint Marten</t>
   </si>
   <si>
-    <t>New e</t>
-  </si>
-  <si>
     <t>Sènt Denì</t>
   </si>
   <si>
@@ -4697,15 +4649,9 @@
     <t>Duscianbé</t>
   </si>
   <si>
-    <t>Por Dusièm</t>
-  </si>
-  <si>
     <t>Èdinbrha of de Sèven Sìis</t>
   </si>
   <si>
-    <t>Ashgabàt</t>
-  </si>
-  <si>
     <t>Tashkènt</t>
   </si>
   <si>
@@ -4715,18 +4661,12 @@
     <t>Sanà a</t>
   </si>
   <si>
-    <t>Una foti, fai una foto</t>
-  </si>
-  <si>
     <t>Maiuro, Ma giuro</t>
   </si>
   <si>
     <t>Plymuth, Plasmat</t>
   </si>
   <si>
-    <t>Agatnia, agatna</t>
-  </si>
-  <si>
     <t>Chiama Bud</t>
   </si>
   <si>
@@ -4758,6 +4698,138 @@
   </si>
   <si>
     <t>Mauro</t>
+  </si>
+  <si>
+    <t>Ash gabàt</t>
+  </si>
+  <si>
+    <t>Lilòngue</t>
+  </si>
+  <si>
+    <t>Magiuro</t>
+  </si>
+  <si>
+    <t>Ouaga, Ouagadogu, ouagadogo</t>
+  </si>
+  <si>
+    <t>Roso, rousseau</t>
+  </si>
+  <si>
+    <t>rayman</t>
+  </si>
+  <si>
+    <t>Tarawa, Sud Tarawa, garau a sud</t>
+  </si>
+  <si>
+    <t>Mamodzu, Mamotzu, ma mozu</t>
+  </si>
+  <si>
+    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis</t>
+  </si>
+  <si>
+    <t>Sao Tome, Sao to me, Ciao tome, soho to me</t>
+  </si>
+  <si>
+    <t>Valichir, valikir</t>
+  </si>
+  <si>
+    <t>Port Douzieme, cordusiom</t>
+  </si>
+  <si>
+    <t>Coq burn town, coop burn town</t>
+  </si>
+  <si>
+    <t>Una foti, fai una foto, kuna futi</t>
+  </si>
+  <si>
+    <t>base terra, passe terra</t>
+  </si>
+  <si>
+    <t>bel mo pan, belgio pan</t>
+  </si>
+  <si>
+    <t>carlot amelie, sciarlot</t>
+  </si>
+  <si>
+    <t>porto moresby, port mores bi</t>
+  </si>
+  <si>
+    <t>in giamena, engiamena</t>
+  </si>
+  <si>
+    <t>Mia Mail, Nia may, ni a me</t>
+  </si>
+  <si>
+    <t>Yamussukro, Yamusucro, gli amusso cro, yamusu cro</t>
+  </si>
+  <si>
+    <t>Cigali, Cialis, chi gali</t>
+  </si>
+  <si>
+    <t>kiscinao, kishinau</t>
+  </si>
+  <si>
+    <t>Dujabbe, Due gambe, du scian be</t>
+  </si>
+  <si>
+    <t>Bishkek, Biscake, Bistecca, bisquet, bis check</t>
+  </si>
+  <si>
+    <t>orientana</t>
+  </si>
+  <si>
+    <t>Azkaban, Azkabat, asgabat</t>
+  </si>
+  <si>
+    <t>papete, papete beach</t>
+  </si>
+  <si>
+    <t>Wally se futura, mata utu, mad a u2</t>
+  </si>
+  <si>
+    <t>a lo fi, all of i</t>
+  </si>
+  <si>
+    <t>New e, new wave, noi e</t>
+  </si>
+  <si>
+    <t>Nuku alofa, Mutualopa, Nukolov, nucu alofa, nuco a lo fa</t>
+  </si>
+  <si>
+    <t>lictenstain, frankenstein</t>
+  </si>
+  <si>
+    <t>Seiscel</t>
+  </si>
+  <si>
+    <t>Maurizio, Maurizius</t>
+  </si>
+  <si>
+    <t>Sòfia</t>
+  </si>
+  <si>
+    <t>Pnòm Pèn</t>
+  </si>
+  <si>
+    <t>Agàt gna</t>
+  </si>
+  <si>
+    <t>Antatanarivo, Antanarivo</t>
+  </si>
+  <si>
+    <t>Fòrt de France</t>
+  </si>
+  <si>
+    <t>Pòr Dusièm</t>
+  </si>
+  <si>
+    <t>graal dick, cralendic, cra l'endic, tra l'endic, crale, calendar</t>
+  </si>
+  <si>
+    <t>Agatnia, agatna, agata, a gatta, la gatta, accatna, a canna</t>
+  </si>
+  <si>
+    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte, cotti, sri giaia, striglia guarda, free java, tre giaia, pura cotte</t>
   </si>
 </sst>
 </file>
@@ -4876,21 +4948,47 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -16143,12 +16241,12 @@
     <sortCondition ref="B1:B254"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{C69A84BF-08C6-4051-820A-053DF45718B4}" name="Sigla" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{C69A84BF-08C6-4051-820A-053DF45718B4}" name="Sigla" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{E07D78F6-8AAC-46C7-9978-B6D2697016C9}" name="Paese" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{237EE744-113E-41B5-A3B5-EAE5FB442A2A}" name="Alias - paese"/>
+    <tableColumn id="7" xr3:uid="{237EE744-113E-41B5-A3B5-EAE5FB442A2A}" name="Alias - paese" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{0025EC9F-08BF-408D-9B17-F0234A6D6CF3}" name="Pronuncia_paese"/>
     <tableColumn id="4" xr3:uid="{50A4CCBE-582F-4110-BFBE-9A82392BC235}" name="Capitale"/>
-    <tableColumn id="11" xr3:uid="{6A83C5DC-9025-46CB-87AA-3A300C8CF314}" name="Alias - capitale"/>
+    <tableColumn id="11" xr3:uid="{6A83C5DC-9025-46CB-87AA-3A300C8CF314}" name="Alias - capitale" dataDxfId="0"/>
     <tableColumn id="15" xr3:uid="{AC13460F-731B-4E22-ABFF-160F80636E6A}" name="Pronuncia_capitale"/>
     <tableColumn id="8" xr3:uid="{D0F9292E-BC3F-4A24-BCFF-7BC92AA199DC}" name="Confini"/>
     <tableColumn id="12" xr3:uid="{5E4DE2A9-E4C6-4C56-9D54-D689B707F205}" name="Continente/Area geografica"/>
@@ -16156,8 +16254,8 @@
     <tableColumn id="6" xr3:uid="{1693D812-90EC-4EB0-992E-5CCE55839A4A}" name="Colore emblema"/>
     <tableColumn id="10" xr3:uid="{C924A7D7-A27D-4A41-9F45-DAF1CF135E69}" name="simboli bandiera"/>
     <tableColumn id="5" xr3:uid="{00F3A94F-DF24-4C44-822F-B9855F17B5A1}" name="dipendente"/>
-    <tableColumn id="14" xr3:uid="{1D457A4D-7A9B-4CE0-A285-4706192AD985}" name="Caratteristiche bandiera" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{FE0D03FC-F89A-4732-8C5E-E7737E148AB2}" name="Livello" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{1D457A4D-7A9B-4CE0-A285-4706192AD985}" name="Caratteristiche bandiera" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{FE0D03FC-F89A-4732-8C5E-E7737E148AB2}" name="Livello" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16555,11 +16653,11 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="10" t="s">
         <v>749</v>
       </c>
       <c r="D1" t="s">
-        <v>1503</v>
+        <v>1490</v>
       </c>
       <c r="E1" t="s">
         <v>497</v>
@@ -16568,7 +16666,7 @@
         <v>750</v>
       </c>
       <c r="G1" t="s">
-        <v>1504</v>
+        <v>1491</v>
       </c>
       <c r="H1" t="s">
         <v>748</v>
@@ -16602,12 +16700,13 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="11" t="s">
         <v>752</v>
       </c>
       <c r="E2" t="s">
         <v>498</v>
       </c>
+      <c r="F2" s="11"/>
       <c r="H2" t="s">
         <v>753</v>
       </c>
@@ -16644,11 +16743,12 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
+      <c r="C3" s="11"/>
       <c r="E3" t="s">
         <v>499</v>
       </c>
-      <c r="F3" t="s">
-        <v>1445</v>
+      <c r="F3" s="11" t="s">
+        <v>1441</v>
       </c>
       <c r="H3" t="s">
         <v>1195</v>
@@ -16686,9 +16786,11 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="11"/>
       <c r="E4" t="s">
         <v>500</v>
       </c>
+      <c r="F4" s="11"/>
       <c r="H4" t="s">
         <v>827</v>
       </c>
@@ -16725,17 +16827,18 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
+      <c r="C5" s="11"/>
       <c r="D5" t="s">
-        <v>1506</v>
+        <v>1493</v>
       </c>
       <c r="E5" t="s">
         <v>501</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="11" t="s">
         <v>756</v>
       </c>
       <c r="G5" t="s">
-        <v>1505</v>
+        <v>1492</v>
       </c>
       <c r="H5" t="s">
         <v>757</v>
@@ -16763,9 +16866,11 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
+      <c r="C6" s="11"/>
       <c r="E6" t="s">
         <v>502</v>
       </c>
+      <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" t="s">
         <v>828</v>
@@ -16796,9 +16901,11 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
+      <c r="C7" s="11"/>
       <c r="E7" t="s">
         <v>503</v>
       </c>
+      <c r="F7" s="11"/>
       <c r="I7" t="s">
         <v>888</v>
       </c>
@@ -16822,14 +16929,14 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="11" t="s">
         <v>759</v>
       </c>
       <c r="E8" t="s">
         <v>504</v>
       </c>
-      <c r="F8" t="s">
-        <v>1422</v>
+      <c r="F8" s="11" t="s">
+        <v>1421</v>
       </c>
       <c r="I8" t="s">
         <v>888</v>
@@ -16851,17 +16958,17 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="11" t="s">
         <v>762</v>
       </c>
       <c r="E9" t="s">
         <v>514</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="11" t="s">
         <v>763</v>
       </c>
       <c r="G9" t="s">
-        <v>1565</v>
+        <v>1545</v>
       </c>
       <c r="H9" t="s">
         <v>829</v>
@@ -16892,9 +16999,11 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
+      <c r="C10" s="11"/>
       <c r="E10" t="s">
         <v>505</v>
       </c>
+      <c r="F10" s="11"/>
       <c r="H10" t="s">
         <v>830</v>
       </c>
@@ -16924,9 +17033,11 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
+      <c r="C11" s="11"/>
       <c r="E11" t="s">
         <v>506</v>
       </c>
+      <c r="F11" s="11"/>
       <c r="H11" t="s">
         <v>765</v>
       </c>
@@ -16950,11 +17061,12 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
+      <c r="C12" s="11"/>
       <c r="E12" t="s">
         <v>513</v>
       </c>
-      <c r="F12" t="s">
-        <v>1465</v>
+      <c r="F12" s="11" t="s">
+        <v>1457</v>
       </c>
       <c r="I12" t="s">
         <v>888</v>
@@ -16982,12 +17094,13 @@
       <c r="B13" t="s">
         <v>745</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="11" t="s">
         <v>784</v>
       </c>
       <c r="E13" t="s">
         <v>583</v>
       </c>
+      <c r="F13" s="11"/>
       <c r="I13" t="s">
         <v>1399</v>
       </c>
@@ -17011,9 +17124,11 @@
       <c r="B14" t="s">
         <v>13</v>
       </c>
+      <c r="C14" s="11"/>
       <c r="E14" t="s">
         <v>507</v>
       </c>
+      <c r="F14" s="11"/>
       <c r="I14" t="s">
         <v>844</v>
       </c>
@@ -17040,9 +17155,11 @@
       <c r="B15" t="s">
         <v>14</v>
       </c>
+      <c r="C15" s="11"/>
       <c r="E15" t="s">
         <v>508</v>
       </c>
+      <c r="F15" s="11"/>
       <c r="H15" t="s">
         <v>768</v>
       </c>
@@ -17066,12 +17183,13 @@
       <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
-        <v>1486</v>
+      <c r="C16" s="11" t="s">
+        <v>1474</v>
       </c>
       <c r="E16" t="s">
         <v>509</v>
       </c>
+      <c r="F16" s="11"/>
       <c r="H16" t="s">
         <v>887</v>
       </c>
@@ -17101,9 +17219,11 @@
       <c r="B17" t="s">
         <v>16</v>
       </c>
+      <c r="C17" s="11"/>
       <c r="E17" t="s">
         <v>510</v>
       </c>
+      <c r="F17" s="11"/>
       <c r="I17" t="s">
         <v>888</v>
       </c>
@@ -17124,12 +17244,13 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="11" t="s">
         <v>793</v>
       </c>
       <c r="E18" t="s">
         <v>511</v>
       </c>
+      <c r="F18" s="11"/>
       <c r="H18" t="s">
         <v>831</v>
       </c>
@@ -17150,17 +17271,17 @@
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>1471</v>
+      <c r="C19" s="11" t="s">
+        <v>1462</v>
       </c>
       <c r="E19" t="s">
         <v>512</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="11" t="s">
         <v>1390</v>
       </c>
       <c r="G19" t="s">
-        <v>1507</v>
+        <v>1494</v>
       </c>
       <c r="I19" t="s">
         <v>1397</v>
@@ -17185,9 +17306,11 @@
       <c r="B20" t="s">
         <v>19</v>
       </c>
+      <c r="C20" s="11"/>
       <c r="E20" t="s">
         <v>515</v>
       </c>
+      <c r="F20" s="11"/>
       <c r="G20" s="10"/>
       <c r="H20" t="s">
         <v>832</v>
@@ -17218,11 +17341,12 @@
       <c r="B21" t="s">
         <v>20</v>
       </c>
+      <c r="C21" s="11"/>
       <c r="E21" t="s">
         <v>516</v>
       </c>
-      <c r="F21" t="s">
-        <v>1451</v>
+      <c r="F21" s="11" t="s">
+        <v>1446</v>
       </c>
       <c r="I21" t="s">
         <v>888</v>
@@ -17250,9 +17374,11 @@
       <c r="B22" t="s">
         <v>21</v>
       </c>
+      <c r="C22" s="11"/>
       <c r="E22" t="s">
         <v>517</v>
       </c>
+      <c r="F22" s="11"/>
       <c r="H22" t="s">
         <v>1205</v>
       </c>
@@ -17276,8 +17402,12 @@
       <c r="B23" t="s">
         <v>22</v>
       </c>
+      <c r="C23" s="11"/>
       <c r="E23" t="s">
         <v>518</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>1568</v>
       </c>
       <c r="H23" t="s">
         <v>833</v>
@@ -17308,11 +17438,12 @@
       <c r="B24" t="s">
         <v>23</v>
       </c>
+      <c r="C24" s="11"/>
       <c r="E24" t="s">
         <v>519</v>
       </c>
-      <c r="F24" t="s">
-        <v>1423</v>
+      <c r="F24" s="11" t="s">
+        <v>1422</v>
       </c>
       <c r="H24" t="s">
         <v>834</v>
@@ -17334,9 +17465,11 @@
       <c r="B25" t="s">
         <v>24</v>
       </c>
+      <c r="C25" s="11"/>
       <c r="E25" t="s">
         <v>520</v>
       </c>
+      <c r="F25" s="11"/>
       <c r="I25" t="s">
         <v>851</v>
       </c>
@@ -17360,14 +17493,14 @@
       <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="11" t="s">
         <v>885</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
       </c>
-      <c r="F26" t="s">
-        <v>1497</v>
+      <c r="F26" s="11" t="s">
+        <v>1485</v>
       </c>
       <c r="H26" t="s">
         <v>802</v>
@@ -17395,12 +17528,13 @@
       <c r="B27" t="s">
         <v>26</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="11" t="s">
         <v>1298</v>
       </c>
       <c r="E27" t="s">
         <v>522</v>
       </c>
+      <c r="F27" s="11"/>
       <c r="H27" t="s">
         <v>804</v>
       </c>
@@ -17424,14 +17558,15 @@
       <c r="B28" t="s">
         <v>28</v>
       </c>
+      <c r="C28" s="11"/>
       <c r="E28" t="s">
         <v>524</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="11" t="s">
         <v>1297</v>
       </c>
       <c r="G28" t="s">
-        <v>1508</v>
+        <v>1495</v>
       </c>
       <c r="H28" t="s">
         <v>810</v>
@@ -17459,17 +17594,18 @@
       <c r="B29" t="s">
         <v>484</v>
       </c>
-      <c r="C29" t="s">
-        <v>1509</v>
+      <c r="C29" s="11"/>
+      <c r="D29" t="s">
+        <v>1496</v>
       </c>
       <c r="E29" t="s">
         <v>525</v>
       </c>
-      <c r="F29" t="s">
-        <v>1452</v>
+      <c r="F29" s="11" t="s">
+        <v>1594</v>
       </c>
       <c r="G29" t="s">
-        <v>1510</v>
+        <v>1497</v>
       </c>
       <c r="I29" t="s">
         <v>888</v>
@@ -17500,12 +17636,13 @@
       <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="C30" t="s">
-        <v>1568</v>
+      <c r="C30" s="11" t="s">
+        <v>1548</v>
       </c>
       <c r="E30" t="s">
         <v>526</v>
       </c>
+      <c r="F30" s="11"/>
       <c r="G30" s="10"/>
       <c r="H30" t="s">
         <v>836</v>
@@ -17536,11 +17673,12 @@
       <c r="B31" t="s">
         <v>30</v>
       </c>
+      <c r="C31" s="11"/>
       <c r="E31" t="s">
         <v>527</v>
       </c>
-      <c r="F31" t="s">
-        <v>1514</v>
+      <c r="F31" s="11" t="s">
+        <v>1501</v>
       </c>
       <c r="H31" t="s">
         <v>1056</v>
@@ -17565,9 +17703,11 @@
       <c r="B32" t="s">
         <v>31</v>
       </c>
+      <c r="C32" s="11"/>
       <c r="E32" t="s">
         <v>528</v>
       </c>
+      <c r="F32" s="11"/>
       <c r="H32" t="s">
         <v>837</v>
       </c>
@@ -17597,14 +17737,15 @@
       <c r="B33" t="s">
         <v>32</v>
       </c>
+      <c r="C33" s="11"/>
       <c r="E33" t="s">
         <v>529</v>
       </c>
-      <c r="F33" t="s">
-        <v>1454</v>
+      <c r="F33" s="11" t="s">
+        <v>1447</v>
       </c>
       <c r="G33" t="s">
-        <v>1511</v>
+        <v>1498</v>
       </c>
       <c r="H33" t="s">
         <v>1031</v>
@@ -17635,8 +17776,13 @@
       <c r="B34" t="s">
         <v>33</v>
       </c>
+      <c r="C34" s="11"/>
       <c r="E34" t="s">
         <v>530</v>
+      </c>
+      <c r="F34" s="11"/>
+      <c r="G34" t="s">
+        <v>1588</v>
       </c>
       <c r="H34" t="s">
         <v>838</v>
@@ -17661,11 +17807,12 @@
       <c r="B35" t="s">
         <v>34</v>
       </c>
+      <c r="C35" s="11"/>
       <c r="E35" t="s">
         <v>531</v>
       </c>
-      <c r="F35" t="s">
-        <v>824</v>
+      <c r="F35" s="11" t="s">
+        <v>1556</v>
       </c>
       <c r="H35" t="s">
         <v>820</v>
@@ -17696,11 +17843,12 @@
       <c r="B36" t="s">
         <v>35</v>
       </c>
+      <c r="C36" s="11"/>
       <c r="E36" t="s">
         <v>532</v>
       </c>
-      <c r="F36" t="s">
-        <v>1444</v>
+      <c r="F36" s="11" t="s">
+        <v>1440</v>
       </c>
       <c r="H36" t="s">
         <v>826</v>
@@ -17731,11 +17879,15 @@
       <c r="B37" t="s">
         <v>36</v>
       </c>
+      <c r="C37" s="11"/>
       <c r="E37" t="s">
         <v>533</v>
       </c>
-      <c r="F37" t="s">
-        <v>1424</v>
+      <c r="F37" s="11" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1589</v>
       </c>
       <c r="H37" t="s">
         <v>929</v>
@@ -17766,14 +17918,14 @@
       <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="11" t="s">
         <v>923</v>
       </c>
       <c r="E38" t="s">
         <v>534</v>
       </c>
-      <c r="F38" t="s">
-        <v>1499</v>
+      <c r="F38" s="11" t="s">
+        <v>1487</v>
       </c>
       <c r="H38" t="s">
         <v>856</v>
@@ -17804,9 +17956,11 @@
       <c r="B39" t="s">
         <v>38</v>
       </c>
+      <c r="C39" s="11"/>
       <c r="E39" t="s">
         <v>535</v>
       </c>
+      <c r="F39" s="11"/>
       <c r="H39" t="s">
         <v>959</v>
       </c>
@@ -17836,9 +17990,11 @@
       <c r="B40" s="8" t="s">
         <v>39</v>
       </c>
+      <c r="C40" s="12"/>
       <c r="E40" s="8" t="s">
         <v>536</v>
       </c>
+      <c r="F40" s="12"/>
       <c r="I40" s="8" t="s">
         <v>1401</v>
       </c>
@@ -17862,12 +18018,13 @@
       <c r="B41" t="s">
         <v>1097</v>
       </c>
-      <c r="C41" t="s">
-        <v>1492</v>
+      <c r="C41" s="11" t="s">
+        <v>1480</v>
       </c>
       <c r="E41" t="s">
         <v>671</v>
       </c>
+      <c r="F41" s="11"/>
       <c r="H41" t="s">
         <v>1099</v>
       </c>
@@ -17891,8 +18048,12 @@
       <c r="B42" t="s">
         <v>40</v>
       </c>
+      <c r="C42" s="11"/>
       <c r="E42" t="s">
         <v>537</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>1571</v>
       </c>
       <c r="H42" t="s">
         <v>861</v>
@@ -17917,10 +18078,11 @@
       <c r="B43" t="s">
         <v>41</v>
       </c>
+      <c r="C43" s="11"/>
       <c r="E43" t="s">
         <v>538</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="11" t="s">
         <v>862</v>
       </c>
       <c r="H43" t="s">
@@ -17952,10 +18114,11 @@
       <c r="B44" t="s">
         <v>42</v>
       </c>
+      <c r="C44" s="11"/>
       <c r="E44" t="s">
         <v>539</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="11" t="s">
         <v>863</v>
       </c>
       <c r="H44" t="s">
@@ -17987,9 +18150,11 @@
       <c r="B45" t="s">
         <v>43</v>
       </c>
+      <c r="C45" s="11"/>
       <c r="E45" t="s">
         <v>540</v>
       </c>
+      <c r="F45" s="11"/>
       <c r="I45" t="s">
         <v>1416</v>
       </c>
@@ -18016,13 +18181,13 @@
       <c r="B46" t="s">
         <v>44</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="11" t="s">
         <v>868</v>
       </c>
       <c r="E46" t="s">
         <v>44</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="11" t="s">
         <v>868</v>
       </c>
       <c r="H46" t="s">
@@ -18051,9 +18216,11 @@
       <c r="B47" t="s">
         <v>45</v>
       </c>
+      <c r="C47" s="11"/>
       <c r="E47" t="s">
         <v>541</v>
       </c>
+      <c r="F47" s="11"/>
       <c r="H47" t="s">
         <v>870</v>
       </c>
@@ -18077,9 +18244,11 @@
       <c r="B48" t="s">
         <v>46</v>
       </c>
+      <c r="C48" s="11"/>
       <c r="E48" t="s">
         <v>542</v>
       </c>
+      <c r="F48" s="11"/>
       <c r="I48" t="s">
         <v>1402</v>
       </c>
@@ -18106,12 +18275,13 @@
       <c r="B49" t="s">
         <v>47</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="11" t="s">
         <v>876</v>
       </c>
       <c r="E49" t="s">
         <v>543</v>
       </c>
+      <c r="F49" s="11"/>
       <c r="H49" t="s">
         <v>962</v>
       </c>
@@ -18132,12 +18302,13 @@
       <c r="B50" t="s">
         <v>48</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="11" t="s">
         <v>877</v>
       </c>
       <c r="E50" t="s">
         <v>544</v>
       </c>
+      <c r="F50" s="11"/>
       <c r="H50" t="s">
         <v>963</v>
       </c>
@@ -18167,13 +18338,13 @@
       <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="11" t="s">
         <v>878</v>
       </c>
       <c r="E51" t="s">
         <v>545</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="11" t="s">
         <v>880</v>
       </c>
       <c r="H51" t="s">
@@ -18205,14 +18376,14 @@
       <c r="B52" t="s">
         <v>50</v>
       </c>
-      <c r="C52" t="s">
-        <v>1462</v>
+      <c r="C52" s="11" t="s">
+        <v>1455</v>
       </c>
       <c r="E52" t="s">
         <v>546</v>
       </c>
-      <c r="F52" t="s">
-        <v>1439</v>
+      <c r="F52" s="11" t="s">
+        <v>1573</v>
       </c>
       <c r="G52" t="s">
         <v>883</v>
@@ -18240,9 +18411,11 @@
       <c r="B53" t="s">
         <v>51</v>
       </c>
+      <c r="C53" s="11"/>
       <c r="E53" t="s">
         <v>547</v>
       </c>
+      <c r="F53" s="11"/>
       <c r="H53" t="s">
         <v>966</v>
       </c>
@@ -18269,9 +18442,11 @@
       <c r="B54" t="s">
         <v>52</v>
       </c>
+      <c r="C54" s="11"/>
       <c r="E54" t="s">
         <v>548</v>
       </c>
+      <c r="F54" s="11"/>
       <c r="H54" t="s">
         <v>967</v>
       </c>
@@ -18298,11 +18473,12 @@
       <c r="B55" t="s">
         <v>53</v>
       </c>
+      <c r="C55" s="11"/>
       <c r="E55" t="s">
         <v>549</v>
       </c>
-      <c r="F55" t="s">
-        <v>1477</v>
+      <c r="F55" s="11" t="s">
+        <v>1468</v>
       </c>
       <c r="I55" t="s">
         <v>888</v>
@@ -18330,14 +18506,14 @@
       <c r="B56" t="s">
         <v>54</v>
       </c>
-      <c r="C56" t="s">
-        <v>1472</v>
+      <c r="C56" s="11" t="s">
+        <v>1463</v>
       </c>
       <c r="E56" t="s">
         <v>550</v>
       </c>
-      <c r="F56" t="s">
-        <v>1425</v>
+      <c r="F56" s="11" t="s">
+        <v>1424</v>
       </c>
       <c r="I56" t="s">
         <v>888</v>
@@ -18368,9 +18544,11 @@
       <c r="B57" t="s">
         <v>55</v>
       </c>
+      <c r="C57" s="11"/>
       <c r="E57" t="s">
         <v>551</v>
       </c>
+      <c r="F57" s="11"/>
       <c r="H57" t="s">
         <v>1341</v>
       </c>
@@ -18394,11 +18572,12 @@
       <c r="B58" t="s">
         <v>56</v>
       </c>
+      <c r="C58" s="11"/>
       <c r="E58" t="s">
         <v>552</v>
       </c>
-      <c r="F58" t="s">
-        <v>1467</v>
+      <c r="F58" s="11" t="s">
+        <v>1557</v>
       </c>
       <c r="I58" t="s">
         <v>888</v>
@@ -18426,9 +18605,11 @@
       <c r="B59" t="s">
         <v>57</v>
       </c>
+      <c r="C59" s="11"/>
       <c r="E59" t="s">
         <v>553</v>
       </c>
+      <c r="F59" s="11"/>
       <c r="H59" t="s">
         <v>892</v>
       </c>
@@ -18439,7 +18620,7 @@
         <v>871</v>
       </c>
       <c r="L59" t="s">
-        <v>1519</v>
+        <v>1505</v>
       </c>
       <c r="N59" t="s">
         <v>1245</v>
@@ -18455,11 +18636,12 @@
       <c r="B60" t="s">
         <v>58</v>
       </c>
+      <c r="C60" s="11"/>
       <c r="E60" t="s">
         <v>554</v>
       </c>
-      <c r="F60" t="s">
-        <v>1474</v>
+      <c r="F60" s="11" t="s">
+        <v>1465</v>
       </c>
       <c r="H60" t="s">
         <v>894</v>
@@ -18490,13 +18672,13 @@
       <c r="B61" t="s">
         <v>59</v>
       </c>
-      <c r="C61" t="s">
-        <v>1473</v>
+      <c r="C61" s="11" t="s">
+        <v>1464</v>
       </c>
       <c r="E61" t="s">
         <v>555</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="11" t="s">
         <v>899</v>
       </c>
       <c r="H61" t="s">
@@ -18525,13 +18707,13 @@
       <c r="B62" t="s">
         <v>60</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="11" t="s">
         <v>900</v>
       </c>
       <c r="E62" t="s">
         <v>556</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="11" t="s">
         <v>901</v>
       </c>
       <c r="H62" t="s">
@@ -18554,9 +18736,11 @@
       <c r="B63" t="s">
         <v>61</v>
       </c>
+      <c r="C63" s="11"/>
       <c r="E63" t="s">
         <v>573</v>
       </c>
+      <c r="F63" s="11"/>
       <c r="H63" t="s">
         <v>905</v>
       </c>
@@ -18583,12 +18767,13 @@
       <c r="B64" t="s">
         <v>62</v>
       </c>
-      <c r="C64" t="s">
-        <v>1569</v>
+      <c r="C64" s="11" t="s">
+        <v>1549</v>
       </c>
       <c r="E64" t="s">
         <v>558</v>
       </c>
+      <c r="F64" s="11"/>
       <c r="H64" t="s">
         <v>909</v>
       </c>
@@ -18612,14 +18797,14 @@
       <c r="B65" t="s">
         <v>741</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="11" t="s">
         <v>1386</v>
       </c>
       <c r="E65" t="s">
         <v>709</v>
       </c>
-      <c r="F65" t="s">
-        <v>1564</v>
+      <c r="F65" s="11" t="s">
+        <v>1544</v>
       </c>
       <c r="H65" t="s">
         <v>1057</v>
@@ -18647,9 +18832,11 @@
       <c r="B66" t="s">
         <v>63</v>
       </c>
+      <c r="C66" s="11"/>
       <c r="E66" t="s">
         <v>559</v>
       </c>
+      <c r="F66" s="11"/>
       <c r="H66" t="s">
         <v>915</v>
       </c>
@@ -18679,12 +18866,13 @@
       <c r="B67" t="s">
         <v>64</v>
       </c>
-      <c r="C67" t="s">
-        <v>1542</v>
+      <c r="C67" s="11" t="s">
+        <v>1527</v>
       </c>
       <c r="E67" t="s">
         <v>560</v>
       </c>
+      <c r="F67" s="11"/>
       <c r="I67" t="s">
         <v>844</v>
       </c>
@@ -18705,9 +18893,11 @@
       <c r="B68" t="s">
         <v>65</v>
       </c>
+      <c r="C68" s="11"/>
       <c r="E68" t="s">
         <v>561</v>
       </c>
+      <c r="F68" s="11"/>
       <c r="I68" t="s">
         <v>1360</v>
       </c>
@@ -18734,9 +18924,11 @@
       <c r="B69" t="s">
         <v>66</v>
       </c>
+      <c r="C69" s="11"/>
       <c r="E69" t="s">
         <v>562</v>
       </c>
+      <c r="F69" s="11"/>
       <c r="H69" t="s">
         <v>917</v>
       </c>
@@ -18760,9 +18952,11 @@
       <c r="B70" t="s">
         <v>67</v>
       </c>
+      <c r="C70" s="11"/>
       <c r="E70" t="s">
         <v>563</v>
       </c>
+      <c r="F70" s="11"/>
       <c r="H70" t="s">
         <v>1052</v>
       </c>
@@ -18786,14 +18980,15 @@
       <c r="B71" t="s">
         <v>68</v>
       </c>
+      <c r="C71" s="11"/>
       <c r="E71" t="s">
         <v>564</v>
       </c>
-      <c r="F71" t="s">
-        <v>1495</v>
+      <c r="F71" s="11" t="s">
+        <v>1483</v>
       </c>
       <c r="G71" t="s">
-        <v>1512</v>
+        <v>1499</v>
       </c>
       <c r="H71" t="s">
         <v>968</v>
@@ -18818,9 +19013,11 @@
       <c r="B72" t="s">
         <v>69</v>
       </c>
+      <c r="C72" s="11"/>
       <c r="E72" t="s">
         <v>565</v>
       </c>
+      <c r="F72" s="11"/>
       <c r="H72" t="s">
         <v>926</v>
       </c>
@@ -18850,11 +19047,12 @@
       <c r="B73" t="s">
         <v>70</v>
       </c>
+      <c r="C73" s="11"/>
       <c r="E73" t="s">
         <v>566</v>
       </c>
-      <c r="F73" t="s">
-        <v>1478</v>
+      <c r="F73" s="11" t="s">
+        <v>1469</v>
       </c>
       <c r="H73" t="s">
         <v>925</v>
@@ -18879,9 +19077,11 @@
       <c r="B74" t="s">
         <v>71</v>
       </c>
+      <c r="C74" s="11"/>
       <c r="E74" t="s">
         <v>567</v>
       </c>
+      <c r="F74" s="11"/>
       <c r="H74" t="s">
         <v>931</v>
       </c>
@@ -18905,13 +19105,13 @@
       <c r="B75" t="s">
         <v>72</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="11" t="s">
         <v>932</v>
       </c>
       <c r="E75" t="s">
         <v>568</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="11" t="s">
         <v>933</v>
       </c>
       <c r="I75" t="s">
@@ -18937,9 +19137,11 @@
       <c r="B76" t="s">
         <v>73</v>
       </c>
+      <c r="C76" s="11"/>
       <c r="E76" t="s">
         <v>569</v>
       </c>
+      <c r="F76" s="11"/>
       <c r="H76" t="s">
         <v>934</v>
       </c>
@@ -18963,12 +19165,13 @@
       <c r="B77" t="s">
         <v>74</v>
       </c>
-      <c r="C77" t="s">
-        <v>1487</v>
+      <c r="C77" s="11" t="s">
+        <v>1475</v>
       </c>
       <c r="E77" t="s">
         <v>570</v>
       </c>
+      <c r="F77" s="11"/>
       <c r="H77" t="s">
         <v>969</v>
       </c>
@@ -18998,12 +19201,13 @@
       <c r="B78" t="s">
         <v>75</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="11" t="s">
         <v>1332</v>
       </c>
       <c r="E78" t="s">
         <v>571</v>
       </c>
+      <c r="F78" s="11"/>
       <c r="I78" t="s">
         <v>888</v>
       </c>
@@ -19024,9 +19228,11 @@
       <c r="B79" t="s">
         <v>76</v>
       </c>
+      <c r="C79" s="11"/>
       <c r="E79" t="s">
         <v>572</v>
       </c>
+      <c r="F79" s="11"/>
       <c r="I79" t="s">
         <v>1405</v>
       </c>
@@ -19053,9 +19259,11 @@
       <c r="B80" t="s">
         <v>77</v>
       </c>
+      <c r="C80" s="11"/>
       <c r="E80" t="s">
         <v>77</v>
       </c>
+      <c r="F80" s="11"/>
       <c r="H80" t="s">
         <v>938</v>
       </c>
@@ -19088,14 +19296,14 @@
       <c r="B81" t="s">
         <v>78</v>
       </c>
-      <c r="C81" t="s">
-        <v>1460</v>
+      <c r="C81" s="11" t="s">
+        <v>1453</v>
       </c>
       <c r="E81" t="s">
         <v>78</v>
       </c>
-      <c r="F81" t="s">
-        <v>1460</v>
+      <c r="F81" s="11" t="s">
+        <v>1453</v>
       </c>
       <c r="H81" t="s">
         <v>944</v>
@@ -19126,9 +19334,11 @@
       <c r="B82" t="s">
         <v>79</v>
       </c>
+      <c r="C82" s="11"/>
       <c r="E82" t="s">
         <v>557</v>
       </c>
+      <c r="F82" s="11"/>
       <c r="H82" t="s">
         <v>961</v>
       </c>
@@ -19158,9 +19368,11 @@
       <c r="B83" t="s">
         <v>80</v>
       </c>
+      <c r="C83" s="11"/>
       <c r="E83" t="s">
         <v>574</v>
       </c>
+      <c r="F83" s="11"/>
       <c r="H83" t="s">
         <v>945</v>
       </c>
@@ -19184,11 +19396,12 @@
       <c r="B84" t="s">
         <v>81</v>
       </c>
+      <c r="C84" s="11"/>
       <c r="E84" t="s">
         <v>575</v>
       </c>
-      <c r="F84" t="s">
-        <v>1490</v>
+      <c r="F84" s="11" t="s">
+        <v>1478</v>
       </c>
       <c r="I84" t="s">
         <v>1117</v>
@@ -19216,10 +19429,11 @@
       <c r="B85" t="s">
         <v>82</v>
       </c>
+      <c r="C85" s="11"/>
       <c r="E85" t="s">
         <v>576</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="11" t="s">
         <v>1417</v>
       </c>
       <c r="H85" t="s">
@@ -19248,8 +19462,12 @@
       <c r="B86" t="s">
         <v>83</v>
       </c>
+      <c r="C86" s="11"/>
       <c r="E86" t="s">
         <v>577</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>1567</v>
       </c>
       <c r="I86" t="s">
         <v>1117</v>
@@ -19274,17 +19492,17 @@
       <c r="B87" t="s">
         <v>84</v>
       </c>
-      <c r="C87" t="s">
-        <v>1570</v>
+      <c r="C87" s="11" t="s">
+        <v>1550</v>
       </c>
       <c r="E87" t="s">
         <v>578</v>
       </c>
-      <c r="F87" t="s">
-        <v>1561</v>
+      <c r="F87" s="11" t="s">
+        <v>1595</v>
       </c>
       <c r="G87" t="s">
-        <v>1521</v>
+        <v>1590</v>
       </c>
       <c r="I87" t="s">
         <v>844</v>
@@ -19309,10 +19527,11 @@
       <c r="B88" t="s">
         <v>85</v>
       </c>
+      <c r="C88" s="11"/>
       <c r="E88" t="s">
         <v>579</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="11" t="s">
         <v>85</v>
       </c>
       <c r="H88" t="s">
@@ -19341,11 +19560,12 @@
       <c r="B89" t="s">
         <v>86</v>
       </c>
+      <c r="C89" s="11"/>
       <c r="E89" t="s">
         <v>580</v>
       </c>
-      <c r="F89" t="s">
-        <v>1541</v>
+      <c r="F89" s="11" t="s">
+        <v>1526</v>
       </c>
       <c r="I89" t="s">
         <v>1397</v>
@@ -19370,11 +19590,12 @@
       <c r="B90" t="s">
         <v>87</v>
       </c>
+      <c r="C90" s="11"/>
       <c r="E90" t="s">
         <v>581</v>
       </c>
-      <c r="F90" t="s">
-        <v>1431</v>
+      <c r="F90" s="11" t="s">
+        <v>1430</v>
       </c>
       <c r="H90" t="s">
         <v>1012</v>
@@ -19399,14 +19620,15 @@
       <c r="B91" t="s">
         <v>88</v>
       </c>
+      <c r="C91" s="11"/>
       <c r="E91" t="s">
         <v>948</v>
       </c>
-      <c r="F91" t="s">
-        <v>1440</v>
+      <c r="F91" s="11" t="s">
+        <v>1438</v>
       </c>
       <c r="G91" t="s">
-        <v>1522</v>
+        <v>1507</v>
       </c>
       <c r="H91" t="s">
         <v>949</v>
@@ -19434,12 +19656,13 @@
       <c r="B92" t="s">
         <v>89</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="11" t="s">
         <v>954</v>
       </c>
       <c r="E92" t="s">
         <v>582</v>
       </c>
+      <c r="F92" s="11"/>
       <c r="H92" t="s">
         <v>951</v>
       </c>
@@ -19469,9 +19692,11 @@
       <c r="B93" t="s">
         <v>90</v>
       </c>
+      <c r="C93" s="11"/>
       <c r="E93" t="s">
         <v>583</v>
       </c>
+      <c r="F93" s="11"/>
       <c r="H93" t="s">
         <v>952</v>
       </c>
@@ -19495,14 +19720,15 @@
       <c r="B94" t="s">
         <v>91</v>
       </c>
+      <c r="C94" s="11"/>
       <c r="E94" t="s">
         <v>584</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="11" t="s">
         <v>953</v>
       </c>
       <c r="G94" t="s">
-        <v>1523</v>
+        <v>1508</v>
       </c>
       <c r="H94" t="s">
         <v>955</v>
@@ -19536,11 +19762,12 @@
       <c r="B95" t="s">
         <v>92</v>
       </c>
+      <c r="C95" s="11"/>
       <c r="E95" t="s">
         <v>626</v>
       </c>
-      <c r="F95" t="s">
-        <v>1457</v>
+      <c r="F95" s="11" t="s">
+        <v>1450</v>
       </c>
       <c r="H95" t="s">
         <v>972</v>
@@ -19568,9 +19795,11 @@
       <c r="B96" t="s">
         <v>93</v>
       </c>
+      <c r="C96" s="11"/>
       <c r="E96" t="s">
         <v>585</v>
       </c>
+      <c r="F96" s="11"/>
       <c r="H96" t="s">
         <v>976</v>
       </c>
@@ -19600,9 +19829,11 @@
       <c r="B97" t="s">
         <v>94</v>
       </c>
+      <c r="C97" s="11"/>
       <c r="E97" t="s">
         <v>586</v>
       </c>
+      <c r="F97" s="11"/>
       <c r="H97" t="s">
         <v>975</v>
       </c>
@@ -19635,10 +19866,11 @@
       <c r="B98" t="s">
         <v>95</v>
       </c>
+      <c r="C98" s="11"/>
       <c r="E98" t="s">
         <v>587</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="11" t="s">
         <v>1053</v>
       </c>
       <c r="H98" t="s">
@@ -19670,10 +19902,11 @@
       <c r="B99" t="s">
         <v>96</v>
       </c>
+      <c r="C99" s="11"/>
       <c r="E99" t="s">
         <v>588</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="11" t="s">
         <v>1365</v>
       </c>
       <c r="H99" t="s">
@@ -19699,9 +19932,11 @@
       <c r="B100" t="s">
         <v>97</v>
       </c>
+      <c r="C100" s="11"/>
       <c r="E100" t="s">
         <v>589</v>
       </c>
+      <c r="F100" s="11"/>
       <c r="H100" t="s">
         <v>977</v>
       </c>
@@ -19728,9 +19963,11 @@
       <c r="B101" t="s">
         <v>98</v>
       </c>
+      <c r="C101" s="11"/>
       <c r="E101" t="s">
         <v>590</v>
       </c>
+      <c r="F101" s="11"/>
       <c r="H101" t="s">
         <v>978</v>
       </c>
@@ -19760,9 +19997,11 @@
       <c r="B102" t="s">
         <v>99</v>
       </c>
+      <c r="C102" s="11"/>
       <c r="E102" t="s">
         <v>591</v>
       </c>
+      <c r="F102" s="11"/>
       <c r="H102" t="s">
         <v>980</v>
       </c>
@@ -19792,9 +20031,11 @@
       <c r="B103" t="s">
         <v>100</v>
       </c>
+      <c r="C103" s="11"/>
       <c r="E103" t="s">
         <v>592</v>
       </c>
+      <c r="F103" s="11"/>
       <c r="H103" t="s">
         <v>981</v>
       </c>
@@ -19818,12 +20059,13 @@
       <c r="B104" t="s">
         <v>489</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="11" t="s">
         <v>920</v>
       </c>
       <c r="E104" t="s">
         <v>593</v>
       </c>
+      <c r="F104" s="11"/>
       <c r="H104" t="s">
         <v>982</v>
       </c>
@@ -19850,10 +20092,11 @@
       <c r="B105" t="s">
         <v>101</v>
       </c>
+      <c r="C105" s="11"/>
       <c r="E105" t="s">
         <v>594</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="11" t="s">
         <v>983</v>
       </c>
       <c r="I105" t="s">
@@ -19876,14 +20119,15 @@
       <c r="B106" t="s">
         <v>102</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="11" t="s">
         <v>990</v>
       </c>
       <c r="E106" t="s">
         <v>595</v>
       </c>
+      <c r="F106" s="11"/>
       <c r="G106" t="s">
-        <v>1524</v>
+        <v>1509</v>
       </c>
       <c r="I106" t="s">
         <v>1397</v>
@@ -19914,17 +20158,17 @@
       <c r="B107" t="s">
         <v>103</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="11" t="s">
         <v>984</v>
       </c>
       <c r="E107" t="s">
         <v>596</v>
       </c>
-      <c r="F107" t="s">
-        <v>1426</v>
+      <c r="F107" s="11" t="s">
+        <v>1425</v>
       </c>
       <c r="G107" t="s">
-        <v>1525</v>
+        <v>1510</v>
       </c>
       <c r="I107" t="s">
         <v>844</v>
@@ -19955,12 +20199,13 @@
       <c r="B108" t="s">
         <v>104</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="11" t="s">
         <v>985</v>
       </c>
       <c r="E108" t="s">
         <v>571</v>
       </c>
+      <c r="F108" s="11"/>
       <c r="I108" t="s">
         <v>844</v>
       </c>
@@ -19990,17 +20235,17 @@
       <c r="B109" t="s">
         <v>432</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="11" t="s">
         <v>789</v>
       </c>
       <c r="D109" t="s">
-        <v>1527</v>
+        <v>1512</v>
       </c>
       <c r="E109" t="s">
         <v>598</v>
       </c>
-      <c r="F109" t="s">
-        <v>1446</v>
+      <c r="F109" s="11" t="s">
+        <v>1442</v>
       </c>
       <c r="I109" t="s">
         <v>1397</v>
@@ -20025,12 +20270,16 @@
       <c r="B110" t="s">
         <v>105</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="11" t="s">
         <v>986</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1558</v>
       </c>
       <c r="E110" t="s">
         <v>599</v>
       </c>
+      <c r="F110" s="11"/>
       <c r="I110" t="s">
         <v>888</v>
       </c>
@@ -20054,14 +20303,14 @@
       <c r="B111" t="s">
         <v>823</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="11" t="s">
         <v>822</v>
       </c>
       <c r="E111" t="s">
         <v>600</v>
       </c>
-      <c r="F111" t="s">
-        <v>1432</v>
+      <c r="F111" s="11" t="s">
+        <v>1431</v>
       </c>
       <c r="I111" t="s">
         <v>844</v>
@@ -20092,14 +20341,15 @@
       <c r="B112" t="s">
         <v>106</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="11" t="s">
         <v>886</v>
       </c>
       <c r="E112" t="s">
         <v>601</v>
       </c>
+      <c r="F112" s="11"/>
       <c r="G112" t="s">
-        <v>1526</v>
+        <v>1511</v>
       </c>
       <c r="I112" t="s">
         <v>844</v>
@@ -20130,14 +20380,15 @@
       <c r="B113" t="s">
         <v>107</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="11" t="s">
         <v>914</v>
       </c>
       <c r="E113" t="s">
         <v>602</v>
       </c>
+      <c r="F113" s="11"/>
       <c r="G113" t="s">
-        <v>1528</v>
+        <v>1513</v>
       </c>
       <c r="I113" t="s">
         <v>850</v>
@@ -20162,17 +20413,17 @@
       <c r="B114" t="s">
         <v>603</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="11" t="s">
         <v>921</v>
       </c>
       <c r="E114" t="s">
         <v>604</v>
       </c>
-      <c r="F114" t="s">
-        <v>1494</v>
+      <c r="F114" s="11" t="s">
+        <v>1482</v>
       </c>
       <c r="G114" t="s">
-        <v>1529</v>
+        <v>1514</v>
       </c>
       <c r="I114" t="s">
         <v>1397</v>
@@ -20197,13 +20448,13 @@
       <c r="B115" t="s">
         <v>108</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="11" t="s">
         <v>1393</v>
       </c>
       <c r="E115" t="s">
         <v>605</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="11" t="s">
         <v>1394</v>
       </c>
       <c r="I115" t="s">
@@ -20232,14 +20483,17 @@
       <c r="B116" t="s">
         <v>109</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="11" t="s">
         <v>987</v>
       </c>
       <c r="E116" t="s">
         <v>606</v>
       </c>
-      <c r="F116" t="s">
-        <v>1559</v>
+      <c r="F116" s="11" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1555</v>
       </c>
       <c r="I116" t="s">
         <v>844</v>
@@ -20264,13 +20518,13 @@
       <c r="B117" t="s">
         <v>110</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="11" t="s">
         <v>988</v>
       </c>
       <c r="E117" t="s">
         <v>597</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="11" t="s">
         <v>1418</v>
       </c>
       <c r="I117" t="s">
@@ -20296,14 +20550,14 @@
       <c r="B118" t="s">
         <v>111</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="11" t="s">
         <v>989</v>
       </c>
       <c r="E118" t="s">
         <v>607</v>
       </c>
-      <c r="F118" t="s">
-        <v>1427</v>
+      <c r="F118" s="11" t="s">
+        <v>1426</v>
       </c>
       <c r="I118" t="s">
         <v>844</v>
@@ -20331,11 +20585,14 @@
       <c r="B119" t="s">
         <v>112</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="11" t="s">
         <v>991</v>
       </c>
       <c r="E119" t="s">
         <v>608</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>1569</v>
       </c>
       <c r="I119" t="s">
         <v>888</v>
@@ -20363,12 +20620,13 @@
       <c r="B120" t="s">
         <v>113</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="11" t="s">
         <v>992</v>
       </c>
       <c r="E120" t="s">
         <v>609</v>
       </c>
+      <c r="F120" s="11"/>
       <c r="I120" t="s">
         <v>888</v>
       </c>
@@ -20392,9 +20650,11 @@
       <c r="B121" t="s">
         <v>114</v>
       </c>
+      <c r="C121" s="11"/>
       <c r="E121" t="s">
         <v>610</v>
       </c>
+      <c r="F121" s="11"/>
       <c r="H121" t="s">
         <v>994</v>
       </c>
@@ -20424,9 +20684,11 @@
       <c r="B122" t="s">
         <v>115</v>
       </c>
+      <c r="C122" s="11"/>
       <c r="E122" t="s">
         <v>611</v>
       </c>
+      <c r="F122" s="11"/>
       <c r="H122" t="s">
         <v>995</v>
       </c>
@@ -20450,9 +20712,11 @@
       <c r="B123" t="s">
         <v>116</v>
       </c>
+      <c r="C123" s="11"/>
       <c r="E123" t="s">
         <v>612</v>
       </c>
+      <c r="F123" s="11"/>
       <c r="H123" t="s">
         <v>998</v>
       </c>
@@ -20479,9 +20743,11 @@
       <c r="B124" t="s">
         <v>117</v>
       </c>
+      <c r="C124" s="11"/>
       <c r="E124" t="s">
         <v>613</v>
       </c>
+      <c r="F124" s="11"/>
       <c r="H124" t="s">
         <v>1340</v>
       </c>
@@ -20508,11 +20774,12 @@
       <c r="B125" t="s">
         <v>118</v>
       </c>
+      <c r="C125" s="11"/>
       <c r="E125" t="s">
         <v>614</v>
       </c>
-      <c r="F125" t="s">
-        <v>1500</v>
+      <c r="F125" s="11" t="s">
+        <v>1577</v>
       </c>
       <c r="G125" t="s">
         <v>1010</v>
@@ -20546,14 +20813,15 @@
       <c r="B126" t="s">
         <v>119</v>
       </c>
+      <c r="C126" s="11"/>
       <c r="E126" t="s">
         <v>615</v>
       </c>
-      <c r="F126" t="s">
-        <v>1009</v>
+      <c r="F126" s="11" t="s">
+        <v>1559</v>
       </c>
       <c r="G126" t="s">
-        <v>1530</v>
+        <v>1515</v>
       </c>
       <c r="I126" t="s">
         <v>844</v>
@@ -20578,9 +20846,11 @@
       <c r="B127" t="s">
         <v>120</v>
       </c>
+      <c r="C127" s="11"/>
       <c r="E127" t="s">
         <v>616</v>
       </c>
+      <c r="F127" s="11"/>
       <c r="H127" t="s">
         <v>1006</v>
       </c>
@@ -20613,20 +20883,20 @@
       <c r="B128" t="s">
         <v>121</v>
       </c>
-      <c r="C128" t="s">
-        <v>1437</v>
+      <c r="C128" s="11" t="s">
+        <v>1436</v>
       </c>
       <c r="D128" t="s">
-        <v>1531</v>
+        <v>1516</v>
       </c>
       <c r="E128" t="s">
         <v>617</v>
       </c>
-      <c r="F128" t="s">
-        <v>1438</v>
+      <c r="F128" s="11" t="s">
+        <v>1437</v>
       </c>
       <c r="G128" t="s">
-        <v>1532</v>
+        <v>1517</v>
       </c>
       <c r="H128" t="s">
         <v>1008</v>
@@ -20651,8 +20921,12 @@
       <c r="B129" t="s">
         <v>122</v>
       </c>
+      <c r="C129" s="11"/>
       <c r="E129" t="s">
         <v>618</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>1578</v>
       </c>
       <c r="H129" t="s">
         <v>1013</v>
@@ -20683,11 +20957,12 @@
       <c r="B130" t="s">
         <v>123</v>
       </c>
+      <c r="C130" s="11"/>
       <c r="E130" t="s">
         <v>619</v>
       </c>
-      <c r="F130" t="s">
-        <v>1464</v>
+      <c r="F130" s="11" t="s">
+        <v>1456</v>
       </c>
       <c r="H130" t="s">
         <v>1058</v>
@@ -20715,9 +20990,11 @@
       <c r="B131" t="s">
         <v>124</v>
       </c>
+      <c r="C131" s="11"/>
       <c r="E131" t="s">
         <v>620</v>
       </c>
+      <c r="F131" s="11"/>
       <c r="H131" t="s">
         <v>1015</v>
       </c>
@@ -20741,9 +21018,11 @@
       <c r="B132" t="s">
         <v>125</v>
       </c>
+      <c r="C132" s="11"/>
       <c r="E132" t="s">
         <v>621</v>
       </c>
+      <c r="F132" s="11"/>
       <c r="H132" t="s">
         <v>1016</v>
       </c>
@@ -20773,11 +21052,12 @@
       <c r="B133" t="s">
         <v>126</v>
       </c>
+      <c r="C133" s="11"/>
       <c r="E133" t="s">
         <v>622</v>
       </c>
-      <c r="F133" t="s">
-        <v>1433</v>
+      <c r="F133" s="11" t="s">
+        <v>1432</v>
       </c>
       <c r="H133" t="s">
         <v>1018</v>
@@ -20808,9 +21088,11 @@
       <c r="B134" t="s">
         <v>127</v>
       </c>
+      <c r="C134" s="11"/>
       <c r="E134" t="s">
         <v>623</v>
       </c>
+      <c r="F134" s="11"/>
       <c r="H134" t="s">
         <v>1019</v>
       </c>
@@ -20840,11 +21122,14 @@
       <c r="B135" t="s">
         <v>128</v>
       </c>
+      <c r="C135" s="11" t="s">
+        <v>1585</v>
+      </c>
       <c r="E135" t="s">
         <v>624</v>
       </c>
-      <c r="F135" t="s">
-        <v>1498</v>
+      <c r="F135" s="11" t="s">
+        <v>1486</v>
       </c>
       <c r="H135" t="s">
         <v>1021</v>
@@ -20875,9 +21160,11 @@
       <c r="B136" t="s">
         <v>129</v>
       </c>
+      <c r="C136" s="11"/>
       <c r="E136" t="s">
         <v>625</v>
       </c>
+      <c r="F136" s="11"/>
       <c r="H136" t="s">
         <v>1049</v>
       </c>
@@ -20901,9 +21188,11 @@
       <c r="B137" t="s">
         <v>130</v>
       </c>
+      <c r="C137" s="11"/>
       <c r="E137" t="s">
         <v>130</v>
       </c>
+      <c r="F137" s="11"/>
       <c r="H137" t="s">
         <v>1024</v>
       </c>
@@ -20927,9 +21216,11 @@
       <c r="B138" t="s">
         <v>131</v>
       </c>
+      <c r="C138" s="11"/>
       <c r="E138" t="s">
         <v>131</v>
       </c>
+      <c r="F138" s="11"/>
       <c r="H138" t="s">
         <v>975</v>
       </c>
@@ -20962,13 +21253,13 @@
       <c r="B139" t="s">
         <v>132</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="11" t="s">
         <v>1029</v>
       </c>
       <c r="E139" t="s">
         <v>627</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F139" s="11" t="s">
         <v>1028</v>
       </c>
       <c r="H139" t="s">
@@ -20994,8 +21285,12 @@
       <c r="B140" t="s">
         <v>133</v>
       </c>
+      <c r="C140" s="11"/>
       <c r="E140" t="s">
         <v>628</v>
+      </c>
+      <c r="F140" s="11" t="s">
+        <v>1591</v>
       </c>
       <c r="I140" t="s">
         <v>1402</v>
@@ -21014,11 +21309,16 @@
       <c r="B141" t="s">
         <v>134</v>
       </c>
+      <c r="C141" s="11"/>
       <c r="D141" t="s">
-        <v>1533</v>
+        <v>1518</v>
       </c>
       <c r="E141" t="s">
         <v>629</v>
+      </c>
+      <c r="F141" s="11"/>
+      <c r="G141" t="s">
+        <v>1554</v>
       </c>
       <c r="H141" t="s">
         <v>1027</v>
@@ -21049,12 +21349,13 @@
       <c r="B142" t="s">
         <v>335</v>
       </c>
-      <c r="C142" t="s">
-        <v>1488</v>
+      <c r="C142" s="11" t="s">
+        <v>1476</v>
       </c>
       <c r="E142" t="s">
         <v>630</v>
       </c>
+      <c r="F142" s="11"/>
       <c r="H142" t="s">
         <v>1047</v>
       </c>
@@ -21084,11 +21385,12 @@
       <c r="B143" t="s">
         <v>135</v>
       </c>
+      <c r="C143" s="11"/>
       <c r="E143" t="s">
         <v>631</v>
       </c>
-      <c r="F143" t="s">
-        <v>1470</v>
+      <c r="F143" s="11" t="s">
+        <v>1461</v>
       </c>
       <c r="I143" t="s">
         <v>1349</v>
@@ -21116,12 +21418,13 @@
       <c r="B144" t="s">
         <v>136</v>
       </c>
-      <c r="C144" t="s">
-        <v>1571</v>
+      <c r="C144" s="11" t="s">
+        <v>1551</v>
       </c>
       <c r="E144" t="s">
         <v>632</v>
       </c>
+      <c r="F144" s="11"/>
       <c r="H144" t="s">
         <v>1034</v>
       </c>
@@ -21145,10 +21448,11 @@
       <c r="B145" t="s">
         <v>137</v>
       </c>
+      <c r="C145" s="11"/>
       <c r="E145" t="s">
         <v>633</v>
       </c>
-      <c r="F145" t="s">
+      <c r="F145" s="11" t="s">
         <v>1044</v>
       </c>
       <c r="I145" t="s">
@@ -21174,9 +21478,11 @@
       <c r="B146" t="s">
         <v>138</v>
       </c>
+      <c r="C146" s="11"/>
       <c r="E146" t="s">
         <v>634</v>
       </c>
+      <c r="F146" s="11"/>
       <c r="H146" t="s">
         <v>1050</v>
       </c>
@@ -21206,11 +21512,15 @@
       <c r="B147" t="s">
         <v>139</v>
       </c>
+      <c r="C147" s="11"/>
       <c r="E147" t="s">
         <v>635</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F147" s="11" t="s">
         <v>1045</v>
+      </c>
+      <c r="G147" t="s">
+        <v>1592</v>
       </c>
       <c r="I147" t="s">
         <v>1117</v>
@@ -21235,11 +21545,12 @@
       <c r="B148" t="s">
         <v>140</v>
       </c>
+      <c r="C148" s="11"/>
       <c r="E148" t="s">
         <v>636</v>
       </c>
-      <c r="F148" t="s">
-        <v>1483</v>
+      <c r="F148" s="11" t="s">
+        <v>1471</v>
       </c>
       <c r="H148" t="s">
         <v>1036</v>
@@ -21270,11 +21581,14 @@
       <c r="B149" t="s">
         <v>141</v>
       </c>
+      <c r="C149" s="11" t="s">
+        <v>1587</v>
+      </c>
       <c r="E149" t="s">
         <v>637</v>
       </c>
-      <c r="F149" t="s">
-        <v>1479</v>
+      <c r="F149" s="11" t="s">
+        <v>1470</v>
       </c>
       <c r="I149" t="s">
         <v>1402</v>
@@ -21296,17 +21610,17 @@
       <c r="B150" t="s">
         <v>142</v>
       </c>
-      <c r="C150" t="s">
-        <v>1493</v>
+      <c r="C150" s="11" t="s">
+        <v>1481</v>
       </c>
       <c r="E150" t="s">
         <v>638</v>
       </c>
-      <c r="F150" t="s">
-        <v>1463</v>
+      <c r="F150" s="11" t="s">
+        <v>1560</v>
       </c>
       <c r="G150" t="s">
-        <v>1534</v>
+        <v>1519</v>
       </c>
       <c r="I150" t="s">
         <v>1402</v>
@@ -21334,13 +21648,13 @@
       <c r="B151" t="s">
         <v>143</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="11" t="s">
         <v>1051</v>
       </c>
       <c r="E151" t="s">
         <v>639</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F151" s="11" t="s">
         <v>143</v>
       </c>
       <c r="H151" t="s">
@@ -21369,11 +21683,15 @@
       <c r="B152" t="s">
         <v>144</v>
       </c>
+      <c r="C152" s="11"/>
       <c r="E152" t="s">
         <v>641</v>
       </c>
+      <c r="F152" s="11" t="s">
+        <v>1575</v>
+      </c>
       <c r="G152" t="s">
-        <v>1535</v>
+        <v>1520</v>
       </c>
       <c r="H152" t="s">
         <v>1039</v>
@@ -21401,10 +21719,11 @@
       <c r="B153" t="s">
         <v>145</v>
       </c>
+      <c r="C153" s="11"/>
       <c r="E153" t="s">
         <v>643</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F153" s="11" t="s">
         <v>1043</v>
       </c>
       <c r="H153" t="s">
@@ -21436,9 +21755,11 @@
       <c r="B154" t="s">
         <v>146</v>
       </c>
+      <c r="C154" s="11"/>
       <c r="E154" t="s">
         <v>644</v>
       </c>
+      <c r="F154" s="11"/>
       <c r="H154" t="s">
         <v>1197</v>
       </c>
@@ -21465,11 +21786,12 @@
       <c r="B155" t="s">
         <v>147</v>
       </c>
+      <c r="C155" s="11"/>
       <c r="E155" t="s">
         <v>645</v>
       </c>
-      <c r="F155" t="s">
-        <v>1560</v>
+      <c r="F155" s="11" t="s">
+        <v>1541</v>
       </c>
       <c r="I155" t="s">
         <v>1117</v>
@@ -21494,9 +21816,11 @@
       <c r="B156" t="s">
         <v>148</v>
       </c>
+      <c r="C156" s="11"/>
       <c r="E156" t="s">
         <v>646</v>
       </c>
+      <c r="F156" s="11"/>
       <c r="H156" t="s">
         <v>1059</v>
       </c>
@@ -21523,17 +21847,17 @@
       <c r="B157" t="s">
         <v>795</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="11" t="s">
         <v>1295</v>
       </c>
       <c r="E157" t="s">
         <v>523</v>
       </c>
-      <c r="F157" t="s">
-        <v>1428</v>
+      <c r="F157" s="11" t="s">
+        <v>1427</v>
       </c>
       <c r="G157" t="s">
-        <v>1536</v>
+        <v>1521</v>
       </c>
       <c r="H157" t="s">
         <v>835</v>
@@ -21564,17 +21888,17 @@
       <c r="B158" t="s">
         <v>149</v>
       </c>
-      <c r="C158" t="s">
-        <v>1421</v>
+      <c r="C158" s="11" t="s">
+        <v>1420</v>
       </c>
       <c r="E158" t="s">
         <v>647</v>
       </c>
-      <c r="F158" t="s">
-        <v>1447</v>
+      <c r="F158" s="11" t="s">
+        <v>1443</v>
       </c>
       <c r="G158" t="s">
-        <v>1539</v>
+        <v>1524</v>
       </c>
       <c r="H158" t="s">
         <v>1065</v>
@@ -21602,14 +21926,14 @@
       <c r="B159" t="s">
         <v>150</v>
       </c>
-      <c r="C159" t="s">
-        <v>1572</v>
+      <c r="C159" s="11" t="s">
+        <v>1552</v>
       </c>
       <c r="E159" t="s">
         <v>648</v>
       </c>
-      <c r="F159" t="s">
-        <v>1502</v>
+      <c r="F159" s="11" t="s">
+        <v>1489</v>
       </c>
       <c r="I159" t="s">
         <v>844</v>
@@ -21637,11 +21961,12 @@
       <c r="B160" t="s">
         <v>151</v>
       </c>
+      <c r="C160" s="11"/>
       <c r="E160" t="s">
         <v>649</v>
       </c>
-      <c r="F160" t="s">
-        <v>1540</v>
+      <c r="F160" s="11" t="s">
+        <v>1525</v>
       </c>
       <c r="H160" t="s">
         <v>1061</v>
@@ -21672,11 +21997,12 @@
       <c r="B161" t="s">
         <v>152</v>
       </c>
+      <c r="C161" s="11"/>
       <c r="E161" t="s">
         <v>650</v>
       </c>
-      <c r="F161" t="s">
-        <v>1496</v>
+      <c r="F161" s="11" t="s">
+        <v>1484</v>
       </c>
       <c r="H161" t="s">
         <v>1062</v>
@@ -21704,14 +22030,15 @@
       <c r="B162" t="s">
         <v>153</v>
       </c>
+      <c r="C162" s="11"/>
       <c r="E162" t="s">
         <v>651</v>
       </c>
-      <c r="F162" t="s">
-        <v>1453</v>
+      <c r="F162" s="11" t="s">
+        <v>1572</v>
       </c>
       <c r="G162" t="s">
-        <v>1537</v>
+        <v>1522</v>
       </c>
       <c r="H162" t="s">
         <v>1064</v>
@@ -21742,14 +22069,15 @@
       <c r="B163" t="s">
         <v>154</v>
       </c>
+      <c r="C163" s="11"/>
       <c r="E163" t="s">
         <v>652</v>
       </c>
-      <c r="F163" t="s">
-        <v>1466</v>
+      <c r="F163" s="11" t="s">
+        <v>1458</v>
       </c>
       <c r="G163" t="s">
-        <v>1538</v>
+        <v>1523</v>
       </c>
       <c r="H163" t="s">
         <v>1070</v>
@@ -21774,11 +22102,15 @@
       <c r="B164" t="s">
         <v>155</v>
       </c>
+      <c r="C164" s="11"/>
       <c r="D164" t="s">
-        <v>1545</v>
+        <v>1583</v>
       </c>
       <c r="E164" t="s">
         <v>653</v>
+      </c>
+      <c r="F164" s="11" t="s">
+        <v>1582</v>
       </c>
       <c r="I164" t="s">
         <v>844</v>
@@ -21809,9 +22141,11 @@
       <c r="B165" t="s">
         <v>156</v>
       </c>
+      <c r="C165" s="11"/>
       <c r="E165" t="s">
         <v>654</v>
       </c>
+      <c r="F165" s="11"/>
       <c r="H165" t="s">
         <v>1072</v>
       </c>
@@ -21835,14 +22169,14 @@
       <c r="B166" t="s">
         <v>157</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="11" t="s">
         <v>1081</v>
       </c>
       <c r="E166" t="s">
         <v>655</v>
       </c>
-      <c r="F166" t="s">
-        <v>1501</v>
+      <c r="F166" s="11" t="s">
+        <v>1488</v>
       </c>
       <c r="I166" t="s">
         <v>844</v>
@@ -21873,9 +22207,11 @@
       <c r="B167" t="s">
         <v>158</v>
       </c>
+      <c r="C167" s="11"/>
       <c r="E167" t="s">
         <v>656</v>
       </c>
+      <c r="F167" s="11"/>
       <c r="I167" t="s">
         <v>844</v>
       </c>
@@ -21902,12 +22238,13 @@
       <c r="B168" t="s">
         <v>159</v>
       </c>
-      <c r="C168" t="s">
-        <v>1484</v>
+      <c r="C168" s="11" t="s">
+        <v>1472</v>
       </c>
       <c r="E168" t="s">
         <v>658</v>
       </c>
+      <c r="F168" s="11"/>
       <c r="H168" t="s">
         <v>1334</v>
       </c>
@@ -21931,12 +22268,13 @@
       <c r="B169" t="s">
         <v>1079</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="11" t="s">
         <v>1292</v>
       </c>
       <c r="E169" t="s">
         <v>657</v>
       </c>
+      <c r="F169" s="11"/>
       <c r="H169" t="s">
         <v>1082</v>
       </c>
@@ -21960,11 +22298,12 @@
       <c r="B170" t="s">
         <v>160</v>
       </c>
+      <c r="C170" s="11"/>
       <c r="E170" t="s">
         <v>659</v>
       </c>
-      <c r="F170" t="s">
-        <v>1562</v>
+      <c r="F170" s="11" t="s">
+        <v>1542</v>
       </c>
       <c r="H170" t="s">
         <v>1083</v>
@@ -21995,14 +22334,15 @@
       <c r="B171" t="s">
         <v>161</v>
       </c>
+      <c r="C171" s="11"/>
       <c r="E171" t="s">
         <v>660</v>
       </c>
-      <c r="F171" t="s">
-        <v>1563</v>
+      <c r="F171" s="11" t="s">
+        <v>1543</v>
       </c>
       <c r="G171" t="s">
-        <v>1547</v>
+        <v>1531</v>
       </c>
       <c r="I171" t="s">
         <v>844</v>
@@ -22030,11 +22370,12 @@
       <c r="B172" t="s">
         <v>162</v>
       </c>
+      <c r="C172" s="11"/>
       <c r="E172" t="s">
         <v>661</v>
       </c>
-      <c r="F172" t="s">
-        <v>1461</v>
+      <c r="F172" s="11" t="s">
+        <v>1454</v>
       </c>
       <c r="H172" t="s">
         <v>1342</v>
@@ -22062,10 +22403,11 @@
       <c r="B173" t="s">
         <v>163</v>
       </c>
+      <c r="C173" s="11"/>
       <c r="E173" t="s">
         <v>163</v>
       </c>
-      <c r="F173" t="s">
+      <c r="F173" s="11" t="s">
         <v>1119</v>
       </c>
       <c r="H173" t="s">
@@ -22097,11 +22439,14 @@
       <c r="B174" t="s">
         <v>164</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="11" t="s">
         <v>1089</v>
       </c>
       <c r="E174" t="s">
         <v>662</v>
+      </c>
+      <c r="F174" s="11" t="s">
+        <v>1570</v>
       </c>
       <c r="H174" t="s">
         <v>1088</v>
@@ -22132,10 +22477,11 @@
       <c r="B175" t="s">
         <v>165</v>
       </c>
+      <c r="C175" s="11"/>
       <c r="E175" t="s">
         <v>663</v>
       </c>
-      <c r="F175" t="s">
+      <c r="F175" s="11" t="s">
         <v>1419</v>
       </c>
       <c r="H175" t="s">
@@ -22164,9 +22510,11 @@
       <c r="B176" t="s">
         <v>166</v>
       </c>
+      <c r="C176" s="11"/>
       <c r="E176" t="s">
         <v>664</v>
       </c>
+      <c r="F176" s="11"/>
       <c r="H176" t="s">
         <v>1093</v>
       </c>
@@ -22190,11 +22538,14 @@
       <c r="B177" t="s">
         <v>167</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="11" t="s">
         <v>1389</v>
       </c>
       <c r="E177" t="s">
         <v>665</v>
+      </c>
+      <c r="F177" s="11" t="s">
+        <v>1580</v>
       </c>
       <c r="I177" t="s">
         <v>844</v>
@@ -22222,9 +22573,11 @@
       <c r="B178" t="s">
         <v>168</v>
       </c>
+      <c r="C178" s="11"/>
       <c r="E178" t="s">
         <v>666</v>
       </c>
+      <c r="F178" s="11"/>
       <c r="H178" t="s">
         <v>1337</v>
       </c>
@@ -22248,9 +22601,11 @@
       <c r="B179" t="s">
         <v>169</v>
       </c>
+      <c r="C179" s="11"/>
       <c r="E179" t="s">
         <v>667</v>
       </c>
+      <c r="F179" s="11"/>
       <c r="I179" t="s">
         <v>888</v>
       </c>
@@ -22280,9 +22635,11 @@
       <c r="B180" t="s">
         <v>170</v>
       </c>
+      <c r="C180" s="11"/>
       <c r="E180" t="s">
         <v>668</v>
       </c>
+      <c r="F180" s="11"/>
       <c r="H180" t="s">
         <v>938</v>
       </c>
@@ -22309,12 +22666,13 @@
       <c r="B181" t="s">
         <v>171</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="11" t="s">
         <v>1293</v>
       </c>
       <c r="E181" t="s">
         <v>669</v>
       </c>
+      <c r="F181" s="11"/>
       <c r="H181" t="s">
         <v>1095</v>
       </c>
@@ -22338,9 +22696,11 @@
       <c r="B182" t="s">
         <v>172</v>
       </c>
+      <c r="C182" s="11"/>
       <c r="E182" t="s">
         <v>670</v>
       </c>
+      <c r="F182" s="11"/>
       <c r="H182" t="s">
         <v>831</v>
       </c>
@@ -22361,12 +22721,13 @@
       <c r="B183" t="s">
         <v>173</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="11" t="s">
         <v>1294</v>
       </c>
       <c r="E183" t="s">
         <v>589</v>
       </c>
+      <c r="F183" s="11"/>
       <c r="H183" t="s">
         <v>982</v>
       </c>
@@ -22390,12 +22751,13 @@
       <c r="B184" t="s">
         <v>174</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="11" t="s">
         <v>1100</v>
       </c>
       <c r="E184" t="s">
         <v>672</v>
       </c>
+      <c r="F184" s="11"/>
       <c r="H184" t="s">
         <v>1101</v>
       </c>
@@ -22425,12 +22787,13 @@
       <c r="B185" t="s">
         <v>1103</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="11" t="s">
         <v>1104</v>
       </c>
       <c r="E185" t="s">
         <v>673</v>
       </c>
+      <c r="F185" s="11"/>
       <c r="H185" t="s">
         <v>1105</v>
       </c>
@@ -22460,13 +22823,13 @@
       <c r="B186" t="s">
         <v>1202</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C186" s="11" t="s">
         <v>1396</v>
       </c>
       <c r="E186" t="s">
         <v>688</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F186" s="11" t="s">
         <v>187</v>
       </c>
       <c r="H186" t="s">
@@ -22495,12 +22858,13 @@
       <c r="B187" t="s">
         <v>175</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="11" t="s">
         <v>1106</v>
       </c>
       <c r="E187" t="s">
         <v>674</v>
       </c>
+      <c r="F187" s="11"/>
       <c r="H187" t="s">
         <v>1107</v>
       </c>
@@ -22524,17 +22888,17 @@
       <c r="B188" t="s">
         <v>176</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="11" t="s">
         <v>1108</v>
       </c>
       <c r="E188" t="s">
         <v>675</v>
       </c>
-      <c r="F188" t="s">
+      <c r="F188" s="11" t="s">
         <v>1109</v>
       </c>
       <c r="G188" t="s">
-        <v>1546</v>
+        <v>1530</v>
       </c>
       <c r="I188" t="s">
         <v>1402</v>
@@ -22556,9 +22920,11 @@
       <c r="B189" t="s">
         <v>177</v>
       </c>
+      <c r="C189" s="11"/>
       <c r="E189" t="s">
         <v>676</v>
       </c>
+      <c r="F189" s="11"/>
       <c r="H189" t="s">
         <v>1111</v>
       </c>
@@ -22582,11 +22948,12 @@
       <c r="B190" t="s">
         <v>178</v>
       </c>
+      <c r="C190" s="11"/>
       <c r="E190" t="s">
         <v>677</v>
       </c>
-      <c r="F190" t="s">
-        <v>1482</v>
+      <c r="F190" s="11" t="s">
+        <v>1574</v>
       </c>
       <c r="H190" t="s">
         <v>1112</v>
@@ -22617,9 +22984,11 @@
       <c r="B191" t="s">
         <v>179</v>
       </c>
+      <c r="C191" s="11"/>
       <c r="E191" t="s">
         <v>678</v>
       </c>
+      <c r="F191" s="11"/>
       <c r="H191" t="s">
         <v>1114</v>
       </c>
@@ -22643,11 +23012,12 @@
       <c r="B192" t="s">
         <v>486</v>
       </c>
+      <c r="C192" s="11"/>
       <c r="E192" t="s">
         <v>679</v>
       </c>
-      <c r="F192" t="s">
-        <v>1455</v>
+      <c r="F192" s="11" t="s">
+        <v>1448</v>
       </c>
       <c r="I192" t="s">
         <v>1117</v>
@@ -22678,17 +23048,17 @@
       <c r="B193" t="s">
         <v>180</v>
       </c>
-      <c r="C193" t="s">
-        <v>1450</v>
+      <c r="C193" s="11" t="s">
+        <v>1445</v>
       </c>
       <c r="E193" t="s">
         <v>680</v>
       </c>
-      <c r="F193" t="s">
-        <v>1475</v>
+      <c r="F193" s="11" t="s">
+        <v>1466</v>
       </c>
       <c r="G193" t="s">
-        <v>1548</v>
+        <v>1532</v>
       </c>
       <c r="H193" t="s">
         <v>1118</v>
@@ -22722,11 +23092,14 @@
       <c r="B194" t="s">
         <v>181</v>
       </c>
-      <c r="C194" t="s">
-        <v>1126</v>
+      <c r="C194" s="11" t="s">
+        <v>1561</v>
       </c>
       <c r="E194" t="s">
         <v>681</v>
+      </c>
+      <c r="F194" s="11" t="s">
+        <v>1567</v>
       </c>
       <c r="I194" t="s">
         <v>1117</v>
@@ -22754,12 +23127,13 @@
       <c r="B195" t="s">
         <v>739</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C195" s="11" t="s">
         <v>1124</v>
       </c>
       <c r="E195" t="s">
         <v>689</v>
       </c>
+      <c r="F195" s="11"/>
       <c r="I195" t="s">
         <v>1117</v>
       </c>
@@ -22783,14 +23157,14 @@
       <c r="B196" t="s">
         <v>182</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="11" t="s">
         <v>1213</v>
       </c>
       <c r="E196" t="s">
         <v>682</v>
       </c>
-      <c r="F196" t="s">
-        <v>1448</v>
+      <c r="F196" s="11" t="s">
+        <v>1444</v>
       </c>
       <c r="I196" t="s">
         <v>1117</v>
@@ -22815,12 +23189,13 @@
       <c r="B197" t="s">
         <v>183</v>
       </c>
-      <c r="C197" t="s">
-        <v>1567</v>
+      <c r="C197" s="11" t="s">
+        <v>1547</v>
       </c>
       <c r="E197" t="s">
         <v>683</v>
       </c>
+      <c r="F197" s="11"/>
       <c r="I197" t="s">
         <v>1117</v>
       </c>
@@ -22847,20 +23222,20 @@
       <c r="B198" t="s">
         <v>482</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C198" s="11" t="s">
         <v>1128</v>
       </c>
       <c r="D198" t="s">
-        <v>1550</v>
+        <v>1534</v>
       </c>
       <c r="E198" t="s">
         <v>684</v>
       </c>
-      <c r="F198" t="s">
-        <v>1434</v>
+      <c r="F198" s="11" t="s">
+        <v>1433</v>
       </c>
       <c r="G198" t="s">
-        <v>1549</v>
+        <v>1533</v>
       </c>
       <c r="H198" t="s">
         <v>1138</v>
@@ -22891,13 +23266,13 @@
       <c r="B199" t="s">
         <v>184</v>
       </c>
-      <c r="C199" t="s">
-        <v>1489</v>
+      <c r="C199" s="11" t="s">
+        <v>1477</v>
       </c>
       <c r="E199" t="s">
         <v>685</v>
       </c>
-      <c r="F199" t="s">
+      <c r="F199" s="11" t="s">
         <v>1133</v>
       </c>
       <c r="I199" t="s">
@@ -22926,11 +23301,12 @@
       <c r="B200" t="s">
         <v>185</v>
       </c>
+      <c r="C200" s="11"/>
       <c r="E200" t="s">
         <v>686</v>
       </c>
-      <c r="F200" t="s">
-        <v>1429</v>
+      <c r="F200" s="11" t="s">
+        <v>1428</v>
       </c>
       <c r="I200" t="s">
         <v>844</v>
@@ -22958,9 +23334,11 @@
       <c r="B201" t="s">
         <v>186</v>
       </c>
+      <c r="C201" s="11"/>
       <c r="E201" t="s">
         <v>687</v>
       </c>
+      <c r="F201" s="11"/>
       <c r="I201" t="s">
         <v>844</v>
       </c>
@@ -22984,11 +23362,12 @@
       <c r="B202" t="s">
         <v>744</v>
       </c>
+      <c r="C202" s="11"/>
       <c r="E202" t="s">
         <v>738</v>
       </c>
-      <c r="F202" t="s">
-        <v>1459</v>
+      <c r="F202" s="11" t="s">
+        <v>1452</v>
       </c>
       <c r="I202" t="s">
         <v>1404</v>
@@ -23013,14 +23392,14 @@
       <c r="B203" t="s">
         <v>188</v>
       </c>
-      <c r="C203" t="s">
-        <v>1485</v>
+      <c r="C203" s="11" t="s">
+        <v>1562</v>
       </c>
       <c r="E203" t="s">
         <v>690</v>
       </c>
-      <c r="F203" t="s">
-        <v>1485</v>
+      <c r="F203" s="11" t="s">
+        <v>1473</v>
       </c>
       <c r="I203" t="s">
         <v>1350</v>
@@ -23048,9 +23427,11 @@
       <c r="B204" t="s">
         <v>189</v>
       </c>
+      <c r="C204" s="11"/>
       <c r="E204" t="s">
         <v>691</v>
       </c>
+      <c r="F204" s="11"/>
       <c r="H204" t="s">
         <v>926</v>
       </c>
@@ -23077,9 +23458,11 @@
       <c r="B205" t="s">
         <v>190</v>
       </c>
+      <c r="C205" s="11"/>
       <c r="E205" t="s">
         <v>692</v>
       </c>
+      <c r="F205" s="11"/>
       <c r="H205" t="s">
         <v>1300</v>
       </c>
@@ -23109,9 +23492,11 @@
       <c r="B206" t="s">
         <v>191</v>
       </c>
+      <c r="C206" s="11"/>
       <c r="E206" t="s">
         <v>693</v>
       </c>
+      <c r="F206" s="11"/>
       <c r="H206" t="s">
         <v>1134</v>
       </c>
@@ -23138,9 +23523,13 @@
       <c r="B207" t="s">
         <v>192</v>
       </c>
+      <c r="C207" s="11" t="s">
+        <v>1586</v>
+      </c>
       <c r="E207" t="s">
         <v>586</v>
       </c>
+      <c r="F207" s="11"/>
       <c r="I207" t="s">
         <v>1402</v>
       </c>
@@ -23158,9 +23547,11 @@
       <c r="B208" t="s">
         <v>193</v>
       </c>
+      <c r="C208" s="11"/>
       <c r="E208" t="s">
         <v>694</v>
       </c>
+      <c r="F208" s="11"/>
       <c r="H208" t="s">
         <v>1135</v>
       </c>
@@ -23184,9 +23575,11 @@
       <c r="B209" t="s">
         <v>194</v>
       </c>
+      <c r="C209" s="11"/>
       <c r="E209" t="s">
         <v>194</v>
       </c>
+      <c r="F209" s="11"/>
       <c r="H209" t="s">
         <v>1208</v>
       </c>
@@ -23213,14 +23606,14 @@
       <c r="B210" t="s">
         <v>485</v>
       </c>
-      <c r="C210" t="s">
-        <v>1491</v>
+      <c r="C210" s="11" t="s">
+        <v>1479</v>
       </c>
       <c r="E210" t="s">
         <v>513</v>
       </c>
-      <c r="F210" t="s">
-        <v>1465</v>
+      <c r="F210" s="11" t="s">
+        <v>1457</v>
       </c>
       <c r="I210" t="s">
         <v>888</v>
@@ -23251,14 +23644,14 @@
       <c r="B211" t="s">
         <v>195</v>
       </c>
-      <c r="C211" t="s">
-        <v>1544</v>
+      <c r="C211" s="11" t="s">
+        <v>1529</v>
       </c>
       <c r="E211" t="s">
         <v>695</v>
       </c>
-      <c r="F211" t="s">
-        <v>1435</v>
+      <c r="F211" s="11" t="s">
+        <v>1434</v>
       </c>
       <c r="H211" t="s">
         <v>1139</v>
@@ -23289,9 +23682,11 @@
       <c r="B212" t="s">
         <v>196</v>
       </c>
+      <c r="C212" s="11"/>
       <c r="E212" t="s">
         <v>696</v>
       </c>
+      <c r="F212" s="11"/>
       <c r="H212" t="s">
         <v>1140</v>
       </c>
@@ -23315,37 +23710,33 @@
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A213" s="11" t="s">
+      <c r="A213" t="s">
         <v>391</v>
       </c>
-      <c r="B213" s="11" t="s">
+      <c r="B213" t="s">
         <v>197</v>
       </c>
       <c r="C213" s="11"/>
-      <c r="D213" s="11"/>
-      <c r="E213" s="11" t="s">
+      <c r="E213" t="s">
         <v>697</v>
       </c>
       <c r="F213" s="11"/>
-      <c r="G213" s="11"/>
-      <c r="H213" s="11" t="s">
+      <c r="H213" t="s">
         <v>1142</v>
       </c>
-      <c r="I213" s="11" t="s">
+      <c r="I213" t="s">
         <v>846</v>
       </c>
-      <c r="J213" s="11" t="s">
+      <c r="J213" t="s">
         <v>1115</v>
       </c>
-      <c r="K213" s="11"/>
-      <c r="L213" s="11" t="s">
+      <c r="L213" t="s">
         <v>1221</v>
       </c>
-      <c r="M213" s="11"/>
       <c r="N213" t="s">
         <v>1245</v>
       </c>
-      <c r="O213" s="12">
+      <c r="O213" s="1">
         <v>1</v>
       </c>
     </row>
@@ -23356,11 +23747,12 @@
       <c r="B214" t="s">
         <v>198</v>
       </c>
+      <c r="C214" s="11"/>
       <c r="E214" t="s">
         <v>698</v>
       </c>
-      <c r="F214" t="s">
-        <v>1469</v>
+      <c r="F214" s="11" t="s">
+        <v>1460</v>
       </c>
       <c r="H214" t="s">
         <v>1143</v>
@@ -23388,9 +23780,11 @@
       <c r="B215" t="s">
         <v>199</v>
       </c>
+      <c r="C215" s="11"/>
       <c r="E215" t="s">
         <v>699</v>
       </c>
+      <c r="F215" s="11"/>
       <c r="H215" t="s">
         <v>1144</v>
       </c>
@@ -23420,9 +23814,11 @@
       <c r="B216" t="s">
         <v>200</v>
       </c>
+      <c r="C216" s="11"/>
       <c r="E216" t="s">
         <v>700</v>
       </c>
+      <c r="F216" s="11"/>
       <c r="H216" t="s">
         <v>1338</v>
       </c>
@@ -23449,14 +23845,15 @@
       <c r="B217" t="s">
         <v>201</v>
       </c>
+      <c r="C217" s="11"/>
       <c r="E217" t="s">
         <v>701</v>
       </c>
-      <c r="F217" t="s">
-        <v>1516</v>
+      <c r="F217" s="11" t="s">
+        <v>1596</v>
       </c>
       <c r="G217" t="s">
-        <v>1517</v>
+        <v>1503</v>
       </c>
       <c r="I217" t="s">
         <v>1349</v>
@@ -23481,14 +23878,14 @@
       <c r="B218" t="s">
         <v>740</v>
       </c>
-      <c r="C218" t="s">
-        <v>1543</v>
+      <c r="C218" s="11" t="s">
+        <v>1528</v>
       </c>
       <c r="E218" t="s">
         <v>640</v>
       </c>
-      <c r="F218" t="s">
-        <v>1420</v>
+      <c r="F218" s="11" t="s">
+        <v>1563</v>
       </c>
       <c r="I218" t="s">
         <v>844</v>
@@ -23516,13 +23913,13 @@
       <c r="B219" t="s">
         <v>202</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C219" s="11" t="s">
         <v>1188</v>
       </c>
       <c r="E219" t="s">
         <v>1189</v>
       </c>
-      <c r="F219" t="s">
+      <c r="F219" s="11" t="s">
         <v>702</v>
       </c>
       <c r="H219" t="s">
@@ -23554,10 +23951,11 @@
       <c r="B220" t="s">
         <v>203</v>
       </c>
+      <c r="C220" s="11"/>
       <c r="E220" t="s">
         <v>703</v>
       </c>
-      <c r="F220" t="s">
+      <c r="F220" s="11" t="s">
         <v>1296</v>
       </c>
       <c r="H220" t="s">
@@ -23580,14 +23978,15 @@
       <c r="B221" t="s">
         <v>204</v>
       </c>
+      <c r="C221" s="11"/>
       <c r="E221" t="s">
         <v>704</v>
       </c>
-      <c r="F221" t="s">
-        <v>1458</v>
+      <c r="F221" s="11" t="s">
+        <v>1451</v>
       </c>
       <c r="G221" t="s">
-        <v>1566</v>
+        <v>1546</v>
       </c>
       <c r="H221" t="s">
         <v>1150</v>
@@ -23615,14 +24014,14 @@
       <c r="B222" t="s">
         <v>205</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C222" s="11" t="s">
         <v>1211</v>
       </c>
       <c r="E222" t="s">
         <v>705</v>
       </c>
-      <c r="F222" t="s">
-        <v>1430</v>
+      <c r="F222" s="11" t="s">
+        <v>1429</v>
       </c>
       <c r="G222" s="10"/>
       <c r="H222" t="s">
@@ -23654,9 +24053,11 @@
       <c r="B223" t="s">
         <v>206</v>
       </c>
+      <c r="C223" s="11"/>
       <c r="E223" t="s">
         <v>706</v>
       </c>
+      <c r="F223" s="11"/>
       <c r="H223" t="s">
         <v>1153</v>
       </c>
@@ -23686,9 +24087,11 @@
       <c r="B224" t="s">
         <v>207</v>
       </c>
+      <c r="C224" s="11"/>
       <c r="E224" t="s">
         <v>707</v>
       </c>
+      <c r="F224" s="11"/>
       <c r="H224" t="s">
         <v>1154</v>
       </c>
@@ -23712,9 +24115,11 @@
       <c r="B225" t="s">
         <v>208</v>
       </c>
+      <c r="C225" s="11"/>
       <c r="E225" t="s">
         <v>708</v>
       </c>
+      <c r="F225" s="11"/>
       <c r="H225" t="s">
         <v>1155</v>
       </c>
@@ -23744,14 +24149,15 @@
       <c r="B226" t="s">
         <v>209</v>
       </c>
+      <c r="C226" s="11"/>
       <c r="E226" t="s">
         <v>710</v>
       </c>
-      <c r="F226" t="s">
-        <v>1480</v>
+      <c r="F226" s="11" t="s">
+        <v>1576</v>
       </c>
       <c r="G226" t="s">
-        <v>1551</v>
+        <v>1535</v>
       </c>
       <c r="H226" t="s">
         <v>1204</v>
@@ -23782,11 +24188,12 @@
       <c r="B227" t="s">
         <v>210</v>
       </c>
+      <c r="C227" s="11"/>
       <c r="E227" t="s">
         <v>711</v>
       </c>
-      <c r="F227" t="s">
-        <v>1513</v>
+      <c r="F227" s="11" t="s">
+        <v>1500</v>
       </c>
       <c r="I227" t="s">
         <v>1405</v>
@@ -23814,9 +24221,11 @@
       <c r="B228" t="s">
         <v>211</v>
       </c>
+      <c r="C228" s="11"/>
       <c r="E228" t="s">
         <v>712</v>
       </c>
+      <c r="F228" s="11"/>
       <c r="H228" t="s">
         <v>1156</v>
       </c>
@@ -23837,17 +24246,17 @@
       <c r="B229" t="s">
         <v>487</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="11" t="s">
         <v>1184</v>
       </c>
       <c r="E229" t="s">
         <v>713</v>
       </c>
-      <c r="F229" t="s">
-        <v>1186</v>
+      <c r="F229" s="11" t="s">
+        <v>1564</v>
       </c>
       <c r="G229" t="s">
-        <v>1552</v>
+        <v>1593</v>
       </c>
       <c r="J229" t="s">
         <v>767</v>
@@ -23872,12 +24281,13 @@
       <c r="B230" t="s">
         <v>212</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C230" s="11" t="s">
         <v>1185</v>
       </c>
       <c r="E230" t="s">
         <v>714</v>
       </c>
+      <c r="F230" s="11"/>
       <c r="I230" t="s">
         <v>1349</v>
       </c>
@@ -23901,9 +24311,11 @@
       <c r="B231" t="s">
         <v>213</v>
       </c>
+      <c r="C231" s="11"/>
       <c r="E231" t="s">
         <v>715</v>
       </c>
+      <c r="F231" s="11"/>
       <c r="H231" t="s">
         <v>1159</v>
       </c>
@@ -23927,9 +24339,11 @@
       <c r="B232" t="s">
         <v>214</v>
       </c>
+      <c r="C232" s="11"/>
       <c r="E232" t="s">
         <v>716</v>
       </c>
+      <c r="F232" s="11"/>
       <c r="H232" t="s">
         <v>1088</v>
       </c>
@@ -23959,11 +24373,12 @@
       <c r="B233" t="s">
         <v>215</v>
       </c>
+      <c r="C233" s="11"/>
       <c r="E233" t="s">
         <v>717</v>
       </c>
-      <c r="F233" t="s">
-        <v>1468</v>
+      <c r="F233" s="11" t="s">
+        <v>1459</v>
       </c>
       <c r="H233" t="s">
         <v>1160</v>
@@ -23994,11 +24409,12 @@
       <c r="B234" t="s">
         <v>216</v>
       </c>
+      <c r="C234" s="11"/>
       <c r="E234" t="s">
         <v>718</v>
       </c>
-      <c r="F234" t="s">
-        <v>1456</v>
+      <c r="F234" s="11" t="s">
+        <v>1449</v>
       </c>
       <c r="I234" t="s">
         <v>844</v>
@@ -24029,11 +24445,12 @@
       <c r="B235" t="s">
         <v>217</v>
       </c>
+      <c r="C235" s="11"/>
       <c r="E235" t="s">
         <v>719</v>
       </c>
-      <c r="F235" t="s">
-        <v>1481</v>
+      <c r="F235" s="11" t="s">
+        <v>1584</v>
       </c>
       <c r="I235" t="s">
         <v>844</v>
@@ -24058,12 +24475,13 @@
       <c r="B236" t="s">
         <v>218</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C236" s="11" t="s">
         <v>1388</v>
       </c>
       <c r="E236" t="s">
         <v>720</v>
       </c>
+      <c r="F236" s="11"/>
       <c r="I236" t="s">
         <v>888</v>
       </c>
@@ -24081,20 +24499,20 @@
       <c r="B237" t="s">
         <v>746</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C237" s="11" t="s">
         <v>1387</v>
       </c>
       <c r="D237" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="E237" t="s">
         <v>747</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F237" s="11" t="s">
         <v>1181</v>
       </c>
       <c r="G237" t="s">
-        <v>1553</v>
+        <v>1536</v>
       </c>
       <c r="I237" t="s">
         <v>1404</v>
@@ -24122,9 +24540,11 @@
       <c r="B238" t="s">
         <v>219</v>
       </c>
+      <c r="C238" s="11"/>
       <c r="E238" t="s">
         <v>721</v>
       </c>
+      <c r="F238" s="11"/>
       <c r="H238" t="s">
         <v>1162</v>
       </c>
@@ -24154,9 +24574,11 @@
       <c r="B239" t="s">
         <v>220</v>
       </c>
+      <c r="C239" s="11"/>
       <c r="E239" t="s">
         <v>722</v>
       </c>
+      <c r="F239" s="11"/>
       <c r="H239" t="s">
         <v>1335</v>
       </c>
@@ -24186,14 +24608,15 @@
       <c r="B240" t="s">
         <v>221</v>
       </c>
+      <c r="C240" s="11"/>
       <c r="E240" t="s">
         <v>723</v>
       </c>
-      <c r="F240" t="s">
-        <v>1449</v>
+      <c r="F240" s="11" t="s">
+        <v>1579</v>
       </c>
       <c r="G240" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H240" t="s">
         <v>1165</v>
@@ -24224,14 +24647,14 @@
       <c r="B241" t="s">
         <v>222</v>
       </c>
-      <c r="C241" t="s">
-        <v>1520</v>
+      <c r="C241" s="11" t="s">
+        <v>1506</v>
       </c>
       <c r="E241" t="s">
         <v>724</v>
       </c>
-      <c r="F241" t="s">
-        <v>1441</v>
+      <c r="F241" s="11" t="s">
+        <v>1565</v>
       </c>
       <c r="I241" t="s">
         <v>1117</v>
@@ -24256,11 +24679,12 @@
       <c r="B242" t="s">
         <v>223</v>
       </c>
+      <c r="C242" s="11"/>
       <c r="E242" t="s">
         <v>725</v>
       </c>
-      <c r="F242" t="s">
-        <v>1558</v>
+      <c r="F242" s="11" t="s">
+        <v>1566</v>
       </c>
       <c r="I242" t="s">
         <v>844</v>
@@ -24288,9 +24712,11 @@
       <c r="B243" t="s">
         <v>224</v>
       </c>
+      <c r="C243" s="11"/>
       <c r="E243" t="s">
         <v>726</v>
       </c>
+      <c r="F243" s="11"/>
       <c r="H243" t="s">
         <v>1166</v>
       </c>
@@ -24314,9 +24740,11 @@
       <c r="B244" t="s">
         <v>225</v>
       </c>
+      <c r="C244" s="11"/>
       <c r="E244" t="s">
         <v>727</v>
       </c>
+      <c r="F244" s="11"/>
       <c r="H244" t="s">
         <v>1167</v>
       </c>
@@ -24346,9 +24774,11 @@
       <c r="B245" t="s">
         <v>226</v>
       </c>
+      <c r="C245" s="11"/>
       <c r="E245" t="s">
         <v>728</v>
       </c>
+      <c r="F245" s="11"/>
       <c r="H245" t="s">
         <v>1168</v>
       </c>
@@ -24372,9 +24802,11 @@
       <c r="B246" t="s">
         <v>227</v>
       </c>
+      <c r="C246" s="11"/>
       <c r="E246" t="s">
         <v>729</v>
       </c>
+      <c r="F246" s="11"/>
       <c r="H246" t="s">
         <v>1169</v>
       </c>
@@ -24401,14 +24833,15 @@
       <c r="B247" t="s">
         <v>228</v>
       </c>
+      <c r="C247" s="11"/>
       <c r="E247" t="s">
         <v>730</v>
       </c>
-      <c r="F247" t="s">
-        <v>1515</v>
+      <c r="F247" s="11" t="s">
+        <v>1502</v>
       </c>
       <c r="G247" t="s">
-        <v>1555</v>
+        <v>1537</v>
       </c>
       <c r="H247" t="s">
         <v>1170</v>
@@ -24439,11 +24872,12 @@
       <c r="B248" t="s">
         <v>229</v>
       </c>
+      <c r="C248" s="11"/>
       <c r="E248" t="s">
         <v>731</v>
       </c>
-      <c r="F248" t="s">
-        <v>1436</v>
+      <c r="F248" s="11" t="s">
+        <v>1435</v>
       </c>
       <c r="I248" t="s">
         <v>844</v>
@@ -24468,9 +24902,11 @@
       <c r="B249" t="s">
         <v>230</v>
       </c>
+      <c r="C249" s="11"/>
       <c r="E249" t="s">
         <v>732</v>
       </c>
+      <c r="F249" s="11"/>
       <c r="H249" t="s">
         <v>1173</v>
       </c>
@@ -24500,14 +24936,15 @@
       <c r="B250" t="s">
         <v>231</v>
       </c>
+      <c r="C250" s="11"/>
       <c r="E250" t="s">
         <v>733</v>
       </c>
-      <c r="F250" t="s">
-        <v>1476</v>
+      <c r="F250" s="11" t="s">
+        <v>1467</v>
       </c>
       <c r="G250" t="s">
-        <v>1556</v>
+        <v>1538</v>
       </c>
       <c r="H250" t="s">
         <v>1175</v>
@@ -24538,14 +24975,14 @@
       <c r="B251" t="s">
         <v>232</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C251" s="11" t="s">
         <v>1392</v>
       </c>
       <c r="E251" t="s">
         <v>734</v>
       </c>
-      <c r="F251" t="s">
-        <v>1443</v>
+      <c r="F251" s="11" t="s">
+        <v>1581</v>
       </c>
       <c r="I251" t="s">
         <v>844</v>
@@ -24573,14 +25010,15 @@
       <c r="B252" t="s">
         <v>233</v>
       </c>
+      <c r="C252" s="11"/>
       <c r="E252" t="s">
         <v>735</v>
       </c>
-      <c r="F252" t="s">
+      <c r="F252" s="11" t="s">
         <v>1183</v>
       </c>
       <c r="G252" t="s">
-        <v>1557</v>
+        <v>1539</v>
       </c>
       <c r="H252" t="s">
         <v>902</v>
@@ -24605,9 +25043,11 @@
       <c r="B253" t="s">
         <v>234</v>
       </c>
+      <c r="C253" s="11"/>
       <c r="E253" t="s">
         <v>736</v>
       </c>
+      <c r="F253" s="11"/>
       <c r="H253" t="s">
         <v>1339</v>
       </c>
@@ -24634,11 +25074,12 @@
       <c r="B254" t="s">
         <v>235</v>
       </c>
+      <c r="C254" s="11"/>
       <c r="E254" t="s">
         <v>737</v>
       </c>
-      <c r="F254" t="s">
-        <v>1442</v>
+      <c r="F254" s="11" t="s">
+        <v>1439</v>
       </c>
       <c r="H254" t="s">
         <v>1179</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E76307-CC90-41AC-8D43-26B8F5A2CC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EB3787-63B5-4102-94DA-52ED9CEF41A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="20985" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4359" uniqueCount="1597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4363" uniqueCount="1604">
   <si>
     <t>Sigla</t>
   </si>
@@ -4328,9 +4328,6 @@
     <t>Abbia, Appia</t>
   </si>
   <si>
-    <t>Ruba</t>
-  </si>
-  <si>
     <t>Con Acri</t>
   </si>
   <si>
@@ -4628,9 +4625,6 @@
     <t>*Micronesia, datti federati di micronesia</t>
   </si>
   <si>
-    <t>S Maarten, Sint Marten</t>
-  </si>
-  <si>
     <t>Sènt Denì</t>
   </si>
   <si>
@@ -4790,9 +4784,6 @@
     <t>a lo fi, all of i</t>
   </si>
   <si>
-    <t>New e, new wave, noi e</t>
-  </si>
-  <si>
     <t>Nuku alofa, Mutualopa, Nukolov, nucu alofa, nuco a lo fa</t>
   </si>
   <si>
@@ -4830,6 +4821,36 @@
   </si>
   <si>
     <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte, cotti, sri giaia, striglia guarda, free java, tre giaia, pura cotte</t>
+  </si>
+  <si>
+    <t>Santiago, Santhiago, Santhiago del cile, lago del cile</t>
+  </si>
+  <si>
+    <t>Tito</t>
+  </si>
+  <si>
+    <t>Ruba, Juve</t>
+  </si>
+  <si>
+    <t>Sile</t>
+  </si>
+  <si>
+    <t>Comare</t>
+  </si>
+  <si>
+    <t>Linea equatoriale</t>
+  </si>
+  <si>
+    <t>Pitcairn, isole big cairn, isole pick up</t>
+  </si>
+  <si>
+    <t>Saint Martin, S Martin, San marten</t>
+  </si>
+  <si>
+    <t>S Maarten, Sint Marten, synth martin</t>
+  </si>
+  <si>
+    <t>New e, new wave, noi e, miura</t>
   </si>
 </sst>
 </file>
@@ -4932,7 +4953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4948,13 +4969,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4982,13 +5008,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -16242,11 +16261,11 @@
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{C69A84BF-08C6-4051-820A-053DF45718B4}" name="Sigla" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{E07D78F6-8AAC-46C7-9978-B6D2697016C9}" name="Paese" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{237EE744-113E-41B5-A3B5-EAE5FB442A2A}" name="Alias - paese" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{E07D78F6-8AAC-46C7-9978-B6D2697016C9}" name="Paese" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{237EE744-113E-41B5-A3B5-EAE5FB442A2A}" name="Alias - paese" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{0025EC9F-08BF-408D-9B17-F0234A6D6CF3}" name="Pronuncia_paese"/>
     <tableColumn id="4" xr3:uid="{50A4CCBE-582F-4110-BFBE-9A82392BC235}" name="Capitale"/>
-    <tableColumn id="11" xr3:uid="{6A83C5DC-9025-46CB-87AA-3A300C8CF314}" name="Alias - capitale" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{6A83C5DC-9025-46CB-87AA-3A300C8CF314}" name="Alias - capitale" dataDxfId="2"/>
     <tableColumn id="15" xr3:uid="{AC13460F-731B-4E22-ABFF-160F80636E6A}" name="Pronuncia_capitale"/>
     <tableColumn id="8" xr3:uid="{D0F9292E-BC3F-4A24-BCFF-7BC92AA199DC}" name="Confini"/>
     <tableColumn id="12" xr3:uid="{5E4DE2A9-E4C6-4C56-9D54-D689B707F205}" name="Continente/Area geografica"/>
@@ -16254,8 +16273,8 @@
     <tableColumn id="6" xr3:uid="{1693D812-90EC-4EB0-992E-5CCE55839A4A}" name="Colore emblema"/>
     <tableColumn id="10" xr3:uid="{C924A7D7-A27D-4A41-9F45-DAF1CF135E69}" name="simboli bandiera"/>
     <tableColumn id="5" xr3:uid="{00F3A94F-DF24-4C44-822F-B9855F17B5A1}" name="dipendente"/>
-    <tableColumn id="14" xr3:uid="{1D457A4D-7A9B-4CE0-A285-4706192AD985}" name="Caratteristiche bandiera" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{FE0D03FC-F89A-4732-8C5E-E7737E148AB2}" name="Livello" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{1D457A4D-7A9B-4CE0-A285-4706192AD985}" name="Caratteristiche bandiera" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{FE0D03FC-F89A-4732-8C5E-E7737E148AB2}" name="Livello" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16657,7 +16676,7 @@
         <v>749</v>
       </c>
       <c r="D1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E1" t="s">
         <v>497</v>
@@ -16666,7 +16685,7 @@
         <v>750</v>
       </c>
       <c r="G1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H1" t="s">
         <v>748</v>
@@ -16700,13 +16719,12 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" t="s">
         <v>752</v>
       </c>
       <c r="E2" t="s">
         <v>498</v>
       </c>
-      <c r="F2" s="11"/>
       <c r="H2" t="s">
         <v>753</v>
       </c>
@@ -16743,12 +16761,11 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11"/>
       <c r="E3" t="s">
         <v>499</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>1441</v>
+      <c r="F3" t="s">
+        <v>1440</v>
       </c>
       <c r="H3" t="s">
         <v>1195</v>
@@ -16786,11 +16803,9 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11"/>
       <c r="E4" t="s">
         <v>500</v>
       </c>
-      <c r="F4" s="11"/>
       <c r="H4" t="s">
         <v>827</v>
       </c>
@@ -16827,18 +16842,17 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="11"/>
       <c r="D5" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="E5" t="s">
         <v>501</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" t="s">
         <v>756</v>
       </c>
       <c r="G5" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H5" t="s">
         <v>757</v>
@@ -16866,11 +16880,9 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="11"/>
       <c r="E6" t="s">
         <v>502</v>
       </c>
-      <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" t="s">
         <v>828</v>
@@ -16901,11 +16913,9 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11"/>
       <c r="E7" t="s">
         <v>503</v>
       </c>
-      <c r="F7" s="11"/>
       <c r="I7" t="s">
         <v>888</v>
       </c>
@@ -16929,13 +16939,13 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" t="s">
         <v>759</v>
       </c>
       <c r="E8" t="s">
         <v>504</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" t="s">
         <v>1421</v>
       </c>
       <c r="I8" t="s">
@@ -16958,17 +16968,17 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" t="s">
         <v>762</v>
       </c>
       <c r="E9" t="s">
         <v>514</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" t="s">
         <v>763</v>
       </c>
       <c r="G9" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="H9" t="s">
         <v>829</v>
@@ -16999,11 +17009,9 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="11"/>
       <c r="E10" t="s">
         <v>505</v>
       </c>
-      <c r="F10" s="11"/>
       <c r="H10" t="s">
         <v>830</v>
       </c>
@@ -17033,11 +17041,9 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="11"/>
       <c r="E11" t="s">
         <v>506</v>
       </c>
-      <c r="F11" s="11"/>
       <c r="H11" t="s">
         <v>765</v>
       </c>
@@ -17061,12 +17067,11 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="11"/>
       <c r="E12" t="s">
         <v>513</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>1457</v>
+      <c r="F12" t="s">
+        <v>1456</v>
       </c>
       <c r="I12" t="s">
         <v>888</v>
@@ -17094,13 +17099,12 @@
       <c r="B13" t="s">
         <v>745</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" t="s">
         <v>784</v>
       </c>
       <c r="E13" t="s">
         <v>583</v>
       </c>
-      <c r="F13" s="11"/>
       <c r="I13" t="s">
         <v>1399</v>
       </c>
@@ -17124,11 +17128,9 @@
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="11"/>
       <c r="E14" t="s">
         <v>507</v>
       </c>
-      <c r="F14" s="11"/>
       <c r="I14" t="s">
         <v>844</v>
       </c>
@@ -17155,11 +17157,9 @@
       <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11"/>
       <c r="E15" t="s">
         <v>508</v>
       </c>
-      <c r="F15" s="11"/>
       <c r="H15" t="s">
         <v>768</v>
       </c>
@@ -17183,13 +17183,12 @@
       <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>1474</v>
+      <c r="C16" t="s">
+        <v>1473</v>
       </c>
       <c r="E16" t="s">
         <v>509</v>
       </c>
-      <c r="F16" s="11"/>
       <c r="H16" t="s">
         <v>887</v>
       </c>
@@ -17219,11 +17218,9 @@
       <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11"/>
       <c r="E17" t="s">
         <v>510</v>
       </c>
-      <c r="F17" s="11"/>
       <c r="I17" t="s">
         <v>888</v>
       </c>
@@ -17244,13 +17241,12 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" t="s">
         <v>793</v>
       </c>
       <c r="E18" t="s">
         <v>511</v>
       </c>
-      <c r="F18" s="11"/>
       <c r="H18" t="s">
         <v>831</v>
       </c>
@@ -17271,17 +17267,17 @@
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>1462</v>
+      <c r="C19" t="s">
+        <v>1461</v>
       </c>
       <c r="E19" t="s">
         <v>512</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" t="s">
         <v>1390</v>
       </c>
       <c r="G19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="I19" t="s">
         <v>1397</v>
@@ -17306,11 +17302,9 @@
       <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11"/>
       <c r="E20" t="s">
         <v>515</v>
       </c>
-      <c r="F20" s="11"/>
       <c r="G20" s="10"/>
       <c r="H20" t="s">
         <v>832</v>
@@ -17341,12 +17335,11 @@
       <c r="B21" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="11"/>
       <c r="E21" t="s">
         <v>516</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>1446</v>
+      <c r="F21" t="s">
+        <v>1445</v>
       </c>
       <c r="I21" t="s">
         <v>888</v>
@@ -17374,11 +17367,9 @@
       <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="11"/>
       <c r="E22" t="s">
         <v>517</v>
       </c>
-      <c r="F22" s="11"/>
       <c r="H22" t="s">
         <v>1205</v>
       </c>
@@ -17402,12 +17393,11 @@
       <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11"/>
       <c r="E23" t="s">
         <v>518</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>1568</v>
+      <c r="F23" t="s">
+        <v>1566</v>
       </c>
       <c r="H23" t="s">
         <v>833</v>
@@ -17438,11 +17428,10 @@
       <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="11"/>
       <c r="E24" t="s">
         <v>519</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" t="s">
         <v>1422</v>
       </c>
       <c r="H24" t="s">
@@ -17465,11 +17454,9 @@
       <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11"/>
       <c r="E25" t="s">
         <v>520</v>
       </c>
-      <c r="F25" s="11"/>
       <c r="I25" t="s">
         <v>851</v>
       </c>
@@ -17493,14 +17480,14 @@
       <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" t="s">
         <v>885</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>1485</v>
+      <c r="F26" t="s">
+        <v>1484</v>
       </c>
       <c r="H26" t="s">
         <v>802</v>
@@ -17528,13 +17515,12 @@
       <c r="B27" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" t="s">
         <v>1298</v>
       </c>
       <c r="E27" t="s">
         <v>522</v>
       </c>
-      <c r="F27" s="11"/>
       <c r="H27" t="s">
         <v>804</v>
       </c>
@@ -17558,15 +17544,14 @@
       <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="11"/>
       <c r="E28" t="s">
         <v>524</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" t="s">
         <v>1297</v>
       </c>
       <c r="G28" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H28" t="s">
         <v>810</v>
@@ -17594,18 +17579,17 @@
       <c r="B29" t="s">
         <v>484</v>
       </c>
-      <c r="C29" s="11"/>
       <c r="D29" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E29" t="s">
         <v>525</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>1594</v>
+      <c r="F29" t="s">
+        <v>1591</v>
       </c>
       <c r="G29" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="I29" t="s">
         <v>888</v>
@@ -17636,13 +17620,12 @@
       <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>1548</v>
+      <c r="C30" t="s">
+        <v>1546</v>
       </c>
       <c r="E30" t="s">
         <v>526</v>
       </c>
-      <c r="F30" s="11"/>
       <c r="G30" s="10"/>
       <c r="H30" t="s">
         <v>836</v>
@@ -17673,12 +17656,11 @@
       <c r="B31" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11"/>
       <c r="E31" t="s">
         <v>527</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>1501</v>
+      <c r="F31" t="s">
+        <v>1500</v>
       </c>
       <c r="H31" t="s">
         <v>1056</v>
@@ -17703,11 +17685,9 @@
       <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11"/>
       <c r="E32" t="s">
         <v>528</v>
       </c>
-      <c r="F32" s="11"/>
       <c r="H32" t="s">
         <v>837</v>
       </c>
@@ -17737,15 +17717,14 @@
       <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11"/>
       <c r="E33" t="s">
         <v>529</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>1447</v>
+      <c r="F33" t="s">
+        <v>1446</v>
       </c>
       <c r="G33" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H33" t="s">
         <v>1031</v>
@@ -17776,13 +17755,11 @@
       <c r="B34" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11"/>
       <c r="E34" t="s">
         <v>530</v>
       </c>
-      <c r="F34" s="11"/>
       <c r="G34" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="H34" t="s">
         <v>838</v>
@@ -17807,12 +17784,11 @@
       <c r="B35" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11"/>
       <c r="E35" t="s">
         <v>531</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>1556</v>
+      <c r="F35" t="s">
+        <v>1554</v>
       </c>
       <c r="H35" t="s">
         <v>820</v>
@@ -17843,12 +17819,11 @@
       <c r="B36" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11"/>
       <c r="E36" t="s">
         <v>532</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>1440</v>
+      <c r="F36" t="s">
+        <v>1439</v>
       </c>
       <c r="H36" t="s">
         <v>826</v>
@@ -17879,15 +17854,14 @@
       <c r="B37" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11"/>
       <c r="E37" t="s">
         <v>533</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" t="s">
         <v>1423</v>
       </c>
       <c r="G37" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="H37" t="s">
         <v>929</v>
@@ -17918,14 +17892,14 @@
       <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" t="s">
         <v>923</v>
       </c>
       <c r="E38" t="s">
         <v>534</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>1487</v>
+      <c r="F38" t="s">
+        <v>1486</v>
       </c>
       <c r="H38" t="s">
         <v>856</v>
@@ -17956,11 +17930,9 @@
       <c r="B39" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11"/>
       <c r="E39" t="s">
         <v>535</v>
       </c>
-      <c r="F39" s="11"/>
       <c r="H39" t="s">
         <v>959</v>
       </c>
@@ -17990,11 +17962,9 @@
       <c r="B40" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="12"/>
       <c r="E40" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="F40" s="12"/>
       <c r="I40" s="8" t="s">
         <v>1401</v>
       </c>
@@ -18018,13 +17988,12 @@
       <c r="B41" t="s">
         <v>1097</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>1480</v>
+      <c r="C41" t="s">
+        <v>1479</v>
       </c>
       <c r="E41" t="s">
         <v>671</v>
       </c>
-      <c r="F41" s="11"/>
       <c r="H41" t="s">
         <v>1099</v>
       </c>
@@ -18048,12 +18017,11 @@
       <c r="B42" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="11"/>
       <c r="E42" t="s">
         <v>537</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>1571</v>
+      <c r="F42" t="s">
+        <v>1569</v>
       </c>
       <c r="H42" t="s">
         <v>861</v>
@@ -18078,12 +18046,14 @@
       <c r="B43" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="11"/>
+      <c r="C43" t="s">
+        <v>1597</v>
+      </c>
       <c r="E43" t="s">
         <v>538</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>862</v>
+      <c r="F43" t="s">
+        <v>1594</v>
       </c>
       <c r="H43" t="s">
         <v>865</v>
@@ -18114,11 +18084,10 @@
       <c r="B44" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="11"/>
       <c r="E44" t="s">
         <v>539</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" t="s">
         <v>863</v>
       </c>
       <c r="H44" t="s">
@@ -18150,11 +18119,9 @@
       <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="11"/>
       <c r="E45" t="s">
         <v>540</v>
       </c>
-      <c r="F45" s="11"/>
       <c r="I45" t="s">
         <v>1416</v>
       </c>
@@ -18181,13 +18148,13 @@
       <c r="B46" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" t="s">
         <v>868</v>
       </c>
       <c r="E46" t="s">
         <v>44</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" t="s">
         <v>868</v>
       </c>
       <c r="H46" t="s">
@@ -18216,11 +18183,9 @@
       <c r="B47" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="11"/>
       <c r="E47" t="s">
         <v>541</v>
       </c>
-      <c r="F47" s="11"/>
       <c r="H47" t="s">
         <v>870</v>
       </c>
@@ -18244,11 +18209,12 @@
       <c r="B48" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="11"/>
+      <c r="C48" t="s">
+        <v>1598</v>
+      </c>
       <c r="E48" t="s">
         <v>542</v>
       </c>
-      <c r="F48" s="11"/>
       <c r="I48" t="s">
         <v>1402</v>
       </c>
@@ -18275,13 +18241,12 @@
       <c r="B49" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" t="s">
         <v>876</v>
       </c>
       <c r="E49" t="s">
         <v>543</v>
       </c>
-      <c r="F49" s="11"/>
       <c r="H49" t="s">
         <v>962</v>
       </c>
@@ -18302,13 +18267,12 @@
       <c r="B50" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" t="s">
         <v>877</v>
       </c>
       <c r="E50" t="s">
         <v>544</v>
       </c>
-      <c r="F50" s="11"/>
       <c r="H50" t="s">
         <v>963</v>
       </c>
@@ -18338,13 +18302,13 @@
       <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" t="s">
         <v>878</v>
       </c>
       <c r="E51" t="s">
         <v>545</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" t="s">
         <v>880</v>
       </c>
       <c r="H51" t="s">
@@ -18376,14 +18340,14 @@
       <c r="B52" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>1455</v>
+      <c r="C52" t="s">
+        <v>1454</v>
       </c>
       <c r="E52" t="s">
         <v>546</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>1573</v>
+      <c r="F52" t="s">
+        <v>1571</v>
       </c>
       <c r="G52" t="s">
         <v>883</v>
@@ -18411,11 +18375,9 @@
       <c r="B53" t="s">
         <v>51</v>
       </c>
-      <c r="C53" s="11"/>
       <c r="E53" t="s">
         <v>547</v>
       </c>
-      <c r="F53" s="11"/>
       <c r="H53" t="s">
         <v>966</v>
       </c>
@@ -18442,11 +18404,9 @@
       <c r="B54" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="11"/>
       <c r="E54" t="s">
         <v>548</v>
       </c>
-      <c r="F54" s="11"/>
       <c r="H54" t="s">
         <v>967</v>
       </c>
@@ -18473,12 +18433,11 @@
       <c r="B55" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="11"/>
       <c r="E55" t="s">
         <v>549</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>1468</v>
+      <c r="F55" t="s">
+        <v>1467</v>
       </c>
       <c r="I55" t="s">
         <v>888</v>
@@ -18506,13 +18465,13 @@
       <c r="B56" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>1463</v>
+      <c r="C56" t="s">
+        <v>1462</v>
       </c>
       <c r="E56" t="s">
         <v>550</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" t="s">
         <v>1424</v>
       </c>
       <c r="I56" t="s">
@@ -18544,11 +18503,9 @@
       <c r="B57" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="11"/>
       <c r="E57" t="s">
         <v>551</v>
       </c>
-      <c r="F57" s="11"/>
       <c r="H57" t="s">
         <v>1341</v>
       </c>
@@ -18572,12 +18529,11 @@
       <c r="B58" t="s">
         <v>56</v>
       </c>
-      <c r="C58" s="11"/>
       <c r="E58" t="s">
         <v>552</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>1557</v>
+      <c r="F58" t="s">
+        <v>1555</v>
       </c>
       <c r="I58" t="s">
         <v>888</v>
@@ -18605,11 +18561,12 @@
       <c r="B59" t="s">
         <v>57</v>
       </c>
-      <c r="C59" s="11"/>
       <c r="E59" t="s">
         <v>553</v>
       </c>
-      <c r="F59" s="11"/>
+      <c r="F59" t="s">
+        <v>1595</v>
+      </c>
       <c r="H59" t="s">
         <v>892</v>
       </c>
@@ -18620,7 +18577,7 @@
         <v>871</v>
       </c>
       <c r="L59" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="N59" t="s">
         <v>1245</v>
@@ -18636,12 +18593,11 @@
       <c r="B60" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="11"/>
       <c r="E60" t="s">
         <v>554</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>1465</v>
+      <c r="F60" t="s">
+        <v>1464</v>
       </c>
       <c r="H60" t="s">
         <v>894</v>
@@ -18672,13 +18628,13 @@
       <c r="B61" t="s">
         <v>59</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>1464</v>
+      <c r="C61" t="s">
+        <v>1463</v>
       </c>
       <c r="E61" t="s">
         <v>555</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" t="s">
         <v>899</v>
       </c>
       <c r="H61" t="s">
@@ -18707,13 +18663,13 @@
       <c r="B62" t="s">
         <v>60</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" t="s">
         <v>900</v>
       </c>
       <c r="E62" t="s">
         <v>556</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" t="s">
         <v>901</v>
       </c>
       <c r="H62" t="s">
@@ -18736,11 +18692,9 @@
       <c r="B63" t="s">
         <v>61</v>
       </c>
-      <c r="C63" s="11"/>
       <c r="E63" t="s">
         <v>573</v>
       </c>
-      <c r="F63" s="11"/>
       <c r="H63" t="s">
         <v>905</v>
       </c>
@@ -18767,13 +18721,12 @@
       <c r="B64" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="11" t="s">
-        <v>1549</v>
+      <c r="C64" t="s">
+        <v>1547</v>
       </c>
       <c r="E64" t="s">
         <v>558</v>
       </c>
-      <c r="F64" s="11"/>
       <c r="H64" t="s">
         <v>909</v>
       </c>
@@ -18797,14 +18750,14 @@
       <c r="B65" t="s">
         <v>741</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" t="s">
         <v>1386</v>
       </c>
       <c r="E65" t="s">
         <v>709</v>
       </c>
-      <c r="F65" s="11" t="s">
-        <v>1544</v>
+      <c r="F65" t="s">
+        <v>1542</v>
       </c>
       <c r="H65" t="s">
         <v>1057</v>
@@ -18832,11 +18785,9 @@
       <c r="B66" t="s">
         <v>63</v>
       </c>
-      <c r="C66" s="11"/>
       <c r="E66" t="s">
         <v>559</v>
       </c>
-      <c r="F66" s="11"/>
       <c r="H66" t="s">
         <v>915</v>
       </c>
@@ -18866,13 +18817,12 @@
       <c r="B67" t="s">
         <v>64</v>
       </c>
-      <c r="C67" s="11" t="s">
-        <v>1527</v>
+      <c r="C67" t="s">
+        <v>1526</v>
       </c>
       <c r="E67" t="s">
         <v>560</v>
       </c>
-      <c r="F67" s="11"/>
       <c r="I67" t="s">
         <v>844</v>
       </c>
@@ -18893,11 +18843,9 @@
       <c r="B68" t="s">
         <v>65</v>
       </c>
-      <c r="C68" s="11"/>
       <c r="E68" t="s">
         <v>561</v>
       </c>
-      <c r="F68" s="11"/>
       <c r="I68" t="s">
         <v>1360</v>
       </c>
@@ -18924,11 +18872,9 @@
       <c r="B69" t="s">
         <v>66</v>
       </c>
-      <c r="C69" s="11"/>
       <c r="E69" t="s">
         <v>562</v>
       </c>
-      <c r="F69" s="11"/>
       <c r="H69" t="s">
         <v>917</v>
       </c>
@@ -18952,11 +18898,9 @@
       <c r="B70" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="11"/>
       <c r="E70" t="s">
         <v>563</v>
       </c>
-      <c r="F70" s="11"/>
       <c r="H70" t="s">
         <v>1052</v>
       </c>
@@ -18980,15 +18924,14 @@
       <c r="B71" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="11"/>
       <c r="E71" t="s">
         <v>564</v>
       </c>
-      <c r="F71" s="11" t="s">
-        <v>1483</v>
+      <c r="F71" t="s">
+        <v>1482</v>
       </c>
       <c r="G71" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H71" t="s">
         <v>968</v>
@@ -19013,11 +18956,9 @@
       <c r="B72" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="11"/>
       <c r="E72" t="s">
         <v>565</v>
       </c>
-      <c r="F72" s="11"/>
       <c r="H72" t="s">
         <v>926</v>
       </c>
@@ -19047,12 +18988,11 @@
       <c r="B73" t="s">
         <v>70</v>
       </c>
-      <c r="C73" s="11"/>
       <c r="E73" t="s">
         <v>566</v>
       </c>
-      <c r="F73" s="11" t="s">
-        <v>1469</v>
+      <c r="F73" t="s">
+        <v>1468</v>
       </c>
       <c r="H73" t="s">
         <v>925</v>
@@ -19077,11 +19017,9 @@
       <c r="B74" t="s">
         <v>71</v>
       </c>
-      <c r="C74" s="11"/>
       <c r="E74" t="s">
         <v>567</v>
       </c>
-      <c r="F74" s="11"/>
       <c r="H74" t="s">
         <v>931</v>
       </c>
@@ -19105,13 +19043,13 @@
       <c r="B75" t="s">
         <v>72</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" t="s">
         <v>932</v>
       </c>
       <c r="E75" t="s">
         <v>568</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" t="s">
         <v>933</v>
       </c>
       <c r="I75" t="s">
@@ -19137,11 +19075,9 @@
       <c r="B76" t="s">
         <v>73</v>
       </c>
-      <c r="C76" s="11"/>
       <c r="E76" t="s">
         <v>569</v>
       </c>
-      <c r="F76" s="11"/>
       <c r="H76" t="s">
         <v>934</v>
       </c>
@@ -19165,13 +19101,12 @@
       <c r="B77" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="11" t="s">
-        <v>1475</v>
+      <c r="C77" t="s">
+        <v>1474</v>
       </c>
       <c r="E77" t="s">
         <v>570</v>
       </c>
-      <c r="F77" s="11"/>
       <c r="H77" t="s">
         <v>969</v>
       </c>
@@ -19201,13 +19136,12 @@
       <c r="B78" t="s">
         <v>75</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" t="s">
         <v>1332</v>
       </c>
       <c r="E78" t="s">
         <v>571</v>
       </c>
-      <c r="F78" s="11"/>
       <c r="I78" t="s">
         <v>888</v>
       </c>
@@ -19228,11 +19162,9 @@
       <c r="B79" t="s">
         <v>76</v>
       </c>
-      <c r="C79" s="11"/>
       <c r="E79" t="s">
         <v>572</v>
       </c>
-      <c r="F79" s="11"/>
       <c r="I79" t="s">
         <v>1405</v>
       </c>
@@ -19259,11 +19191,9 @@
       <c r="B80" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="11"/>
       <c r="E80" t="s">
         <v>77</v>
       </c>
-      <c r="F80" s="11"/>
       <c r="H80" t="s">
         <v>938</v>
       </c>
@@ -19296,14 +19226,14 @@
       <c r="B81" t="s">
         <v>78</v>
       </c>
-      <c r="C81" s="11" t="s">
-        <v>1453</v>
+      <c r="C81" t="s">
+        <v>1452</v>
       </c>
       <c r="E81" t="s">
         <v>78</v>
       </c>
-      <c r="F81" s="11" t="s">
-        <v>1453</v>
+      <c r="F81" t="s">
+        <v>1452</v>
       </c>
       <c r="H81" t="s">
         <v>944</v>
@@ -19334,11 +19264,9 @@
       <c r="B82" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="11"/>
       <c r="E82" t="s">
         <v>557</v>
       </c>
-      <c r="F82" s="11"/>
       <c r="H82" t="s">
         <v>961</v>
       </c>
@@ -19368,11 +19296,9 @@
       <c r="B83" t="s">
         <v>80</v>
       </c>
-      <c r="C83" s="11"/>
       <c r="E83" t="s">
         <v>574</v>
       </c>
-      <c r="F83" s="11"/>
       <c r="H83" t="s">
         <v>945</v>
       </c>
@@ -19396,12 +19322,11 @@
       <c r="B84" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="11"/>
       <c r="E84" t="s">
         <v>575</v>
       </c>
-      <c r="F84" s="11" t="s">
-        <v>1478</v>
+      <c r="F84" t="s">
+        <v>1477</v>
       </c>
       <c r="I84" t="s">
         <v>1117</v>
@@ -19429,11 +19354,10 @@
       <c r="B85" t="s">
         <v>82</v>
       </c>
-      <c r="C85" s="11"/>
       <c r="E85" t="s">
         <v>576</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" t="s">
         <v>1417</v>
       </c>
       <c r="H85" t="s">
@@ -19462,12 +19386,11 @@
       <c r="B86" t="s">
         <v>83</v>
       </c>
-      <c r="C86" s="11"/>
       <c r="E86" t="s">
         <v>577</v>
       </c>
-      <c r="F86" s="11" t="s">
-        <v>1567</v>
+      <c r="F86" t="s">
+        <v>1565</v>
       </c>
       <c r="I86" t="s">
         <v>1117</v>
@@ -19492,17 +19415,17 @@
       <c r="B87" t="s">
         <v>84</v>
       </c>
-      <c r="C87" s="11" t="s">
-        <v>1550</v>
+      <c r="C87" t="s">
+        <v>1548</v>
       </c>
       <c r="E87" t="s">
         <v>578</v>
       </c>
-      <c r="F87" s="11" t="s">
-        <v>1595</v>
+      <c r="F87" t="s">
+        <v>1592</v>
       </c>
       <c r="G87" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="I87" t="s">
         <v>844</v>
@@ -19527,11 +19450,10 @@
       <c r="B88" t="s">
         <v>85</v>
       </c>
-      <c r="C88" s="11"/>
       <c r="E88" t="s">
         <v>579</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" t="s">
         <v>85</v>
       </c>
       <c r="H88" t="s">
@@ -19560,12 +19482,11 @@
       <c r="B89" t="s">
         <v>86</v>
       </c>
-      <c r="C89" s="11"/>
       <c r="E89" t="s">
         <v>580</v>
       </c>
-      <c r="F89" s="11" t="s">
-        <v>1526</v>
+      <c r="F89" t="s">
+        <v>1525</v>
       </c>
       <c r="I89" t="s">
         <v>1397</v>
@@ -19590,12 +19511,11 @@
       <c r="B90" t="s">
         <v>87</v>
       </c>
-      <c r="C90" s="11"/>
       <c r="E90" t="s">
         <v>581</v>
       </c>
-      <c r="F90" s="11" t="s">
-        <v>1430</v>
+      <c r="F90" t="s">
+        <v>1429</v>
       </c>
       <c r="H90" t="s">
         <v>1012</v>
@@ -19620,15 +19540,17 @@
       <c r="B91" t="s">
         <v>88</v>
       </c>
-      <c r="C91" s="11"/>
+      <c r="C91" t="s">
+        <v>1599</v>
+      </c>
       <c r="E91" t="s">
         <v>948</v>
       </c>
-      <c r="F91" s="11" t="s">
-        <v>1438</v>
+      <c r="F91" t="s">
+        <v>1437</v>
       </c>
       <c r="G91" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H91" t="s">
         <v>949</v>
@@ -19656,13 +19578,12 @@
       <c r="B92" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" t="s">
         <v>954</v>
       </c>
       <c r="E92" t="s">
         <v>582</v>
       </c>
-      <c r="F92" s="11"/>
       <c r="H92" t="s">
         <v>951</v>
       </c>
@@ -19692,11 +19613,9 @@
       <c r="B93" t="s">
         <v>90</v>
       </c>
-      <c r="C93" s="11"/>
       <c r="E93" t="s">
         <v>583</v>
       </c>
-      <c r="F93" s="11"/>
       <c r="H93" t="s">
         <v>952</v>
       </c>
@@ -19720,15 +19639,14 @@
       <c r="B94" t="s">
         <v>91</v>
       </c>
-      <c r="C94" s="11"/>
       <c r="E94" t="s">
         <v>584</v>
       </c>
-      <c r="F94" s="11" t="s">
+      <c r="F94" t="s">
         <v>953</v>
       </c>
       <c r="G94" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H94" t="s">
         <v>955</v>
@@ -19762,12 +19680,11 @@
       <c r="B95" t="s">
         <v>92</v>
       </c>
-      <c r="C95" s="11"/>
       <c r="E95" t="s">
         <v>626</v>
       </c>
-      <c r="F95" s="11" t="s">
-        <v>1450</v>
+      <c r="F95" t="s">
+        <v>1449</v>
       </c>
       <c r="H95" t="s">
         <v>972</v>
@@ -19795,11 +19712,9 @@
       <c r="B96" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="11"/>
       <c r="E96" t="s">
         <v>585</v>
       </c>
-      <c r="F96" s="11"/>
       <c r="H96" t="s">
         <v>976</v>
       </c>
@@ -19829,11 +19744,9 @@
       <c r="B97" t="s">
         <v>94</v>
       </c>
-      <c r="C97" s="11"/>
       <c r="E97" t="s">
         <v>586</v>
       </c>
-      <c r="F97" s="11"/>
       <c r="H97" t="s">
         <v>975</v>
       </c>
@@ -19866,11 +19779,10 @@
       <c r="B98" t="s">
         <v>95</v>
       </c>
-      <c r="C98" s="11"/>
       <c r="E98" t="s">
         <v>587</v>
       </c>
-      <c r="F98" s="11" t="s">
+      <c r="F98" t="s">
         <v>1053</v>
       </c>
       <c r="H98" t="s">
@@ -19902,11 +19814,10 @@
       <c r="B99" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="11"/>
       <c r="E99" t="s">
         <v>588</v>
       </c>
-      <c r="F99" s="11" t="s">
+      <c r="F99" t="s">
         <v>1365</v>
       </c>
       <c r="H99" t="s">
@@ -19932,11 +19843,9 @@
       <c r="B100" t="s">
         <v>97</v>
       </c>
-      <c r="C100" s="11"/>
       <c r="E100" t="s">
         <v>589</v>
       </c>
-      <c r="F100" s="11"/>
       <c r="H100" t="s">
         <v>977</v>
       </c>
@@ -19963,11 +19872,9 @@
       <c r="B101" t="s">
         <v>98</v>
       </c>
-      <c r="C101" s="11"/>
       <c r="E101" t="s">
         <v>590</v>
       </c>
-      <c r="F101" s="11"/>
       <c r="H101" t="s">
         <v>978</v>
       </c>
@@ -19997,11 +19904,9 @@
       <c r="B102" t="s">
         <v>99</v>
       </c>
-      <c r="C102" s="11"/>
       <c r="E102" t="s">
         <v>591</v>
       </c>
-      <c r="F102" s="11"/>
       <c r="H102" t="s">
         <v>980</v>
       </c>
@@ -20031,11 +19936,9 @@
       <c r="B103" t="s">
         <v>100</v>
       </c>
-      <c r="C103" s="11"/>
       <c r="E103" t="s">
         <v>592</v>
       </c>
-      <c r="F103" s="11"/>
       <c r="H103" t="s">
         <v>981</v>
       </c>
@@ -20059,13 +19962,12 @@
       <c r="B104" t="s">
         <v>489</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" t="s">
         <v>920</v>
       </c>
       <c r="E104" t="s">
         <v>593</v>
       </c>
-      <c r="F104" s="11"/>
       <c r="H104" t="s">
         <v>982</v>
       </c>
@@ -20092,11 +19994,10 @@
       <c r="B105" t="s">
         <v>101</v>
       </c>
-      <c r="C105" s="11"/>
       <c r="E105" t="s">
         <v>594</v>
       </c>
-      <c r="F105" s="11" t="s">
+      <c r="F105" t="s">
         <v>983</v>
       </c>
       <c r="I105" t="s">
@@ -20119,15 +20020,14 @@
       <c r="B106" t="s">
         <v>102</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C106" t="s">
         <v>990</v>
       </c>
       <c r="E106" t="s">
         <v>595</v>
       </c>
-      <c r="F106" s="11"/>
       <c r="G106" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="I106" t="s">
         <v>1397</v>
@@ -20158,17 +20058,17 @@
       <c r="B107" t="s">
         <v>103</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" t="s">
         <v>984</v>
       </c>
       <c r="E107" t="s">
         <v>596</v>
       </c>
-      <c r="F107" s="11" t="s">
+      <c r="F107" t="s">
         <v>1425</v>
       </c>
       <c r="G107" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="I107" t="s">
         <v>844</v>
@@ -20199,13 +20099,12 @@
       <c r="B108" t="s">
         <v>104</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" t="s">
         <v>985</v>
       </c>
       <c r="E108" t="s">
         <v>571</v>
       </c>
-      <c r="F108" s="11"/>
       <c r="I108" t="s">
         <v>844</v>
       </c>
@@ -20235,17 +20134,17 @@
       <c r="B109" t="s">
         <v>432</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" t="s">
         <v>789</v>
       </c>
       <c r="D109" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E109" t="s">
         <v>598</v>
       </c>
-      <c r="F109" s="11" t="s">
-        <v>1442</v>
+      <c r="F109" t="s">
+        <v>1441</v>
       </c>
       <c r="I109" t="s">
         <v>1397</v>
@@ -20270,16 +20169,15 @@
       <c r="B110" t="s">
         <v>105</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" t="s">
         <v>986</v>
       </c>
       <c r="D110" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="E110" t="s">
         <v>599</v>
       </c>
-      <c r="F110" s="11"/>
       <c r="I110" t="s">
         <v>888</v>
       </c>
@@ -20303,14 +20201,14 @@
       <c r="B111" t="s">
         <v>823</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" t="s">
         <v>822</v>
       </c>
       <c r="E111" t="s">
         <v>600</v>
       </c>
-      <c r="F111" s="11" t="s">
-        <v>1431</v>
+      <c r="F111" t="s">
+        <v>1430</v>
       </c>
       <c r="I111" t="s">
         <v>844</v>
@@ -20341,15 +20239,14 @@
       <c r="B112" t="s">
         <v>106</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" t="s">
         <v>886</v>
       </c>
       <c r="E112" t="s">
         <v>601</v>
       </c>
-      <c r="F112" s="11"/>
       <c r="G112" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="I112" t="s">
         <v>844</v>
@@ -20380,15 +20277,14 @@
       <c r="B113" t="s">
         <v>107</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" t="s">
         <v>914</v>
       </c>
       <c r="E113" t="s">
         <v>602</v>
       </c>
-      <c r="F113" s="11"/>
       <c r="G113" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="I113" t="s">
         <v>850</v>
@@ -20413,17 +20309,17 @@
       <c r="B114" t="s">
         <v>603</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" t="s">
         <v>921</v>
       </c>
       <c r="E114" t="s">
         <v>604</v>
       </c>
-      <c r="F114" s="11" t="s">
-        <v>1482</v>
+      <c r="F114" t="s">
+        <v>1481</v>
       </c>
       <c r="G114" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="I114" t="s">
         <v>1397</v>
@@ -20448,13 +20344,13 @@
       <c r="B115" t="s">
         <v>108</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" t="s">
         <v>1393</v>
       </c>
       <c r="E115" t="s">
         <v>605</v>
       </c>
-      <c r="F115" s="11" t="s">
+      <c r="F115" t="s">
         <v>1394</v>
       </c>
       <c r="I115" t="s">
@@ -20483,17 +20379,17 @@
       <c r="B116" t="s">
         <v>109</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" t="s">
         <v>987</v>
       </c>
       <c r="E116" t="s">
         <v>606</v>
       </c>
-      <c r="F116" s="11" t="s">
-        <v>1540</v>
+      <c r="F116" t="s">
+        <v>1538</v>
       </c>
       <c r="G116" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="I116" t="s">
         <v>844</v>
@@ -20518,13 +20414,13 @@
       <c r="B117" t="s">
         <v>110</v>
       </c>
-      <c r="C117" s="11" t="s">
-        <v>988</v>
+      <c r="C117" t="s">
+        <v>1600</v>
       </c>
       <c r="E117" t="s">
         <v>597</v>
       </c>
-      <c r="F117" s="11" t="s">
+      <c r="F117" t="s">
         <v>1418</v>
       </c>
       <c r="I117" t="s">
@@ -20550,13 +20446,13 @@
       <c r="B118" t="s">
         <v>111</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" t="s">
         <v>989</v>
       </c>
       <c r="E118" t="s">
         <v>607</v>
       </c>
-      <c r="F118" s="11" t="s">
+      <c r="F118" t="s">
         <v>1426</v>
       </c>
       <c r="I118" t="s">
@@ -20585,14 +20481,14 @@
       <c r="B119" t="s">
         <v>112</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" t="s">
         <v>991</v>
       </c>
       <c r="E119" t="s">
         <v>608</v>
       </c>
-      <c r="F119" s="11" t="s">
-        <v>1569</v>
+      <c r="F119" t="s">
+        <v>1567</v>
       </c>
       <c r="I119" t="s">
         <v>888</v>
@@ -20620,13 +20516,12 @@
       <c r="B120" t="s">
         <v>113</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" t="s">
         <v>992</v>
       </c>
       <c r="E120" t="s">
         <v>609</v>
       </c>
-      <c r="F120" s="11"/>
       <c r="I120" t="s">
         <v>888</v>
       </c>
@@ -20650,11 +20545,9 @@
       <c r="B121" t="s">
         <v>114</v>
       </c>
-      <c r="C121" s="11"/>
       <c r="E121" t="s">
         <v>610</v>
       </c>
-      <c r="F121" s="11"/>
       <c r="H121" t="s">
         <v>994</v>
       </c>
@@ -20684,11 +20577,9 @@
       <c r="B122" t="s">
         <v>115</v>
       </c>
-      <c r="C122" s="11"/>
       <c r="E122" t="s">
         <v>611</v>
       </c>
-      <c r="F122" s="11"/>
       <c r="H122" t="s">
         <v>995</v>
       </c>
@@ -20712,11 +20603,9 @@
       <c r="B123" t="s">
         <v>116</v>
       </c>
-      <c r="C123" s="11"/>
       <c r="E123" t="s">
         <v>612</v>
       </c>
-      <c r="F123" s="11"/>
       <c r="H123" t="s">
         <v>998</v>
       </c>
@@ -20743,11 +20632,9 @@
       <c r="B124" t="s">
         <v>117</v>
       </c>
-      <c r="C124" s="11"/>
       <c r="E124" t="s">
         <v>613</v>
       </c>
-      <c r="F124" s="11"/>
       <c r="H124" t="s">
         <v>1340</v>
       </c>
@@ -20774,12 +20661,11 @@
       <c r="B125" t="s">
         <v>118</v>
       </c>
-      <c r="C125" s="11"/>
       <c r="E125" t="s">
         <v>614</v>
       </c>
-      <c r="F125" s="11" t="s">
-        <v>1577</v>
+      <c r="F125" t="s">
+        <v>1575</v>
       </c>
       <c r="G125" t="s">
         <v>1010</v>
@@ -20813,15 +20699,14 @@
       <c r="B126" t="s">
         <v>119</v>
       </c>
-      <c r="C126" s="11"/>
       <c r="E126" t="s">
         <v>615</v>
       </c>
-      <c r="F126" s="11" t="s">
-        <v>1559</v>
+      <c r="F126" t="s">
+        <v>1557</v>
       </c>
       <c r="G126" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="I126" t="s">
         <v>844</v>
@@ -20846,11 +20731,9 @@
       <c r="B127" t="s">
         <v>120</v>
       </c>
-      <c r="C127" s="11"/>
       <c r="E127" t="s">
         <v>616</v>
       </c>
-      <c r="F127" s="11"/>
       <c r="H127" t="s">
         <v>1006</v>
       </c>
@@ -20883,20 +20766,20 @@
       <c r="B128" t="s">
         <v>121</v>
       </c>
-      <c r="C128" s="11" t="s">
-        <v>1436</v>
+      <c r="C128" t="s">
+        <v>1435</v>
       </c>
       <c r="D128" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="E128" t="s">
         <v>617</v>
       </c>
-      <c r="F128" s="11" t="s">
-        <v>1437</v>
+      <c r="F128" t="s">
+        <v>1436</v>
       </c>
       <c r="G128" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H128" t="s">
         <v>1008</v>
@@ -20921,12 +20804,11 @@
       <c r="B129" t="s">
         <v>122</v>
       </c>
-      <c r="C129" s="11"/>
       <c r="E129" t="s">
         <v>618</v>
       </c>
-      <c r="F129" s="11" t="s">
-        <v>1578</v>
+      <c r="F129" t="s">
+        <v>1576</v>
       </c>
       <c r="H129" t="s">
         <v>1013</v>
@@ -20957,12 +20839,11 @@
       <c r="B130" t="s">
         <v>123</v>
       </c>
-      <c r="C130" s="11"/>
       <c r="E130" t="s">
         <v>619</v>
       </c>
-      <c r="F130" s="11" t="s">
-        <v>1456</v>
+      <c r="F130" t="s">
+        <v>1455</v>
       </c>
       <c r="H130" t="s">
         <v>1058</v>
@@ -20990,11 +20871,9 @@
       <c r="B131" t="s">
         <v>124</v>
       </c>
-      <c r="C131" s="11"/>
       <c r="E131" t="s">
         <v>620</v>
       </c>
-      <c r="F131" s="11"/>
       <c r="H131" t="s">
         <v>1015</v>
       </c>
@@ -21018,11 +20897,9 @@
       <c r="B132" t="s">
         <v>125</v>
       </c>
-      <c r="C132" s="11"/>
       <c r="E132" t="s">
         <v>621</v>
       </c>
-      <c r="F132" s="11"/>
       <c r="H132" t="s">
         <v>1016</v>
       </c>
@@ -21052,12 +20929,11 @@
       <c r="B133" t="s">
         <v>126</v>
       </c>
-      <c r="C133" s="11"/>
       <c r="E133" t="s">
         <v>622</v>
       </c>
-      <c r="F133" s="11" t="s">
-        <v>1432</v>
+      <c r="F133" t="s">
+        <v>1431</v>
       </c>
       <c r="H133" t="s">
         <v>1018</v>
@@ -21088,11 +20964,9 @@
       <c r="B134" t="s">
         <v>127</v>
       </c>
-      <c r="C134" s="11"/>
       <c r="E134" t="s">
         <v>623</v>
       </c>
-      <c r="F134" s="11"/>
       <c r="H134" t="s">
         <v>1019</v>
       </c>
@@ -21122,14 +20996,14 @@
       <c r="B135" t="s">
         <v>128</v>
       </c>
-      <c r="C135" s="11" t="s">
-        <v>1585</v>
+      <c r="C135" t="s">
+        <v>1582</v>
       </c>
       <c r="E135" t="s">
         <v>624</v>
       </c>
-      <c r="F135" s="11" t="s">
-        <v>1486</v>
+      <c r="F135" t="s">
+        <v>1485</v>
       </c>
       <c r="H135" t="s">
         <v>1021</v>
@@ -21160,11 +21034,9 @@
       <c r="B136" t="s">
         <v>129</v>
       </c>
-      <c r="C136" s="11"/>
       <c r="E136" t="s">
         <v>625</v>
       </c>
-      <c r="F136" s="11"/>
       <c r="H136" t="s">
         <v>1049</v>
       </c>
@@ -21188,11 +21060,9 @@
       <c r="B137" t="s">
         <v>130</v>
       </c>
-      <c r="C137" s="11"/>
       <c r="E137" t="s">
         <v>130</v>
       </c>
-      <c r="F137" s="11"/>
       <c r="H137" t="s">
         <v>1024</v>
       </c>
@@ -21216,11 +21086,9 @@
       <c r="B138" t="s">
         <v>131</v>
       </c>
-      <c r="C138" s="11"/>
       <c r="E138" t="s">
         <v>131</v>
       </c>
-      <c r="F138" s="11"/>
       <c r="H138" t="s">
         <v>975</v>
       </c>
@@ -21253,13 +21121,13 @@
       <c r="B139" t="s">
         <v>132</v>
       </c>
-      <c r="C139" s="11" t="s">
+      <c r="C139" t="s">
         <v>1029</v>
       </c>
       <c r="E139" t="s">
         <v>627</v>
       </c>
-      <c r="F139" s="11" t="s">
+      <c r="F139" t="s">
         <v>1028</v>
       </c>
       <c r="H139" t="s">
@@ -21285,12 +21153,11 @@
       <c r="B140" t="s">
         <v>133</v>
       </c>
-      <c r="C140" s="11"/>
       <c r="E140" t="s">
         <v>628</v>
       </c>
-      <c r="F140" s="11" t="s">
-        <v>1591</v>
+      <c r="F140" t="s">
+        <v>1588</v>
       </c>
       <c r="I140" t="s">
         <v>1402</v>
@@ -21309,16 +21176,14 @@
       <c r="B141" t="s">
         <v>134</v>
       </c>
-      <c r="C141" s="11"/>
       <c r="D141" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="E141" t="s">
         <v>629</v>
       </c>
-      <c r="F141" s="11"/>
       <c r="G141" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="H141" t="s">
         <v>1027</v>
@@ -21349,13 +21214,12 @@
       <c r="B142" t="s">
         <v>335</v>
       </c>
-      <c r="C142" s="11" t="s">
-        <v>1476</v>
+      <c r="C142" t="s">
+        <v>1475</v>
       </c>
       <c r="E142" t="s">
         <v>630</v>
       </c>
-      <c r="F142" s="11"/>
       <c r="H142" t="s">
         <v>1047</v>
       </c>
@@ -21385,12 +21249,11 @@
       <c r="B143" t="s">
         <v>135</v>
       </c>
-      <c r="C143" s="11"/>
       <c r="E143" t="s">
         <v>631</v>
       </c>
-      <c r="F143" s="11" t="s">
-        <v>1461</v>
+      <c r="F143" t="s">
+        <v>1460</v>
       </c>
       <c r="I143" t="s">
         <v>1349</v>
@@ -21418,13 +21281,12 @@
       <c r="B144" t="s">
         <v>136</v>
       </c>
-      <c r="C144" s="11" t="s">
-        <v>1551</v>
+      <c r="C144" t="s">
+        <v>1549</v>
       </c>
       <c r="E144" t="s">
         <v>632</v>
       </c>
-      <c r="F144" s="11"/>
       <c r="H144" t="s">
         <v>1034</v>
       </c>
@@ -21448,11 +21310,10 @@
       <c r="B145" t="s">
         <v>137</v>
       </c>
-      <c r="C145" s="11"/>
       <c r="E145" t="s">
         <v>633</v>
       </c>
-      <c r="F145" s="11" t="s">
+      <c r="F145" t="s">
         <v>1044</v>
       </c>
       <c r="I145" t="s">
@@ -21478,11 +21339,9 @@
       <c r="B146" t="s">
         <v>138</v>
       </c>
-      <c r="C146" s="11"/>
       <c r="E146" t="s">
         <v>634</v>
       </c>
-      <c r="F146" s="11"/>
       <c r="H146" t="s">
         <v>1050</v>
       </c>
@@ -21512,15 +21371,14 @@
       <c r="B147" t="s">
         <v>139</v>
       </c>
-      <c r="C147" s="11"/>
       <c r="E147" t="s">
         <v>635</v>
       </c>
-      <c r="F147" s="11" t="s">
+      <c r="F147" t="s">
         <v>1045</v>
       </c>
       <c r="G147" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="I147" t="s">
         <v>1117</v>
@@ -21545,12 +21403,11 @@
       <c r="B148" t="s">
         <v>140</v>
       </c>
-      <c r="C148" s="11"/>
       <c r="E148" t="s">
         <v>636</v>
       </c>
-      <c r="F148" s="11" t="s">
-        <v>1471</v>
+      <c r="F148" t="s">
+        <v>1470</v>
       </c>
       <c r="H148" t="s">
         <v>1036</v>
@@ -21581,14 +21438,14 @@
       <c r="B149" t="s">
         <v>141</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>1587</v>
+      <c r="C149" t="s">
+        <v>1584</v>
       </c>
       <c r="E149" t="s">
         <v>637</v>
       </c>
-      <c r="F149" s="11" t="s">
-        <v>1470</v>
+      <c r="F149" t="s">
+        <v>1469</v>
       </c>
       <c r="I149" t="s">
         <v>1402</v>
@@ -21610,17 +21467,17 @@
       <c r="B150" t="s">
         <v>142</v>
       </c>
-      <c r="C150" s="11" t="s">
-        <v>1481</v>
+      <c r="C150" t="s">
+        <v>1480</v>
       </c>
       <c r="E150" t="s">
         <v>638</v>
       </c>
-      <c r="F150" s="11" t="s">
-        <v>1560</v>
+      <c r="F150" t="s">
+        <v>1558</v>
       </c>
       <c r="G150" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="I150" t="s">
         <v>1402</v>
@@ -21648,13 +21505,13 @@
       <c r="B151" t="s">
         <v>143</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" t="s">
         <v>1051</v>
       </c>
       <c r="E151" t="s">
         <v>639</v>
       </c>
-      <c r="F151" s="11" t="s">
+      <c r="F151" t="s">
         <v>143</v>
       </c>
       <c r="H151" t="s">
@@ -21683,15 +21540,14 @@
       <c r="B152" t="s">
         <v>144</v>
       </c>
-      <c r="C152" s="11"/>
       <c r="E152" t="s">
         <v>641</v>
       </c>
-      <c r="F152" s="11" t="s">
-        <v>1575</v>
+      <c r="F152" t="s">
+        <v>1573</v>
       </c>
       <c r="G152" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H152" t="s">
         <v>1039</v>
@@ -21719,11 +21575,10 @@
       <c r="B153" t="s">
         <v>145</v>
       </c>
-      <c r="C153" s="11"/>
       <c r="E153" t="s">
         <v>643</v>
       </c>
-      <c r="F153" s="11" t="s">
+      <c r="F153" t="s">
         <v>1043</v>
       </c>
       <c r="H153" t="s">
@@ -21755,11 +21610,9 @@
       <c r="B154" t="s">
         <v>146</v>
       </c>
-      <c r="C154" s="11"/>
       <c r="E154" t="s">
         <v>644</v>
       </c>
-      <c r="F154" s="11"/>
       <c r="H154" t="s">
         <v>1197</v>
       </c>
@@ -21786,12 +21639,11 @@
       <c r="B155" t="s">
         <v>147</v>
       </c>
-      <c r="C155" s="11"/>
       <c r="E155" t="s">
         <v>645</v>
       </c>
-      <c r="F155" s="11" t="s">
-        <v>1541</v>
+      <c r="F155" t="s">
+        <v>1539</v>
       </c>
       <c r="I155" t="s">
         <v>1117</v>
@@ -21816,11 +21668,9 @@
       <c r="B156" t="s">
         <v>148</v>
       </c>
-      <c r="C156" s="11"/>
       <c r="E156" t="s">
         <v>646</v>
       </c>
-      <c r="F156" s="11"/>
       <c r="H156" t="s">
         <v>1059</v>
       </c>
@@ -21847,17 +21697,17 @@
       <c r="B157" t="s">
         <v>795</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="C157" t="s">
         <v>1295</v>
       </c>
       <c r="E157" t="s">
         <v>523</v>
       </c>
-      <c r="F157" s="11" t="s">
+      <c r="F157" t="s">
         <v>1427</v>
       </c>
       <c r="G157" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H157" t="s">
         <v>835</v>
@@ -21888,17 +21738,17 @@
       <c r="B158" t="s">
         <v>149</v>
       </c>
-      <c r="C158" s="11" t="s">
+      <c r="C158" t="s">
         <v>1420</v>
       </c>
       <c r="E158" t="s">
         <v>647</v>
       </c>
-      <c r="F158" s="11" t="s">
-        <v>1443</v>
+      <c r="F158" t="s">
+        <v>1442</v>
       </c>
       <c r="G158" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H158" t="s">
         <v>1065</v>
@@ -21926,14 +21776,14 @@
       <c r="B159" t="s">
         <v>150</v>
       </c>
-      <c r="C159" s="11" t="s">
-        <v>1552</v>
+      <c r="C159" t="s">
+        <v>1550</v>
       </c>
       <c r="E159" t="s">
         <v>648</v>
       </c>
-      <c r="F159" s="11" t="s">
-        <v>1489</v>
+      <c r="F159" t="s">
+        <v>1488</v>
       </c>
       <c r="I159" t="s">
         <v>844</v>
@@ -21961,12 +21811,11 @@
       <c r="B160" t="s">
         <v>151</v>
       </c>
-      <c r="C160" s="11"/>
       <c r="E160" t="s">
         <v>649</v>
       </c>
-      <c r="F160" s="11" t="s">
-        <v>1525</v>
+      <c r="F160" t="s">
+        <v>1524</v>
       </c>
       <c r="H160" t="s">
         <v>1061</v>
@@ -21997,12 +21846,11 @@
       <c r="B161" t="s">
         <v>152</v>
       </c>
-      <c r="C161" s="11"/>
       <c r="E161" t="s">
         <v>650</v>
       </c>
-      <c r="F161" s="11" t="s">
-        <v>1484</v>
+      <c r="F161" t="s">
+        <v>1483</v>
       </c>
       <c r="H161" t="s">
         <v>1062</v>
@@ -22030,15 +21878,14 @@
       <c r="B162" t="s">
         <v>153</v>
       </c>
-      <c r="C162" s="11"/>
       <c r="E162" t="s">
         <v>651</v>
       </c>
-      <c r="F162" s="11" t="s">
-        <v>1572</v>
+      <c r="F162" t="s">
+        <v>1570</v>
       </c>
       <c r="G162" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H162" t="s">
         <v>1064</v>
@@ -22069,15 +21916,14 @@
       <c r="B163" t="s">
         <v>154</v>
       </c>
-      <c r="C163" s="11"/>
       <c r="E163" t="s">
         <v>652</v>
       </c>
-      <c r="F163" s="11" t="s">
-        <v>1458</v>
+      <c r="F163" t="s">
+        <v>1457</v>
       </c>
       <c r="G163" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H163" t="s">
         <v>1070</v>
@@ -22102,15 +21948,14 @@
       <c r="B164" t="s">
         <v>155</v>
       </c>
-      <c r="C164" s="11"/>
       <c r="D164" t="s">
-        <v>1583</v>
+        <v>1603</v>
       </c>
       <c r="E164" t="s">
         <v>653</v>
       </c>
-      <c r="F164" s="11" t="s">
-        <v>1582</v>
+      <c r="F164" t="s">
+        <v>1580</v>
       </c>
       <c r="I164" t="s">
         <v>844</v>
@@ -22141,11 +21986,9 @@
       <c r="B165" t="s">
         <v>156</v>
       </c>
-      <c r="C165" s="11"/>
       <c r="E165" t="s">
         <v>654</v>
       </c>
-      <c r="F165" s="11"/>
       <c r="H165" t="s">
         <v>1072</v>
       </c>
@@ -22169,14 +22012,14 @@
       <c r="B166" t="s">
         <v>157</v>
       </c>
-      <c r="C166" s="11" t="s">
+      <c r="C166" t="s">
         <v>1081</v>
       </c>
       <c r="E166" t="s">
         <v>655</v>
       </c>
-      <c r="F166" s="11" t="s">
-        <v>1488</v>
+      <c r="F166" t="s">
+        <v>1487</v>
       </c>
       <c r="I166" t="s">
         <v>844</v>
@@ -22207,11 +22050,9 @@
       <c r="B167" t="s">
         <v>158</v>
       </c>
-      <c r="C167" s="11"/>
       <c r="E167" t="s">
         <v>656</v>
       </c>
-      <c r="F167" s="11"/>
       <c r="I167" t="s">
         <v>844</v>
       </c>
@@ -22238,13 +22079,12 @@
       <c r="B168" t="s">
         <v>159</v>
       </c>
-      <c r="C168" s="11" t="s">
-        <v>1472</v>
+      <c r="C168" t="s">
+        <v>1471</v>
       </c>
       <c r="E168" t="s">
         <v>658</v>
       </c>
-      <c r="F168" s="11"/>
       <c r="H168" t="s">
         <v>1334</v>
       </c>
@@ -22268,13 +22108,12 @@
       <c r="B169" t="s">
         <v>1079</v>
       </c>
-      <c r="C169" s="11" t="s">
+      <c r="C169" t="s">
         <v>1292</v>
       </c>
       <c r="E169" t="s">
         <v>657</v>
       </c>
-      <c r="F169" s="11"/>
       <c r="H169" t="s">
         <v>1082</v>
       </c>
@@ -22298,12 +22137,11 @@
       <c r="B170" t="s">
         <v>160</v>
       </c>
-      <c r="C170" s="11"/>
       <c r="E170" t="s">
         <v>659</v>
       </c>
-      <c r="F170" s="11" t="s">
-        <v>1542</v>
+      <c r="F170" t="s">
+        <v>1540</v>
       </c>
       <c r="H170" t="s">
         <v>1083</v>
@@ -22334,15 +22172,14 @@
       <c r="B171" t="s">
         <v>161</v>
       </c>
-      <c r="C171" s="11"/>
       <c r="E171" t="s">
         <v>660</v>
       </c>
-      <c r="F171" s="11" t="s">
-        <v>1543</v>
+      <c r="F171" t="s">
+        <v>1541</v>
       </c>
       <c r="G171" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="I171" t="s">
         <v>844</v>
@@ -22370,12 +22207,11 @@
       <c r="B172" t="s">
         <v>162</v>
       </c>
-      <c r="C172" s="11"/>
       <c r="E172" t="s">
         <v>661</v>
       </c>
-      <c r="F172" s="11" t="s">
-        <v>1454</v>
+      <c r="F172" t="s">
+        <v>1453</v>
       </c>
       <c r="H172" t="s">
         <v>1342</v>
@@ -22403,11 +22239,10 @@
       <c r="B173" t="s">
         <v>163</v>
       </c>
-      <c r="C173" s="11"/>
       <c r="E173" t="s">
         <v>163</v>
       </c>
-      <c r="F173" s="11" t="s">
+      <c r="F173" t="s">
         <v>1119</v>
       </c>
       <c r="H173" t="s">
@@ -22439,14 +22274,14 @@
       <c r="B174" t="s">
         <v>164</v>
       </c>
-      <c r="C174" s="11" t="s">
+      <c r="C174" t="s">
         <v>1089</v>
       </c>
       <c r="E174" t="s">
         <v>662</v>
       </c>
-      <c r="F174" s="11" t="s">
-        <v>1570</v>
+      <c r="F174" t="s">
+        <v>1568</v>
       </c>
       <c r="H174" t="s">
         <v>1088</v>
@@ -22477,11 +22312,10 @@
       <c r="B175" t="s">
         <v>165</v>
       </c>
-      <c r="C175" s="11"/>
       <c r="E175" t="s">
         <v>663</v>
       </c>
-      <c r="F175" s="11" t="s">
+      <c r="F175" t="s">
         <v>1419</v>
       </c>
       <c r="H175" t="s">
@@ -22510,11 +22344,9 @@
       <c r="B176" t="s">
         <v>166</v>
       </c>
-      <c r="C176" s="11"/>
       <c r="E176" t="s">
         <v>664</v>
       </c>
-      <c r="F176" s="11"/>
       <c r="H176" t="s">
         <v>1093</v>
       </c>
@@ -22538,14 +22370,14 @@
       <c r="B177" t="s">
         <v>167</v>
       </c>
-      <c r="C177" s="11" t="s">
+      <c r="C177" t="s">
         <v>1389</v>
       </c>
       <c r="E177" t="s">
         <v>665</v>
       </c>
-      <c r="F177" s="11" t="s">
-        <v>1580</v>
+      <c r="F177" t="s">
+        <v>1578</v>
       </c>
       <c r="I177" t="s">
         <v>844</v>
@@ -22573,11 +22405,9 @@
       <c r="B178" t="s">
         <v>168</v>
       </c>
-      <c r="C178" s="11"/>
       <c r="E178" t="s">
         <v>666</v>
       </c>
-      <c r="F178" s="11"/>
       <c r="H178" t="s">
         <v>1337</v>
       </c>
@@ -22601,11 +22431,9 @@
       <c r="B179" t="s">
         <v>169</v>
       </c>
-      <c r="C179" s="11"/>
       <c r="E179" t="s">
         <v>667</v>
       </c>
-      <c r="F179" s="11"/>
       <c r="I179" t="s">
         <v>888</v>
       </c>
@@ -22635,11 +22463,9 @@
       <c r="B180" t="s">
         <v>170</v>
       </c>
-      <c r="C180" s="11"/>
       <c r="E180" t="s">
         <v>668</v>
       </c>
-      <c r="F180" s="11"/>
       <c r="H180" t="s">
         <v>938</v>
       </c>
@@ -22666,13 +22492,12 @@
       <c r="B181" t="s">
         <v>171</v>
       </c>
-      <c r="C181" s="11" t="s">
+      <c r="C181" t="s">
         <v>1293</v>
       </c>
       <c r="E181" t="s">
         <v>669</v>
       </c>
-      <c r="F181" s="11"/>
       <c r="H181" t="s">
         <v>1095</v>
       </c>
@@ -22696,11 +22521,9 @@
       <c r="B182" t="s">
         <v>172</v>
       </c>
-      <c r="C182" s="11"/>
       <c r="E182" t="s">
         <v>670</v>
       </c>
-      <c r="F182" s="11"/>
       <c r="H182" t="s">
         <v>831</v>
       </c>
@@ -22721,13 +22544,12 @@
       <c r="B183" t="s">
         <v>173</v>
       </c>
-      <c r="C183" s="11" t="s">
+      <c r="C183" t="s">
         <v>1294</v>
       </c>
       <c r="E183" t="s">
         <v>589</v>
       </c>
-      <c r="F183" s="11"/>
       <c r="H183" t="s">
         <v>982</v>
       </c>
@@ -22751,13 +22573,12 @@
       <c r="B184" t="s">
         <v>174</v>
       </c>
-      <c r="C184" s="11" t="s">
+      <c r="C184" t="s">
         <v>1100</v>
       </c>
       <c r="E184" t="s">
         <v>672</v>
       </c>
-      <c r="F184" s="11"/>
       <c r="H184" t="s">
         <v>1101</v>
       </c>
@@ -22787,13 +22608,12 @@
       <c r="B185" t="s">
         <v>1103</v>
       </c>
-      <c r="C185" s="11" t="s">
+      <c r="C185" t="s">
         <v>1104</v>
       </c>
       <c r="E185" t="s">
         <v>673</v>
       </c>
-      <c r="F185" s="11"/>
       <c r="H185" t="s">
         <v>1105</v>
       </c>
@@ -22823,13 +22643,13 @@
       <c r="B186" t="s">
         <v>1202</v>
       </c>
-      <c r="C186" s="11" t="s">
+      <c r="C186" t="s">
         <v>1396</v>
       </c>
       <c r="E186" t="s">
         <v>688</v>
       </c>
-      <c r="F186" s="11" t="s">
+      <c r="F186" t="s">
         <v>187</v>
       </c>
       <c r="H186" t="s">
@@ -22858,13 +22678,12 @@
       <c r="B187" t="s">
         <v>175</v>
       </c>
-      <c r="C187" s="11" t="s">
+      <c r="C187" t="s">
         <v>1106</v>
       </c>
       <c r="E187" t="s">
         <v>674</v>
       </c>
-      <c r="F187" s="11"/>
       <c r="H187" t="s">
         <v>1107</v>
       </c>
@@ -22888,17 +22707,17 @@
       <c r="B188" t="s">
         <v>176</v>
       </c>
-      <c r="C188" s="11" t="s">
+      <c r="C188" t="s">
         <v>1108</v>
       </c>
       <c r="E188" t="s">
         <v>675</v>
       </c>
-      <c r="F188" s="11" t="s">
+      <c r="F188" t="s">
         <v>1109</v>
       </c>
       <c r="G188" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="I188" t="s">
         <v>1402</v>
@@ -22920,11 +22739,9 @@
       <c r="B189" t="s">
         <v>177</v>
       </c>
-      <c r="C189" s="11"/>
       <c r="E189" t="s">
         <v>676</v>
       </c>
-      <c r="F189" s="11"/>
       <c r="H189" t="s">
         <v>1111</v>
       </c>
@@ -22948,12 +22765,11 @@
       <c r="B190" t="s">
         <v>178</v>
       </c>
-      <c r="C190" s="11"/>
       <c r="E190" t="s">
         <v>677</v>
       </c>
-      <c r="F190" s="11" t="s">
-        <v>1574</v>
+      <c r="F190" t="s">
+        <v>1572</v>
       </c>
       <c r="H190" t="s">
         <v>1112</v>
@@ -22984,11 +22800,9 @@
       <c r="B191" t="s">
         <v>179</v>
       </c>
-      <c r="C191" s="11"/>
       <c r="E191" t="s">
         <v>678</v>
       </c>
-      <c r="F191" s="11"/>
       <c r="H191" t="s">
         <v>1114</v>
       </c>
@@ -23012,12 +22826,11 @@
       <c r="B192" t="s">
         <v>486</v>
       </c>
-      <c r="C192" s="11"/>
       <c r="E192" t="s">
         <v>679</v>
       </c>
-      <c r="F192" s="11" t="s">
-        <v>1448</v>
+      <c r="F192" t="s">
+        <v>1447</v>
       </c>
       <c r="I192" t="s">
         <v>1117</v>
@@ -23048,17 +22861,17 @@
       <c r="B193" t="s">
         <v>180</v>
       </c>
-      <c r="C193" s="11" t="s">
-        <v>1445</v>
+      <c r="C193" t="s">
+        <v>1444</v>
       </c>
       <c r="E193" t="s">
         <v>680</v>
       </c>
-      <c r="F193" s="11" t="s">
-        <v>1466</v>
+      <c r="F193" t="s">
+        <v>1465</v>
       </c>
       <c r="G193" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="H193" t="s">
         <v>1118</v>
@@ -23092,14 +22905,14 @@
       <c r="B194" t="s">
         <v>181</v>
       </c>
-      <c r="C194" s="11" t="s">
-        <v>1561</v>
+      <c r="C194" t="s">
+        <v>1559</v>
       </c>
       <c r="E194" t="s">
         <v>681</v>
       </c>
-      <c r="F194" s="11" t="s">
-        <v>1567</v>
+      <c r="F194" t="s">
+        <v>1565</v>
       </c>
       <c r="I194" t="s">
         <v>1117</v>
@@ -23127,13 +22940,12 @@
       <c r="B195" t="s">
         <v>739</v>
       </c>
-      <c r="C195" s="11" t="s">
+      <c r="C195" t="s">
         <v>1124</v>
       </c>
       <c r="E195" t="s">
         <v>689</v>
       </c>
-      <c r="F195" s="11"/>
       <c r="I195" t="s">
         <v>1117</v>
       </c>
@@ -23157,14 +22969,14 @@
       <c r="B196" t="s">
         <v>182</v>
       </c>
-      <c r="C196" s="11" t="s">
+      <c r="C196" t="s">
         <v>1213</v>
       </c>
       <c r="E196" t="s">
         <v>682</v>
       </c>
-      <c r="F196" s="11" t="s">
-        <v>1444</v>
+      <c r="F196" t="s">
+        <v>1443</v>
       </c>
       <c r="I196" t="s">
         <v>1117</v>
@@ -23189,13 +23001,12 @@
       <c r="B197" t="s">
         <v>183</v>
       </c>
-      <c r="C197" s="11" t="s">
-        <v>1547</v>
+      <c r="C197" t="s">
+        <v>1545</v>
       </c>
       <c r="E197" t="s">
         <v>683</v>
       </c>
-      <c r="F197" s="11"/>
       <c r="I197" t="s">
         <v>1117</v>
       </c>
@@ -23222,20 +23033,20 @@
       <c r="B198" t="s">
         <v>482</v>
       </c>
-      <c r="C198" s="11" t="s">
-        <v>1128</v>
+      <c r="C198" t="s">
+        <v>1601</v>
       </c>
       <c r="D198" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="E198" t="s">
         <v>684</v>
       </c>
-      <c r="F198" s="11" t="s">
-        <v>1433</v>
+      <c r="F198" t="s">
+        <v>1432</v>
       </c>
       <c r="G198" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="H198" t="s">
         <v>1138</v>
@@ -23266,13 +23077,13 @@
       <c r="B199" t="s">
         <v>184</v>
       </c>
-      <c r="C199" s="11" t="s">
-        <v>1477</v>
+      <c r="C199" t="s">
+        <v>1476</v>
       </c>
       <c r="E199" t="s">
         <v>685</v>
       </c>
-      <c r="F199" s="11" t="s">
+      <c r="F199" t="s">
         <v>1133</v>
       </c>
       <c r="I199" t="s">
@@ -23301,11 +23112,10 @@
       <c r="B200" t="s">
         <v>185</v>
       </c>
-      <c r="C200" s="11"/>
       <c r="E200" t="s">
         <v>686</v>
       </c>
-      <c r="F200" s="11" t="s">
+      <c r="F200" t="s">
         <v>1428</v>
       </c>
       <c r="I200" t="s">
@@ -23334,11 +23144,9 @@
       <c r="B201" t="s">
         <v>186</v>
       </c>
-      <c r="C201" s="11"/>
       <c r="E201" t="s">
         <v>687</v>
       </c>
-      <c r="F201" s="11"/>
       <c r="I201" t="s">
         <v>844</v>
       </c>
@@ -23362,12 +23170,11 @@
       <c r="B202" t="s">
         <v>744</v>
       </c>
-      <c r="C202" s="11"/>
       <c r="E202" t="s">
         <v>738</v>
       </c>
-      <c r="F202" s="11" t="s">
-        <v>1452</v>
+      <c r="F202" t="s">
+        <v>1451</v>
       </c>
       <c r="I202" t="s">
         <v>1404</v>
@@ -23392,14 +23199,14 @@
       <c r="B203" t="s">
         <v>188</v>
       </c>
-      <c r="C203" s="11" t="s">
-        <v>1562</v>
+      <c r="C203" t="s">
+        <v>1560</v>
       </c>
       <c r="E203" t="s">
         <v>690</v>
       </c>
-      <c r="F203" s="11" t="s">
-        <v>1473</v>
+      <c r="F203" t="s">
+        <v>1472</v>
       </c>
       <c r="I203" t="s">
         <v>1350</v>
@@ -23427,11 +23234,9 @@
       <c r="B204" t="s">
         <v>189</v>
       </c>
-      <c r="C204" s="11"/>
       <c r="E204" t="s">
         <v>691</v>
       </c>
-      <c r="F204" s="11"/>
       <c r="H204" t="s">
         <v>926</v>
       </c>
@@ -23458,11 +23263,9 @@
       <c r="B205" t="s">
         <v>190</v>
       </c>
-      <c r="C205" s="11"/>
       <c r="E205" t="s">
         <v>692</v>
       </c>
-      <c r="F205" s="11"/>
       <c r="H205" t="s">
         <v>1300</v>
       </c>
@@ -23492,11 +23295,9 @@
       <c r="B206" t="s">
         <v>191</v>
       </c>
-      <c r="C206" s="11"/>
       <c r="E206" t="s">
         <v>693</v>
       </c>
-      <c r="F206" s="11"/>
       <c r="H206" t="s">
         <v>1134</v>
       </c>
@@ -23523,13 +23324,12 @@
       <c r="B207" t="s">
         <v>192</v>
       </c>
-      <c r="C207" s="11" t="s">
-        <v>1586</v>
+      <c r="C207" t="s">
+        <v>1583</v>
       </c>
       <c r="E207" t="s">
         <v>586</v>
       </c>
-      <c r="F207" s="11"/>
       <c r="I207" t="s">
         <v>1402</v>
       </c>
@@ -23547,11 +23347,9 @@
       <c r="B208" t="s">
         <v>193</v>
       </c>
-      <c r="C208" s="11"/>
       <c r="E208" t="s">
         <v>694</v>
       </c>
-      <c r="F208" s="11"/>
       <c r="H208" t="s">
         <v>1135</v>
       </c>
@@ -23575,11 +23373,9 @@
       <c r="B209" t="s">
         <v>194</v>
       </c>
-      <c r="C209" s="11"/>
       <c r="E209" t="s">
         <v>194</v>
       </c>
-      <c r="F209" s="11"/>
       <c r="H209" t="s">
         <v>1208</v>
       </c>
@@ -23606,14 +23402,14 @@
       <c r="B210" t="s">
         <v>485</v>
       </c>
-      <c r="C210" s="11" t="s">
-        <v>1479</v>
+      <c r="C210" t="s">
+        <v>1478</v>
       </c>
       <c r="E210" t="s">
         <v>513</v>
       </c>
-      <c r="F210" s="11" t="s">
-        <v>1457</v>
+      <c r="F210" t="s">
+        <v>1456</v>
       </c>
       <c r="I210" t="s">
         <v>888</v>
@@ -23644,14 +23440,14 @@
       <c r="B211" t="s">
         <v>195</v>
       </c>
-      <c r="C211" s="11" t="s">
-        <v>1529</v>
+      <c r="C211" t="s">
+        <v>1602</v>
       </c>
       <c r="E211" t="s">
         <v>695</v>
       </c>
-      <c r="F211" s="11" t="s">
-        <v>1434</v>
+      <c r="F211" t="s">
+        <v>1433</v>
       </c>
       <c r="H211" t="s">
         <v>1139</v>
@@ -23682,11 +23478,9 @@
       <c r="B212" t="s">
         <v>196</v>
       </c>
-      <c r="C212" s="11"/>
       <c r="E212" t="s">
         <v>696</v>
       </c>
-      <c r="F212" s="11"/>
       <c r="H212" t="s">
         <v>1140</v>
       </c>
@@ -23716,11 +23510,9 @@
       <c r="B213" t="s">
         <v>197</v>
       </c>
-      <c r="C213" s="11"/>
       <c r="E213" t="s">
         <v>697</v>
       </c>
-      <c r="F213" s="11"/>
       <c r="H213" t="s">
         <v>1142</v>
       </c>
@@ -23747,12 +23539,11 @@
       <c r="B214" t="s">
         <v>198</v>
       </c>
-      <c r="C214" s="11"/>
       <c r="E214" t="s">
         <v>698</v>
       </c>
-      <c r="F214" s="11" t="s">
-        <v>1460</v>
+      <c r="F214" t="s">
+        <v>1459</v>
       </c>
       <c r="H214" t="s">
         <v>1143</v>
@@ -23780,11 +23571,9 @@
       <c r="B215" t="s">
         <v>199</v>
       </c>
-      <c r="C215" s="11"/>
       <c r="E215" t="s">
         <v>699</v>
       </c>
-      <c r="F215" s="11"/>
       <c r="H215" t="s">
         <v>1144</v>
       </c>
@@ -23814,11 +23603,9 @@
       <c r="B216" t="s">
         <v>200</v>
       </c>
-      <c r="C216" s="11"/>
       <c r="E216" t="s">
         <v>700</v>
       </c>
-      <c r="F216" s="11"/>
       <c r="H216" t="s">
         <v>1338</v>
       </c>
@@ -23845,15 +23632,14 @@
       <c r="B217" t="s">
         <v>201</v>
       </c>
-      <c r="C217" s="11"/>
       <c r="E217" t="s">
         <v>701</v>
       </c>
-      <c r="F217" s="11" t="s">
-        <v>1596</v>
+      <c r="F217" t="s">
+        <v>1593</v>
       </c>
       <c r="G217" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="I217" t="s">
         <v>1349</v>
@@ -23878,14 +23664,14 @@
       <c r="B218" t="s">
         <v>740</v>
       </c>
-      <c r="C218" s="11" t="s">
-        <v>1528</v>
+      <c r="C218" t="s">
+        <v>1527</v>
       </c>
       <c r="E218" t="s">
         <v>640</v>
       </c>
-      <c r="F218" s="11" t="s">
-        <v>1563</v>
+      <c r="F218" t="s">
+        <v>1561</v>
       </c>
       <c r="I218" t="s">
         <v>844</v>
@@ -23913,13 +23699,13 @@
       <c r="B219" t="s">
         <v>202</v>
       </c>
-      <c r="C219" s="11" t="s">
+      <c r="C219" t="s">
         <v>1188</v>
       </c>
       <c r="E219" t="s">
         <v>1189</v>
       </c>
-      <c r="F219" s="11" t="s">
+      <c r="F219" t="s">
         <v>702</v>
       </c>
       <c r="H219" t="s">
@@ -23951,11 +23737,10 @@
       <c r="B220" t="s">
         <v>203</v>
       </c>
-      <c r="C220" s="11"/>
       <c r="E220" t="s">
         <v>703</v>
       </c>
-      <c r="F220" s="11" t="s">
+      <c r="F220" t="s">
         <v>1296</v>
       </c>
       <c r="H220" t="s">
@@ -23978,15 +23763,14 @@
       <c r="B221" t="s">
         <v>204</v>
       </c>
-      <c r="C221" s="11"/>
       <c r="E221" t="s">
         <v>704</v>
       </c>
-      <c r="F221" s="11" t="s">
-        <v>1451</v>
+      <c r="F221" t="s">
+        <v>1450</v>
       </c>
       <c r="G221" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="H221" t="s">
         <v>1150</v>
@@ -24014,14 +23798,14 @@
       <c r="B222" t="s">
         <v>205</v>
       </c>
-      <c r="C222" s="11" t="s">
+      <c r="C222" t="s">
         <v>1211</v>
       </c>
       <c r="E222" t="s">
         <v>705</v>
       </c>
-      <c r="F222" s="11" t="s">
-        <v>1429</v>
+      <c r="F222" t="s">
+        <v>1596</v>
       </c>
       <c r="G222" s="10"/>
       <c r="H222" t="s">
@@ -24053,11 +23837,9 @@
       <c r="B223" t="s">
         <v>206</v>
       </c>
-      <c r="C223" s="11"/>
       <c r="E223" t="s">
         <v>706</v>
       </c>
-      <c r="F223" s="11"/>
       <c r="H223" t="s">
         <v>1153</v>
       </c>
@@ -24087,11 +23869,9 @@
       <c r="B224" t="s">
         <v>207</v>
       </c>
-      <c r="C224" s="11"/>
       <c r="E224" t="s">
         <v>707</v>
       </c>
-      <c r="F224" s="11"/>
       <c r="H224" t="s">
         <v>1154</v>
       </c>
@@ -24115,11 +23895,9 @@
       <c r="B225" t="s">
         <v>208</v>
       </c>
-      <c r="C225" s="11"/>
       <c r="E225" t="s">
         <v>708</v>
       </c>
-      <c r="F225" s="11"/>
       <c r="H225" t="s">
         <v>1155</v>
       </c>
@@ -24149,15 +23927,14 @@
       <c r="B226" t="s">
         <v>209</v>
       </c>
-      <c r="C226" s="11"/>
       <c r="E226" t="s">
         <v>710</v>
       </c>
-      <c r="F226" s="11" t="s">
-        <v>1576</v>
+      <c r="F226" t="s">
+        <v>1574</v>
       </c>
       <c r="G226" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="H226" t="s">
         <v>1204</v>
@@ -24188,12 +23965,11 @@
       <c r="B227" t="s">
         <v>210</v>
       </c>
-      <c r="C227" s="11"/>
       <c r="E227" t="s">
         <v>711</v>
       </c>
-      <c r="F227" s="11" t="s">
-        <v>1500</v>
+      <c r="F227" t="s">
+        <v>1499</v>
       </c>
       <c r="I227" t="s">
         <v>1405</v>
@@ -24221,11 +23997,9 @@
       <c r="B228" t="s">
         <v>211</v>
       </c>
-      <c r="C228" s="11"/>
       <c r="E228" t="s">
         <v>712</v>
       </c>
-      <c r="F228" s="11"/>
       <c r="H228" t="s">
         <v>1156</v>
       </c>
@@ -24246,17 +24020,17 @@
       <c r="B229" t="s">
         <v>487</v>
       </c>
-      <c r="C229" s="11" t="s">
+      <c r="C229" t="s">
         <v>1184</v>
       </c>
       <c r="E229" t="s">
         <v>713</v>
       </c>
-      <c r="F229" s="11" t="s">
-        <v>1564</v>
+      <c r="F229" t="s">
+        <v>1562</v>
       </c>
       <c r="G229" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="J229" t="s">
         <v>767</v>
@@ -24281,13 +24055,12 @@
       <c r="B230" t="s">
         <v>212</v>
       </c>
-      <c r="C230" s="11" t="s">
+      <c r="C230" t="s">
         <v>1185</v>
       </c>
       <c r="E230" t="s">
         <v>714</v>
       </c>
-      <c r="F230" s="11"/>
       <c r="I230" t="s">
         <v>1349</v>
       </c>
@@ -24311,11 +24084,9 @@
       <c r="B231" t="s">
         <v>213</v>
       </c>
-      <c r="C231" s="11"/>
       <c r="E231" t="s">
         <v>715</v>
       </c>
-      <c r="F231" s="11"/>
       <c r="H231" t="s">
         <v>1159</v>
       </c>
@@ -24339,11 +24110,9 @@
       <c r="B232" t="s">
         <v>214</v>
       </c>
-      <c r="C232" s="11"/>
       <c r="E232" t="s">
         <v>716</v>
       </c>
-      <c r="F232" s="11"/>
       <c r="H232" t="s">
         <v>1088</v>
       </c>
@@ -24373,12 +24142,11 @@
       <c r="B233" t="s">
         <v>215</v>
       </c>
-      <c r="C233" s="11"/>
       <c r="E233" t="s">
         <v>717</v>
       </c>
-      <c r="F233" s="11" t="s">
-        <v>1459</v>
+      <c r="F233" t="s">
+        <v>1458</v>
       </c>
       <c r="H233" t="s">
         <v>1160</v>
@@ -24409,12 +24177,11 @@
       <c r="B234" t="s">
         <v>216</v>
       </c>
-      <c r="C234" s="11"/>
       <c r="E234" t="s">
         <v>718</v>
       </c>
-      <c r="F234" s="11" t="s">
-        <v>1449</v>
+      <c r="F234" t="s">
+        <v>1448</v>
       </c>
       <c r="I234" t="s">
         <v>844</v>
@@ -24445,12 +24212,11 @@
       <c r="B235" t="s">
         <v>217</v>
       </c>
-      <c r="C235" s="11"/>
       <c r="E235" t="s">
         <v>719</v>
       </c>
-      <c r="F235" s="11" t="s">
-        <v>1584</v>
+      <c r="F235" t="s">
+        <v>1581</v>
       </c>
       <c r="I235" t="s">
         <v>844</v>
@@ -24475,13 +24241,12 @@
       <c r="B236" t="s">
         <v>218</v>
       </c>
-      <c r="C236" s="11" t="s">
+      <c r="C236" t="s">
         <v>1388</v>
       </c>
       <c r="E236" t="s">
         <v>720</v>
       </c>
-      <c r="F236" s="11"/>
       <c r="I236" t="s">
         <v>888</v>
       </c>
@@ -24499,20 +24264,20 @@
       <c r="B237" t="s">
         <v>746</v>
       </c>
-      <c r="C237" s="11" t="s">
+      <c r="C237" t="s">
         <v>1387</v>
       </c>
       <c r="D237" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E237" t="s">
         <v>747</v>
       </c>
-      <c r="F237" s="11" t="s">
+      <c r="F237" t="s">
         <v>1181</v>
       </c>
       <c r="G237" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="I237" t="s">
         <v>1404</v>
@@ -24540,11 +24305,9 @@
       <c r="B238" t="s">
         <v>219</v>
       </c>
-      <c r="C238" s="11"/>
       <c r="E238" t="s">
         <v>721</v>
       </c>
-      <c r="F238" s="11"/>
       <c r="H238" t="s">
         <v>1162</v>
       </c>
@@ -24574,11 +24337,9 @@
       <c r="B239" t="s">
         <v>220</v>
       </c>
-      <c r="C239" s="11"/>
       <c r="E239" t="s">
         <v>722</v>
       </c>
-      <c r="F239" s="11"/>
       <c r="H239" t="s">
         <v>1335</v>
       </c>
@@ -24608,15 +24369,14 @@
       <c r="B240" t="s">
         <v>221</v>
       </c>
-      <c r="C240" s="11"/>
       <c r="E240" t="s">
         <v>723</v>
       </c>
-      <c r="F240" s="11" t="s">
-        <v>1579</v>
+      <c r="F240" t="s">
+        <v>1577</v>
       </c>
       <c r="G240" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="H240" t="s">
         <v>1165</v>
@@ -24647,14 +24407,14 @@
       <c r="B241" t="s">
         <v>222</v>
       </c>
-      <c r="C241" s="11" t="s">
-        <v>1506</v>
+      <c r="C241" t="s">
+        <v>1505</v>
       </c>
       <c r="E241" t="s">
         <v>724</v>
       </c>
-      <c r="F241" s="11" t="s">
-        <v>1565</v>
+      <c r="F241" t="s">
+        <v>1563</v>
       </c>
       <c r="I241" t="s">
         <v>1117</v>
@@ -24679,12 +24439,11 @@
       <c r="B242" t="s">
         <v>223</v>
       </c>
-      <c r="C242" s="11"/>
       <c r="E242" t="s">
         <v>725</v>
       </c>
-      <c r="F242" s="11" t="s">
-        <v>1566</v>
+      <c r="F242" t="s">
+        <v>1564</v>
       </c>
       <c r="I242" t="s">
         <v>844</v>
@@ -24712,11 +24471,9 @@
       <c r="B243" t="s">
         <v>224</v>
       </c>
-      <c r="C243" s="11"/>
       <c r="E243" t="s">
         <v>726</v>
       </c>
-      <c r="F243" s="11"/>
       <c r="H243" t="s">
         <v>1166</v>
       </c>
@@ -24740,11 +24497,9 @@
       <c r="B244" t="s">
         <v>225</v>
       </c>
-      <c r="C244" s="11"/>
       <c r="E244" t="s">
         <v>727</v>
       </c>
-      <c r="F244" s="11"/>
       <c r="H244" t="s">
         <v>1167</v>
       </c>
@@ -24774,11 +24529,9 @@
       <c r="B245" t="s">
         <v>226</v>
       </c>
-      <c r="C245" s="11"/>
       <c r="E245" t="s">
         <v>728</v>
       </c>
-      <c r="F245" s="11"/>
       <c r="H245" t="s">
         <v>1168</v>
       </c>
@@ -24802,11 +24555,9 @@
       <c r="B246" t="s">
         <v>227</v>
       </c>
-      <c r="C246" s="11"/>
       <c r="E246" t="s">
         <v>729</v>
       </c>
-      <c r="F246" s="11"/>
       <c r="H246" t="s">
         <v>1169</v>
       </c>
@@ -24833,15 +24584,14 @@
       <c r="B247" t="s">
         <v>228</v>
       </c>
-      <c r="C247" s="11"/>
       <c r="E247" t="s">
         <v>730</v>
       </c>
-      <c r="F247" s="11" t="s">
-        <v>1502</v>
+      <c r="F247" t="s">
+        <v>1501</v>
       </c>
       <c r="G247" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="H247" t="s">
         <v>1170</v>
@@ -24872,12 +24622,11 @@
       <c r="B248" t="s">
         <v>229</v>
       </c>
-      <c r="C248" s="11"/>
       <c r="E248" t="s">
         <v>731</v>
       </c>
-      <c r="F248" s="11" t="s">
-        <v>1435</v>
+      <c r="F248" t="s">
+        <v>1434</v>
       </c>
       <c r="I248" t="s">
         <v>844</v>
@@ -24902,11 +24651,9 @@
       <c r="B249" t="s">
         <v>230</v>
       </c>
-      <c r="C249" s="11"/>
       <c r="E249" t="s">
         <v>732</v>
       </c>
-      <c r="F249" s="11"/>
       <c r="H249" t="s">
         <v>1173</v>
       </c>
@@ -24936,15 +24683,14 @@
       <c r="B250" t="s">
         <v>231</v>
       </c>
-      <c r="C250" s="11"/>
       <c r="E250" t="s">
         <v>733</v>
       </c>
-      <c r="F250" s="11" t="s">
-        <v>1467</v>
+      <c r="F250" t="s">
+        <v>1466</v>
       </c>
       <c r="G250" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="H250" t="s">
         <v>1175</v>
@@ -24975,14 +24721,14 @@
       <c r="B251" t="s">
         <v>232</v>
       </c>
-      <c r="C251" s="11" t="s">
+      <c r="C251" t="s">
         <v>1392</v>
       </c>
       <c r="E251" t="s">
         <v>734</v>
       </c>
-      <c r="F251" s="11" t="s">
-        <v>1581</v>
+      <c r="F251" t="s">
+        <v>1579</v>
       </c>
       <c r="I251" t="s">
         <v>844</v>
@@ -25010,15 +24756,14 @@
       <c r="B252" t="s">
         <v>233</v>
       </c>
-      <c r="C252" s="11"/>
       <c r="E252" t="s">
         <v>735</v>
       </c>
-      <c r="F252" s="11" t="s">
+      <c r="F252" t="s">
         <v>1183</v>
       </c>
       <c r="G252" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="H252" t="s">
         <v>902</v>
@@ -25043,11 +24788,9 @@
       <c r="B253" t="s">
         <v>234</v>
       </c>
-      <c r="C253" s="11"/>
       <c r="E253" t="s">
         <v>736</v>
       </c>
-      <c r="F253" s="11"/>
       <c r="H253" t="s">
         <v>1339</v>
       </c>
@@ -25074,12 +24817,11 @@
       <c r="B254" t="s">
         <v>235</v>
       </c>
-      <c r="C254" s="11"/>
       <c r="E254" t="s">
         <v>737</v>
       </c>
-      <c r="F254" s="11" t="s">
-        <v>1439</v>
+      <c r="F254" t="s">
+        <v>1438</v>
       </c>
       <c r="H254" t="s">
         <v>1179</v>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34649F8E-90FE-4530-B697-8033D2A87339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF04C2F-82FF-4D2F-8E5E-2EC8C7863EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="3570" windowWidth="38625" windowHeight="15855" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="30180" windowHeight="17970" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Elenco" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3391" uniqueCount="1671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="1676">
   <si>
     <t>Sigla</t>
   </si>
@@ -2388,9 +2388,6 @@
     <t>stella</t>
   </si>
   <si>
-    <t>Aland</t>
-  </si>
-  <si>
     <t>nero, azzurro, giallo</t>
   </si>
   <si>
@@ -3255,18 +3252,12 @@
     <t>blu, giallo, verde</t>
   </si>
   <si>
-    <t>S Lucia</t>
-  </si>
-  <si>
     <t>rosso, bianco, azzurro, giallo</t>
   </si>
   <si>
     <t>nave</t>
   </si>
   <si>
-    <t>Saint Pierre, S Pierre</t>
-  </si>
-  <si>
     <t>kosovo, montenegro, bosnia ed erzegovina, croazia, ungheria, romania, bulgaria, macedonia del nord</t>
   </si>
   <si>
@@ -3594,9 +3585,6 @@
     <t>*La Paz</t>
   </si>
   <si>
-    <t>*Belarus</t>
-  </si>
-  <si>
     <t>croce del sud, stella, uccello, animale, sagoma paese, cerchio</t>
   </si>
   <si>
@@ -3969,9 +3957,6 @@
     <t>Irama</t>
   </si>
   <si>
-    <t>Mary Anne,</t>
-  </si>
-  <si>
     <t>Windoek, Windows</t>
   </si>
   <si>
@@ -3984,15 +3969,9 @@
     <t>Bridgestone</t>
   </si>
   <si>
-    <t>Bandar, bandarzeri begawan</t>
-  </si>
-  <si>
     <t>Bottom, de botto</t>
   </si>
   <si>
-    <t>Faco, Vaccarofo</t>
-  </si>
-  <si>
     <t>Port au Prince, Port u prince, Porto Prince</t>
   </si>
   <si>
@@ -4011,9 +3990,6 @@
     <t>Masero</t>
   </si>
   <si>
-    <t>oranistad, oranistadt, orangestar, Orari estad, Orangestadt</t>
-  </si>
-  <si>
     <t>Buia</t>
   </si>
   <si>
@@ -4059,9 +4035,6 @@
     <t>st george's, st george, saint george, Giorgis, sangiorgis</t>
   </si>
   <si>
-    <t>S eustatius, sintestatius, sintastatius</t>
-  </si>
-  <si>
     <t>Maiott, Mariott, Mariotti, Mylot</t>
   </si>
   <si>
@@ -4350,9 +4323,6 @@
     <t>Pòr Dusièm</t>
   </si>
   <si>
-    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte, cotti, sri giaia, striglia guarda, free java, tre giaia, pura cotte</t>
-  </si>
-  <si>
     <t>Santiago, Santhiago, Santhiago del cile, lago del cile</t>
   </si>
   <si>
@@ -4446,9 +4416,6 @@
     <t>Ciao, Curasao</t>
   </si>
   <si>
-    <t>*Swaziland, e suatini</t>
-  </si>
-  <si>
     <t>Cambia</t>
   </si>
   <si>
@@ -4482,12 +4449,6 @@
     <t>Mamodzu, Mamotzu, ma mozu, mahmood</t>
   </si>
   <si>
-    <t>Saint Pierre, S Pierre, Miquelon, san pierre michelon, san pierre e miquelon</t>
-  </si>
-  <si>
-    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy, bartalemi, synth bardellemi</t>
-  </si>
-  <si>
     <t>Sapeva</t>
   </si>
   <si>
@@ -4558,9 +4519,6 @@
   </si>
   <si>
     <t>Con Acri, Macri</t>
-  </si>
-  <si>
-    <t>Bon Air</t>
   </si>
   <si>
     <t>Nome</t>
@@ -5439,21 +5397,12 @@
     <t>Philips burger, flixbus</t>
   </si>
   <si>
-    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis, sanchez &amp; nevis</t>
-  </si>
-  <si>
     <t>in giamena, engiamena, mangiamena</t>
   </si>
   <si>
-    <t>Pitcairn, isole big cairn, isole pick up, isole fitkair, fitkair, speedcairn</t>
-  </si>
-  <si>
     <t>*Kuwait, Al-Kuwait, Kuwait city, Q8, Madina al Q8, matina talk q8</t>
   </si>
   <si>
-    <t>new wave, noi e, miura, miue, minue</t>
-  </si>
-  <si>
     <t>Bologna</t>
   </si>
   <si>
@@ -5511,9 +5460,6 @@
     <t>King edward, edward point</t>
   </si>
   <si>
-    <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come</t>
-  </si>
-  <si>
     <t>Work of spain</t>
   </si>
   <si>
@@ -5524,6 +5470,75 @@
   </si>
   <si>
     <t>Duck</t>
+  </si>
+  <si>
+    <t>oranistad, oranistadt, orangestar, Orari estad, Orangestadt, oranistag, orari estate, orari istant</t>
+  </si>
+  <si>
+    <t>Nasso</t>
+  </si>
+  <si>
+    <t>Bandar, bandarzeri begawan, bandar serie bargawan, bandar seri, begawan</t>
+  </si>
+  <si>
+    <t>Mary Anne, Mary ann</t>
+  </si>
+  <si>
+    <t>Aland, Alan</t>
+  </si>
+  <si>
+    <t>Saint Pierre, S Pierre, Miquelon, san pierre michelon, san pierre e miquelon, sentiero michielon</t>
+  </si>
+  <si>
+    <t>Saint Pierre, S Pierre, sentiero</t>
+  </si>
+  <si>
+    <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte, cotti, sri giaia, striglia guarda, free java, tre giaia, pura cotte, gioia quando ne pura cotte</t>
+  </si>
+  <si>
+    <t>Faco, Vaccarofo, acaofo</t>
+  </si>
+  <si>
+    <t>*Belarus, velarus</t>
+  </si>
+  <si>
+    <t>Bon Air, boner</t>
+  </si>
+  <si>
+    <t>*Swaziland, e suatini, swatini, eduatini</t>
+  </si>
+  <si>
+    <t>Hermana</t>
+  </si>
+  <si>
+    <t>Pitcairn, isole big cairn, isole pick up, isole fitkair, fitkair, speedcairn, isole bitcoin, bitcoin</t>
+  </si>
+  <si>
+    <t>Esodo</t>
+  </si>
+  <si>
+    <t>Rocco</t>
+  </si>
+  <si>
+    <t>new wave, noi e, miura, miue, minue, nue</t>
+  </si>
+  <si>
+    <t>S Lucia, Santa Lucia</t>
+  </si>
+  <si>
+    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy, bartalemi, synth bardellemi, sing bardellemy, saint barthelemy, san barthelemy</t>
+  </si>
+  <si>
+    <t>S eustatius, sintestatius, sintastatius, sinteu status</t>
+  </si>
+  <si>
+    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis, sanchez &amp; nevis, saint kitze nevis, send kids in iris, sankitsi nevis, thank you say nadies, zenkids e nevis, send kids a nevis</t>
+  </si>
+  <si>
+    <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come, soã come, sauto me principe, sau tome</t>
+  </si>
+  <si>
+    <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come, soã come, sau tome</t>
   </si>
 </sst>
 </file>
@@ -17994,7 +18009,7 @@
         <v>747</v>
       </c>
       <c r="D1" t="s">
-        <v>1347</v>
+        <v>1338</v>
       </c>
       <c r="E1" t="s">
         <v>495</v>
@@ -18003,13 +18018,13 @@
         <v>748</v>
       </c>
       <c r="G1" t="s">
-        <v>1348</v>
+        <v>1339</v>
       </c>
       <c r="H1" t="s">
         <v>746</v>
       </c>
       <c r="I1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J1" t="s">
         <v>764</v>
@@ -18021,13 +18036,13 @@
         <v>772</v>
       </c>
       <c r="M1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N1" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="O1" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -18047,7 +18062,7 @@
         <v>750</v>
       </c>
       <c r="I2" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J2" t="s">
         <v>765</v>
@@ -18056,10 +18071,10 @@
         <v>766</v>
       </c>
       <c r="L2" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="N2" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O2" s="1">
         <v>1</v>
@@ -18083,13 +18098,13 @@
         <v>497</v>
       </c>
       <c r="F3" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="H3" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="I3" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="J3" t="s">
         <v>751</v>
@@ -18101,7 +18116,7 @@
         <v>773</v>
       </c>
       <c r="N3" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
@@ -18125,10 +18140,10 @@
         <v>498</v>
       </c>
       <c r="H4" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J4" t="s">
         <v>758</v>
@@ -18137,10 +18152,10 @@
         <v>769</v>
       </c>
       <c r="L4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N4" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -18161,31 +18176,31 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1350</v>
+        <v>1341</v>
       </c>
       <c r="E5" t="s">
         <v>499</v>
       </c>
       <c r="F5" t="s">
-        <v>1471</v>
+        <v>1460</v>
       </c>
       <c r="G5" t="s">
-        <v>1349</v>
+        <v>1340</v>
       </c>
       <c r="H5" t="s">
         <v>753</v>
       </c>
       <c r="I5" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="J5" t="s">
         <v>754</v>
       </c>
       <c r="L5" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N5" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O5" s="1">
         <v>2</v>
@@ -18202,10 +18217,10 @@
         <v>500</v>
       </c>
       <c r="H6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I6" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="J6" t="s">
         <v>751</v>
@@ -18214,10 +18229,10 @@
         <v>770</v>
       </c>
       <c r="L6" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="N6" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="O6" s="1">
         <v>2</v>
@@ -18234,13 +18249,13 @@
         <v>501</v>
       </c>
       <c r="I7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J7" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L7" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="M7" t="s">
         <v>492</v>
@@ -18263,13 +18278,13 @@
         <v>502</v>
       </c>
       <c r="F8" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="I8" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J8" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="L8" t="s">
         <v>775</v>
@@ -18295,13 +18310,13 @@
         <v>757</v>
       </c>
       <c r="G9" t="s">
-        <v>1397</v>
+        <v>1388</v>
       </c>
       <c r="H9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I9" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="J9" t="s">
         <v>771</v>
@@ -18310,10 +18325,10 @@
         <v>766</v>
       </c>
       <c r="L9" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="N9" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -18330,10 +18345,10 @@
         <v>503</v>
       </c>
       <c r="H10" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I10" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="J10" t="s">
         <v>778</v>
@@ -18345,7 +18360,7 @@
         <v>775</v>
       </c>
       <c r="N10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O10" s="1">
         <v>1</v>
@@ -18359,7 +18374,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>1651</v>
+        <v>1634</v>
       </c>
       <c r="E11" t="s">
         <v>504</v>
@@ -18368,13 +18383,13 @@
         <v>759</v>
       </c>
       <c r="I11" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="J11" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="N11" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O11" s="1">
         <v>2</v>
@@ -18391,10 +18406,10 @@
         <v>511</v>
       </c>
       <c r="F12" t="s">
-        <v>1322</v>
+        <v>1653</v>
       </c>
       <c r="I12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J12" t="s">
         <v>779</v>
@@ -18406,7 +18421,7 @@
         <v>492</v>
       </c>
       <c r="N12" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="O12" s="1">
         <v>3</v>
@@ -18426,13 +18441,13 @@
         <v>581</v>
       </c>
       <c r="I13" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J13" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L13" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="M13" t="s">
         <v>492</v>
@@ -18452,19 +18467,19 @@
         <v>505</v>
       </c>
       <c r="I14" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J14" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="K14" t="s">
         <v>766</v>
       </c>
       <c r="L14" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="N14" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="O14" s="1">
         <v>1</v>
@@ -18484,13 +18499,13 @@
         <v>761</v>
       </c>
       <c r="I15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J15" t="s">
         <v>762</v>
       </c>
       <c r="N15" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O15" s="1">
         <v>1</v>
@@ -18504,16 +18519,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
       <c r="E16" t="s">
         <v>507</v>
       </c>
       <c r="H16" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="I16" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="J16" t="s">
         <v>763</v>
@@ -18522,10 +18537,10 @@
         <v>766</v>
       </c>
       <c r="L16" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N16" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="O16" s="1">
         <v>2</v>
@@ -18541,14 +18556,17 @@
       <c r="E17" t="s">
         <v>508</v>
       </c>
+      <c r="F17" t="s">
+        <v>1654</v>
+      </c>
       <c r="I17" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J17" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="N17" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="O17" s="1">
         <v>2</v>
@@ -18562,22 +18580,22 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E18" t="s">
         <v>509</v>
       </c>
       <c r="H18" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I18" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="J18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N18" t="s">
-        <v>1492</v>
+        <v>1479</v>
       </c>
       <c r="O18" s="1">
         <v>2</v>
@@ -18591,28 +18609,28 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="E19" t="s">
         <v>510</v>
       </c>
       <c r="F19" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="G19" t="s">
-        <v>1351</v>
+        <v>1342</v>
       </c>
       <c r="I19" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J19" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="M19" t="s">
         <v>492</v>
       </c>
       <c r="N19" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="O19" s="1">
         <v>3</v>
@@ -18629,25 +18647,25 @@
         <v>513</v>
       </c>
       <c r="F20" t="s">
-        <v>1670</v>
+        <v>1652</v>
       </c>
       <c r="H20" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I20" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J20" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K20" t="s">
         <v>769</v>
       </c>
       <c r="L20" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N20" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="O20" s="1">
         <v>2</v>
@@ -18664,22 +18682,22 @@
         <v>514</v>
       </c>
       <c r="F21" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="I21" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J21" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K21" t="s">
         <v>768</v>
       </c>
       <c r="L21" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="N21" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O21" s="1">
         <v>2</v>
@@ -18696,16 +18714,16 @@
         <v>515</v>
       </c>
       <c r="H22" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="I22" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="J22" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="N22" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O22" s="1">
         <v>1</v>
@@ -18719,31 +18737,31 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>1463</v>
+        <v>1453</v>
       </c>
       <c r="E23" t="s">
         <v>516</v>
       </c>
       <c r="F23" t="s">
-        <v>1503</v>
+        <v>1490</v>
       </c>
       <c r="H23" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I23" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="J23" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="K23" t="s">
         <v>766</v>
       </c>
       <c r="L23" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="N23" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="O23" s="1">
         <v>2</v>
@@ -18760,19 +18778,19 @@
         <v>517</v>
       </c>
       <c r="F24" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="H24" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I24" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="J24" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="N24" t="s">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="O24" s="1">
         <v>2</v>
@@ -18789,13 +18807,13 @@
         <v>518</v>
       </c>
       <c r="I25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="J25" t="s">
         <v>769</v>
       </c>
       <c r="L25" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M25" t="s">
         <v>492</v>
@@ -18812,31 +18830,31 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E26" t="s">
         <v>519</v>
       </c>
       <c r="F26" t="s">
-        <v>1343</v>
+        <v>1334</v>
       </c>
       <c r="H26" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="I26" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J26" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="K26" t="s">
         <v>766</v>
       </c>
       <c r="L26" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="N26" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
       <c r="O26" s="1">
         <v>2</v>
@@ -18850,25 +18868,25 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>1183</v>
+        <v>1662</v>
       </c>
       <c r="E27" t="s">
         <v>520</v>
       </c>
       <c r="H27" t="s">
+        <v>795</v>
+      </c>
+      <c r="I27" t="s">
+        <v>826</v>
+      </c>
+      <c r="J27" t="s">
         <v>796</v>
       </c>
-      <c r="I27" t="s">
-        <v>827</v>
-      </c>
-      <c r="J27" t="s">
-        <v>797</v>
-      </c>
       <c r="K27" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N27" t="s">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="O27" s="1">
         <v>1</v>
@@ -18882,31 +18900,31 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
       <c r="E28" t="s">
         <v>522</v>
       </c>
       <c r="F28" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G28" t="s">
-        <v>1352</v>
+        <v>1343</v>
       </c>
       <c r="H28" t="s">
+        <v>799</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J28" t="s">
         <v>800</v>
       </c>
-      <c r="I28" t="s">
-        <v>1232</v>
-      </c>
-      <c r="J28" t="s">
-        <v>801</v>
-      </c>
       <c r="L28" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N28" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O28" s="1">
         <v>1</v>
@@ -18920,28 +18938,28 @@
         <v>482</v>
       </c>
       <c r="C29" t="s">
-        <v>1505</v>
+        <v>1663</v>
       </c>
       <c r="D29" t="s">
-        <v>1353</v>
+        <v>1344</v>
       </c>
       <c r="E29" t="s">
         <v>523</v>
       </c>
       <c r="F29" t="s">
-        <v>1477</v>
+        <v>1466</v>
       </c>
       <c r="G29" t="s">
-        <v>1354</v>
+        <v>1345</v>
       </c>
       <c r="I29" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J29" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K29" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L29" t="s">
         <v>780</v>
@@ -18950,7 +18968,7 @@
         <v>492</v>
       </c>
       <c r="N29" t="s">
-        <v>1485</v>
+        <v>1472</v>
       </c>
       <c r="O29" s="1">
         <v>3</v>
@@ -18964,19 +18982,19 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="E30" t="s">
         <v>524</v>
       </c>
       <c r="H30" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I30" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="J30" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K30" t="s">
         <v>766</v>
@@ -18985,7 +19003,7 @@
         <v>780</v>
       </c>
       <c r="N30" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="O30" s="1">
         <v>1</v>
@@ -19002,19 +19020,19 @@
         <v>525</v>
       </c>
       <c r="F31" t="s">
-        <v>1358</v>
+        <v>1349</v>
       </c>
       <c r="H31" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="I31" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="J31" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N31" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O31" s="1">
         <v>2</v>
@@ -19031,22 +19049,22 @@
         <v>526</v>
       </c>
       <c r="H32" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I32" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="J32" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K32" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L32" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="N32" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="O32" s="1">
         <v>1</v>
@@ -19063,28 +19081,28 @@
         <v>527</v>
       </c>
       <c r="F33" t="s">
-        <v>1313</v>
+        <v>1655</v>
       </c>
       <c r="G33" t="s">
-        <v>1355</v>
+        <v>1346</v>
       </c>
       <c r="H33" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="I33" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="J33" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="K33" t="s">
         <v>769</v>
       </c>
       <c r="L33" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="N33" t="s">
-        <v>1484</v>
+        <v>1471</v>
       </c>
       <c r="O33" s="1">
         <v>2</v>
@@ -19101,19 +19119,19 @@
         <v>528</v>
       </c>
       <c r="G34" t="s">
-        <v>1430</v>
+        <v>1421</v>
       </c>
       <c r="H34" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I34" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="J34" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N34" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O34" s="1">
         <v>1</v>
@@ -19130,16 +19148,16 @@
         <v>529</v>
       </c>
       <c r="F35" t="s">
-        <v>1407</v>
+        <v>1398</v>
       </c>
       <c r="H35" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="I35" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J35" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K35" t="s">
         <v>770</v>
@@ -19148,7 +19166,7 @@
         <v>780</v>
       </c>
       <c r="N35" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="O35" s="1">
         <v>2</v>
@@ -19165,25 +19183,25 @@
         <v>530</v>
       </c>
       <c r="F36" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="H36" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I36" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J36" t="s">
         <v>752</v>
       </c>
       <c r="K36" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L36" t="s">
         <v>780</v>
       </c>
       <c r="N36" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="O36" s="1">
         <v>2</v>
@@ -19200,28 +19218,28 @@
         <v>531</v>
       </c>
       <c r="F37" t="s">
-        <v>1444</v>
+        <v>1434</v>
       </c>
       <c r="G37" t="s">
-        <v>1431</v>
+        <v>1422</v>
       </c>
       <c r="H37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I37" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="K37" t="s">
         <v>766</v>
       </c>
       <c r="L37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="N37" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O37" s="1">
         <v>1</v>
@@ -19235,22 +19253,22 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E38" t="s">
         <v>532</v>
       </c>
       <c r="F38" t="s">
-        <v>1345</v>
+        <v>1336</v>
       </c>
       <c r="H38" t="s">
+        <v>835</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J38" t="s">
         <v>836</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1231</v>
-      </c>
-      <c r="J38" t="s">
-        <v>837</v>
       </c>
       <c r="K38" t="s">
         <v>770</v>
@@ -19259,7 +19277,7 @@
         <v>780</v>
       </c>
       <c r="N38" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="O38" s="1">
         <v>1</v>
@@ -19276,10 +19294,10 @@
         <v>533</v>
       </c>
       <c r="H39" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I39" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="J39" t="s">
         <v>762</v>
@@ -19288,10 +19306,10 @@
         <v>769</v>
       </c>
       <c r="L39" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N39" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O39" s="1">
         <v>1</v>
@@ -19308,16 +19326,16 @@
         <v>534</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>780</v>
       </c>
       <c r="N40" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="O40" s="15">
         <v>2</v>
@@ -19328,25 +19346,25 @@
         <v>443</v>
       </c>
       <c r="B41" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C41" t="s">
-        <v>1648</v>
+        <v>1631</v>
       </c>
       <c r="E41" t="s">
         <v>669</v>
       </c>
       <c r="H41" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I41" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J41" t="s">
         <v>760</v>
       </c>
       <c r="N41" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="O41" s="1">
         <v>1</v>
@@ -19360,25 +19378,25 @@
         <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>1655</v>
+        <v>1638</v>
       </c>
       <c r="E42" t="s">
         <v>535</v>
       </c>
       <c r="F42" t="s">
-        <v>1643</v>
+        <v>1628</v>
       </c>
       <c r="H42" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I42" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J42" t="s">
         <v>754</v>
       </c>
       <c r="N42" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O42" s="1">
         <v>2</v>
@@ -19392,19 +19410,19 @@
         <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="E43" t="s">
         <v>536</v>
       </c>
       <c r="F43" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="H43" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I43" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="J43" t="s">
         <v>760</v>
@@ -19416,7 +19434,7 @@
         <v>780</v>
       </c>
       <c r="N43" t="s">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="O43" s="1">
         <v>1</v>
@@ -19433,16 +19451,16 @@
         <v>537</v>
       </c>
       <c r="F44" t="s">
+        <v>841</v>
+      </c>
+      <c r="H44" t="s">
+        <v>924</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J44" t="s">
         <v>842</v>
-      </c>
-      <c r="H44" t="s">
-        <v>925</v>
-      </c>
-      <c r="I44" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J44" t="s">
-        <v>843</v>
       </c>
       <c r="K44" t="s">
         <v>770</v>
@@ -19451,7 +19469,7 @@
         <v>780</v>
       </c>
       <c r="N44" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="O44" s="1">
         <v>1</v>
@@ -19468,19 +19486,19 @@
         <v>538</v>
       </c>
       <c r="I45" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="J45" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K45" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="L45" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N45" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="O45" s="1">
         <v>1</v>
@@ -19494,28 +19512,28 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E46" t="s">
         <v>43</v>
       </c>
       <c r="F46" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H46" t="s">
         <v>114</v>
       </c>
       <c r="I46" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J46" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="L46" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="N46" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="O46" s="1">
         <v>3</v>
@@ -19532,16 +19550,16 @@
         <v>539</v>
       </c>
       <c r="H47" t="s">
+        <v>848</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J47" t="s">
         <v>849</v>
       </c>
-      <c r="I47" t="s">
-        <v>1232</v>
-      </c>
-      <c r="J47" t="s">
-        <v>850</v>
-      </c>
       <c r="N47" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O47" s="1">
         <v>1</v>
@@ -19555,25 +19573,25 @@
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="E48" t="s">
         <v>540</v>
       </c>
       <c r="I48" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J48" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K48" t="s">
         <v>766</v>
       </c>
       <c r="L48" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N48" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="O48" s="1">
         <v>2</v>
@@ -19587,22 +19605,22 @@
         <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E49" t="s">
         <v>541</v>
       </c>
       <c r="H49" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I49" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J49" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="N49" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
       <c r="O49" s="1">
         <v>2</v>
@@ -19616,16 +19634,16 @@
         <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E50" t="s">
         <v>542</v>
       </c>
       <c r="H50" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I50" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J50" t="s">
         <v>760</v>
@@ -19634,10 +19652,10 @@
         <v>762</v>
       </c>
       <c r="L50" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N50" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="O50" s="1">
         <v>1</v>
@@ -19651,31 +19669,31 @@
         <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E51" t="s">
         <v>543</v>
       </c>
       <c r="F51" t="s">
+        <v>858</v>
+      </c>
+      <c r="H51" t="s">
+        <v>930</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J51" t="s">
         <v>859</v>
       </c>
-      <c r="H51" t="s">
-        <v>931</v>
-      </c>
-      <c r="I51" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>860</v>
       </c>
-      <c r="K51" t="s">
-        <v>861</v>
-      </c>
       <c r="L51" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N51" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -19689,28 +19707,28 @@
         <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
       <c r="E52" t="s">
         <v>544</v>
       </c>
       <c r="F52" t="s">
-        <v>1418</v>
+        <v>1409</v>
       </c>
       <c r="G52" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H52" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I52" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J52" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="N52" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O52" s="1">
         <v>2</v>
@@ -19727,19 +19745,19 @@
         <v>545</v>
       </c>
       <c r="H53" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I53" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="J53" t="s">
         <v>760</v>
       </c>
       <c r="L53" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N53" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O53" s="1">
         <v>1</v>
@@ -19756,19 +19774,19 @@
         <v>546</v>
       </c>
       <c r="H54" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I54" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="J54" t="s">
         <v>777</v>
       </c>
       <c r="L54" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N54" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O54" s="1">
         <v>1</v>
@@ -19785,10 +19803,10 @@
         <v>547</v>
       </c>
       <c r="F55" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="I55" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J55" t="s">
         <v>777</v>
@@ -19800,7 +19818,7 @@
         <v>780</v>
       </c>
       <c r="N55" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="O55" s="1">
         <v>1</v>
@@ -19814,19 +19832,19 @@
         <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
       <c r="E56" t="s">
         <v>548</v>
       </c>
       <c r="F56" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="I56" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J56" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K56" t="s">
         <v>766</v>
@@ -19838,7 +19856,7 @@
         <v>492</v>
       </c>
       <c r="N56" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="O56" s="1">
         <v>3</v>
@@ -19855,16 +19873,16 @@
         <v>549</v>
       </c>
       <c r="H57" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="I57" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J57" t="s">
         <v>762</v>
       </c>
       <c r="L57" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O57" s="1">
         <v>1</v>
@@ -19881,22 +19899,22 @@
         <v>550</v>
       </c>
       <c r="F58" t="s">
-        <v>1408</v>
+        <v>1399</v>
       </c>
       <c r="I58" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J58" t="s">
+        <v>867</v>
+      </c>
+      <c r="K58" t="s">
         <v>868</v>
       </c>
-      <c r="K58" t="s">
-        <v>869</v>
-      </c>
       <c r="L58" t="s">
-        <v>1495</v>
+        <v>1482</v>
       </c>
       <c r="N58" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="O58" s="1">
         <v>2</v>
@@ -19913,22 +19931,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="s">
-        <v>1437</v>
+        <v>1427</v>
       </c>
       <c r="H59" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="I59" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="J59" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L59" t="s">
-        <v>1362</v>
+        <v>1353</v>
       </c>
       <c r="N59" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O59" s="1">
         <v>1</v>
@@ -19945,25 +19963,25 @@
         <v>552</v>
       </c>
       <c r="F60" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="H60" t="s">
+        <v>870</v>
+      </c>
+      <c r="I60" t="s">
+        <v>884</v>
+      </c>
+      <c r="J60" t="s">
         <v>871</v>
-      </c>
-      <c r="I60" t="s">
-        <v>885</v>
-      </c>
-      <c r="J60" t="s">
-        <v>872</v>
       </c>
       <c r="K60" t="s">
         <v>770</v>
       </c>
       <c r="L60" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="N60" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -19977,28 +19995,28 @@
         <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="E61" t="s">
         <v>553</v>
       </c>
       <c r="F61" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I61" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="J61" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L61" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N61" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O61" s="1">
         <v>2</v>
@@ -20012,25 +20030,25 @@
         <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E62" t="s">
         <v>554</v>
       </c>
       <c r="F62" t="s">
+        <v>875</v>
+      </c>
+      <c r="H62" t="s">
         <v>876</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J62" t="s">
         <v>877</v>
       </c>
-      <c r="I62" t="s">
-        <v>1239</v>
-      </c>
-      <c r="J62" t="s">
-        <v>878</v>
-      </c>
       <c r="N62" t="s">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="O62" s="1">
         <v>1</v>
@@ -20047,19 +20065,19 @@
         <v>571</v>
       </c>
       <c r="H63" t="s">
+        <v>879</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1282</v>
+      </c>
+      <c r="J63" t="s">
         <v>880</v>
-      </c>
-      <c r="I63" t="s">
-        <v>1286</v>
-      </c>
-      <c r="J63" t="s">
-        <v>881</v>
       </c>
       <c r="K63" t="s">
         <v>770</v>
       </c>
       <c r="L63" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="O63" s="1">
         <v>2</v>
@@ -20073,22 +20091,22 @@
         <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>1400</v>
+        <v>1391</v>
       </c>
       <c r="E64" t="s">
         <v>556</v>
       </c>
       <c r="H64" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I64" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J64" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="N64" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O64" s="1">
         <v>1</v>
@@ -20102,28 +20120,28 @@
         <v>739</v>
       </c>
       <c r="C65" t="s">
-        <v>1467</v>
+        <v>1664</v>
       </c>
       <c r="E65" t="s">
         <v>707</v>
       </c>
       <c r="F65" t="s">
-        <v>1456</v>
+        <v>1446</v>
       </c>
       <c r="H65" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I65" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J65" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="L65" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="N65" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O65" s="1">
         <v>2</v>
@@ -20140,25 +20158,25 @@
         <v>557</v>
       </c>
       <c r="F66" t="s">
-        <v>1481</v>
+        <v>1468</v>
       </c>
       <c r="H66" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I66" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="J66" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="K66" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L66" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="N66" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="O66" s="1">
         <v>1</v>
@@ -20172,19 +20190,19 @@
         <v>63</v>
       </c>
       <c r="C67" t="s">
-        <v>1499</v>
+        <v>1486</v>
       </c>
       <c r="E67" t="s">
         <v>558</v>
       </c>
       <c r="I67" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J67" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="L67" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="O67" s="1">
         <v>2</v>
@@ -20201,19 +20219,19 @@
         <v>559</v>
       </c>
       <c r="I68" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="J68" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K68" t="s">
         <v>770</v>
       </c>
       <c r="L68" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="N68" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="O68" s="1">
         <v>1</v>
@@ -20230,16 +20248,16 @@
         <v>560</v>
       </c>
       <c r="H69" t="s">
+        <v>890</v>
+      </c>
+      <c r="I69" t="s">
+        <v>1269</v>
+      </c>
+      <c r="J69" t="s">
         <v>891</v>
       </c>
-      <c r="I69" t="s">
-        <v>1273</v>
-      </c>
-      <c r="J69" t="s">
-        <v>892</v>
-      </c>
       <c r="L69" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O69" s="1">
         <v>1</v>
@@ -20256,16 +20274,16 @@
         <v>561</v>
       </c>
       <c r="H70" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="I70" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J70" t="s">
         <v>760</v>
       </c>
       <c r="N70" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O70" s="1">
         <v>1</v>
@@ -20282,22 +20300,22 @@
         <v>562</v>
       </c>
       <c r="F71" t="s">
-        <v>1341</v>
+        <v>1332</v>
       </c>
       <c r="G71" t="s">
-        <v>1356</v>
+        <v>1347</v>
       </c>
       <c r="H71" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="I71" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J71" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N71" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O71" s="1">
         <v>2</v>
@@ -20314,19 +20332,19 @@
         <v>563</v>
       </c>
       <c r="H72" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I72" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J72" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K72" t="s">
         <v>769</v>
       </c>
       <c r="L72" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="M72" t="s">
         <v>492</v>
@@ -20343,25 +20361,25 @@
         <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>1468</v>
+        <v>1457</v>
       </c>
       <c r="E73" t="s">
         <v>564</v>
       </c>
       <c r="F73" t="s">
-        <v>1482</v>
+        <v>1469</v>
       </c>
       <c r="H73" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I73" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J73" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N73" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O73" s="1">
         <v>2</v>
@@ -20378,16 +20396,16 @@
         <v>565</v>
       </c>
       <c r="H74" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I74" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="J74" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L74" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="O74" s="1">
         <v>2</v>
@@ -20401,22 +20419,22 @@
         <v>71</v>
       </c>
       <c r="C75" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E75" t="s">
         <v>566</v>
       </c>
       <c r="F75" t="s">
-        <v>1665</v>
+        <v>1648</v>
       </c>
       <c r="I75" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J75" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L75" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="M75" t="s">
         <v>492</v>
@@ -20432,20 +20450,23 @@
       <c r="B76" t="s">
         <v>72</v>
       </c>
+      <c r="C76" t="s">
+        <v>1665</v>
+      </c>
       <c r="E76" t="s">
         <v>567</v>
       </c>
       <c r="H76" t="s">
+        <v>903</v>
+      </c>
+      <c r="I76" t="s">
+        <v>828</v>
+      </c>
+      <c r="J76" t="s">
         <v>904</v>
       </c>
-      <c r="I76" t="s">
-        <v>829</v>
-      </c>
-      <c r="J76" t="s">
-        <v>905</v>
-      </c>
       <c r="N76" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O76" s="1">
         <v>1</v>
@@ -20459,19 +20480,19 @@
         <v>73</v>
       </c>
       <c r="C77" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
       <c r="E77" t="s">
         <v>568</v>
       </c>
       <c r="H77" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="I77" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J77" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="K77" t="s">
         <v>768</v>
@@ -20480,7 +20501,7 @@
         <v>780</v>
       </c>
       <c r="N77" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="O77" s="1">
         <v>1</v>
@@ -20494,19 +20515,19 @@
         <v>74</v>
       </c>
       <c r="C78" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="E78" t="s">
         <v>569</v>
       </c>
       <c r="I78" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J78" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N78" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="O78" s="1">
         <v>1</v>
@@ -20523,19 +20544,19 @@
         <v>570</v>
       </c>
       <c r="I79" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J79" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K79" t="s">
         <v>769</v>
       </c>
       <c r="L79" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N79" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="O79" s="1">
         <v>1</v>
@@ -20552,25 +20573,25 @@
         <v>76</v>
       </c>
       <c r="H80" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="I80" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="J80" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K80" t="s">
         <v>769</v>
       </c>
       <c r="L80" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M80" t="s">
         <v>492</v>
       </c>
       <c r="N80" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O80" s="1">
         <v>3</v>
@@ -20584,22 +20605,22 @@
         <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="E81" t="s">
         <v>77</v>
       </c>
       <c r="F81" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="H81" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="I81" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="J81" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K81" t="s">
         <v>769</v>
@@ -20608,7 +20629,7 @@
         <v>780</v>
       </c>
       <c r="N81" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="O81" s="1">
         <v>2</v>
@@ -20625,13 +20646,13 @@
         <v>555</v>
       </c>
       <c r="H82" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I82" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="J82" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K82" t="s">
         <v>766</v>
@@ -20640,7 +20661,7 @@
         <v>780</v>
       </c>
       <c r="N82" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="O82" s="1">
         <v>2</v>
@@ -20657,19 +20678,19 @@
         <v>572</v>
       </c>
       <c r="H83" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="I83" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="J83" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="L83" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N83" t="s">
-        <v>1497</v>
+        <v>1484</v>
       </c>
       <c r="O83" s="1">
         <v>1</v>
@@ -20686,25 +20707,25 @@
         <v>573</v>
       </c>
       <c r="F84" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="G84" t="s">
-        <v>1661</v>
+        <v>1644</v>
       </c>
       <c r="I84" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J84" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K84" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L84" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N84" t="s">
-        <v>1488</v>
+        <v>1475</v>
       </c>
       <c r="O84" s="1">
         <v>2</v>
@@ -20721,25 +20742,25 @@
         <v>574</v>
       </c>
       <c r="F85" t="s">
-        <v>1663</v>
+        <v>1646</v>
       </c>
       <c r="H85" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I85" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="J85" t="s">
         <v>762</v>
       </c>
       <c r="L85" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M85" t="s">
         <v>492</v>
       </c>
       <c r="N85" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O85" s="1">
         <v>3</v>
@@ -20756,16 +20777,16 @@
         <v>575</v>
       </c>
       <c r="F86" t="s">
-        <v>1414</v>
+        <v>1405</v>
       </c>
       <c r="I86" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J86" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L86" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="M86" t="s">
         <v>492</v>
@@ -20782,31 +20803,31 @@
         <v>83</v>
       </c>
       <c r="C87" t="s">
-        <v>1401</v>
+        <v>1392</v>
       </c>
       <c r="E87" t="s">
         <v>576</v>
       </c>
       <c r="F87" t="s">
-        <v>1662</v>
+        <v>1645</v>
       </c>
       <c r="G87" t="s">
-        <v>1432</v>
+        <v>1423</v>
       </c>
       <c r="I87" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J87" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L87" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M87" t="s">
         <v>492</v>
       </c>
       <c r="N87" t="s">
-        <v>1489</v>
+        <v>1476</v>
       </c>
       <c r="O87" s="1">
         <v>3</v>
@@ -20826,19 +20847,19 @@
         <v>84</v>
       </c>
       <c r="H88" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="I88" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="J88" t="s">
         <v>778</v>
       </c>
       <c r="L88" t="s">
-        <v>1658</v>
+        <v>1641</v>
       </c>
       <c r="N88" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O88" s="1">
         <v>2</v>
@@ -20855,16 +20876,16 @@
         <v>578</v>
       </c>
       <c r="F89" t="s">
-        <v>1382</v>
+        <v>1373</v>
       </c>
       <c r="I89" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J89" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L89" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="M89" t="s">
         <v>492</v>
@@ -20884,19 +20905,19 @@
         <v>579</v>
       </c>
       <c r="F90" t="s">
-        <v>1504</v>
+        <v>1491</v>
       </c>
       <c r="H90" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="I90" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J90" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N90" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O90" s="1">
         <v>2</v>
@@ -20910,31 +20931,31 @@
         <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="E91" t="s">
+        <v>915</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1647</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H91" t="s">
         <v>916</v>
       </c>
-      <c r="F91" t="s">
-        <v>1664</v>
-      </c>
-      <c r="G91" t="s">
-        <v>1363</v>
-      </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J91" t="s">
         <v>917</v>
       </c>
-      <c r="I91" t="s">
-        <v>1231</v>
-      </c>
-      <c r="J91" t="s">
-        <v>918</v>
-      </c>
       <c r="L91" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="N91" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="O91" s="1">
         <v>2</v>
@@ -20948,19 +20969,19 @@
         <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E92" t="s">
         <v>580</v>
       </c>
       <c r="H92" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I92" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J92" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K92" t="s">
         <v>768</v>
@@ -20969,7 +20990,7 @@
         <v>780</v>
       </c>
       <c r="N92" t="s">
-        <v>1501</v>
+        <v>1488</v>
       </c>
       <c r="O92" s="1">
         <v>2</v>
@@ -20986,16 +21007,16 @@
         <v>581</v>
       </c>
       <c r="H93" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I93" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="J93" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N93" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="O93" s="1">
         <v>2</v>
@@ -21012,19 +21033,19 @@
         <v>582</v>
       </c>
       <c r="F94" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G94" t="s">
-        <v>1364</v>
+        <v>1355</v>
       </c>
       <c r="H94" t="s">
+        <v>922</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1230</v>
+      </c>
+      <c r="J94" t="s">
         <v>923</v>
-      </c>
-      <c r="I94" t="s">
-        <v>1234</v>
-      </c>
-      <c r="J94" t="s">
-        <v>924</v>
       </c>
       <c r="K94" t="s">
         <v>769</v>
@@ -21036,7 +21057,7 @@
         <v>492</v>
       </c>
       <c r="N94" t="s">
-        <v>1485</v>
+        <v>1472</v>
       </c>
       <c r="O94" s="1">
         <v>3</v>
@@ -21053,22 +21074,22 @@
         <v>624</v>
       </c>
       <c r="F95" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
       <c r="H95" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="I95" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J95" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L95" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="N95" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O95" s="1">
         <v>1</v>
@@ -21085,22 +21106,22 @@
         <v>583</v>
       </c>
       <c r="H96" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I96" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="J96" t="s">
         <v>778</v>
       </c>
       <c r="K96" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="L96" t="s">
         <v>780</v>
       </c>
       <c r="N96" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="O96" s="1">
         <v>2</v>
@@ -21117,10 +21138,10 @@
         <v>584</v>
       </c>
       <c r="H97" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I97" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J97" t="s">
         <v>762</v>
@@ -21135,7 +21156,7 @@
         <v>492</v>
       </c>
       <c r="N97" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="O97" s="1">
         <v>3</v>
@@ -21152,25 +21173,25 @@
         <v>585</v>
       </c>
       <c r="F98" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H98" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="I98" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J98" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="K98" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L98" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N98" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O98" s="1">
         <v>1</v>
@@ -21187,19 +21208,19 @@
         <v>586</v>
       </c>
       <c r="F99" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="H99" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="I99" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="J99" t="s">
         <v>762</v>
       </c>
       <c r="N99" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O99" s="1">
         <v>1</v>
@@ -21216,16 +21237,16 @@
         <v>587</v>
       </c>
       <c r="H100" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="I100" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J100" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L100" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="M100" t="s">
         <v>492</v>
@@ -21245,22 +21266,22 @@
         <v>588</v>
       </c>
       <c r="H101" t="s">
+        <v>943</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J101" t="s">
         <v>944</v>
-      </c>
-      <c r="I101" t="s">
-        <v>1243</v>
-      </c>
-      <c r="J101" t="s">
-        <v>945</v>
       </c>
       <c r="K101" t="s">
         <v>769</v>
       </c>
       <c r="L101" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N101" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O101" s="1">
         <v>1</v>
@@ -21277,13 +21298,13 @@
         <v>589</v>
       </c>
       <c r="H102" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I102" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="J102" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K102" t="s">
         <v>771</v>
@@ -21292,7 +21313,7 @@
         <v>774</v>
       </c>
       <c r="N102" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O102" s="1">
         <v>1</v>
@@ -21309,16 +21330,16 @@
         <v>590</v>
       </c>
       <c r="H103" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I103" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J103" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="N103" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O103" s="1">
         <v>1</v>
@@ -21332,22 +21353,22 @@
         <v>487</v>
       </c>
       <c r="C104" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E104" t="s">
         <v>591</v>
       </c>
       <c r="H104" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="I104" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J104" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L104" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="M104" t="s">
         <v>492</v>
@@ -21367,19 +21388,19 @@
         <v>592</v>
       </c>
       <c r="F105" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G105" t="s">
-        <v>1660</v>
+        <v>1643</v>
       </c>
       <c r="I105" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J105" t="s">
         <v>760</v>
       </c>
       <c r="L105" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O105" s="1">
         <v>1</v>
@@ -21393,16 +21414,16 @@
         <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E106" t="s">
         <v>593</v>
       </c>
       <c r="G106" t="s">
-        <v>1365</v>
+        <v>1356</v>
       </c>
       <c r="I106" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J106" t="s">
         <v>762</v>
@@ -21411,13 +21432,13 @@
         <v>766</v>
       </c>
       <c r="L106" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M106" t="s">
         <v>492</v>
       </c>
       <c r="N106" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="O106" s="1">
         <v>3</v>
@@ -21431,34 +21452,34 @@
         <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E107" t="s">
         <v>594</v>
       </c>
       <c r="F107" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="G107" t="s">
-        <v>1366</v>
+        <v>1357</v>
       </c>
       <c r="I107" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J107" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K107" t="s">
         <v>771</v>
       </c>
       <c r="L107" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="M107" t="s">
         <v>492</v>
       </c>
       <c r="N107" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="O107" s="1">
         <v>3</v>
@@ -21472,13 +21493,13 @@
         <v>103</v>
       </c>
       <c r="C108" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E108" t="s">
         <v>569</v>
       </c>
       <c r="I108" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J108" t="s">
         <v>758</v>
@@ -21487,13 +21508,13 @@
         <v>771</v>
       </c>
       <c r="L108" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="M108" t="s">
         <v>492</v>
       </c>
       <c r="N108" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O108" s="1">
         <v>3</v>
@@ -21507,25 +21528,25 @@
         <v>431</v>
       </c>
       <c r="C109" t="s">
-        <v>781</v>
+        <v>1657</v>
       </c>
       <c r="D109" t="s">
-        <v>1368</v>
+        <v>1359</v>
       </c>
       <c r="E109" t="s">
         <v>596</v>
       </c>
       <c r="F109" t="s">
-        <v>1308</v>
+        <v>1656</v>
       </c>
       <c r="I109" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J109" t="s">
         <v>754</v>
       </c>
       <c r="L109" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M109" t="s">
         <v>492</v>
@@ -21542,22 +21563,22 @@
         <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D110" t="s">
-        <v>1409</v>
+        <v>1400</v>
       </c>
       <c r="E110" t="s">
         <v>597</v>
       </c>
       <c r="I110" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J110" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L110" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="M110" t="s">
         <v>492</v>
@@ -21571,34 +21592,34 @@
         <v>269</v>
       </c>
       <c r="B111" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C111" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E111" t="s">
         <v>598</v>
       </c>
       <c r="F111" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="I111" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J111" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K111" t="s">
         <v>770</v>
       </c>
       <c r="L111" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M111" t="s">
         <v>492</v>
       </c>
       <c r="N111" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="O111" s="1">
         <v>3</v>
@@ -21612,31 +21633,31 @@
         <v>105</v>
       </c>
       <c r="C112" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E112" t="s">
         <v>599</v>
       </c>
       <c r="G112" t="s">
-        <v>1367</v>
+        <v>1358</v>
       </c>
       <c r="I112" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J112" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="K112" t="s">
         <v>766</v>
       </c>
       <c r="L112" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="M112" t="s">
         <v>492</v>
       </c>
       <c r="N112" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="O112" s="1">
         <v>3</v>
@@ -21650,22 +21671,22 @@
         <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E113" t="s">
         <v>600</v>
       </c>
       <c r="G113" t="s">
-        <v>1369</v>
+        <v>1360</v>
       </c>
       <c r="I113" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J113" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L113" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="M113" t="s">
         <v>492</v>
@@ -21682,25 +21703,25 @@
         <v>601</v>
       </c>
       <c r="C114" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E114" t="s">
         <v>602</v>
       </c>
       <c r="F114" t="s">
-        <v>1340</v>
+        <v>1331</v>
       </c>
       <c r="G114" t="s">
-        <v>1370</v>
+        <v>1361</v>
       </c>
       <c r="I114" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J114" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L114" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M114" t="s">
         <v>492</v>
@@ -21717,28 +21738,28 @@
         <v>107</v>
       </c>
       <c r="C115" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="E115" t="s">
         <v>603</v>
       </c>
       <c r="F115" t="s">
-        <v>1457</v>
+        <v>1447</v>
       </c>
       <c r="I115" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J115" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L115" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="M115" t="s">
         <v>492</v>
       </c>
       <c r="N115" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="O115" s="1">
         <v>3</v>
@@ -21752,28 +21773,28 @@
         <v>108</v>
       </c>
       <c r="C116" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E116" t="s">
         <v>604</v>
       </c>
       <c r="F116" t="s">
-        <v>1394</v>
+        <v>1385</v>
       </c>
       <c r="G116" t="s">
-        <v>1406</v>
+        <v>1397</v>
       </c>
       <c r="I116" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J116" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L116" t="s">
         <v>780</v>
       </c>
       <c r="N116" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="O116" s="1">
         <v>2</v>
@@ -21787,22 +21808,22 @@
         <v>109</v>
       </c>
       <c r="C117" t="s">
-        <v>1644</v>
+        <v>1666</v>
       </c>
       <c r="E117" t="s">
         <v>595</v>
       </c>
       <c r="F117" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="I117" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J117" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L117" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M117" t="s">
         <v>492</v>
@@ -21819,19 +21840,19 @@
         <v>110</v>
       </c>
       <c r="C118" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E118" t="s">
         <v>605</v>
       </c>
       <c r="F118" t="s">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="I118" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J118" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="K118" t="s">
         <v>766</v>
@@ -21840,7 +21861,7 @@
         <v>780</v>
       </c>
       <c r="N118" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="O118" s="1">
         <v>2</v>
@@ -21854,28 +21875,28 @@
         <v>111</v>
       </c>
       <c r="C119" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E119" t="s">
         <v>606</v>
       </c>
       <c r="F119" t="s">
-        <v>1415</v>
+        <v>1406</v>
       </c>
       <c r="I119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J119" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="L119" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="M119" t="s">
         <v>492</v>
       </c>
       <c r="N119" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="O119" s="1">
         <v>3</v>
@@ -21889,19 +21910,19 @@
         <v>112</v>
       </c>
       <c r="C120" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E120" t="s">
         <v>607</v>
       </c>
       <c r="I120" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J120" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L120" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="M120" t="s">
         <v>492</v>
@@ -21921,22 +21942,22 @@
         <v>608</v>
       </c>
       <c r="H121" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I121" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="J121" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K121" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L121" t="s">
         <v>780</v>
       </c>
       <c r="N121" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="O121" s="1">
         <v>1</v>
@@ -21953,16 +21974,16 @@
         <v>609</v>
       </c>
       <c r="H122" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I122" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J122" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="N122" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O122" s="1">
         <v>1</v>
@@ -21979,19 +22000,19 @@
         <v>610</v>
       </c>
       <c r="H123" t="s">
+        <v>960</v>
+      </c>
+      <c r="I123" t="s">
+        <v>1278</v>
+      </c>
+      <c r="J123" t="s">
         <v>961</v>
       </c>
-      <c r="I123" t="s">
-        <v>1282</v>
-      </c>
-      <c r="J123" t="s">
-        <v>962</v>
-      </c>
       <c r="L123" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="N123" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="O123" s="1">
         <v>1</v>
@@ -22008,19 +22029,19 @@
         <v>611</v>
       </c>
       <c r="H124" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="I124" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J124" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="L124" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="N124" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O124" s="1">
         <v>1</v>
@@ -22034,25 +22055,25 @@
         <v>117</v>
       </c>
       <c r="C125" t="s">
-        <v>1669</v>
+        <v>1651</v>
       </c>
       <c r="E125" t="s">
         <v>612</v>
       </c>
       <c r="F125" t="s">
-        <v>1422</v>
+        <v>1413</v>
       </c>
       <c r="G125" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H125" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I125" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J125" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="K125" t="s">
         <v>770</v>
@@ -22061,7 +22082,7 @@
         <v>775</v>
       </c>
       <c r="N125" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="O125" s="1">
         <v>2</v>
@@ -22078,22 +22099,22 @@
         <v>613</v>
       </c>
       <c r="F126" t="s">
-        <v>1458</v>
+        <v>1448</v>
       </c>
       <c r="G126" t="s">
-        <v>1371</v>
+        <v>1362</v>
       </c>
       <c r="I126" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J126" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="K126" t="s">
         <v>770</v>
       </c>
       <c r="L126" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="O126" s="1">
         <v>2</v>
@@ -22110,25 +22131,25 @@
         <v>614</v>
       </c>
       <c r="H127" t="s">
+        <v>967</v>
+      </c>
+      <c r="I127" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J127" t="s">
+        <v>788</v>
+      </c>
+      <c r="K127" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L127" t="s">
         <v>968</v>
-      </c>
-      <c r="I127" t="s">
-        <v>1233</v>
-      </c>
-      <c r="J127" t="s">
-        <v>789</v>
-      </c>
-      <c r="K127" t="s">
-        <v>1040</v>
-      </c>
-      <c r="L127" t="s">
-        <v>969</v>
       </c>
       <c r="M127" t="s">
         <v>492</v>
       </c>
       <c r="N127" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="O127" s="1">
         <v>3</v>
@@ -22142,31 +22163,31 @@
         <v>120</v>
       </c>
       <c r="C128" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="D128" t="s">
-        <v>1372</v>
+        <v>1363</v>
       </c>
       <c r="E128" t="s">
         <v>615</v>
       </c>
       <c r="F128" t="s">
-        <v>1645</v>
+        <v>1629</v>
       </c>
       <c r="G128" t="s">
-        <v>1373</v>
+        <v>1364</v>
       </c>
       <c r="H128" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="I128" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="J128" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="N128" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="O128" s="1">
         <v>2</v>
@@ -22183,25 +22204,25 @@
         <v>616</v>
       </c>
       <c r="F129" t="s">
-        <v>1459</v>
+        <v>1449</v>
       </c>
       <c r="H129" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="I129" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J129" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="K129" t="s">
         <v>766</v>
       </c>
       <c r="L129" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N129" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="O129" s="1">
         <v>2</v>
@@ -22214,26 +22235,29 @@
       <c r="B130" t="s">
         <v>122</v>
       </c>
+      <c r="C130" t="s">
+        <v>1667</v>
+      </c>
       <c r="E130" t="s">
         <v>617</v>
       </c>
       <c r="F130" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="H130" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="I130" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J130" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="K130" t="s">
         <v>768</v>
       </c>
       <c r="N130" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O130" s="1">
         <v>2</v>
@@ -22250,16 +22274,16 @@
         <v>618</v>
       </c>
       <c r="H131" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="I131" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J131" t="s">
         <v>762</v>
       </c>
       <c r="N131" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O131" s="1">
         <v>1</v>
@@ -22276,22 +22300,22 @@
         <v>619</v>
       </c>
       <c r="H132" t="s">
+        <v>975</v>
+      </c>
+      <c r="I132" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J132" t="s">
         <v>976</v>
-      </c>
-      <c r="I132" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J132" t="s">
-        <v>977</v>
       </c>
       <c r="K132" t="s">
         <v>771</v>
       </c>
       <c r="L132" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="N132" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O132" s="1">
         <v>1</v>
@@ -22308,16 +22332,16 @@
         <v>620</v>
       </c>
       <c r="F133" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="H133" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="I133" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J133" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K133" t="s">
         <v>766</v>
@@ -22326,7 +22350,7 @@
         <v>780</v>
       </c>
       <c r="N133" t="s">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="O133" s="1">
         <v>2</v>
@@ -22343,10 +22367,10 @@
         <v>621</v>
       </c>
       <c r="H134" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="I134" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J134" t="s">
         <v>765</v>
@@ -22355,10 +22379,10 @@
         <v>766</v>
       </c>
       <c r="L134" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N134" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="O134" s="1">
         <v>1</v>
@@ -22372,31 +22396,31 @@
         <v>127</v>
       </c>
       <c r="C135" t="s">
-        <v>1427</v>
+        <v>1418</v>
       </c>
       <c r="E135" t="s">
         <v>622</v>
       </c>
       <c r="F135" t="s">
-        <v>1344</v>
+        <v>1335</v>
       </c>
       <c r="H135" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="I135" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J135" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="K135" t="s">
         <v>770</v>
       </c>
       <c r="L135" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="N135" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O135" s="1">
         <v>2</v>
@@ -22413,16 +22437,16 @@
         <v>623</v>
       </c>
       <c r="H136" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="I136" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J136" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="N136" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O136" s="1">
         <v>1</v>
@@ -22439,16 +22463,16 @@
         <v>129</v>
       </c>
       <c r="H137" t="s">
+        <v>983</v>
+      </c>
+      <c r="I137" t="s">
+        <v>1281</v>
+      </c>
+      <c r="J137" t="s">
         <v>984</v>
       </c>
-      <c r="I137" t="s">
-        <v>1285</v>
-      </c>
-      <c r="J137" t="s">
-        <v>985</v>
-      </c>
       <c r="N137" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O137" s="1">
         <v>2</v>
@@ -22465,16 +22489,16 @@
         <v>130</v>
       </c>
       <c r="H138" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I138" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J138" t="s">
         <v>771</v>
       </c>
       <c r="K138" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="L138" t="s">
         <v>780</v>
@@ -22483,7 +22507,7 @@
         <v>492</v>
       </c>
       <c r="N138" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="O138" s="1">
         <v>3</v>
@@ -22497,28 +22521,28 @@
         <v>131</v>
       </c>
       <c r="C139" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E139" t="s">
         <v>625</v>
       </c>
       <c r="F139" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H139" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="I139" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="J139" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L139" t="s">
         <v>775</v>
       </c>
       <c r="N139" t="s">
-        <v>1494</v>
+        <v>1481</v>
       </c>
       <c r="O139" s="1">
         <v>2</v>
@@ -22535,16 +22559,16 @@
         <v>626</v>
       </c>
       <c r="F140" t="s">
-        <v>1653</v>
+        <v>1636</v>
       </c>
       <c r="I140" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J140" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N140" t="s">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="O140" s="1">
         <v>1</v>
@@ -22558,22 +22582,22 @@
         <v>133</v>
       </c>
       <c r="D141" t="s">
-        <v>1374</v>
+        <v>1365</v>
       </c>
       <c r="E141" t="s">
         <v>627</v>
       </c>
       <c r="G141" t="s">
-        <v>1405</v>
+        <v>1396</v>
       </c>
       <c r="H141" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="I141" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J141" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="K141" t="s">
         <v>769</v>
@@ -22582,7 +22606,7 @@
         <v>775</v>
       </c>
       <c r="N141" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O141" s="1">
         <v>2</v>
@@ -22596,28 +22620,28 @@
         <v>334</v>
       </c>
       <c r="C142" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="E142" t="s">
         <v>628</v>
       </c>
       <c r="H142" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I142" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J142" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="K142" t="s">
         <v>770</v>
       </c>
       <c r="L142" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N142" t="s">
-        <v>1498</v>
+        <v>1485</v>
       </c>
       <c r="O142" s="1">
         <v>1</v>
@@ -22634,22 +22658,22 @@
         <v>629</v>
       </c>
       <c r="F143" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="I143" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J143" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K143" t="s">
         <v>766</v>
       </c>
       <c r="L143" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="N143" t="s">
-        <v>1490</v>
+        <v>1477</v>
       </c>
       <c r="O143" s="1">
         <v>2</v>
@@ -22663,22 +22687,22 @@
         <v>135</v>
       </c>
       <c r="C144" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="E144" t="s">
         <v>630</v>
       </c>
       <c r="H144" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="I144" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J144" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="N144" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O144" s="1">
         <v>2</v>
@@ -22695,19 +22719,19 @@
         <v>631</v>
       </c>
       <c r="F145" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="I145" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J145" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L145" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N145" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O145" s="1">
         <v>1</v>
@@ -22720,17 +22744,20 @@
       <c r="B146" t="s">
         <v>137</v>
       </c>
+      <c r="C146" t="s">
+        <v>1668</v>
+      </c>
       <c r="E146" t="s">
         <v>632</v>
       </c>
       <c r="H146" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I146" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J146" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K146" t="s">
         <v>771</v>
@@ -22739,7 +22766,7 @@
         <v>780</v>
       </c>
       <c r="N146" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="O146" s="1">
         <v>1</v>
@@ -22756,22 +22783,22 @@
         <v>633</v>
       </c>
       <c r="F147" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G147" t="s">
-        <v>1433</v>
+        <v>1424</v>
       </c>
       <c r="I147" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J147" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="M147" t="s">
         <v>492</v>
       </c>
       <c r="N147" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="O147" s="1">
         <v>3</v>
@@ -22788,25 +22815,25 @@
         <v>634</v>
       </c>
       <c r="F148" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="H148" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="I148" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J148" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K148" t="s">
         <v>770</v>
       </c>
       <c r="L148" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N148" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="O148" s="1">
         <v>2</v>
@@ -22820,22 +22847,22 @@
         <v>140</v>
       </c>
       <c r="C149" t="s">
-        <v>1429</v>
+        <v>1420</v>
       </c>
       <c r="E149" t="s">
         <v>635</v>
       </c>
       <c r="F149" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="I149" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J149" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="N149" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O149" s="1">
         <v>2</v>
@@ -22849,31 +22876,31 @@
         <v>141</v>
       </c>
       <c r="C150" t="s">
-        <v>1339</v>
+        <v>1330</v>
       </c>
       <c r="E150" t="s">
         <v>636</v>
       </c>
       <c r="F150" t="s">
-        <v>1478</v>
+        <v>1467</v>
       </c>
       <c r="G150" t="s">
-        <v>1375</v>
+        <v>1366</v>
       </c>
       <c r="I150" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J150" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L150" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="M150" t="s">
         <v>492</v>
       </c>
       <c r="N150" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="O150" s="1">
         <v>3</v>
@@ -22887,7 +22914,7 @@
         <v>142</v>
       </c>
       <c r="C151" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E151" t="s">
         <v>637</v>
@@ -22896,19 +22923,19 @@
         <v>142</v>
       </c>
       <c r="H151" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="I151" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="J151" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L151" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="N151" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O151" s="1">
         <v>1</v>
@@ -22925,25 +22952,25 @@
         <v>639</v>
       </c>
       <c r="F152" t="s">
-        <v>1420</v>
+        <v>1411</v>
       </c>
       <c r="G152" t="s">
-        <v>1376</v>
+        <v>1367</v>
       </c>
       <c r="H152" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="I152" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J152" t="s">
         <v>754</v>
       </c>
       <c r="L152" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="N152" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O152" s="1">
         <v>2</v>
@@ -22960,25 +22987,25 @@
         <v>641</v>
       </c>
       <c r="F153" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H153" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="I153" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J153" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K153" t="s">
         <v>770</v>
       </c>
       <c r="L153" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N153" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O153" s="1">
         <v>2</v>
@@ -22995,22 +23022,22 @@
         <v>642</v>
       </c>
       <c r="H154" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="I154" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="J154" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="K154" t="s">
         <v>770</v>
       </c>
       <c r="L154" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="N154" t="s">
-        <v>1489</v>
+        <v>1476</v>
       </c>
       <c r="O154" s="1">
         <v>1</v>
@@ -23027,16 +23054,16 @@
         <v>643</v>
       </c>
       <c r="F155" t="s">
-        <v>1395</v>
+        <v>1386</v>
       </c>
       <c r="I155" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J155" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L155" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="M155" t="s">
         <v>492</v>
@@ -23056,19 +23083,19 @@
         <v>644</v>
       </c>
       <c r="H156" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="I156" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J156" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="L156" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="N156" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="O156" s="1">
         <v>2</v>
@@ -23079,28 +23106,28 @@
         <v>348</v>
       </c>
       <c r="B157" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C157" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="E157" t="s">
         <v>521</v>
       </c>
       <c r="F157" t="s">
-        <v>1441</v>
+        <v>1431</v>
       </c>
       <c r="G157" t="s">
-        <v>1377</v>
+        <v>1368</v>
       </c>
       <c r="H157" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I157" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J157" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K157" t="s">
         <v>766</v>
@@ -23109,7 +23136,7 @@
         <v>780</v>
       </c>
       <c r="N157" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="O157" s="1">
         <v>2</v>
@@ -23123,25 +23150,25 @@
         <v>148</v>
       </c>
       <c r="C158" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="E158" t="s">
         <v>645</v>
       </c>
       <c r="F158" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="G158" t="s">
-        <v>1380</v>
+        <v>1371</v>
       </c>
       <c r="H158" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="I158" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J158" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="K158" t="s">
         <v>770</v>
@@ -23150,7 +23177,7 @@
         <v>775</v>
       </c>
       <c r="N158" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
       <c r="O158" s="1">
         <v>2</v>
@@ -23164,19 +23191,19 @@
         <v>149</v>
       </c>
       <c r="C159" t="s">
-        <v>1403</v>
+        <v>1394</v>
       </c>
       <c r="E159" t="s">
         <v>646</v>
       </c>
       <c r="F159" t="s">
-        <v>1346</v>
+        <v>1337</v>
       </c>
       <c r="I159" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J159" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K159" t="s">
         <v>766</v>
@@ -23185,7 +23212,7 @@
         <v>780</v>
       </c>
       <c r="N159" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="O159" s="1">
         <v>2</v>
@@ -23202,16 +23229,16 @@
         <v>647</v>
       </c>
       <c r="F160" t="s">
-        <v>1381</v>
+        <v>1372</v>
       </c>
       <c r="H160" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="I160" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J160" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K160" t="s">
         <v>766</v>
@@ -23220,7 +23247,7 @@
         <v>775</v>
       </c>
       <c r="N160" t="s">
-        <v>1491</v>
+        <v>1478</v>
       </c>
       <c r="O160" s="1">
         <v>2</v>
@@ -23237,22 +23264,22 @@
         <v>648</v>
       </c>
       <c r="F161" t="s">
-        <v>1342</v>
+        <v>1333</v>
       </c>
       <c r="H161" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I161" t="s">
         <v>1016</v>
-      </c>
-      <c r="I161" t="s">
-        <v>1017</v>
       </c>
       <c r="J161" t="s">
         <v>778</v>
       </c>
       <c r="L161" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="N161" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O161" s="1">
         <v>2</v>
@@ -23269,28 +23296,28 @@
         <v>649</v>
       </c>
       <c r="F162" t="s">
-        <v>1417</v>
+        <v>1408</v>
       </c>
       <c r="G162" t="s">
-        <v>1378</v>
+        <v>1369</v>
       </c>
       <c r="H162" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="I162" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J162" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="K162" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="L162" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N162" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="O162" s="1">
         <v>1</v>
@@ -23307,22 +23334,22 @@
         <v>650</v>
       </c>
       <c r="F163" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
       <c r="G163" t="s">
-        <v>1379</v>
+        <v>1370</v>
       </c>
       <c r="H163" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="I163" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J163" t="s">
         <v>758</v>
       </c>
       <c r="N163" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O163" s="1">
         <v>1</v>
@@ -23336,19 +23363,19 @@
         <v>154</v>
       </c>
       <c r="C164" t="s">
-        <v>1646</v>
+        <v>1669</v>
       </c>
       <c r="D164" t="s">
-        <v>1469</v>
+        <v>1458</v>
       </c>
       <c r="E164" t="s">
         <v>651</v>
       </c>
       <c r="F164" t="s">
-        <v>1425</v>
+        <v>1416</v>
       </c>
       <c r="I164" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J164" t="s">
         <v>770</v>
@@ -23357,13 +23384,13 @@
         <v>770</v>
       </c>
       <c r="L164" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="M164" t="s">
         <v>492</v>
       </c>
       <c r="N164" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="O164" s="1">
         <v>3</v>
@@ -23380,16 +23407,16 @@
         <v>652</v>
       </c>
       <c r="H165" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="I165" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J165" t="s">
         <v>777</v>
       </c>
       <c r="L165" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O165" s="1">
         <v>1</v>
@@ -23403,31 +23430,31 @@
         <v>156</v>
       </c>
       <c r="C166" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E166" t="s">
         <v>653</v>
       </c>
       <c r="F166" t="s">
-        <v>1460</v>
+        <v>1450</v>
       </c>
       <c r="I166" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J166" t="s">
+        <v>1026</v>
+      </c>
+      <c r="K166" t="s">
         <v>1027</v>
       </c>
-      <c r="K166" t="s">
-        <v>1028</v>
-      </c>
       <c r="L166" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M166" t="s">
         <v>492</v>
       </c>
       <c r="N166" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="O166" s="1">
         <v>3</v>
@@ -23444,19 +23471,19 @@
         <v>654</v>
       </c>
       <c r="I167" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J167" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="K167" t="s">
         <v>762</v>
       </c>
       <c r="L167" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="N167" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="O167" s="1">
         <v>1</v>
@@ -23470,25 +23497,25 @@
         <v>158</v>
       </c>
       <c r="C168" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
       <c r="E168" t="s">
         <v>656</v>
       </c>
       <c r="H168" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="I168" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="J168" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="L168" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N168" t="s">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="O168" s="1">
         <v>2</v>
@@ -23499,25 +23526,25 @@
         <v>469</v>
       </c>
       <c r="B169" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C169" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="E169" t="s">
         <v>655</v>
       </c>
       <c r="H169" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="I169" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="J169" t="s">
         <v>777</v>
       </c>
       <c r="N169" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O169" s="1">
         <v>1</v>
@@ -23534,25 +23561,25 @@
         <v>657</v>
       </c>
       <c r="F170" t="s">
-        <v>1396</v>
+        <v>1387</v>
       </c>
       <c r="H170" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J170" t="s">
         <v>1035</v>
-      </c>
-      <c r="I170" t="s">
-        <v>1230</v>
-      </c>
-      <c r="J170" t="s">
-        <v>1036</v>
       </c>
       <c r="K170" t="s">
         <v>766</v>
       </c>
       <c r="L170" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N170" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="O170" s="1">
         <v>1</v>
@@ -23569,25 +23596,25 @@
         <v>658</v>
       </c>
       <c r="F171" t="s">
-        <v>1652</v>
+        <v>1635</v>
       </c>
       <c r="G171" t="s">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="I171" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J171" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="K171" t="s">
         <v>770</v>
       </c>
       <c r="L171" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N171" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="O171" s="1">
         <v>2</v>
@@ -23604,22 +23631,22 @@
         <v>659</v>
       </c>
       <c r="F172" t="s">
-        <v>1656</v>
+        <v>1639</v>
       </c>
       <c r="H172" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="I172" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="J172" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="M172" t="s">
         <v>492</v>
       </c>
       <c r="N172" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="O172" s="1">
         <v>3</v>
@@ -23636,25 +23663,25 @@
         <v>162</v>
       </c>
       <c r="F173" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H173" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="I173" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="J173" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K173" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L173" t="s">
         <v>780</v>
       </c>
       <c r="N173" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="O173" s="1">
         <v>1</v>
@@ -23668,31 +23695,31 @@
         <v>163</v>
       </c>
       <c r="C174" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E174" t="s">
         <v>660</v>
       </c>
       <c r="F174" t="s">
-        <v>1416</v>
+        <v>1407</v>
       </c>
       <c r="H174" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="I174" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J174" t="s">
         <v>751</v>
       </c>
       <c r="K174" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L174" t="s">
         <v>1040</v>
       </c>
-      <c r="L174" t="s">
-        <v>1041</v>
-      </c>
       <c r="N174" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="O174" s="1">
         <v>2</v>
@@ -23709,22 +23736,22 @@
         <v>661</v>
       </c>
       <c r="F175" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="H175" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I175" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J175" t="s">
         <v>777</v>
       </c>
       <c r="L175" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="N175" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O175" s="1">
         <v>2</v>
@@ -23741,16 +23768,16 @@
         <v>662</v>
       </c>
       <c r="H176" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="I176" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="J176" t="s">
         <v>762</v>
       </c>
       <c r="N176" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O176" s="1">
         <v>1</v>
@@ -23764,28 +23791,28 @@
         <v>166</v>
       </c>
       <c r="C177" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="E177" t="s">
         <v>663</v>
       </c>
       <c r="F177" t="s">
-        <v>1424</v>
+        <v>1415</v>
       </c>
       <c r="I177" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J177" t="s">
         <v>762</v>
       </c>
       <c r="L177" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M177" t="s">
         <v>492</v>
       </c>
       <c r="N177" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O177" s="1">
         <v>3</v>
@@ -23799,22 +23826,22 @@
         <v>167</v>
       </c>
       <c r="C178" t="s">
-        <v>1647</v>
+        <v>1630</v>
       </c>
       <c r="E178" t="s">
         <v>664</v>
       </c>
       <c r="H178" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="I178" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J178" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N178" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O178" s="1">
         <v>1</v>
@@ -23831,10 +23858,10 @@
         <v>665</v>
       </c>
       <c r="I179" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J179" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="K179" t="s">
         <v>766</v>
@@ -23846,7 +23873,7 @@
         <v>492</v>
       </c>
       <c r="N179" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="O179" s="1">
         <v>3</v>
@@ -23863,19 +23890,19 @@
         <v>666</v>
       </c>
       <c r="H180" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="I180" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J180" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K180" t="s">
         <v>770</v>
       </c>
       <c r="L180" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="O180" s="1">
         <v>1</v>
@@ -23889,22 +23916,22 @@
         <v>170</v>
       </c>
       <c r="C181" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="E181" t="s">
         <v>667</v>
       </c>
       <c r="H181" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="I181" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J181" t="s">
         <v>762</v>
       </c>
       <c r="N181" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O181" s="1">
         <v>2</v>
@@ -23921,16 +23948,16 @@
         <v>668</v>
       </c>
       <c r="H182" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I182" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="J182" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N182" t="s">
-        <v>1492</v>
+        <v>1479</v>
       </c>
       <c r="O182" s="1">
         <v>1</v>
@@ -23944,22 +23971,22 @@
         <v>172</v>
       </c>
       <c r="C183" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="E183" t="s">
         <v>587</v>
       </c>
       <c r="H183" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="I183" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J183" t="s">
+        <v>838</v>
+      </c>
+      <c r="L183" t="s">
         <v>839</v>
-      </c>
-      <c r="L183" t="s">
-        <v>840</v>
       </c>
       <c r="O183" s="1">
         <v>1</v>
@@ -23973,22 +24000,22 @@
         <v>173</v>
       </c>
       <c r="C184" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E184" t="s">
         <v>670</v>
       </c>
       <c r="F184" t="s">
-        <v>1472</v>
+        <v>1461</v>
       </c>
       <c r="H184" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I184" t="s">
+        <v>829</v>
+      </c>
+      <c r="J184" t="s">
         <v>1048</v>
-      </c>
-      <c r="I184" t="s">
-        <v>830</v>
-      </c>
-      <c r="J184" t="s">
-        <v>1049</v>
       </c>
       <c r="K184" t="s">
         <v>770</v>
@@ -23997,7 +24024,7 @@
         <v>780</v>
       </c>
       <c r="N184" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="O184" s="1">
         <v>2</v>
@@ -24008,19 +24035,19 @@
         <v>272</v>
       </c>
       <c r="B185" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C185" t="s">
         <v>1050</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1051</v>
       </c>
       <c r="E185" t="s">
         <v>671</v>
       </c>
       <c r="H185" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I185" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J185" t="s">
         <v>779</v>
@@ -24032,7 +24059,7 @@
         <v>780</v>
       </c>
       <c r="N185" t="s">
-        <v>1487</v>
+        <v>1474</v>
       </c>
       <c r="O185" s="1">
         <v>1</v>
@@ -24043,10 +24070,10 @@
         <v>381</v>
       </c>
       <c r="B186" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C186" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="E186" t="s">
         <v>686</v>
@@ -24058,16 +24085,16 @@
         <v>114</v>
       </c>
       <c r="I186" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J186" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="L186" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="N186" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O186" s="1">
         <v>2</v>
@@ -24081,22 +24108,22 @@
         <v>174</v>
       </c>
       <c r="C187" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E187" t="s">
         <v>672</v>
       </c>
       <c r="H187" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="I187" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J187" t="s">
         <v>760</v>
       </c>
       <c r="L187" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="O187" s="1">
         <v>1</v>
@@ -24110,28 +24137,28 @@
         <v>175</v>
       </c>
       <c r="C188" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E188" t="s">
         <v>673</v>
       </c>
       <c r="F188" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G188" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1274</v>
+      </c>
+      <c r="J188" t="s">
         <v>1056</v>
-      </c>
-      <c r="G188" t="s">
-        <v>1384</v>
-      </c>
-      <c r="I188" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J188" t="s">
-        <v>1057</v>
       </c>
       <c r="M188" t="s">
         <v>492</v>
       </c>
       <c r="N188" t="s">
-        <v>1494</v>
+        <v>1481</v>
       </c>
       <c r="O188" s="1">
         <v>3</v>
@@ -24148,16 +24175,16 @@
         <v>674</v>
       </c>
       <c r="H189" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="I189" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="J189" t="s">
         <v>754</v>
       </c>
       <c r="N189" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O189" s="1">
         <v>1</v>
@@ -24174,16 +24201,16 @@
         <v>675</v>
       </c>
       <c r="F190" t="s">
-        <v>1419</v>
+        <v>1410</v>
       </c>
       <c r="H190" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1274</v>
+      </c>
+      <c r="J190" t="s">
         <v>1059</v>
-      </c>
-      <c r="I190" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J190" t="s">
-        <v>1060</v>
       </c>
       <c r="K190" t="s">
         <v>770</v>
@@ -24192,7 +24219,7 @@
         <v>775</v>
       </c>
       <c r="N190" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O190" s="1">
         <v>2</v>
@@ -24209,16 +24236,16 @@
         <v>676</v>
       </c>
       <c r="H191" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I191" t="s">
+        <v>828</v>
+      </c>
+      <c r="J191" t="s">
         <v>1061</v>
       </c>
-      <c r="I191" t="s">
-        <v>829</v>
-      </c>
-      <c r="J191" t="s">
-        <v>1062</v>
-      </c>
       <c r="N191" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O191" s="1">
         <v>1</v>
@@ -24235,10 +24262,10 @@
         <v>677</v>
       </c>
       <c r="F192" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="I192" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J192" t="s">
         <v>777</v>
@@ -24253,7 +24280,7 @@
         <v>492</v>
       </c>
       <c r="N192" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="O192" s="1">
         <v>3</v>
@@ -24267,37 +24294,37 @@
         <v>179</v>
       </c>
       <c r="C193" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="E193" t="s">
         <v>678</v>
       </c>
       <c r="F193" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="G193" t="s">
-        <v>1386</v>
+        <v>1377</v>
       </c>
       <c r="H193" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I193" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="J193" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K193" t="s">
         <v>769</v>
       </c>
       <c r="L193" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M193" t="s">
         <v>492</v>
       </c>
       <c r="N193" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="O193" s="1">
         <v>3</v>
@@ -24311,22 +24338,22 @@
         <v>180</v>
       </c>
       <c r="C194" t="s">
-        <v>1642</v>
+        <v>1673</v>
       </c>
       <c r="D194" t="s">
-        <v>1502</v>
+        <v>1489</v>
       </c>
       <c r="E194" t="s">
         <v>679</v>
       </c>
       <c r="F194" t="s">
-        <v>1414</v>
+        <v>1405</v>
       </c>
       <c r="I194" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J194" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="K194" t="s">
         <v>766</v>
@@ -24335,7 +24362,7 @@
         <v>780</v>
       </c>
       <c r="N194" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="O194" s="1">
         <v>2</v>
@@ -24349,22 +24376,22 @@
         <v>737</v>
       </c>
       <c r="C195" t="s">
-        <v>1070</v>
+        <v>1670</v>
       </c>
       <c r="E195" t="s">
         <v>687</v>
       </c>
       <c r="I195" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J195" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K195" t="s">
         <v>1066</v>
       </c>
-      <c r="K195" t="s">
-        <v>1067</v>
-      </c>
       <c r="N195" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="O195" s="1">
         <v>2</v>
@@ -24378,25 +24405,25 @@
         <v>181</v>
       </c>
       <c r="C196" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="E196" t="s">
         <v>680</v>
       </c>
       <c r="F196" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="I196" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J196" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K196" t="s">
         <v>771</v>
       </c>
       <c r="N196" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O196" s="1">
         <v>2</v>
@@ -24410,25 +24437,25 @@
         <v>182</v>
       </c>
       <c r="C197" t="s">
-        <v>1480</v>
+        <v>1671</v>
       </c>
       <c r="E197" t="s">
         <v>681</v>
       </c>
       <c r="I197" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J197" t="s">
         <v>766</v>
       </c>
       <c r="L197" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="M197" t="s">
         <v>492</v>
       </c>
       <c r="N197" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="O197" s="1">
         <v>3</v>
@@ -24442,37 +24469,37 @@
         <v>481</v>
       </c>
       <c r="C198" t="s">
-        <v>1461</v>
+        <v>1451</v>
       </c>
       <c r="D198" t="s">
-        <v>1388</v>
+        <v>1379</v>
       </c>
       <c r="E198" t="s">
         <v>682</v>
       </c>
       <c r="F198" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G198" t="s">
-        <v>1387</v>
+        <v>1378</v>
       </c>
       <c r="H198" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="I198" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J198" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L198" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="M198" t="s">
         <v>492</v>
       </c>
       <c r="N198" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O198" s="1">
         <v>3</v>
@@ -24486,25 +24513,25 @@
         <v>183</v>
       </c>
       <c r="C199" t="s">
-        <v>1479</v>
+        <v>1658</v>
       </c>
       <c r="E199" t="s">
         <v>683</v>
       </c>
       <c r="F199" t="s">
-        <v>1073</v>
+        <v>1659</v>
       </c>
       <c r="I199" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="J199" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="K199" t="s">
         <v>770</v>
       </c>
       <c r="L199" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="M199" t="s">
         <v>492</v>
@@ -24524,22 +24551,22 @@
         <v>684</v>
       </c>
       <c r="F200" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="I200" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J200" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K200" t="s">
         <v>766</v>
       </c>
       <c r="L200" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="N200" t="s">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="O200" s="1">
         <v>2</v>
@@ -24556,13 +24583,13 @@
         <v>685</v>
       </c>
       <c r="I201" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J201" t="s">
         <v>760</v>
       </c>
       <c r="L201" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="M201" t="s">
         <v>492</v>
@@ -24582,16 +24609,16 @@
         <v>736</v>
       </c>
       <c r="F202" t="s">
-        <v>1318</v>
+        <v>1311</v>
       </c>
       <c r="I202" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="J202" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L202" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="M202" t="s">
         <v>492</v>
@@ -24608,19 +24635,19 @@
         <v>187</v>
       </c>
       <c r="C203" t="s">
-        <v>1666</v>
+        <v>1674</v>
       </c>
       <c r="E203" t="s">
         <v>688</v>
       </c>
       <c r="F203" t="s">
-        <v>1666</v>
+        <v>1675</v>
       </c>
       <c r="I203" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J203" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="K203" t="s">
         <v>768</v>
@@ -24629,7 +24656,7 @@
         <v>780</v>
       </c>
       <c r="N203" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="O203" s="1">
         <v>2</v>
@@ -24646,19 +24673,19 @@
         <v>689</v>
       </c>
       <c r="H204" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I204" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J204" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="M204" t="s">
         <v>492</v>
       </c>
       <c r="N204" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="O204" s="1">
         <v>3</v>
@@ -24675,13 +24702,13 @@
         <v>690</v>
       </c>
       <c r="H205" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="I205" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J205" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="K205" t="s">
         <v>771</v>
@@ -24690,7 +24717,7 @@
         <v>780</v>
       </c>
       <c r="N205" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="O205" s="1">
         <v>1</v>
@@ -24707,19 +24734,19 @@
         <v>691</v>
       </c>
       <c r="H206" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="I206" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="J206" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="L206" t="s">
+        <v>1156</v>
+      </c>
+      <c r="N206" t="s">
         <v>1159</v>
-      </c>
-      <c r="N206" t="s">
-        <v>1162</v>
       </c>
       <c r="O206" s="1">
         <v>1</v>
@@ -24733,19 +24760,19 @@
         <v>191</v>
       </c>
       <c r="C207" t="s">
-        <v>1428</v>
+        <v>1419</v>
       </c>
       <c r="E207" t="s">
         <v>584</v>
       </c>
       <c r="I207" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J207" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="N207" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
       <c r="O207" s="1">
         <v>2</v>
@@ -24762,16 +24789,16 @@
         <v>692</v>
       </c>
       <c r="H208" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="I208" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J208" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="N208" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O208" s="1">
         <v>2</v>
@@ -24788,19 +24815,19 @@
         <v>193</v>
       </c>
       <c r="H209" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="I209" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="J209" t="s">
         <v>762</v>
       </c>
       <c r="L209" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N209" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="O209" s="1">
         <v>1</v>
@@ -24814,19 +24841,19 @@
         <v>483</v>
       </c>
       <c r="C210" t="s">
-        <v>1338</v>
+        <v>1672</v>
       </c>
       <c r="E210" t="s">
         <v>511</v>
       </c>
       <c r="F210" t="s">
-        <v>1322</v>
+        <v>1653</v>
       </c>
       <c r="I210" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J210" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="K210" t="s">
         <v>758</v>
@@ -24838,7 +24865,7 @@
         <v>492</v>
       </c>
       <c r="N210" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="O210" s="1">
         <v>3</v>
@@ -24852,31 +24879,31 @@
         <v>194</v>
       </c>
       <c r="C211" t="s">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="E211" t="s">
         <v>693</v>
       </c>
       <c r="F211" t="s">
-        <v>1641</v>
+        <v>1627</v>
       </c>
       <c r="H211" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="I211" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J211" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L211" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M211" t="s">
         <v>492</v>
       </c>
       <c r="N211" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="O211" s="1">
         <v>3</v>
@@ -24893,13 +24920,13 @@
         <v>694</v>
       </c>
       <c r="H212" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="I212" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="J212" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="K212" t="s">
         <v>769</v>
@@ -24908,7 +24935,7 @@
         <v>780</v>
       </c>
       <c r="N212" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="O212" s="1">
         <v>1</v>
@@ -24925,19 +24952,19 @@
         <v>695</v>
       </c>
       <c r="H213" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="I213" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J213" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="L213" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N213" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O213" s="1">
         <v>1</v>
@@ -24954,22 +24981,22 @@
         <v>696</v>
       </c>
       <c r="F214" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="H214" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="I214" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="J214" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="L214" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N214" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O214" s="1">
         <v>1</v>
@@ -24983,16 +25010,16 @@
         <v>198</v>
       </c>
       <c r="C215" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="E215" t="s">
         <v>697</v>
       </c>
       <c r="H215" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="I215" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="J215" t="s">
         <v>778</v>
@@ -25004,7 +25031,7 @@
         <v>780</v>
       </c>
       <c r="N215" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="O215" s="1">
         <v>1</v>
@@ -25021,19 +25048,19 @@
         <v>698</v>
       </c>
       <c r="H216" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="I216" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="J216" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L216" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="N216" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O216" s="1">
         <v>1</v>
@@ -25050,25 +25077,25 @@
         <v>699</v>
       </c>
       <c r="F217" t="s">
-        <v>1435</v>
+        <v>1660</v>
       </c>
       <c r="G217" t="s">
-        <v>1360</v>
+        <v>1351</v>
       </c>
       <c r="I217" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J217" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="K217" t="s">
         <v>770</v>
       </c>
       <c r="L217" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N217" t="s">
-        <v>1489</v>
+        <v>1476</v>
       </c>
       <c r="O217" s="1">
         <v>2</v>
@@ -25082,16 +25109,16 @@
         <v>738</v>
       </c>
       <c r="C218" t="s">
-        <v>1383</v>
+        <v>1374</v>
       </c>
       <c r="E218" t="s">
         <v>638</v>
       </c>
       <c r="F218" t="s">
-        <v>1410</v>
+        <v>1401</v>
       </c>
       <c r="I218" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J218" t="s">
         <v>778</v>
@@ -25103,7 +25130,7 @@
         <v>780</v>
       </c>
       <c r="N218" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="O218" s="1">
         <v>2</v>
@@ -25117,22 +25144,22 @@
         <v>201</v>
       </c>
       <c r="C219" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="E219" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="F219" t="s">
         <v>700</v>
       </c>
       <c r="H219" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="I219" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="J219" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="K219" t="s">
         <v>766</v>
@@ -25141,7 +25168,7 @@
         <v>780</v>
       </c>
       <c r="N219" t="s">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="O219" s="1">
         <v>1</v>
@@ -25158,19 +25185,19 @@
         <v>701</v>
       </c>
       <c r="F220" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="H220" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="I220" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J220" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="N220" t="s">
-        <v>1493</v>
+        <v>1480</v>
       </c>
       <c r="O220" s="1">
         <v>1</v>
@@ -25187,25 +25214,25 @@
         <v>702</v>
       </c>
       <c r="F221" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
       <c r="G221" t="s">
-        <v>1398</v>
+        <v>1389</v>
       </c>
       <c r="H221" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="I221" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="J221" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="K221" t="s">
         <v>771</v>
       </c>
       <c r="N221" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="O221" s="1">
         <v>1</v>
@@ -25219,22 +25246,22 @@
         <v>204</v>
       </c>
       <c r="C222" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="E222" t="s">
         <v>703</v>
       </c>
       <c r="F222" t="s">
-        <v>1474</v>
+        <v>1463</v>
       </c>
       <c r="H222" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="I222" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J222" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="K222" t="s">
         <v>770</v>
@@ -25243,7 +25270,7 @@
         <v>780</v>
       </c>
       <c r="N222" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="O222" s="1">
         <v>2</v>
@@ -25260,13 +25287,13 @@
         <v>704</v>
       </c>
       <c r="H223" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="I223" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="J223" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="K223" t="s">
         <v>770</v>
@@ -25275,7 +25302,7 @@
         <v>780</v>
       </c>
       <c r="N223" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="O223" s="1">
         <v>2</v>
@@ -25292,16 +25319,16 @@
         <v>705</v>
       </c>
       <c r="H224" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="I224" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J224" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L224" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O224" s="1">
         <v>1</v>
@@ -25318,10 +25345,10 @@
         <v>706</v>
       </c>
       <c r="H225" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="I225" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J225" t="s">
         <v>762</v>
@@ -25330,10 +25357,10 @@
         <v>766</v>
       </c>
       <c r="L225" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N225" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="O225" s="1">
         <v>1</v>
@@ -25350,28 +25377,28 @@
         <v>708</v>
       </c>
       <c r="F226" t="s">
-        <v>1421</v>
+        <v>1412</v>
       </c>
       <c r="G226" t="s">
-        <v>1389</v>
+        <v>1380</v>
       </c>
       <c r="H226" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="I226" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J226" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="K226" t="s">
         <v>770</v>
       </c>
       <c r="L226" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="N226" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="O226" s="1">
         <v>2</v>
@@ -25388,13 +25415,13 @@
         <v>709</v>
       </c>
       <c r="F227" t="s">
-        <v>1357</v>
+        <v>1348</v>
       </c>
       <c r="I227" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J227" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="K227" t="s">
         <v>766</v>
@@ -25406,7 +25433,7 @@
         <v>492</v>
       </c>
       <c r="N227" t="s">
-        <v>1497</v>
+        <v>1484</v>
       </c>
       <c r="O227" s="1">
         <v>3</v>
@@ -25423,16 +25450,16 @@
         <v>710</v>
       </c>
       <c r="H228" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="I228" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J228" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="N228" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
       <c r="O228" s="1">
         <v>1</v>
@@ -25446,25 +25473,25 @@
         <v>485</v>
       </c>
       <c r="C229" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="E229" t="s">
         <v>711</v>
       </c>
       <c r="F229" t="s">
-        <v>1411</v>
+        <v>1402</v>
       </c>
       <c r="G229" t="s">
-        <v>1434</v>
+        <v>1425</v>
       </c>
       <c r="J229" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K229" t="s">
         <v>766</v>
       </c>
       <c r="L229" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="M229" t="s">
         <v>492</v>
@@ -25481,19 +25508,19 @@
         <v>211</v>
       </c>
       <c r="C230" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E230" t="s">
         <v>712</v>
       </c>
       <c r="I230" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="J230" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L230" t="s">
-        <v>1659</v>
+        <v>1642</v>
       </c>
       <c r="M230" t="s">
         <v>492</v>
@@ -25513,16 +25540,16 @@
         <v>713</v>
       </c>
       <c r="H231" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="I231" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J231" t="s">
         <v>777</v>
       </c>
       <c r="N231" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O231" s="1">
         <v>1</v>
@@ -25539,13 +25566,13 @@
         <v>714</v>
       </c>
       <c r="H232" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="I232" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="J232" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K232" t="s">
         <v>766</v>
@@ -25554,7 +25581,7 @@
         <v>780</v>
       </c>
       <c r="N232" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="O232" s="1">
         <v>2</v>
@@ -25568,22 +25595,22 @@
         <v>214</v>
       </c>
       <c r="C233" t="s">
-        <v>1649</v>
+        <v>1632</v>
       </c>
       <c r="E233" t="s">
         <v>715</v>
       </c>
       <c r="F233" t="s">
-        <v>1650</v>
+        <v>1633</v>
       </c>
       <c r="H233" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="I233" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J233" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="K233" t="s">
         <v>766</v>
@@ -25592,7 +25619,7 @@
         <v>780</v>
       </c>
       <c r="N233" t="s">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="O233" s="1">
         <v>2</v>
@@ -25606,31 +25633,31 @@
         <v>215</v>
       </c>
       <c r="C234" t="s">
-        <v>1668</v>
+        <v>1650</v>
       </c>
       <c r="E234" t="s">
         <v>716</v>
       </c>
       <c r="F234" t="s">
-        <v>1315</v>
+        <v>1661</v>
       </c>
       <c r="I234" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J234" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K234" t="s">
         <v>766</v>
       </c>
       <c r="L234" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M234" t="s">
         <v>492</v>
       </c>
       <c r="N234" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="O234" s="1">
         <v>3</v>
@@ -25647,10 +25674,10 @@
         <v>717</v>
       </c>
       <c r="F235" t="s">
-        <v>1426</v>
+        <v>1417</v>
       </c>
       <c r="I235" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J235" t="s">
         <v>762</v>
@@ -25659,10 +25686,10 @@
         <v>769</v>
       </c>
       <c r="L235" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N235" t="s">
-        <v>1497</v>
+        <v>1484</v>
       </c>
       <c r="O235" s="1">
         <v>2</v>
@@ -25676,22 +25703,22 @@
         <v>217</v>
       </c>
       <c r="C236" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="E236" t="s">
         <v>718</v>
       </c>
       <c r="F236" t="s">
-        <v>1667</v>
+        <v>1649</v>
       </c>
       <c r="I236" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J236" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="N236" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
       <c r="O236" s="1">
         <v>2</v>
@@ -25705,34 +25732,34 @@
         <v>744</v>
       </c>
       <c r="C237" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="D237" t="s">
-        <v>1361</v>
+        <v>1352</v>
       </c>
       <c r="E237" t="s">
         <v>745</v>
       </c>
       <c r="F237" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="G237" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="I237" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="J237" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L237" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="M237" t="s">
         <v>492</v>
       </c>
       <c r="N237" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O237" s="1">
         <v>3</v>
@@ -25749,10 +25776,10 @@
         <v>719</v>
       </c>
       <c r="H238" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="I238" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J238" t="s">
         <v>762</v>
@@ -25761,10 +25788,10 @@
         <v>762</v>
       </c>
       <c r="L238" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="N238" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="O238" s="1">
         <v>1</v>
@@ -25781,10 +25808,10 @@
         <v>720</v>
       </c>
       <c r="H239" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="I239" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="J239" t="s">
         <v>762</v>
@@ -25793,10 +25820,10 @@
         <v>766</v>
       </c>
       <c r="L239" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N239" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="O239" s="1">
         <v>1</v>
@@ -25813,28 +25840,28 @@
         <v>721</v>
       </c>
       <c r="F240" t="s">
-        <v>1423</v>
+        <v>1414</v>
       </c>
       <c r="G240" t="s">
-        <v>1404</v>
+        <v>1395</v>
       </c>
       <c r="H240" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="I240" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J240" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K240" t="s">
         <v>766</v>
       </c>
       <c r="L240" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N240" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="O240" s="1">
         <v>2</v>
@@ -25848,22 +25875,22 @@
         <v>221</v>
       </c>
       <c r="C241" t="s">
-        <v>1654</v>
+        <v>1637</v>
       </c>
       <c r="E241" t="s">
         <v>722</v>
       </c>
       <c r="F241" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
       <c r="I241" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="J241" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L241" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M241" t="s">
         <v>492</v>
@@ -25883,22 +25910,22 @@
         <v>723</v>
       </c>
       <c r="F242" t="s">
-        <v>1413</v>
+        <v>1404</v>
       </c>
       <c r="I242" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J242" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="K242" t="s">
         <v>770</v>
       </c>
       <c r="L242" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N242" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="O242" s="1">
         <v>2</v>
@@ -25915,16 +25942,16 @@
         <v>724</v>
       </c>
       <c r="H243" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="I243" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J243" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="N243" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O243" s="1">
         <v>1</v>
@@ -25941,22 +25968,22 @@
         <v>725</v>
       </c>
       <c r="H244" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="I244" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J244" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K244" t="s">
         <v>766</v>
       </c>
       <c r="L244" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="N244" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O244" s="1">
         <v>2</v>
@@ -25973,16 +26000,16 @@
         <v>726</v>
       </c>
       <c r="H245" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="I245" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J245" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N245" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O245" s="1">
         <v>1</v>
@@ -25999,13 +26026,13 @@
         <v>727</v>
       </c>
       <c r="H246" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="I246" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J246" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K246" t="s">
         <v>770</v>
@@ -26014,7 +26041,7 @@
         <v>775</v>
       </c>
       <c r="N246" t="s">
-        <v>1497</v>
+        <v>1484</v>
       </c>
       <c r="O246" s="1">
         <v>1</v>
@@ -26031,28 +26058,28 @@
         <v>728</v>
       </c>
       <c r="F247" t="s">
-        <v>1359</v>
+        <v>1350</v>
       </c>
       <c r="G247" t="s">
-        <v>1391</v>
+        <v>1382</v>
       </c>
       <c r="H247" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="I247" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J247" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="K247" t="s">
         <v>766</v>
       </c>
       <c r="L247" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N247" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="O247" s="1">
         <v>2</v>
@@ -26069,22 +26096,22 @@
         <v>729</v>
       </c>
       <c r="F248" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="I248" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J248" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="K248" t="s">
         <v>770</v>
       </c>
       <c r="L248" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="N248" t="s">
-        <v>1493</v>
+        <v>1480</v>
       </c>
       <c r="O248" s="1">
         <v>2</v>
@@ -26101,13 +26128,13 @@
         <v>730</v>
       </c>
       <c r="H249" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="I249" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="J249" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="K249" t="s">
         <v>766</v>
@@ -26116,7 +26143,7 @@
         <v>780</v>
       </c>
       <c r="N249" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="O249" s="1">
         <v>1</v>
@@ -26133,19 +26160,19 @@
         <v>731</v>
       </c>
       <c r="F250" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="G250" t="s">
-        <v>1392</v>
+        <v>1383</v>
       </c>
       <c r="H250" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="I250" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J250" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="K250" t="s">
         <v>770</v>
@@ -26154,7 +26181,7 @@
         <v>780</v>
       </c>
       <c r="N250" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="O250" s="1">
         <v>1</v>
@@ -26168,16 +26195,16 @@
         <v>231</v>
       </c>
       <c r="C251" t="s">
-        <v>1443</v>
+        <v>1433</v>
       </c>
       <c r="E251" t="s">
         <v>732</v>
       </c>
       <c r="F251" t="s">
-        <v>1442</v>
+        <v>1432</v>
       </c>
       <c r="I251" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J251" t="s">
         <v>762</v>
@@ -26186,7 +26213,7 @@
         <v>766</v>
       </c>
       <c r="L251" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="M251" t="s">
         <v>492</v>
@@ -26206,22 +26233,22 @@
         <v>733</v>
       </c>
       <c r="F252" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G252" t="s">
-        <v>1393</v>
+        <v>1384</v>
       </c>
       <c r="H252" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I252" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="J252" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="N252" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O252" s="1">
         <v>2</v>
@@ -26238,19 +26265,19 @@
         <v>734</v>
       </c>
       <c r="H253" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="I253" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J253" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="K253" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="L253" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="O253" s="1">
         <v>2</v>
@@ -26267,25 +26294,25 @@
         <v>735</v>
       </c>
       <c r="F254" t="s">
-        <v>1475</v>
+        <v>1464</v>
       </c>
       <c r="H254" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="I254" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J254" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="K254" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L254" t="s">
         <v>780</v>
       </c>
       <c r="N254" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="O254" s="1">
         <v>1</v>
@@ -26322,40 +26349,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>1445</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1451</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1452</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1453</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1454</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1450</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1446</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1447</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1448</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1449</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -28041,7 +28068,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C41" s="1">
         <v>34</v>
@@ -31051,7 +31078,7 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -33029,7 +33056,7 @@
         <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C157" s="1">
         <v>42</v>
@@ -33545,7 +33572,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C169" s="1">
         <v>47</v>
@@ -34233,7 +34260,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C185" s="1">
         <v>51</v>
@@ -34276,7 +34303,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C186" s="1">
         <v>59</v>
@@ -37338,40 +37365,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>1445</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1451</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1452</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1453</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1454</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1450</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1446</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1447</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1448</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1449</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -37598,7 +37625,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -37813,7 +37840,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -37856,7 +37883,7 @@
         <v>743</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -38114,7 +38141,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -38372,7 +38399,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -38544,7 +38571,7 @@
         <v>482</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -39057,7 +39084,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C41" s="1">
         <v>43</v>
@@ -39705,7 +39732,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -40393,7 +40420,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -40522,7 +40549,7 @@
         <v>71</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -40737,7 +40764,7 @@
         <v>76</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
@@ -40952,7 +40979,7 @@
         <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -40995,7 +41022,7 @@
         <v>82</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -41038,7 +41065,7 @@
         <v>83</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -41124,7 +41151,7 @@
         <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -41339,7 +41366,7 @@
         <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -41468,7 +41495,7 @@
         <v>93</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -41597,7 +41624,7 @@
         <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
@@ -41769,7 +41796,7 @@
         <v>487</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
@@ -41855,7 +41882,7 @@
         <v>101</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
@@ -41898,7 +41925,7 @@
         <v>102</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
@@ -41941,7 +41968,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
@@ -41984,7 +42011,7 @@
         <v>431</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
@@ -42027,7 +42054,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
@@ -42067,10 +42094,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
@@ -42113,7 +42140,7 @@
         <v>105</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -42156,7 +42183,7 @@
         <v>106</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
@@ -42199,7 +42226,7 @@
         <v>601</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -42242,7 +42269,7 @@
         <v>107</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
@@ -42328,7 +42355,7 @@
         <v>109</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
@@ -42414,7 +42441,7 @@
         <v>111</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
@@ -42457,7 +42484,7 @@
         <v>112</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
@@ -42758,7 +42785,7 @@
         <v>119</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
@@ -43231,7 +43258,7 @@
         <v>130</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
@@ -43618,7 +43645,7 @@
         <v>138</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
@@ -43747,7 +43774,7 @@
         <v>141</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
@@ -43962,7 +43989,7 @@
         <v>146</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
@@ -44045,7 +44072,7 @@
         <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C157" s="1">
         <v>64</v>
@@ -44349,7 +44376,7 @@
         <v>154</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
@@ -44435,7 +44462,7 @@
         <v>156</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -44561,7 +44588,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C169" s="1">
         <v>46</v>
@@ -44693,7 +44720,7 @@
         <v>161</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -44908,7 +44935,7 @@
         <v>166</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D177" s="1">
         <v>0</v>
@@ -44994,7 +45021,7 @@
         <v>168</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
@@ -45249,7 +45276,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C185" s="1">
         <v>42</v>
@@ -45292,7 +45319,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C186" s="1">
         <v>55</v>
@@ -45381,7 +45408,7 @@
         <v>175</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D188" s="1">
         <v>0</v>
@@ -45553,7 +45580,7 @@
         <v>484</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D192" s="1">
         <v>0</v>
@@ -45596,7 +45623,7 @@
         <v>179</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D193" s="1">
         <v>0</v>
@@ -45768,7 +45795,7 @@
         <v>182</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D197" s="1">
         <v>0</v>
@@ -45811,7 +45838,7 @@
         <v>481</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D198" s="1">
         <v>0</v>
@@ -45854,7 +45881,7 @@
         <v>183</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D199" s="1">
         <v>0</v>
@@ -45940,7 +45967,7 @@
         <v>185</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D201" s="1">
         <v>0</v>
@@ -45983,7 +46010,7 @@
         <v>742</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D202" s="1">
         <v>0</v>
@@ -46069,7 +46096,7 @@
         <v>188</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D204" s="1">
         <v>0</v>
@@ -46327,7 +46354,7 @@
         <v>483</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D210" s="1">
         <v>0</v>
@@ -46370,7 +46397,7 @@
         <v>194</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D211" s="1">
         <v>0</v>
@@ -47058,7 +47085,7 @@
         <v>209</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D227" s="1">
         <v>0</v>
@@ -47144,7 +47171,7 @@
         <v>485</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D229" s="1">
         <v>0</v>
@@ -47187,7 +47214,7 @@
         <v>211</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D230" s="1">
         <v>0</v>
@@ -47359,7 +47386,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D234" s="1">
         <v>0</v>
@@ -47488,7 +47515,7 @@
         <v>744</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D237" s="1">
         <v>0</v>
@@ -47660,7 +47687,7 @@
         <v>221</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D241" s="1">
         <v>0</v>
@@ -48090,7 +48117,7 @@
         <v>231</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="D251" s="1">
         <v>0</v>
@@ -48355,40 +48382,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>1445</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1451</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1452</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1453</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1454</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1450</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1446</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1447</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1448</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1449</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -50074,7 +50101,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C41" s="1">
         <v>59</v>
@@ -53084,7 +53111,7 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -55062,7 +55089,7 @@
         <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C157" s="1">
         <v>43</v>
@@ -55578,7 +55605,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C169" s="1">
         <v>53</v>
@@ -56266,7 +56293,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C185" s="1">
         <v>50</v>
@@ -56309,7 +56336,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C186" s="1">
         <v>41</v>
@@ -59363,19 +59390,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1515</v>
+        <v>1501</v>
       </c>
       <c r="B1" t="s">
-        <v>1625</v>
+        <v>1611</v>
       </c>
       <c r="C1" t="s">
-        <v>1626</v>
+        <v>1612</v>
       </c>
       <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>1627</v>
+        <v>1613</v>
       </c>
       <c r="B2" s="1">
         <v>938</v>
@@ -59387,7 +59414,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1628</v>
+        <v>1614</v>
       </c>
       <c r="B3" s="1">
         <v>935</v>
@@ -59399,7 +59426,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1629</v>
+        <v>1615</v>
       </c>
       <c r="B4" s="1">
         <v>932</v>
@@ -59411,7 +59438,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1630</v>
+        <v>1616</v>
       </c>
       <c r="B5" s="1">
         <v>672</v>
@@ -59423,7 +59450,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1631</v>
+        <v>1617</v>
       </c>
       <c r="B6" s="1">
         <v>757</v>
@@ -59435,7 +59462,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="B7" s="1">
         <v>343</v>
@@ -59447,7 +59474,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="B8" s="1">
         <v>899</v>
@@ -59459,7 +59486,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1634</v>
+        <v>1620</v>
       </c>
       <c r="B9" s="1">
         <v>822</v>
@@ -59471,7 +59498,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>1635</v>
+        <v>1621</v>
       </c>
       <c r="B10" s="1">
         <v>953</v>
@@ -59483,7 +59510,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>1636</v>
+        <v>1622</v>
       </c>
       <c r="B11" s="1">
         <v>909</v>
@@ -59495,7 +59522,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1638</v>
+        <v>1624</v>
       </c>
       <c r="B12" s="1">
         <v>853</v>
@@ -59507,7 +59534,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="B13" s="1">
         <v>987</v>
@@ -59519,7 +59546,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="B14" s="1">
         <v>802</v>
@@ -59531,7 +59558,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -59543,19 +59570,19 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1523</v>
+        <v>1509</v>
       </c>
       <c r="B17" t="s">
-        <v>1625</v>
+        <v>1611</v>
       </c>
       <c r="C17" t="s">
-        <v>1626</v>
+        <v>1612</v>
       </c>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>1627</v>
+        <v>1613</v>
       </c>
       <c r="B18" s="1">
         <v>976</v>
@@ -59567,7 +59594,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>1628</v>
+        <v>1614</v>
       </c>
       <c r="B19" s="1">
         <v>956</v>
@@ -59579,7 +59606,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>1629</v>
+        <v>1615</v>
       </c>
       <c r="B20" s="1">
         <v>808</v>
@@ -59591,7 +59618,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>1630</v>
+        <v>1616</v>
       </c>
       <c r="B21" s="1">
         <v>696</v>
@@ -59603,7 +59630,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1631</v>
+        <v>1617</v>
       </c>
       <c r="B22" s="1">
         <v>506</v>
@@ -59615,7 +59642,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="B23" s="1">
         <v>274</v>
@@ -59627,7 +59654,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="B24" s="1">
         <v>977</v>
@@ -59639,7 +59666,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1634</v>
+        <v>1620</v>
       </c>
       <c r="B25" s="1">
         <v>371</v>
@@ -59651,7 +59678,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1635</v>
+        <v>1621</v>
       </c>
       <c r="B26" s="1">
         <v>916</v>
@@ -59663,7 +59690,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>1636</v>
+        <v>1622</v>
       </c>
       <c r="B27" s="1">
         <v>976</v>
@@ -59675,7 +59702,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>1637</v>
+        <v>1623</v>
       </c>
       <c r="B28" s="1">
         <v>959</v>
@@ -59687,7 +59714,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>1638</v>
+        <v>1624</v>
       </c>
       <c r="B29" s="1">
         <v>783</v>
@@ -59699,7 +59726,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="B30" s="1">
         <v>802</v>
@@ -59711,7 +59738,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
@@ -59723,18 +59750,18 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1526</v>
+        <v>1512</v>
       </c>
       <c r="B33" t="s">
-        <v>1625</v>
+        <v>1611</v>
       </c>
       <c r="C33" t="s">
-        <v>1626</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1627</v>
+        <v>1613</v>
       </c>
       <c r="B34" s="1">
         <v>1041</v>
@@ -59746,7 +59773,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1628</v>
+        <v>1614</v>
       </c>
       <c r="B35" s="1">
         <v>979</v>
@@ -59758,7 +59785,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1629</v>
+        <v>1615</v>
       </c>
       <c r="B36" s="1">
         <v>690</v>
@@ -59770,7 +59797,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1630</v>
+        <v>1616</v>
       </c>
       <c r="B37" s="1">
         <v>745</v>
@@ -59782,7 +59809,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1631</v>
+        <v>1617</v>
       </c>
       <c r="B38" s="1">
         <v>519</v>
@@ -59794,7 +59821,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="B39" s="1">
         <v>291</v>
@@ -59806,7 +59833,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="B40" s="1">
         <v>962</v>
@@ -59818,7 +59845,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1634</v>
+        <v>1620</v>
       </c>
       <c r="B41" s="1">
         <v>77</v>
@@ -59830,7 +59857,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1635</v>
+        <v>1621</v>
       </c>
       <c r="B42" s="1">
         <v>964</v>
@@ -59842,7 +59869,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1636</v>
+        <v>1622</v>
       </c>
       <c r="B43" s="1">
         <v>1038</v>
@@ -59854,7 +59881,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1637</v>
+        <v>1623</v>
       </c>
       <c r="B44" s="1">
         <v>980</v>
@@ -59866,7 +59893,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1638</v>
+        <v>1624</v>
       </c>
       <c r="B45" s="1">
         <v>782</v>
@@ -59878,7 +59905,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="B46" s="1">
         <v>932</v>
@@ -59890,7 +59917,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="B47" s="1">
         <v>0</v>
@@ -59924,155 +59951,155 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1">
       <c r="A1" s="7" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1506</v>
+        <v>1492</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1507</v>
+        <v>1493</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1508</v>
+        <v>1494</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1509</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>1510</v>
+        <v>1496</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1511</v>
+        <v>1497</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1512</v>
+        <v>1498</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1513</v>
+        <v>1499</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>1515</v>
+        <v>1501</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1516</v>
+        <v>1502</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1517</v>
+        <v>1503</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>1519</v>
+        <v>1505</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1521</v>
+        <v>1507</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1522</v>
+        <v>1508</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>1523</v>
+        <v>1509</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1524</v>
+        <v>1510</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1525</v>
+        <v>1511</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1522</v>
+        <v>1508</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>1526</v>
+        <v>1512</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1527</v>
+        <v>1513</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1528</v>
+        <v>1514</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1529</v>
+        <v>1515</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1530</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>1531</v>
+        <v>1517</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1532</v>
+        <v>1518</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1533</v>
+        <v>1519</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1534</v>
+        <v>1520</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1535</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>1536</v>
+        <v>1522</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1537</v>
+        <v>1523</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1538</v>
+        <v>1524</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1539</v>
+        <v>1525</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1540</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>1541</v>
+        <v>1527</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1542</v>
+        <v>1528</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1543</v>
+        <v>1529</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1544</v>
+        <v>1530</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1"/>
@@ -60081,280 +60108,280 @@
         <v>312</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>1546</v>
+        <v>1532</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1547</v>
+        <v>1533</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>1548</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29.25" thickBot="1">
       <c r="A12" s="9" t="s">
-        <v>1549</v>
+        <v>1535</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1550</v>
+        <v>1536</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1552</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="29.25" thickBot="1">
       <c r="A13" s="9" t="s">
-        <v>1553</v>
+        <v>1539</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1554</v>
+        <v>1540</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1555</v>
+        <v>1541</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="43.5" thickBot="1">
       <c r="A14" s="9" t="s">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1558</v>
+        <v>1544</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1559</v>
+        <v>1545</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1560</v>
+        <v>1546</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>1561</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.5" thickBot="1">
       <c r="A15" s="9" t="s">
-        <v>1562</v>
+        <v>1548</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1559</v>
+        <v>1545</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1565</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.5" thickBot="1">
       <c r="A16" s="9" t="s">
-        <v>1566</v>
+        <v>1552</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1567</v>
+        <v>1553</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1569</v>
+        <v>1555</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.5" thickBot="1">
       <c r="A17" s="9" t="s">
-        <v>1571</v>
+        <v>1557</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1573</v>
+        <v>1559</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1574</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="29.25" thickBot="1">
       <c r="A18" s="9" t="s">
-        <v>1575</v>
+        <v>1561</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1576</v>
+        <v>1562</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1578</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="29.25" thickBot="1">
       <c r="A19" s="9" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="43.5" thickBot="1">
       <c r="A20" s="9" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1583</v>
+        <v>1569</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1559</v>
+        <v>1545</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1584</v>
+        <v>1570</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="43.5" thickBot="1">
       <c r="A21" s="9" t="s">
-        <v>1586</v>
+        <v>1572</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1588</v>
+        <v>1574</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1589</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="29.25" thickBot="1">
       <c r="A22" s="9" t="s">
-        <v>1590</v>
+        <v>1576</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1591</v>
+        <v>1577</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>1593</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.5" thickBot="1">
       <c r="A23" s="9" t="s">
-        <v>1594</v>
+        <v>1580</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1595</v>
+        <v>1581</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1559</v>
+        <v>1545</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1596</v>
+        <v>1582</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="43.5" thickBot="1">
       <c r="A24" s="9" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1601</v>
+        <v>1587</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>1602</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.25" thickBot="1">
       <c r="A25" s="9" t="s">
-        <v>1603</v>
+        <v>1589</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1604</v>
+        <v>1590</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1605</v>
+        <v>1591</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>1606</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1"/>
     <row r="27" spans="1:5" ht="60.75" thickBot="1">
       <c r="A27" s="9" t="s">
-        <v>1607</v>
+        <v>1593</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1608</v>
+        <v>1594</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1609</v>
+        <v>1595</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1610</v>
+        <v>1596</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>1611</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="102" thickBot="1">
       <c r="A28" s="9" t="s">
-        <v>1612</v>
+        <v>1598</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1613</v>
+        <v>1599</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -60363,58 +60390,58 @@
         <v>0</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>1614</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="116.25" thickBot="1">
       <c r="A29" s="9" t="s">
-        <v>1615</v>
+        <v>1601</v>
       </c>
       <c r="B29" s="11">
         <v>0.4</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1616</v>
+        <v>1602</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1616</v>
+        <v>1602</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>1617</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="116.25" thickBot="1">
       <c r="A30" s="9" t="s">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1619</v>
+        <v>1605</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1620</v>
+        <v>1606</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>1621</v>
+        <v>1607</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>1617</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="116.25" thickBot="1">
       <c r="A31" s="9" t="s">
-        <v>1622</v>
+        <v>1608</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1619</v>
+        <v>1605</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1623</v>
+        <v>1609</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>1621</v>
+        <v>1607</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>1624</v>
+        <v>1610</v>
       </c>
     </row>
   </sheetData>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\QUIZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF04C2F-82FF-4D2F-8E5E-2EC8C7863EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8A877E-6BEE-4B8B-A90F-1D1CE84E7AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="30180" windowHeight="17970" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="30180" windowHeight="17970" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Elenco" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="1679">
   <si>
     <t>Sigla</t>
   </si>
@@ -2472,9 +2472,6 @@
     <t>verde, giallo</t>
   </si>
   <si>
-    <t>Cocos, Keeling</t>
-  </si>
-  <si>
     <t>Isole Cocos</t>
   </si>
   <si>
@@ -3831,9 +3828,6 @@
     <t>Tristan</t>
   </si>
   <si>
-    <t>Trinidad, Tobago</t>
-  </si>
-  <si>
     <t>Polinesia</t>
   </si>
   <si>
@@ -3972,9 +3966,6 @@
     <t>Bottom, de botto</t>
   </si>
   <si>
-    <t>Port au Prince, Port u prince, Porto Prince</t>
-  </si>
-  <si>
     <t>Cartoon</t>
   </si>
   <si>
@@ -4257,9 +4248,6 @@
     <t>Coq burn town, coop burn town</t>
   </si>
   <si>
-    <t>Una foti, fai una foto, kuna futi</t>
-  </si>
-  <si>
     <t>base terra, passe terra</t>
   </si>
   <si>
@@ -4272,9 +4260,6 @@
     <t>Mia Mail, Nia may, ni a me</t>
   </si>
   <si>
-    <t>Yamussukro, Yamusucro, gli amusso cro, yamusu cro</t>
-  </si>
-  <si>
     <t>Cigali, Cialis, chi gali</t>
   </si>
   <si>
@@ -4284,15 +4269,9 @@
     <t>Dujabbe, Due gambe, du scian be</t>
   </si>
   <si>
-    <t>Bishkek, Biscake, Bistecca, bisquet, bis check</t>
-  </si>
-  <si>
     <t>Azkaban, Azkabat, asgabat</t>
   </si>
   <si>
-    <t>papete, papete beach</t>
-  </si>
-  <si>
     <t>a lo fi, all of i</t>
   </si>
   <si>
@@ -4329,15 +4308,9 @@
     <t>Tito</t>
   </si>
   <si>
-    <t>Comare</t>
-  </si>
-  <si>
     <t>Linea equatoriale</t>
   </si>
   <si>
-    <t>S Maarten, Sint Marten, synth martin</t>
-  </si>
-  <si>
     <t>Naypidaw, Naipidau, Mypidau, Naked out, Nipedau</t>
   </si>
   <si>
@@ -4398,9 +4371,6 @@
     <t>Numea, Lumea, nomea, nu mea</t>
   </si>
   <si>
-    <t>Saint Martin, S Martin, San marten, Sim Martin</t>
-  </si>
-  <si>
     <t>MEDIA.SE</t>
   </si>
   <si>
@@ -4441,9 +4411,6 @@
   </si>
   <si>
     <t>Onyara, Uniara, Onira</t>
-  </si>
-  <si>
-    <t>graal dick, cralendic, cra l'endic, tra l'endic, crale, calendar, trein bike</t>
   </si>
   <si>
     <t>Mamodzu, Mamotzu, ma mozu, mahmood</t>
@@ -5409,9 +5376,6 @@
     <t>*Repubblica Ceca, Rep Ceca, Cecchia, Secchia</t>
   </si>
   <si>
-    <t>Dogo</t>
-  </si>
-  <si>
     <t>Lume, elome</t>
   </si>
   <si>
@@ -5463,12 +5427,6 @@
     <t>Work of spain</t>
   </si>
   <si>
-    <t>ho detto che lau</t>
-  </si>
-  <si>
-    <t>bergizzistan</t>
-  </si>
-  <si>
     <t>Duck</t>
   </si>
   <si>
@@ -5502,18 +5460,9 @@
     <t>*Belarus, velarus</t>
   </si>
   <si>
-    <t>Bon Air, boner</t>
-  </si>
-  <si>
-    <t>*Swaziland, e suatini, swatini, eduatini</t>
-  </si>
-  <si>
     <t>Hermana</t>
   </si>
   <si>
-    <t>Pitcairn, isole big cairn, isole pick up, isole fitkair, fitkair, speedcairn, isole bitcoin, bitcoin</t>
-  </si>
-  <si>
     <t>Esodo</t>
   </si>
   <si>
@@ -5532,13 +5481,73 @@
     <t>S eustatius, sintestatius, sintastatius, sinteu status</t>
   </si>
   <si>
-    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis, sanchez &amp; nevis, saint kitze nevis, send kids in iris, sankitsi nevis, thank you say nadies, zenkids e nevis, send kids a nevis</t>
-  </si>
-  <si>
     <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come, soã come, sauto me principe, sau tome</t>
   </si>
   <si>
     <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come, soã come, sau tome</t>
+  </si>
+  <si>
+    <t>graal dick, cralendic, cra l'endic, tra l'endic, crale, calendar, trein bike, cral e decker</t>
+  </si>
+  <si>
+    <t>ho detto che lau, togelao</t>
+  </si>
+  <si>
+    <t>Grado</t>
+  </si>
+  <si>
+    <t>Comare, Amore</t>
+  </si>
+  <si>
+    <t>*Swaziland, e suatini, swatini, eduatini, e swattini</t>
+  </si>
+  <si>
+    <t>Trinidad, Tobago, trinida de tobago</t>
+  </si>
+  <si>
+    <t>bergizzistan, ciclista</t>
+  </si>
+  <si>
+    <t>Una foti, fai una foto, kuna futi, fu una foti</t>
+  </si>
+  <si>
+    <t>Yamussukro, Yamusucro, gli amusso cro, yamusu cro, diamo sucro</t>
+  </si>
+  <si>
+    <t>Bishkek, Biscake, Bistecca, bisquet, bis check, bischeck</t>
+  </si>
+  <si>
+    <t>Saint Martin, S Martin, San marten, Sim Martin, syd martin</t>
+  </si>
+  <si>
+    <t>Dogo, tg</t>
+  </si>
+  <si>
+    <t>Bon Air, boner, bonheur, on air</t>
+  </si>
+  <si>
+    <t>Tina, Pina</t>
+  </si>
+  <si>
+    <t>Guersi</t>
+  </si>
+  <si>
+    <t>Port au Prince, Port u prince, Porto Prince, Portalo prince</t>
+  </si>
+  <si>
+    <t>S Maarten, Sint Marten, synth martin, sean marten</t>
+  </si>
+  <si>
+    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis, sanchez &amp; nevis, saint kitze nevis, send kids in iris, sankitsi nevis, thank you say nadies, zenkids e nevis, send kids a nevis, schizzenavis, senkids e nadies, sentize nevis, than kisse nevis, sam kitchenavis, kids e nevis</t>
+  </si>
+  <si>
+    <t>papete, papete beach, tappeti</t>
+  </si>
+  <si>
+    <t>Cocos, Keeling, the cocos</t>
+  </si>
+  <si>
+    <t>Pitcairn, isole big cairn, isole pick up, isole fitkair, fitkair, speedcairn, isole bitcoin, bitcoin, isole pitcar, isole pittar, pittar</t>
   </si>
 </sst>
 </file>
@@ -18009,7 +18018,7 @@
         <v>747</v>
       </c>
       <c r="D1" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="E1" t="s">
         <v>495</v>
@@ -18018,13 +18027,13 @@
         <v>748</v>
       </c>
       <c r="G1" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H1" t="s">
         <v>746</v>
       </c>
       <c r="I1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="J1" t="s">
         <v>764</v>
@@ -18036,13 +18045,13 @@
         <v>772</v>
       </c>
       <c r="M1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="O1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -18062,7 +18071,7 @@
         <v>750</v>
       </c>
       <c r="I2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J2" t="s">
         <v>765</v>
@@ -18071,10 +18080,10 @@
         <v>766</v>
       </c>
       <c r="L2" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="N2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O2" s="1">
         <v>1</v>
@@ -18098,13 +18107,13 @@
         <v>497</v>
       </c>
       <c r="F3" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="H3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I3" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="J3" t="s">
         <v>751</v>
@@ -18116,7 +18125,7 @@
         <v>773</v>
       </c>
       <c r="N3" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
@@ -18140,10 +18149,10 @@
         <v>498</v>
       </c>
       <c r="H4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J4" t="s">
         <v>758</v>
@@ -18155,7 +18164,7 @@
         <v>805</v>
       </c>
       <c r="N4" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -18176,31 +18185,31 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="E5" t="s">
         <v>499</v>
       </c>
       <c r="F5" t="s">
-        <v>1460</v>
+        <v>1450</v>
       </c>
       <c r="G5" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H5" t="s">
         <v>753</v>
       </c>
       <c r="I5" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="J5" t="s">
         <v>754</v>
       </c>
       <c r="L5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N5" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O5" s="1">
         <v>2</v>
@@ -18217,10 +18226,10 @@
         <v>500</v>
       </c>
       <c r="H6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I6" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="J6" t="s">
         <v>751</v>
@@ -18229,10 +18238,10 @@
         <v>770</v>
       </c>
       <c r="L6" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="N6" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O6" s="1">
         <v>2</v>
@@ -18249,13 +18258,13 @@
         <v>501</v>
       </c>
       <c r="I7" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J7" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L7" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="M7" t="s">
         <v>492</v>
@@ -18278,13 +18287,13 @@
         <v>502</v>
       </c>
       <c r="F8" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="I8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J8" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="L8" t="s">
         <v>775</v>
@@ -18310,13 +18319,13 @@
         <v>757</v>
       </c>
       <c r="G9" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J9" t="s">
         <v>771</v>
@@ -18325,10 +18334,10 @@
         <v>766</v>
       </c>
       <c r="L9" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="N9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -18345,10 +18354,10 @@
         <v>503</v>
       </c>
       <c r="H10" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I10" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="J10" t="s">
         <v>778</v>
@@ -18360,7 +18369,7 @@
         <v>775</v>
       </c>
       <c r="N10" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O10" s="1">
         <v>1</v>
@@ -18374,7 +18383,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>1634</v>
+        <v>1622</v>
       </c>
       <c r="E11" t="s">
         <v>504</v>
@@ -18383,13 +18392,13 @@
         <v>759</v>
       </c>
       <c r="I11" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J11" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="N11" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O11" s="1">
         <v>2</v>
@@ -18406,10 +18415,10 @@
         <v>511</v>
       </c>
       <c r="F12" t="s">
-        <v>1653</v>
+        <v>1639</v>
       </c>
       <c r="I12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J12" t="s">
         <v>779</v>
@@ -18421,7 +18430,7 @@
         <v>492</v>
       </c>
       <c r="N12" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="O12" s="1">
         <v>3</v>
@@ -18441,13 +18450,13 @@
         <v>581</v>
       </c>
       <c r="I13" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="J13" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L13" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="M13" t="s">
         <v>492</v>
@@ -18467,19 +18476,19 @@
         <v>505</v>
       </c>
       <c r="I14" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J14" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K14" t="s">
         <v>766</v>
       </c>
       <c r="L14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="N14" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="O14" s="1">
         <v>1</v>
@@ -18499,13 +18508,13 @@
         <v>761</v>
       </c>
       <c r="I15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J15" t="s">
         <v>762</v>
       </c>
       <c r="N15" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O15" s="1">
         <v>1</v>
@@ -18519,16 +18528,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="E16" t="s">
         <v>507</v>
       </c>
       <c r="H16" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I16" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J16" t="s">
         <v>763</v>
@@ -18540,7 +18549,7 @@
         <v>805</v>
       </c>
       <c r="N16" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="O16" s="1">
         <v>2</v>
@@ -18557,16 +18566,16 @@
         <v>508</v>
       </c>
       <c r="F17" t="s">
-        <v>1654</v>
+        <v>1640</v>
       </c>
       <c r="I17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J17" t="s">
         <v>781</v>
       </c>
       <c r="N17" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="O17" s="1">
         <v>2</v>
@@ -18586,16 +18595,16 @@
         <v>509</v>
       </c>
       <c r="H18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I18" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J18" t="s">
         <v>785</v>
       </c>
       <c r="N18" t="s">
-        <v>1479</v>
+        <v>1468</v>
       </c>
       <c r="O18" s="1">
         <v>2</v>
@@ -18609,19 +18618,19 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="E19" t="s">
         <v>510</v>
       </c>
       <c r="F19" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="G19" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="I19" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J19" t="s">
         <v>785</v>
@@ -18630,7 +18639,7 @@
         <v>492</v>
       </c>
       <c r="N19" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="O19" s="1">
         <v>3</v>
@@ -18647,13 +18656,13 @@
         <v>513</v>
       </c>
       <c r="F20" t="s">
-        <v>1652</v>
+        <v>1638</v>
       </c>
       <c r="H20" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I20" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J20" t="s">
         <v>787</v>
@@ -18665,7 +18674,7 @@
         <v>783</v>
       </c>
       <c r="N20" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="O20" s="1">
         <v>2</v>
@@ -18682,10 +18691,10 @@
         <v>514</v>
       </c>
       <c r="F21" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="I21" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J21" t="s">
         <v>788</v>
@@ -18697,7 +18706,7 @@
         <v>789</v>
       </c>
       <c r="N21" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O21" s="1">
         <v>2</v>
@@ -18714,16 +18723,16 @@
         <v>515</v>
       </c>
       <c r="H22" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="I22" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="J22" t="s">
         <v>790</v>
       </c>
       <c r="N22" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O22" s="1">
         <v>1</v>
@@ -18737,31 +18746,31 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="E23" t="s">
         <v>516</v>
       </c>
       <c r="F23" t="s">
-        <v>1490</v>
+        <v>1479</v>
       </c>
       <c r="H23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I23" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J23" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K23" t="s">
         <v>766</v>
       </c>
       <c r="L23" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="N23" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="O23" s="1">
         <v>2</v>
@@ -18778,19 +18787,19 @@
         <v>517</v>
       </c>
       <c r="F24" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="H24" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I24" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="J24" t="s">
         <v>792</v>
       </c>
       <c r="N24" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="O24" s="1">
         <v>2</v>
@@ -18807,13 +18816,13 @@
         <v>518</v>
       </c>
       <c r="I25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J25" t="s">
         <v>769</v>
       </c>
       <c r="L25" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="M25" t="s">
         <v>492</v>
@@ -18830,22 +18839,22 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E26" t="s">
         <v>519</v>
       </c>
       <c r="F26" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="H26" t="s">
         <v>793</v>
       </c>
       <c r="I26" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J26" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="K26" t="s">
         <v>766</v>
@@ -18854,7 +18863,7 @@
         <v>794</v>
       </c>
       <c r="N26" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="O26" s="1">
         <v>2</v>
@@ -18868,7 +18877,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>1662</v>
+        <v>1648</v>
       </c>
       <c r="E27" t="s">
         <v>520</v>
@@ -18877,7 +18886,7 @@
         <v>795</v>
       </c>
       <c r="I27" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J27" t="s">
         <v>796</v>
@@ -18886,7 +18895,7 @@
         <v>785</v>
       </c>
       <c r="N27" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="O27" s="1">
         <v>1</v>
@@ -18900,31 +18909,31 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>1454</v>
+        <v>1444</v>
       </c>
       <c r="E28" t="s">
         <v>522</v>
       </c>
       <c r="F28" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G28" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="H28" t="s">
         <v>799</v>
       </c>
       <c r="I28" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J28" t="s">
         <v>800</v>
       </c>
       <c r="L28" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N28" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O28" s="1">
         <v>1</v>
@@ -18938,22 +18947,22 @@
         <v>482</v>
       </c>
       <c r="C29" t="s">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="D29" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="E29" t="s">
         <v>523</v>
       </c>
       <c r="F29" t="s">
-        <v>1466</v>
+        <v>1658</v>
       </c>
       <c r="G29" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="I29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J29" t="s">
         <v>798</v>
@@ -18968,7 +18977,7 @@
         <v>492</v>
       </c>
       <c r="N29" t="s">
-        <v>1472</v>
+        <v>1461</v>
       </c>
       <c r="O29" s="1">
         <v>3</v>
@@ -18982,16 +18991,16 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="E30" t="s">
         <v>524</v>
       </c>
       <c r="H30" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I30" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="J30" t="s">
         <v>788</v>
@@ -19003,7 +19012,7 @@
         <v>780</v>
       </c>
       <c r="N30" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="O30" s="1">
         <v>1</v>
@@ -19020,19 +19029,19 @@
         <v>525</v>
       </c>
       <c r="F31" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="H31" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="I31" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="J31" t="s">
         <v>801</v>
       </c>
       <c r="N31" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O31" s="1">
         <v>2</v>
@@ -19049,10 +19058,10 @@
         <v>526</v>
       </c>
       <c r="H32" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I32" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J32" t="s">
         <v>803</v>
@@ -19061,10 +19070,10 @@
         <v>802</v>
       </c>
       <c r="L32" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="N32" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="O32" s="1">
         <v>1</v>
@@ -19081,16 +19090,16 @@
         <v>527</v>
       </c>
       <c r="F33" t="s">
-        <v>1655</v>
+        <v>1641</v>
       </c>
       <c r="G33" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="H33" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="I33" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="J33" t="s">
         <v>804</v>
@@ -19099,10 +19108,10 @@
         <v>769</v>
       </c>
       <c r="L33" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="N33" t="s">
-        <v>1471</v>
+        <v>1460</v>
       </c>
       <c r="O33" s="1">
         <v>2</v>
@@ -19119,19 +19128,19 @@
         <v>528</v>
       </c>
       <c r="G34" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="H34" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I34" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J34" t="s">
         <v>806</v>
       </c>
       <c r="N34" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O34" s="1">
         <v>1</v>
@@ -19148,13 +19157,13 @@
         <v>529</v>
       </c>
       <c r="F35" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="H35" t="s">
         <v>807</v>
       </c>
       <c r="I35" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J35" t="s">
         <v>796</v>
@@ -19166,7 +19175,7 @@
         <v>780</v>
       </c>
       <c r="N35" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O35" s="1">
         <v>2</v>
@@ -19183,13 +19192,13 @@
         <v>530</v>
       </c>
       <c r="F36" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="H36" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I36" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J36" t="s">
         <v>752</v>
@@ -19201,7 +19210,7 @@
         <v>780</v>
       </c>
       <c r="N36" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="O36" s="1">
         <v>2</v>
@@ -19218,28 +19227,28 @@
         <v>531</v>
       </c>
       <c r="F37" t="s">
-        <v>1434</v>
+        <v>1425</v>
       </c>
       <c r="G37" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="H37" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I37" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J37" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K37" t="s">
         <v>766</v>
       </c>
       <c r="L37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N37" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O37" s="1">
         <v>1</v>
@@ -19253,22 +19262,22 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E38" t="s">
         <v>532</v>
       </c>
       <c r="F38" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H38" t="s">
+        <v>834</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J38" t="s">
         <v>835</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J38" t="s">
-        <v>836</v>
       </c>
       <c r="K38" t="s">
         <v>770</v>
@@ -19277,7 +19286,7 @@
         <v>780</v>
       </c>
       <c r="N38" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="O38" s="1">
         <v>1</v>
@@ -19294,10 +19303,10 @@
         <v>533</v>
       </c>
       <c r="H39" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="I39" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J39" t="s">
         <v>762</v>
@@ -19306,10 +19315,10 @@
         <v>769</v>
       </c>
       <c r="L39" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="N39" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O39" s="1">
         <v>1</v>
@@ -19326,16 +19335,16 @@
         <v>534</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>780</v>
       </c>
       <c r="N40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O40" s="15">
         <v>2</v>
@@ -19346,25 +19355,25 @@
         <v>443</v>
       </c>
       <c r="B41" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C41" t="s">
-        <v>1631</v>
+        <v>1620</v>
       </c>
       <c r="E41" t="s">
         <v>669</v>
       </c>
       <c r="H41" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I41" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J41" t="s">
         <v>760</v>
       </c>
       <c r="N41" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="O41" s="1">
         <v>1</v>
@@ -19378,25 +19387,25 @@
         <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>1638</v>
+        <v>1626</v>
       </c>
       <c r="E42" t="s">
         <v>535</v>
       </c>
       <c r="F42" t="s">
-        <v>1628</v>
+        <v>1617</v>
       </c>
       <c r="H42" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="I42" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J42" t="s">
         <v>754</v>
       </c>
       <c r="N42" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O42" s="1">
         <v>2</v>
@@ -19410,19 +19419,19 @@
         <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>1455</v>
+        <v>1445</v>
       </c>
       <c r="E43" t="s">
         <v>536</v>
       </c>
       <c r="F43" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="H43" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I43" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="J43" t="s">
         <v>760</v>
@@ -19434,7 +19443,7 @@
         <v>780</v>
       </c>
       <c r="N43" t="s">
-        <v>1483</v>
+        <v>1472</v>
       </c>
       <c r="O43" s="1">
         <v>1</v>
@@ -19447,20 +19456,23 @@
       <c r="B44" t="s">
         <v>41</v>
       </c>
+      <c r="C44" t="s">
+        <v>1671</v>
+      </c>
       <c r="E44" t="s">
         <v>537</v>
       </c>
       <c r="F44" t="s">
+        <v>840</v>
+      </c>
+      <c r="H44" t="s">
+        <v>923</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J44" t="s">
         <v>841</v>
-      </c>
-      <c r="H44" t="s">
-        <v>924</v>
-      </c>
-      <c r="I44" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J44" t="s">
-        <v>842</v>
       </c>
       <c r="K44" t="s">
         <v>770</v>
@@ -19469,7 +19481,7 @@
         <v>780</v>
       </c>
       <c r="N44" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="O44" s="1">
         <v>1</v>
@@ -19486,19 +19498,19 @@
         <v>538</v>
       </c>
       <c r="I45" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="J45" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="K45" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="L45" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="N45" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="O45" s="1">
         <v>1</v>
@@ -19512,28 +19524,28 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E46" t="s">
         <v>43</v>
       </c>
       <c r="F46" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H46" t="s">
         <v>114</v>
       </c>
       <c r="I46" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J46" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="L46" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="N46" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="O46" s="1">
         <v>3</v>
@@ -19550,16 +19562,16 @@
         <v>539</v>
       </c>
       <c r="H47" t="s">
+        <v>847</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J47" t="s">
         <v>848</v>
       </c>
-      <c r="I47" t="s">
-        <v>1228</v>
-      </c>
-      <c r="J47" t="s">
-        <v>849</v>
-      </c>
       <c r="N47" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O47" s="1">
         <v>1</v>
@@ -19573,16 +19585,16 @@
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>1428</v>
+        <v>1661</v>
       </c>
       <c r="E48" t="s">
         <v>540</v>
       </c>
       <c r="I48" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J48" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="K48" t="s">
         <v>766</v>
@@ -19591,7 +19603,7 @@
         <v>805</v>
       </c>
       <c r="N48" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="O48" s="1">
         <v>2</v>
@@ -19605,22 +19617,22 @@
         <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E49" t="s">
         <v>541</v>
       </c>
       <c r="H49" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I49" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J49" t="s">
         <v>792</v>
       </c>
       <c r="N49" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="O49" s="1">
         <v>2</v>
@@ -19634,16 +19646,16 @@
         <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E50" t="s">
         <v>542</v>
       </c>
       <c r="H50" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I50" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="J50" t="s">
         <v>760</v>
@@ -19652,10 +19664,10 @@
         <v>762</v>
       </c>
       <c r="L50" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N50" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="O50" s="1">
         <v>1</v>
@@ -19669,31 +19681,31 @@
         <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E51" t="s">
         <v>543</v>
       </c>
       <c r="F51" t="s">
+        <v>857</v>
+      </c>
+      <c r="H51" t="s">
+        <v>929</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J51" t="s">
         <v>858</v>
       </c>
-      <c r="H51" t="s">
-        <v>930</v>
-      </c>
-      <c r="I51" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>859</v>
-      </c>
-      <c r="K51" t="s">
-        <v>860</v>
       </c>
       <c r="L51" t="s">
         <v>783</v>
       </c>
       <c r="N51" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -19707,28 +19719,28 @@
         <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="E52" t="s">
         <v>544</v>
       </c>
       <c r="F52" t="s">
-        <v>1409</v>
+        <v>1666</v>
       </c>
       <c r="G52" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H52" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I52" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="J52" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N52" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O52" s="1">
         <v>2</v>
@@ -19745,19 +19757,19 @@
         <v>545</v>
       </c>
       <c r="H53" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I53" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J53" t="s">
         <v>760</v>
       </c>
       <c r="L53" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N53" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O53" s="1">
         <v>1</v>
@@ -19774,19 +19786,19 @@
         <v>546</v>
       </c>
       <c r="H54" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I54" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="J54" t="s">
         <v>777</v>
       </c>
       <c r="L54" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N54" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O54" s="1">
         <v>1</v>
@@ -19803,10 +19815,10 @@
         <v>547</v>
       </c>
       <c r="F55" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="I55" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J55" t="s">
         <v>777</v>
@@ -19818,7 +19830,7 @@
         <v>780</v>
       </c>
       <c r="N55" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="O55" s="1">
         <v>1</v>
@@ -19832,16 +19844,16 @@
         <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>1456</v>
+        <v>1446</v>
       </c>
       <c r="E56" t="s">
         <v>548</v>
       </c>
       <c r="F56" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="I56" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J56" t="s">
         <v>788</v>
@@ -19856,7 +19868,7 @@
         <v>492</v>
       </c>
       <c r="N56" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="O56" s="1">
         <v>3</v>
@@ -19873,10 +19885,10 @@
         <v>549</v>
       </c>
       <c r="H57" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="I57" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J57" t="s">
         <v>762</v>
@@ -19899,22 +19911,22 @@
         <v>550</v>
       </c>
       <c r="F58" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="I58" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J58" t="s">
+        <v>866</v>
+      </c>
+      <c r="K58" t="s">
         <v>867</v>
       </c>
-      <c r="K58" t="s">
-        <v>868</v>
-      </c>
       <c r="L58" t="s">
-        <v>1482</v>
+        <v>1471</v>
       </c>
       <c r="N58" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="O58" s="1">
         <v>2</v>
@@ -19931,22 +19943,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
       <c r="H59" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="I59" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J59" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L59" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="N59" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O59" s="1">
         <v>1</v>
@@ -19963,25 +19975,25 @@
         <v>552</v>
       </c>
       <c r="F60" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="H60" t="s">
+        <v>869</v>
+      </c>
+      <c r="I60" t="s">
+        <v>883</v>
+      </c>
+      <c r="J60" t="s">
         <v>870</v>
-      </c>
-      <c r="I60" t="s">
-        <v>884</v>
-      </c>
-      <c r="J60" t="s">
-        <v>871</v>
       </c>
       <c r="K60" t="s">
         <v>770</v>
       </c>
       <c r="L60" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="N60" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -19995,28 +20007,28 @@
         <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="E61" t="s">
         <v>553</v>
       </c>
       <c r="F61" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H61" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I61" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J61" t="s">
         <v>802</v>
       </c>
       <c r="L61" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N61" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O61" s="1">
         <v>2</v>
@@ -20030,25 +20042,25 @@
         <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E62" t="s">
         <v>554</v>
       </c>
       <c r="F62" t="s">
+        <v>874</v>
+      </c>
+      <c r="H62" t="s">
         <v>875</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J62" t="s">
         <v>876</v>
       </c>
-      <c r="I62" t="s">
-        <v>1235</v>
-      </c>
-      <c r="J62" t="s">
-        <v>877</v>
-      </c>
       <c r="N62" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="O62" s="1">
         <v>1</v>
@@ -20065,19 +20077,19 @@
         <v>571</v>
       </c>
       <c r="H63" t="s">
+        <v>878</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J63" t="s">
         <v>879</v>
-      </c>
-      <c r="I63" t="s">
-        <v>1282</v>
-      </c>
-      <c r="J63" t="s">
-        <v>880</v>
       </c>
       <c r="K63" t="s">
         <v>770</v>
       </c>
       <c r="L63" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O63" s="1">
         <v>2</v>
@@ -20091,22 +20103,22 @@
         <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="E64" t="s">
         <v>556</v>
       </c>
       <c r="H64" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I64" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J64" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N64" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O64" s="1">
         <v>1</v>
@@ -20120,28 +20132,28 @@
         <v>739</v>
       </c>
       <c r="C65" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="E65" t="s">
         <v>707</v>
       </c>
       <c r="F65" t="s">
-        <v>1446</v>
+        <v>1437</v>
       </c>
       <c r="H65" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="I65" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J65" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="L65" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="N65" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O65" s="1">
         <v>2</v>
@@ -20158,13 +20170,13 @@
         <v>557</v>
       </c>
       <c r="F66" t="s">
-        <v>1468</v>
+        <v>1457</v>
       </c>
       <c r="H66" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I66" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="J66" t="s">
         <v>792</v>
@@ -20173,10 +20185,10 @@
         <v>788</v>
       </c>
       <c r="L66" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="N66" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O66" s="1">
         <v>1</v>
@@ -20190,19 +20202,19 @@
         <v>63</v>
       </c>
       <c r="C67" t="s">
-        <v>1486</v>
+        <v>1475</v>
       </c>
       <c r="E67" t="s">
         <v>558</v>
       </c>
       <c r="I67" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J67" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L67" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="O67" s="1">
         <v>2</v>
@@ -20219,19 +20231,19 @@
         <v>559</v>
       </c>
       <c r="I68" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="J68" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K68" t="s">
         <v>770</v>
       </c>
       <c r="L68" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="N68" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="O68" s="1">
         <v>1</v>
@@ -20248,13 +20260,13 @@
         <v>560</v>
       </c>
       <c r="H69" t="s">
+        <v>889</v>
+      </c>
+      <c r="I69" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J69" t="s">
         <v>890</v>
-      </c>
-      <c r="I69" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J69" t="s">
-        <v>891</v>
       </c>
       <c r="L69" t="s">
         <v>782</v>
@@ -20274,16 +20286,16 @@
         <v>561</v>
       </c>
       <c r="H70" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="I70" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J70" t="s">
         <v>760</v>
       </c>
       <c r="N70" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O70" s="1">
         <v>1</v>
@@ -20300,22 +20312,22 @@
         <v>562</v>
       </c>
       <c r="F71" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="G71" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="H71" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I71" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="J71" t="s">
         <v>803</v>
       </c>
       <c r="N71" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O71" s="1">
         <v>2</v>
@@ -20332,10 +20344,10 @@
         <v>563</v>
       </c>
       <c r="H72" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I72" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J72" t="s">
         <v>806</v>
@@ -20361,25 +20373,25 @@
         <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>1457</v>
+        <v>1447</v>
       </c>
       <c r="E73" t="s">
         <v>564</v>
       </c>
       <c r="F73" t="s">
-        <v>1469</v>
+        <v>1458</v>
       </c>
       <c r="H73" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I73" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J73" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N73" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O73" s="1">
         <v>2</v>
@@ -20396,16 +20408,16 @@
         <v>565</v>
       </c>
       <c r="H74" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I74" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J74" t="s">
         <v>785</v>
       </c>
       <c r="L74" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="O74" s="1">
         <v>2</v>
@@ -20419,22 +20431,22 @@
         <v>71</v>
       </c>
       <c r="C75" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E75" t="s">
         <v>566</v>
       </c>
       <c r="F75" t="s">
-        <v>1648</v>
+        <v>1636</v>
       </c>
       <c r="I75" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J75" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L75" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="M75" t="s">
         <v>492</v>
@@ -20451,22 +20463,22 @@
         <v>72</v>
       </c>
       <c r="C76" t="s">
-        <v>1665</v>
+        <v>1649</v>
       </c>
       <c r="E76" t="s">
         <v>567</v>
       </c>
       <c r="H76" t="s">
+        <v>902</v>
+      </c>
+      <c r="I76" t="s">
+        <v>827</v>
+      </c>
+      <c r="J76" t="s">
         <v>903</v>
       </c>
-      <c r="I76" t="s">
-        <v>828</v>
-      </c>
-      <c r="J76" t="s">
-        <v>904</v>
-      </c>
       <c r="N76" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O76" s="1">
         <v>1</v>
@@ -20480,19 +20492,19 @@
         <v>73</v>
       </c>
       <c r="C77" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="E77" t="s">
         <v>568</v>
       </c>
       <c r="H77" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="I77" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="J77" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K77" t="s">
         <v>768</v>
@@ -20501,7 +20513,7 @@
         <v>780</v>
       </c>
       <c r="N77" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O77" s="1">
         <v>1</v>
@@ -20515,19 +20527,19 @@
         <v>74</v>
       </c>
       <c r="C78" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E78" t="s">
         <v>569</v>
       </c>
       <c r="I78" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J78" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="N78" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="O78" s="1">
         <v>1</v>
@@ -20544,7 +20556,7 @@
         <v>570</v>
       </c>
       <c r="I79" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="J79" t="s">
         <v>785</v>
@@ -20556,7 +20568,7 @@
         <v>783</v>
       </c>
       <c r="N79" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="O79" s="1">
         <v>1</v>
@@ -20573,10 +20585,10 @@
         <v>76</v>
       </c>
       <c r="H80" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="I80" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="J80" t="s">
         <v>785</v>
@@ -20585,13 +20597,13 @@
         <v>769</v>
       </c>
       <c r="L80" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M80" t="s">
         <v>492</v>
       </c>
       <c r="N80" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O80" s="1">
         <v>3</v>
@@ -20605,22 +20617,22 @@
         <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="E81" t="s">
         <v>77</v>
       </c>
       <c r="F81" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="H81" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="I81" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="J81" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K81" t="s">
         <v>769</v>
@@ -20629,7 +20641,7 @@
         <v>780</v>
       </c>
       <c r="N81" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="O81" s="1">
         <v>2</v>
@@ -20646,13 +20658,13 @@
         <v>555</v>
       </c>
       <c r="H82" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I82" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J82" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K82" t="s">
         <v>766</v>
@@ -20661,7 +20673,7 @@
         <v>780</v>
       </c>
       <c r="N82" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="O82" s="1">
         <v>2</v>
@@ -20678,19 +20690,19 @@
         <v>572</v>
       </c>
       <c r="H83" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="I83" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="J83" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="L83" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N83" t="s">
-        <v>1484</v>
+        <v>1473</v>
       </c>
       <c r="O83" s="1">
         <v>1</v>
@@ -20707,25 +20719,25 @@
         <v>573</v>
       </c>
       <c r="F84" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="G84" t="s">
-        <v>1644</v>
+        <v>1632</v>
       </c>
       <c r="I84" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J84" t="s">
         <v>800</v>
       </c>
       <c r="K84" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="L84" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N84" t="s">
-        <v>1475</v>
+        <v>1464</v>
       </c>
       <c r="O84" s="1">
         <v>2</v>
@@ -20742,13 +20754,13 @@
         <v>574</v>
       </c>
       <c r="F85" t="s">
-        <v>1646</v>
+        <v>1634</v>
       </c>
       <c r="H85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I85" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="J85" t="s">
         <v>762</v>
@@ -20760,7 +20772,7 @@
         <v>492</v>
       </c>
       <c r="N85" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O85" s="1">
         <v>3</v>
@@ -20777,16 +20789,16 @@
         <v>575</v>
       </c>
       <c r="F86" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="I86" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J86" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="L86" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="M86" t="s">
         <v>492</v>
@@ -20803,31 +20815,31 @@
         <v>83</v>
       </c>
       <c r="C87" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="E87" t="s">
         <v>576</v>
       </c>
       <c r="F87" t="s">
-        <v>1645</v>
+        <v>1633</v>
       </c>
       <c r="G87" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="I87" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J87" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L87" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="M87" t="s">
         <v>492</v>
       </c>
       <c r="N87" t="s">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="O87" s="1">
         <v>3</v>
@@ -20847,19 +20859,19 @@
         <v>84</v>
       </c>
       <c r="H88" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="I88" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="J88" t="s">
         <v>778</v>
       </c>
       <c r="L88" t="s">
-        <v>1641</v>
+        <v>1629</v>
       </c>
       <c r="N88" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O88" s="1">
         <v>2</v>
@@ -20872,20 +20884,23 @@
       <c r="B89" t="s">
         <v>85</v>
       </c>
+      <c r="C89" t="s">
+        <v>1672</v>
+      </c>
       <c r="E89" t="s">
         <v>578</v>
       </c>
       <c r="F89" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="I89" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J89" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="L89" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M89" t="s">
         <v>492</v>
@@ -20905,19 +20920,19 @@
         <v>579</v>
       </c>
       <c r="F90" t="s">
-        <v>1491</v>
+        <v>1480</v>
       </c>
       <c r="H90" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="I90" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J90" t="s">
         <v>800</v>
       </c>
       <c r="N90" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O90" s="1">
         <v>2</v>
@@ -20931,31 +20946,31 @@
         <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="E91" t="s">
+        <v>914</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H91" t="s">
         <v>915</v>
       </c>
-      <c r="F91" t="s">
-        <v>1647</v>
-      </c>
-      <c r="G91" t="s">
-        <v>1354</v>
-      </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J91" t="s">
         <v>916</v>
       </c>
-      <c r="I91" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J91" t="s">
-        <v>917</v>
-      </c>
       <c r="L91" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="N91" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="O91" s="1">
         <v>2</v>
@@ -20969,16 +20984,16 @@
         <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E92" t="s">
         <v>580</v>
       </c>
       <c r="H92" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="I92" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J92" t="s">
         <v>800</v>
@@ -20990,7 +21005,7 @@
         <v>780</v>
       </c>
       <c r="N92" t="s">
-        <v>1488</v>
+        <v>1477</v>
       </c>
       <c r="O92" s="1">
         <v>2</v>
@@ -21007,16 +21022,16 @@
         <v>581</v>
       </c>
       <c r="H93" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I93" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J93" t="s">
         <v>800</v>
       </c>
       <c r="N93" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="O93" s="1">
         <v>2</v>
@@ -21033,19 +21048,19 @@
         <v>582</v>
       </c>
       <c r="F94" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G94" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="H94" t="s">
+        <v>921</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J94" t="s">
         <v>922</v>
-      </c>
-      <c r="I94" t="s">
-        <v>1230</v>
-      </c>
-      <c r="J94" t="s">
-        <v>923</v>
       </c>
       <c r="K94" t="s">
         <v>769</v>
@@ -21057,7 +21072,7 @@
         <v>492</v>
       </c>
       <c r="N94" t="s">
-        <v>1472</v>
+        <v>1461</v>
       </c>
       <c r="O94" s="1">
         <v>3</v>
@@ -21074,22 +21089,22 @@
         <v>624</v>
       </c>
       <c r="F95" t="s">
-        <v>1309</v>
+        <v>1673</v>
       </c>
       <c r="H95" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="I95" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J95" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L95" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="N95" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O95" s="1">
         <v>1</v>
@@ -21106,22 +21121,22 @@
         <v>583</v>
       </c>
       <c r="H96" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I96" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="J96" t="s">
         <v>778</v>
       </c>
       <c r="K96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L96" t="s">
         <v>780</v>
       </c>
       <c r="N96" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="O96" s="1">
         <v>2</v>
@@ -21138,10 +21153,10 @@
         <v>584</v>
       </c>
       <c r="H97" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I97" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="J97" t="s">
         <v>762</v>
@@ -21156,7 +21171,7 @@
         <v>492</v>
       </c>
       <c r="N97" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O97" s="1">
         <v>3</v>
@@ -21173,25 +21188,25 @@
         <v>585</v>
       </c>
       <c r="F98" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H98" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="I98" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J98" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="K98" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L98" t="s">
         <v>783</v>
       </c>
       <c r="N98" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O98" s="1">
         <v>1</v>
@@ -21208,19 +21223,19 @@
         <v>586</v>
       </c>
       <c r="F99" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H99" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="I99" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="J99" t="s">
         <v>762</v>
       </c>
       <c r="N99" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O99" s="1">
         <v>1</v>
@@ -21237,16 +21252,16 @@
         <v>587</v>
       </c>
       <c r="H100" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I100" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J100" t="s">
         <v>785</v>
       </c>
       <c r="L100" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M100" t="s">
         <v>492</v>
@@ -21266,22 +21281,22 @@
         <v>588</v>
       </c>
       <c r="H101" t="s">
+        <v>942</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J101" t="s">
         <v>943</v>
-      </c>
-      <c r="I101" t="s">
-        <v>1239</v>
-      </c>
-      <c r="J101" t="s">
-        <v>944</v>
       </c>
       <c r="K101" t="s">
         <v>769</v>
       </c>
       <c r="L101" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N101" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O101" s="1">
         <v>1</v>
@@ -21298,13 +21313,13 @@
         <v>589</v>
       </c>
       <c r="H102" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="I102" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J102" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K102" t="s">
         <v>771</v>
@@ -21313,7 +21328,7 @@
         <v>774</v>
       </c>
       <c r="N102" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O102" s="1">
         <v>1</v>
@@ -21330,16 +21345,16 @@
         <v>590</v>
       </c>
       <c r="H103" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I103" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J103" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="N103" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O103" s="1">
         <v>1</v>
@@ -21353,22 +21368,22 @@
         <v>487</v>
       </c>
       <c r="C104" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E104" t="s">
         <v>591</v>
       </c>
       <c r="H104" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I104" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J104" t="s">
         <v>785</v>
       </c>
       <c r="L104" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="M104" t="s">
         <v>492</v>
@@ -21388,13 +21403,13 @@
         <v>592</v>
       </c>
       <c r="F105" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G105" t="s">
-        <v>1643</v>
+        <v>1631</v>
       </c>
       <c r="I105" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J105" t="s">
         <v>760</v>
@@ -21414,16 +21429,16 @@
         <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E106" t="s">
         <v>593</v>
       </c>
       <c r="G106" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="I106" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J106" t="s">
         <v>762</v>
@@ -21432,13 +21447,13 @@
         <v>766</v>
       </c>
       <c r="L106" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="M106" t="s">
         <v>492</v>
       </c>
       <c r="N106" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="O106" s="1">
         <v>3</v>
@@ -21452,34 +21467,34 @@
         <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E107" t="s">
         <v>594</v>
       </c>
       <c r="F107" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="G107" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="I107" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J107" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K107" t="s">
         <v>771</v>
       </c>
       <c r="L107" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M107" t="s">
         <v>492</v>
       </c>
       <c r="N107" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="O107" s="1">
         <v>3</v>
@@ -21493,13 +21508,13 @@
         <v>103</v>
       </c>
       <c r="C108" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E108" t="s">
         <v>569</v>
       </c>
       <c r="I108" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J108" t="s">
         <v>758</v>
@@ -21508,13 +21523,13 @@
         <v>771</v>
       </c>
       <c r="L108" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="M108" t="s">
         <v>492</v>
       </c>
       <c r="N108" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O108" s="1">
         <v>3</v>
@@ -21528,19 +21543,19 @@
         <v>431</v>
       </c>
       <c r="C109" t="s">
-        <v>1657</v>
+        <v>1643</v>
       </c>
       <c r="D109" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="E109" t="s">
         <v>596</v>
       </c>
       <c r="F109" t="s">
-        <v>1656</v>
+        <v>1642</v>
       </c>
       <c r="I109" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J109" t="s">
         <v>754</v>
@@ -21563,22 +21578,22 @@
         <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D110" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="E110" t="s">
         <v>597</v>
       </c>
       <c r="I110" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J110" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L110" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="M110" t="s">
         <v>492</v>
@@ -21592,19 +21607,19 @@
         <v>269</v>
       </c>
       <c r="B111" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C111" t="s">
-        <v>809</v>
+        <v>1677</v>
       </c>
       <c r="E111" t="s">
         <v>598</v>
       </c>
       <c r="F111" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="I111" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J111" t="s">
         <v>808</v>
@@ -21613,13 +21628,13 @@
         <v>770</v>
       </c>
       <c r="L111" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M111" t="s">
         <v>492</v>
       </c>
       <c r="N111" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="O111" s="1">
         <v>3</v>
@@ -21633,31 +21648,31 @@
         <v>105</v>
       </c>
       <c r="C112" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E112" t="s">
         <v>599</v>
       </c>
       <c r="G112" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="I112" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J112" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K112" t="s">
         <v>766</v>
       </c>
       <c r="L112" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="M112" t="s">
         <v>492</v>
       </c>
       <c r="N112" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="O112" s="1">
         <v>3</v>
@@ -21671,22 +21686,22 @@
         <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E113" t="s">
         <v>600</v>
       </c>
       <c r="G113" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="I113" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J113" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L113" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="M113" t="s">
         <v>492</v>
@@ -21703,22 +21718,22 @@
         <v>601</v>
       </c>
       <c r="C114" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E114" t="s">
         <v>602</v>
       </c>
       <c r="F114" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="G114" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="I114" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J114" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L114" t="s">
         <v>782</v>
@@ -21738,28 +21753,28 @@
         <v>107</v>
       </c>
       <c r="C115" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="E115" t="s">
         <v>603</v>
       </c>
       <c r="F115" t="s">
-        <v>1447</v>
+        <v>1438</v>
       </c>
       <c r="I115" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J115" t="s">
         <v>802</v>
       </c>
       <c r="L115" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="M115" t="s">
         <v>492</v>
       </c>
       <c r="N115" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="O115" s="1">
         <v>3</v>
@@ -21773,28 +21788,28 @@
         <v>108</v>
       </c>
       <c r="C116" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E116" t="s">
         <v>604</v>
       </c>
       <c r="F116" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="G116" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="I116" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J116" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="L116" t="s">
         <v>780</v>
       </c>
       <c r="N116" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="O116" s="1">
         <v>2</v>
@@ -21808,22 +21823,22 @@
         <v>109</v>
       </c>
       <c r="C117" t="s">
-        <v>1666</v>
+        <v>1678</v>
       </c>
       <c r="E117" t="s">
         <v>595</v>
       </c>
       <c r="F117" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I117" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J117" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L117" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="M117" t="s">
         <v>492</v>
@@ -21840,19 +21855,19 @@
         <v>110</v>
       </c>
       <c r="C118" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E118" t="s">
         <v>605</v>
       </c>
       <c r="F118" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="I118" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J118" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="K118" t="s">
         <v>766</v>
@@ -21861,7 +21876,7 @@
         <v>780</v>
       </c>
       <c r="N118" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="O118" s="1">
         <v>2</v>
@@ -21875,28 +21890,28 @@
         <v>111</v>
       </c>
       <c r="C119" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E119" t="s">
         <v>606</v>
       </c>
       <c r="F119" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="I119" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J119" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="L119" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M119" t="s">
         <v>492</v>
       </c>
       <c r="N119" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="O119" s="1">
         <v>3</v>
@@ -21910,19 +21925,19 @@
         <v>112</v>
       </c>
       <c r="C120" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E120" t="s">
         <v>607</v>
       </c>
       <c r="I120" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J120" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L120" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="M120" t="s">
         <v>492</v>
@@ -21942,22 +21957,22 @@
         <v>608</v>
       </c>
       <c r="H121" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="I121" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J121" t="s">
         <v>802</v>
       </c>
       <c r="K121" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L121" t="s">
         <v>780</v>
       </c>
       <c r="N121" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="O121" s="1">
         <v>1</v>
@@ -21974,16 +21989,16 @@
         <v>609</v>
       </c>
       <c r="H122" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I122" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J122" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="N122" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O122" s="1">
         <v>1</v>
@@ -22000,19 +22015,19 @@
         <v>610</v>
       </c>
       <c r="H123" t="s">
+        <v>959</v>
+      </c>
+      <c r="I123" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J123" t="s">
         <v>960</v>
       </c>
-      <c r="I123" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J123" t="s">
-        <v>961</v>
-      </c>
       <c r="L123" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="N123" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="O123" s="1">
         <v>1</v>
@@ -22029,19 +22044,19 @@
         <v>611</v>
       </c>
       <c r="H124" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="I124" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J124" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="L124" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="N124" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O124" s="1">
         <v>1</v>
@@ -22055,25 +22070,25 @@
         <v>117</v>
       </c>
       <c r="C125" t="s">
-        <v>1651</v>
+        <v>1664</v>
       </c>
       <c r="E125" t="s">
         <v>612</v>
       </c>
       <c r="F125" t="s">
-        <v>1413</v>
+        <v>1667</v>
       </c>
       <c r="G125" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H125" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="I125" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="J125" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K125" t="s">
         <v>770</v>
@@ -22082,7 +22097,7 @@
         <v>775</v>
       </c>
       <c r="N125" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="O125" s="1">
         <v>2</v>
@@ -22099,22 +22114,22 @@
         <v>613</v>
       </c>
       <c r="F126" t="s">
-        <v>1448</v>
+        <v>1439</v>
       </c>
       <c r="G126" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="I126" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J126" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="K126" t="s">
         <v>770</v>
       </c>
       <c r="L126" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="O126" s="1">
         <v>2</v>
@@ -22131,25 +22146,25 @@
         <v>614</v>
       </c>
       <c r="H127" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I127" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J127" t="s">
         <v>788</v>
       </c>
       <c r="K127" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="L127" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="M127" t="s">
         <v>492</v>
       </c>
       <c r="N127" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="O127" s="1">
         <v>3</v>
@@ -22163,31 +22178,31 @@
         <v>120</v>
       </c>
       <c r="C128" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D128" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="E128" t="s">
         <v>615</v>
       </c>
       <c r="F128" t="s">
-        <v>1629</v>
+        <v>1618</v>
       </c>
       <c r="G128" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="H128" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="I128" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J128" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="N128" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="O128" s="1">
         <v>2</v>
@@ -22204,16 +22219,16 @@
         <v>616</v>
       </c>
       <c r="F129" t="s">
-        <v>1449</v>
+        <v>1440</v>
       </c>
       <c r="H129" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="I129" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J129" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K129" t="s">
         <v>766</v>
@@ -22222,7 +22237,7 @@
         <v>783</v>
       </c>
       <c r="N129" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="O129" s="1">
         <v>2</v>
@@ -22236,28 +22251,28 @@
         <v>122</v>
       </c>
       <c r="C130" t="s">
-        <v>1667</v>
+        <v>1650</v>
       </c>
       <c r="E130" t="s">
         <v>617</v>
       </c>
       <c r="F130" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="H130" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I130" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J130" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="K130" t="s">
         <v>768</v>
       </c>
       <c r="N130" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O130" s="1">
         <v>2</v>
@@ -22274,16 +22289,16 @@
         <v>618</v>
       </c>
       <c r="H131" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="I131" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J131" t="s">
         <v>762</v>
       </c>
       <c r="N131" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O131" s="1">
         <v>1</v>
@@ -22300,22 +22315,22 @@
         <v>619</v>
       </c>
       <c r="H132" t="s">
+        <v>974</v>
+      </c>
+      <c r="I132" t="s">
+        <v>1237</v>
+      </c>
+      <c r="J132" t="s">
         <v>975</v>
-      </c>
-      <c r="I132" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J132" t="s">
-        <v>976</v>
       </c>
       <c r="K132" t="s">
         <v>771</v>
       </c>
       <c r="L132" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="N132" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O132" s="1">
         <v>1</v>
@@ -22332,16 +22347,16 @@
         <v>620</v>
       </c>
       <c r="F133" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="H133" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="I133" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J133" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K133" t="s">
         <v>766</v>
@@ -22350,7 +22365,7 @@
         <v>780</v>
       </c>
       <c r="N133" t="s">
-        <v>1483</v>
+        <v>1472</v>
       </c>
       <c r="O133" s="1">
         <v>2</v>
@@ -22367,10 +22382,10 @@
         <v>621</v>
       </c>
       <c r="H134" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="I134" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J134" t="s">
         <v>765</v>
@@ -22382,7 +22397,7 @@
         <v>805</v>
       </c>
       <c r="N134" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="O134" s="1">
         <v>1</v>
@@ -22396,31 +22411,31 @@
         <v>127</v>
       </c>
       <c r="C135" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="E135" t="s">
         <v>622</v>
       </c>
       <c r="F135" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="H135" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I135" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J135" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="K135" t="s">
         <v>770</v>
       </c>
       <c r="L135" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="N135" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O135" s="1">
         <v>2</v>
@@ -22437,16 +22452,16 @@
         <v>623</v>
       </c>
       <c r="H136" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="I136" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J136" t="s">
         <v>797</v>
       </c>
       <c r="N136" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O136" s="1">
         <v>1</v>
@@ -22463,16 +22478,16 @@
         <v>129</v>
       </c>
       <c r="H137" t="s">
+        <v>982</v>
+      </c>
+      <c r="I137" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J137" t="s">
         <v>983</v>
       </c>
-      <c r="I137" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J137" t="s">
-        <v>984</v>
-      </c>
       <c r="N137" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O137" s="1">
         <v>2</v>
@@ -22489,16 +22504,16 @@
         <v>130</v>
       </c>
       <c r="H138" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I138" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="J138" t="s">
         <v>771</v>
       </c>
       <c r="K138" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="L138" t="s">
         <v>780</v>
@@ -22507,7 +22522,7 @@
         <v>492</v>
       </c>
       <c r="N138" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="O138" s="1">
         <v>3</v>
@@ -22521,28 +22536,28 @@
         <v>131</v>
       </c>
       <c r="C139" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E139" t="s">
         <v>625</v>
       </c>
       <c r="F139" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H139" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="I139" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J139" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="L139" t="s">
         <v>775</v>
       </c>
       <c r="N139" t="s">
-        <v>1481</v>
+        <v>1470</v>
       </c>
       <c r="O139" s="1">
         <v>2</v>
@@ -22559,16 +22574,16 @@
         <v>626</v>
       </c>
       <c r="F140" t="s">
-        <v>1636</v>
+        <v>1624</v>
       </c>
       <c r="I140" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J140" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N140" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="O140" s="1">
         <v>1</v>
@@ -22582,22 +22597,22 @@
         <v>133</v>
       </c>
       <c r="D141" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="E141" t="s">
         <v>627</v>
       </c>
       <c r="G141" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="H141" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="I141" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J141" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K141" t="s">
         <v>769</v>
@@ -22606,7 +22621,7 @@
         <v>775</v>
       </c>
       <c r="N141" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O141" s="1">
         <v>2</v>
@@ -22620,19 +22635,19 @@
         <v>334</v>
       </c>
       <c r="C142" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="E142" t="s">
         <v>628</v>
       </c>
       <c r="H142" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="I142" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J142" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K142" t="s">
         <v>770</v>
@@ -22641,7 +22656,7 @@
         <v>805</v>
       </c>
       <c r="N142" t="s">
-        <v>1485</v>
+        <v>1474</v>
       </c>
       <c r="O142" s="1">
         <v>1</v>
@@ -22658,10 +22673,10 @@
         <v>629</v>
       </c>
       <c r="F143" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="I143" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J143" t="s">
         <v>796</v>
@@ -22670,10 +22685,10 @@
         <v>766</v>
       </c>
       <c r="L143" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="N143" t="s">
-        <v>1477</v>
+        <v>1466</v>
       </c>
       <c r="O143" s="1">
         <v>2</v>
@@ -22687,22 +22702,22 @@
         <v>135</v>
       </c>
       <c r="C144" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="E144" t="s">
         <v>630</v>
       </c>
       <c r="H144" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="I144" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J144" t="s">
         <v>792</v>
       </c>
       <c r="N144" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O144" s="1">
         <v>2</v>
@@ -22719,19 +22734,19 @@
         <v>631</v>
       </c>
       <c r="F145" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="I145" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J145" t="s">
         <v>785</v>
       </c>
       <c r="L145" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N145" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O145" s="1">
         <v>1</v>
@@ -22745,16 +22760,16 @@
         <v>137</v>
       </c>
       <c r="C146" t="s">
-        <v>1668</v>
+        <v>1651</v>
       </c>
       <c r="E146" t="s">
         <v>632</v>
       </c>
       <c r="H146" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="I146" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J146" t="s">
         <v>796</v>
@@ -22766,7 +22781,7 @@
         <v>780</v>
       </c>
       <c r="N146" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="O146" s="1">
         <v>1</v>
@@ -22783,22 +22798,22 @@
         <v>633</v>
       </c>
       <c r="F147" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G147" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
       <c r="I147" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J147" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="M147" t="s">
         <v>492</v>
       </c>
       <c r="N147" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="O147" s="1">
         <v>3</v>
@@ -22815,13 +22830,13 @@
         <v>634</v>
       </c>
       <c r="F148" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="H148" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I148" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J148" t="s">
         <v>796</v>
@@ -22833,7 +22848,7 @@
         <v>805</v>
       </c>
       <c r="N148" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="O148" s="1">
         <v>2</v>
@@ -22847,22 +22862,22 @@
         <v>140</v>
       </c>
       <c r="C149" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="E149" t="s">
         <v>635</v>
       </c>
       <c r="F149" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="I149" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J149" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="N149" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O149" s="1">
         <v>2</v>
@@ -22876,31 +22891,31 @@
         <v>141</v>
       </c>
       <c r="C150" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="E150" t="s">
         <v>636</v>
       </c>
       <c r="F150" t="s">
-        <v>1467</v>
+        <v>1456</v>
       </c>
       <c r="G150" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="I150" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J150" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L150" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="M150" t="s">
         <v>492</v>
       </c>
       <c r="N150" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="O150" s="1">
         <v>3</v>
@@ -22914,7 +22929,7 @@
         <v>142</v>
       </c>
       <c r="C151" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E151" t="s">
         <v>637</v>
@@ -22923,19 +22938,19 @@
         <v>142</v>
       </c>
       <c r="H151" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I151" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="J151" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L151" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="N151" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O151" s="1">
         <v>1</v>
@@ -22952,25 +22967,25 @@
         <v>639</v>
       </c>
       <c r="F152" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="G152" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="H152" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="I152" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J152" t="s">
         <v>754</v>
       </c>
       <c r="L152" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="N152" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O152" s="1">
         <v>2</v>
@@ -22987,13 +23002,13 @@
         <v>641</v>
       </c>
       <c r="F153" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H153" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="I153" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="J153" t="s">
         <v>791</v>
@@ -23002,10 +23017,10 @@
         <v>770</v>
       </c>
       <c r="L153" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N153" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O153" s="1">
         <v>2</v>
@@ -23022,22 +23037,22 @@
         <v>642</v>
       </c>
       <c r="H154" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I154" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="J154" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K154" t="s">
         <v>770</v>
       </c>
       <c r="L154" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="N154" t="s">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="O154" s="1">
         <v>1</v>
@@ -23054,16 +23069,16 @@
         <v>643</v>
       </c>
       <c r="F155" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="I155" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J155" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L155" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="M155" t="s">
         <v>492</v>
@@ -23083,19 +23098,19 @@
         <v>644</v>
       </c>
       <c r="H156" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="I156" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J156" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="L156" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="N156" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="O156" s="1">
         <v>2</v>
@@ -23109,22 +23124,22 @@
         <v>786</v>
       </c>
       <c r="C157" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E157" t="s">
         <v>521</v>
       </c>
       <c r="F157" t="s">
-        <v>1431</v>
+        <v>1422</v>
       </c>
       <c r="G157" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="H157" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I157" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J157" t="s">
         <v>797</v>
@@ -23136,7 +23151,7 @@
         <v>780</v>
       </c>
       <c r="N157" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="O157" s="1">
         <v>2</v>
@@ -23150,25 +23165,25 @@
         <v>148</v>
       </c>
       <c r="C158" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="E158" t="s">
         <v>645</v>
       </c>
       <c r="F158" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="G158" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H158" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="I158" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J158" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="K158" t="s">
         <v>770</v>
@@ -23177,7 +23192,7 @@
         <v>775</v>
       </c>
       <c r="N158" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="O158" s="1">
         <v>2</v>
@@ -23191,16 +23206,16 @@
         <v>149</v>
       </c>
       <c r="C159" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="E159" t="s">
         <v>646</v>
       </c>
       <c r="F159" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="I159" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J159" t="s">
         <v>788</v>
@@ -23212,7 +23227,7 @@
         <v>780</v>
       </c>
       <c r="N159" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="O159" s="1">
         <v>2</v>
@@ -23229,13 +23244,13 @@
         <v>647</v>
       </c>
       <c r="F160" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="H160" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="I160" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J160" t="s">
         <v>791</v>
@@ -23247,7 +23262,7 @@
         <v>775</v>
       </c>
       <c r="N160" t="s">
-        <v>1478</v>
+        <v>1467</v>
       </c>
       <c r="O160" s="1">
         <v>2</v>
@@ -23264,22 +23279,22 @@
         <v>648</v>
       </c>
       <c r="F161" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="H161" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I161" t="s">
         <v>1015</v>
-      </c>
-      <c r="I161" t="s">
-        <v>1016</v>
       </c>
       <c r="J161" t="s">
         <v>778</v>
       </c>
       <c r="L161" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="N161" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O161" s="1">
         <v>2</v>
@@ -23296,28 +23311,28 @@
         <v>649</v>
       </c>
       <c r="F162" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="G162" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="H162" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="I162" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J162" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="K162" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="L162" t="s">
         <v>783</v>
       </c>
       <c r="N162" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="O162" s="1">
         <v>1</v>
@@ -23334,22 +23349,22 @@
         <v>650</v>
       </c>
       <c r="F163" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="G163" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="H163" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="I163" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="J163" t="s">
         <v>758</v>
       </c>
       <c r="N163" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O163" s="1">
         <v>1</v>
@@ -23363,19 +23378,19 @@
         <v>154</v>
       </c>
       <c r="C164" t="s">
-        <v>1669</v>
+        <v>1652</v>
       </c>
       <c r="D164" t="s">
-        <v>1458</v>
+        <v>1448</v>
       </c>
       <c r="E164" t="s">
         <v>651</v>
       </c>
       <c r="F164" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="I164" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J164" t="s">
         <v>770</v>
@@ -23384,13 +23399,13 @@
         <v>770</v>
       </c>
       <c r="L164" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="M164" t="s">
         <v>492</v>
       </c>
       <c r="N164" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="O164" s="1">
         <v>3</v>
@@ -23407,10 +23422,10 @@
         <v>652</v>
       </c>
       <c r="H165" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="I165" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J165" t="s">
         <v>777</v>
@@ -23430,22 +23445,22 @@
         <v>156</v>
       </c>
       <c r="C166" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E166" t="s">
         <v>653</v>
       </c>
       <c r="F166" t="s">
-        <v>1450</v>
+        <v>1441</v>
       </c>
       <c r="I166" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J166" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K166" t="s">
         <v>1026</v>
-      </c>
-      <c r="K166" t="s">
-        <v>1027</v>
       </c>
       <c r="L166" t="s">
         <v>783</v>
@@ -23454,7 +23469,7 @@
         <v>492</v>
       </c>
       <c r="N166" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="O166" s="1">
         <v>3</v>
@@ -23471,19 +23486,19 @@
         <v>654</v>
       </c>
       <c r="I167" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J167" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K167" t="s">
         <v>762</v>
       </c>
       <c r="L167" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="N167" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="O167" s="1">
         <v>1</v>
@@ -23497,25 +23512,25 @@
         <v>158</v>
       </c>
       <c r="C168" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="E168" t="s">
         <v>656</v>
       </c>
       <c r="H168" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="I168" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J168" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="L168" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N168" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="O168" s="1">
         <v>2</v>
@@ -23526,25 +23541,25 @@
         <v>469</v>
       </c>
       <c r="B169" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C169" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E169" t="s">
         <v>655</v>
       </c>
       <c r="H169" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="I169" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="J169" t="s">
         <v>777</v>
       </c>
       <c r="N169" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O169" s="1">
         <v>1</v>
@@ -23561,16 +23576,16 @@
         <v>657</v>
       </c>
       <c r="F170" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="H170" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J170" t="s">
         <v>1034</v>
-      </c>
-      <c r="I170" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J170" t="s">
-        <v>1035</v>
       </c>
       <c r="K170" t="s">
         <v>766</v>
@@ -23579,7 +23594,7 @@
         <v>805</v>
       </c>
       <c r="N170" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="O170" s="1">
         <v>1</v>
@@ -23596,16 +23611,16 @@
         <v>658</v>
       </c>
       <c r="F171" t="s">
-        <v>1635</v>
+        <v>1623</v>
       </c>
       <c r="G171" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="I171" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J171" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="K171" t="s">
         <v>770</v>
@@ -23614,7 +23629,7 @@
         <v>783</v>
       </c>
       <c r="N171" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="O171" s="1">
         <v>2</v>
@@ -23631,22 +23646,22 @@
         <v>659</v>
       </c>
       <c r="F172" t="s">
-        <v>1639</v>
+        <v>1627</v>
       </c>
       <c r="H172" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="I172" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J172" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M172" t="s">
         <v>492</v>
       </c>
       <c r="N172" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="O172" s="1">
         <v>3</v>
@@ -23663,16 +23678,16 @@
         <v>162</v>
       </c>
       <c r="F173" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H173" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="I173" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="J173" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K173" t="s">
         <v>791</v>
@@ -23681,7 +23696,7 @@
         <v>780</v>
       </c>
       <c r="N173" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="O173" s="1">
         <v>1</v>
@@ -23695,31 +23710,31 @@
         <v>163</v>
       </c>
       <c r="C174" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E174" t="s">
         <v>660</v>
       </c>
       <c r="F174" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H174" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="I174" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J174" t="s">
         <v>751</v>
       </c>
       <c r="K174" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L174" t="s">
         <v>1039</v>
       </c>
-      <c r="L174" t="s">
-        <v>1040</v>
-      </c>
       <c r="N174" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="O174" s="1">
         <v>2</v>
@@ -23736,22 +23751,22 @@
         <v>661</v>
       </c>
       <c r="F175" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="H175" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="I175" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J175" t="s">
         <v>777</v>
       </c>
       <c r="L175" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="N175" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O175" s="1">
         <v>2</v>
@@ -23768,16 +23783,16 @@
         <v>662</v>
       </c>
       <c r="H176" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I176" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J176" t="s">
         <v>762</v>
       </c>
       <c r="N176" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O176" s="1">
         <v>1</v>
@@ -23791,28 +23806,28 @@
         <v>166</v>
       </c>
       <c r="C177" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="E177" t="s">
         <v>663</v>
       </c>
       <c r="F177" t="s">
-        <v>1415</v>
+        <v>1676</v>
       </c>
       <c r="I177" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J177" t="s">
         <v>762</v>
       </c>
       <c r="L177" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="M177" t="s">
         <v>492</v>
       </c>
       <c r="N177" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O177" s="1">
         <v>3</v>
@@ -23826,22 +23841,22 @@
         <v>167</v>
       </c>
       <c r="C178" t="s">
-        <v>1630</v>
+        <v>1619</v>
       </c>
       <c r="E178" t="s">
         <v>664</v>
       </c>
       <c r="H178" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="I178" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J178" t="s">
         <v>785</v>
       </c>
       <c r="N178" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O178" s="1">
         <v>1</v>
@@ -23858,10 +23873,10 @@
         <v>665</v>
       </c>
       <c r="I179" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J179" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K179" t="s">
         <v>766</v>
@@ -23873,7 +23888,7 @@
         <v>492</v>
       </c>
       <c r="N179" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="O179" s="1">
         <v>3</v>
@@ -23890,10 +23905,10 @@
         <v>666</v>
       </c>
       <c r="H180" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="I180" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="J180" t="s">
         <v>787</v>
@@ -23902,7 +23917,7 @@
         <v>770</v>
       </c>
       <c r="L180" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O180" s="1">
         <v>1</v>
@@ -23916,22 +23931,22 @@
         <v>170</v>
       </c>
       <c r="C181" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E181" t="s">
         <v>667</v>
       </c>
       <c r="H181" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="I181" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J181" t="s">
         <v>762</v>
       </c>
       <c r="N181" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O181" s="1">
         <v>2</v>
@@ -23948,16 +23963,16 @@
         <v>668</v>
       </c>
       <c r="H182" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I182" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J182" t="s">
         <v>785</v>
       </c>
       <c r="N182" t="s">
-        <v>1479</v>
+        <v>1468</v>
       </c>
       <c r="O182" s="1">
         <v>1</v>
@@ -23971,22 +23986,22 @@
         <v>172</v>
       </c>
       <c r="C183" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E183" t="s">
         <v>587</v>
       </c>
       <c r="H183" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I183" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J183" t="s">
+        <v>837</v>
+      </c>
+      <c r="L183" t="s">
         <v>838</v>
-      </c>
-      <c r="L183" t="s">
-        <v>839</v>
       </c>
       <c r="O183" s="1">
         <v>1</v>
@@ -24000,22 +24015,22 @@
         <v>173</v>
       </c>
       <c r="C184" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E184" t="s">
         <v>670</v>
       </c>
       <c r="F184" t="s">
-        <v>1461</v>
+        <v>1451</v>
       </c>
       <c r="H184" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I184" t="s">
+        <v>828</v>
+      </c>
+      <c r="J184" t="s">
         <v>1047</v>
-      </c>
-      <c r="I184" t="s">
-        <v>829</v>
-      </c>
-      <c r="J184" t="s">
-        <v>1048</v>
       </c>
       <c r="K184" t="s">
         <v>770</v>
@@ -24024,7 +24039,7 @@
         <v>780</v>
       </c>
       <c r="N184" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="O184" s="1">
         <v>2</v>
@@ -24035,19 +24050,19 @@
         <v>272</v>
       </c>
       <c r="B185" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C185" t="s">
         <v>1049</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1050</v>
       </c>
       <c r="E185" t="s">
         <v>671</v>
       </c>
       <c r="H185" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I185" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J185" t="s">
         <v>779</v>
@@ -24059,7 +24074,7 @@
         <v>780</v>
       </c>
       <c r="N185" t="s">
-        <v>1474</v>
+        <v>1463</v>
       </c>
       <c r="O185" s="1">
         <v>1</v>
@@ -24070,10 +24085,10 @@
         <v>381</v>
       </c>
       <c r="B186" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C186" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="E186" t="s">
         <v>686</v>
@@ -24085,16 +24100,16 @@
         <v>114</v>
       </c>
       <c r="I186" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J186" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="L186" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="N186" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O186" s="1">
         <v>2</v>
@@ -24108,22 +24123,22 @@
         <v>174</v>
       </c>
       <c r="C187" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E187" t="s">
         <v>672</v>
       </c>
       <c r="H187" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="I187" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J187" t="s">
         <v>760</v>
       </c>
       <c r="L187" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O187" s="1">
         <v>1</v>
@@ -24137,28 +24152,28 @@
         <v>175</v>
       </c>
       <c r="C188" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E188" t="s">
         <v>673</v>
       </c>
       <c r="F188" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G188" t="s">
+        <v>1372</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J188" t="s">
         <v>1055</v>
-      </c>
-      <c r="G188" t="s">
-        <v>1375</v>
-      </c>
-      <c r="I188" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J188" t="s">
-        <v>1056</v>
       </c>
       <c r="M188" t="s">
         <v>492</v>
       </c>
       <c r="N188" t="s">
-        <v>1481</v>
+        <v>1470</v>
       </c>
       <c r="O188" s="1">
         <v>3</v>
@@ -24175,16 +24190,16 @@
         <v>674</v>
       </c>
       <c r="H189" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="I189" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J189" t="s">
         <v>754</v>
       </c>
       <c r="N189" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O189" s="1">
         <v>1</v>
@@ -24201,16 +24216,16 @@
         <v>675</v>
       </c>
       <c r="F190" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="H190" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J190" t="s">
         <v>1058</v>
-      </c>
-      <c r="I190" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J190" t="s">
-        <v>1059</v>
       </c>
       <c r="K190" t="s">
         <v>770</v>
@@ -24219,7 +24234,7 @@
         <v>775</v>
       </c>
       <c r="N190" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O190" s="1">
         <v>2</v>
@@ -24236,16 +24251,16 @@
         <v>676</v>
       </c>
       <c r="H191" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I191" t="s">
+        <v>827</v>
+      </c>
+      <c r="J191" t="s">
         <v>1060</v>
       </c>
-      <c r="I191" t="s">
-        <v>828</v>
-      </c>
-      <c r="J191" t="s">
-        <v>1061</v>
-      </c>
       <c r="N191" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O191" s="1">
         <v>1</v>
@@ -24262,10 +24277,10 @@
         <v>677</v>
       </c>
       <c r="F192" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="I192" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J192" t="s">
         <v>777</v>
@@ -24280,7 +24295,7 @@
         <v>492</v>
       </c>
       <c r="N192" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="O192" s="1">
         <v>3</v>
@@ -24294,25 +24309,25 @@
         <v>179</v>
       </c>
       <c r="C193" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="E193" t="s">
         <v>678</v>
       </c>
       <c r="F193" t="s">
-        <v>1462</v>
+        <v>1452</v>
       </c>
       <c r="G193" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="H193" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I193" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J193" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K193" t="s">
         <v>769</v>
@@ -24324,7 +24339,7 @@
         <v>492</v>
       </c>
       <c r="N193" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="O193" s="1">
         <v>3</v>
@@ -24338,22 +24353,22 @@
         <v>180</v>
       </c>
       <c r="C194" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="D194" t="s">
-        <v>1489</v>
+        <v>1478</v>
       </c>
       <c r="E194" t="s">
         <v>679</v>
       </c>
       <c r="F194" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="I194" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J194" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="K194" t="s">
         <v>766</v>
@@ -24362,7 +24377,7 @@
         <v>780</v>
       </c>
       <c r="N194" t="s">
-        <v>1473</v>
+        <v>1462</v>
       </c>
       <c r="O194" s="1">
         <v>2</v>
@@ -24376,22 +24391,22 @@
         <v>737</v>
       </c>
       <c r="C195" t="s">
-        <v>1670</v>
+        <v>1653</v>
       </c>
       <c r="E195" t="s">
         <v>687</v>
       </c>
       <c r="I195" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J195" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K195" t="s">
         <v>1065</v>
       </c>
-      <c r="K195" t="s">
-        <v>1066</v>
-      </c>
       <c r="N195" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="O195" s="1">
         <v>2</v>
@@ -24405,25 +24420,25 @@
         <v>181</v>
       </c>
       <c r="C196" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="E196" t="s">
         <v>680</v>
       </c>
       <c r="F196" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="I196" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J196" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="K196" t="s">
         <v>771</v>
       </c>
       <c r="N196" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O196" s="1">
         <v>2</v>
@@ -24437,25 +24452,25 @@
         <v>182</v>
       </c>
       <c r="C197" t="s">
-        <v>1671</v>
+        <v>1654</v>
       </c>
       <c r="E197" t="s">
         <v>681</v>
       </c>
       <c r="I197" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J197" t="s">
         <v>766</v>
       </c>
       <c r="L197" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="M197" t="s">
         <v>492</v>
       </c>
       <c r="N197" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="O197" s="1">
         <v>3</v>
@@ -24469,37 +24484,37 @@
         <v>481</v>
       </c>
       <c r="C198" t="s">
-        <v>1451</v>
+        <v>1668</v>
       </c>
       <c r="D198" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="E198" t="s">
         <v>682</v>
       </c>
       <c r="F198" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G198" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="H198" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="I198" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J198" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L198" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="M198" t="s">
         <v>492</v>
       </c>
       <c r="N198" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O198" s="1">
         <v>3</v>
@@ -24513,25 +24528,25 @@
         <v>183</v>
       </c>
       <c r="C199" t="s">
-        <v>1658</v>
+        <v>1644</v>
       </c>
       <c r="E199" t="s">
         <v>683</v>
       </c>
       <c r="F199" t="s">
-        <v>1659</v>
+        <v>1645</v>
       </c>
       <c r="I199" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="J199" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K199" t="s">
         <v>770</v>
       </c>
       <c r="L199" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M199" t="s">
         <v>492</v>
@@ -24551,10 +24566,10 @@
         <v>684</v>
       </c>
       <c r="F200" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="I200" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J200" t="s">
         <v>791</v>
@@ -24563,10 +24578,10 @@
         <v>766</v>
       </c>
       <c r="L200" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="N200" t="s">
-        <v>1483</v>
+        <v>1472</v>
       </c>
       <c r="O200" s="1">
         <v>2</v>
@@ -24583,13 +24598,13 @@
         <v>685</v>
       </c>
       <c r="I201" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J201" t="s">
         <v>760</v>
       </c>
       <c r="L201" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="M201" t="s">
         <v>492</v>
@@ -24609,16 +24624,16 @@
         <v>736</v>
       </c>
       <c r="F202" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="I202" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="J202" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L202" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M202" t="s">
         <v>492</v>
@@ -24635,16 +24650,16 @@
         <v>187</v>
       </c>
       <c r="C203" t="s">
-        <v>1674</v>
+        <v>1656</v>
       </c>
       <c r="E203" t="s">
         <v>688</v>
       </c>
       <c r="F203" t="s">
-        <v>1675</v>
+        <v>1657</v>
       </c>
       <c r="I203" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="J203" t="s">
         <v>792</v>
@@ -24656,7 +24671,7 @@
         <v>780</v>
       </c>
       <c r="N203" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="O203" s="1">
         <v>2</v>
@@ -24673,19 +24688,19 @@
         <v>689</v>
       </c>
       <c r="H204" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I204" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J204" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="M204" t="s">
         <v>492</v>
       </c>
       <c r="N204" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="O204" s="1">
         <v>3</v>
@@ -24702,10 +24717,10 @@
         <v>690</v>
       </c>
       <c r="H205" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="I205" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="J205" t="s">
         <v>792</v>
@@ -24717,7 +24732,7 @@
         <v>780</v>
       </c>
       <c r="N205" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="O205" s="1">
         <v>1</v>
@@ -24733,20 +24748,23 @@
       <c r="E206" t="s">
         <v>691</v>
       </c>
+      <c r="F206" t="s">
+        <v>1660</v>
+      </c>
       <c r="H206" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="I206" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J206" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L206" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="N206" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O206" s="1">
         <v>1</v>
@@ -24760,19 +24778,19 @@
         <v>191</v>
       </c>
       <c r="C207" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="E207" t="s">
         <v>584</v>
       </c>
       <c r="I207" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J207" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="N207" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="O207" s="1">
         <v>2</v>
@@ -24789,16 +24807,16 @@
         <v>692</v>
       </c>
       <c r="H208" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I208" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J208" t="s">
         <v>1072</v>
       </c>
-      <c r="I208" t="s">
-        <v>1273</v>
-      </c>
-      <c r="J208" t="s">
-        <v>1073</v>
-      </c>
       <c r="N208" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O208" s="1">
         <v>2</v>
@@ -24815,10 +24833,10 @@
         <v>193</v>
       </c>
       <c r="H209" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="I209" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="J209" t="s">
         <v>762</v>
@@ -24827,7 +24845,7 @@
         <v>805</v>
       </c>
       <c r="N209" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="O209" s="1">
         <v>1</v>
@@ -24841,19 +24859,19 @@
         <v>483</v>
       </c>
       <c r="C210" t="s">
-        <v>1672</v>
+        <v>1655</v>
       </c>
       <c r="E210" t="s">
         <v>511</v>
       </c>
       <c r="F210" t="s">
-        <v>1653</v>
+        <v>1639</v>
       </c>
       <c r="I210" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J210" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K210" t="s">
         <v>758</v>
@@ -24865,7 +24883,7 @@
         <v>492</v>
       </c>
       <c r="N210" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="O210" s="1">
         <v>3</v>
@@ -24879,31 +24897,31 @@
         <v>194</v>
       </c>
       <c r="C211" t="s">
-        <v>1430</v>
+        <v>1674</v>
       </c>
       <c r="E211" t="s">
         <v>693</v>
       </c>
       <c r="F211" t="s">
-        <v>1627</v>
+        <v>1616</v>
       </c>
       <c r="H211" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="I211" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J211" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L211" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="M211" t="s">
         <v>492</v>
       </c>
       <c r="N211" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="O211" s="1">
         <v>3</v>
@@ -24920,13 +24938,13 @@
         <v>694</v>
       </c>
       <c r="H212" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I212" t="s">
+        <v>1237</v>
+      </c>
+      <c r="J212" t="s">
         <v>1076</v>
-      </c>
-      <c r="I212" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J212" t="s">
-        <v>1077</v>
       </c>
       <c r="K212" t="s">
         <v>769</v>
@@ -24935,7 +24953,7 @@
         <v>780</v>
       </c>
       <c r="N212" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="O212" s="1">
         <v>1</v>
@@ -24952,19 +24970,19 @@
         <v>695</v>
       </c>
       <c r="H213" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="I213" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J213" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="L213" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N213" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O213" s="1">
         <v>1</v>
@@ -24981,22 +24999,22 @@
         <v>696</v>
       </c>
       <c r="F214" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="H214" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="I214" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="J214" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="L214" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N214" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O214" s="1">
         <v>1</v>
@@ -25010,16 +25028,16 @@
         <v>198</v>
       </c>
       <c r="C215" t="s">
-        <v>1459</v>
+        <v>1449</v>
       </c>
       <c r="E215" t="s">
         <v>697</v>
       </c>
       <c r="H215" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I215" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="J215" t="s">
         <v>778</v>
@@ -25031,7 +25049,7 @@
         <v>780</v>
       </c>
       <c r="N215" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="O215" s="1">
         <v>1</v>
@@ -25048,19 +25066,19 @@
         <v>698</v>
       </c>
       <c r="H216" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="I216" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="J216" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="L216" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="N216" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O216" s="1">
         <v>1</v>
@@ -25077,25 +25095,25 @@
         <v>699</v>
       </c>
       <c r="F217" t="s">
-        <v>1660</v>
+        <v>1646</v>
       </c>
       <c r="G217" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="I217" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J217" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="K217" t="s">
         <v>770</v>
       </c>
       <c r="L217" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N217" t="s">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="O217" s="1">
         <v>2</v>
@@ -25109,16 +25127,16 @@
         <v>738</v>
       </c>
       <c r="C218" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="E218" t="s">
         <v>638</v>
       </c>
       <c r="F218" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="I218" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J218" t="s">
         <v>778</v>
@@ -25130,7 +25148,7 @@
         <v>780</v>
       </c>
       <c r="N218" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="O218" s="1">
         <v>2</v>
@@ -25144,22 +25162,22 @@
         <v>201</v>
       </c>
       <c r="C219" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E219" t="s">
         <v>1118</v>
-      </c>
-      <c r="E219" t="s">
-        <v>1119</v>
       </c>
       <c r="F219" t="s">
         <v>700</v>
       </c>
       <c r="H219" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I219" t="s">
         <v>1082</v>
       </c>
-      <c r="I219" t="s">
-        <v>1083</v>
-      </c>
       <c r="J219" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K219" t="s">
         <v>766</v>
@@ -25168,7 +25186,7 @@
         <v>780</v>
       </c>
       <c r="N219" t="s">
-        <v>1483</v>
+        <v>1472</v>
       </c>
       <c r="O219" s="1">
         <v>1</v>
@@ -25185,19 +25203,19 @@
         <v>701</v>
       </c>
       <c r="F220" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H220" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I220" t="s">
+        <v>882</v>
+      </c>
+      <c r="J220" t="s">
         <v>1084</v>
       </c>
-      <c r="I220" t="s">
-        <v>883</v>
-      </c>
-      <c r="J220" t="s">
-        <v>1085</v>
-      </c>
       <c r="N220" t="s">
-        <v>1480</v>
+        <v>1469</v>
       </c>
       <c r="O220" s="1">
         <v>1</v>
@@ -25214,25 +25232,25 @@
         <v>702</v>
       </c>
       <c r="F221" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="G221" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="H221" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I221" t="s">
+        <v>978</v>
+      </c>
+      <c r="J221" t="s">
         <v>1086</v>
-      </c>
-      <c r="I221" t="s">
-        <v>979</v>
-      </c>
-      <c r="J221" t="s">
-        <v>1087</v>
       </c>
       <c r="K221" t="s">
         <v>771</v>
       </c>
       <c r="N221" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="O221" s="1">
         <v>1</v>
@@ -25246,22 +25264,22 @@
         <v>204</v>
       </c>
       <c r="C222" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E222" t="s">
         <v>703</v>
       </c>
       <c r="F222" t="s">
-        <v>1463</v>
+        <v>1453</v>
       </c>
       <c r="H222" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="I222" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J222" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K222" t="s">
         <v>770</v>
@@ -25270,7 +25288,7 @@
         <v>780</v>
       </c>
       <c r="N222" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="O222" s="1">
         <v>2</v>
@@ -25287,13 +25305,13 @@
         <v>704</v>
       </c>
       <c r="H223" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="I223" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J223" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="K223" t="s">
         <v>770</v>
@@ -25302,7 +25320,7 @@
         <v>780</v>
       </c>
       <c r="N223" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O223" s="1">
         <v>2</v>
@@ -25319,10 +25337,10 @@
         <v>705</v>
       </c>
       <c r="H224" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I224" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="J224" t="s">
         <v>788</v>
@@ -25345,10 +25363,10 @@
         <v>706</v>
       </c>
       <c r="H225" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I225" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J225" t="s">
         <v>762</v>
@@ -25357,10 +25375,10 @@
         <v>766</v>
       </c>
       <c r="L225" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N225" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="O225" s="1">
         <v>1</v>
@@ -25377,28 +25395,28 @@
         <v>708</v>
       </c>
       <c r="F226" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="G226" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="H226" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="I226" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="J226" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K226" t="s">
         <v>770</v>
       </c>
       <c r="L226" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N226" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="O226" s="1">
         <v>2</v>
@@ -25415,13 +25433,13 @@
         <v>709</v>
       </c>
       <c r="F227" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="I227" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="J227" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="K227" t="s">
         <v>766</v>
@@ -25433,7 +25451,7 @@
         <v>492</v>
       </c>
       <c r="N227" t="s">
-        <v>1484</v>
+        <v>1473</v>
       </c>
       <c r="O227" s="1">
         <v>3</v>
@@ -25450,16 +25468,16 @@
         <v>710</v>
       </c>
       <c r="H228" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I228" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J228" t="s">
         <v>1092</v>
       </c>
-      <c r="I228" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J228" t="s">
-        <v>1093</v>
-      </c>
       <c r="N228" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="O228" s="1">
         <v>1</v>
@@ -25473,16 +25491,16 @@
         <v>485</v>
       </c>
       <c r="C229" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E229" t="s">
         <v>711</v>
       </c>
       <c r="F229" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="G229" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J229" t="s">
         <v>802</v>
@@ -25491,7 +25509,7 @@
         <v>766</v>
       </c>
       <c r="L229" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M229" t="s">
         <v>492</v>
@@ -25508,19 +25526,19 @@
         <v>211</v>
       </c>
       <c r="C230" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E230" t="s">
         <v>712</v>
       </c>
       <c r="I230" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J230" t="s">
         <v>802</v>
       </c>
       <c r="L230" t="s">
-        <v>1642</v>
+        <v>1630</v>
       </c>
       <c r="M230" t="s">
         <v>492</v>
@@ -25540,16 +25558,16 @@
         <v>713</v>
       </c>
       <c r="H231" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I231" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J231" t="s">
         <v>777</v>
       </c>
       <c r="N231" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O231" s="1">
         <v>1</v>
@@ -25566,10 +25584,10 @@
         <v>714</v>
       </c>
       <c r="H232" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="I232" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="J232" t="s">
         <v>790</v>
@@ -25581,7 +25599,7 @@
         <v>780</v>
       </c>
       <c r="N232" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="O232" s="1">
         <v>2</v>
@@ -25595,22 +25613,22 @@
         <v>214</v>
       </c>
       <c r="C233" t="s">
-        <v>1632</v>
+        <v>1669</v>
       </c>
       <c r="E233" t="s">
         <v>715</v>
       </c>
       <c r="F233" t="s">
-        <v>1633</v>
+        <v>1621</v>
       </c>
       <c r="H233" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I233" t="s">
+        <v>1273</v>
+      </c>
+      <c r="J233" t="s">
         <v>1095</v>
-      </c>
-      <c r="I233" t="s">
-        <v>1275</v>
-      </c>
-      <c r="J233" t="s">
-        <v>1096</v>
       </c>
       <c r="K233" t="s">
         <v>766</v>
@@ -25619,7 +25637,7 @@
         <v>780</v>
       </c>
       <c r="N233" t="s">
-        <v>1483</v>
+        <v>1472</v>
       </c>
       <c r="O233" s="1">
         <v>2</v>
@@ -25633,16 +25651,16 @@
         <v>215</v>
       </c>
       <c r="C234" t="s">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="E234" t="s">
         <v>716</v>
       </c>
       <c r="F234" t="s">
-        <v>1661</v>
+        <v>1647</v>
       </c>
       <c r="I234" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J234" t="s">
         <v>788</v>
@@ -25651,13 +25669,13 @@
         <v>766</v>
       </c>
       <c r="L234" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M234" t="s">
         <v>492</v>
       </c>
       <c r="N234" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="O234" s="1">
         <v>3</v>
@@ -25674,10 +25692,10 @@
         <v>717</v>
       </c>
       <c r="F235" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="I235" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J235" t="s">
         <v>762</v>
@@ -25686,10 +25704,10 @@
         <v>769</v>
       </c>
       <c r="L235" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N235" t="s">
-        <v>1484</v>
+        <v>1473</v>
       </c>
       <c r="O235" s="1">
         <v>2</v>
@@ -25703,22 +25721,22 @@
         <v>217</v>
       </c>
       <c r="C236" t="s">
-        <v>1262</v>
+        <v>1663</v>
       </c>
       <c r="E236" t="s">
         <v>718</v>
       </c>
       <c r="F236" t="s">
-        <v>1649</v>
+        <v>1637</v>
       </c>
       <c r="I236" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J236" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N236" t="s">
-        <v>1470</v>
+        <v>1459</v>
       </c>
       <c r="O236" s="1">
         <v>2</v>
@@ -25732,34 +25750,34 @@
         <v>744</v>
       </c>
       <c r="C237" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D237" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="E237" t="s">
         <v>745</v>
       </c>
       <c r="F237" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G237" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="I237" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="J237" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L237" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="M237" t="s">
         <v>492</v>
       </c>
       <c r="N237" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O237" s="1">
         <v>3</v>
@@ -25776,10 +25794,10 @@
         <v>719</v>
       </c>
       <c r="H238" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="I238" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J238" t="s">
         <v>762</v>
@@ -25788,10 +25806,10 @@
         <v>762</v>
       </c>
       <c r="L238" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="N238" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="O238" s="1">
         <v>1</v>
@@ -25808,10 +25826,10 @@
         <v>720</v>
       </c>
       <c r="H239" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="I239" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="J239" t="s">
         <v>762</v>
@@ -25823,7 +25841,7 @@
         <v>805</v>
       </c>
       <c r="N239" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="O239" s="1">
         <v>1</v>
@@ -25840,16 +25858,16 @@
         <v>721</v>
       </c>
       <c r="F240" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="G240" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="H240" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="I240" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="J240" t="s">
         <v>787</v>
@@ -25861,7 +25879,7 @@
         <v>805</v>
       </c>
       <c r="N240" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="O240" s="1">
         <v>2</v>
@@ -25875,22 +25893,22 @@
         <v>221</v>
       </c>
       <c r="C241" t="s">
-        <v>1637</v>
+        <v>1625</v>
       </c>
       <c r="E241" t="s">
         <v>722</v>
       </c>
       <c r="F241" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="I241" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="J241" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L241" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="M241" t="s">
         <v>492</v>
@@ -25910,22 +25928,22 @@
         <v>723</v>
       </c>
       <c r="F242" t="s">
-        <v>1404</v>
+        <v>1665</v>
       </c>
       <c r="I242" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J242" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="K242" t="s">
         <v>770</v>
       </c>
       <c r="L242" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="N242" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="O242" s="1">
         <v>2</v>
@@ -25942,16 +25960,16 @@
         <v>724</v>
       </c>
       <c r="H243" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I243" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J243" t="s">
         <v>788</v>
       </c>
       <c r="N243" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O243" s="1">
         <v>1</v>
@@ -25968,10 +25986,10 @@
         <v>725</v>
       </c>
       <c r="H244" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="I244" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J244" t="s">
         <v>790</v>
@@ -25980,10 +25998,10 @@
         <v>766</v>
       </c>
       <c r="L244" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="N244" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O244" s="1">
         <v>2</v>
@@ -26000,16 +26018,16 @@
         <v>726</v>
       </c>
       <c r="H245" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="I245" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J245" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="N245" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O245" s="1">
         <v>1</v>
@@ -26026,13 +26044,13 @@
         <v>727</v>
       </c>
       <c r="H246" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I246" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J246" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="K246" t="s">
         <v>770</v>
@@ -26041,7 +26059,7 @@
         <v>775</v>
       </c>
       <c r="N246" t="s">
-        <v>1484</v>
+        <v>1473</v>
       </c>
       <c r="O246" s="1">
         <v>1</v>
@@ -26058,19 +26076,19 @@
         <v>728</v>
       </c>
       <c r="F247" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="G247" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="H247" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I247" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J247" t="s">
         <v>1104</v>
-      </c>
-      <c r="I247" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J247" t="s">
-        <v>1105</v>
       </c>
       <c r="K247" t="s">
         <v>766</v>
@@ -26079,7 +26097,7 @@
         <v>805</v>
       </c>
       <c r="N247" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="O247" s="1">
         <v>2</v>
@@ -26096,22 +26114,22 @@
         <v>729</v>
       </c>
       <c r="F248" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="I248" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J248" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="K248" t="s">
         <v>770</v>
       </c>
       <c r="L248" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="N248" t="s">
-        <v>1480</v>
+        <v>1469</v>
       </c>
       <c r="O248" s="1">
         <v>2</v>
@@ -26128,13 +26146,13 @@
         <v>730</v>
       </c>
       <c r="H249" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="I249" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J249" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K249" t="s">
         <v>766</v>
@@ -26143,7 +26161,7 @@
         <v>780</v>
       </c>
       <c r="N249" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="O249" s="1">
         <v>1</v>
@@ -26160,19 +26178,19 @@
         <v>731</v>
       </c>
       <c r="F250" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="G250" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="H250" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I250" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J250" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K250" t="s">
         <v>770</v>
@@ -26181,7 +26199,7 @@
         <v>780</v>
       </c>
       <c r="N250" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="O250" s="1">
         <v>1</v>
@@ -26195,16 +26213,16 @@
         <v>231</v>
       </c>
       <c r="C251" t="s">
-        <v>1433</v>
+        <v>1424</v>
       </c>
       <c r="E251" t="s">
         <v>732</v>
       </c>
       <c r="F251" t="s">
-        <v>1432</v>
+        <v>1423</v>
       </c>
       <c r="I251" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J251" t="s">
         <v>762</v>
@@ -26213,7 +26231,7 @@
         <v>766</v>
       </c>
       <c r="L251" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="M251" t="s">
         <v>492</v>
@@ -26233,22 +26251,22 @@
         <v>733</v>
       </c>
       <c r="F252" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G252" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="H252" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I252" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J252" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N252" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O252" s="1">
         <v>2</v>
@@ -26265,19 +26283,19 @@
         <v>734</v>
       </c>
       <c r="H253" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I253" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="J253" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K253" t="s">
+        <v>844</v>
+      </c>
+      <c r="L253" t="s">
         <v>1110</v>
-      </c>
-      <c r="K253" t="s">
-        <v>845</v>
-      </c>
-      <c r="L253" t="s">
-        <v>1111</v>
       </c>
       <c r="O253" s="1">
         <v>2</v>
@@ -26294,25 +26312,25 @@
         <v>735</v>
       </c>
       <c r="F254" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
       <c r="H254" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I254" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J254" t="s">
         <v>1112</v>
       </c>
-      <c r="I254" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J254" t="s">
-        <v>1113</v>
-      </c>
       <c r="K254" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="L254" t="s">
         <v>780</v>
       </c>
       <c r="N254" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="O254" s="1">
         <v>1</v>
@@ -26349,40 +26367,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1435</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1442</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1445</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1440</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1436</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1437</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1438</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1439</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -28068,7 +28086,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C41" s="1">
         <v>34</v>
@@ -31078,7 +31096,7 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -33572,7 +33590,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C169" s="1">
         <v>47</v>
@@ -34260,7 +34278,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C185" s="1">
         <v>51</v>
@@ -34303,7 +34321,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C186" s="1">
         <v>59</v>
@@ -37365,40 +37383,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1435</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1442</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1445</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1440</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1436</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1437</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1438</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1439</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -37625,7 +37643,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -37840,7 +37858,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -37883,7 +37901,7 @@
         <v>743</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -38141,7 +38159,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -38399,7 +38417,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -38571,7 +38589,7 @@
         <v>482</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -39084,7 +39102,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C41" s="1">
         <v>43</v>
@@ -39732,7 +39750,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -40420,7 +40438,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -40549,7 +40567,7 @@
         <v>71</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -40764,7 +40782,7 @@
         <v>76</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
@@ -40979,7 +40997,7 @@
         <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -41022,7 +41040,7 @@
         <v>82</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -41065,7 +41083,7 @@
         <v>83</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -41151,7 +41169,7 @@
         <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -41366,7 +41384,7 @@
         <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -41495,7 +41513,7 @@
         <v>93</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -41624,7 +41642,7 @@
         <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
@@ -41796,7 +41814,7 @@
         <v>487</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
@@ -41882,7 +41900,7 @@
         <v>101</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
@@ -41925,7 +41943,7 @@
         <v>102</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
@@ -41968,7 +41986,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
@@ -42011,7 +42029,7 @@
         <v>431</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
@@ -42054,7 +42072,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
@@ -42094,10 +42112,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
@@ -42140,7 +42158,7 @@
         <v>105</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -42183,7 +42201,7 @@
         <v>106</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
@@ -42226,7 +42244,7 @@
         <v>601</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -42269,7 +42287,7 @@
         <v>107</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
@@ -42355,7 +42373,7 @@
         <v>109</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
@@ -42441,7 +42459,7 @@
         <v>111</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
@@ -42484,7 +42502,7 @@
         <v>112</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
@@ -42785,7 +42803,7 @@
         <v>119</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
@@ -43258,7 +43276,7 @@
         <v>130</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
@@ -43645,7 +43663,7 @@
         <v>138</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
@@ -43774,7 +43792,7 @@
         <v>141</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
@@ -43989,7 +44007,7 @@
         <v>146</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
@@ -44376,7 +44394,7 @@
         <v>154</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
@@ -44462,7 +44480,7 @@
         <v>156</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -44588,7 +44606,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C169" s="1">
         <v>46</v>
@@ -44720,7 +44738,7 @@
         <v>161</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -44935,7 +44953,7 @@
         <v>166</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D177" s="1">
         <v>0</v>
@@ -45021,7 +45039,7 @@
         <v>168</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
@@ -45276,7 +45294,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C185" s="1">
         <v>42</v>
@@ -45319,7 +45337,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C186" s="1">
         <v>55</v>
@@ -45408,7 +45426,7 @@
         <v>175</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D188" s="1">
         <v>0</v>
@@ -45580,7 +45598,7 @@
         <v>484</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D192" s="1">
         <v>0</v>
@@ -45623,7 +45641,7 @@
         <v>179</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D193" s="1">
         <v>0</v>
@@ -45795,7 +45813,7 @@
         <v>182</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D197" s="1">
         <v>0</v>
@@ -45838,7 +45856,7 @@
         <v>481</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D198" s="1">
         <v>0</v>
@@ -45881,7 +45899,7 @@
         <v>183</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D199" s="1">
         <v>0</v>
@@ -45967,7 +45985,7 @@
         <v>185</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D201" s="1">
         <v>0</v>
@@ -46010,7 +46028,7 @@
         <v>742</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D202" s="1">
         <v>0</v>
@@ -46096,7 +46114,7 @@
         <v>188</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D204" s="1">
         <v>0</v>
@@ -46354,7 +46372,7 @@
         <v>483</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D210" s="1">
         <v>0</v>
@@ -46397,7 +46415,7 @@
         <v>194</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D211" s="1">
         <v>0</v>
@@ -47085,7 +47103,7 @@
         <v>209</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D227" s="1">
         <v>0</v>
@@ -47171,7 +47189,7 @@
         <v>485</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D229" s="1">
         <v>0</v>
@@ -47214,7 +47232,7 @@
         <v>211</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D230" s="1">
         <v>0</v>
@@ -47386,7 +47404,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D234" s="1">
         <v>0</v>
@@ -47515,7 +47533,7 @@
         <v>744</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D237" s="1">
         <v>0</v>
@@ -47687,7 +47705,7 @@
         <v>221</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D241" s="1">
         <v>0</v>
@@ -48117,7 +48135,7 @@
         <v>231</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="D251" s="1">
         <v>0</v>
@@ -48382,40 +48400,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1435</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1442</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1445</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1440</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1436</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1437</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1438</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1439</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -50101,7 +50119,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C41" s="1">
         <v>59</v>
@@ -53111,7 +53129,7 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -55605,7 +55623,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C169" s="1">
         <v>53</v>
@@ -56293,7 +56311,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C185" s="1">
         <v>50</v>
@@ -56336,7 +56354,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C186" s="1">
         <v>41</v>
@@ -59390,19 +59408,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1501</v>
+        <v>1490</v>
       </c>
       <c r="B1" t="s">
-        <v>1611</v>
+        <v>1600</v>
       </c>
       <c r="C1" t="s">
-        <v>1612</v>
+        <v>1601</v>
       </c>
       <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>1613</v>
+        <v>1602</v>
       </c>
       <c r="B2" s="1">
         <v>938</v>
@@ -59414,7 +59432,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1614</v>
+        <v>1603</v>
       </c>
       <c r="B3" s="1">
         <v>935</v>
@@ -59426,7 +59444,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1615</v>
+        <v>1604</v>
       </c>
       <c r="B4" s="1">
         <v>932</v>
@@ -59438,7 +59456,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1616</v>
+        <v>1605</v>
       </c>
       <c r="B5" s="1">
         <v>672</v>
@@ -59450,7 +59468,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1617</v>
+        <v>1606</v>
       </c>
       <c r="B6" s="1">
         <v>757</v>
@@ -59462,7 +59480,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1618</v>
+        <v>1607</v>
       </c>
       <c r="B7" s="1">
         <v>343</v>
@@ -59474,7 +59492,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1619</v>
+        <v>1608</v>
       </c>
       <c r="B8" s="1">
         <v>899</v>
@@ -59486,7 +59504,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="B9" s="1">
         <v>822</v>
@@ -59498,7 +59516,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>1621</v>
+        <v>1610</v>
       </c>
       <c r="B10" s="1">
         <v>953</v>
@@ -59510,7 +59528,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>1622</v>
+        <v>1611</v>
       </c>
       <c r="B11" s="1">
         <v>909</v>
@@ -59522,7 +59540,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1624</v>
+        <v>1613</v>
       </c>
       <c r="B12" s="1">
         <v>853</v>
@@ -59534,7 +59552,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
       <c r="B13" s="1">
         <v>987</v>
@@ -59546,7 +59564,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
       <c r="B14" s="1">
         <v>802</v>
@@ -59558,7 +59576,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>1626</v>
+        <v>1615</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -59570,19 +59588,19 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1509</v>
+        <v>1498</v>
       </c>
       <c r="B17" t="s">
-        <v>1611</v>
+        <v>1600</v>
       </c>
       <c r="C17" t="s">
-        <v>1612</v>
+        <v>1601</v>
       </c>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>1613</v>
+        <v>1602</v>
       </c>
       <c r="B18" s="1">
         <v>976</v>
@@ -59594,7 +59612,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>1614</v>
+        <v>1603</v>
       </c>
       <c r="B19" s="1">
         <v>956</v>
@@ -59606,7 +59624,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>1615</v>
+        <v>1604</v>
       </c>
       <c r="B20" s="1">
         <v>808</v>
@@ -59618,7 +59636,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>1616</v>
+        <v>1605</v>
       </c>
       <c r="B21" s="1">
         <v>696</v>
@@ -59630,7 +59648,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1617</v>
+        <v>1606</v>
       </c>
       <c r="B22" s="1">
         <v>506</v>
@@ -59642,7 +59660,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>1618</v>
+        <v>1607</v>
       </c>
       <c r="B23" s="1">
         <v>274</v>
@@ -59654,7 +59672,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1619</v>
+        <v>1608</v>
       </c>
       <c r="B24" s="1">
         <v>977</v>
@@ -59666,7 +59684,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="B25" s="1">
         <v>371</v>
@@ -59678,7 +59696,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1621</v>
+        <v>1610</v>
       </c>
       <c r="B26" s="1">
         <v>916</v>
@@ -59690,7 +59708,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>1622</v>
+        <v>1611</v>
       </c>
       <c r="B27" s="1">
         <v>976</v>
@@ -59702,7 +59720,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>1623</v>
+        <v>1612</v>
       </c>
       <c r="B28" s="1">
         <v>959</v>
@@ -59714,7 +59732,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>1624</v>
+        <v>1613</v>
       </c>
       <c r="B29" s="1">
         <v>783</v>
@@ -59726,7 +59744,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
       <c r="B30" s="1">
         <v>802</v>
@@ -59738,7 +59756,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>1626</v>
+        <v>1615</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
@@ -59750,18 +59768,18 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1512</v>
+        <v>1501</v>
       </c>
       <c r="B33" t="s">
-        <v>1611</v>
+        <v>1600</v>
       </c>
       <c r="C33" t="s">
-        <v>1612</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1613</v>
+        <v>1602</v>
       </c>
       <c r="B34" s="1">
         <v>1041</v>
@@ -59773,7 +59791,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1614</v>
+        <v>1603</v>
       </c>
       <c r="B35" s="1">
         <v>979</v>
@@ -59785,7 +59803,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1615</v>
+        <v>1604</v>
       </c>
       <c r="B36" s="1">
         <v>690</v>
@@ -59797,7 +59815,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1616</v>
+        <v>1605</v>
       </c>
       <c r="B37" s="1">
         <v>745</v>
@@ -59809,7 +59827,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1617</v>
+        <v>1606</v>
       </c>
       <c r="B38" s="1">
         <v>519</v>
@@ -59821,7 +59839,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1618</v>
+        <v>1607</v>
       </c>
       <c r="B39" s="1">
         <v>291</v>
@@ -59833,7 +59851,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1619</v>
+        <v>1608</v>
       </c>
       <c r="B40" s="1">
         <v>962</v>
@@ -59845,7 +59863,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="B41" s="1">
         <v>77</v>
@@ -59857,7 +59875,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1621</v>
+        <v>1610</v>
       </c>
       <c r="B42" s="1">
         <v>964</v>
@@ -59869,7 +59887,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1622</v>
+        <v>1611</v>
       </c>
       <c r="B43" s="1">
         <v>1038</v>
@@ -59881,7 +59899,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1623</v>
+        <v>1612</v>
       </c>
       <c r="B44" s="1">
         <v>980</v>
@@ -59893,7 +59911,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1624</v>
+        <v>1613</v>
       </c>
       <c r="B45" s="1">
         <v>782</v>
@@ -59905,7 +59923,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
       <c r="B46" s="1">
         <v>932</v>
@@ -59917,7 +59935,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1626</v>
+        <v>1615</v>
       </c>
       <c r="B47" s="1">
         <v>0</v>
@@ -59951,155 +59969,155 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1">
       <c r="A1" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1492</v>
+        <v>1481</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1493</v>
+        <v>1482</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1494</v>
+        <v>1483</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1495</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>1496</v>
+        <v>1485</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1497</v>
+        <v>1486</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1498</v>
+        <v>1487</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1499</v>
+        <v>1488</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1500</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>1501</v>
+        <v>1490</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1502</v>
+        <v>1491</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1503</v>
+        <v>1492</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1504</v>
+        <v>1493</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1500</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>1505</v>
+        <v>1494</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1506</v>
+        <v>1495</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1507</v>
+        <v>1496</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1508</v>
+        <v>1497</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1500</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>1509</v>
+        <v>1498</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1510</v>
+        <v>1499</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1511</v>
+        <v>1500</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1508</v>
+        <v>1497</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1500</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>1512</v>
+        <v>1501</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1513</v>
+        <v>1502</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1514</v>
+        <v>1503</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1515</v>
+        <v>1504</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1516</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>1517</v>
+        <v>1506</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1518</v>
+        <v>1507</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1519</v>
+        <v>1508</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1520</v>
+        <v>1509</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1521</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>1522</v>
+        <v>1511</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1523</v>
+        <v>1512</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1524</v>
+        <v>1513</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1525</v>
+        <v>1514</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1526</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>1527</v>
+        <v>1516</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1528</v>
+        <v>1517</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1529</v>
+        <v>1518</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1530</v>
+        <v>1519</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1500</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1"/>
@@ -60108,280 +60126,280 @@
         <v>312</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1531</v>
+        <v>1520</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>1532</v>
+        <v>1521</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1533</v>
+        <v>1522</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>1534</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29.25" thickBot="1">
       <c r="A12" s="9" t="s">
-        <v>1535</v>
+        <v>1524</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1536</v>
+        <v>1525</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1537</v>
+        <v>1526</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1538</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="29.25" thickBot="1">
       <c r="A13" s="9" t="s">
-        <v>1539</v>
+        <v>1528</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1540</v>
+        <v>1529</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1541</v>
+        <v>1530</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1542</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="43.5" thickBot="1">
       <c r="A14" s="9" t="s">
-        <v>1543</v>
+        <v>1532</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1544</v>
+        <v>1533</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1545</v>
+        <v>1534</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1546</v>
+        <v>1535</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>1547</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.5" thickBot="1">
       <c r="A15" s="9" t="s">
-        <v>1548</v>
+        <v>1537</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1549</v>
+        <v>1538</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1545</v>
+        <v>1534</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1550</v>
+        <v>1539</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1551</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.5" thickBot="1">
       <c r="A16" s="9" t="s">
-        <v>1552</v>
+        <v>1541</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1553</v>
+        <v>1542</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1554</v>
+        <v>1543</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1555</v>
+        <v>1544</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1556</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.5" thickBot="1">
       <c r="A17" s="9" t="s">
-        <v>1557</v>
+        <v>1546</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1558</v>
+        <v>1547</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1554</v>
+        <v>1543</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1559</v>
+        <v>1548</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1560</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="29.25" thickBot="1">
       <c r="A18" s="9" t="s">
-        <v>1561</v>
+        <v>1550</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1562</v>
+        <v>1551</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1563</v>
+        <v>1552</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1564</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="29.25" thickBot="1">
       <c r="A19" s="9" t="s">
-        <v>1565</v>
+        <v>1554</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1566</v>
+        <v>1555</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1554</v>
+        <v>1543</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1567</v>
+        <v>1556</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1542</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="43.5" thickBot="1">
       <c r="A20" s="9" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1545</v>
+        <v>1534</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1570</v>
+        <v>1559</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1571</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="43.5" thickBot="1">
       <c r="A21" s="9" t="s">
-        <v>1572</v>
+        <v>1561</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1573</v>
+        <v>1562</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1574</v>
+        <v>1563</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1575</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="29.25" thickBot="1">
       <c r="A22" s="9" t="s">
-        <v>1576</v>
+        <v>1565</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1577</v>
+        <v>1566</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1578</v>
+        <v>1567</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>1579</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.5" thickBot="1">
       <c r="A23" s="9" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1581</v>
+        <v>1570</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1545</v>
+        <v>1534</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1582</v>
+        <v>1571</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>1583</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="43.5" thickBot="1">
       <c r="A24" s="9" t="s">
-        <v>1584</v>
+        <v>1573</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1585</v>
+        <v>1574</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1586</v>
+        <v>1575</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1587</v>
+        <v>1576</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>1588</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.25" thickBot="1">
       <c r="A25" s="9" t="s">
-        <v>1589</v>
+        <v>1578</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1590</v>
+        <v>1579</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1591</v>
+        <v>1580</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>1592</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1"/>
     <row r="27" spans="1:5" ht="60.75" thickBot="1">
       <c r="A27" s="9" t="s">
-        <v>1593</v>
+        <v>1582</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1594</v>
+        <v>1583</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1595</v>
+        <v>1584</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1596</v>
+        <v>1585</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>1597</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="102" thickBot="1">
       <c r="A28" s="9" t="s">
-        <v>1598</v>
+        <v>1587</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1599</v>
+        <v>1588</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -60390,58 +60408,58 @@
         <v>0</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>1600</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="116.25" thickBot="1">
       <c r="A29" s="9" t="s">
-        <v>1601</v>
+        <v>1590</v>
       </c>
       <c r="B29" s="11">
         <v>0.4</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1602</v>
+        <v>1591</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1602</v>
+        <v>1591</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>1603</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="116.25" thickBot="1">
       <c r="A30" s="9" t="s">
-        <v>1604</v>
+        <v>1593</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1605</v>
+        <v>1594</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1606</v>
+        <v>1595</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>1607</v>
+        <v>1596</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>1603</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="116.25" thickBot="1">
       <c r="A31" s="9" t="s">
-        <v>1608</v>
+        <v>1597</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1605</v>
+        <v>1594</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1609</v>
+        <v>1598</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>1607</v>
+        <v>1596</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>1610</v>
+        <v>1599</v>
       </c>
     </row>
   </sheetData>

--- a/Elenco-quiz 5.0.xlsx
+++ b/Elenco-quiz 5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.bellasio\Desktop\LUCA\Bandiere\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8A877E-6BEE-4B8B-A90F-1D1CE84E7AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD74A88-A3ED-4760-9186-E3084EAAA3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="30180" windowHeight="17970" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
+    <workbookView xWindow="2850" yWindow="1170" windowWidth="30180" windowHeight="17970" xr2:uid="{4DBE396F-7C4D-4E6E-A332-C331B1342690}"/>
   </bookViews>
   <sheets>
     <sheet name="Elenco" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="1679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="1685">
   <si>
     <t>Sigla</t>
   </si>
@@ -3042,9 +3042,6 @@
     <t>Valletta</t>
   </si>
   <si>
-    <t>Fort de France</t>
-  </si>
-  <si>
     <t>thailandia, singapore, brunei, indonesia, mare</t>
   </si>
   <si>
@@ -3132,9 +3129,6 @@
     <t>union jack,croce del sud, stella</t>
   </si>
   <si>
-    <t>mezzaluna,croce del sud, palma, cerchio</t>
-  </si>
-  <si>
     <t>Paesi Bassi</t>
   </si>
   <si>
@@ -3441,9 +3435,6 @@
     <t>blu</t>
   </si>
   <si>
-    <t>cerchio, scritta</t>
-  </si>
-  <si>
     <t>foglia</t>
   </si>
   <si>
@@ -3780,9 +3771,6 @@
     <t>cerchio rosso, lenzuolo verde</t>
   </si>
   <si>
-    <t>cerchio blu, lenzuolo verde</t>
-  </si>
-  <si>
     <t>stella gialla, lenzuolo rosso</t>
   </si>
   <si>
@@ -3924,9 +3912,6 @@
     <t>Dillendstadt</t>
   </si>
   <si>
-    <t>Flying Fish Club</t>
-  </si>
-  <si>
     <t>Abbia, Appia</t>
   </si>
   <si>
@@ -3936,9 +3921,6 @@
     <t>Con rovia</t>
   </si>
   <si>
-    <t>Marigoz</t>
-  </si>
-  <si>
     <t>Sport Villa</t>
   </si>
   <si>
@@ -4191,9 +4173,6 @@
     <t>Sanà a</t>
   </si>
   <si>
-    <t>Maiuro, Ma giuro</t>
-  </si>
-  <si>
     <t>Plymuth, Plasmat</t>
   </si>
   <si>
@@ -4251,9 +4230,6 @@
     <t>base terra, passe terra</t>
   </si>
   <si>
-    <t>carlot amelie, sciarlot</t>
-  </si>
-  <si>
     <t>porto moresby, port mores bi</t>
   </si>
   <si>
@@ -4272,12 +4248,6 @@
     <t>Azkaban, Azkabat, asgabat</t>
   </si>
   <si>
-    <t>a lo fi, all of i</t>
-  </si>
-  <si>
-    <t>Nuku alofa, Mutualopa, Nukolov, nucu alofa, nuco a lo fa</t>
-  </si>
-  <si>
     <t>lictenstain, frankenstein</t>
   </si>
   <si>
@@ -4317,9 +4287,6 @@
     <t>mata utu, mad a u2</t>
   </si>
   <si>
-    <t>Wallis, Futuna, Wallis e Futura, Wally se futura</t>
-  </si>
-  <si>
     <t>Pnom Pen, Non Pen, Pnonten, Pnom Pehn</t>
   </si>
   <si>
@@ -4374,9 +4341,6 @@
     <t>MEDIA.SE</t>
   </si>
   <si>
-    <t>felice</t>
-  </si>
-  <si>
     <t>Olivia</t>
   </si>
   <si>
@@ -4395,24 +4359,15 @@
     <t>Sono aria</t>
   </si>
   <si>
-    <t>La Vella, dora la vella</t>
-  </si>
-  <si>
     <t>Langui, bottega</t>
   </si>
   <si>
-    <t>el aiun, aaiun, Ela jun, Aiun, elaine</t>
-  </si>
-  <si>
     <t>Ruba, Juve, giuva</t>
   </si>
   <si>
     <t>Arare, sparare</t>
   </si>
   <si>
-    <t>Onyara, Uniara, Onira</t>
-  </si>
-  <si>
     <t>Mamodzu, Mamotzu, ma mozu, mahmood</t>
   </si>
   <si>
@@ -4468,9 +4423,6 @@
   </si>
   <si>
     <t>mezzaluna gialla, stella gialla, Riquadro in alto a sinistra</t>
-  </si>
-  <si>
-    <t>Gigi, Fiji, Luigi, Pigi</t>
   </si>
   <si>
     <t>Banda verticale a lato</t>
@@ -5403,9 +5355,6 @@
     <t>emblema nazionale, arma, animale, uccello</t>
   </si>
   <si>
-    <t>albero, union jack, corona</t>
-  </si>
-  <si>
     <t>Reikiavik</t>
   </si>
   <si>
@@ -5415,12 +5364,6 @@
     <t>Agatnia, agatna, agata, a gatta, la gatta, accatna, a canna, a gadna</t>
   </si>
   <si>
-    <t>Nuk, nuke</t>
-  </si>
-  <si>
-    <t>*Malabo, la pass, città della pace</t>
-  </si>
-  <si>
     <t>King edward, edward point</t>
   </si>
   <si>
@@ -5430,9 +5373,6 @@
     <t>Duck</t>
   </si>
   <si>
-    <t>oranistad, oranistadt, orangestar, Orari estad, Orangestadt, oranistag, orari estate, orari istant</t>
-  </si>
-  <si>
     <t>Nasso</t>
   </si>
   <si>
@@ -5448,15 +5388,9 @@
     <t>Saint Pierre, S Pierre, Miquelon, san pierre michelon, san pierre e miquelon, sentiero michielon</t>
   </si>
   <si>
-    <t>Saint Pierre, S Pierre, sentiero</t>
-  </si>
-  <si>
     <t>Kotte, Sri Jayawardenapura, Colombo, sdriglia one den pura cotte, sdrigia yahoo antenne pura cotte, cotti, sri giaia, striglia guarda, free java, tre giaia, pura cotte, gioia quando ne pura cotte</t>
   </si>
   <si>
-    <t>Faco, Vaccarofo, acaofo</t>
-  </si>
-  <si>
     <t>*Belarus, velarus</t>
   </si>
   <si>
@@ -5475,21 +5409,12 @@
     <t>S Lucia, Santa Lucia</t>
   </si>
   <si>
-    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy, bartalemi, synth bardellemi, sing bardellemy, saint barthelemy, san barthelemy</t>
-  </si>
-  <si>
-    <t>S eustatius, sintestatius, sintastatius, sinteu status</t>
-  </si>
-  <si>
     <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come, soã come, sauto me principe, sau tome</t>
   </si>
   <si>
     <t>Sao Tome, Sao to me, Ciao tome, soho to me, sau come, soã come, sau tome</t>
   </si>
   <si>
-    <t>graal dick, cralendic, cra l'endic, tra l'endic, crale, calendar, trein bike, cral e decker</t>
-  </si>
-  <si>
     <t>ho detto che lau, togelao</t>
   </si>
   <si>
@@ -5538,16 +5463,109 @@
     <t>S Maarten, Sint Marten, synth martin, sean marten</t>
   </si>
   <si>
-    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis, sanchez &amp; nevis, saint kitze nevis, send kids in iris, sankitsi nevis, thank you say nadies, zenkids e nevis, send kids a nevis, schizzenavis, senkids e nadies, sentize nevis, than kisse nevis, sam kitchenavis, kids e nevis</t>
-  </si>
-  <si>
     <t>papete, papete beach, tappeti</t>
   </si>
   <si>
     <t>Cocos, Keeling, the cocos</t>
   </si>
   <si>
-    <t>Pitcairn, isole big cairn, isole pick up, isole fitkair, fitkair, speedcairn, isole bitcoin, bitcoin, isole pitcar, isole pittar, pittar</t>
+    <t>Onyara, Uniara, Onira, ogni ara</t>
+  </si>
+  <si>
+    <t>Marigoz, marigo, mario</t>
+  </si>
+  <si>
+    <t>San Bartolomeo, St Barthelemy, Saint Barthelemy, sig bar televi, simbartelemy, bartalemi, synth bardellemi, sing bardellemy, saint barthelemy, san barthelemy, si imbarrtelemy</t>
+  </si>
+  <si>
+    <t>Gigi, Fiji, Luigi, Pigi, sigi</t>
+  </si>
+  <si>
+    <t>Faco, Vaccarofo, acaofo, fuckofo</t>
+  </si>
+  <si>
+    <t>*Malabo, la pass, città della pace, dotato della pace</t>
+  </si>
+  <si>
+    <t>oranistad, oranistadt, orangestar, Orari estad, Orangestadt, oranistag, orari estate, orari istant, brani estate</t>
+  </si>
+  <si>
+    <t>felice, elise</t>
+  </si>
+  <si>
+    <t>Nuk, nuke, look, muk</t>
+  </si>
+  <si>
+    <t>base terra, passe terra, basse e terre</t>
+  </si>
+  <si>
+    <t>Maiuro, Ma giuro, Lavoro</t>
+  </si>
+  <si>
+    <t>Fort de France, ford e franz, ford france</t>
+  </si>
+  <si>
+    <t>Caragua</t>
+  </si>
+  <si>
+    <t>a lo fi, all of i, alosi, malossi</t>
+  </si>
+  <si>
+    <t>S eustatius, sintestatius, sintastatius, sinteu status, interstatius</t>
+  </si>
+  <si>
+    <t>Saint Kitts, S Kitts, Nevis, sun kids and nevis, sanchizza e nevis, sanchez &amp; nevis, saint kitze nevis, send kids in iris, sankitsi nevis, thank you say nadies, zenkids e nevis, send kids a nevis, schizzenavis, senkids e nadies, sentize nevis, than kisse nevis, sam kitchenavis, kids e nevis, sanchizze nevis, saint kitchenavis</t>
+  </si>
+  <si>
+    <t>Wallis, Futuna, Wallis e Futura, Wally se futura, quali sei futura, wally su foto</t>
+  </si>
+  <si>
+    <t>graal dick, cralendic, cra l'endic, tra l'endic, crale, calendar, trein bike, cral e decker, crane bike, cralindick, crane night, crane &amp; decker, cral &amp; dake</t>
+  </si>
+  <si>
+    <t>Flying Fish Club, flying disco</t>
+  </si>
+  <si>
+    <t>carlot amelie, sciarlot, carlotta meli</t>
+  </si>
+  <si>
+    <t>Saint Pierre, S Pierre, sentiero, sentire michelon, saint pierre michelon, piera michelon</t>
+  </si>
+  <si>
+    <t>Nuku alofa, Mutualopa, Nukolov, nucu alofa, nuco a lo fa, nupualofa, nucu a lofa</t>
+  </si>
+  <si>
+    <t>emblema nazionale, animale</t>
+  </si>
+  <si>
+    <t>cerchio, scritta, stella</t>
+  </si>
+  <si>
+    <t>cerchio blu, lenzuolo verde, stella bianca</t>
+  </si>
+  <si>
+    <t>mezzaluna, croce del sud, albero, palma, cerchio</t>
+  </si>
+  <si>
+    <t>emblema nazionale, albero, palma</t>
+  </si>
+  <si>
+    <t>emblema nazionale, union jack, albero, palma</t>
+  </si>
+  <si>
+    <t>albero, palma, union jack, corona</t>
+  </si>
+  <si>
+    <t>Mal di neve</t>
+  </si>
+  <si>
+    <t>el aiun, aaiun, Ela jun, Aiun, elaine, e la hyunda, e la une</t>
+  </si>
+  <si>
+    <t>Pitcairn, isole big cairn, isole pick up, isole fitkair, fitkair, speedcairn, isole bitcoin, bitcoin, isole pitcar, isole pittar, pittar, isole pitbull, pitbull, isole pitburn, pitburn, isole fitker, fitker, isole pitcher</t>
+  </si>
+  <si>
+    <t>La Vella, dora la vella, pandora ravenna, pandora la vella, vella</t>
   </si>
 </sst>
 </file>
@@ -18018,7 +18036,7 @@
         <v>747</v>
       </c>
       <c r="D1" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="E1" t="s">
         <v>495</v>
@@ -18027,7 +18045,7 @@
         <v>748</v>
       </c>
       <c r="G1" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="H1" t="s">
         <v>746</v>
@@ -18048,10 +18066,10 @@
         <v>895</v>
       </c>
       <c r="N1" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="O1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -18071,7 +18089,7 @@
         <v>750</v>
       </c>
       <c r="I2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J2" t="s">
         <v>765</v>
@@ -18080,10 +18098,10 @@
         <v>766</v>
       </c>
       <c r="L2" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="N2" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O2" s="1">
         <v>1</v>
@@ -18107,13 +18125,13 @@
         <v>497</v>
       </c>
       <c r="F3" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
       <c r="H3" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I3" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="J3" t="s">
         <v>751</v>
@@ -18125,7 +18143,7 @@
         <v>773</v>
       </c>
       <c r="N3" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
@@ -18164,7 +18182,7 @@
         <v>805</v>
       </c>
       <c r="N4" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -18185,31 +18203,31 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="E5" t="s">
         <v>499</v>
       </c>
       <c r="F5" t="s">
-        <v>1450</v>
+        <v>1684</v>
       </c>
       <c r="G5" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="H5" t="s">
         <v>753</v>
       </c>
       <c r="I5" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="J5" t="s">
         <v>754</v>
       </c>
       <c r="L5" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N5" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O5" s="1">
         <v>2</v>
@@ -18229,7 +18247,7 @@
         <v>812</v>
       </c>
       <c r="I6" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="J6" t="s">
         <v>751</v>
@@ -18238,10 +18256,10 @@
         <v>770</v>
       </c>
       <c r="L6" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="N6" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="O6" s="1">
         <v>2</v>
@@ -18261,10 +18279,10 @@
         <v>864</v>
       </c>
       <c r="J7" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L7" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="M7" t="s">
         <v>492</v>
@@ -18287,13 +18305,13 @@
         <v>502</v>
       </c>
       <c r="F8" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="I8" t="s">
         <v>864</v>
       </c>
       <c r="J8" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="L8" t="s">
         <v>775</v>
@@ -18319,13 +18337,13 @@
         <v>757</v>
       </c>
       <c r="G9" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="H9" t="s">
         <v>813</v>
       </c>
       <c r="I9" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J9" t="s">
         <v>771</v>
@@ -18334,10 +18352,10 @@
         <v>766</v>
       </c>
       <c r="L9" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="N9" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -18357,7 +18375,7 @@
         <v>814</v>
       </c>
       <c r="I10" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="J10" t="s">
         <v>778</v>
@@ -18369,7 +18387,7 @@
         <v>775</v>
       </c>
       <c r="N10" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O10" s="1">
         <v>1</v>
@@ -18383,7 +18401,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>1622</v>
+        <v>1606</v>
       </c>
       <c r="E11" t="s">
         <v>504</v>
@@ -18392,13 +18410,13 @@
         <v>759</v>
       </c>
       <c r="I11" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J11" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="N11" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O11" s="1">
         <v>2</v>
@@ -18415,7 +18433,7 @@
         <v>511</v>
       </c>
       <c r="F12" t="s">
-        <v>1639</v>
+        <v>1658</v>
       </c>
       <c r="I12" t="s">
         <v>864</v>
@@ -18430,7 +18448,7 @@
         <v>492</v>
       </c>
       <c r="N12" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="O12" s="1">
         <v>3</v>
@@ -18450,13 +18468,13 @@
         <v>581</v>
       </c>
       <c r="I13" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="J13" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L13" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="M13" t="s">
         <v>492</v>
@@ -18479,16 +18497,16 @@
         <v>826</v>
       </c>
       <c r="J14" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="K14" t="s">
         <v>766</v>
       </c>
       <c r="L14" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="N14" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="O14" s="1">
         <v>1</v>
@@ -18514,7 +18532,7 @@
         <v>762</v>
       </c>
       <c r="N15" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O15" s="1">
         <v>1</v>
@@ -18528,7 +18546,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="E16" t="s">
         <v>507</v>
@@ -18537,7 +18555,7 @@
         <v>863</v>
       </c>
       <c r="I16" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J16" t="s">
         <v>763</v>
@@ -18549,7 +18567,7 @@
         <v>805</v>
       </c>
       <c r="N16" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="O16" s="1">
         <v>2</v>
@@ -18566,7 +18584,7 @@
         <v>508</v>
       </c>
       <c r="F17" t="s">
-        <v>1640</v>
+        <v>1620</v>
       </c>
       <c r="I17" t="s">
         <v>864</v>
@@ -18575,7 +18593,7 @@
         <v>781</v>
       </c>
       <c r="N17" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="O17" s="1">
         <v>2</v>
@@ -18598,13 +18616,13 @@
         <v>815</v>
       </c>
       <c r="I18" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J18" t="s">
         <v>785</v>
       </c>
       <c r="N18" t="s">
-        <v>1468</v>
+        <v>1453</v>
       </c>
       <c r="O18" s="1">
         <v>2</v>
@@ -18618,19 +18636,19 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="E19" t="s">
         <v>510</v>
       </c>
       <c r="F19" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="G19" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="I19" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J19" t="s">
         <v>785</v>
@@ -18639,7 +18657,7 @@
         <v>492</v>
       </c>
       <c r="N19" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="O19" s="1">
         <v>3</v>
@@ -18656,13 +18674,13 @@
         <v>513</v>
       </c>
       <c r="F20" t="s">
-        <v>1638</v>
+        <v>1619</v>
       </c>
       <c r="H20" t="s">
         <v>816</v>
       </c>
       <c r="I20" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J20" t="s">
         <v>787</v>
@@ -18674,7 +18692,7 @@
         <v>783</v>
       </c>
       <c r="N20" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="O20" s="1">
         <v>2</v>
@@ -18691,7 +18709,7 @@
         <v>514</v>
       </c>
       <c r="F21" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="I21" t="s">
         <v>864</v>
@@ -18706,7 +18724,7 @@
         <v>789</v>
       </c>
       <c r="N21" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O21" s="1">
         <v>2</v>
@@ -18723,16 +18741,16 @@
         <v>515</v>
       </c>
       <c r="H22" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="I22" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J22" t="s">
         <v>790</v>
       </c>
       <c r="N22" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O22" s="1">
         <v>1</v>
@@ -18746,13 +18764,13 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>1443</v>
+        <v>1659</v>
       </c>
       <c r="E23" t="s">
         <v>516</v>
       </c>
       <c r="F23" t="s">
-        <v>1479</v>
+        <v>1463</v>
       </c>
       <c r="H23" t="s">
         <v>817</v>
@@ -18767,10 +18785,10 @@
         <v>766</v>
       </c>
       <c r="L23" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="N23" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="O23" s="1">
         <v>2</v>
@@ -18787,19 +18805,19 @@
         <v>517</v>
       </c>
       <c r="F24" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="H24" t="s">
         <v>818</v>
       </c>
       <c r="I24" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="J24" t="s">
         <v>792</v>
       </c>
       <c r="N24" t="s">
-        <v>1476</v>
+        <v>1460</v>
       </c>
       <c r="O24" s="1">
         <v>2</v>
@@ -18822,7 +18840,7 @@
         <v>769</v>
       </c>
       <c r="L25" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M25" t="s">
         <v>492</v>
@@ -18845,16 +18863,16 @@
         <v>519</v>
       </c>
       <c r="F26" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="H26" t="s">
         <v>793</v>
       </c>
       <c r="I26" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J26" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="K26" t="s">
         <v>766</v>
@@ -18863,7 +18881,7 @@
         <v>794</v>
       </c>
       <c r="N26" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="O26" s="1">
         <v>2</v>
@@ -18877,7 +18895,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>1648</v>
+        <v>1626</v>
       </c>
       <c r="E27" t="s">
         <v>520</v>
@@ -18895,7 +18913,7 @@
         <v>785</v>
       </c>
       <c r="N27" t="s">
-        <v>1476</v>
+        <v>1460</v>
       </c>
       <c r="O27" s="1">
         <v>1</v>
@@ -18909,31 +18927,31 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>1444</v>
+        <v>1432</v>
       </c>
       <c r="E28" t="s">
         <v>522</v>
       </c>
       <c r="F28" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="G28" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="H28" t="s">
         <v>799</v>
       </c>
       <c r="I28" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J28" t="s">
         <v>800</v>
       </c>
       <c r="L28" t="s">
-        <v>1137</v>
+        <v>1674</v>
       </c>
       <c r="N28" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O28" s="1">
         <v>1</v>
@@ -18947,19 +18965,19 @@
         <v>482</v>
       </c>
       <c r="C29" t="s">
-        <v>1670</v>
+        <v>1645</v>
       </c>
       <c r="D29" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="E29" t="s">
         <v>523</v>
       </c>
       <c r="F29" t="s">
-        <v>1658</v>
+        <v>1669</v>
       </c>
       <c r="G29" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="I29" t="s">
         <v>864</v>
@@ -18977,7 +18995,7 @@
         <v>492</v>
       </c>
       <c r="N29" t="s">
-        <v>1461</v>
+        <v>1446</v>
       </c>
       <c r="O29" s="1">
         <v>3</v>
@@ -18991,7 +19009,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
       <c r="E30" t="s">
         <v>524</v>
@@ -19000,7 +19018,7 @@
         <v>820</v>
       </c>
       <c r="I30" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="J30" t="s">
         <v>788</v>
@@ -19012,7 +19030,7 @@
         <v>780</v>
       </c>
       <c r="N30" t="s">
-        <v>1462</v>
+        <v>1447</v>
       </c>
       <c r="O30" s="1">
         <v>1</v>
@@ -19029,10 +19047,10 @@
         <v>525</v>
       </c>
       <c r="F31" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="H31" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="I31" t="s">
         <v>958</v>
@@ -19041,7 +19059,7 @@
         <v>801</v>
       </c>
       <c r="N31" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O31" s="1">
         <v>2</v>
@@ -19061,7 +19079,7 @@
         <v>821</v>
       </c>
       <c r="I32" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="J32" t="s">
         <v>803</v>
@@ -19070,10 +19088,10 @@
         <v>802</v>
       </c>
       <c r="L32" t="s">
-        <v>1132</v>
+        <v>1675</v>
       </c>
       <c r="N32" t="s">
-        <v>1245</v>
+        <v>1676</v>
       </c>
       <c r="O32" s="1">
         <v>1</v>
@@ -19090,16 +19108,16 @@
         <v>527</v>
       </c>
       <c r="F33" t="s">
-        <v>1641</v>
+        <v>1621</v>
       </c>
       <c r="G33" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="H33" t="s">
         <v>988</v>
       </c>
       <c r="I33" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="J33" t="s">
         <v>804</v>
@@ -19108,10 +19126,10 @@
         <v>769</v>
       </c>
       <c r="L33" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="N33" t="s">
-        <v>1460</v>
+        <v>1445</v>
       </c>
       <c r="O33" s="1">
         <v>2</v>
@@ -19128,19 +19146,19 @@
         <v>528</v>
       </c>
       <c r="G34" t="s">
-        <v>1414</v>
+        <v>1404</v>
       </c>
       <c r="H34" t="s">
         <v>822</v>
       </c>
       <c r="I34" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="J34" t="s">
         <v>806</v>
       </c>
       <c r="N34" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O34" s="1">
         <v>1</v>
@@ -19157,13 +19175,13 @@
         <v>529</v>
       </c>
       <c r="F35" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
       <c r="H35" t="s">
         <v>807</v>
       </c>
       <c r="I35" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J35" t="s">
         <v>796</v>
@@ -19175,7 +19193,7 @@
         <v>780</v>
       </c>
       <c r="N35" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="O35" s="1">
         <v>2</v>
@@ -19192,13 +19210,13 @@
         <v>530</v>
       </c>
       <c r="F36" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="H36" t="s">
         <v>810</v>
       </c>
       <c r="I36" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J36" t="s">
         <v>752</v>
@@ -19210,7 +19228,7 @@
         <v>780</v>
       </c>
       <c r="N36" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="O36" s="1">
         <v>2</v>
@@ -19227,16 +19245,16 @@
         <v>531</v>
       </c>
       <c r="F37" t="s">
-        <v>1425</v>
+        <v>1414</v>
       </c>
       <c r="G37" t="s">
-        <v>1415</v>
+        <v>1405</v>
       </c>
       <c r="H37" t="s">
         <v>899</v>
       </c>
       <c r="I37" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="J37" t="s">
         <v>832</v>
@@ -19248,7 +19266,7 @@
         <v>833</v>
       </c>
       <c r="N37" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O37" s="1">
         <v>1</v>
@@ -19268,13 +19286,13 @@
         <v>532</v>
       </c>
       <c r="F38" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="H38" t="s">
         <v>834</v>
       </c>
       <c r="I38" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="J38" t="s">
         <v>835</v>
@@ -19286,7 +19304,7 @@
         <v>780</v>
       </c>
       <c r="N38" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="O38" s="1">
         <v>1</v>
@@ -19315,10 +19333,10 @@
         <v>769</v>
       </c>
       <c r="L39" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="N39" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O39" s="1">
         <v>1</v>
@@ -19335,7 +19353,7 @@
         <v>534</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>836</v>
@@ -19344,7 +19362,7 @@
         <v>780</v>
       </c>
       <c r="N40" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="O40" s="15">
         <v>2</v>
@@ -19355,16 +19373,16 @@
         <v>443</v>
       </c>
       <c r="B41" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C41" t="s">
-        <v>1620</v>
+        <v>1604</v>
       </c>
       <c r="E41" t="s">
         <v>669</v>
       </c>
       <c r="H41" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="I41" t="s">
         <v>827</v>
@@ -19373,7 +19391,7 @@
         <v>760</v>
       </c>
       <c r="N41" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="O41" s="1">
         <v>1</v>
@@ -19387,13 +19405,13 @@
         <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>1626</v>
+        <v>1610</v>
       </c>
       <c r="E42" t="s">
         <v>535</v>
       </c>
       <c r="F42" t="s">
-        <v>1617</v>
+        <v>1601</v>
       </c>
       <c r="H42" t="s">
         <v>839</v>
@@ -19405,7 +19423,7 @@
         <v>754</v>
       </c>
       <c r="N42" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O42" s="1">
         <v>2</v>
@@ -19419,19 +19437,19 @@
         <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="E43" t="s">
         <v>536</v>
       </c>
       <c r="F43" t="s">
-        <v>1419</v>
+        <v>1409</v>
       </c>
       <c r="H43" t="s">
         <v>842</v>
       </c>
       <c r="I43" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="J43" t="s">
         <v>760</v>
@@ -19443,7 +19461,7 @@
         <v>780</v>
       </c>
       <c r="N43" t="s">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="O43" s="1">
         <v>1</v>
@@ -19457,7 +19475,7 @@
         <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>1671</v>
+        <v>1646</v>
       </c>
       <c r="E44" t="s">
         <v>537</v>
@@ -19469,7 +19487,7 @@
         <v>923</v>
       </c>
       <c r="I44" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J44" t="s">
         <v>841</v>
@@ -19481,7 +19499,7 @@
         <v>780</v>
       </c>
       <c r="N44" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="O44" s="1">
         <v>1</v>
@@ -19498,19 +19516,19 @@
         <v>538</v>
       </c>
       <c r="I45" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="J45" t="s">
         <v>843</v>
       </c>
       <c r="K45" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="L45" t="s">
         <v>852</v>
       </c>
       <c r="N45" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="O45" s="1">
         <v>1</v>
@@ -19542,10 +19560,10 @@
         <v>846</v>
       </c>
       <c r="L46" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="N46" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="O46" s="1">
         <v>3</v>
@@ -19565,13 +19583,13 @@
         <v>847</v>
       </c>
       <c r="I47" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J47" t="s">
         <v>848</v>
       </c>
       <c r="N47" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O47" s="1">
         <v>1</v>
@@ -19585,13 +19603,13 @@
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>1661</v>
+        <v>1636</v>
       </c>
       <c r="E48" t="s">
         <v>540</v>
       </c>
       <c r="I48" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J48" t="s">
         <v>849</v>
@@ -19603,7 +19621,7 @@
         <v>805</v>
       </c>
       <c r="N48" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="O48" s="1">
         <v>2</v>
@@ -19632,7 +19650,7 @@
         <v>792</v>
       </c>
       <c r="N49" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="O49" s="1">
         <v>2</v>
@@ -19655,7 +19673,7 @@
         <v>928</v>
       </c>
       <c r="I50" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J50" t="s">
         <v>760</v>
@@ -19667,7 +19685,7 @@
         <v>856</v>
       </c>
       <c r="N50" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="O50" s="1">
         <v>1</v>
@@ -19693,7 +19711,7 @@
         <v>929</v>
       </c>
       <c r="I51" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J51" t="s">
         <v>858</v>
@@ -19705,7 +19723,7 @@
         <v>783</v>
       </c>
       <c r="N51" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -19719,13 +19737,13 @@
         <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="E52" t="s">
         <v>544</v>
       </c>
       <c r="F52" t="s">
-        <v>1666</v>
+        <v>1641</v>
       </c>
       <c r="G52" t="s">
         <v>860</v>
@@ -19734,13 +19752,13 @@
         <v>930</v>
       </c>
       <c r="I52" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J52" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="N52" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O52" s="1">
         <v>2</v>
@@ -19766,10 +19784,10 @@
         <v>760</v>
       </c>
       <c r="L53" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N53" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O53" s="1">
         <v>1</v>
@@ -19789,16 +19807,16 @@
         <v>932</v>
       </c>
       <c r="I54" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="J54" t="s">
         <v>777</v>
       </c>
       <c r="L54" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N54" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O54" s="1">
         <v>1</v>
@@ -19815,7 +19833,7 @@
         <v>547</v>
       </c>
       <c r="F55" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="I55" t="s">
         <v>864</v>
@@ -19830,7 +19848,7 @@
         <v>780</v>
       </c>
       <c r="N55" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="O55" s="1">
         <v>1</v>
@@ -19844,13 +19862,13 @@
         <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>1446</v>
+        <v>1434</v>
       </c>
       <c r="E56" t="s">
         <v>548</v>
       </c>
       <c r="F56" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="I56" t="s">
         <v>864</v>
@@ -19868,7 +19886,7 @@
         <v>492</v>
       </c>
       <c r="N56" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="O56" s="1">
         <v>3</v>
@@ -19885,10 +19903,10 @@
         <v>549</v>
       </c>
       <c r="H57" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="I57" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J57" t="s">
         <v>762</v>
@@ -19911,7 +19929,7 @@
         <v>550</v>
       </c>
       <c r="F58" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
       <c r="I58" t="s">
         <v>864</v>
@@ -19923,10 +19941,10 @@
         <v>867</v>
       </c>
       <c r="L58" t="s">
-        <v>1471</v>
+        <v>1456</v>
       </c>
       <c r="N58" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="O58" s="1">
         <v>2</v>
@@ -19943,22 +19961,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="s">
-        <v>1420</v>
+        <v>1410</v>
       </c>
       <c r="H59" t="s">
         <v>868</v>
       </c>
       <c r="I59" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J59" t="s">
         <v>848</v>
       </c>
       <c r="L59" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="N59" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O59" s="1">
         <v>1</v>
@@ -19975,7 +19993,7 @@
         <v>552</v>
       </c>
       <c r="F60" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="H60" t="s">
         <v>869</v>
@@ -19990,10 +20008,10 @@
         <v>770</v>
       </c>
       <c r="L60" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="N60" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -20007,7 +20025,7 @@
         <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="E61" t="s">
         <v>553</v>
@@ -20025,10 +20043,10 @@
         <v>802</v>
       </c>
       <c r="L61" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N61" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O61" s="1">
         <v>2</v>
@@ -20054,13 +20072,13 @@
         <v>875</v>
       </c>
       <c r="I62" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J62" t="s">
         <v>876</v>
       </c>
       <c r="N62" t="s">
-        <v>1476</v>
+        <v>1460</v>
       </c>
       <c r="O62" s="1">
         <v>1</v>
@@ -20080,7 +20098,7 @@
         <v>878</v>
       </c>
       <c r="I63" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="J63" t="s">
         <v>879</v>
@@ -20089,7 +20107,7 @@
         <v>770</v>
       </c>
       <c r="L63" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="O63" s="1">
         <v>2</v>
@@ -20103,7 +20121,7 @@
         <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="E64" t="s">
         <v>556</v>
@@ -20112,13 +20130,13 @@
         <v>881</v>
       </c>
       <c r="I64" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J64" t="s">
         <v>880</v>
       </c>
       <c r="N64" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O64" s="1">
         <v>1</v>
@@ -20132,16 +20150,16 @@
         <v>739</v>
       </c>
       <c r="C65" t="s">
-        <v>1662</v>
+        <v>1637</v>
       </c>
       <c r="E65" t="s">
         <v>707</v>
       </c>
       <c r="F65" t="s">
-        <v>1437</v>
+        <v>1426</v>
       </c>
       <c r="H65" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="I65" t="s">
         <v>882</v>
@@ -20150,10 +20168,10 @@
         <v>885</v>
       </c>
       <c r="L65" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="N65" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O65" s="1">
         <v>2</v>
@@ -20170,13 +20188,13 @@
         <v>557</v>
       </c>
       <c r="F66" t="s">
-        <v>1457</v>
+        <v>1442</v>
       </c>
       <c r="H66" t="s">
         <v>887</v>
       </c>
       <c r="I66" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="J66" t="s">
         <v>792</v>
@@ -20185,10 +20203,10 @@
         <v>788</v>
       </c>
       <c r="L66" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="N66" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="O66" s="1">
         <v>1</v>
@@ -20202,7 +20220,7 @@
         <v>63</v>
       </c>
       <c r="C67" t="s">
-        <v>1475</v>
+        <v>1655</v>
       </c>
       <c r="E67" t="s">
         <v>558</v>
@@ -20214,7 +20232,7 @@
         <v>938</v>
       </c>
       <c r="L67" t="s">
-        <v>1141</v>
+        <v>1679</v>
       </c>
       <c r="O67" s="1">
         <v>2</v>
@@ -20231,7 +20249,7 @@
         <v>559</v>
       </c>
       <c r="I68" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="J68" t="s">
         <v>888</v>
@@ -20240,10 +20258,10 @@
         <v>770</v>
       </c>
       <c r="L68" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="N68" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="O68" s="1">
         <v>1</v>
@@ -20263,7 +20281,7 @@
         <v>889</v>
       </c>
       <c r="I69" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J69" t="s">
         <v>890</v>
@@ -20286,7 +20304,7 @@
         <v>561</v>
       </c>
       <c r="H70" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I70" t="s">
         <v>829</v>
@@ -20295,7 +20313,7 @@
         <v>760</v>
       </c>
       <c r="N70" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O70" s="1">
         <v>1</v>
@@ -20312,22 +20330,22 @@
         <v>562</v>
       </c>
       <c r="F71" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
       <c r="G71" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="H71" t="s">
         <v>933</v>
       </c>
       <c r="I71" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="J71" t="s">
         <v>803</v>
       </c>
       <c r="N71" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O71" s="1">
         <v>2</v>
@@ -20347,7 +20365,7 @@
         <v>897</v>
       </c>
       <c r="I72" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J72" t="s">
         <v>806</v>
@@ -20373,25 +20391,25 @@
         <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>1447</v>
+        <v>1435</v>
       </c>
       <c r="E73" t="s">
         <v>564</v>
       </c>
       <c r="F73" t="s">
-        <v>1458</v>
+        <v>1443</v>
       </c>
       <c r="H73" t="s">
         <v>896</v>
       </c>
       <c r="I73" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J73" t="s">
         <v>898</v>
       </c>
       <c r="N73" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O73" s="1">
         <v>2</v>
@@ -20411,13 +20429,13 @@
         <v>900</v>
       </c>
       <c r="I74" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J74" t="s">
         <v>785</v>
       </c>
       <c r="L74" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="O74" s="1">
         <v>2</v>
@@ -20437,16 +20455,16 @@
         <v>566</v>
       </c>
       <c r="F75" t="s">
-        <v>1636</v>
+        <v>1617</v>
       </c>
       <c r="I75" t="s">
         <v>830</v>
       </c>
       <c r="J75" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L75" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M75" t="s">
         <v>492</v>
@@ -20463,7 +20481,7 @@
         <v>72</v>
       </c>
       <c r="C76" t="s">
-        <v>1649</v>
+        <v>1627</v>
       </c>
       <c r="E76" t="s">
         <v>567</v>
@@ -20478,7 +20496,7 @@
         <v>903</v>
       </c>
       <c r="N76" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O76" s="1">
         <v>1</v>
@@ -20492,7 +20510,7 @@
         <v>73</v>
       </c>
       <c r="C77" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="E77" t="s">
         <v>568</v>
@@ -20501,7 +20519,7 @@
         <v>934</v>
       </c>
       <c r="I77" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J77" t="s">
         <v>904</v>
@@ -20513,7 +20531,7 @@
         <v>780</v>
       </c>
       <c r="N77" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="O77" s="1">
         <v>1</v>
@@ -20527,7 +20545,7 @@
         <v>74</v>
       </c>
       <c r="C78" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="E78" t="s">
         <v>569</v>
@@ -20539,7 +20557,7 @@
         <v>905</v>
       </c>
       <c r="N78" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="O78" s="1">
         <v>1</v>
@@ -20556,7 +20574,7 @@
         <v>570</v>
       </c>
       <c r="I79" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J79" t="s">
         <v>785</v>
@@ -20568,7 +20586,7 @@
         <v>783</v>
       </c>
       <c r="N79" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="O79" s="1">
         <v>1</v>
@@ -20588,7 +20606,7 @@
         <v>906</v>
       </c>
       <c r="I80" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J80" t="s">
         <v>785</v>
@@ -20603,7 +20621,7 @@
         <v>492</v>
       </c>
       <c r="N80" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O80" s="1">
         <v>3</v>
@@ -20617,19 +20635,19 @@
         <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="E81" t="s">
         <v>77</v>
       </c>
       <c r="F81" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="H81" t="s">
         <v>911</v>
       </c>
       <c r="I81" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="J81" t="s">
         <v>907</v>
@@ -20641,7 +20659,7 @@
         <v>780</v>
       </c>
       <c r="N81" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="O81" s="1">
         <v>2</v>
@@ -20661,7 +20679,7 @@
         <v>926</v>
       </c>
       <c r="I82" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="J82" t="s">
         <v>871</v>
@@ -20673,7 +20691,7 @@
         <v>780</v>
       </c>
       <c r="N82" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="O82" s="1">
         <v>2</v>
@@ -20693,16 +20711,16 @@
         <v>912</v>
       </c>
       <c r="I83" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="J83" t="s">
         <v>891</v>
       </c>
       <c r="L83" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N83" t="s">
-        <v>1473</v>
+        <v>1458</v>
       </c>
       <c r="O83" s="1">
         <v>1</v>
@@ -20719,13 +20737,13 @@
         <v>573</v>
       </c>
       <c r="F84" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="G84" t="s">
-        <v>1632</v>
+        <v>1615</v>
       </c>
       <c r="I84" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J84" t="s">
         <v>800</v>
@@ -20737,7 +20755,7 @@
         <v>856</v>
       </c>
       <c r="N84" t="s">
-        <v>1464</v>
+        <v>1449</v>
       </c>
       <c r="O84" s="1">
         <v>2</v>
@@ -20754,13 +20772,13 @@
         <v>574</v>
       </c>
       <c r="F85" t="s">
-        <v>1634</v>
+        <v>1660</v>
       </c>
       <c r="H85" t="s">
         <v>925</v>
       </c>
       <c r="I85" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J85" t="s">
         <v>762</v>
@@ -20772,7 +20790,7 @@
         <v>492</v>
       </c>
       <c r="N85" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O85" s="1">
         <v>3</v>
@@ -20789,16 +20807,16 @@
         <v>575</v>
       </c>
       <c r="F86" t="s">
-        <v>1401</v>
+        <v>1661</v>
       </c>
       <c r="I86" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J86" t="s">
         <v>908</v>
       </c>
       <c r="L86" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="M86" t="s">
         <v>492</v>
@@ -20815,16 +20833,16 @@
         <v>83</v>
       </c>
       <c r="C87" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="E87" t="s">
         <v>576</v>
       </c>
       <c r="F87" t="s">
-        <v>1633</v>
+        <v>1616</v>
       </c>
       <c r="G87" t="s">
-        <v>1416</v>
+        <v>1406</v>
       </c>
       <c r="I87" t="s">
         <v>826</v>
@@ -20833,13 +20851,13 @@
         <v>909</v>
       </c>
       <c r="L87" t="s">
-        <v>1137</v>
+        <v>1678</v>
       </c>
       <c r="M87" t="s">
         <v>492</v>
       </c>
       <c r="N87" t="s">
-        <v>1465</v>
+        <v>1450</v>
       </c>
       <c r="O87" s="1">
         <v>3</v>
@@ -20862,16 +20880,16 @@
         <v>910</v>
       </c>
       <c r="I88" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="J88" t="s">
         <v>778</v>
       </c>
       <c r="L88" t="s">
-        <v>1629</v>
+        <v>1613</v>
       </c>
       <c r="N88" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O88" s="1">
         <v>2</v>
@@ -20885,22 +20903,22 @@
         <v>85</v>
       </c>
       <c r="C89" t="s">
-        <v>1672</v>
+        <v>1647</v>
       </c>
       <c r="E89" t="s">
         <v>578</v>
       </c>
       <c r="F89" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="I89" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J89" t="s">
         <v>913</v>
       </c>
       <c r="L89" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M89" t="s">
         <v>492</v>
@@ -20920,19 +20938,19 @@
         <v>579</v>
       </c>
       <c r="F90" t="s">
-        <v>1480</v>
+        <v>1464</v>
       </c>
       <c r="H90" t="s">
         <v>970</v>
       </c>
       <c r="I90" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J90" t="s">
         <v>800</v>
       </c>
       <c r="N90" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O90" s="1">
         <v>2</v>
@@ -20946,31 +20964,31 @@
         <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>1421</v>
+        <v>1411</v>
       </c>
       <c r="E91" t="s">
         <v>914</v>
       </c>
       <c r="F91" t="s">
-        <v>1635</v>
+        <v>1657</v>
       </c>
       <c r="G91" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="H91" t="s">
         <v>915</v>
       </c>
       <c r="I91" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="J91" t="s">
         <v>916</v>
       </c>
       <c r="L91" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="N91" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="O91" s="1">
         <v>2</v>
@@ -20993,7 +21011,7 @@
         <v>917</v>
       </c>
       <c r="I92" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J92" t="s">
         <v>800</v>
@@ -21005,7 +21023,7 @@
         <v>780</v>
       </c>
       <c r="N92" t="s">
-        <v>1477</v>
+        <v>1461</v>
       </c>
       <c r="O92" s="1">
         <v>2</v>
@@ -21025,13 +21043,13 @@
         <v>918</v>
       </c>
       <c r="I93" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="J93" t="s">
         <v>800</v>
       </c>
       <c r="N93" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="O93" s="1">
         <v>2</v>
@@ -21051,13 +21069,13 @@
         <v>919</v>
       </c>
       <c r="G94" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="H94" t="s">
         <v>921</v>
       </c>
       <c r="I94" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="J94" t="s">
         <v>922</v>
@@ -21072,7 +21090,7 @@
         <v>492</v>
       </c>
       <c r="N94" t="s">
-        <v>1461</v>
+        <v>1446</v>
       </c>
       <c r="O94" s="1">
         <v>3</v>
@@ -21089,22 +21107,22 @@
         <v>624</v>
       </c>
       <c r="F95" t="s">
-        <v>1673</v>
+        <v>1648</v>
       </c>
       <c r="H95" t="s">
         <v>936</v>
       </c>
       <c r="I95" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J95" t="s">
         <v>909</v>
       </c>
       <c r="L95" t="s">
-        <v>1146</v>
+        <v>1678</v>
       </c>
       <c r="N95" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O95" s="1">
         <v>1</v>
@@ -21124,7 +21142,7 @@
         <v>940</v>
       </c>
       <c r="I96" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="J96" t="s">
         <v>778</v>
@@ -21136,7 +21154,7 @@
         <v>780</v>
       </c>
       <c r="N96" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="O96" s="1">
         <v>2</v>
@@ -21156,7 +21174,7 @@
         <v>939</v>
       </c>
       <c r="I97" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J97" t="s">
         <v>762</v>
@@ -21171,7 +21189,7 @@
         <v>492</v>
       </c>
       <c r="N97" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="O97" s="1">
         <v>3</v>
@@ -21188,25 +21206,25 @@
         <v>585</v>
       </c>
       <c r="F98" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H98" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="I98" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J98" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="K98" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L98" t="s">
         <v>783</v>
       </c>
       <c r="N98" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O98" s="1">
         <v>1</v>
@@ -21223,19 +21241,19 @@
         <v>586</v>
       </c>
       <c r="F99" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="H99" t="s">
         <v>989</v>
       </c>
       <c r="I99" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="J99" t="s">
         <v>762</v>
       </c>
       <c r="N99" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O99" s="1">
         <v>1</v>
@@ -21255,13 +21273,13 @@
         <v>941</v>
       </c>
       <c r="I100" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J100" t="s">
         <v>785</v>
       </c>
       <c r="L100" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="M100" t="s">
         <v>492</v>
@@ -21284,7 +21302,7 @@
         <v>942</v>
       </c>
       <c r="I101" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="J101" t="s">
         <v>943</v>
@@ -21293,10 +21311,10 @@
         <v>769</v>
       </c>
       <c r="L101" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N101" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O101" s="1">
         <v>1</v>
@@ -21316,7 +21334,7 @@
         <v>944</v>
       </c>
       <c r="I102" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="J102" t="s">
         <v>870</v>
@@ -21328,7 +21346,7 @@
         <v>774</v>
       </c>
       <c r="N102" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O102" s="1">
         <v>1</v>
@@ -21348,13 +21366,13 @@
         <v>945</v>
       </c>
       <c r="I103" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J103" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N103" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O103" s="1">
         <v>1</v>
@@ -21377,13 +21395,13 @@
         <v>946</v>
       </c>
       <c r="I104" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J104" t="s">
         <v>785</v>
       </c>
       <c r="L104" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="M104" t="s">
         <v>492</v>
@@ -21406,10 +21424,10 @@
         <v>947</v>
       </c>
       <c r="G105" t="s">
-        <v>1631</v>
+        <v>1614</v>
       </c>
       <c r="I105" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J105" t="s">
         <v>760</v>
@@ -21435,10 +21453,10 @@
         <v>593</v>
       </c>
       <c r="G106" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="I106" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J106" t="s">
         <v>762</v>
@@ -21447,13 +21465,13 @@
         <v>766</v>
       </c>
       <c r="L106" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="M106" t="s">
         <v>492</v>
       </c>
       <c r="N106" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="O106" s="1">
         <v>3</v>
@@ -21473,10 +21491,10 @@
         <v>594</v>
       </c>
       <c r="F107" t="s">
-        <v>1293</v>
+        <v>1670</v>
       </c>
       <c r="G107" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="I107" t="s">
         <v>826</v>
@@ -21488,13 +21506,13 @@
         <v>771</v>
       </c>
       <c r="L107" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="M107" t="s">
         <v>492</v>
       </c>
       <c r="N107" t="s">
-        <v>1462</v>
+        <v>1447</v>
       </c>
       <c r="O107" s="1">
         <v>3</v>
@@ -21529,7 +21547,7 @@
         <v>492</v>
       </c>
       <c r="N108" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O108" s="1">
         <v>3</v>
@@ -21543,19 +21561,19 @@
         <v>431</v>
       </c>
       <c r="C109" t="s">
-        <v>1643</v>
+        <v>1623</v>
       </c>
       <c r="D109" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="E109" t="s">
         <v>596</v>
       </c>
       <c r="F109" t="s">
-        <v>1642</v>
+        <v>1622</v>
       </c>
       <c r="I109" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J109" t="s">
         <v>754</v>
@@ -21581,7 +21599,7 @@
         <v>950</v>
       </c>
       <c r="D110" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="E110" t="s">
         <v>597</v>
@@ -21590,10 +21608,10 @@
         <v>864</v>
       </c>
       <c r="J110" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L110" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="M110" t="s">
         <v>492</v>
@@ -21610,13 +21628,13 @@
         <v>809</v>
       </c>
       <c r="C111" t="s">
-        <v>1677</v>
+        <v>1651</v>
       </c>
       <c r="E111" t="s">
         <v>598</v>
       </c>
       <c r="F111" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="I111" t="s">
         <v>826</v>
@@ -21628,13 +21646,13 @@
         <v>770</v>
       </c>
       <c r="L111" t="s">
-        <v>1029</v>
+        <v>1677</v>
       </c>
       <c r="M111" t="s">
         <v>492</v>
       </c>
       <c r="N111" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="O111" s="1">
         <v>3</v>
@@ -21654,25 +21672,25 @@
         <v>599</v>
       </c>
       <c r="G112" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="I112" t="s">
         <v>826</v>
       </c>
       <c r="J112" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="K112" t="s">
         <v>766</v>
       </c>
       <c r="L112" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M112" t="s">
         <v>492</v>
       </c>
       <c r="N112" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="O112" s="1">
         <v>3</v>
@@ -21692,16 +21710,16 @@
         <v>600</v>
       </c>
       <c r="G113" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="I113" t="s">
         <v>830</v>
       </c>
       <c r="J113" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L113" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M113" t="s">
         <v>492</v>
@@ -21724,13 +21742,13 @@
         <v>602</v>
       </c>
       <c r="F114" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="G114" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="I114" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J114" t="s">
         <v>888</v>
@@ -21753,13 +21771,13 @@
         <v>107</v>
       </c>
       <c r="C115" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="E115" t="s">
         <v>603</v>
       </c>
       <c r="F115" t="s">
-        <v>1438</v>
+        <v>1427</v>
       </c>
       <c r="I115" t="s">
         <v>824</v>
@@ -21768,13 +21786,13 @@
         <v>802</v>
       </c>
       <c r="L115" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="M115" t="s">
         <v>492</v>
       </c>
       <c r="N115" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="O115" s="1">
         <v>3</v>
@@ -21794,22 +21812,22 @@
         <v>604</v>
       </c>
       <c r="F116" t="s">
-        <v>1382</v>
+        <v>1662</v>
       </c>
       <c r="G116" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="I116" t="s">
         <v>826</v>
       </c>
       <c r="J116" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="L116" t="s">
         <v>780</v>
       </c>
       <c r="N116" t="s">
-        <v>1462</v>
+        <v>1447</v>
       </c>
       <c r="O116" s="1">
         <v>2</v>
@@ -21823,22 +21841,22 @@
         <v>109</v>
       </c>
       <c r="C117" t="s">
-        <v>1678</v>
+        <v>1683</v>
       </c>
       <c r="E117" t="s">
         <v>595</v>
       </c>
       <c r="F117" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="I117" t="s">
         <v>826</v>
       </c>
       <c r="J117" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L117" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M117" t="s">
         <v>492</v>
@@ -21861,13 +21879,13 @@
         <v>605</v>
       </c>
       <c r="F118" t="s">
-        <v>1455</v>
+        <v>1652</v>
       </c>
       <c r="I118" t="s">
         <v>826</v>
       </c>
       <c r="J118" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="K118" t="s">
         <v>766</v>
@@ -21876,7 +21894,7 @@
         <v>780</v>
       </c>
       <c r="N118" t="s">
-        <v>1462</v>
+        <v>1447</v>
       </c>
       <c r="O118" s="1">
         <v>2</v>
@@ -21896,22 +21914,22 @@
         <v>606</v>
       </c>
       <c r="F119" t="s">
-        <v>1402</v>
+        <v>1671</v>
       </c>
       <c r="I119" t="s">
         <v>864</v>
       </c>
       <c r="J119" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="L119" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="M119" t="s">
         <v>492</v>
       </c>
       <c r="N119" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="O119" s="1">
         <v>3</v>
@@ -21934,10 +21952,10 @@
         <v>864</v>
       </c>
       <c r="J120" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L120" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="M120" t="s">
         <v>492</v>
@@ -21960,19 +21978,19 @@
         <v>956</v>
       </c>
       <c r="I121" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="J121" t="s">
         <v>802</v>
       </c>
       <c r="K121" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L121" t="s">
         <v>780</v>
       </c>
       <c r="N121" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="O121" s="1">
         <v>1</v>
@@ -21998,7 +22016,7 @@
         <v>943</v>
       </c>
       <c r="N122" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O122" s="1">
         <v>1</v>
@@ -22018,7 +22036,7 @@
         <v>959</v>
       </c>
       <c r="I123" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="J123" t="s">
         <v>960</v>
@@ -22027,7 +22045,7 @@
         <v>965</v>
       </c>
       <c r="N123" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="O123" s="1">
         <v>1</v>
@@ -22044,19 +22062,19 @@
         <v>611</v>
       </c>
       <c r="H124" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="I124" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J124" t="s">
         <v>961</v>
       </c>
       <c r="L124" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="N124" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O124" s="1">
         <v>1</v>
@@ -22070,13 +22088,13 @@
         <v>117</v>
       </c>
       <c r="C125" t="s">
-        <v>1664</v>
+        <v>1639</v>
       </c>
       <c r="E125" t="s">
         <v>612</v>
       </c>
       <c r="F125" t="s">
-        <v>1667</v>
+        <v>1642</v>
       </c>
       <c r="G125" t="s">
         <v>969</v>
@@ -22085,7 +22103,7 @@
         <v>962</v>
       </c>
       <c r="I125" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="J125" t="s">
         <v>841</v>
@@ -22097,7 +22115,7 @@
         <v>775</v>
       </c>
       <c r="N125" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="O125" s="1">
         <v>2</v>
@@ -22114,10 +22132,10 @@
         <v>613</v>
       </c>
       <c r="F126" t="s">
-        <v>1439</v>
+        <v>1428</v>
       </c>
       <c r="G126" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="I126" t="s">
         <v>826</v>
@@ -22149,13 +22167,13 @@
         <v>966</v>
       </c>
       <c r="I127" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="J127" t="s">
         <v>788</v>
       </c>
       <c r="K127" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="L127" t="s">
         <v>967</v>
@@ -22164,7 +22182,7 @@
         <v>492</v>
       </c>
       <c r="N127" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="O127" s="1">
         <v>3</v>
@@ -22178,31 +22196,31 @@
         <v>120</v>
       </c>
       <c r="C128" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="D128" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="E128" t="s">
         <v>615</v>
       </c>
       <c r="F128" t="s">
-        <v>1618</v>
+        <v>1602</v>
       </c>
       <c r="G128" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="H128" t="s">
         <v>968</v>
       </c>
       <c r="I128" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="J128" t="s">
         <v>961</v>
       </c>
       <c r="N128" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="O128" s="1">
         <v>2</v>
@@ -22219,13 +22237,13 @@
         <v>616</v>
       </c>
       <c r="F129" t="s">
-        <v>1440</v>
+        <v>1429</v>
       </c>
       <c r="H129" t="s">
         <v>971</v>
       </c>
       <c r="I129" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="J129" t="s">
         <v>832</v>
@@ -22237,7 +22255,7 @@
         <v>783</v>
       </c>
       <c r="N129" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="O129" s="1">
         <v>2</v>
@@ -22251,16 +22269,16 @@
         <v>122</v>
       </c>
       <c r="C130" t="s">
-        <v>1650</v>
+        <v>1628</v>
       </c>
       <c r="E130" t="s">
         <v>617</v>
       </c>
       <c r="F130" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
       <c r="H130" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="I130" t="s">
         <v>882</v>
@@ -22272,7 +22290,7 @@
         <v>768</v>
       </c>
       <c r="N130" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O130" s="1">
         <v>2</v>
@@ -22292,13 +22310,13 @@
         <v>973</v>
       </c>
       <c r="I131" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J131" t="s">
         <v>762</v>
       </c>
       <c r="N131" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O131" s="1">
         <v>1</v>
@@ -22318,7 +22336,7 @@
         <v>974</v>
       </c>
       <c r="I132" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="J132" t="s">
         <v>975</v>
@@ -22330,7 +22348,7 @@
         <v>937</v>
       </c>
       <c r="N132" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O132" s="1">
         <v>1</v>
@@ -22347,13 +22365,13 @@
         <v>620</v>
       </c>
       <c r="F133" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="H133" t="s">
         <v>976</v>
       </c>
       <c r="I133" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J133" t="s">
         <v>888</v>
@@ -22365,7 +22383,7 @@
         <v>780</v>
       </c>
       <c r="N133" t="s">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="O133" s="1">
         <v>2</v>
@@ -22397,7 +22415,7 @@
         <v>805</v>
       </c>
       <c r="N134" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="O134" s="1">
         <v>1</v>
@@ -22411,13 +22429,13 @@
         <v>127</v>
       </c>
       <c r="C135" t="s">
-        <v>1411</v>
+        <v>1401</v>
       </c>
       <c r="E135" t="s">
         <v>622</v>
       </c>
       <c r="F135" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="H135" t="s">
         <v>979</v>
@@ -22435,7 +22453,7 @@
         <v>980</v>
       </c>
       <c r="N135" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O135" s="1">
         <v>2</v>
@@ -22452,16 +22470,16 @@
         <v>623</v>
       </c>
       <c r="H136" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I136" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J136" t="s">
         <v>797</v>
       </c>
       <c r="N136" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O136" s="1">
         <v>1</v>
@@ -22481,13 +22499,13 @@
         <v>982</v>
       </c>
       <c r="I137" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J137" t="s">
         <v>983</v>
       </c>
       <c r="N137" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O137" s="1">
         <v>2</v>
@@ -22507,7 +22525,7 @@
         <v>939</v>
       </c>
       <c r="I138" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J138" t="s">
         <v>771</v>
@@ -22522,7 +22540,7 @@
         <v>492</v>
       </c>
       <c r="N138" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="O138" s="1">
         <v>3</v>
@@ -22545,10 +22563,10 @@
         <v>986</v>
       </c>
       <c r="H139" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="I139" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="J139" t="s">
         <v>841</v>
@@ -22557,7 +22575,7 @@
         <v>775</v>
       </c>
       <c r="N139" t="s">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="O139" s="1">
         <v>2</v>
@@ -22574,16 +22592,16 @@
         <v>626</v>
       </c>
       <c r="F140" t="s">
-        <v>1624</v>
+        <v>1608</v>
       </c>
       <c r="I140" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J140" t="s">
         <v>984</v>
       </c>
       <c r="N140" t="s">
-        <v>1476</v>
+        <v>1460</v>
       </c>
       <c r="O140" s="1">
         <v>1</v>
@@ -22597,19 +22615,19 @@
         <v>133</v>
       </c>
       <c r="D141" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="E141" t="s">
         <v>627</v>
       </c>
       <c r="G141" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="H141" t="s">
         <v>985</v>
       </c>
       <c r="I141" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J141" t="s">
         <v>981</v>
@@ -22621,7 +22639,7 @@
         <v>775</v>
       </c>
       <c r="N141" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O141" s="1">
         <v>2</v>
@@ -22635,16 +22653,16 @@
         <v>334</v>
       </c>
       <c r="C142" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="E142" t="s">
         <v>628</v>
       </c>
       <c r="H142" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="I142" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="J142" t="s">
         <v>837</v>
@@ -22656,7 +22674,7 @@
         <v>805</v>
       </c>
       <c r="N142" t="s">
-        <v>1474</v>
+        <v>1459</v>
       </c>
       <c r="O142" s="1">
         <v>1</v>
@@ -22669,14 +22687,17 @@
       <c r="B143" t="s">
         <v>134</v>
       </c>
+      <c r="C143" t="s">
+        <v>1681</v>
+      </c>
       <c r="E143" t="s">
         <v>629</v>
       </c>
       <c r="F143" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="I143" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J143" t="s">
         <v>796</v>
@@ -22688,7 +22709,7 @@
         <v>850</v>
       </c>
       <c r="N143" t="s">
-        <v>1466</v>
+        <v>1451</v>
       </c>
       <c r="O143" s="1">
         <v>2</v>
@@ -22702,7 +22723,7 @@
         <v>135</v>
       </c>
       <c r="C144" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="E144" t="s">
         <v>630</v>
@@ -22711,13 +22732,13 @@
         <v>990</v>
       </c>
       <c r="I144" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J144" t="s">
         <v>792</v>
       </c>
       <c r="N144" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O144" s="1">
         <v>2</v>
@@ -22743,10 +22764,10 @@
         <v>785</v>
       </c>
       <c r="L145" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N145" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O145" s="1">
         <v>1</v>
@@ -22760,13 +22781,13 @@
         <v>137</v>
       </c>
       <c r="C146" t="s">
-        <v>1651</v>
+        <v>1629</v>
       </c>
       <c r="E146" t="s">
         <v>632</v>
       </c>
       <c r="H146" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="I146" t="s">
         <v>883</v>
@@ -22781,7 +22802,7 @@
         <v>780</v>
       </c>
       <c r="N146" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="O146" s="1">
         <v>1</v>
@@ -22798,13 +22819,13 @@
         <v>633</v>
       </c>
       <c r="F147" t="s">
-        <v>999</v>
+        <v>1663</v>
       </c>
       <c r="G147" t="s">
-        <v>1417</v>
+        <v>1407</v>
       </c>
       <c r="I147" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J147" t="s">
         <v>991</v>
@@ -22813,7 +22834,7 @@
         <v>492</v>
       </c>
       <c r="N147" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="O147" s="1">
         <v>3</v>
@@ -22830,13 +22851,13 @@
         <v>634</v>
       </c>
       <c r="F148" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="H148" t="s">
         <v>992</v>
       </c>
       <c r="I148" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J148" t="s">
         <v>796</v>
@@ -22848,7 +22869,7 @@
         <v>805</v>
       </c>
       <c r="N148" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="O148" s="1">
         <v>2</v>
@@ -22862,22 +22883,22 @@
         <v>140</v>
       </c>
       <c r="C149" t="s">
-        <v>1413</v>
+        <v>1403</v>
       </c>
       <c r="E149" t="s">
         <v>635</v>
       </c>
       <c r="F149" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="I149" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J149" t="s">
         <v>993</v>
       </c>
       <c r="N149" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O149" s="1">
         <v>2</v>
@@ -22891,31 +22912,31 @@
         <v>141</v>
       </c>
       <c r="C150" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="E150" t="s">
         <v>636</v>
       </c>
       <c r="F150" t="s">
-        <v>1456</v>
+        <v>1441</v>
       </c>
       <c r="G150" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="I150" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J150" t="s">
         <v>888</v>
       </c>
       <c r="L150" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="M150" t="s">
         <v>492</v>
       </c>
       <c r="N150" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="O150" s="1">
         <v>3</v>
@@ -22929,7 +22950,7 @@
         <v>142</v>
       </c>
       <c r="C151" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E151" t="s">
         <v>637</v>
@@ -22938,19 +22959,19 @@
         <v>142</v>
       </c>
       <c r="H151" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="I151" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="J151" t="s">
         <v>943</v>
       </c>
       <c r="L151" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="N151" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O151" s="1">
         <v>1</v>
@@ -22967,10 +22988,10 @@
         <v>639</v>
       </c>
       <c r="F152" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
       <c r="G152" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="H152" t="s">
         <v>994</v>
@@ -22982,10 +23003,10 @@
         <v>754</v>
       </c>
       <c r="L152" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="N152" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O152" s="1">
         <v>2</v>
@@ -23008,7 +23029,7 @@
         <v>995</v>
       </c>
       <c r="I153" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J153" t="s">
         <v>791</v>
@@ -23017,10 +23038,10 @@
         <v>770</v>
       </c>
       <c r="L153" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N153" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O153" s="1">
         <v>2</v>
@@ -23037,10 +23058,10 @@
         <v>642</v>
       </c>
       <c r="H154" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="I154" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="J154" t="s">
         <v>841</v>
@@ -23049,10 +23070,10 @@
         <v>770</v>
       </c>
       <c r="L154" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="N154" t="s">
-        <v>1465</v>
+        <v>1450</v>
       </c>
       <c r="O154" s="1">
         <v>1</v>
@@ -23069,16 +23090,16 @@
         <v>643</v>
       </c>
       <c r="F155" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="I155" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J155" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L155" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="M155" t="s">
         <v>492</v>
@@ -23098,19 +23119,19 @@
         <v>644</v>
       </c>
       <c r="H156" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I156" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J156" t="s">
         <v>996</v>
       </c>
       <c r="L156" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="N156" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="O156" s="1">
         <v>2</v>
@@ -23124,22 +23145,22 @@
         <v>786</v>
       </c>
       <c r="C157" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="E157" t="s">
         <v>521</v>
       </c>
       <c r="F157" t="s">
-        <v>1422</v>
+        <v>1412</v>
       </c>
       <c r="G157" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="H157" t="s">
         <v>819</v>
       </c>
       <c r="I157" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="J157" t="s">
         <v>797</v>
@@ -23151,7 +23172,7 @@
         <v>780</v>
       </c>
       <c r="N157" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="O157" s="1">
         <v>2</v>
@@ -23165,25 +23186,25 @@
         <v>148</v>
       </c>
       <c r="C158" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="E158" t="s">
         <v>645</v>
       </c>
       <c r="F158" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="G158" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="H158" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="I158" t="s">
         <v>882</v>
       </c>
       <c r="J158" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="K158" t="s">
         <v>770</v>
@@ -23192,7 +23213,7 @@
         <v>775</v>
       </c>
       <c r="N158" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="O158" s="1">
         <v>2</v>
@@ -23206,13 +23227,13 @@
         <v>149</v>
       </c>
       <c r="C159" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="E159" t="s">
         <v>646</v>
       </c>
       <c r="F159" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="I159" t="s">
         <v>826</v>
@@ -23227,7 +23248,7 @@
         <v>780</v>
       </c>
       <c r="N159" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="O159" s="1">
         <v>2</v>
@@ -23244,13 +23265,13 @@
         <v>647</v>
       </c>
       <c r="F160" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="H160" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="I160" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J160" t="s">
         <v>791</v>
@@ -23262,7 +23283,7 @@
         <v>775</v>
       </c>
       <c r="N160" t="s">
-        <v>1467</v>
+        <v>1452</v>
       </c>
       <c r="O160" s="1">
         <v>2</v>
@@ -23275,26 +23296,29 @@
       <c r="B161" t="s">
         <v>151</v>
       </c>
+      <c r="C161" t="s">
+        <v>1664</v>
+      </c>
       <c r="E161" t="s">
         <v>648</v>
       </c>
       <c r="F161" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="H161" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I161" t="s">
         <v>1014</v>
-      </c>
-      <c r="I161" t="s">
-        <v>1015</v>
       </c>
       <c r="J161" t="s">
         <v>778</v>
       </c>
       <c r="L161" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="N161" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O161" s="1">
         <v>2</v>
@@ -23311,19 +23335,19 @@
         <v>649</v>
       </c>
       <c r="F162" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
       <c r="G162" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="H162" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="I162" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J162" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="K162" t="s">
         <v>844</v>
@@ -23332,7 +23356,7 @@
         <v>783</v>
       </c>
       <c r="N162" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="O162" s="1">
         <v>1</v>
@@ -23349,22 +23373,22 @@
         <v>650</v>
       </c>
       <c r="F163" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="G163" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="H163" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I163" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J163" t="s">
         <v>758</v>
       </c>
       <c r="N163" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O163" s="1">
         <v>1</v>
@@ -23378,16 +23402,16 @@
         <v>154</v>
       </c>
       <c r="C164" t="s">
-        <v>1652</v>
+        <v>1630</v>
       </c>
       <c r="D164" t="s">
-        <v>1448</v>
+        <v>1436</v>
       </c>
       <c r="E164" t="s">
         <v>651</v>
       </c>
       <c r="F164" t="s">
-        <v>1409</v>
+        <v>1665</v>
       </c>
       <c r="I164" t="s">
         <v>826</v>
@@ -23399,13 +23423,13 @@
         <v>770</v>
       </c>
       <c r="L164" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M164" t="s">
         <v>492</v>
       </c>
       <c r="N164" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="O164" s="1">
         <v>3</v>
@@ -23422,10 +23446,10 @@
         <v>652</v>
       </c>
       <c r="H165" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="I165" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J165" t="s">
         <v>777</v>
@@ -23445,22 +23469,22 @@
         <v>156</v>
       </c>
       <c r="C166" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="E166" t="s">
         <v>653</v>
       </c>
       <c r="F166" t="s">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="I166" t="s">
         <v>826</v>
       </c>
       <c r="J166" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K166" t="s">
         <v>1025</v>
-      </c>
-      <c r="K166" t="s">
-        <v>1026</v>
       </c>
       <c r="L166" t="s">
         <v>783</v>
@@ -23469,7 +23493,7 @@
         <v>492</v>
       </c>
       <c r="N166" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="O166" s="1">
         <v>3</v>
@@ -23489,16 +23513,16 @@
         <v>826</v>
       </c>
       <c r="J167" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="K167" t="s">
         <v>762</v>
       </c>
       <c r="L167" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="N167" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="O167" s="1">
         <v>1</v>
@@ -23512,25 +23536,25 @@
         <v>158</v>
       </c>
       <c r="C168" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="E168" t="s">
         <v>656</v>
       </c>
       <c r="H168" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="I168" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J168" t="s">
         <v>984</v>
       </c>
       <c r="L168" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N168" t="s">
-        <v>1476</v>
+        <v>1460</v>
       </c>
       <c r="O168" s="1">
         <v>2</v>
@@ -23541,25 +23565,25 @@
         <v>469</v>
       </c>
       <c r="B169" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C169" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E169" t="s">
         <v>655</v>
       </c>
       <c r="H169" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="I169" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J169" t="s">
         <v>777</v>
       </c>
       <c r="N169" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O169" s="1">
         <v>1</v>
@@ -23576,16 +23600,16 @@
         <v>657</v>
       </c>
       <c r="F170" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="H170" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="I170" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J170" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="K170" t="s">
         <v>766</v>
@@ -23594,7 +23618,7 @@
         <v>805</v>
       </c>
       <c r="N170" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="O170" s="1">
         <v>1</v>
@@ -23611,10 +23635,10 @@
         <v>658</v>
       </c>
       <c r="F171" t="s">
-        <v>1623</v>
+        <v>1607</v>
       </c>
       <c r="G171" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="I171" t="s">
         <v>826</v>
@@ -23629,7 +23653,7 @@
         <v>783</v>
       </c>
       <c r="N171" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="O171" s="1">
         <v>2</v>
@@ -23646,13 +23670,13 @@
         <v>659</v>
       </c>
       <c r="F172" t="s">
-        <v>1627</v>
+        <v>1611</v>
       </c>
       <c r="H172" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="I172" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="J172" t="s">
         <v>871</v>
@@ -23661,7 +23685,7 @@
         <v>492</v>
       </c>
       <c r="N172" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="O172" s="1">
         <v>3</v>
@@ -23678,13 +23702,13 @@
         <v>162</v>
       </c>
       <c r="F173" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H173" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="I173" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="J173" t="s">
         <v>888</v>
@@ -23696,7 +23720,7 @@
         <v>780</v>
       </c>
       <c r="N173" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="O173" s="1">
         <v>1</v>
@@ -23710,16 +23734,16 @@
         <v>163</v>
       </c>
       <c r="C174" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E174" t="s">
         <v>660</v>
       </c>
       <c r="F174" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="H174" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="I174" t="s">
         <v>826</v>
@@ -23728,13 +23752,13 @@
         <v>751</v>
       </c>
       <c r="K174" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="L174" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="N174" t="s">
-        <v>1462</v>
+        <v>1447</v>
       </c>
       <c r="O174" s="1">
         <v>2</v>
@@ -23751,10 +23775,10 @@
         <v>661</v>
       </c>
       <c r="F175" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="H175" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="I175" t="s">
         <v>830</v>
@@ -23763,10 +23787,10 @@
         <v>777</v>
       </c>
       <c r="L175" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="N175" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O175" s="1">
         <v>2</v>
@@ -23783,16 +23807,16 @@
         <v>662</v>
       </c>
       <c r="H176" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="I176" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J176" t="s">
         <v>762</v>
       </c>
       <c r="N176" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O176" s="1">
         <v>1</v>
@@ -23806,13 +23830,13 @@
         <v>166</v>
       </c>
       <c r="C177" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="E177" t="s">
         <v>663</v>
       </c>
       <c r="F177" t="s">
-        <v>1676</v>
+        <v>1650</v>
       </c>
       <c r="I177" t="s">
         <v>826</v>
@@ -23821,13 +23845,13 @@
         <v>762</v>
       </c>
       <c r="L177" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="M177" t="s">
         <v>492</v>
       </c>
       <c r="N177" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O177" s="1">
         <v>3</v>
@@ -23841,13 +23865,13 @@
         <v>167</v>
       </c>
       <c r="C178" t="s">
-        <v>1619</v>
+        <v>1603</v>
       </c>
       <c r="E178" t="s">
         <v>664</v>
       </c>
       <c r="H178" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="I178" t="s">
         <v>827</v>
@@ -23856,7 +23880,7 @@
         <v>785</v>
       </c>
       <c r="N178" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O178" s="1">
         <v>1</v>
@@ -23888,7 +23912,7 @@
         <v>492</v>
       </c>
       <c r="N179" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="O179" s="1">
         <v>3</v>
@@ -23908,7 +23932,7 @@
         <v>906</v>
       </c>
       <c r="I180" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="J180" t="s">
         <v>787</v>
@@ -23917,7 +23941,7 @@
         <v>770</v>
       </c>
       <c r="L180" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="O180" s="1">
         <v>1</v>
@@ -23931,13 +23955,13 @@
         <v>170</v>
       </c>
       <c r="C181" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="E181" t="s">
         <v>667</v>
       </c>
       <c r="H181" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="I181" t="s">
         <v>829</v>
@@ -23946,7 +23970,7 @@
         <v>762</v>
       </c>
       <c r="N181" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O181" s="1">
         <v>2</v>
@@ -23966,13 +23990,13 @@
         <v>815</v>
       </c>
       <c r="I182" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J182" t="s">
         <v>785</v>
       </c>
       <c r="N182" t="s">
-        <v>1468</v>
+        <v>1453</v>
       </c>
       <c r="O182" s="1">
         <v>1</v>
@@ -23986,7 +24010,7 @@
         <v>172</v>
       </c>
       <c r="C183" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E183" t="s">
         <v>587</v>
@@ -23995,7 +24019,7 @@
         <v>946</v>
       </c>
       <c r="I183" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J183" t="s">
         <v>837</v>
@@ -24015,22 +24039,22 @@
         <v>173</v>
       </c>
       <c r="C184" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E184" t="s">
         <v>670</v>
       </c>
       <c r="F184" t="s">
-        <v>1451</v>
+        <v>1438</v>
       </c>
       <c r="H184" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="I184" t="s">
         <v>828</v>
       </c>
       <c r="J184" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="K184" t="s">
         <v>770</v>
@@ -24039,7 +24063,7 @@
         <v>780</v>
       </c>
       <c r="N184" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="O184" s="1">
         <v>2</v>
@@ -24050,16 +24074,16 @@
         <v>272</v>
       </c>
       <c r="B185" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C185" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E185" t="s">
         <v>671</v>
       </c>
       <c r="H185" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="I185" t="s">
         <v>828</v>
@@ -24074,7 +24098,7 @@
         <v>780</v>
       </c>
       <c r="N185" t="s">
-        <v>1463</v>
+        <v>1448</v>
       </c>
       <c r="O185" s="1">
         <v>1</v>
@@ -24085,10 +24109,10 @@
         <v>381</v>
       </c>
       <c r="B186" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C186" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="E186" t="s">
         <v>686</v>
@@ -24106,10 +24130,10 @@
         <v>891</v>
       </c>
       <c r="L186" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="N186" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O186" s="1">
         <v>2</v>
@@ -24123,13 +24147,13 @@
         <v>174</v>
       </c>
       <c r="C187" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E187" t="s">
         <v>672</v>
       </c>
       <c r="H187" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="I187" t="s">
         <v>864</v>
@@ -24138,7 +24162,7 @@
         <v>760</v>
       </c>
       <c r="L187" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="O187" s="1">
         <v>1</v>
@@ -24152,28 +24176,28 @@
         <v>175</v>
       </c>
       <c r="C188" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E188" t="s">
         <v>673</v>
       </c>
       <c r="F188" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G188" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="I188" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J188" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="M188" t="s">
         <v>492</v>
       </c>
       <c r="N188" t="s">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="O188" s="1">
         <v>3</v>
@@ -24190,16 +24214,16 @@
         <v>674</v>
       </c>
       <c r="H189" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="I189" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="J189" t="s">
         <v>754</v>
       </c>
       <c r="N189" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O189" s="1">
         <v>1</v>
@@ -24216,16 +24240,16 @@
         <v>675</v>
       </c>
       <c r="F190" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="H190" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="I190" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J190" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="K190" t="s">
         <v>770</v>
@@ -24234,7 +24258,7 @@
         <v>775</v>
       </c>
       <c r="N190" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O190" s="1">
         <v>2</v>
@@ -24251,16 +24275,16 @@
         <v>676</v>
       </c>
       <c r="H191" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="I191" t="s">
         <v>827</v>
       </c>
       <c r="J191" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="N191" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O191" s="1">
         <v>1</v>
@@ -24277,10 +24301,10 @@
         <v>677</v>
       </c>
       <c r="F192" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="I192" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J192" t="s">
         <v>777</v>
@@ -24295,7 +24319,7 @@
         <v>492</v>
       </c>
       <c r="N192" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="O192" s="1">
         <v>3</v>
@@ -24309,19 +24333,19 @@
         <v>179</v>
       </c>
       <c r="C193" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="E193" t="s">
         <v>678</v>
       </c>
       <c r="F193" t="s">
-        <v>1452</v>
+        <v>1682</v>
       </c>
       <c r="G193" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="H193" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="I193" t="s">
         <v>884</v>
@@ -24339,7 +24363,7 @@
         <v>492</v>
       </c>
       <c r="N193" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="O193" s="1">
         <v>3</v>
@@ -24353,22 +24377,22 @@
         <v>180</v>
       </c>
       <c r="C194" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
       <c r="D194" t="s">
-        <v>1478</v>
+        <v>1462</v>
       </c>
       <c r="E194" t="s">
         <v>679</v>
       </c>
       <c r="F194" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="I194" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J194" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="K194" t="s">
         <v>766</v>
@@ -24377,7 +24401,7 @@
         <v>780</v>
       </c>
       <c r="N194" t="s">
-        <v>1462</v>
+        <v>1447</v>
       </c>
       <c r="O194" s="1">
         <v>2</v>
@@ -24391,22 +24415,22 @@
         <v>737</v>
       </c>
       <c r="C195" t="s">
-        <v>1653</v>
+        <v>1631</v>
       </c>
       <c r="E195" t="s">
         <v>687</v>
       </c>
       <c r="I195" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J195" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="K195" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="N195" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="O195" s="1">
         <v>2</v>
@@ -24420,25 +24444,25 @@
         <v>181</v>
       </c>
       <c r="C196" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E196" t="s">
         <v>680</v>
       </c>
       <c r="F196" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="I196" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J196" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="K196" t="s">
         <v>771</v>
       </c>
       <c r="N196" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O196" s="1">
         <v>2</v>
@@ -24458,19 +24482,19 @@
         <v>681</v>
       </c>
       <c r="I197" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J197" t="s">
         <v>766</v>
       </c>
       <c r="L197" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="M197" t="s">
         <v>492</v>
       </c>
       <c r="N197" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="O197" s="1">
         <v>3</v>
@@ -24484,37 +24508,37 @@
         <v>481</v>
       </c>
       <c r="C198" t="s">
-        <v>1668</v>
+        <v>1643</v>
       </c>
       <c r="D198" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="E198" t="s">
         <v>682</v>
       </c>
       <c r="F198" t="s">
-        <v>1297</v>
+        <v>1653</v>
       </c>
       <c r="G198" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="H198" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="I198" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J198" t="s">
         <v>888</v>
       </c>
       <c r="L198" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="M198" t="s">
         <v>492</v>
       </c>
       <c r="N198" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="O198" s="1">
         <v>3</v>
@@ -24528,25 +24552,25 @@
         <v>183</v>
       </c>
       <c r="C199" t="s">
-        <v>1644</v>
+        <v>1624</v>
       </c>
       <c r="E199" t="s">
         <v>683</v>
       </c>
       <c r="F199" t="s">
-        <v>1645</v>
+        <v>1672</v>
       </c>
       <c r="I199" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J199" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="K199" t="s">
         <v>770</v>
       </c>
       <c r="L199" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="M199" t="s">
         <v>492</v>
@@ -24566,7 +24590,7 @@
         <v>684</v>
       </c>
       <c r="F200" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="I200" t="s">
         <v>826</v>
@@ -24578,10 +24602,10 @@
         <v>766</v>
       </c>
       <c r="L200" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="N200" t="s">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="O200" s="1">
         <v>2</v>
@@ -24604,7 +24628,7 @@
         <v>760</v>
       </c>
       <c r="L201" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="M201" t="s">
         <v>492</v>
@@ -24624,16 +24648,16 @@
         <v>736</v>
       </c>
       <c r="F202" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="I202" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="J202" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L202" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="M202" t="s">
         <v>492</v>
@@ -24650,16 +24674,16 @@
         <v>187</v>
       </c>
       <c r="C203" t="s">
-        <v>1656</v>
+        <v>1632</v>
       </c>
       <c r="E203" t="s">
         <v>688</v>
       </c>
       <c r="F203" t="s">
-        <v>1657</v>
+        <v>1633</v>
       </c>
       <c r="I203" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="J203" t="s">
         <v>792</v>
@@ -24671,7 +24695,7 @@
         <v>780</v>
       </c>
       <c r="N203" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="O203" s="1">
         <v>2</v>
@@ -24691,7 +24715,7 @@
         <v>897</v>
       </c>
       <c r="I204" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J204" t="s">
         <v>891</v>
@@ -24700,7 +24724,7 @@
         <v>492</v>
       </c>
       <c r="N204" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="O204" s="1">
         <v>3</v>
@@ -24717,10 +24741,10 @@
         <v>690</v>
       </c>
       <c r="H205" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="I205" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J205" t="s">
         <v>792</v>
@@ -24732,7 +24756,7 @@
         <v>780</v>
       </c>
       <c r="N205" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="O205" s="1">
         <v>1</v>
@@ -24749,22 +24773,22 @@
         <v>691</v>
       </c>
       <c r="F206" t="s">
-        <v>1660</v>
+        <v>1635</v>
       </c>
       <c r="H206" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I206" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="J206" t="s">
         <v>832</v>
       </c>
       <c r="L206" t="s">
+        <v>1152</v>
+      </c>
+      <c r="N206" t="s">
         <v>1155</v>
-      </c>
-      <c r="N206" t="s">
-        <v>1158</v>
       </c>
       <c r="O206" s="1">
         <v>1</v>
@@ -24778,19 +24802,19 @@
         <v>191</v>
       </c>
       <c r="C207" t="s">
-        <v>1412</v>
+        <v>1402</v>
       </c>
       <c r="E207" t="s">
         <v>584</v>
       </c>
       <c r="I207" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J207" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="N207" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="O207" s="1">
         <v>2</v>
@@ -24807,16 +24831,16 @@
         <v>692</v>
       </c>
       <c r="H208" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I208" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="J208" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="N208" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O208" s="1">
         <v>2</v>
@@ -24833,10 +24857,10 @@
         <v>193</v>
       </c>
       <c r="H209" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="I209" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="J209" t="s">
         <v>762</v>
@@ -24845,7 +24869,7 @@
         <v>805</v>
       </c>
       <c r="N209" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="O209" s="1">
         <v>1</v>
@@ -24859,13 +24883,13 @@
         <v>483</v>
       </c>
       <c r="C210" t="s">
-        <v>1655</v>
+        <v>1666</v>
       </c>
       <c r="E210" t="s">
         <v>511</v>
       </c>
       <c r="F210" t="s">
-        <v>1639</v>
+        <v>1658</v>
       </c>
       <c r="I210" t="s">
         <v>864</v>
@@ -24883,7 +24907,7 @@
         <v>492</v>
       </c>
       <c r="N210" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="O210" s="1">
         <v>3</v>
@@ -24897,16 +24921,16 @@
         <v>194</v>
       </c>
       <c r="C211" t="s">
-        <v>1674</v>
+        <v>1649</v>
       </c>
       <c r="E211" t="s">
         <v>693</v>
       </c>
       <c r="F211" t="s">
-        <v>1616</v>
+        <v>1600</v>
       </c>
       <c r="H211" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="I211" t="s">
         <v>864</v>
@@ -24915,13 +24939,13 @@
         <v>888</v>
       </c>
       <c r="L211" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="M211" t="s">
         <v>492</v>
       </c>
       <c r="N211" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="O211" s="1">
         <v>3</v>
@@ -24938,13 +24962,13 @@
         <v>694</v>
       </c>
       <c r="H212" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="I212" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="J212" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="K212" t="s">
         <v>769</v>
@@ -24953,7 +24977,7 @@
         <v>780</v>
       </c>
       <c r="N212" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="O212" s="1">
         <v>1</v>
@@ -24970,19 +24994,19 @@
         <v>695</v>
       </c>
       <c r="H213" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="I213" t="s">
         <v>827</v>
       </c>
       <c r="J213" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="L213" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N213" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O213" s="1">
         <v>1</v>
@@ -24999,22 +25023,22 @@
         <v>696</v>
       </c>
       <c r="F214" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="H214" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="I214" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="J214" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="L214" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N214" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O214" s="1">
         <v>1</v>
@@ -25028,16 +25052,16 @@
         <v>198</v>
       </c>
       <c r="C215" t="s">
-        <v>1449</v>
+        <v>1437</v>
       </c>
       <c r="E215" t="s">
         <v>697</v>
       </c>
       <c r="H215" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="I215" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="J215" t="s">
         <v>778</v>
@@ -25049,7 +25073,7 @@
         <v>780</v>
       </c>
       <c r="N215" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="O215" s="1">
         <v>1</v>
@@ -25066,19 +25090,19 @@
         <v>698</v>
       </c>
       <c r="H216" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="I216" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="J216" t="s">
         <v>841</v>
       </c>
       <c r="L216" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="N216" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O216" s="1">
         <v>1</v>
@@ -25095,25 +25119,25 @@
         <v>699</v>
       </c>
       <c r="F217" t="s">
-        <v>1646</v>
+        <v>1625</v>
       </c>
       <c r="G217" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="I217" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J217" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="K217" t="s">
         <v>770</v>
       </c>
       <c r="L217" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N217" t="s">
-        <v>1465</v>
+        <v>1450</v>
       </c>
       <c r="O217" s="1">
         <v>2</v>
@@ -25127,13 +25151,13 @@
         <v>738</v>
       </c>
       <c r="C218" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="E218" t="s">
         <v>638</v>
       </c>
       <c r="F218" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="I218" t="s">
         <v>826</v>
@@ -25148,7 +25172,7 @@
         <v>780</v>
       </c>
       <c r="N218" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="O218" s="1">
         <v>2</v>
@@ -25162,19 +25186,19 @@
         <v>201</v>
       </c>
       <c r="C219" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="E219" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F219" t="s">
         <v>700</v>
       </c>
       <c r="H219" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="I219" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J219" t="s">
         <v>837</v>
@@ -25186,7 +25210,7 @@
         <v>780</v>
       </c>
       <c r="N219" t="s">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="O219" s="1">
         <v>1</v>
@@ -25203,19 +25227,19 @@
         <v>701</v>
       </c>
       <c r="F220" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="H220" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I220" t="s">
         <v>882</v>
       </c>
       <c r="J220" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="N220" t="s">
-        <v>1469</v>
+        <v>1454</v>
       </c>
       <c r="O220" s="1">
         <v>1</v>
@@ -25232,25 +25256,25 @@
         <v>702</v>
       </c>
       <c r="F221" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="G221" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="H221" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I221" t="s">
         <v>978</v>
       </c>
       <c r="J221" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="K221" t="s">
         <v>771</v>
       </c>
       <c r="N221" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="O221" s="1">
         <v>1</v>
@@ -25264,22 +25288,22 @@
         <v>204</v>
       </c>
       <c r="C222" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="E222" t="s">
         <v>703</v>
       </c>
       <c r="F222" t="s">
-        <v>1453</v>
+        <v>1439</v>
       </c>
       <c r="H222" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="I222" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J222" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="K222" t="s">
         <v>770</v>
@@ -25288,7 +25312,7 @@
         <v>780</v>
       </c>
       <c r="N222" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="O222" s="1">
         <v>2</v>
@@ -25305,10 +25329,10 @@
         <v>704</v>
       </c>
       <c r="H223" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I223" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="J223" t="s">
         <v>943</v>
@@ -25320,7 +25344,7 @@
         <v>780</v>
       </c>
       <c r="N223" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="O223" s="1">
         <v>2</v>
@@ -25337,10 +25361,10 @@
         <v>705</v>
       </c>
       <c r="H224" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="I224" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="J224" t="s">
         <v>788</v>
@@ -25363,7 +25387,7 @@
         <v>706</v>
       </c>
       <c r="H225" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="I225" t="s">
         <v>827</v>
@@ -25375,10 +25399,10 @@
         <v>766</v>
       </c>
       <c r="L225" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N225" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="O225" s="1">
         <v>1</v>
@@ -25395,16 +25419,16 @@
         <v>708</v>
       </c>
       <c r="F226" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="G226" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="H226" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="I226" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="J226" t="s">
         <v>975</v>
@@ -25413,10 +25437,10 @@
         <v>770</v>
       </c>
       <c r="L226" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="N226" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="O226" s="1">
         <v>2</v>
@@ -25433,10 +25457,10 @@
         <v>709</v>
       </c>
       <c r="F227" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="I227" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="J227" t="s">
         <v>909</v>
@@ -25451,7 +25475,7 @@
         <v>492</v>
       </c>
       <c r="N227" t="s">
-        <v>1473</v>
+        <v>1458</v>
       </c>
       <c r="O227" s="1">
         <v>3</v>
@@ -25468,16 +25492,16 @@
         <v>710</v>
       </c>
       <c r="H228" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I228" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J228" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="N228" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="O228" s="1">
         <v>1</v>
@@ -25491,16 +25515,16 @@
         <v>485</v>
       </c>
       <c r="C229" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E229" t="s">
         <v>711</v>
       </c>
       <c r="F229" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="G229" t="s">
-        <v>1418</v>
+        <v>1408</v>
       </c>
       <c r="J229" t="s">
         <v>802</v>
@@ -25509,7 +25533,7 @@
         <v>766</v>
       </c>
       <c r="L229" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="M229" t="s">
         <v>492</v>
@@ -25526,19 +25550,19 @@
         <v>211</v>
       </c>
       <c r="C230" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="E230" t="s">
         <v>712</v>
       </c>
       <c r="I230" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J230" t="s">
         <v>802</v>
       </c>
       <c r="L230" t="s">
-        <v>1630</v>
+        <v>1680</v>
       </c>
       <c r="M230" t="s">
         <v>492</v>
@@ -25558,16 +25582,16 @@
         <v>713</v>
       </c>
       <c r="H231" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="I231" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="J231" t="s">
         <v>777</v>
       </c>
       <c r="N231" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O231" s="1">
         <v>1</v>
@@ -25584,10 +25608,10 @@
         <v>714</v>
       </c>
       <c r="H232" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="I232" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="J232" t="s">
         <v>790</v>
@@ -25599,7 +25623,7 @@
         <v>780</v>
       </c>
       <c r="N232" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="O232" s="1">
         <v>2</v>
@@ -25613,22 +25637,22 @@
         <v>214</v>
       </c>
       <c r="C233" t="s">
-        <v>1669</v>
+        <v>1644</v>
       </c>
       <c r="E233" t="s">
         <v>715</v>
       </c>
       <c r="F233" t="s">
-        <v>1621</v>
+        <v>1605</v>
       </c>
       <c r="H233" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I233" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J233" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="K233" t="s">
         <v>766</v>
@@ -25637,7 +25661,7 @@
         <v>780</v>
       </c>
       <c r="N233" t="s">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="O233" s="1">
         <v>2</v>
@@ -25651,13 +25675,13 @@
         <v>215</v>
       </c>
       <c r="C234" t="s">
-        <v>1659</v>
+        <v>1634</v>
       </c>
       <c r="E234" t="s">
         <v>716</v>
       </c>
       <c r="F234" t="s">
-        <v>1647</v>
+        <v>1656</v>
       </c>
       <c r="I234" t="s">
         <v>826</v>
@@ -25669,13 +25693,13 @@
         <v>766</v>
       </c>
       <c r="L234" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M234" t="s">
         <v>492</v>
       </c>
       <c r="N234" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="O234" s="1">
         <v>3</v>
@@ -25692,7 +25716,7 @@
         <v>717</v>
       </c>
       <c r="F235" t="s">
-        <v>1410</v>
+        <v>1673</v>
       </c>
       <c r="I235" t="s">
         <v>826</v>
@@ -25704,10 +25728,10 @@
         <v>769</v>
       </c>
       <c r="L235" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N235" t="s">
-        <v>1473</v>
+        <v>1458</v>
       </c>
       <c r="O235" s="1">
         <v>2</v>
@@ -25721,13 +25745,13 @@
         <v>217</v>
       </c>
       <c r="C236" t="s">
-        <v>1663</v>
+        <v>1638</v>
       </c>
       <c r="E236" t="s">
         <v>718</v>
       </c>
       <c r="F236" t="s">
-        <v>1637</v>
+        <v>1618</v>
       </c>
       <c r="I236" t="s">
         <v>864</v>
@@ -25736,7 +25760,7 @@
         <v>870</v>
       </c>
       <c r="N236" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="O236" s="1">
         <v>2</v>
@@ -25750,34 +25774,34 @@
         <v>744</v>
       </c>
       <c r="C237" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D237" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="E237" t="s">
         <v>745</v>
       </c>
       <c r="F237" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G237" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="I237" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="J237" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L237" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="M237" t="s">
         <v>492</v>
       </c>
       <c r="N237" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O237" s="1">
         <v>3</v>
@@ -25794,7 +25818,7 @@
         <v>719</v>
       </c>
       <c r="H238" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="I238" t="s">
         <v>883</v>
@@ -25806,10 +25830,10 @@
         <v>762</v>
       </c>
       <c r="L238" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="N238" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="O238" s="1">
         <v>1</v>
@@ -25826,10 +25850,10 @@
         <v>720</v>
       </c>
       <c r="H239" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="I239" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="J239" t="s">
         <v>762</v>
@@ -25841,7 +25865,7 @@
         <v>805</v>
       </c>
       <c r="N239" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="O239" s="1">
         <v>1</v>
@@ -25858,16 +25882,16 @@
         <v>721</v>
       </c>
       <c r="F240" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="G240" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
       <c r="H240" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="I240" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="J240" t="s">
         <v>787</v>
@@ -25879,7 +25903,7 @@
         <v>805</v>
       </c>
       <c r="N240" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="O240" s="1">
         <v>2</v>
@@ -25893,22 +25917,22 @@
         <v>221</v>
       </c>
       <c r="C241" t="s">
-        <v>1625</v>
+        <v>1609</v>
       </c>
       <c r="E241" t="s">
         <v>722</v>
       </c>
       <c r="F241" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="I241" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J241" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L241" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M241" t="s">
         <v>492</v>
@@ -25928,7 +25952,7 @@
         <v>723</v>
       </c>
       <c r="F242" t="s">
-        <v>1665</v>
+        <v>1640</v>
       </c>
       <c r="I242" t="s">
         <v>826</v>
@@ -25940,10 +25964,10 @@
         <v>770</v>
       </c>
       <c r="L242" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="N242" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="O242" s="1">
         <v>2</v>
@@ -25960,7 +25984,7 @@
         <v>724</v>
       </c>
       <c r="H243" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I243" t="s">
         <v>827</v>
@@ -25969,7 +25993,7 @@
         <v>788</v>
       </c>
       <c r="N243" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O243" s="1">
         <v>1</v>
@@ -25986,10 +26010,10 @@
         <v>725</v>
       </c>
       <c r="H244" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="I244" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J244" t="s">
         <v>790</v>
@@ -26001,7 +26025,7 @@
         <v>935</v>
       </c>
       <c r="N244" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O244" s="1">
         <v>2</v>
@@ -26018,7 +26042,7 @@
         <v>726</v>
       </c>
       <c r="H245" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I245" t="s">
         <v>827</v>
@@ -26027,7 +26051,7 @@
         <v>975</v>
       </c>
       <c r="N245" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O245" s="1">
         <v>1</v>
@@ -26044,7 +26068,7 @@
         <v>727</v>
       </c>
       <c r="H246" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="I246" t="s">
         <v>830</v>
@@ -26059,7 +26083,7 @@
         <v>775</v>
       </c>
       <c r="N246" t="s">
-        <v>1473</v>
+        <v>1458</v>
       </c>
       <c r="O246" s="1">
         <v>1</v>
@@ -26076,19 +26100,19 @@
         <v>728</v>
       </c>
       <c r="F247" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="G247" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
       <c r="H247" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="I247" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="J247" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="K247" t="s">
         <v>766</v>
@@ -26097,7 +26121,7 @@
         <v>805</v>
       </c>
       <c r="N247" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="O247" s="1">
         <v>2</v>
@@ -26114,22 +26138,22 @@
         <v>729</v>
       </c>
       <c r="F248" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="I248" t="s">
         <v>826</v>
       </c>
       <c r="J248" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="K248" t="s">
         <v>770</v>
       </c>
       <c r="L248" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="N248" t="s">
-        <v>1469</v>
+        <v>1454</v>
       </c>
       <c r="O248" s="1">
         <v>2</v>
@@ -26146,10 +26170,10 @@
         <v>730</v>
       </c>
       <c r="H249" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="I249" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J249" t="s">
         <v>848</v>
@@ -26161,7 +26185,7 @@
         <v>780</v>
       </c>
       <c r="N249" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="O249" s="1">
         <v>1</v>
@@ -26178,16 +26202,16 @@
         <v>731</v>
       </c>
       <c r="F250" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="G250" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="H250" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I250" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="J250" t="s">
         <v>841</v>
@@ -26199,7 +26223,7 @@
         <v>780</v>
       </c>
       <c r="N250" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="O250" s="1">
         <v>1</v>
@@ -26213,13 +26237,13 @@
         <v>231</v>
       </c>
       <c r="C251" t="s">
-        <v>1424</v>
+        <v>1668</v>
       </c>
       <c r="E251" t="s">
         <v>732</v>
       </c>
       <c r="F251" t="s">
-        <v>1423</v>
+        <v>1413</v>
       </c>
       <c r="I251" t="s">
         <v>826</v>
@@ -26231,7 +26255,7 @@
         <v>766</v>
       </c>
       <c r="L251" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="M251" t="s">
         <v>492</v>
@@ -26251,22 +26275,22 @@
         <v>733</v>
       </c>
       <c r="F252" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G252" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="H252" t="s">
         <v>875</v>
       </c>
       <c r="I252" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J252" t="s">
         <v>870</v>
       </c>
       <c r="N252" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="O252" s="1">
         <v>2</v>
@@ -26283,19 +26307,19 @@
         <v>734</v>
       </c>
       <c r="H253" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="I253" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J253" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="K253" t="s">
         <v>844</v>
       </c>
       <c r="L253" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="O253" s="1">
         <v>2</v>
@@ -26312,16 +26336,16 @@
         <v>735</v>
       </c>
       <c r="F254" t="s">
-        <v>1454</v>
+        <v>1440</v>
       </c>
       <c r="H254" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="I254" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="J254" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="K254" t="s">
         <v>841</v>
@@ -26330,7 +26354,7 @@
         <v>780</v>
       </c>
       <c r="N254" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="O254" s="1">
         <v>1</v>
@@ -26367,40 +26391,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1432</v>
+        <v>1421</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1433</v>
+        <v>1422</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1435</v>
+        <v>1424</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1436</v>
+        <v>1425</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1431</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1428</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1430</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -28086,7 +28110,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C41" s="1">
         <v>34</v>
@@ -33590,7 +33614,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C169" s="1">
         <v>47</v>
@@ -34278,7 +34302,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C185" s="1">
         <v>51</v>
@@ -34321,7 +34345,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C186" s="1">
         <v>59</v>
@@ -37383,40 +37407,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1432</v>
+        <v>1421</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1433</v>
+        <v>1422</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1435</v>
+        <v>1424</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1436</v>
+        <v>1425</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1431</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1428</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1430</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -37643,7 +37667,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -37858,7 +37882,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -37901,7 +37925,7 @@
         <v>743</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -38159,7 +38183,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -38417,7 +38441,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -38589,7 +38613,7 @@
         <v>482</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -39102,7 +39126,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C41" s="1">
         <v>43</v>
@@ -39750,7 +39774,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -40438,7 +40462,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -40567,7 +40591,7 @@
         <v>71</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -40782,7 +40806,7 @@
         <v>76</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
@@ -40997,7 +41021,7 @@
         <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -41040,7 +41064,7 @@
         <v>82</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -41083,7 +41107,7 @@
         <v>83</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -41169,7 +41193,7 @@
         <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -41384,7 +41408,7 @@
         <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -41513,7 +41537,7 @@
         <v>93</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -41642,7 +41666,7 @@
         <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
@@ -41814,7 +41838,7 @@
         <v>487</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
@@ -41900,7 +41924,7 @@
         <v>101</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
@@ -41943,7 +41967,7 @@
         <v>102</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
@@ -41986,7 +42010,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
@@ -42029,7 +42053,7 @@
         <v>431</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
@@ -42072,7 +42096,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
@@ -42115,7 +42139,7 @@
         <v>809</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
@@ -42158,7 +42182,7 @@
         <v>105</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -42201,7 +42225,7 @@
         <v>106</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
@@ -42244,7 +42268,7 @@
         <v>601</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -42287,7 +42311,7 @@
         <v>107</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
@@ -42373,7 +42397,7 @@
         <v>109</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
@@ -42459,7 +42483,7 @@
         <v>111</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
@@ -42502,7 +42526,7 @@
         <v>112</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
@@ -42803,7 +42827,7 @@
         <v>119</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
@@ -43276,7 +43300,7 @@
         <v>130</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
@@ -43663,7 +43687,7 @@
         <v>138</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
@@ -43792,7 +43816,7 @@
         <v>141</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
@@ -44007,7 +44031,7 @@
         <v>146</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
@@ -44394,7 +44418,7 @@
         <v>154</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
@@ -44480,7 +44504,7 @@
         <v>156</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -44606,7 +44630,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C169" s="1">
         <v>46</v>
@@ -44738,7 +44762,7 @@
         <v>161</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -44953,7 +44977,7 @@
         <v>166</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D177" s="1">
         <v>0</v>
@@ -45039,7 +45063,7 @@
         <v>168</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
@@ -45294,7 +45318,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C185" s="1">
         <v>42</v>
@@ -45337,7 +45361,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C186" s="1">
         <v>55</v>
@@ -45426,7 +45450,7 @@
         <v>175</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D188" s="1">
         <v>0</v>
@@ -45598,7 +45622,7 @@
         <v>484</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D192" s="1">
         <v>0</v>
@@ -45641,7 +45665,7 @@
         <v>179</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D193" s="1">
         <v>0</v>
@@ -45813,7 +45837,7 @@
         <v>182</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D197" s="1">
         <v>0</v>
@@ -45856,7 +45880,7 @@
         <v>481</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D198" s="1">
         <v>0</v>
@@ -45899,7 +45923,7 @@
         <v>183</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D199" s="1">
         <v>0</v>
@@ -45985,7 +46009,7 @@
         <v>185</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D201" s="1">
         <v>0</v>
@@ -46028,7 +46052,7 @@
         <v>742</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D202" s="1">
         <v>0</v>
@@ -46114,7 +46138,7 @@
         <v>188</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D204" s="1">
         <v>0</v>
@@ -46372,7 +46396,7 @@
         <v>483</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D210" s="1">
         <v>0</v>
@@ -46415,7 +46439,7 @@
         <v>194</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D211" s="1">
         <v>0</v>
@@ -47103,7 +47127,7 @@
         <v>209</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D227" s="1">
         <v>0</v>
@@ -47189,7 +47213,7 @@
         <v>485</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D229" s="1">
         <v>0</v>
@@ -47232,7 +47256,7 @@
         <v>211</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D230" s="1">
         <v>0</v>
@@ -47404,7 +47428,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D234" s="1">
         <v>0</v>
@@ -47533,7 +47557,7 @@
         <v>744</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D237" s="1">
         <v>0</v>
@@ -47705,7 +47729,7 @@
         <v>221</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D241" s="1">
         <v>0</v>
@@ -48135,7 +48159,7 @@
         <v>231</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1628</v>
+        <v>1612</v>
       </c>
       <c r="D251" s="1">
         <v>0</v>
@@ -48400,40 +48424,40 @@
         <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1432</v>
+        <v>1421</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1433</v>
+        <v>1422</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1435</v>
+        <v>1424</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1436</v>
+        <v>1425</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>1431</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1428</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1430</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -50119,7 +50143,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C41" s="1">
         <v>59</v>
@@ -55623,7 +55647,7 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C169" s="1">
         <v>53</v>
@@ -56311,7 +56335,7 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C185" s="1">
         <v>50</v>
@@ -56354,7 +56378,7 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C186" s="1">
         <v>41</v>
@@ -59408,19 +59432,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1490</v>
+        <v>1474</v>
       </c>
       <c r="B1" t="s">
-        <v>1600</v>
+        <v>1584</v>
       </c>
       <c r="C1" t="s">
-        <v>1601</v>
+        <v>1585</v>
       </c>
       <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>1602</v>
+        <v>1586</v>
       </c>
       <c r="B2" s="1">
         <v>938</v>
@@ -59432,7 +59456,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1603</v>
+        <v>1587</v>
       </c>
       <c r="B3" s="1">
         <v>935</v>
@@ -59444,7 +59468,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1604</v>
+        <v>1588</v>
       </c>
       <c r="B4" s="1">
         <v>932</v>
@@ -59456,7 +59480,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1605</v>
+        <v>1589</v>
       </c>
       <c r="B5" s="1">
         <v>672</v>
@@ -59468,7 +59492,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="B6" s="1">
         <v>757</v>
@@ -59480,7 +59504,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1607</v>
+        <v>1591</v>
       </c>
       <c r="B7" s="1">
         <v>343</v>
@@ -59492,7 +59516,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1608</v>
+        <v>1592</v>
       </c>
       <c r="B8" s="1">
         <v>899</v>
@@ -59504,7 +59528,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1609</v>
+        <v>1593</v>
       </c>
       <c r="B9" s="1">
         <v>822</v>
@@ -59516,7 +59540,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>1610</v>
+        <v>1594</v>
       </c>
       <c r="B10" s="1">
         <v>953</v>
@@ -59528,7 +59552,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B11" s="1">
         <v>909</v>
@@ -59540,7 +59564,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1613</v>
+        <v>1597</v>
       </c>
       <c r="B12" s="1">
         <v>853</v>
@@ -59552,7 +59576,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="B13" s="1">
         <v>987</v>
@@ -59564,7 +59588,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="B14" s="1">
         <v>802</v>
@@ -59576,7 +59600,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>1615</v>
+        <v>1599</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -59588,19 +59612,19 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1498</v>
+        <v>1482</v>
       </c>
       <c r="B17" t="s">
-        <v>1600</v>
+        <v>1584</v>
       </c>
       <c r="C17" t="s">
-        <v>1601</v>
+        <v>1585</v>
       </c>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>1602</v>
+        <v>1586</v>
       </c>
       <c r="B18" s="1">
         <v>976</v>
@@ -59612,7 +59636,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>1603</v>
+        <v>1587</v>
       </c>
       <c r="B19" s="1">
         <v>956</v>
@@ -59624,7 +59648,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>1604</v>
+        <v>1588</v>
       </c>
       <c r="B20" s="1">
         <v>808</v>
@@ -59636,7 +59660,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>1605</v>
+        <v>1589</v>
       </c>
       <c r="B21" s="1">
         <v>696</v>
@@ -59648,7 +59672,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="B22" s="1">
         <v>506</v>
@@ -59660,7 +59684,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>1607</v>
+        <v>1591</v>
       </c>
       <c r="B23" s="1">
         <v>274</v>
@@ -59672,7 +59696,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1608</v>
+        <v>1592</v>
       </c>
       <c r="B24" s="1">
         <v>977</v>
@@ -59684,7 +59708,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1609</v>
+        <v>1593</v>
       </c>
       <c r="B25" s="1">
         <v>371</v>
@@ -59696,7 +59720,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1610</v>
+        <v>1594</v>
       </c>
       <c r="B26" s="1">
         <v>916</v>
@@ -59708,7 +59732,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B27" s="1">
         <v>976</v>
@@ -59720,7 +59744,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>1612</v>
+        <v>1596</v>
       </c>
       <c r="B28" s="1">
         <v>959</v>
@@ -59732,7 +59756,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>1613</v>
+        <v>1597</v>
       </c>
       <c r="B29" s="1">
         <v>783</v>
@@ -59744,7 +59768,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="B30" s="1">
         <v>802</v>
@@ -59756,7 +59780,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>1615</v>
+        <v>1599</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
@@ -59768,18 +59792,18 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1501</v>
+        <v>1485</v>
       </c>
       <c r="B33" t="s">
-        <v>1600</v>
+        <v>1584</v>
       </c>
       <c r="C33" t="s">
-        <v>1601</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1602</v>
+        <v>1586</v>
       </c>
       <c r="B34" s="1">
         <v>1041</v>
@@ -59791,7 +59815,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1603</v>
+        <v>1587</v>
       </c>
       <c r="B35" s="1">
         <v>979</v>
@@ -59803,7 +59827,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1604</v>
+        <v>1588</v>
       </c>
       <c r="B36" s="1">
         <v>690</v>
@@ -59815,7 +59839,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1605</v>
+        <v>1589</v>
       </c>
       <c r="B37" s="1">
         <v>745</v>
@@ -59827,7 +59851,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="B38" s="1">
         <v>519</v>
@@ -59839,7 +59863,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1607</v>
+        <v>1591</v>
       </c>
       <c r="B39" s="1">
         <v>291</v>
@@ -59851,7 +59875,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1608</v>
+        <v>1592</v>
       </c>
       <c r="B40" s="1">
         <v>962</v>
@@ -59863,7 +59887,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1609</v>
+        <v>1593</v>
       </c>
       <c r="B41" s="1">
         <v>77</v>
@@ -59875,7 +59899,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1610</v>
+        <v>1594</v>
       </c>
       <c r="B42" s="1">
         <v>964</v>
@@ -59887,7 +59911,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B43" s="1">
         <v>1038</v>
@@ -59899,7 +59923,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1612</v>
+        <v>1596</v>
       </c>
       <c r="B44" s="1">
         <v>980</v>
@@ -59911,7 +59935,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1613</v>
+        <v>1597</v>
       </c>
       <c r="B45" s="1">
         <v>782</v>
@@ -59923,7 +59947,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="B46" s="1">
         <v>932</v>
@@ -59935,7 +59959,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1615</v>
+        <v>1599</v>
       </c>
       <c r="B47" s="1">
         <v>0</v>
@@ -59969,155 +59993,155 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1">
       <c r="A1" s="7" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1481</v>
+        <v>1465</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1482</v>
+        <v>1466</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1483</v>
+        <v>1467</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1484</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>1485</v>
+        <v>1469</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1486</v>
+        <v>1470</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1487</v>
+        <v>1471</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1488</v>
+        <v>1472</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1489</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>1490</v>
+        <v>1474</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1491</v>
+        <v>1475</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1492</v>
+        <v>1476</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1493</v>
+        <v>1477</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1489</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>1494</v>
+        <v>1478</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1495</v>
+        <v>1479</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1496</v>
+        <v>1480</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1497</v>
+        <v>1481</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1489</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>1498</v>
+        <v>1482</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1499</v>
+        <v>1483</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1500</v>
+        <v>1484</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1497</v>
+        <v>1481</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1489</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>1501</v>
+        <v>1485</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1502</v>
+        <v>1486</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1503</v>
+        <v>1487</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1504</v>
+        <v>1488</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1505</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>1506</v>
+        <v>1490</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1507</v>
+        <v>1491</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1508</v>
+        <v>1492</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1509</v>
+        <v>1493</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1510</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1512</v>
+        <v>1496</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1513</v>
+        <v>1497</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1514</v>
+        <v>1498</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1515</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>1516</v>
+        <v>1500</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1517</v>
+        <v>1501</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1518</v>
+        <v>1502</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1519</v>
+        <v>1503</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1489</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1"/>
@@ -60126,280 +60150,280 @@
         <v>312</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1520</v>
+        <v>1504</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>1521</v>
+        <v>1505</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1522</v>
+        <v>1506</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>1523</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29.25" thickBot="1">
       <c r="A12" s="9" t="s">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1525</v>
+        <v>1509</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1526</v>
+        <v>1510</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1527</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="29.25" thickBot="1">
       <c r="A13" s="9" t="s">
-        <v>1528</v>
+        <v>1512</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1529</v>
+        <v>1513</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1530</v>
+        <v>1514</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1531</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="43.5" thickBot="1">
       <c r="A14" s="9" t="s">
-        <v>1532</v>
+        <v>1516</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1533</v>
+        <v>1517</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1534</v>
+        <v>1518</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1535</v>
+        <v>1519</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>1536</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.5" thickBot="1">
       <c r="A15" s="9" t="s">
-        <v>1537</v>
+        <v>1521</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1538</v>
+        <v>1522</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1534</v>
+        <v>1518</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1539</v>
+        <v>1523</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1540</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.5" thickBot="1">
       <c r="A16" s="9" t="s">
-        <v>1541</v>
+        <v>1525</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1542</v>
+        <v>1526</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1543</v>
+        <v>1527</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1544</v>
+        <v>1528</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1545</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.5" thickBot="1">
       <c r="A17" s="9" t="s">
-        <v>1546</v>
+        <v>1530</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1547</v>
+        <v>1531</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1543</v>
+        <v>1527</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1548</v>
+        <v>1532</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1549</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="29.25" thickBot="1">
       <c r="A18" s="9" t="s">
-        <v>1550</v>
+        <v>1534</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1551</v>
+        <v>1535</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1552</v>
+        <v>1536</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1553</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="29.25" thickBot="1">
       <c r="A19" s="9" t="s">
-        <v>1554</v>
+        <v>1538</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1555</v>
+        <v>1539</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1543</v>
+        <v>1527</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1556</v>
+        <v>1540</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1531</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="43.5" thickBot="1">
       <c r="A20" s="9" t="s">
-        <v>1557</v>
+        <v>1541</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1558</v>
+        <v>1542</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1534</v>
+        <v>1518</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1559</v>
+        <v>1543</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1560</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="43.5" thickBot="1">
       <c r="A21" s="9" t="s">
-        <v>1561</v>
+        <v>1545</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1562</v>
+        <v>1546</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1563</v>
+        <v>1547</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1564</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="29.25" thickBot="1">
       <c r="A22" s="9" t="s">
-        <v>1565</v>
+        <v>1549</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1566</v>
+        <v>1550</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1567</v>
+        <v>1551</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>1568</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.5" thickBot="1">
       <c r="A23" s="9" t="s">
-        <v>1569</v>
+        <v>1553</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1570</v>
+        <v>1554</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1534</v>
+        <v>1518</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1571</v>
+        <v>1555</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>1572</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="43.5" thickBot="1">
       <c r="A24" s="9" t="s">
-        <v>1573</v>
+        <v>1557</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1574</v>
+        <v>1558</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1575</v>
+        <v>1559</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1576</v>
+        <v>1560</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>1577</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.25" thickBot="1">
       <c r="A25" s="9" t="s">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1579</v>
+        <v>1563</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1580</v>
+        <v>1564</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>1581</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1"/>
     <row r="27" spans="1:5" ht="60.75" thickBot="1">
       <c r="A27" s="9" t="s">
-        <v>1582</v>
+        <v>1566</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1583</v>
+        <v>1567</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1584</v>
+        <v>1568</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1585</v>
+        <v>1569</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>1586</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="102" thickBot="1">
       <c r="A28" s="9" t="s">
-        <v>1587</v>
+        <v>1571</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1588</v>
+        <v>1572</v>
       </c>
       <c r="C28" s="10">
         <v>0</v>
@@ -60408,58 +60432,58 @@
         <v>0</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="116.25" thickBot="1">
       <c r="A29" s="9" t="s">
-        <v>1590</v>
+        <v>1574</v>
       </c>
       <c r="B29" s="11">
         <v>0.4</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1591</v>
+        <v>1575</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1591</v>
+        <v>1575</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>1592</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="116.25" thickBot="1">
       <c r="A30" s="9" t="s">
-        <v>1593</v>
+        <v>1577</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1594</v>
+        <v>1578</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1595</v>
+        <v>1579</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>1596</v>
+        <v>1580</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>1592</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="116.25" thickBot="1">
       <c r="A31" s="9" t="s">
-        <v>1597</v>
+        <v>1581</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1594</v>
+        <v>1578</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1598</v>
+        <v>1582</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>1596</v>
+        <v>1580</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
     </row>
   </sheetData>
